--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2763519287109</t>
+    <t xml:space="preserve">18.2763500213623</t>
   </si>
   <si>
     <t xml:space="preserve">SFER.MI</t>
@@ -47,34 +47,34 @@
     <t xml:space="preserve">18.0109634399414</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4978847503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9401912689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6836528778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2498111724854</t>
+    <t xml:space="preserve">17.4978828430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9401950836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6836547851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2498149871826</t>
   </si>
   <si>
     <t xml:space="preserve">19.4086723327637</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1344356536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8425102233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4621238708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2851982116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0994243621826</t>
+    <t xml:space="preserve">19.1344375610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8425140380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.462121963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2852001190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0994281768799</t>
   </si>
   <si>
     <t xml:space="preserve">17.6394214630127</t>
@@ -92,61 +92,61 @@
     <t xml:space="preserve">18.223274230957</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7632713317871</t>
+    <t xml:space="preserve">17.7632675170898</t>
   </si>
   <si>
     <t xml:space="preserve">18.3913536071777</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6744346618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9578838348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2055816650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.258659362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0817337036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3563404083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9051837921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1617240905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6486434936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0201854705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.48903465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6305770874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4090461730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4532775878906</t>
+    <t xml:space="preserve">18.6744327545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9578857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2055835723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2586555480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0817356109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3563423156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9051818847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1617221832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6486415863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0201816558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4890365600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6305732727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4090423583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.453275680542</t>
   </si>
   <si>
     <t xml:space="preserve">18.9752063751221</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1348114013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3121109008789</t>
+    <t xml:space="preserve">18.1348152160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3121089935303</t>
   </si>
   <si>
     <t xml:space="preserve">17.9048080444336</t>
@@ -155,10 +155,10 @@
     <t xml:space="preserve">18.3471202850342</t>
   </si>
   <si>
-    <t xml:space="preserve">19.019437789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0017414093018</t>
+    <t xml:space="preserve">19.0194358825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0017433166504</t>
   </si>
   <si>
     <t xml:space="preserve">18.8513584136963</t>
@@ -167,19 +167,19 @@
     <t xml:space="preserve">19.3113613128662</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9925212860107</t>
+    <t xml:space="preserve">19.9925231933594</t>
   </si>
   <si>
     <t xml:space="preserve">19.9482917785645</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7271327972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3379001617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.647518157959</t>
+    <t xml:space="preserve">19.7271366119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3379020690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6475200653076</t>
   </si>
   <si>
     <t xml:space="preserve">19.983678817749</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">19.1167449951172</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4440536499023</t>
+    <t xml:space="preserve">19.444055557251</t>
   </si>
   <si>
     <t xml:space="preserve">20.0367546081543</t>
@@ -197,52 +197,52 @@
     <t xml:space="preserve">20.1782932281494</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4971313476562</t>
+    <t xml:space="preserve">19.4971351623535</t>
   </si>
   <si>
     <t xml:space="preserve">19.4705944061279</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9663581848145</t>
+    <t xml:space="preserve">18.9663619995117</t>
   </si>
   <si>
     <t xml:space="preserve">19.4794425964355</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9129066467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8686752319336</t>
+    <t xml:space="preserve">19.9129047393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8686771392822</t>
   </si>
   <si>
     <t xml:space="preserve">19.4175186157227</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8690509796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8336658477783</t>
+    <t xml:space="preserve">18.8690528869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.833667755127</t>
   </si>
   <si>
     <t xml:space="preserve">18.5151996612549</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9309730529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8955879211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5240478515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9486656188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7982788085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8778991699219</t>
+    <t xml:space="preserve">18.9309711456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8955898284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5240459442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9486675262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7982807159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8778972625732</t>
   </si>
   <si>
     <t xml:space="preserve">19.2936706542969</t>
@@ -254,25 +254,25 @@
     <t xml:space="preserve">18.3205814361572</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3648147583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8251914978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0640392303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3117408752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8782711029053</t>
+    <t xml:space="preserve">18.3648128509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8251934051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0640411376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3117370605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.878267288208</t>
   </si>
   <si>
     <t xml:space="preserve">18.0021190643311</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7190380096436</t>
+    <t xml:space="preserve">17.7190361022949</t>
   </si>
   <si>
     <t xml:space="preserve">17.4448051452637</t>
@@ -281,16 +281,16 @@
     <t xml:space="preserve">17.1440296173096</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5509586334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9844245910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4182643890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9313488006592</t>
+    <t xml:space="preserve">17.5509605407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9844264984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4182682037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9313468933105</t>
   </si>
   <si>
     <t xml:space="preserve">17.7367286682129</t>
@@ -299,19 +299,19 @@
     <t xml:space="preserve">17.648265838623</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5939388275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8112602233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7025985717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6482696533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.530553817749</t>
+    <t xml:space="preserve">17.593936920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8112564086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7025947570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6482677459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5305557250977</t>
   </si>
   <si>
     <t xml:space="preserve">17.4128360748291</t>
@@ -320,13 +320,13 @@
     <t xml:space="preserve">17.3041763305664</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4762229919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.430944442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4852752685547</t>
+    <t xml:space="preserve">17.4762210845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4309463500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.485279083252</t>
   </si>
   <si>
     <t xml:space="preserve">17.7478733062744</t>
@@ -338,37 +338,37 @@
     <t xml:space="preserve">17.1502418518066</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7155952453613</t>
+    <t xml:space="preserve">16.71559715271</t>
   </si>
   <si>
     <t xml:space="preserve">16.5435523986816</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0415821075439</t>
+    <t xml:space="preserve">17.0415802001953</t>
   </si>
   <si>
     <t xml:space="preserve">17.0778026580811</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8384246826172</t>
+    <t xml:space="preserve">17.8384227752686</t>
   </si>
   <si>
     <t xml:space="preserve">17.9380283355713</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7297630310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8655891418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1825160980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8514251708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3896160125732</t>
+    <t xml:space="preserve">17.7297611236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8655872344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1825141906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8514232635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3896179199219</t>
   </si>
   <si>
     <t xml:space="preserve">16.6793785095215</t>
@@ -377,31 +377,31 @@
     <t xml:space="preserve">16.262845993042</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5254402160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6069355010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8061485290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8242568969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0726909637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8734798431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3624496459961</t>
+    <t xml:space="preserve">16.5254421234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6069393157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8061466217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8242588043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0726890563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.873480796814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3624534606934</t>
   </si>
   <si>
     <t xml:space="preserve">16.4439468383789</t>
   </si>
   <si>
-    <t xml:space="preserve">16.69748878479</t>
+    <t xml:space="preserve">16.6974906921387</t>
   </si>
   <si>
     <t xml:space="preserve">17.095911026001</t>
@@ -410,7 +410,7 @@
     <t xml:space="preserve">17.1321315765381</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0868549346924</t>
+    <t xml:space="preserve">17.086856842041</t>
   </si>
   <si>
     <t xml:space="preserve">17.0325241088867</t>
@@ -419,25 +419,25 @@
     <t xml:space="preserve">17.3403968811035</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9018077850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1372413635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9289722442627</t>
+    <t xml:space="preserve">17.9018096923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1372375488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9289703369141</t>
   </si>
   <si>
     <t xml:space="preserve">18.7710914611816</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6352691650391</t>
+    <t xml:space="preserve">18.6352672576904</t>
   </si>
   <si>
     <t xml:space="preserve">19.0699081420898</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2147884368896</t>
+    <t xml:space="preserve">19.214786529541</t>
   </si>
   <si>
     <t xml:space="preserve">18.6262111663818</t>
@@ -455,13 +455,13 @@
     <t xml:space="preserve">18.5809364318848</t>
   </si>
   <si>
-    <t xml:space="preserve">18.762035369873</t>
+    <t xml:space="preserve">18.7620334625244</t>
   </si>
   <si>
     <t xml:space="preserve">18.8073120117188</t>
   </si>
   <si>
-    <t xml:space="preserve">18.94313621521</t>
+    <t xml:space="preserve">18.9431381225586</t>
   </si>
   <si>
     <t xml:space="preserve">19.0427436828613</t>
@@ -473,34 +473,34 @@
     <t xml:space="preserve">18.4722766876221</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6171569824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7529811859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9703025817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6805400848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6081027984619</t>
+    <t xml:space="preserve">18.6171550750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7529792785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9703044891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6805419921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6081008911133</t>
   </si>
   <si>
     <t xml:space="preserve">18.653377532959</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5175533294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.870698928833</t>
+    <t xml:space="preserve">18.5175514221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8706970214844</t>
   </si>
   <si>
     <t xml:space="preserve">18.6986522674561</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1061267852783</t>
+    <t xml:space="preserve">19.106128692627</t>
   </si>
   <si>
     <t xml:space="preserve">19.9210815429688</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">19.4592742919922</t>
   </si>
   <si>
-    <t xml:space="preserve">19.314395904541</t>
+    <t xml:space="preserve">19.3143978118896</t>
   </si>
   <si>
     <t xml:space="preserve">18.8888072967529</t>
@@ -524,13 +524,13 @@
     <t xml:space="preserve">19.1332931518555</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1604557037354</t>
+    <t xml:space="preserve">19.1604595184326</t>
   </si>
   <si>
     <t xml:space="preserve">19.9391937255859</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4553279876709</t>
+    <t xml:space="preserve">20.4553298950195</t>
   </si>
   <si>
     <t xml:space="preserve">20.3557224273682</t>
@@ -539,76 +539,76 @@
     <t xml:space="preserve">20.3104496002197</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3919448852539</t>
+    <t xml:space="preserve">20.3919429779053</t>
   </si>
   <si>
     <t xml:space="preserve">20.4643840789795</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6907615661621</t>
+    <t xml:space="preserve">20.6907596588135</t>
   </si>
   <si>
     <t xml:space="preserve">20.8446960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7994213104248</t>
+    <t xml:space="preserve">20.7994194030762</t>
   </si>
   <si>
     <t xml:space="preserve">20.4009990692139</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1021842956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5277709960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3647785186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5458793640137</t>
+    <t xml:space="preserve">20.1021862030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5277690887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3647766113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.545877456665</t>
   </si>
   <si>
     <t xml:space="preserve">20.7541446685791</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4191093444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0116310119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.265172958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3285598754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0387954711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1474590301514</t>
+    <t xml:space="preserve">20.4191074371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0116348266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2651748657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3285579681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.03879737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1474609375</t>
   </si>
   <si>
     <t xml:space="preserve">20.2289524078369</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5006065368652</t>
+    <t xml:space="preserve">20.5006046295166</t>
   </si>
   <si>
     <t xml:space="preserve">20.5639877319336</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1836795806885</t>
+    <t xml:space="preserve">20.1836814880371</t>
   </si>
   <si>
     <t xml:space="preserve">19.549825668335</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4139995574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5045490264893</t>
+    <t xml:space="preserve">19.4140014648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5045509338379</t>
   </si>
   <si>
     <t xml:space="preserve">19.7218723297119</t>
@@ -617,10 +617,10 @@
     <t xml:space="preserve">19.7943115234375</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5226593017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8305320739746</t>
+    <t xml:space="preserve">19.5226573944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.830530166626</t>
   </si>
   <si>
     <t xml:space="preserve">19.9120273590088</t>
@@ -629,46 +629,46 @@
     <t xml:space="preserve">19.7490367889404</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0919647216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3002300262451</t>
+    <t xml:space="preserve">18.0919628143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3002281188965</t>
   </si>
   <si>
     <t xml:space="preserve">18.3273944854736</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2458992004395</t>
+    <t xml:space="preserve">18.2459011077881</t>
   </si>
   <si>
     <t xml:space="preserve">18.0104675292969</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7388191223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8565349578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6392135620117</t>
+    <t xml:space="preserve">17.7388172149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8565330505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8203144073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6392116546631</t>
   </si>
   <si>
     <t xml:space="preserve">18.3455066680908</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3907794952393</t>
+    <t xml:space="preserve">18.3907814025879</t>
   </si>
   <si>
     <t xml:space="preserve">19.1514053344727</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2872276306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3958892822266</t>
+    <t xml:space="preserve">19.2872314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3958911895752</t>
   </si>
   <si>
     <t xml:space="preserve">19.377779006958</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">19.2600650787354</t>
   </si>
   <si>
-    <t xml:space="preserve">20.373836517334</t>
+    <t xml:space="preserve">20.3738327026367</t>
   </si>
   <si>
     <t xml:space="preserve">20.3466682434082</t>
@@ -695,19 +695,19 @@
     <t xml:space="preserve">20.1293487548828</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1565132141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8084754943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6183185577393</t>
+    <t xml:space="preserve">20.15651512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8084735870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6183204650879</t>
   </si>
   <si>
     <t xml:space="preserve">21.4785499572754</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5328788757324</t>
+    <t xml:space="preserve">21.5328807830811</t>
   </si>
   <si>
     <t xml:space="preserve">22.0671272277832</t>
@@ -734,28 +734,28 @@
     <t xml:space="preserve">22.2391700744629</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8186931610107</t>
+    <t xml:space="preserve">22.8186950683594</t>
   </si>
   <si>
     <t xml:space="preserve">23.0722351074219</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8911361694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1537303924561</t>
+    <t xml:space="preserve">22.891134262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1537322998047</t>
   </si>
   <si>
     <t xml:space="preserve">23.099401473999</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5923175811768</t>
+    <t xml:space="preserve">22.5923156738281</t>
   </si>
   <si>
     <t xml:space="preserve">22.3568859100342</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9092426300049</t>
+    <t xml:space="preserve">22.9092445373535</t>
   </si>
   <si>
     <t xml:space="preserve">22.1757850646973</t>
@@ -764,19 +764,19 @@
     <t xml:space="preserve">22.1395645141602</t>
   </si>
   <si>
-    <t xml:space="preserve">23.606481552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7513618469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1226215362549</t>
+    <t xml:space="preserve">23.6064834594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7513637542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1226177215576</t>
   </si>
   <si>
     <t xml:space="preserve">23.6427040100098</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6879787445068</t>
+    <t xml:space="preserve">23.6879768371582</t>
   </si>
   <si>
     <t xml:space="preserve">23.5612087249756</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">23.7423095703125</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7242012023926</t>
+    <t xml:space="preserve">23.7241992950439</t>
   </si>
   <si>
     <t xml:space="preserve">23.6336479187012</t>
@@ -797,31 +797,31 @@
     <t xml:space="preserve">23.6970329284668</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0139617919922</t>
+    <t xml:space="preserve">24.0139598846436</t>
   </si>
   <si>
     <t xml:space="preserve">24.2856101989746</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0682907104492</t>
+    <t xml:space="preserve">24.068286895752</t>
   </si>
   <si>
     <t xml:space="preserve">23.9777393341064</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2946662902832</t>
+    <t xml:space="preserve">24.2946643829346</t>
   </si>
   <si>
     <t xml:space="preserve">24.4304904937744</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6115913391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7655239105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1911125183105</t>
+    <t xml:space="preserve">24.61159324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7655296325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1911144256592</t>
   </si>
   <si>
     <t xml:space="preserve">25.3903255462646</t>
@@ -833,31 +833,31 @@
     <t xml:space="preserve">25.6167011260986</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6710300445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6529197692871</t>
+    <t xml:space="preserve">25.6710319519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6529216766357</t>
   </si>
   <si>
     <t xml:space="preserve">25.7615814208984</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5352077484131</t>
+    <t xml:space="preserve">25.5352058410645</t>
   </si>
   <si>
     <t xml:space="preserve">24.955680847168</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9013519287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0643405914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8017482757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6206474304199</t>
+    <t xml:space="preserve">24.9013500213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0643424987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8017463684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6206493377686</t>
   </si>
   <si>
     <t xml:space="preserve">24.9375743865967</t>
@@ -869,22 +869,22 @@
     <t xml:space="preserve">25.6257553100586</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2273330688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1730003356934</t>
+    <t xml:space="preserve">25.2273349761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1730041503906</t>
   </si>
   <si>
     <t xml:space="preserve">25.163948059082</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3993797302246</t>
+    <t xml:space="preserve">25.399377822876</t>
   </si>
   <si>
     <t xml:space="preserve">25.7253589630127</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2907199859619</t>
+    <t xml:space="preserve">25.2907180786133</t>
   </si>
   <si>
     <t xml:space="preserve">25.1277294158936</t>
@@ -893,49 +893,49 @@
     <t xml:space="preserve">25.7434711456299</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5442562103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4808731079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5080394744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2635517120361</t>
+    <t xml:space="preserve">25.5442581176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4808750152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5080413818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2635536193848</t>
   </si>
   <si>
     <t xml:space="preserve">25.0824527740479</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7836360931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4214363098145</t>
+    <t xml:space="preserve">24.7836380004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4214344024658</t>
   </si>
   <si>
     <t xml:space="preserve">24.2674980163574</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5261497497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1237831115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1871700286865</t>
+    <t xml:space="preserve">25.5261535644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1237850189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1871662139893</t>
   </si>
   <si>
     <t xml:space="preserve">26.6308650970459</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4859848022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3229923248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.676139831543</t>
+    <t xml:space="preserve">26.4859828948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3229904174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6761379241943</t>
   </si>
   <si>
     <t xml:space="preserve">26.893461227417</t>
@@ -944,46 +944,46 @@
     <t xml:space="preserve">26.2596092224121</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6670875549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9115715026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6036968231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5946483612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3088302612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3269367218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8340225219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8984413146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0641078948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7112007141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6159934997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2202491760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1282119750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9625511169434</t>
+    <t xml:space="preserve">26.667085647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9115695953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6036987304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5946464538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3088321685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3269386291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.834020614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8984451293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0641059875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7112045288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6159954071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2202472686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.128210067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9625492095947</t>
   </si>
   <si>
     <t xml:space="preserve">22.8705177307129</t>
@@ -992,16 +992,16 @@
     <t xml:space="preserve">22.8613128662109</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2662658691406</t>
+    <t xml:space="preserve">23.266263961792</t>
   </si>
   <si>
     <t xml:space="preserve">23.2386531829834</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0453834533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8889236450195</t>
+    <t xml:space="preserve">23.0453815460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8889217376709</t>
   </si>
   <si>
     <t xml:space="preserve">22.0882263183594</t>
@@ -1025,28 +1025,28 @@
     <t xml:space="preserve">22.95334815979</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8797225952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2846698760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4871463775635</t>
+    <t xml:space="preserve">22.8797206878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2846717834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4871482849121</t>
   </si>
   <si>
     <t xml:space="preserve">23.4319248199463</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8060932159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0269756317139</t>
+    <t xml:space="preserve">22.806095123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0269737243652</t>
   </si>
   <si>
     <t xml:space="preserve">22.6036167144775</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2538871765137</t>
+    <t xml:space="preserve">22.253885269165</t>
   </si>
   <si>
     <t xml:space="preserve">21.545223236084</t>
@@ -1058,40 +1058,40 @@
     <t xml:space="preserve">21.7200889587402</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5544281005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6740703582764</t>
+    <t xml:space="preserve">21.5544261932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6740684509277</t>
   </si>
   <si>
     <t xml:space="preserve">21.6280536651611</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1678848266602</t>
+    <t xml:space="preserve">21.1678829193115</t>
   </si>
   <si>
     <t xml:space="preserve">21.2046966552734</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1218681335449</t>
+    <t xml:space="preserve">21.1218662261963</t>
   </si>
   <si>
     <t xml:space="preserve">21.416374206543</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5084114074707</t>
+    <t xml:space="preserve">21.5084075927734</t>
   </si>
   <si>
     <t xml:space="preserve">21.9133605957031</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8857498168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9685821533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6220226287842</t>
+    <t xml:space="preserve">21.8857517242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9685840606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6220245361328</t>
   </si>
   <si>
     <t xml:space="preserve">22.3735313415527</t>
@@ -1100,7 +1100,7 @@
     <t xml:space="preserve">22.2170734405518</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4103469848633</t>
+    <t xml:space="preserve">22.4103488922119</t>
   </si>
   <si>
     <t xml:space="preserve">22.5299911499023</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">22.6312274932861</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6404342651367</t>
+    <t xml:space="preserve">22.6404323577881</t>
   </si>
   <si>
     <t xml:space="preserve">22.5576000213623</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">21.6556644439697</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2630920410156</t>
+    <t xml:space="preserve">22.263090133667</t>
   </si>
   <si>
     <t xml:space="preserve">22.5391941070557</t>
@@ -1130,34 +1130,34 @@
     <t xml:space="preserve">22.3551254272461</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0514106750488</t>
+    <t xml:space="preserve">22.0514125823975</t>
   </si>
   <si>
     <t xml:space="preserve">22.7876873016357</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3367176055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.115837097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7661037445068</t>
+    <t xml:space="preserve">22.3367195129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1158332824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7661056518555</t>
   </si>
   <si>
     <t xml:space="preserve">22.0606155395508</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7569007873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9961891174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7016830444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0053939819336</t>
+    <t xml:space="preserve">21.7569026947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9961929321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.701681137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0053958892822</t>
   </si>
   <si>
     <t xml:space="preserve">21.8765468597412</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">22.1250400543213</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7753067016602</t>
+    <t xml:space="preserve">21.7753086090088</t>
   </si>
   <si>
     <t xml:space="preserve">22.0238037109375</t>
@@ -1175,49 +1175,49 @@
     <t xml:space="preserve">21.9041576385498</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6832733154297</t>
+    <t xml:space="preserve">21.6832752227783</t>
   </si>
   <si>
     <t xml:space="preserve">20.8273544311523</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0574417114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.94700050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.799747467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.103458404541</t>
+    <t xml:space="preserve">21.0574436187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9470024108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7997455596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1034603118896</t>
   </si>
   <si>
     <t xml:space="preserve">21.0758476257324</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3243427276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9501762390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0974273681641</t>
+    <t xml:space="preserve">21.3243408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.950174331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0974292755127</t>
   </si>
   <si>
     <t xml:space="preserve">21.8581409454346</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6372566223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2967281341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.974609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.983814239502</t>
+    <t xml:space="preserve">21.6372585296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2967319488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9746112823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9838161468506</t>
   </si>
   <si>
     <t xml:space="preserve">21.1402721405029</t>
@@ -1232,34 +1232,34 @@
     <t xml:space="preserve">21.0942554473877</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1586780548096</t>
+    <t xml:space="preserve">21.1586799621582</t>
   </si>
   <si>
     <t xml:space="preserve">21.0206279754639</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0022220611572</t>
+    <t xml:space="preserve">21.0022201538086</t>
   </si>
   <si>
     <t xml:space="preserve">20.6340827941895</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4500141143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3855895996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3947925567627</t>
+    <t xml:space="preserve">20.4500179290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.385591506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3947944641113</t>
   </si>
   <si>
     <t xml:space="preserve">20.0082511901855</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9714393615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0634727478027</t>
+    <t xml:space="preserve">19.9714374542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0634708404541</t>
   </si>
   <si>
     <t xml:space="preserve">20.4868297576904</t>
@@ -1268,43 +1268,43 @@
     <t xml:space="preserve">20.7445259094238</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8917827606201</t>
+    <t xml:space="preserve">20.8917808532715</t>
   </si>
   <si>
     <t xml:space="preserve">21.2415103912354</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9285945892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2475395202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1647071838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0910835266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2719783782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6953353881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8057765960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7321491241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1831188201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0450630187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2935562133789</t>
+    <t xml:space="preserve">20.9285926818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2475414276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1647090911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0910816192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2719764709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.695333480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8057746887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7321510314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1831150054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0450668334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2935581207275</t>
   </si>
   <si>
     <t xml:space="preserve">20.4316120147705</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">20.5696601867676</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6616973876953</t>
+    <t xml:space="preserve">20.661693572998</t>
   </si>
   <si>
     <t xml:space="preserve">21.1310691833496</t>
@@ -1322,55 +1322,55 @@
     <t xml:space="preserve">21.0482387542725</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1954917907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4531898498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8089504241943</t>
+    <t xml:space="preserve">21.1954936981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4531879425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8089485168457</t>
   </si>
   <si>
     <t xml:space="preserve">20.6708965301514</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7721366882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4652481079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7965717315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8609981536865</t>
+    <t xml:space="preserve">20.7721347808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4652500152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.796573638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8609943389893</t>
   </si>
   <si>
     <t xml:space="preserve">20.0174541473389</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2199306488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.229133605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5236415863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.652494430542</t>
+    <t xml:space="preserve">20.2199287414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2291316986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5236434936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6524925231934</t>
   </si>
   <si>
     <t xml:space="preserve">20.9101867675781</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2659473419189</t>
+    <t xml:space="preserve">20.2659492492676</t>
   </si>
   <si>
     <t xml:space="preserve">20.4684219360352</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1555023193359</t>
+    <t xml:space="preserve">20.1555042266846</t>
   </si>
   <si>
     <t xml:space="preserve">20.1739139556885</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">21.2599182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3703594207764</t>
+    <t xml:space="preserve">21.3703556060791</t>
   </si>
   <si>
     <t xml:space="preserve">21.5176124572754</t>
@@ -1388,25 +1388,25 @@
     <t xml:space="preserve">20.8549652099609</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9193897247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5052356719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3487777709961</t>
+    <t xml:space="preserve">20.9193916320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5052375793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3487796783447</t>
   </si>
   <si>
     <t xml:space="preserve">20.0266571044922</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7229461669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9162158966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5604572296143</t>
+    <t xml:space="preserve">19.7229442596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9162139892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5604553222656</t>
   </si>
   <si>
     <t xml:space="preserve">20.7169151306152</t>
@@ -1418,10 +1418,10 @@
     <t xml:space="preserve">20.8365592956543</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6004447937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6248779296875</t>
+    <t xml:space="preserve">21.6004428863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6248798370361</t>
   </si>
   <si>
     <t xml:space="preserve">20.2751502990723</t>
@@ -1430,7 +1430,7 @@
     <t xml:space="preserve">20.1094875335693</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6493186950684</t>
+    <t xml:space="preserve">19.6493167877197</t>
   </si>
   <si>
     <t xml:space="preserve">19.9990463256836</t>
@@ -1442,25 +1442,25 @@
     <t xml:space="preserve">20.3303718566895</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8733730316162</t>
+    <t xml:space="preserve">20.8733749389648</t>
   </si>
   <si>
     <t xml:space="preserve">20.3763885498047</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5328483581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3027610778809</t>
+    <t xml:space="preserve">20.5328464508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3027591705322</t>
   </si>
   <si>
     <t xml:space="preserve">20.64328956604</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6156749725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7261161804199</t>
+    <t xml:space="preserve">20.6156768798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7261180877686</t>
   </si>
   <si>
     <t xml:space="preserve">21.2783260345459</t>
@@ -1469,64 +1469,64 @@
     <t xml:space="preserve">21.3151359558105</t>
   </si>
   <si>
-    <t xml:space="preserve">21.536018371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7937183380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.64963722229</t>
+    <t xml:space="preserve">21.5360164642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7937164306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6496353149414</t>
   </si>
   <si>
     <t xml:space="preserve">22.548397064209</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4195499420166</t>
+    <t xml:space="preserve">22.419548034668</t>
   </si>
   <si>
     <t xml:space="preserve">22.2078685760498</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5668029785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6128196716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9165325164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6864490509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7324657440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8337020874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7692794799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9073295593262</t>
+    <t xml:space="preserve">22.5668048858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6128215789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9165344238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6864471435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7324676513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.833703994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7692775726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9073276519775</t>
   </si>
   <si>
     <t xml:space="preserve">23.2754688262939</t>
   </si>
   <si>
-    <t xml:space="preserve">22.991304397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3090705871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4118766784668</t>
+    <t xml:space="preserve">22.9913024902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3090686798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4118747711182</t>
   </si>
   <si>
     <t xml:space="preserve">22.9071884155273</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9819583892822</t>
+    <t xml:space="preserve">22.9819564819336</t>
   </si>
   <si>
     <t xml:space="preserve">22.7296123504639</t>
@@ -1535,7 +1535,7 @@
     <t xml:space="preserve">22.3557720184326</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6174621582031</t>
+    <t xml:space="preserve">22.6174602508545</t>
   </si>
   <si>
     <t xml:space="preserve">23.0754165649414</t>
@@ -1544,52 +1544,52 @@
     <t xml:space="preserve">23.3557987213135</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1969165802002</t>
+    <t xml:space="preserve">23.1969146728516</t>
   </si>
   <si>
     <t xml:space="preserve">23.206262588501</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4586048126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6548461914062</t>
+    <t xml:space="preserve">23.4586067199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6548442840576</t>
   </si>
   <si>
     <t xml:space="preserve">22.7389602661133</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1595325469971</t>
+    <t xml:space="preserve">23.1595344543457</t>
   </si>
   <si>
     <t xml:space="preserve">23.5053367614746</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3838386535645</t>
+    <t xml:space="preserve">23.3838367462158</t>
   </si>
   <si>
     <t xml:space="preserve">23.3931846618652</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2623386383057</t>
+    <t xml:space="preserve">23.262336730957</t>
   </si>
   <si>
     <t xml:space="preserve">22.9258804321289</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9912433624268</t>
+    <t xml:space="preserve">20.9912452697754</t>
   </si>
   <si>
     <t xml:space="preserve">20.3370227813721</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9912166595459</t>
+    <t xml:space="preserve">19.9912185668945</t>
   </si>
   <si>
     <t xml:space="preserve">19.7388763427734</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5612983703613</t>
+    <t xml:space="preserve">19.56130027771</t>
   </si>
   <si>
     <t xml:space="preserve">19.3089561462402</t>
@@ -1601,13 +1601,13 @@
     <t xml:space="preserve">19.4958782196045</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3463401794434</t>
+    <t xml:space="preserve">19.346342086792</t>
   </si>
   <si>
     <t xml:space="preserve">19.0285739898682</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6266937255859</t>
+    <t xml:space="preserve">18.6266918182373</t>
   </si>
   <si>
     <t xml:space="preserve">18.3836975097656</t>
@@ -1619,31 +1619,31 @@
     <t xml:space="preserve">18.6220188140869</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0799503326416</t>
+    <t xml:space="preserve">18.079948425293</t>
   </si>
   <si>
     <t xml:space="preserve">18.603328704834</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6360397338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.794921875</t>
+    <t xml:space="preserve">18.6360416412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7949237823486</t>
   </si>
   <si>
     <t xml:space="preserve">18.7762317657471</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7201557159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.575288772583</t>
+    <t xml:space="preserve">18.7201538085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5752906799316</t>
   </si>
   <si>
     <t xml:space="preserve">18.3930416107178</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5285606384277</t>
+    <t xml:space="preserve">18.5285625457764</t>
   </si>
   <si>
     <t xml:space="preserve">18.495849609375</t>
@@ -1652,16 +1652,16 @@
     <t xml:space="preserve">18.4351005554199</t>
   </si>
   <si>
-    <t xml:space="preserve">18.388370513916</t>
+    <t xml:space="preserve">18.3883686065674</t>
   </si>
   <si>
     <t xml:space="preserve">18.4911766052246</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2435073852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8042392730713</t>
+    <t xml:space="preserve">18.2435054779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8042411804199</t>
   </si>
   <si>
     <t xml:space="preserve">17.7715282440186</t>
@@ -1670,13 +1670,13 @@
     <t xml:space="preserve">18.1079883575439</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6734256744385</t>
+    <t xml:space="preserve">18.6734237670898</t>
   </si>
   <si>
     <t xml:space="preserve">18.7575378417969</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7295036315918</t>
+    <t xml:space="preserve">18.7295017242432</t>
   </si>
   <si>
     <t xml:space="preserve">18.276216506958</t>
@@ -1688,10 +1688,10 @@
     <t xml:space="preserve">18.2107944488525</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3790245056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1407241821289</t>
+    <t xml:space="preserve">18.3790264129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1407260894775</t>
   </si>
   <si>
     <t xml:space="preserve">19.4398002624512</t>
@@ -1700,7 +1700,7 @@
     <t xml:space="preserve">19.402416229248</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4117622375488</t>
+    <t xml:space="preserve">19.4117641448975</t>
   </si>
   <si>
     <t xml:space="preserve">19.4304542541504</t>
@@ -1709,25 +1709,25 @@
     <t xml:space="preserve">19.3650321960449</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1594200134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1687641143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1126899719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0939979553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7388439178467</t>
+    <t xml:space="preserve">19.1594181060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1687660217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1126880645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0939960479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7388458251953</t>
   </si>
   <si>
     <t xml:space="preserve">19.0566120147705</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8416538238525</t>
+    <t xml:space="preserve">18.8416519165039</t>
   </si>
   <si>
     <t xml:space="preserve">19.6080284118652</t>
@@ -1748,31 +1748,31 @@
     <t xml:space="preserve">20.0753307342529</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7482204437256</t>
+    <t xml:space="preserve">19.748218536377</t>
   </si>
   <si>
     <t xml:space="preserve">20.0192546844482</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7669124603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7856063842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5706443786621</t>
+    <t xml:space="preserve">19.7669143676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7856044769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5706462860107</t>
   </si>
   <si>
     <t xml:space="preserve">19.2809162139893</t>
   </si>
   <si>
-    <t xml:space="preserve">19.150074005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8977298736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8042678833008</t>
+    <t xml:space="preserve">19.1500720977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8977279663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8042697906494</t>
   </si>
   <si>
     <t xml:space="preserve">18.8790378570557</t>
@@ -1781,19 +1781,19 @@
     <t xml:space="preserve">18.1780834197998</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6453876495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8556461334229</t>
+    <t xml:space="preserve">18.6453857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8556442260742</t>
   </si>
   <si>
     <t xml:space="preserve">17.2528228759766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1546897888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9817867279053</t>
+    <t xml:space="preserve">17.1546878814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9817886352539</t>
   </si>
   <si>
     <t xml:space="preserve">18.1360263824463</t>
@@ -1802,16 +1802,16 @@
     <t xml:space="preserve">17.949104309082</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1173343658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2154674530029</t>
+    <t xml:space="preserve">18.1173324584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2154693603516</t>
   </si>
   <si>
     <t xml:space="preserve">19.1874580383301</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0098838806152</t>
+    <t xml:space="preserve">19.0098819732666</t>
   </si>
   <si>
     <t xml:space="preserve">19.5986843109131</t>
@@ -1820,28 +1820,28 @@
     <t xml:space="preserve">19.5893363952637</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6454162597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4771862030029</t>
+    <t xml:space="preserve">19.645414352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4771842956543</t>
   </si>
   <si>
     <t xml:space="preserve">19.5426082611084</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5799942016602</t>
+    <t xml:space="preserve">19.5799922943115</t>
   </si>
   <si>
     <t xml:space="preserve">20.0005645751953</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6267223358154</t>
+    <t xml:space="preserve">19.6267204284668</t>
   </si>
   <si>
     <t xml:space="preserve">19.4865303039551</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7014923095703</t>
+    <t xml:space="preserve">19.7014904022217</t>
   </si>
   <si>
     <t xml:space="preserve">19.3930702209473</t>
@@ -1859,10 +1859,10 @@
     <t xml:space="preserve">19.5145683288574</t>
   </si>
   <si>
-    <t xml:space="preserve">19.206148147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0472106933594</t>
+    <t xml:space="preserve">19.2061462402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0472087860107</t>
   </si>
   <si>
     <t xml:space="preserve">16.7107524871826</t>
@@ -1871,7 +1871,7 @@
     <t xml:space="preserve">16.8135585784912</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5845813751221</t>
+    <t xml:space="preserve">16.5845832824707</t>
   </si>
   <si>
     <t xml:space="preserve">16.5471954345703</t>
@@ -1883,25 +1883,25 @@
     <t xml:space="preserve">16.7200965881348</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4957904815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7528076171875</t>
+    <t xml:space="preserve">16.495792388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7528095245361</t>
   </si>
   <si>
     <t xml:space="preserve">16.5004653930664</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4630832672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0425090789795</t>
+    <t xml:space="preserve">16.4630813598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0425109863281</t>
   </si>
   <si>
     <t xml:space="preserve">16.3509292602539</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5425243377686</t>
+    <t xml:space="preserve">16.5425224304199</t>
   </si>
   <si>
     <t xml:space="preserve">16.8415966033936</t>
@@ -1910,13 +1910,13 @@
     <t xml:space="preserve">16.6640205383301</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5331764221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5892524719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6827144622803</t>
+    <t xml:space="preserve">16.5331783294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5892543792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6827125549316</t>
   </si>
   <si>
     <t xml:space="preserve">16.5986022949219</t>
@@ -1925,7 +1925,7 @@
     <t xml:space="preserve">16.4256992340088</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1266212463379</t>
+    <t xml:space="preserve">16.1266231536865</t>
   </si>
   <si>
     <t xml:space="preserve">16.1593341827393</t>
@@ -1952,7 +1952,7 @@
     <t xml:space="preserve">16.2995262145996</t>
   </si>
   <si>
-    <t xml:space="preserve">16.579906463623</t>
+    <t xml:space="preserve">16.5799083709717</t>
   </si>
   <si>
     <t xml:space="preserve">17.1874008178711</t>
@@ -1967,7 +1967,7 @@
     <t xml:space="preserve">17.2201118469238</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5752639770508</t>
+    <t xml:space="preserve">17.5752620697021</t>
   </si>
   <si>
     <t xml:space="preserve">17.5518989562988</t>
@@ -1976,13 +1976,13 @@
     <t xml:space="preserve">17.4163799285889</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1079616546631</t>
+    <t xml:space="preserve">17.1079597473145</t>
   </si>
   <si>
     <t xml:space="preserve">17.1313247680664</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2294597625732</t>
+    <t xml:space="preserve">17.2294578552246</t>
   </si>
   <si>
     <t xml:space="preserve">17.4911479949951</t>
@@ -1994,10 +1994,10 @@
     <t xml:space="preserve">17.453763961792</t>
   </si>
   <si>
-    <t xml:space="preserve">17.729471206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6547050476074</t>
+    <t xml:space="preserve">17.7294731140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6547031402588</t>
   </si>
   <si>
     <t xml:space="preserve">17.3369388580322</t>
@@ -2006,13 +2006,13 @@
     <t xml:space="preserve">17.1453437805176</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8462696075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1687107086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8229064941406</t>
+    <t xml:space="preserve">16.8462677001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1687088012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.822904586792</t>
   </si>
   <si>
     <t xml:space="preserve">17.9911613464355</t>
@@ -2024,10 +2024,10 @@
     <t xml:space="preserve">18.0378932952881</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6593761444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7948970794678</t>
+    <t xml:space="preserve">17.6593780517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7948951721191</t>
   </si>
   <si>
     <t xml:space="preserve">17.6360130310059</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">17.3275928497314</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3976879119873</t>
+    <t xml:space="preserve">17.3976898193359</t>
   </si>
   <si>
     <t xml:space="preserve">17.6266670227051</t>
@@ -2048,19 +2048,19 @@
     <t xml:space="preserve">17.8696632385254</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3135986328125</t>
+    <t xml:space="preserve">18.3136005401611</t>
   </si>
   <si>
     <t xml:space="preserve">18.056583404541</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2855625152588</t>
+    <t xml:space="preserve">18.2855606079102</t>
   </si>
   <si>
     <t xml:space="preserve">18.0192012786865</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9677982330322</t>
+    <t xml:space="preserve">17.9677963256836</t>
   </si>
   <si>
     <t xml:space="preserve">17.9070472717285</t>
@@ -2075,10 +2075,10 @@
     <t xml:space="preserve">18.3416385650635</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5565986633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4397716522217</t>
+    <t xml:space="preserve">18.5565967559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4397735595703</t>
   </si>
   <si>
     <t xml:space="preserve">18.5472526550293</t>
@@ -2087,16 +2087,16 @@
     <t xml:space="preserve">18.3089294433594</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8603439331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3696765899658</t>
+    <t xml:space="preserve">18.8603458404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3696784973145</t>
   </si>
   <si>
     <t xml:space="preserve">18.5893096923828</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0238742828369</t>
+    <t xml:space="preserve">18.0238723754883</t>
   </si>
   <si>
     <t xml:space="preserve">17.8603172302246</t>
@@ -2108,13 +2108,13 @@
     <t xml:space="preserve">17.5986270904541</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0939693450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8603744506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0472946166992</t>
+    <t xml:space="preserve">18.0939712524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.860372543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0472965240479</t>
   </si>
   <si>
     <t xml:space="preserve">19.9071025848389</t>
@@ -70949,7 +70949,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6493518519</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>576414</v>
@@ -70970,6 +70970,32 @@
         <v>1978</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6493981481</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>623507</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>5.68499994277954</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>5.47499990463257</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>5.53499984741211</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>5.51999998092651</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>1889</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1981" uniqueCount="1981">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1982" uniqueCount="1982">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,55 +44,55 @@
     <t xml:space="preserve">SFER.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0109634399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4978828430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9401931762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6836528778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.249813079834</t>
+    <t xml:space="preserve">18.01096534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4978809356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9401950836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6836547851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2498111724854</t>
   </si>
   <si>
     <t xml:space="preserve">19.4086723327637</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1344356536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8425102233887</t>
+    <t xml:space="preserve">19.1344375610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8425140380859</t>
   </si>
   <si>
     <t xml:space="preserve">18.4621238708496</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2851963043213</t>
+    <t xml:space="preserve">18.2851982116699</t>
   </si>
   <si>
     <t xml:space="preserve">18.0994262695312</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6394214630127</t>
+    <t xml:space="preserve">17.6394233703613</t>
   </si>
   <si>
     <t xml:space="preserve">17.5686531066895</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1878852844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4798126220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2232761383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7632694244385</t>
+    <t xml:space="preserve">18.1878890991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4798164367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.223274230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7632675170898</t>
   </si>
   <si>
     <t xml:space="preserve">18.3913516998291</t>
@@ -101,46 +101,46 @@
     <t xml:space="preserve">18.6744346618652</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9578857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2055835723877</t>
+    <t xml:space="preserve">17.9578838348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2055816650391</t>
   </si>
   <si>
     <t xml:space="preserve">18.258659362793</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0817337036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3563404083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9051856994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1617221832275</t>
+    <t xml:space="preserve">18.0817356109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3563423156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9051837921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1617240905762</t>
   </si>
   <si>
     <t xml:space="preserve">16.6486396789551</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0201854705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4890365600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6305751800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4090461730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4532775878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9752044677734</t>
+    <t xml:space="preserve">17.0201816558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.48903465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6305732727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4090442657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4532794952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9752063751221</t>
   </si>
   <si>
     <t xml:space="preserve">18.1348114013672</t>
@@ -152,16 +152,16 @@
     <t xml:space="preserve">17.9048080444336</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3471202850342</t>
+    <t xml:space="preserve">18.3471221923828</t>
   </si>
   <si>
     <t xml:space="preserve">19.019437789917</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0017395019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8513584136963</t>
+    <t xml:space="preserve">19.0017414093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8513565063477</t>
   </si>
   <si>
     <t xml:space="preserve">19.3113632202148</t>
@@ -173,10 +173,10 @@
     <t xml:space="preserve">19.9482917785645</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7271347045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3379020690918</t>
+    <t xml:space="preserve">19.7271327972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3379039764404</t>
   </si>
   <si>
     <t xml:space="preserve">19.647518157959</t>
@@ -185,7 +185,7 @@
     <t xml:space="preserve">19.983678817749</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1167449951172</t>
+    <t xml:space="preserve">19.1167469024658</t>
   </si>
   <si>
     <t xml:space="preserve">19.444055557251</t>
@@ -197,16 +197,16 @@
     <t xml:space="preserve">20.178295135498</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4971332550049</t>
+    <t xml:space="preserve">19.4971351623535</t>
   </si>
   <si>
     <t xml:space="preserve">19.4705963134766</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9663600921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4794425964355</t>
+    <t xml:space="preserve">18.9663619995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4794387817383</t>
   </si>
   <si>
     <t xml:space="preserve">19.9129066467285</t>
@@ -218,31 +218,31 @@
     <t xml:space="preserve">19.4175186157227</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8690490722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.833667755127</t>
+    <t xml:space="preserve">18.8690509796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8336658477783</t>
   </si>
   <si>
     <t xml:space="preserve">18.5152015686035</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9309749603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8955879211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5240459442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9486656188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7982769012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8778991699219</t>
+    <t xml:space="preserve">18.9309730529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8955898284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5240440368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9486675262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7982807159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8778972625732</t>
   </si>
   <si>
     <t xml:space="preserve">19.2936687469482</t>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">18.3205814361572</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3648147583008</t>
+    <t xml:space="preserve">18.3648166656494</t>
   </si>
   <si>
     <t xml:space="preserve">17.8251934051514</t>
@@ -266,28 +266,28 @@
     <t xml:space="preserve">18.3117389678955</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8782691955566</t>
+    <t xml:space="preserve">17.878267288208</t>
   </si>
   <si>
     <t xml:space="preserve">18.0021190643311</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7190380096436</t>
+    <t xml:space="preserve">17.7190399169922</t>
   </si>
   <si>
     <t xml:space="preserve">17.444803237915</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1440296173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5509567260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9844245910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4182643890381</t>
+    <t xml:space="preserve">17.1440334320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5509586334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9844264984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4182682037354</t>
   </si>
   <si>
     <t xml:space="preserve">17.9313488006592</t>
@@ -296,34 +296,34 @@
     <t xml:space="preserve">17.7367286682129</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6482677459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5939388275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8112602233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7025985717773</t>
+    <t xml:space="preserve">17.648265838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.593936920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8112564086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7025966644287</t>
   </si>
   <si>
     <t xml:space="preserve">17.6482696533203</t>
   </si>
   <si>
-    <t xml:space="preserve">17.530553817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4128379821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.304178237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4762210845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.430944442749</t>
+    <t xml:space="preserve">17.5305519104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4128341674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3041763305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4762191772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4309463500977</t>
   </si>
   <si>
     <t xml:space="preserve">17.4852752685547</t>
@@ -332,25 +332,25 @@
     <t xml:space="preserve">17.7478733062744</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6844902038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.150239944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.71559715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5435523986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0415802001953</t>
+    <t xml:space="preserve">17.6844863891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1502418518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7155990600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5435543060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0415782928467</t>
   </si>
   <si>
     <t xml:space="preserve">17.0778007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8384246826172</t>
+    <t xml:space="preserve">17.8384227752686</t>
   </si>
   <si>
     <t xml:space="preserve">17.9380283355713</t>
@@ -359,16 +359,16 @@
     <t xml:space="preserve">17.7297630310059</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8655891418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1825160980225</t>
+    <t xml:space="preserve">17.8655872344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1825141906738</t>
   </si>
   <si>
     <t xml:space="preserve">16.8514251708984</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3896160125732</t>
+    <t xml:space="preserve">16.3896179199219</t>
   </si>
   <si>
     <t xml:space="preserve">16.6793785095215</t>
@@ -377,25 +377,25 @@
     <t xml:space="preserve">16.2628440856934</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5254421234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6069374084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8061485290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8242588043213</t>
+    <t xml:space="preserve">16.5254402160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6069412231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8061466217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8242607116699</t>
   </si>
   <si>
     <t xml:space="preserve">16.0726890563965</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8734798431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3624496459961</t>
+    <t xml:space="preserve">15.8734817504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3624515533447</t>
   </si>
   <si>
     <t xml:space="preserve">16.4439468383789</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">17.095911026001</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1321315765381</t>
+    <t xml:space="preserve">17.1321277618408</t>
   </si>
   <si>
     <t xml:space="preserve">17.086856842041</t>
@@ -419,22 +419,22 @@
     <t xml:space="preserve">17.3403968811035</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9018096923828</t>
+    <t xml:space="preserve">17.9018077850342</t>
   </si>
   <si>
     <t xml:space="preserve">18.1372413635254</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9289722442627</t>
+    <t xml:space="preserve">17.9289741516113</t>
   </si>
   <si>
     <t xml:space="preserve">18.7710914611816</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6352691650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0699081420898</t>
+    <t xml:space="preserve">18.6352672576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0699062347412</t>
   </si>
   <si>
     <t xml:space="preserve">19.2147884368896</t>
@@ -443,7 +443,7 @@
     <t xml:space="preserve">18.6262111663818</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4994411468506</t>
+    <t xml:space="preserve">18.4994430541992</t>
   </si>
   <si>
     <t xml:space="preserve">18.2187366485596</t>
@@ -452,16 +452,16 @@
     <t xml:space="preserve">18.7167625427246</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5809383392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7620334625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8073120117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9431343078613</t>
+    <t xml:space="preserve">18.5809364318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.762035369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8073139190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.94313621521</t>
   </si>
   <si>
     <t xml:space="preserve">19.0427436828613</t>
@@ -470,7 +470,7 @@
     <t xml:space="preserve">18.6624317169189</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4722766876221</t>
+    <t xml:space="preserve">18.4722728729248</t>
   </si>
   <si>
     <t xml:space="preserve">18.6171569824219</t>
@@ -479,10 +479,10 @@
     <t xml:space="preserve">18.7529811859131</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9703044891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6805419921875</t>
+    <t xml:space="preserve">18.9703025817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6805400848389</t>
   </si>
   <si>
     <t xml:space="preserve">18.6081027984619</t>
@@ -491,16 +491,16 @@
     <t xml:space="preserve">18.653377532959</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5175533294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.870698928833</t>
+    <t xml:space="preserve">18.5175514221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8706970214844</t>
   </si>
   <si>
     <t xml:space="preserve">18.6986522674561</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1061267852783</t>
+    <t xml:space="preserve">19.106128692627</t>
   </si>
   <si>
     <t xml:space="preserve">19.9210815429688</t>
@@ -509,73 +509,73 @@
     <t xml:space="preserve">19.6947059631348</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5588779449463</t>
+    <t xml:space="preserve">19.5588798522949</t>
   </si>
   <si>
     <t xml:space="preserve">19.4592723846436</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3143939971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8888072967529</t>
+    <t xml:space="preserve">19.314395904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8888111114502</t>
   </si>
   <si>
     <t xml:space="preserve">19.1332912445068</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1604557037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9391918182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4553279876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3557224273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3104496002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3919448852539</t>
+    <t xml:space="preserve">19.1604595184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9391899108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4553298950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3557243347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3104476928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3919429779053</t>
   </si>
   <si>
     <t xml:space="preserve">20.4643840789795</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6907615661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8446960449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7994194030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4009990692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1021842956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5277690887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3647804260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5458793640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7541446685791</t>
+    <t xml:space="preserve">20.6907596588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8446979522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7994174957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4010009765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1021823883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5277709960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3647766113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5458812713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7541484832764</t>
   </si>
   <si>
     <t xml:space="preserve">20.4191074371338</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0116310119629</t>
+    <t xml:space="preserve">20.0116329193115</t>
   </si>
   <si>
     <t xml:space="preserve">20.2651748657227</t>
@@ -602,19 +602,19 @@
     <t xml:space="preserve">20.1836795806885</t>
   </si>
   <si>
-    <t xml:space="preserve">19.549825668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4140014648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5045490264893</t>
+    <t xml:space="preserve">19.5498237609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4140033721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5045528411865</t>
   </si>
   <si>
     <t xml:space="preserve">19.7218704223633</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7943115234375</t>
+    <t xml:space="preserve">19.7943134307861</t>
   </si>
   <si>
     <t xml:space="preserve">19.5226593017578</t>
@@ -623,25 +623,25 @@
     <t xml:space="preserve">19.830530166626</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9120273590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7490367889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0919666290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3002300262451</t>
+    <t xml:space="preserve">19.9120254516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7490348815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0919609069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3002281188965</t>
   </si>
   <si>
     <t xml:space="preserve">18.3273944854736</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2458992004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0104694366455</t>
+    <t xml:space="preserve">18.2459011077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0104675292969</t>
   </si>
   <si>
     <t xml:space="preserve">17.7388191223145</t>
@@ -650,52 +650,52 @@
     <t xml:space="preserve">17.8565330505371</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8203144073486</t>
+    <t xml:space="preserve">17.8203163146973</t>
   </si>
   <si>
     <t xml:space="preserve">17.6392135620117</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3455066680908</t>
+    <t xml:space="preserve">18.3455047607422</t>
   </si>
   <si>
     <t xml:space="preserve">18.3907794952393</t>
   </si>
   <si>
-    <t xml:space="preserve">19.151403427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2872276306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3958892822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3777809143066</t>
+    <t xml:space="preserve">19.1514015197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2872314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3958911895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.377779006958</t>
   </si>
   <si>
     <t xml:space="preserve">19.1151847839355</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5860443115234</t>
+    <t xml:space="preserve">19.5860462188721</t>
   </si>
   <si>
     <t xml:space="preserve">19.2600631713867</t>
   </si>
   <si>
-    <t xml:space="preserve">20.373836517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3466663360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2380065917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1293468475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.15651512146</t>
+    <t xml:space="preserve">20.3738346099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3466701507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2380084991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1293449401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1565132141113</t>
   </si>
   <si>
     <t xml:space="preserve">20.8084754943848</t>
@@ -704,37 +704,37 @@
     <t xml:space="preserve">20.6183185577393</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4785499572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5328788757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0671291351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0580711364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2572822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2935009002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3025550842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3206653594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2753925323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2391700744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8186931610107</t>
+    <t xml:space="preserve">21.4785480499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5328769683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0671253204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.058069229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2572784423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2935028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3025588989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3206634521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2753944396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2391719818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8186950683594</t>
   </si>
   <si>
     <t xml:space="preserve">23.0722332000732</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">23.1537303924561</t>
   </si>
   <si>
-    <t xml:space="preserve">23.099401473999</t>
+    <t xml:space="preserve">23.0993995666504</t>
   </si>
   <si>
     <t xml:space="preserve">22.5923175811768</t>
@@ -755,43 +755,43 @@
     <t xml:space="preserve">22.3568878173828</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9092407226562</t>
+    <t xml:space="preserve">22.9092445373535</t>
   </si>
   <si>
     <t xml:space="preserve">22.1757869720459</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1395664215088</t>
+    <t xml:space="preserve">22.1395645141602</t>
   </si>
   <si>
     <t xml:space="preserve">23.606481552124</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7513618469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1226215362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6427040100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6879787445068</t>
+    <t xml:space="preserve">23.7513637542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1226196289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6427059173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6879768371582</t>
   </si>
   <si>
     <t xml:space="preserve">23.5612087249756</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7423095703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7242012023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6336498260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8238048553467</t>
+    <t xml:space="preserve">23.7423057556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7241992950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6336479187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.823802947998</t>
   </si>
   <si>
     <t xml:space="preserve">23.6970329284668</t>
@@ -806,7 +806,7 @@
     <t xml:space="preserve">24.0682888031006</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9777393341064</t>
+    <t xml:space="preserve">23.9777374267578</t>
   </si>
   <si>
     <t xml:space="preserve">24.2946643829346</t>
@@ -815,13 +815,13 @@
     <t xml:space="preserve">24.4304904937744</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6115894317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7655258178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1911125183105</t>
+    <t xml:space="preserve">24.6115913391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7655239105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1911144256592</t>
   </si>
   <si>
     <t xml:space="preserve">25.3903255462646</t>
@@ -833,7 +833,7 @@
     <t xml:space="preserve">25.6167030334473</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6710300445557</t>
+    <t xml:space="preserve">25.6710319519043</t>
   </si>
   <si>
     <t xml:space="preserve">25.6529216766357</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">25.5352077484131</t>
   </si>
   <si>
-    <t xml:space="preserve">24.955680847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9013519287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0643405914307</t>
+    <t xml:space="preserve">24.9556827545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9013538360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0643463134766</t>
   </si>
   <si>
     <t xml:space="preserve">24.8017482757568</t>
@@ -860,31 +860,31 @@
     <t xml:space="preserve">24.6206474304199</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9375743865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3722133636475</t>
+    <t xml:space="preserve">24.937572479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3722152709961</t>
   </si>
   <si>
     <t xml:space="preserve">25.6257553100586</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2273349761963</t>
+    <t xml:space="preserve">25.2273330688477</t>
   </si>
   <si>
     <t xml:space="preserve">25.173002243042</t>
   </si>
   <si>
-    <t xml:space="preserve">25.163948059082</t>
+    <t xml:space="preserve">25.1639499664307</t>
   </si>
   <si>
     <t xml:space="preserve">25.399377822876</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7253608703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2907180786133</t>
+    <t xml:space="preserve">25.7253589630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2907199859619</t>
   </si>
   <si>
     <t xml:space="preserve">25.1277294158936</t>
@@ -893,106 +893,106 @@
     <t xml:space="preserve">25.7434711456299</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5442562103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4808712005615</t>
+    <t xml:space="preserve">25.5442581176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4808731079102</t>
   </si>
   <si>
     <t xml:space="preserve">25.5080394744873</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2635517120361</t>
+    <t xml:space="preserve">25.2635555267334</t>
   </si>
   <si>
     <t xml:space="preserve">25.0824527740479</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7836360931396</t>
+    <t xml:space="preserve">24.7836380004883</t>
   </si>
   <si>
     <t xml:space="preserve">24.4214363098145</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2674980163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5261516571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1237831115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1871681213379</t>
+    <t xml:space="preserve">24.2674961090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5261497497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1237812042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1871662139893</t>
   </si>
   <si>
     <t xml:space="preserve">26.6308650970459</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4859848022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3229923248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.676139831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8934631347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2596073150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.667085647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9115715026855</t>
+    <t xml:space="preserve">26.4859809875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3229961395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6761379241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8934593200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2596092224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6670837402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9115695953369</t>
   </si>
   <si>
     <t xml:space="preserve">26.6036987304688</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5946483612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3088321685791</t>
+    <t xml:space="preserve">26.5946445465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3088302612305</t>
   </si>
   <si>
     <t xml:space="preserve">25.3269367218018</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8340225219727</t>
+    <t xml:space="preserve">25.834020614624</t>
   </si>
   <si>
     <t xml:space="preserve">25.8984432220459</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0641078948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7112007141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6159934997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2202472686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.128210067749</t>
+    <t xml:space="preserve">26.0641059875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7112045288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6159954071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2202453613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1282119750977</t>
   </si>
   <si>
     <t xml:space="preserve">22.9625511169434</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8705177307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8613147735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2662658691406</t>
+    <t xml:space="preserve">22.8705196380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8613128662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.266263961792</t>
   </si>
   <si>
     <t xml:space="preserve">23.2386531829834</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">23.0453834533691</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8889236450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0882263183594</t>
+    <t xml:space="preserve">22.8889255523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0882244110107</t>
   </si>
   <si>
     <t xml:space="preserve">22.3183116912842</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2262744903564</t>
+    <t xml:space="preserve">22.2262763977051</t>
   </si>
   <si>
     <t xml:space="preserve">22.3827342987061</t>
@@ -1025,13 +1025,13 @@
     <t xml:space="preserve">22.95334815979</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8797225952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2846698760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4871463775635</t>
+    <t xml:space="preserve">22.8797206878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2846717834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4871482849121</t>
   </si>
   <si>
     <t xml:space="preserve">23.4319248199463</t>
@@ -1046,28 +1046,28 @@
     <t xml:space="preserve">22.6036167144775</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2538890838623</t>
+    <t xml:space="preserve">22.2538871765137</t>
   </si>
   <si>
     <t xml:space="preserve">21.545223236084</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4900016784668</t>
+    <t xml:space="preserve">21.4900035858154</t>
   </si>
   <si>
     <t xml:space="preserve">21.7200889587402</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5544281005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.674072265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6280555725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1678848266602</t>
+    <t xml:space="preserve">21.5544261932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6740703582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6280536651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1678829193115</t>
   </si>
   <si>
     <t xml:space="preserve">21.2046966552734</t>
@@ -1082,7 +1082,7 @@
     <t xml:space="preserve">21.5084114074707</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9133605957031</t>
+    <t xml:space="preserve">21.9133586883545</t>
   </si>
   <si>
     <t xml:space="preserve">21.8857498168945</t>
@@ -1106,7 +1106,7 @@
     <t xml:space="preserve">22.5299892425537</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6312274932861</t>
+    <t xml:space="preserve">22.6312294006348</t>
   </si>
   <si>
     <t xml:space="preserve">22.6404323577881</t>
@@ -1115,37 +1115,37 @@
     <t xml:space="preserve">22.5576000213623</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4255790710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6556644439697</t>
+    <t xml:space="preserve">21.4255809783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6556663513184</t>
   </si>
   <si>
     <t xml:space="preserve">22.2630920410156</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5391941070557</t>
+    <t xml:space="preserve">22.539192199707</t>
   </si>
   <si>
     <t xml:space="preserve">22.3551254272461</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0514106750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7876853942871</t>
+    <t xml:space="preserve">22.0514125823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7876873016357</t>
   </si>
   <si>
     <t xml:space="preserve">22.3367176055908</t>
   </si>
   <si>
-    <t xml:space="preserve">22.115837097168</t>
+    <t xml:space="preserve">22.1158390045166</t>
   </si>
   <si>
     <t xml:space="preserve">21.7661037445068</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0606136322021</t>
+    <t xml:space="preserve">22.0606117248535</t>
   </si>
   <si>
     <t xml:space="preserve">21.7569007873535</t>
@@ -1160,28 +1160,28 @@
     <t xml:space="preserve">22.0053939819336</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8765487670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1250400543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7753086090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0238056182861</t>
+    <t xml:space="preserve">21.8765468597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1250381469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7753124237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0238018035889</t>
   </si>
   <si>
     <t xml:space="preserve">21.9041576385498</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6832733154297</t>
+    <t xml:space="preserve">21.6832752227783</t>
   </si>
   <si>
     <t xml:space="preserve">20.827356338501</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0574417114258</t>
+    <t xml:space="preserve">21.0574398040771</t>
   </si>
   <si>
     <t xml:space="preserve">20.94700050354</t>
@@ -1190,19 +1190,19 @@
     <t xml:space="preserve">20.7997455596924</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1034603118896</t>
+    <t xml:space="preserve">21.103458404541</t>
   </si>
   <si>
     <t xml:space="preserve">21.0758476257324</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3243427276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.950174331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0974273681641</t>
+    <t xml:space="preserve">21.3243408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9501762390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0974311828613</t>
   </si>
   <si>
     <t xml:space="preserve">21.8581409454346</t>
@@ -1211,19 +1211,19 @@
     <t xml:space="preserve">21.6372566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2967281341553</t>
+    <t xml:space="preserve">21.2967319488525</t>
   </si>
   <si>
     <t xml:space="preserve">20.9746112823486</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9838161468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1402721405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0666427612305</t>
+    <t xml:space="preserve">20.983814239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1402702331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0666465759277</t>
   </si>
   <si>
     <t xml:space="preserve">20.7077121734619</t>
@@ -1238,10 +1238,10 @@
     <t xml:space="preserve">21.0206279754639</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0022220611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6340847015381</t>
+    <t xml:space="preserve">21.0022239685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6340827941895</t>
   </si>
   <si>
     <t xml:space="preserve">20.4500141143799</t>
@@ -1250,70 +1250,70 @@
     <t xml:space="preserve">20.3855895996094</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3947925567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0082492828369</t>
+    <t xml:space="preserve">20.3947944641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0082511901855</t>
   </si>
   <si>
     <t xml:space="preserve">19.9714393615723</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0634708404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4868278503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7445259094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8917827606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2415084838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9285945892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2475395202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1647071838379</t>
+    <t xml:space="preserve">20.0634727478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4868297576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7445278167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8917808532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2415103912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9285926818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2475414276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1647109985352</t>
   </si>
   <si>
     <t xml:space="preserve">20.0910816192627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2719783782959</t>
+    <t xml:space="preserve">19.2719764709473</t>
   </si>
   <si>
     <t xml:space="preserve">19.695333480835</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8057765960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7321491241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1831188201904</t>
+    <t xml:space="preserve">19.8057746887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7321510314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1831169128418</t>
   </si>
   <si>
     <t xml:space="preserve">20.0450630187988</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2935562133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4316120147705</t>
+    <t xml:space="preserve">20.2935581207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4316082000732</t>
   </si>
   <si>
     <t xml:space="preserve">20.5696601867676</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6616973876953</t>
+    <t xml:space="preserve">20.6616954803467</t>
   </si>
   <si>
     <t xml:space="preserve">21.1310691833496</t>
@@ -1322,7 +1322,7 @@
     <t xml:space="preserve">21.0482387542725</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1954917907715</t>
+    <t xml:space="preserve">21.1954956054688</t>
   </si>
   <si>
     <t xml:space="preserve">21.4531898498535</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">20.7721366882324</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4652500152588</t>
+    <t xml:space="preserve">19.4652481079102</t>
   </si>
   <si>
     <t xml:space="preserve">19.7965717315674</t>
@@ -1346,10 +1346,10 @@
     <t xml:space="preserve">19.8609962463379</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0174541473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2199306488037</t>
+    <t xml:space="preserve">20.0174522399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2199287414551</t>
   </si>
   <si>
     <t xml:space="preserve">20.229133605957</t>
@@ -1361,49 +1361,49 @@
     <t xml:space="preserve">20.6524925231934</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9101867675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2659492492676</t>
+    <t xml:space="preserve">20.9101848602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2659473419189</t>
   </si>
   <si>
     <t xml:space="preserve">20.4684219360352</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1555023193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1739139556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2599182128906</t>
+    <t xml:space="preserve">20.1555061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1739120483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.259916305542</t>
   </si>
   <si>
     <t xml:space="preserve">21.3703575134277</t>
   </si>
   <si>
-    <t xml:space="preserve">21.517614364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8549652099609</t>
+    <t xml:space="preserve">21.5176124572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8549671173096</t>
   </si>
   <si>
     <t xml:space="preserve">20.9193897247314</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5052356719971</t>
+    <t xml:space="preserve">20.5052375793457</t>
   </si>
   <si>
     <t xml:space="preserve">20.3487777709961</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0266571044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7229461669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9162158966064</t>
+    <t xml:space="preserve">20.0266590118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7229442596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9162178039551</t>
   </si>
   <si>
     <t xml:space="preserve">20.5604572296143</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">21.6004428863525</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6248798370361</t>
+    <t xml:space="preserve">20.6248817443848</t>
   </si>
   <si>
     <t xml:space="preserve">20.2751502990723</t>
@@ -1430,13 +1430,13 @@
     <t xml:space="preserve">20.1094875335693</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6493167877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9990463256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1278972625732</t>
+    <t xml:space="preserve">19.6493186950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9990482330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1278953552246</t>
   </si>
   <si>
     <t xml:space="preserve">20.3303718566895</t>
@@ -1451,37 +1451,37 @@
     <t xml:space="preserve">20.5328464508057</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3027610778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.64328956604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6156749725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7261180877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2783260345459</t>
+    <t xml:space="preserve">20.3027591705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6432857513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6156787872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7261161804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2783279418945</t>
   </si>
   <si>
     <t xml:space="preserve">21.3151378631592</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5360164642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7937183380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.64963722229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.548397064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4195518493652</t>
+    <t xml:space="preserve">21.5360202789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7937164306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6496334075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5483989715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4195499420166</t>
   </si>
   <si>
     <t xml:space="preserve">22.2078685760498</t>
@@ -1496,31 +1496,31 @@
     <t xml:space="preserve">22.9165325164795</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6864471435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7324676513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8337020874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7692794799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9073295593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2754688262939</t>
+    <t xml:space="preserve">22.6864452362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7324657440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8337001800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7692775726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9073314666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2754669189453</t>
   </si>
   <si>
     <t xml:space="preserve">22.991304397583</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3090705871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4118766784668</t>
+    <t xml:space="preserve">23.3090686798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4118747711182</t>
   </si>
   <si>
     <t xml:space="preserve">22.9071884155273</t>
@@ -1532,16 +1532,16 @@
     <t xml:space="preserve">22.7296123504639</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3557720184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6174621582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0754165649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3557987213135</t>
+    <t xml:space="preserve">22.355770111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6174583435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.07541847229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3558006286621</t>
   </si>
   <si>
     <t xml:space="preserve">23.1969165802002</t>
@@ -1550,10 +1550,10 @@
     <t xml:space="preserve">23.206262588501</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4586048126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6548461914062</t>
+    <t xml:space="preserve">23.4586067199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6548442840576</t>
   </si>
   <si>
     <t xml:space="preserve">22.7389602661133</t>
@@ -1565,7 +1565,7 @@
     <t xml:space="preserve">23.5053367614746</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3838386535645</t>
+    <t xml:space="preserve">23.3838367462158</t>
   </si>
   <si>
     <t xml:space="preserve">23.3931846618652</t>
@@ -1574,10 +1574,10 @@
     <t xml:space="preserve">23.2623386383057</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9258804321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9912433624268</t>
+    <t xml:space="preserve">22.9258823394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9912452697754</t>
   </si>
   <si>
     <t xml:space="preserve">20.3370227813721</t>
@@ -1586,25 +1586,25 @@
     <t xml:space="preserve">19.9912166595459</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7388763427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5612983703613</t>
+    <t xml:space="preserve">19.7388744354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5613021850586</t>
   </si>
   <si>
     <t xml:space="preserve">19.3089561462402</t>
   </si>
   <si>
-    <t xml:space="preserve">19.533260345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4958782196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3463401794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0285739898682</t>
+    <t xml:space="preserve">19.5332622528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4958801269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.346342086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0285758972168</t>
   </si>
   <si>
     <t xml:space="preserve">18.6266937255859</t>
@@ -1616,31 +1616,31 @@
     <t xml:space="preserve">18.0752754211426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6220188140869</t>
+    <t xml:space="preserve">18.6220207214355</t>
   </si>
   <si>
     <t xml:space="preserve">18.0799503326416</t>
   </si>
   <si>
-    <t xml:space="preserve">18.603328704834</t>
+    <t xml:space="preserve">18.6033306121826</t>
   </si>
   <si>
     <t xml:space="preserve">18.6360397338867</t>
   </si>
   <si>
-    <t xml:space="preserve">18.794921875</t>
+    <t xml:space="preserve">18.7949237823486</t>
   </si>
   <si>
     <t xml:space="preserve">18.7762317657471</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7201557159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.575288772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3930416107178</t>
+    <t xml:space="preserve">18.7201538085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5752906799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3930435180664</t>
   </si>
   <si>
     <t xml:space="preserve">18.5285606384277</t>
@@ -1649,13 +1649,13 @@
     <t xml:space="preserve">18.495849609375</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4351005554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.388370513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4911766052246</t>
+    <t xml:space="preserve">18.4350986480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3883686065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.491174697876</t>
   </si>
   <si>
     <t xml:space="preserve">18.2435073852539</t>
@@ -1667,52 +1667,52 @@
     <t xml:space="preserve">17.7715282440186</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1079883575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6734256744385</t>
+    <t xml:space="preserve">18.1079845428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6734218597412</t>
   </si>
   <si>
     <t xml:space="preserve">18.7575378417969</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7295036315918</t>
+    <t xml:space="preserve">18.7295017242432</t>
   </si>
   <si>
     <t xml:space="preserve">18.276216506958</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2528533935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2107944488525</t>
+    <t xml:space="preserve">18.2528514862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2107963562012</t>
   </si>
   <si>
     <t xml:space="preserve">18.3790245056152</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1407241821289</t>
+    <t xml:space="preserve">19.1407260894775</t>
   </si>
   <si>
     <t xml:space="preserve">19.4398002624512</t>
   </si>
   <si>
-    <t xml:space="preserve">19.402416229248</t>
+    <t xml:space="preserve">19.4024181365967</t>
   </si>
   <si>
     <t xml:space="preserve">19.4117622375488</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4304542541504</t>
+    <t xml:space="preserve">19.430456161499</t>
   </si>
   <si>
     <t xml:space="preserve">19.3650321960449</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1594200134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1687641143799</t>
+    <t xml:space="preserve">19.1594181060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1687660217285</t>
   </si>
   <si>
     <t xml:space="preserve">19.1126899719238</t>
@@ -1736,28 +1736,28 @@
     <t xml:space="preserve">19.2528820037842</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5239162445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4211101531982</t>
+    <t xml:space="preserve">19.5239143371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4211082458496</t>
   </si>
   <si>
     <t xml:space="preserve">19.8136444091797</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0753307342529</t>
+    <t xml:space="preserve">20.0753326416016</t>
   </si>
   <si>
     <t xml:space="preserve">19.7482204437256</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0192546844482</t>
+    <t xml:space="preserve">20.0192565917969</t>
   </si>
   <si>
     <t xml:space="preserve">19.7669124603271</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7856063842773</t>
+    <t xml:space="preserve">19.7856044769287</t>
   </si>
   <si>
     <t xml:space="preserve">19.5706443786621</t>
@@ -1766,25 +1766,25 @@
     <t xml:space="preserve">19.2809162139893</t>
   </si>
   <si>
-    <t xml:space="preserve">19.150074005127</t>
+    <t xml:space="preserve">19.1500720977783</t>
   </si>
   <si>
     <t xml:space="preserve">18.8977298736572</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8042678833008</t>
+    <t xml:space="preserve">18.8042697906494</t>
   </si>
   <si>
     <t xml:space="preserve">18.8790378570557</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1780834197998</t>
+    <t xml:space="preserve">18.1780853271484</t>
   </si>
   <si>
     <t xml:space="preserve">18.6453876495361</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8556461334229</t>
+    <t xml:space="preserve">17.8556423187256</t>
   </si>
   <si>
     <t xml:space="preserve">17.2528228759766</t>
@@ -1793,7 +1793,7 @@
     <t xml:space="preserve">17.1546897888184</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9817867279053</t>
+    <t xml:space="preserve">16.9817886352539</t>
   </si>
   <si>
     <t xml:space="preserve">18.1360263824463</t>
@@ -1811,7 +1811,7 @@
     <t xml:space="preserve">19.1874580383301</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0098838806152</t>
+    <t xml:space="preserve">19.0098819732666</t>
   </si>
   <si>
     <t xml:space="preserve">19.5986843109131</t>
@@ -1823,37 +1823,37 @@
     <t xml:space="preserve">19.6454162597656</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4771862030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5426082611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5799942016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0005645751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6267223358154</t>
+    <t xml:space="preserve">19.4771842956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5426063537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5799922943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0005626678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6267242431641</t>
   </si>
   <si>
     <t xml:space="preserve">19.4865303039551</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7014923095703</t>
+    <t xml:space="preserve">19.701488494873</t>
   </si>
   <si>
     <t xml:space="preserve">19.3930702209473</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7481918334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7855777740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0659580230713</t>
+    <t xml:space="preserve">18.7481937408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7855758666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0659561157227</t>
   </si>
   <si>
     <t xml:space="preserve">19.5145683288574</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">17.0472106933594</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7107524871826</t>
+    <t xml:space="preserve">16.710750579834</t>
   </si>
   <si>
     <t xml:space="preserve">16.8135585784912</t>
@@ -1874,22 +1874,22 @@
     <t xml:space="preserve">16.5845813751221</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5471954345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5378513336182</t>
+    <t xml:space="preserve">16.5471973419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5378475189209</t>
   </si>
   <si>
     <t xml:space="preserve">16.7200965881348</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4957904815674</t>
+    <t xml:space="preserve">16.495792388916</t>
   </si>
   <si>
     <t xml:space="preserve">16.7528076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5004653930664</t>
+    <t xml:space="preserve">16.500467300415</t>
   </si>
   <si>
     <t xml:space="preserve">16.4630832672119</t>
@@ -1901,16 +1901,16 @@
     <t xml:space="preserve">16.3509292602539</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5425243377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8415966033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6640205383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5331764221191</t>
+    <t xml:space="preserve">16.5425224304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8415946960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6640224456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5331783294678</t>
   </si>
   <si>
     <t xml:space="preserve">16.5892524719238</t>
@@ -1919,28 +1919,28 @@
     <t xml:space="preserve">16.6827144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5986022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4256992340088</t>
+    <t xml:space="preserve">16.5986003875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4256954193115</t>
   </si>
   <si>
     <t xml:space="preserve">16.1266212463379</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1593341827393</t>
+    <t xml:space="preserve">16.1593360900879</t>
   </si>
   <si>
     <t xml:space="preserve">16.4490623474121</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1920471191406</t>
+    <t xml:space="preserve">16.192045211792</t>
   </si>
   <si>
     <t xml:space="preserve">16.2154102325439</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4817752838135</t>
+    <t xml:space="preserve">16.4817733764648</t>
   </si>
   <si>
     <t xml:space="preserve">16.5238304138184</t>
@@ -1949,10 +1949,10 @@
     <t xml:space="preserve">16.4023323059082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2995262145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.579906463623</t>
+    <t xml:space="preserve">16.299524307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5799083709717</t>
   </si>
   <si>
     <t xml:space="preserve">17.1874008178711</t>
@@ -1967,22 +1967,22 @@
     <t xml:space="preserve">17.2201118469238</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5752639770508</t>
+    <t xml:space="preserve">17.5752620697021</t>
   </si>
   <si>
     <t xml:space="preserve">17.5518989562988</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4163799285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1079616546631</t>
+    <t xml:space="preserve">17.4163780212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1079578399658</t>
   </si>
   <si>
     <t xml:space="preserve">17.1313247680664</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2294597625732</t>
+    <t xml:space="preserve">17.2294578552246</t>
   </si>
   <si>
     <t xml:space="preserve">17.4911479949951</t>
@@ -1991,40 +1991,40 @@
     <t xml:space="preserve">17.4397430419922</t>
   </si>
   <si>
-    <t xml:space="preserve">17.453763961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.729471206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6547050476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3369388580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1453437805176</t>
+    <t xml:space="preserve">17.4537620544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7294731140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6547012329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3369369506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1453418731689</t>
   </si>
   <si>
     <t xml:space="preserve">16.8462696075439</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1687107086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8229064941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9911613464355</t>
+    <t xml:space="preserve">17.1687088012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.822904586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9911632537842</t>
   </si>
   <si>
     <t xml:space="preserve">17.9117221832275</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0378932952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6593761444092</t>
+    <t xml:space="preserve">18.0378913879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6593780517578</t>
   </si>
   <si>
     <t xml:space="preserve">17.7948970794678</t>
@@ -2039,25 +2039,25 @@
     <t xml:space="preserve">17.3976879119873</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6266670227051</t>
+    <t xml:space="preserve">17.6266651153564</t>
   </si>
   <si>
     <t xml:space="preserve">17.5004940032959</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8696632385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3135986328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.056583404541</t>
+    <t xml:space="preserve">17.869665145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3136005401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0565853118896</t>
   </si>
   <si>
     <t xml:space="preserve">18.2855625152588</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0192012786865</t>
+    <t xml:space="preserve">18.0191993713379</t>
   </si>
   <si>
     <t xml:space="preserve">17.9677982330322</t>
@@ -2075,31 +2075,31 @@
     <t xml:space="preserve">18.3416385650635</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5565986633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4397716522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5472526550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3089294433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8603439331055</t>
+    <t xml:space="preserve">18.5565967559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.439769744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5472507476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3089275360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8603458404541</t>
   </si>
   <si>
     <t xml:space="preserve">18.3696765899658</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5893096923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0238742828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8603172302246</t>
+    <t xml:space="preserve">18.5893077850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0238723754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8603191375732</t>
   </si>
   <si>
     <t xml:space="preserve">18.06125831604</t>
@@ -2129,10 +2129,10 @@
     <t xml:space="preserve">19.4132251739502</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2042751312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4892082214355</t>
+    <t xml:space="preserve">19.2042770385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4892063140869</t>
   </si>
   <si>
     <t xml:space="preserve">19.1187953948975</t>
@@ -2150,16 +2150,16 @@
     <t xml:space="preserve">17.7131423950195</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7273921966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8318614959717</t>
+    <t xml:space="preserve">17.7273902893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8318634033203</t>
   </si>
   <si>
     <t xml:space="preserve">18.3732299804688</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6534099578857</t>
+    <t xml:space="preserve">18.6534118652344</t>
   </si>
   <si>
     <t xml:space="preserve">19.1757831573486</t>
@@ -2171,13 +2171,13 @@
     <t xml:space="preserve">19.2802562713623</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2137756347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9810791015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9050998687744</t>
+    <t xml:space="preserve">19.213773727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9810810089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.905101776123</t>
   </si>
   <si>
     <t xml:space="preserve">19.0333194732666</t>
@@ -2201,16 +2201,16 @@
     <t xml:space="preserve">19.7171497344971</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8121280670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.745641708374</t>
+    <t xml:space="preserve">19.812126159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7456436157227</t>
   </si>
   <si>
     <t xml:space="preserve">19.926097869873</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1350479125977</t>
+    <t xml:space="preserve">20.1350498199463</t>
   </si>
   <si>
     <t xml:space="preserve">20.1920337677002</t>
@@ -2219,7 +2219,7 @@
     <t xml:space="preserve">20.4674644470215</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4864616394043</t>
+    <t xml:space="preserve">20.4864597320557</t>
   </si>
   <si>
     <t xml:space="preserve">20.2870101928711</t>
@@ -2228,13 +2228,13 @@
     <t xml:space="preserve">20.2775115966797</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8406200408936</t>
+    <t xml:space="preserve">19.8406181335449</t>
   </si>
   <si>
     <t xml:space="preserve">19.8216247558594</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8501167297363</t>
+    <t xml:space="preserve">19.850118637085</t>
   </si>
   <si>
     <t xml:space="preserve">19.9545917510986</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">19.8881092071533</t>
   </si>
   <si>
-    <t xml:space="preserve">20.030574798584</t>
+    <t xml:space="preserve">20.0305728912354</t>
   </si>
   <si>
     <t xml:space="preserve">19.8691120147705</t>
@@ -2264,16 +2264,16 @@
     <t xml:space="preserve">18.0218181610107</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9315872192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5754261016846</t>
+    <t xml:space="preserve">17.9315891265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5754241943359</t>
   </si>
   <si>
     <t xml:space="preserve">17.2952442169189</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2762508392334</t>
+    <t xml:space="preserve">17.276252746582</t>
   </si>
   <si>
     <t xml:space="preserve">17.2667541503906</t>
@@ -2285,7 +2285,7 @@
     <t xml:space="preserve">17.0198135375977</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8963432312012</t>
+    <t xml:space="preserve">16.8963451385498</t>
   </si>
   <si>
     <t xml:space="preserve">17.0150661468506</t>
@@ -2294,25 +2294,25 @@
     <t xml:space="preserve">16.59716796875</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2837429046631</t>
+    <t xml:space="preserve">16.2837448120117</t>
   </si>
   <si>
     <t xml:space="preserve">16.8108654022217</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8536071777344</t>
+    <t xml:space="preserve">16.8536052703857</t>
   </si>
   <si>
     <t xml:space="preserve">17.0530548095703</t>
   </si>
   <si>
-    <t xml:space="preserve">16.915340423584</t>
+    <t xml:space="preserve">16.9153385162354</t>
   </si>
   <si>
     <t xml:space="preserve">16.6636505126953</t>
   </si>
   <si>
-    <t xml:space="preserve">16.734884262085</t>
+    <t xml:space="preserve">16.7348861694336</t>
   </si>
   <si>
     <t xml:space="preserve">16.948579788208</t>
@@ -2324,13 +2324,13 @@
     <t xml:space="preserve">16.8441066741943</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4974422454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.668399810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6304111480713</t>
+    <t xml:space="preserve">16.497444152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6683979034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6304092407227</t>
   </si>
   <si>
     <t xml:space="preserve">16.9248371124268</t>
@@ -2354,7 +2354,7 @@
     <t xml:space="preserve">17.2857475280762</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2002696990967</t>
+    <t xml:space="preserve">17.2002716064453</t>
   </si>
   <si>
     <t xml:space="preserve">16.696891784668</t>
@@ -2363,7 +2363,7 @@
     <t xml:space="preserve">16.7538776397705</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2267570495605</t>
+    <t xml:space="preserve">16.2267551422119</t>
   </si>
   <si>
     <t xml:space="preserve">16.1887664794922</t>
@@ -2381,16 +2381,16 @@
     <t xml:space="preserve">16.1032905578613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0178089141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4811906814575</t>
+    <t xml:space="preserve">16.0178108215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4811916351318</t>
   </si>
   <si>
     <t xml:space="preserve">15.5381784439087</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5619230270386</t>
+    <t xml:space="preserve">15.5619220733643</t>
   </si>
   <si>
     <t xml:space="preserve">15.1725187301636</t>
@@ -2402,7 +2402,7 @@
     <t xml:space="preserve">15.3577222824097</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5904150009155</t>
+    <t xml:space="preserve">15.5904159545898</t>
   </si>
   <si>
     <t xml:space="preserve">15.4716949462891</t>
@@ -2411,7 +2411,7 @@
     <t xml:space="preserve">15.680643081665</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4052085876465</t>
+    <t xml:space="preserve">15.4052095413208</t>
   </si>
   <si>
     <t xml:space="preserve">15.324481010437</t>
@@ -2423,7 +2423,7 @@
     <t xml:space="preserve">15.2579975128174</t>
   </si>
   <si>
-    <t xml:space="preserve">15.177267074585</t>
+    <t xml:space="preserve">15.1772661209106</t>
   </si>
   <si>
     <t xml:space="preserve">15.068042755127</t>
@@ -2438,13 +2438,13 @@
     <t xml:space="preserve">15.9608240127563</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7661218643188</t>
+    <t xml:space="preserve">15.7661228179932</t>
   </si>
   <si>
     <t xml:space="preserve">15.8800926208496</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9085874557495</t>
+    <t xml:space="preserve">15.9085865020752</t>
   </si>
   <si>
     <t xml:space="preserve">15.922833442688</t>
@@ -2459,10 +2459,10 @@
     <t xml:space="preserve">16.4024639129639</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5781726837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5734233856201</t>
+    <t xml:space="preserve">16.5781707763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5734252929688</t>
   </si>
   <si>
     <t xml:space="preserve">16.6066665649414</t>
@@ -2471,10 +2471,10 @@
     <t xml:space="preserve">17.2809982299805</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9723262786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4404563903809</t>
+    <t xml:space="preserve">16.9723281860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4404544830322</t>
   </si>
   <si>
     <t xml:space="preserve">16.3074893951416</t>
@@ -2486,40 +2486,40 @@
     <t xml:space="preserve">16.3977165222168</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6209106445312</t>
+    <t xml:space="preserve">16.6209125518799</t>
   </si>
   <si>
     <t xml:space="preserve">17.3047428131104</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1290378570557</t>
+    <t xml:space="preserve">17.129035949707</t>
   </si>
   <si>
     <t xml:space="preserve">17.1860218048096</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6873970031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9695796966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1120452880859</t>
+    <t xml:space="preserve">16.6873950958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9695816040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1120433807373</t>
   </si>
   <si>
     <t xml:space="preserve">17.4282131195068</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3474826812744</t>
+    <t xml:space="preserve">17.3474807739258</t>
   </si>
   <si>
     <t xml:space="preserve">17.2477569580078</t>
   </si>
   <si>
-    <t xml:space="preserve">17.337984085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4092178344727</t>
+    <t xml:space="preserve">17.3379859924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.409215927124</t>
   </si>
   <si>
     <t xml:space="preserve">17.62766456604</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">17.803373336792</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1167945861816</t>
+    <t xml:space="preserve">18.116792678833</t>
   </si>
   <si>
     <t xml:space="preserve">17.8556079864502</t>
@@ -2543,16 +2543,16 @@
     <t xml:space="preserve">17.8081188201904</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0028228759766</t>
+    <t xml:space="preserve">18.0028209686279</t>
   </si>
   <si>
     <t xml:space="preserve">17.6704025268555</t>
   </si>
   <si>
-    <t xml:space="preserve">17.622917175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6799030303955</t>
+    <t xml:space="preserve">17.6229152679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6799011230469</t>
   </si>
   <si>
     <t xml:space="preserve">17.9885749816895</t>
@@ -2564,16 +2564,16 @@
     <t xml:space="preserve">18.0930500030518</t>
   </si>
   <si>
-    <t xml:space="preserve">17.90309715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8508605957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2620029449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.228759765625</t>
+    <t xml:space="preserve">17.9030952453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8508586883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2620048522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2287616729736</t>
   </si>
   <si>
     <t xml:space="preserve">17.0957946777344</t>
@@ -2585,7 +2585,7 @@
     <t xml:space="preserve">16.6161632537842</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5924186706543</t>
+    <t xml:space="preserve">16.5924167633057</t>
   </si>
   <si>
     <t xml:space="preserve">15.8611001968384</t>
@@ -2594,13 +2594,13 @@
     <t xml:space="preserve">16.2694988250732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2979888916016</t>
+    <t xml:space="preserve">16.2979907989502</t>
   </si>
   <si>
     <t xml:space="preserve">16.1175346374512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.846851348877</t>
+    <t xml:space="preserve">15.8468523025513</t>
   </si>
   <si>
     <t xml:space="preserve">16.3217353820801</t>
@@ -2612,13 +2612,13 @@
     <t xml:space="preserve">15.7803688049316</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7186336517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3434762954712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9845685958862</t>
+    <t xml:space="preserve">15.7186317443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3434772491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9845676422119</t>
   </si>
   <si>
     <t xml:space="preserve">15.7471265792847</t>
@@ -2627,10 +2627,10 @@
     <t xml:space="preserve">15.6046619415283</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7043867111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8848419189453</t>
+    <t xml:space="preserve">15.7043857574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8848428726196</t>
   </si>
   <si>
     <t xml:space="preserve">15.5429258346558</t>
@@ -2642,22 +2642,22 @@
     <t xml:space="preserve">13.8096027374268</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8665895462036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1420211791992</t>
+    <t xml:space="preserve">13.8665885925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1420221328735</t>
   </si>
   <si>
     <t xml:space="preserve">13.6054029464722</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5721607208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0735340118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0497894287109</t>
+    <t xml:space="preserve">13.5721616744995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0735349655151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0497903823853</t>
   </si>
   <si>
     <t xml:space="preserve">12.9738092422485</t>
@@ -2678,7 +2678,7 @@
     <t xml:space="preserve">10.7845964431763</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08166694641113</t>
+    <t xml:space="preserve">9.08166599273682</t>
   </si>
   <si>
     <t xml:space="preserve">9.65437507629395</t>
@@ -2693,7 +2693,7 @@
     <t xml:space="preserve">9.4976634979248</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6183891296387</t>
+    <t xml:space="preserve">10.6183881759644</t>
   </si>
   <si>
     <t xml:space="preserve">11.8625822067261</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">13.3964538574219</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9690589904785</t>
+    <t xml:space="preserve">12.9690599441528</t>
   </si>
   <si>
     <t xml:space="preserve">12.2519855499268</t>
@@ -2717,13 +2717,13 @@
     <t xml:space="preserve">11.9195680618286</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4921731948853</t>
+    <t xml:space="preserve">11.4921741485596</t>
   </si>
   <si>
     <t xml:space="preserve">11.2072429656982</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1597547531128</t>
+    <t xml:space="preserve">11.1597557067871</t>
   </si>
   <si>
     <t xml:space="preserve">11.1882476806641</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">11.5586566925049</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6251401901245</t>
+    <t xml:space="preserve">11.6251411437988</t>
   </si>
   <si>
     <t xml:space="preserve">11.9765539169312</t>
@@ -2753,22 +2753,22 @@
     <t xml:space="preserve">10.8178396224976</t>
   </si>
   <si>
-    <t xml:space="preserve">10.399941444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4474296569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3809471130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7323608398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9128150939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.722861289978</t>
+    <t xml:space="preserve">10.3999404907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4474306106567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3809461593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7323598861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9128160476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7228622436523</t>
   </si>
   <si>
     <t xml:space="preserve">10.3049659729004</t>
@@ -2780,19 +2780,19 @@
     <t xml:space="preserve">10.3144626617432</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3429565429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4094390869141</t>
+    <t xml:space="preserve">10.3429555892944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4094400405884</t>
   </si>
   <si>
     <t xml:space="preserve">10.2574768066406</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0295333862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9060640335083</t>
+    <t xml:space="preserve">10.0295324325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90606307983398</t>
   </si>
   <si>
     <t xml:space="preserve">9.89656543731689</t>
@@ -2801,10 +2801,10 @@
     <t xml:space="preserve">9.64962577819824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78259468078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4949188232422</t>
+    <t xml:space="preserve">9.78259372711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4949178695679</t>
   </si>
   <si>
     <t xml:space="preserve">12.346962928772</t>
@@ -2825,13 +2825,13 @@
     <t xml:space="preserve">13.6576404571533</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2872314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1542654037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8218460083008</t>
+    <t xml:space="preserve">13.2872304916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1542644500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8218469619751</t>
   </si>
   <si>
     <t xml:space="preserve">11.8815774917603</t>
@@ -2843,10 +2843,10 @@
     <t xml:space="preserve">12.062032699585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1190185546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2899770736694</t>
+    <t xml:space="preserve">12.1190195083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2899761199951</t>
   </si>
   <si>
     <t xml:space="preserve">12.3089714050293</t>
@@ -2858,16 +2858,16 @@
     <t xml:space="preserve">12.5749063491821</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5844039916992</t>
+    <t xml:space="preserve">12.5844049453735</t>
   </si>
   <si>
     <t xml:space="preserve">11.9955492019653</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8055973052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5111684799194</t>
+    <t xml:space="preserve">11.8055963516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5111694335938</t>
   </si>
   <si>
     <t xml:space="preserve">11.7296152114868</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">11.5206661224365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7581071853638</t>
+    <t xml:space="preserve">11.7581081390381</t>
   </si>
   <si>
     <t xml:space="preserve">11.5871496200562</t>
@@ -2897,7 +2897,7 @@
     <t xml:space="preserve">11.1787509918213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2262382507324</t>
+    <t xml:space="preserve">11.2262372970581</t>
   </si>
   <si>
     <t xml:space="preserve">11.2452335357666</t>
@@ -2909,7 +2909,7 @@
     <t xml:space="preserve">11.1312627792358</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0267868041992</t>
+    <t xml:space="preserve">11.0267877578735</t>
   </si>
   <si>
     <t xml:space="preserve">11.0837736129761</t>
@@ -2918,7 +2918,7 @@
     <t xml:space="preserve">10.8368349075317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0552816390991</t>
+    <t xml:space="preserve">11.0552806854248</t>
   </si>
   <si>
     <t xml:space="preserve">11.2167415618896</t>
@@ -2936,13 +2936,13 @@
     <t xml:space="preserve">10.3619508743286</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6441354751587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.330714225769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0932722091675</t>
+    <t xml:space="preserve">11.644136428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3307132720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0932712554932</t>
   </si>
   <si>
     <t xml:space="preserve">10.9603033065796</t>
@@ -2951,7 +2951,7 @@
     <t xml:space="preserve">10.7608528137207</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7798490524292</t>
+    <t xml:space="preserve">10.7798500061035</t>
   </si>
   <si>
     <t xml:space="preserve">10.6753740310669</t>
@@ -2963,7 +2963,7 @@
     <t xml:space="preserve">11.4636793136597</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3971967697144</t>
+    <t xml:space="preserve">11.3971977233887</t>
   </si>
   <si>
     <t xml:space="preserve">11.5016708374023</t>
@@ -2978,28 +2978,28 @@
     <t xml:space="preserve">11.4256896972656</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5179214477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5654096603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0810289382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6821260452271</t>
+    <t xml:space="preserve">12.5179204940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.565408706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0810279846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6821269989014</t>
   </si>
   <si>
     <t xml:space="preserve">11.6061458587646</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1095209121704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0145444869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9385633468628</t>
+    <t xml:space="preserve">12.1095218658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0145435333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9385623931885</t>
   </si>
   <si>
     <t xml:space="preserve">11.9575576782227</t>
@@ -3014,7 +3014,7 @@
     <t xml:space="preserve">12.2804794311523</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6793823242188</t>
+    <t xml:space="preserve">12.6793813705444</t>
   </si>
   <si>
     <t xml:space="preserve">12.6034002304077</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">12.2044982910156</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4039497375488</t>
+    <t xml:space="preserve">12.4039487838745</t>
   </si>
   <si>
     <t xml:space="preserve">12.8978271484375</t>
@@ -3047,16 +3047,16 @@
     <t xml:space="preserve">10.6943693161011</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5139141082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7988433837891</t>
+    <t xml:space="preserve">10.5139131546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7988443374634</t>
   </si>
   <si>
     <t xml:space="preserve">11.0647783279419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.359206199646</t>
+    <t xml:space="preserve">11.3592052459717</t>
   </si>
   <si>
     <t xml:space="preserve">12.3659582138062</t>
@@ -3068,10 +3068,10 @@
     <t xml:space="preserve">13.3537158966064</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7811098098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7146272659302</t>
+    <t xml:space="preserve">13.7811107635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7146263122559</t>
   </si>
   <si>
     <t xml:space="preserve">13.9235744476318</t>
@@ -3080,10 +3080,10 @@
     <t xml:space="preserve">13.9330730438232</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2369985580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3414716720581</t>
+    <t xml:space="preserve">14.2369976043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3414726257324</t>
   </si>
   <si>
     <t xml:space="preserve">14.0470447540283</t>
@@ -3101,31 +3101,31 @@
     <t xml:space="preserve">14.2464952468872</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4269514083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4649419784546</t>
+    <t xml:space="preserve">14.4269504547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4649410247803</t>
   </si>
   <si>
     <t xml:space="preserve">14.9113321304321</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4934349060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3509702682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5979089736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7498712539673</t>
+    <t xml:space="preserve">14.4934358596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3509693145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5979080200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7498722076416</t>
   </si>
   <si>
     <t xml:space="preserve">15.1487741470337</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8828392028809</t>
+    <t xml:space="preserve">14.8828401565552</t>
   </si>
   <si>
     <t xml:space="preserve">14.8543462753296</t>
@@ -3134,7 +3134,7 @@
     <t xml:space="preserve">14.7593698501587</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3794631958008</t>
+    <t xml:space="preserve">14.3794641494751</t>
   </si>
   <si>
     <t xml:space="preserve">14.5694160461426</t>
@@ -3149,16 +3149,16 @@
     <t xml:space="preserve">15.1107835769653</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0632953643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9493227005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7688674926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7118816375732</t>
+    <t xml:space="preserve">15.0632944107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9493217468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7688684463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7118806838989</t>
   </si>
   <si>
     <t xml:space="preserve">14.5884113311768</t>
@@ -3173,10 +3173,10 @@
     <t xml:space="preserve">14.5504207611084</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5314254760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9615659713745</t>
+    <t xml:space="preserve">14.5314264297485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9615650177002</t>
   </si>
   <si>
     <t xml:space="preserve">14.2085056304932</t>
@@ -3191,10 +3191,10 @@
     <t xml:space="preserve">14.6833877563477</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0537967681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8041124343872</t>
+    <t xml:space="preserve">15.0537977218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8041133880615</t>
   </si>
   <si>
     <t xml:space="preserve">15.6711454391479</t>
@@ -3224,7 +3224,7 @@
     <t xml:space="preserve">15.006308555603</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0822906494141</t>
+    <t xml:space="preserve">15.0822896957397</t>
   </si>
   <si>
     <t xml:space="preserve">14.9778165817261</t>
@@ -3233,7 +3233,7 @@
     <t xml:space="preserve">14.6928853988647</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7783641815186</t>
+    <t xml:space="preserve">14.7783651351929</t>
   </si>
   <si>
     <t xml:space="preserve">14.8258533477783</t>
@@ -3257,31 +3257,31 @@
     <t xml:space="preserve">14.9873132705688</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8705968856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0225582122803</t>
+    <t xml:space="preserve">15.8705959320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0225601196289</t>
   </si>
   <si>
     <t xml:space="preserve">16.0320568084717</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8231067657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9370803833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7376289367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4906883239746</t>
+    <t xml:space="preserve">15.8231077194214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9370794296265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7376279830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4906892776489</t>
   </si>
   <si>
     <t xml:space="preserve">15.7091360092163</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3102350234985</t>
+    <t xml:space="preserve">15.3102340698242</t>
   </si>
   <si>
     <t xml:space="preserve">15.3672199249268</t>
@@ -3290,10 +3290,10 @@
     <t xml:space="preserve">15.3387269973755</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6996383666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6853923797607</t>
+    <t xml:space="preserve">15.6996374130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6853914260864</t>
   </si>
   <si>
     <t xml:space="preserve">15.6189079284668</t>
@@ -3302,13 +3302,13 @@
     <t xml:space="preserve">15.428955078125</t>
   </si>
   <si>
-    <t xml:space="preserve">15.637903213501</t>
+    <t xml:space="preserve">15.6379022598267</t>
   </si>
   <si>
     <t xml:space="preserve">16.7396335601807</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8678531646729</t>
+    <t xml:space="preserve">16.8678512573242</t>
   </si>
   <si>
     <t xml:space="preserve">16.8725986480713</t>
@@ -3332,7 +3332,7 @@
     <t xml:space="preserve">17.2904968261719</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0815505981445</t>
+    <t xml:space="preserve">17.0815486907959</t>
   </si>
   <si>
     <t xml:space="preserve">17.0245628356934</t>
@@ -3347,28 +3347,28 @@
     <t xml:space="preserve">17.4614543914795</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4187164306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2117691040039</t>
+    <t xml:space="preserve">17.4187145233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2117710113525</t>
   </si>
   <si>
     <t xml:space="preserve">18.3589839935303</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1975231170654</t>
+    <t xml:space="preserve">18.1975250244141</t>
   </si>
   <si>
     <t xml:space="preserve">18.1500358581543</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2307662963867</t>
+    <t xml:space="preserve">18.2307643890381</t>
   </si>
   <si>
     <t xml:space="preserve">18.0360641479492</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9125957489014</t>
+    <t xml:space="preserve">17.9125938415527</t>
   </si>
   <si>
     <t xml:space="preserve">17.9553356170654</t>
@@ -3380,10 +3380,10 @@
     <t xml:space="preserve">18.0408134460449</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3304920196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3209934234619</t>
+    <t xml:space="preserve">18.3304901123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3209953308105</t>
   </si>
   <si>
     <t xml:space="preserve">18.368480682373</t>
@@ -3392,7 +3392,7 @@
     <t xml:space="preserve">18.3019981384277</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3542366027832</t>
+    <t xml:space="preserve">18.3542346954346</t>
   </si>
   <si>
     <t xml:space="preserve">18.3969745635986</t>
@@ -3404,10 +3404,10 @@
     <t xml:space="preserve">18.297248840332</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1690292358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.183277130127</t>
+    <t xml:space="preserve">18.1690311431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1832790374756</t>
   </si>
   <si>
     <t xml:space="preserve">18.4444637298584</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">18.6961498260498</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5584373474121</t>
+    <t xml:space="preserve">18.5584354400635</t>
   </si>
   <si>
     <t xml:space="preserve">18.3352394104004</t>
@@ -3431,7 +3431,7 @@
     <t xml:space="preserve">17.1527805328369</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1812744140625</t>
+    <t xml:space="preserve">17.1812725067139</t>
   </si>
   <si>
     <t xml:space="preserve">17.0673007965088</t>
@@ -3446,7 +3446,7 @@
     <t xml:space="preserve">16.5021915435791</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7253856658936</t>
+    <t xml:space="preserve">16.7253875732422</t>
   </si>
   <si>
     <t xml:space="preserve">16.877347946167</t>
@@ -3455,7 +3455,7 @@
     <t xml:space="preserve">16.4214611053467</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9798212051392</t>
+    <t xml:space="preserve">15.9798202514648</t>
   </si>
   <si>
     <t xml:space="preserve">16.0985412597656</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">16.2505035400391</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4736976623535</t>
+    <t xml:space="preserve">16.4736957550049</t>
   </si>
   <si>
     <t xml:space="preserve">16.169771194458</t>
@@ -3479,19 +3479,19 @@
     <t xml:space="preserve">16.0368061065674</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9988136291504</t>
+    <t xml:space="preserve">15.9988145828247</t>
   </si>
   <si>
     <t xml:space="preserve">16.2600021362305</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0652980804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0510501861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1100387573242</t>
+    <t xml:space="preserve">16.065299987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0510520935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1100406646729</t>
   </si>
   <si>
     <t xml:space="preserve">17.3949718475342</t>
@@ -3506,7 +3506,7 @@
     <t xml:space="preserve">17.6609039306641</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0008163452148</t>
+    <t xml:space="preserve">17.0008182525635</t>
   </si>
   <si>
     <t xml:space="preserve">16.6731491088867</t>
@@ -3515,10 +3515,10 @@
     <t xml:space="preserve">16.5164375305176</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7328815460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7423791885376</t>
+    <t xml:space="preserve">15.7328805923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7423782348633</t>
   </si>
   <si>
     <t xml:space="preserve">16.1460285186768</t>
@@ -3527,13 +3527,13 @@
     <t xml:space="preserve">15.9275827407837</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9703226089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6541538238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7586269378662</t>
+    <t xml:space="preserve">15.9703216552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6541519165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7586288452148</t>
   </si>
   <si>
     <t xml:space="preserve">18.0123195648193</t>
@@ -3551,13 +3551,13 @@
     <t xml:space="preserve">16.8251113891602</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7206363677979</t>
+    <t xml:space="preserve">16.7206382751465</t>
   </si>
   <si>
     <t xml:space="preserve">16.9628295898438</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9438323974609</t>
+    <t xml:space="preserve">16.9438304901123</t>
   </si>
   <si>
     <t xml:space="preserve">16.8298587799072</t>
@@ -3566,7 +3566,7 @@
     <t xml:space="preserve">16.9913196563721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8346080780029</t>
+    <t xml:space="preserve">16.8346099853516</t>
   </si>
   <si>
     <t xml:space="preserve">17.0435581207275</t>
@@ -3578,19 +3578,19 @@
     <t xml:space="preserve">16.7111377716064</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2145156860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4424591064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3427352905273</t>
+    <t xml:space="preserve">17.2145175933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4424610137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3427333831787</t>
   </si>
   <si>
     <t xml:space="preserve">17.4662036895752</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7178916931152</t>
+    <t xml:space="preserve">17.7178936004639</t>
   </si>
   <si>
     <t xml:space="preserve">17.7748775482178</t>
@@ -3599,10 +3599,10 @@
     <t xml:space="preserve">17.6988964080811</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1405391693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7008991241455</t>
+    <t xml:space="preserve">18.1405372619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7009010314941</t>
   </si>
   <si>
     <t xml:space="preserve">18.7911281585693</t>
@@ -3617,10 +3617,10 @@
     <t xml:space="preserve">18.4302177429199</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5536880493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7626323699951</t>
+    <t xml:space="preserve">18.5536861419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7626342773438</t>
   </si>
   <si>
     <t xml:space="preserve">19.0903053283691</t>
@@ -3641,13 +3641,13 @@
     <t xml:space="preserve">20.5529441833496</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6221733093262</t>
+    <t xml:space="preserve">19.6221752166748</t>
   </si>
   <si>
     <t xml:space="preserve">19.1377925872803</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6316699981689</t>
+    <t xml:space="preserve">19.6316719055176</t>
   </si>
   <si>
     <t xml:space="preserve">20.4579677581787</t>
@@ -3656,40 +3656,40 @@
     <t xml:space="preserve">20.6289253234863</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0373249053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4457225799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9898376464844</t>
+    <t xml:space="preserve">21.0373229980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4457244873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9898357391357</t>
   </si>
   <si>
     <t xml:space="preserve">20.7523956298828</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6384239196777</t>
+    <t xml:space="preserve">20.6384220123291</t>
   </si>
   <si>
     <t xml:space="preserve">20.1635398864746</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0970554351807</t>
+    <t xml:space="preserve">20.0970573425293</t>
   </si>
   <si>
     <t xml:space="preserve">20.7903861999512</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7144050598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0278282165527</t>
+    <t xml:space="preserve">20.7144031524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0278263092041</t>
   </si>
   <si>
     <t xml:space="preserve">21.0183296203613</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0943088531494</t>
+    <t xml:space="preserve">21.094310760498</t>
   </si>
   <si>
     <t xml:space="preserve">21.4172306060791</t>
@@ -3707,7 +3707,7 @@
     <t xml:space="preserve">22.0820693969727</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5976867675781</t>
+    <t xml:space="preserve">21.5976886749268</t>
   </si>
   <si>
     <t xml:space="preserve">21.6261806488037</t>
@@ -3716,10 +3716,10 @@
     <t xml:space="preserve">19.4797096252441</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0998020172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5366954803467</t>
+    <t xml:space="preserve">19.0998001098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.536693572998</t>
   </si>
   <si>
     <t xml:space="preserve">19.2517642974854</t>
@@ -3731,7 +3731,7 @@
     <t xml:space="preserve">18.0550594329834</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4946956634521</t>
+    <t xml:space="preserve">17.4946975708008</t>
   </si>
   <si>
     <t xml:space="preserve">18.2212677001953</t>
@@ -3761,13 +3761,13 @@
     <t xml:space="preserve">18.1452865600586</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5679340362549</t>
+    <t xml:space="preserve">18.5679321289062</t>
   </si>
   <si>
     <t xml:space="preserve">18.68190574646</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7721328735352</t>
+    <t xml:space="preserve">18.7721309661865</t>
   </si>
   <si>
     <t xml:space="preserve">18.8006267547607</t>
@@ -3809,10 +3809,10 @@
     <t xml:space="preserve">15.9133348464966</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3529739379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4574480056763</t>
+    <t xml:space="preserve">15.3529748916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4574489593506</t>
   </si>
   <si>
     <t xml:space="preserve">14.8733415603638</t>
@@ -3833,7 +3833,7 @@
     <t xml:space="preserve">15.2532472610474</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5191812515259</t>
+    <t xml:space="preserve">15.5191822052002</t>
   </si>
   <si>
     <t xml:space="preserve">15.8278579711914</t>
@@ -3857,7 +3857,7 @@
     <t xml:space="preserve">15.6521492004395</t>
   </si>
   <si>
-    <t xml:space="preserve">15.889591217041</t>
+    <t xml:space="preserve">15.8895902633667</t>
   </si>
   <si>
     <t xml:space="preserve">15.5096855163574</t>
@@ -3869,10 +3869,10 @@
     <t xml:space="preserve">14.8638439178467</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1392765045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7851181030273</t>
+    <t xml:space="preserve">15.1392755508423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7851190567017</t>
   </si>
   <si>
     <t xml:space="preserve">14.3034820556641</t>
@@ -3881,7 +3881,7 @@
     <t xml:space="preserve">14.3224773406982</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8285999298096</t>
+    <t xml:space="preserve">13.8285989761353</t>
   </si>
   <si>
     <t xml:space="preserve">12.8123483657837</t>
@@ -3893,7 +3893,7 @@
     <t xml:space="preserve">14.1990070343018</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0158061981201</t>
+    <t xml:space="preserve">15.0158071517944</t>
   </si>
   <si>
     <t xml:space="preserve">14.5219278335571</t>
@@ -5955,6 +5955,9 @@
   </si>
   <si>
     <t xml:space="preserve">6.28499984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23999977111816</t>
   </si>
 </sst>
 </file>
@@ -71111,7 +71114,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.6495138889</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>372425</v>
@@ -71132,6 +71135,32 @@
         <v>1980</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.6495601852</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>380430</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>6.28000020980835</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>6.09499979019165</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>6.27500009536743</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>6.23999977111816</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>1981</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1984" uniqueCount="1984">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1985" uniqueCount="1985">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2763519287109</t>
+    <t xml:space="preserve">18.2763500213623</t>
   </si>
   <si>
     <t xml:space="preserve">SFER.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0109672546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4978828430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9401969909668</t>
+    <t xml:space="preserve">18.01096534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4978809356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9401950836182</t>
   </si>
   <si>
     <t xml:space="preserve">17.6836528778076</t>
   </si>
   <si>
-    <t xml:space="preserve">18.249813079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4086742401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1344356536865</t>
+    <t xml:space="preserve">18.2498149871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4086723327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1344375610352</t>
   </si>
   <si>
     <t xml:space="preserve">18.8425121307373</t>
@@ -71,46 +71,46 @@
     <t xml:space="preserve">18.4621238708496</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2852001190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0994281768799</t>
+    <t xml:space="preserve">18.2851982116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0994262695312</t>
   </si>
   <si>
     <t xml:space="preserve">17.6394214630127</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5686511993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1878890991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4798145294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2232761383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7632656097412</t>
+    <t xml:space="preserve">17.5686531066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1878871917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4798126220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2232723236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7632694244385</t>
   </si>
   <si>
     <t xml:space="preserve">18.3913536071777</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6744327545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9578876495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2055816650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2586555480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0817356109619</t>
+    <t xml:space="preserve">18.674430847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9578857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2055835723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2586574554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0817337036133</t>
   </si>
   <si>
     <t xml:space="preserve">17.3563423156738</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">16.9051818847656</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1617240905762</t>
+    <t xml:space="preserve">17.1617221832275</t>
   </si>
   <si>
     <t xml:space="preserve">16.6486415863037</t>
@@ -128,40 +128,40 @@
     <t xml:space="preserve">17.0201835632324</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4890365600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6305732727051</t>
+    <t xml:space="preserve">17.4890384674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6305751800537</t>
   </si>
   <si>
     <t xml:space="preserve">18.4090442657471</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4532775878906</t>
+    <t xml:space="preserve">18.453275680542</t>
   </si>
   <si>
     <t xml:space="preserve">18.9752063751221</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1348133087158</t>
+    <t xml:space="preserve">18.1348114013672</t>
   </si>
   <si>
     <t xml:space="preserve">17.3121089935303</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9048118591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3471202850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0194358825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0017414093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8513603210449</t>
+    <t xml:space="preserve">17.9048099517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3471221923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0194320678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0017433166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8513584136963</t>
   </si>
   <si>
     <t xml:space="preserve">19.3113613128662</t>
@@ -170,19 +170,19 @@
     <t xml:space="preserve">19.9925231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9482917785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7271366119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3379001617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6475200653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9836769104004</t>
+    <t xml:space="preserve">19.9482936859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7271385192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3379020690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.647518157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9836807250977</t>
   </si>
   <si>
     <t xml:space="preserve">19.1167449951172</t>
@@ -197,10 +197,10 @@
     <t xml:space="preserve">20.1782932281494</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4971332550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4705944061279</t>
+    <t xml:space="preserve">19.4971351623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4705963134766</t>
   </si>
   <si>
     <t xml:space="preserve">18.9663619995117</t>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">19.4794425964355</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9129085540771</t>
+    <t xml:space="preserve">19.9129066467285</t>
   </si>
   <si>
     <t xml:space="preserve">19.8686752319336</t>
@@ -218,10 +218,10 @@
     <t xml:space="preserve">19.4175186157227</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8690490722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8336658477783</t>
+    <t xml:space="preserve">18.8690509796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.833667755127</t>
   </si>
   <si>
     <t xml:space="preserve">18.5151996612549</t>
@@ -239,13 +239,13 @@
     <t xml:space="preserve">18.9486675262451</t>
   </si>
   <si>
-    <t xml:space="preserve">18.798282623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8778953552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2936706542969</t>
+    <t xml:space="preserve">18.7982788085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8778972625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2936687469482</t>
   </si>
   <si>
     <t xml:space="preserve">18.8071269989014</t>
@@ -254,34 +254,34 @@
     <t xml:space="preserve">18.3205814361572</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3648109436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8251934051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0640411376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3117351531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8782691955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0021190643311</t>
+    <t xml:space="preserve">18.3648128509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8251914978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0640430450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3117370605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.878267288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0021171569824</t>
   </si>
   <si>
     <t xml:space="preserve">17.7190399169922</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4448051452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1440296173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5509605407715</t>
+    <t xml:space="preserve">17.444803237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1440315246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5509586334229</t>
   </si>
   <si>
     <t xml:space="preserve">17.9844264984131</t>
@@ -290,19 +290,19 @@
     <t xml:space="preserve">17.4182662963867</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9313468933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7367305755615</t>
+    <t xml:space="preserve">17.9313488006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7367286682129</t>
   </si>
   <si>
     <t xml:space="preserve">17.648265838623</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5939407348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.81125831604</t>
+    <t xml:space="preserve">17.5939388275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8112602233887</t>
   </si>
   <si>
     <t xml:space="preserve">17.7025966644287</t>
@@ -311,7 +311,7 @@
     <t xml:space="preserve">17.530553817749</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4128360748291</t>
+    <t xml:space="preserve">17.4128379821777</t>
   </si>
   <si>
     <t xml:space="preserve">17.3041763305664</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">17.4309463500977</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4852752685547</t>
+    <t xml:space="preserve">17.4852771759033</t>
   </si>
   <si>
     <t xml:space="preserve">17.7478733062744</t>
@@ -335,55 +335,55 @@
     <t xml:space="preserve">17.1502418518066</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7155990600586</t>
+    <t xml:space="preserve">16.71559715271</t>
   </si>
   <si>
     <t xml:space="preserve">16.5435543060303</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0415802001953</t>
+    <t xml:space="preserve">17.0415782928467</t>
   </si>
   <si>
     <t xml:space="preserve">17.0778026580811</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8384246826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9380264282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7297630310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8655891418457</t>
+    <t xml:space="preserve">17.8384265899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9380283355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7297611236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8655872344971</t>
   </si>
   <si>
     <t xml:space="preserve">18.1825141906738</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8514251708984</t>
+    <t xml:space="preserve">16.8514232635498</t>
   </si>
   <si>
     <t xml:space="preserve">16.3896198272705</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6793785095215</t>
+    <t xml:space="preserve">16.6793804168701</t>
   </si>
   <si>
     <t xml:space="preserve">16.2628479003906</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5254440307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6069374084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8061466217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8242607116699</t>
+    <t xml:space="preserve">16.5254459381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6069393157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8061504364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8242588043213</t>
   </si>
   <si>
     <t xml:space="preserve">16.0726928710938</t>
@@ -398,25 +398,25 @@
     <t xml:space="preserve">16.4439468383789</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6974906921387</t>
+    <t xml:space="preserve">16.69748878479</t>
   </si>
   <si>
     <t xml:space="preserve">17.0959091186523</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1321296691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0868587493896</t>
+    <t xml:space="preserve">17.1321315765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.086856842041</t>
   </si>
   <si>
     <t xml:space="preserve">17.0325260162354</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3403968811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9018077850342</t>
+    <t xml:space="preserve">17.3403949737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9018096923828</t>
   </si>
   <si>
     <t xml:space="preserve">18.1372413635254</t>
@@ -431,19 +431,19 @@
     <t xml:space="preserve">18.6352672576904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0699062347412</t>
+    <t xml:space="preserve">19.0699081420898</t>
   </si>
   <si>
     <t xml:space="preserve">19.2147903442383</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6262130737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4994430541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2187347412109</t>
+    <t xml:space="preserve">18.6262111663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4994411468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2187366485596</t>
   </si>
   <si>
     <t xml:space="preserve">18.716760635376</t>
@@ -467,19 +467,19 @@
     <t xml:space="preserve">18.6624336242676</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4722766876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6171550750732</t>
+    <t xml:space="preserve">18.4722747802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6171569824219</t>
   </si>
   <si>
     <t xml:space="preserve">18.7529811859131</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9703025817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6805400848389</t>
+    <t xml:space="preserve">18.9703044891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6805419921875</t>
   </si>
   <si>
     <t xml:space="preserve">18.6081008911133</t>
@@ -524,13 +524,13 @@
     <t xml:space="preserve">19.1604595184326</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9391937255859</t>
+    <t xml:space="preserve">19.9391918182373</t>
   </si>
   <si>
     <t xml:space="preserve">20.4553279876709</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3557205200195</t>
+    <t xml:space="preserve">20.3557224273682</t>
   </si>
   <si>
     <t xml:space="preserve">20.3104496002197</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">20.3919429779053</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4643821716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6907615661621</t>
+    <t xml:space="preserve">20.4643840789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6907596588135</t>
   </si>
   <si>
     <t xml:space="preserve">20.8446960449219</t>
@@ -554,10 +554,10 @@
     <t xml:space="preserve">20.4009990692139</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1021842956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5277671813965</t>
+    <t xml:space="preserve">20.1021862030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5277690887451</t>
   </si>
   <si>
     <t xml:space="preserve">20.3647766113281</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">20.03879737854</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1474609375</t>
+    <t xml:space="preserve">20.1474590301514</t>
   </si>
   <si>
     <t xml:space="preserve">20.2289543151855</t>
@@ -593,13 +593,13 @@
     <t xml:space="preserve">20.5006046295166</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5639896392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1836814880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5498237609863</t>
+    <t xml:space="preserve">20.5639877319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1836795806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.549825668335</t>
   </si>
   <si>
     <t xml:space="preserve">19.4140014648438</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">19.5045490264893</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7218723297119</t>
+    <t xml:space="preserve">19.7218704223633</t>
   </si>
   <si>
     <t xml:space="preserve">19.7943115234375</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">19.5226593017578</t>
   </si>
   <si>
-    <t xml:space="preserve">19.830530166626</t>
+    <t xml:space="preserve">19.8305320739746</t>
   </si>
   <si>
     <t xml:space="preserve">19.9120273590088</t>
@@ -626,37 +626,37 @@
     <t xml:space="preserve">19.7490348815918</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0919628143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3002319335938</t>
+    <t xml:space="preserve">18.0919647216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3002300262451</t>
   </si>
   <si>
     <t xml:space="preserve">18.3273963928223</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2459011077881</t>
+    <t xml:space="preserve">18.2458992004395</t>
   </si>
   <si>
     <t xml:space="preserve">18.0104675292969</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7388172149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8565349578857</t>
+    <t xml:space="preserve">17.7388191223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8565330505371</t>
   </si>
   <si>
     <t xml:space="preserve">17.8203144073486</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6392097473145</t>
+    <t xml:space="preserve">17.6392116546631</t>
   </si>
   <si>
     <t xml:space="preserve">18.3455066680908</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3907794952393</t>
+    <t xml:space="preserve">18.3907814025879</t>
   </si>
   <si>
     <t xml:space="preserve">19.1514053344727</t>
@@ -689,22 +689,22 @@
     <t xml:space="preserve">20.2380084991455</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1293487548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1565132141113</t>
+    <t xml:space="preserve">20.1293506622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.15651512146</t>
   </si>
   <si>
     <t xml:space="preserve">20.8084754943848</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6183204650879</t>
+    <t xml:space="preserve">20.6183185577393</t>
   </si>
   <si>
     <t xml:space="preserve">21.4785480499268</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5328788757324</t>
+    <t xml:space="preserve">21.5328807830811</t>
   </si>
   <si>
     <t xml:space="preserve">22.0671272277832</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">22.2935028076172</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3025569915771</t>
+    <t xml:space="preserve">22.3025550842285</t>
   </si>
   <si>
     <t xml:space="preserve">22.3206672668457</t>
@@ -746,22 +746,22 @@
     <t xml:space="preserve">23.0993995666504</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5923156738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3568897247314</t>
+    <t xml:space="preserve">22.5923175811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3568878173828</t>
   </si>
   <si>
     <t xml:space="preserve">22.9092426300049</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1757831573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1395645141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.606481552124</t>
+    <t xml:space="preserve">22.1757850646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1395664215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6064834594727</t>
   </si>
   <si>
     <t xml:space="preserve">23.7513637542725</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">24.1226177215576</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6427040100098</t>
+    <t xml:space="preserve">23.6427021026611</t>
   </si>
   <si>
     <t xml:space="preserve">23.6879768371582</t>
@@ -785,13 +785,13 @@
     <t xml:space="preserve">23.7241992950439</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6336460113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.823802947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6970310211182</t>
+    <t xml:space="preserve">23.6336479187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8238048553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6970329284668</t>
   </si>
   <si>
     <t xml:space="preserve">24.0139598846436</t>
@@ -806,7 +806,7 @@
     <t xml:space="preserve">23.9777374267578</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2946662902832</t>
+    <t xml:space="preserve">24.2946643829346</t>
   </si>
   <si>
     <t xml:space="preserve">24.4304904937744</t>
@@ -815,13 +815,13 @@
     <t xml:space="preserve">24.6115951538086</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7655296325684</t>
+    <t xml:space="preserve">24.765531539917</t>
   </si>
   <si>
     <t xml:space="preserve">25.1911144256592</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3903274536133</t>
+    <t xml:space="preserve">25.3903255462646</t>
   </si>
   <si>
     <t xml:space="preserve">25.4265441894531</t>
@@ -833,7 +833,7 @@
     <t xml:space="preserve">25.6710300445557</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6529216766357</t>
+    <t xml:space="preserve">25.6529197692871</t>
   </si>
   <si>
     <t xml:space="preserve">25.7615795135498</t>
@@ -842,13 +842,13 @@
     <t xml:space="preserve">25.5352058410645</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9556789398193</t>
+    <t xml:space="preserve">24.955680847168</t>
   </si>
   <si>
     <t xml:space="preserve">24.9013500213623</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0643444061279</t>
+    <t xml:space="preserve">25.0643424987793</t>
   </si>
   <si>
     <t xml:space="preserve">24.8017482757568</t>
@@ -872,25 +872,25 @@
     <t xml:space="preserve">25.173002243042</t>
   </si>
   <si>
-    <t xml:space="preserve">25.163948059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3993797302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7253608703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2907199859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1277294158936</t>
+    <t xml:space="preserve">25.1639499664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.399377822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7253589630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2907218933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1277256011963</t>
   </si>
   <si>
     <t xml:space="preserve">25.7434711456299</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5442600250244</t>
+    <t xml:space="preserve">25.544261932373</t>
   </si>
   <si>
     <t xml:space="preserve">25.4808750152588</t>
@@ -899,16 +899,16 @@
     <t xml:space="preserve">25.5080413818359</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2635555267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0824527740479</t>
+    <t xml:space="preserve">25.2635536193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0824546813965</t>
   </si>
   <si>
     <t xml:space="preserve">24.7836380004883</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4214363098145</t>
+    <t xml:space="preserve">24.4214344024658</t>
   </si>
   <si>
     <t xml:space="preserve">24.2674980163574</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">25.5261516571045</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1237812042236</t>
+    <t xml:space="preserve">26.1237831115723</t>
   </si>
   <si>
     <t xml:space="preserve">26.1871681213379</t>
@@ -950,13 +950,13 @@
     <t xml:space="preserve">26.6037006378174</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5946445465088</t>
+    <t xml:space="preserve">26.5946464538574</t>
   </si>
   <si>
     <t xml:space="preserve">25.3088302612305</t>
   </si>
   <si>
-    <t xml:space="preserve">25.326940536499</t>
+    <t xml:space="preserve">25.3269386291504</t>
   </si>
   <si>
     <t xml:space="preserve">25.8340225219727</t>
@@ -965,7 +965,7 @@
     <t xml:space="preserve">25.8984451293945</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0641059875488</t>
+    <t xml:space="preserve">26.0641078948975</t>
   </si>
   <si>
     <t xml:space="preserve">24.7112045288086</t>
@@ -977,13 +977,13 @@
     <t xml:space="preserve">23.2202491760254</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1282119750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9625492095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8705158233643</t>
+    <t xml:space="preserve">23.128210067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9625511169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8705177307129</t>
   </si>
   <si>
     <t xml:space="preserve">22.8613147735596</t>
@@ -992,10 +992,10 @@
     <t xml:space="preserve">23.266263961792</t>
   </si>
   <si>
-    <t xml:space="preserve">23.238655090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0453815460205</t>
+    <t xml:space="preserve">23.2386531829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0453834533691</t>
   </si>
   <si>
     <t xml:space="preserve">22.8889217376709</t>
@@ -1004,7 +1004,7 @@
     <t xml:space="preserve">22.0882263183594</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3183097839355</t>
+    <t xml:space="preserve">22.3183116912842</t>
   </si>
   <si>
     <t xml:space="preserve">22.2262763977051</t>
@@ -1016,28 +1016,28 @@
     <t xml:space="preserve">22.3643283843994</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7416706085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9533500671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8797225952148</t>
+    <t xml:space="preserve">22.7416687011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.95334815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8797206878662</t>
   </si>
   <si>
     <t xml:space="preserve">23.2846698760986</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4871501922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4319267272949</t>
+    <t xml:space="preserve">23.4871482849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4319248199463</t>
   </si>
   <si>
     <t xml:space="preserve">22.8060932159424</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0269737243652</t>
+    <t xml:space="preserve">23.0269756317139</t>
   </si>
   <si>
     <t xml:space="preserve">22.6036167144775</t>
@@ -1061,10 +1061,10 @@
     <t xml:space="preserve">21.6740703582764</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6280536651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1678810119629</t>
+    <t xml:space="preserve">21.6280555725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1678829193115</t>
   </si>
   <si>
     <t xml:space="preserve">21.2046966552734</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">21.5084114074707</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9133586883545</t>
+    <t xml:space="preserve">21.9133605957031</t>
   </si>
   <si>
     <t xml:space="preserve">21.8857517242432</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">21.9685821533203</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6220226287842</t>
+    <t xml:space="preserve">22.6220245361328</t>
   </si>
   <si>
     <t xml:space="preserve">22.3735313415527</t>
@@ -1097,13 +1097,13 @@
     <t xml:space="preserve">22.2170715332031</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4103450775146</t>
+    <t xml:space="preserve">22.4103469848633</t>
   </si>
   <si>
     <t xml:space="preserve">22.5299892425537</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6312294006348</t>
+    <t xml:space="preserve">22.6312274932861</t>
   </si>
   <si>
     <t xml:space="preserve">22.6404323577881</t>
@@ -1118,13 +1118,13 @@
     <t xml:space="preserve">21.6556663513184</t>
   </si>
   <si>
-    <t xml:space="preserve">22.263090133667</t>
+    <t xml:space="preserve">22.2630920410156</t>
   </si>
   <si>
     <t xml:space="preserve">22.539192199707</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3551235198975</t>
+    <t xml:space="preserve">22.3551254272461</t>
   </si>
   <si>
     <t xml:space="preserve">22.0514106750488</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">21.7569026947021</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9961929321289</t>
+    <t xml:space="preserve">21.9961910247803</t>
   </si>
   <si>
     <t xml:space="preserve">21.701681137085</t>
@@ -1160,28 +1160,28 @@
     <t xml:space="preserve">21.8765468597412</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1250381469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7753086090088</t>
+    <t xml:space="preserve">22.1250400543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7753105163574</t>
   </si>
   <si>
     <t xml:space="preserve">22.0238037109375</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9041595458984</t>
+    <t xml:space="preserve">21.9041576385498</t>
   </si>
   <si>
     <t xml:space="preserve">21.6832733154297</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8273525238037</t>
+    <t xml:space="preserve">20.8273544311523</t>
   </si>
   <si>
     <t xml:space="preserve">21.0574417114258</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9470024108887</t>
+    <t xml:space="preserve">20.94700050354</t>
   </si>
   <si>
     <t xml:space="preserve">20.7997455596924</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">21.1034603118896</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0758476257324</t>
+    <t xml:space="preserve">21.0758495330811</t>
   </si>
   <si>
     <t xml:space="preserve">21.3243408203125</t>
@@ -1202,13 +1202,13 @@
     <t xml:space="preserve">22.0974292755127</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8581390380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6372585296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2967338562012</t>
+    <t xml:space="preserve">21.8581409454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6372566223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2967319488525</t>
   </si>
   <si>
     <t xml:space="preserve">20.9746131896973</t>
@@ -1217,7 +1217,7 @@
     <t xml:space="preserve">20.983814239502</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1402740478516</t>
+    <t xml:space="preserve">21.1402721405029</t>
   </si>
   <si>
     <t xml:space="preserve">21.0666446685791</t>
@@ -1229,10 +1229,10 @@
     <t xml:space="preserve">21.0942554473877</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1586818695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0206279754639</t>
+    <t xml:space="preserve">21.1586799621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0206298828125</t>
   </si>
   <si>
     <t xml:space="preserve">21.0022201538086</t>
@@ -1241,34 +1241,34 @@
     <t xml:space="preserve">20.6340827941895</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4500179290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3855895996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.39479637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0082492828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9714393615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0634689331055</t>
+    <t xml:space="preserve">20.4500160217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.385591506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3947944641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0082511901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9714374542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0634708404541</t>
   </si>
   <si>
     <t xml:space="preserve">20.4868297576904</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7445278167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8917808532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.241512298584</t>
+    <t xml:space="preserve">20.7445259094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8917789459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2415103912354</t>
   </si>
   <si>
     <t xml:space="preserve">20.9285945892334</t>
@@ -1277,7 +1277,7 @@
     <t xml:space="preserve">20.2475414276123</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1647109985352</t>
+    <t xml:space="preserve">20.1647090911865</t>
   </si>
   <si>
     <t xml:space="preserve">20.0910816192627</t>
@@ -1310,10 +1310,10 @@
     <t xml:space="preserve">20.5696601867676</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6616954803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.131067276001</t>
+    <t xml:space="preserve">20.661693572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1310691833496</t>
   </si>
   <si>
     <t xml:space="preserve">21.0482406616211</t>
@@ -1328,10 +1328,10 @@
     <t xml:space="preserve">20.8089485168457</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6708946228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7721328735352</t>
+    <t xml:space="preserve">20.6708965301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7721347808838</t>
   </si>
   <si>
     <t xml:space="preserve">19.4652500152588</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">20.229133605957</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5236415863037</t>
+    <t xml:space="preserve">20.5236434936523</t>
   </si>
   <si>
     <t xml:space="preserve">20.6524906158447</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">21.3703575134277</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5176105499268</t>
+    <t xml:space="preserve">21.5176124572754</t>
   </si>
   <si>
     <t xml:space="preserve">20.8549671173096</t>
@@ -1406,7 +1406,7 @@
     <t xml:space="preserve">20.5604553222656</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7169170379639</t>
+    <t xml:space="preserve">20.7169151306152</t>
   </si>
   <si>
     <t xml:space="preserve">20.9377956390381</t>
@@ -1421,22 +1421,22 @@
     <t xml:space="preserve">20.6248798370361</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2751502990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1094913482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6493186950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9990482330322</t>
+    <t xml:space="preserve">20.2751522064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.109489440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6493167877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9990463256836</t>
   </si>
   <si>
     <t xml:space="preserve">20.1278972625732</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3303699493408</t>
+    <t xml:space="preserve">20.3303718566895</t>
   </si>
   <si>
     <t xml:space="preserve">20.8733749389648</t>
@@ -1454,13 +1454,13 @@
     <t xml:space="preserve">20.6432876586914</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6156749725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7261180877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2783260345459</t>
+    <t xml:space="preserve">20.6156768798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7261199951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2783279418945</t>
   </si>
   <si>
     <t xml:space="preserve">21.3151378631592</t>
@@ -1469,7 +1469,7 @@
     <t xml:space="preserve">21.536018371582</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7937183380127</t>
+    <t xml:space="preserve">21.7937164306641</t>
   </si>
   <si>
     <t xml:space="preserve">22.64963722229</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">22.2078704833984</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5668029785156</t>
+    <t xml:space="preserve">22.5668048858643</t>
   </si>
   <si>
     <t xml:space="preserve">22.6128234863281</t>
@@ -1493,7 +1493,7 @@
     <t xml:space="preserve">22.9165344238281</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6864490509033</t>
+    <t xml:space="preserve">22.6864471435547</t>
   </si>
   <si>
     <t xml:space="preserve">22.7324657440186</t>
@@ -1508,19 +1508,19 @@
     <t xml:space="preserve">22.9073295593262</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2754688262939</t>
+    <t xml:space="preserve">23.2754707336426</t>
   </si>
   <si>
     <t xml:space="preserve">22.991304397583</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3090667724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4118766784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9071884155273</t>
+    <t xml:space="preserve">23.3090686798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4118747711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.907190322876</t>
   </si>
   <si>
     <t xml:space="preserve">22.9819564819336</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">23.4586067199707</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6548461914062</t>
+    <t xml:space="preserve">22.6548442840576</t>
   </si>
   <si>
     <t xml:space="preserve">22.7389583587646</t>
@@ -1562,7 +1562,7 @@
     <t xml:space="preserve">23.505334854126</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3838367462158</t>
+    <t xml:space="preserve">23.3838386535645</t>
   </si>
   <si>
     <t xml:space="preserve">23.3931846618652</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">23.2623386383057</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9258804321289</t>
+    <t xml:space="preserve">22.9258823394775</t>
   </si>
   <si>
     <t xml:space="preserve">20.9912452697754</t>
@@ -1613,16 +1613,16 @@
     <t xml:space="preserve">18.0752754211426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6220188140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0799503326416</t>
+    <t xml:space="preserve">18.6220207214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.079948425293</t>
   </si>
   <si>
     <t xml:space="preserve">18.6033306121826</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6360416412354</t>
+    <t xml:space="preserve">18.6360397338867</t>
   </si>
   <si>
     <t xml:space="preserve">18.7949237823486</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">18.7762317657471</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7201538085938</t>
+    <t xml:space="preserve">18.7201557159424</t>
   </si>
   <si>
     <t xml:space="preserve">18.5752906799316</t>
@@ -1640,7 +1640,7 @@
     <t xml:space="preserve">18.3930416107178</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5285606384277</t>
+    <t xml:space="preserve">18.5285587310791</t>
   </si>
   <si>
     <t xml:space="preserve">18.495849609375</t>
@@ -1652,7 +1652,7 @@
     <t xml:space="preserve">18.3883686065674</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4911766052246</t>
+    <t xml:space="preserve">18.491174697876</t>
   </si>
   <si>
     <t xml:space="preserve">18.2435054779053</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">18.2528533935547</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2107925415039</t>
+    <t xml:space="preserve">18.2107944488525</t>
   </si>
   <si>
     <t xml:space="preserve">18.3790245056152</t>
@@ -1691,7 +1691,7 @@
     <t xml:space="preserve">19.1407260894775</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4398002624512</t>
+    <t xml:space="preserve">19.4398021697998</t>
   </si>
   <si>
     <t xml:space="preserve">19.4024143218994</t>
@@ -1706,13 +1706,13 @@
     <t xml:space="preserve">19.3650302886963</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1594219207764</t>
+    <t xml:space="preserve">19.1594200134277</t>
   </si>
   <si>
     <t xml:space="preserve">19.1687660217285</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1126880645752</t>
+    <t xml:space="preserve">19.1126899719238</t>
   </si>
   <si>
     <t xml:space="preserve">19.0939960479736</t>
@@ -1733,16 +1733,16 @@
     <t xml:space="preserve">19.2528800964355</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5239143371582</t>
+    <t xml:space="preserve">19.5239162445068</t>
   </si>
   <si>
     <t xml:space="preserve">19.4211101531982</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8136444091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0753326416016</t>
+    <t xml:space="preserve">19.8136425018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0753307342529</t>
   </si>
   <si>
     <t xml:space="preserve">19.748218536377</t>
@@ -1760,13 +1760,13 @@
     <t xml:space="preserve">19.5706462860107</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2809181213379</t>
+    <t xml:space="preserve">19.2809162139893</t>
   </si>
   <si>
     <t xml:space="preserve">19.1500720977783</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8977279663086</t>
+    <t xml:space="preserve">18.89772605896</t>
   </si>
   <si>
     <t xml:space="preserve">18.8042697906494</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">18.1780853271484</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6453838348389</t>
+    <t xml:space="preserve">18.6453857421875</t>
   </si>
   <si>
     <t xml:space="preserve">17.8556442260742</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">17.949104309082</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1173343658447</t>
+    <t xml:space="preserve">18.1173324584961</t>
   </si>
   <si>
     <t xml:space="preserve">18.2154693603516</t>
@@ -1814,13 +1814,13 @@
     <t xml:space="preserve">19.5986824035645</t>
   </si>
   <si>
-    <t xml:space="preserve">19.589334487915</t>
+    <t xml:space="preserve">19.5893363952637</t>
   </si>
   <si>
     <t xml:space="preserve">19.6454124450684</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4771842956543</t>
+    <t xml:space="preserve">19.4771862030029</t>
   </si>
   <si>
     <t xml:space="preserve">19.5426082611084</t>
@@ -1844,19 +1844,19 @@
     <t xml:space="preserve">19.3930702209473</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7481937408447</t>
+    <t xml:space="preserve">18.7481918334961</t>
   </si>
   <si>
     <t xml:space="preserve">18.7855777740479</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0659561157227</t>
+    <t xml:space="preserve">19.0659580230713</t>
   </si>
   <si>
     <t xml:space="preserve">19.5145683288574</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2061500549316</t>
+    <t xml:space="preserve">19.206148147583</t>
   </si>
   <si>
     <t xml:space="preserve">17.0472087860107</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">16.7107524871826</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8135585784912</t>
+    <t xml:space="preserve">16.8135566711426</t>
   </si>
   <si>
     <t xml:space="preserve">16.5845813751221</t>
@@ -1874,13 +1874,13 @@
     <t xml:space="preserve">16.5471954345703</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5378475189209</t>
+    <t xml:space="preserve">16.5378494262695</t>
   </si>
   <si>
     <t xml:space="preserve">16.7200965881348</t>
   </si>
   <si>
-    <t xml:space="preserve">16.495792388916</t>
+    <t xml:space="preserve">16.4957942962646</t>
   </si>
   <si>
     <t xml:space="preserve">16.7528076171875</t>
@@ -1889,7 +1889,7 @@
     <t xml:space="preserve">16.5004653930664</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4630794525146</t>
+    <t xml:space="preserve">16.4630813598633</t>
   </si>
   <si>
     <t xml:space="preserve">16.0425090789795</t>
@@ -1910,25 +1910,25 @@
     <t xml:space="preserve">16.5331783294678</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5892543792725</t>
+    <t xml:space="preserve">16.5892524719238</t>
   </si>
   <si>
     <t xml:space="preserve">16.6827125549316</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5985984802246</t>
+    <t xml:space="preserve">16.5986003875732</t>
   </si>
   <si>
     <t xml:space="preserve">16.4256973266602</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1266231536865</t>
+    <t xml:space="preserve">16.1266250610352</t>
   </si>
   <si>
     <t xml:space="preserve">16.1593341827393</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4490623474121</t>
+    <t xml:space="preserve">16.4490642547607</t>
   </si>
   <si>
     <t xml:space="preserve">16.1920471191406</t>
@@ -1973,7 +1973,7 @@
     <t xml:space="preserve">17.4163799285889</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1079597473145</t>
+    <t xml:space="preserve">17.1079616546631</t>
   </si>
   <si>
     <t xml:space="preserve">17.1313228607178</t>
@@ -1988,10 +1988,10 @@
     <t xml:space="preserve">17.4397449493408</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4537620544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.729471206665</t>
+    <t xml:space="preserve">17.453763961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7294731140137</t>
   </si>
   <si>
     <t xml:space="preserve">17.6547012329102</t>
@@ -2012,22 +2012,22 @@
     <t xml:space="preserve">16.822904586792</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9911632537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9117202758789</t>
+    <t xml:space="preserve">17.9911613464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9117221832275</t>
   </si>
   <si>
     <t xml:space="preserve">18.0378913879395</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6593780517578</t>
+    <t xml:space="preserve">17.6593761444092</t>
   </si>
   <si>
     <t xml:space="preserve">17.7948951721191</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6360130310059</t>
+    <t xml:space="preserve">17.6360111236572</t>
   </si>
   <si>
     <t xml:space="preserve">17.3275928497314</t>
@@ -2045,19 +2045,19 @@
     <t xml:space="preserve">17.869665145874</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3136024475098</t>
+    <t xml:space="preserve">18.3136005401611</t>
   </si>
   <si>
     <t xml:space="preserve">18.056583404541</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2855606079102</t>
+    <t xml:space="preserve">18.2855625152588</t>
   </si>
   <si>
     <t xml:space="preserve">18.0192012786865</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9677982330322</t>
+    <t xml:space="preserve">17.9677963256836</t>
   </si>
   <si>
     <t xml:space="preserve">17.9070472717285</t>
@@ -2066,16 +2066,16 @@
     <t xml:space="preserve">18.69211769104</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5051956176758</t>
+    <t xml:space="preserve">18.5051937103271</t>
   </si>
   <si>
     <t xml:space="preserve">18.3416404724121</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5565967559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4397735595703</t>
+    <t xml:space="preserve">18.5565986633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4397716522217</t>
   </si>
   <si>
     <t xml:space="preserve">18.5472526550293</t>
@@ -2084,13 +2084,13 @@
     <t xml:space="preserve">18.3089275360107</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8603458404541</t>
+    <t xml:space="preserve">18.8603439331055</t>
   </si>
   <si>
     <t xml:space="preserve">18.3696784973145</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5893077850342</t>
+    <t xml:space="preserve">18.5893096923828</t>
   </si>
   <si>
     <t xml:space="preserve">18.0238723754883</t>
@@ -2105,13 +2105,13 @@
     <t xml:space="preserve">17.5986270904541</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0939693450928</t>
+    <t xml:space="preserve">18.0939674377441</t>
   </si>
   <si>
     <t xml:space="preserve">19.860372543335</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0472946166992</t>
+    <t xml:space="preserve">20.0472965240479</t>
   </si>
   <si>
     <t xml:space="preserve">19.9071044921875</t>
@@ -2126,34 +2126,34 @@
     <t xml:space="preserve">19.4132251739502</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2042751312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4892063140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1187973022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2327709197998</t>
+    <t xml:space="preserve">19.204273223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4892082214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1187953948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2327690124512</t>
   </si>
   <si>
     <t xml:space="preserve">18.9525890350342</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4397144317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7131423950195</t>
+    <t xml:space="preserve">18.4397163391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7131443023682</t>
   </si>
   <si>
     <t xml:space="preserve">17.7273902893066</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8318634033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3732318878174</t>
+    <t xml:space="preserve">17.8318614959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3732299804688</t>
   </si>
   <si>
     <t xml:space="preserve">18.6534099578857</t>
@@ -2165,13 +2165,13 @@
     <t xml:space="preserve">19.3657360076904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2802581787109</t>
+    <t xml:space="preserve">19.2802562713623</t>
   </si>
   <si>
     <t xml:space="preserve">19.2137718200684</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9810810089111</t>
+    <t xml:space="preserve">18.9810829162598</t>
   </si>
   <si>
     <t xml:space="preserve">18.905101776123</t>
@@ -2186,10 +2186,10 @@
     <t xml:space="preserve">19.6886558532715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9355964660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0210742950439</t>
+    <t xml:space="preserve">19.9355945587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0210762023926</t>
   </si>
   <si>
     <t xml:space="preserve">19.8026294708252</t>
@@ -2207,16 +2207,16 @@
     <t xml:space="preserve">19.926097869873</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1350479125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1920318603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4674644470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4864597320557</t>
+    <t xml:space="preserve">20.135046005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1920337677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4674625396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4864616394043</t>
   </si>
   <si>
     <t xml:space="preserve">20.2870121002197</t>
@@ -2225,7 +2225,7 @@
     <t xml:space="preserve">20.2775135040283</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8406181335449</t>
+    <t xml:space="preserve">19.8406200408936</t>
   </si>
   <si>
     <t xml:space="preserve">19.821626663208</t>
@@ -2234,10 +2234,10 @@
     <t xml:space="preserve">19.8501167297363</t>
   </si>
   <si>
-    <t xml:space="preserve">19.95458984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9071006774902</t>
+    <t xml:space="preserve">19.9545917510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9071025848389</t>
   </si>
   <si>
     <t xml:space="preserve">19.8881092071533</t>
@@ -2252,7 +2252,7 @@
     <t xml:space="preserve">19.9640884399414</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0020809173584</t>
+    <t xml:space="preserve">20.0020790100098</t>
   </si>
   <si>
     <t xml:space="preserve">19.9450931549072</t>
@@ -2264,22 +2264,22 @@
     <t xml:space="preserve">18.0218181610107</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9315891265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5754241943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2952442169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.276252746582</t>
+    <t xml:space="preserve">17.9315872192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5754261016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2952461242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2762508392334</t>
   </si>
   <si>
     <t xml:space="preserve">17.2667541503906</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3854732513428</t>
+    <t xml:space="preserve">17.3854751586914</t>
   </si>
   <si>
     <t xml:space="preserve">17.0198135375977</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">17.015064239502</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5971698760986</t>
+    <t xml:space="preserve">16.59716796875</t>
   </si>
   <si>
     <t xml:space="preserve">16.2837448120117</t>
@@ -2315,13 +2315,13 @@
     <t xml:space="preserve">16.7348861694336</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9485816955566</t>
+    <t xml:space="preserve">16.948579788208</t>
   </si>
   <si>
     <t xml:space="preserve">16.7491302490234</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8441066741943</t>
+    <t xml:space="preserve">16.844108581543</t>
   </si>
   <si>
     <t xml:space="preserve">16.497444152832</t>
@@ -2330,10 +2330,10 @@
     <t xml:space="preserve">16.6683979034424</t>
   </si>
   <si>
-    <t xml:space="preserve">16.630407333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9248371124268</t>
+    <t xml:space="preserve">16.6304092407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9248352050781</t>
   </si>
   <si>
     <t xml:space="preserve">17.4329605102539</t>
@@ -2345,28 +2345,28 @@
     <t xml:space="preserve">17.2097682952881</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1385345458984</t>
+    <t xml:space="preserve">17.1385364532471</t>
   </si>
   <si>
     <t xml:space="preserve">17.5231895446777</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2857475280762</t>
+    <t xml:space="preserve">17.2857494354248</t>
   </si>
   <si>
     <t xml:space="preserve">17.2002696990967</t>
   </si>
   <si>
-    <t xml:space="preserve">16.696891784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7538776397705</t>
+    <t xml:space="preserve">16.6968936920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7538795471191</t>
   </si>
   <si>
     <t xml:space="preserve">16.2267570495605</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1887664794922</t>
+    <t xml:space="preserve">16.1887683868408</t>
   </si>
   <si>
     <t xml:space="preserve">16.1365299224854</t>
@@ -2378,19 +2378,19 @@
     <t xml:space="preserve">16.1840190887451</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1032905578613</t>
+    <t xml:space="preserve">16.1032886505127</t>
   </si>
   <si>
     <t xml:space="preserve">16.0178089141846</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4811916351318</t>
+    <t xml:space="preserve">15.4811906814575</t>
   </si>
   <si>
     <t xml:space="preserve">15.538179397583</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5619211196899</t>
+    <t xml:space="preserve">15.5619220733643</t>
   </si>
   <si>
     <t xml:space="preserve">15.1725187301636</t>
@@ -2408,7 +2408,7 @@
     <t xml:space="preserve">15.4716949462891</t>
   </si>
   <si>
-    <t xml:space="preserve">15.680643081665</t>
+    <t xml:space="preserve">15.6806421279907</t>
   </si>
   <si>
     <t xml:space="preserve">15.4052104949951</t>
@@ -2429,22 +2429,22 @@
     <t xml:space="preserve">15.0680437088013</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0348024368286</t>
+    <t xml:space="preserve">15.0348014831543</t>
   </si>
   <si>
     <t xml:space="preserve">15.319730758667</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9608240127563</t>
+    <t xml:space="preserve">15.9608249664307</t>
   </si>
   <si>
     <t xml:space="preserve">15.7661228179932</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8800926208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9085865020752</t>
+    <t xml:space="preserve">15.8800916671753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9085855484009</t>
   </si>
   <si>
     <t xml:space="preserve">15.922833442688</t>
@@ -2456,7 +2456,7 @@
     <t xml:space="preserve">16.1745204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4024639129639</t>
+    <t xml:space="preserve">16.4024658203125</t>
   </si>
   <si>
     <t xml:space="preserve">16.5781726837158</t>
@@ -2471,7 +2471,7 @@
     <t xml:space="preserve">17.2809982299805</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9723281860352</t>
+    <t xml:space="preserve">16.9723262786865</t>
   </si>
   <si>
     <t xml:space="preserve">16.4404544830322</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">16.3977165222168</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6209125518799</t>
+    <t xml:space="preserve">16.6209106445312</t>
   </si>
   <si>
     <t xml:space="preserve">17.3047428131104</t>
@@ -2501,10 +2501,10 @@
     <t xml:space="preserve">16.6873950958252</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9695816040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1120433807373</t>
+    <t xml:space="preserve">17.9695796966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1120452880859</t>
   </si>
   <si>
     <t xml:space="preserve">17.4282131195068</t>
@@ -2513,7 +2513,7 @@
     <t xml:space="preserve">17.3474826812744</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2477569580078</t>
+    <t xml:space="preserve">17.2477588653564</t>
   </si>
   <si>
     <t xml:space="preserve">17.3379859924316</t>
@@ -2525,37 +2525,37 @@
     <t xml:space="preserve">17.62766456604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5421848297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4804515838623</t>
+    <t xml:space="preserve">17.5421829223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4804496765137</t>
   </si>
   <si>
     <t xml:space="preserve">17.8033714294434</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1167945861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8556079864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8081207275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0028209686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6704025268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6229152679443</t>
+    <t xml:space="preserve">18.1167964935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8556060791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8081188201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0028228759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6704044342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.622917175293</t>
   </si>
   <si>
     <t xml:space="preserve">17.6799011230469</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9885768890381</t>
+    <t xml:space="preserve">17.9885749816895</t>
   </si>
   <si>
     <t xml:space="preserve">18.4207191467285</t>
@@ -2567,13 +2567,13 @@
     <t xml:space="preserve">17.9030952453613</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8508586883545</t>
+    <t xml:space="preserve">17.8508605957031</t>
   </si>
   <si>
     <t xml:space="preserve">17.2620029449463</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2287616729736</t>
+    <t xml:space="preserve">17.2287635803223</t>
   </si>
   <si>
     <t xml:space="preserve">17.0957946777344</t>
@@ -2594,7 +2594,7 @@
     <t xml:space="preserve">16.2694988250732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2979907989502</t>
+    <t xml:space="preserve">16.2979927062988</t>
   </si>
   <si>
     <t xml:space="preserve">16.1175346374512</t>
@@ -2603,13 +2603,13 @@
     <t xml:space="preserve">15.8468523025513</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3217334747314</t>
+    <t xml:space="preserve">16.3217353820801</t>
   </si>
   <si>
     <t xml:space="preserve">16.0842933654785</t>
   </si>
   <si>
-    <t xml:space="preserve">15.780366897583</t>
+    <t xml:space="preserve">15.7803678512573</t>
   </si>
   <si>
     <t xml:space="preserve">15.7186336517334</t>
@@ -2618,19 +2618,19 @@
     <t xml:space="preserve">15.3434762954712</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9845676422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7471265792847</t>
+    <t xml:space="preserve">15.9845695495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.747127532959</t>
   </si>
   <si>
     <t xml:space="preserve">15.6046619415283</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7043876647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8848447799683</t>
+    <t xml:space="preserve">15.7043867111206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8848428726196</t>
   </si>
   <si>
     <t xml:space="preserve">15.5429258346558</t>
@@ -2639,10 +2639,10 @@
     <t xml:space="preserve">15.1582717895508</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8096027374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8665885925293</t>
+    <t xml:space="preserve">13.8096036911011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8665895462036</t>
   </si>
   <si>
     <t xml:space="preserve">14.1420221328735</t>
@@ -2654,10 +2654,10 @@
     <t xml:space="preserve">13.5721616744995</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0735349655151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0497903823853</t>
+    <t xml:space="preserve">13.0735340118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0497894287109</t>
   </si>
   <si>
     <t xml:space="preserve">12.9738082885742</t>
@@ -2669,19 +2669,19 @@
     <t xml:space="preserve">12.0477876663208</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2784767150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.656379699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7845964431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08166599273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65437507629395</t>
+    <t xml:space="preserve">11.2784757614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6563787460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7845973968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08166694641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65437602996826</t>
   </si>
   <si>
     <t xml:space="preserve">10.0057888031006</t>
@@ -2699,7 +2699,7 @@
     <t xml:space="preserve">11.8625812530518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1665086746216</t>
+    <t xml:space="preserve">12.1665077209473</t>
   </si>
   <si>
     <t xml:space="preserve">13.0877799987793</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">13.3964548110962</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9690589904785</t>
+    <t xml:space="preserve">12.9690599441528</t>
   </si>
   <si>
     <t xml:space="preserve">12.2519865036011</t>
@@ -2720,16 +2720,16 @@
     <t xml:space="preserve">11.4921731948853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2072429656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1597557067871</t>
+    <t xml:space="preserve">11.2072439193726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1597547531128</t>
   </si>
   <si>
     <t xml:space="preserve">11.1882476806641</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5681552886963</t>
+    <t xml:space="preserve">11.568154335022</t>
   </si>
   <si>
     <t xml:space="preserve">11.5586566925049</t>
@@ -2741,7 +2741,7 @@
     <t xml:space="preserve">11.9765529632568</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4541835784912</t>
+    <t xml:space="preserve">11.4541826248169</t>
   </si>
   <si>
     <t xml:space="preserve">11.2927227020264</t>
@@ -2756,7 +2756,7 @@
     <t xml:space="preserve">10.399941444397</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4474306106567</t>
+    <t xml:space="preserve">10.4474296569824</t>
   </si>
   <si>
     <t xml:space="preserve">10.3809471130371</t>
@@ -2765,13 +2765,13 @@
     <t xml:space="preserve">10.7323598861694</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9128160476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7228622436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3049650192261</t>
+    <t xml:space="preserve">10.9128150939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.722861289978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3049659729004</t>
   </si>
   <si>
     <t xml:space="preserve">10.3524532318115</t>
@@ -2780,13 +2780,13 @@
     <t xml:space="preserve">10.3144626617432</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3429555892944</t>
+    <t xml:space="preserve">10.3429565429688</t>
   </si>
   <si>
     <t xml:space="preserve">10.4094400405884</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2574777603149</t>
+    <t xml:space="preserve">10.2574768066406</t>
   </si>
   <si>
     <t xml:space="preserve">10.0295333862305</t>
@@ -2795,10 +2795,10 @@
     <t xml:space="preserve">9.9060640335083</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89656543731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64962577819824</t>
+    <t xml:space="preserve">9.89656639099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64962673187256</t>
   </si>
   <si>
     <t xml:space="preserve">9.78259372711182</t>
@@ -2807,7 +2807,7 @@
     <t xml:space="preserve">10.4949188232422</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3469619750977</t>
+    <t xml:space="preserve">12.346962928772</t>
   </si>
   <si>
     <t xml:space="preserve">11.9005727767944</t>
@@ -2828,16 +2828,16 @@
     <t xml:space="preserve">13.2872314453125</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1542644500732</t>
+    <t xml:space="preserve">13.1542654037476</t>
   </si>
   <si>
     <t xml:space="preserve">12.8218460083008</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8815774917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7771034240723</t>
+    <t xml:space="preserve">11.8815784454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7771024703979</t>
   </si>
   <si>
     <t xml:space="preserve">12.062032699585</t>
@@ -2846,7 +2846,7 @@
     <t xml:space="preserve">12.1190185546875</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2899761199951</t>
+    <t xml:space="preserve">12.2899770736694</t>
   </si>
   <si>
     <t xml:space="preserve">12.3089723587036</t>
@@ -2867,7 +2867,7 @@
     <t xml:space="preserve">11.8055963516235</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5111694335938</t>
+    <t xml:space="preserve">11.5111684799194</t>
   </si>
   <si>
     <t xml:space="preserve">11.7296142578125</t>
@@ -2882,7 +2882,7 @@
     <t xml:space="preserve">11.7581081390381</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5871496200562</t>
+    <t xml:space="preserve">11.5871486663818</t>
   </si>
   <si>
     <t xml:space="preserve">11.4826755523682</t>
@@ -2897,7 +2897,7 @@
     <t xml:space="preserve">11.1787509918213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2262372970581</t>
+    <t xml:space="preserve">11.2262382507324</t>
   </si>
   <si>
     <t xml:space="preserve">11.2452344894409</t>
@@ -2924,7 +2924,7 @@
     <t xml:space="preserve">11.2167415618896</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5708990097046</t>
+    <t xml:space="preserve">10.5708999633789</t>
   </si>
   <si>
     <t xml:space="preserve">10.580397605896</t>
@@ -2933,19 +2933,19 @@
     <t xml:space="preserve">10.4379320144653</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3619508743286</t>
+    <t xml:space="preserve">10.3619518280029</t>
   </si>
   <si>
     <t xml:space="preserve">11.644136428833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3307132720947</t>
+    <t xml:space="preserve">11.3307123184204</t>
   </si>
   <si>
     <t xml:space="preserve">11.0932712554932</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9603033065796</t>
+    <t xml:space="preserve">10.9603042602539</t>
   </si>
   <si>
     <t xml:space="preserve">10.760853767395</t>
@@ -2957,19 +2957,19 @@
     <t xml:space="preserve">10.6753740310669</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6156415939331</t>
+    <t xml:space="preserve">11.6156425476074</t>
   </si>
   <si>
     <t xml:space="preserve">11.4636793136597</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3971977233887</t>
+    <t xml:space="preserve">11.3971967697144</t>
   </si>
   <si>
     <t xml:space="preserve">11.5016708374023</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7960987091064</t>
+    <t xml:space="preserve">11.7960977554321</t>
   </si>
   <si>
     <t xml:space="preserve">11.4731779098511</t>
@@ -2984,13 +2984,13 @@
     <t xml:space="preserve">12.565408706665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0810279846191</t>
+    <t xml:space="preserve">12.0810289382935</t>
   </si>
   <si>
     <t xml:space="preserve">11.6821269989014</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6061449050903</t>
+    <t xml:space="preserve">11.6061458587646</t>
   </si>
   <si>
     <t xml:space="preserve">12.1095209121704</t>
@@ -2999,16 +2999,16 @@
     <t xml:space="preserve">12.0145444869995</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9385623931885</t>
+    <t xml:space="preserve">11.9385633468628</t>
   </si>
   <si>
     <t xml:space="preserve">11.957558631897</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9860515594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1285181045532</t>
+    <t xml:space="preserve">11.9860506057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1285171508789</t>
   </si>
   <si>
     <t xml:space="preserve">12.2804803848267</t>
@@ -3032,13 +3032,13 @@
     <t xml:space="preserve">12.8978281021118</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1950006484985</t>
+    <t xml:space="preserve">12.1949996948242</t>
   </si>
   <si>
     <t xml:space="preserve">11.8910760879517</t>
   </si>
   <si>
-    <t xml:space="preserve">11.67262840271</t>
+    <t xml:space="preserve">11.6726293563843</t>
   </si>
   <si>
     <t xml:space="preserve">11.3117170333862</t>
@@ -3047,13 +3047,13 @@
     <t xml:space="preserve">10.6943693161011</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5139131546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7988443374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0647783279419</t>
+    <t xml:space="preserve">10.5139141082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7988433837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0647773742676</t>
   </si>
   <si>
     <t xml:space="preserve">11.3592052459717</t>
@@ -3089,22 +3089,22 @@
     <t xml:space="preserve">14.0470447540283</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6264019012451</t>
+    <t xml:space="preserve">14.6264009475708</t>
   </si>
   <si>
     <t xml:space="preserve">14.3129787445068</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1515197753906</t>
+    <t xml:space="preserve">14.1515188217163</t>
   </si>
   <si>
     <t xml:space="preserve">14.2464952468872</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4269504547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4649410247803</t>
+    <t xml:space="preserve">14.4269514083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4649419784546</t>
   </si>
   <si>
     <t xml:space="preserve">14.9113321304321</t>
@@ -3134,10 +3134,10 @@
     <t xml:space="preserve">14.7593698501587</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3794631958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5694169998169</t>
+    <t xml:space="preserve">14.3794622421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5694160461426</t>
   </si>
   <si>
     <t xml:space="preserve">14.6453981399536</t>
@@ -3155,13 +3155,13 @@
     <t xml:space="preserve">14.9493227005005</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7688684463501</t>
+    <t xml:space="preserve">14.7688674926758</t>
   </si>
   <si>
     <t xml:space="preserve">14.7118806838989</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5884113311768</t>
+    <t xml:space="preserve">14.5884103775024</t>
   </si>
   <si>
     <t xml:space="preserve">14.5789136886597</t>
@@ -3185,19 +3185,19 @@
     <t xml:space="preserve">14.4459466934204</t>
   </si>
   <si>
-    <t xml:space="preserve">15.29123878479</t>
+    <t xml:space="preserve">15.2912397384644</t>
   </si>
   <si>
     <t xml:space="preserve">14.683388710022</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0537977218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8041114807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6711454391479</t>
+    <t xml:space="preserve">15.0537967681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8041124343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6711444854736</t>
   </si>
   <si>
     <t xml:space="preserve">15.2627458572388</t>
@@ -3212,7 +3212,7 @@
     <t xml:space="preserve">14.721378326416</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6358995437622</t>
+    <t xml:space="preserve">14.6359004974365</t>
   </si>
   <si>
     <t xml:space="preserve">14.4364490509033</t>
@@ -3224,19 +3224,19 @@
     <t xml:space="preserve">15.006308555603</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0822896957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9778165817261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6928853988647</t>
+    <t xml:space="preserve">15.0822906494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9778156280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6928863525391</t>
   </si>
   <si>
     <t xml:space="preserve">14.7783651351929</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8258533477783</t>
+    <t xml:space="preserve">14.825852394104</t>
   </si>
   <si>
     <t xml:space="preserve">15.2057600021362</t>
@@ -3251,13 +3251,13 @@
     <t xml:space="preserve">15.1012849807739</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8448486328125</t>
+    <t xml:space="preserve">14.8448476791382</t>
   </si>
   <si>
     <t xml:space="preserve">14.9873123168945</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8705940246582</t>
+    <t xml:space="preserve">15.8705949783325</t>
   </si>
   <si>
     <t xml:space="preserve">16.0225601196289</t>
@@ -3269,7 +3269,7 @@
     <t xml:space="preserve">15.8231077194214</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9370794296265</t>
+    <t xml:space="preserve">15.9370803833008</t>
   </si>
   <si>
     <t xml:space="preserve">15.7376298904419</t>
@@ -3278,7 +3278,7 @@
     <t xml:space="preserve">15.4906892776489</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7091379165649</t>
+    <t xml:space="preserve">15.7091369628906</t>
   </si>
   <si>
     <t xml:space="preserve">15.3102350234985</t>
@@ -3293,22 +3293,22 @@
     <t xml:space="preserve">15.6996374130249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6853914260864</t>
+    <t xml:space="preserve">15.6853904724121</t>
   </si>
   <si>
     <t xml:space="preserve">15.6189079284668</t>
   </si>
   <si>
-    <t xml:space="preserve">15.428955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.637903213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.739631652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8678493499756</t>
+    <t xml:space="preserve">15.4289560317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6379041671753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7396335601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8678512573242</t>
   </si>
   <si>
     <t xml:space="preserve">16.8726005554199</t>
@@ -3317,16 +3317,16 @@
     <t xml:space="preserve">16.4784469604492</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0340595245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5136947631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4567070007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0388107299805</t>
+    <t xml:space="preserve">17.0340576171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.513692855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4567050933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0388088226318</t>
   </si>
   <si>
     <t xml:space="preserve">17.2904968261719</t>
@@ -3371,19 +3371,19 @@
     <t xml:space="preserve">17.9125938415527</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9553356170654</t>
+    <t xml:space="preserve">17.9553337097168</t>
   </si>
   <si>
     <t xml:space="preserve">17.6846504211426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0408115386963</t>
+    <t xml:space="preserve">18.0408134460449</t>
   </si>
   <si>
     <t xml:space="preserve">18.3304901123047</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3209953308105</t>
+    <t xml:space="preserve">18.3209934234619</t>
   </si>
   <si>
     <t xml:space="preserve">18.368480682373</t>
@@ -3395,22 +3395,22 @@
     <t xml:space="preserve">18.3542366027832</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3969764709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5299415588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.297248840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1690311431885</t>
+    <t xml:space="preserve">18.3969745635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5299434661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2972469329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1690292358398</t>
   </si>
   <si>
     <t xml:space="preserve">18.1832790374756</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4444618225098</t>
+    <t xml:space="preserve">18.4444637298584</t>
   </si>
   <si>
     <t xml:space="preserve">18.8956031799316</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">18.6961498260498</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5584354400635</t>
+    <t xml:space="preserve">18.5584373474121</t>
   </si>
   <si>
     <t xml:space="preserve">18.3352394104004</t>
@@ -3431,16 +3431,16 @@
     <t xml:space="preserve">17.1527805328369</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1812725067139</t>
+    <t xml:space="preserve">17.1812744140625</t>
   </si>
   <si>
     <t xml:space="preserve">17.0673007965088</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1575298309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6114139556885</t>
+    <t xml:space="preserve">17.1575317382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6114120483398</t>
   </si>
   <si>
     <t xml:space="preserve">16.5021896362305</t>
@@ -3458,10 +3458,10 @@
     <t xml:space="preserve">15.9798202514648</t>
   </si>
   <si>
-    <t xml:space="preserve">16.098539352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0083103179932</t>
+    <t xml:space="preserve">16.0985412597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0083122253418</t>
   </si>
   <si>
     <t xml:space="preserve">16.2505035400391</t>
@@ -3470,7 +3470,7 @@
     <t xml:space="preserve">16.4736976623535</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1697731018066</t>
+    <t xml:space="preserve">16.169771194458</t>
   </si>
   <si>
     <t xml:space="preserve">16.0463027954102</t>
@@ -3479,25 +3479,25 @@
     <t xml:space="preserve">16.0368041992188</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9988145828247</t>
+    <t xml:space="preserve">15.9988136291504</t>
   </si>
   <si>
     <t xml:space="preserve">16.2600021362305</t>
   </si>
   <si>
-    <t xml:space="preserve">16.065299987793</t>
+    <t xml:space="preserve">16.0652980804443</t>
   </si>
   <si>
     <t xml:space="preserve">16.0510520935059</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1100425720215</t>
+    <t xml:space="preserve">17.1100406646729</t>
   </si>
   <si>
     <t xml:space="preserve">17.3949718475342</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4919509887695</t>
+    <t xml:space="preserve">18.4919528961182</t>
   </si>
   <si>
     <t xml:space="preserve">17.5896739959717</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">16.6731491088867</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5164356231689</t>
+    <t xml:space="preserve">16.5164375305176</t>
   </si>
   <si>
     <t xml:space="preserve">15.7328805923462</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">15.7423782348633</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1460285186768</t>
+    <t xml:space="preserve">16.1460266113281</t>
   </si>
   <si>
     <t xml:space="preserve">15.9275808334351</t>
@@ -3551,7 +3551,7 @@
     <t xml:space="preserve">16.8251113891602</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7206363677979</t>
+    <t xml:space="preserve">16.7206382751465</t>
   </si>
   <si>
     <t xml:space="preserve">16.9628295898438</t>
@@ -3560,13 +3560,13 @@
     <t xml:space="preserve">16.9438304901123</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8298587799072</t>
+    <t xml:space="preserve">16.8298606872559</t>
   </si>
   <si>
     <t xml:space="preserve">16.9913196563721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8346118927002</t>
+    <t xml:space="preserve">16.8346099853516</t>
   </si>
   <si>
     <t xml:space="preserve">17.0435562133789</t>
@@ -3602,16 +3602,16 @@
     <t xml:space="preserve">18.1405372619629</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7009010314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7911281585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9715824127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.945837020874</t>
+    <t xml:space="preserve">18.7008991241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7911262512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9715843200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9458351135254</t>
   </si>
   <si>
     <t xml:space="preserve">18.4302177429199</t>
@@ -3620,19 +3620,19 @@
     <t xml:space="preserve">18.5536861419678</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7626342773438</t>
+    <t xml:space="preserve">18.7626323699951</t>
   </si>
   <si>
     <t xml:space="preserve">19.0903053283691</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3752326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.92409324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1662864685059</t>
+    <t xml:space="preserve">19.3752346038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9240951538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1662845611572</t>
   </si>
   <si>
     <t xml:space="preserve">19.4037265777588</t>
@@ -3647,7 +3647,7 @@
     <t xml:space="preserve">19.1377906799316</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6316719055176</t>
+    <t xml:space="preserve">19.6316699981689</t>
   </si>
   <si>
     <t xml:space="preserve">20.4579677581787</t>
@@ -3656,25 +3656,25 @@
     <t xml:space="preserve">20.6289253234863</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0373249053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4457244873047</t>
+    <t xml:space="preserve">21.0373268127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4457225799561</t>
   </si>
   <si>
     <t xml:space="preserve">20.9898376464844</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7523956298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6384220123291</t>
+    <t xml:space="preserve">20.7523975372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6384239196777</t>
   </si>
   <si>
     <t xml:space="preserve">20.1635398864746</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0970573425293</t>
+    <t xml:space="preserve">20.0970554351807</t>
   </si>
   <si>
     <t xml:space="preserve">20.7903861999512</t>
@@ -3683,7 +3683,7 @@
     <t xml:space="preserve">20.7144031524658</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0278263092041</t>
+    <t xml:space="preserve">21.0278282165527</t>
   </si>
   <si>
     <t xml:space="preserve">21.0183296203613</t>
@@ -3695,19 +3695,19 @@
     <t xml:space="preserve">21.4172306060791</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3982372283936</t>
+    <t xml:space="preserve">21.3982353210449</t>
   </si>
   <si>
     <t xml:space="preserve">21.7021617889404</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5691928863525</t>
+    <t xml:space="preserve">21.5691947937012</t>
   </si>
   <si>
     <t xml:space="preserve">22.0820693969727</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5976886749268</t>
+    <t xml:space="preserve">21.5976867675781</t>
   </si>
   <si>
     <t xml:space="preserve">21.6261806488037</t>
@@ -3749,10 +3749,10 @@
     <t xml:space="preserve">18.0977993011475</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0503082275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2830047607422</t>
+    <t xml:space="preserve">18.0503101348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2830028533936</t>
   </si>
   <si>
     <t xml:space="preserve">18.1927757263184</t>
@@ -3773,31 +3773,31 @@
     <t xml:space="preserve">18.8006248474121</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5964241027832</t>
+    <t xml:space="preserve">18.5964260101318</t>
   </si>
   <si>
     <t xml:space="preserve">18.7768821716309</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9220924377441</t>
+    <t xml:space="preserve">17.9220905303955</t>
   </si>
   <si>
     <t xml:space="preserve">18.6581611633301</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4492111206055</t>
+    <t xml:space="preserve">18.4492130279541</t>
   </si>
   <si>
     <t xml:space="preserve">17.6324138641357</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7368850708008</t>
+    <t xml:space="preserve">17.7368869781494</t>
   </si>
   <si>
     <t xml:space="preserve">17.12428855896</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1867647171021</t>
+    <t xml:space="preserve">15.1867637634277</t>
   </si>
   <si>
     <t xml:space="preserve">14.8306016921997</t>
@@ -3812,16 +3812,16 @@
     <t xml:space="preserve">15.3529739379883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4574480056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8733406066895</t>
+    <t xml:space="preserve">15.457447052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8733415603638</t>
   </si>
   <si>
     <t xml:space="preserve">15.5856657028198</t>
   </si>
   <si>
-    <t xml:space="preserve">15.81360912323</t>
+    <t xml:space="preserve">15.8136100769043</t>
   </si>
   <si>
     <t xml:space="preserve">15.5334281921387</t>
@@ -3836,7 +3836,7 @@
     <t xml:space="preserve">15.5191831588745</t>
   </si>
   <si>
-    <t xml:space="preserve">15.82785987854</t>
+    <t xml:space="preserve">15.8278589248657</t>
   </si>
   <si>
     <t xml:space="preserve">16.7681255340576</t>
@@ -3845,16 +3845,16 @@
     <t xml:space="preserve">16.316987991333</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9750719070435</t>
+    <t xml:space="preserve">15.9750709533691</t>
   </si>
   <si>
     <t xml:space="preserve">15.0253038406372</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6331539154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6521492004395</t>
+    <t xml:space="preserve">15.633152961731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6521482467651</t>
   </si>
   <si>
     <t xml:space="preserve">15.8895902633667</t>
@@ -3869,19 +3869,19 @@
     <t xml:space="preserve">14.8638439178467</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1392755508423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7851190567017</t>
+    <t xml:space="preserve">15.1392765045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7851181030273</t>
   </si>
   <si>
     <t xml:space="preserve">14.3034820556641</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3224773406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8285980224609</t>
+    <t xml:space="preserve">14.3224763870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8285989761353</t>
   </si>
   <si>
     <t xml:space="preserve">12.8123483657837</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">14.1040306091309</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1990070343018</t>
+    <t xml:space="preserve">14.1990079879761</t>
   </si>
   <si>
     <t xml:space="preserve">15.0158071517944</t>
@@ -5964,6 +5964,9 @@
   </si>
   <si>
     <t xml:space="preserve">7.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28499984741211</t>
   </si>
 </sst>
 </file>
@@ -71224,7 +71227,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6910185185</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>851695</v>
@@ -71245,6 +71248,32 @@
         <v>1983</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.6909837963</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>1127122</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>7.61499977111816</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>7.19000005722046</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>7.22499990463257</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>7.28499984741211</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>1984</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -47,28 +47,28 @@
     <t xml:space="preserve">18.0109634399414</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4978847503662</t>
+    <t xml:space="preserve">17.4978790283203</t>
   </si>
   <si>
     <t xml:space="preserve">17.9401950836182</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6836547851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2498111724854</t>
+    <t xml:space="preserve">17.6836528778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2498092651367</t>
   </si>
   <si>
     <t xml:space="preserve">19.4086723327637</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1344337463379</t>
+    <t xml:space="preserve">19.1344356536865</t>
   </si>
   <si>
     <t xml:space="preserve">18.84250831604</t>
   </si>
   <si>
-    <t xml:space="preserve">18.462121963501</t>
+    <t xml:space="preserve">18.4621238708496</t>
   </si>
   <si>
     <t xml:space="preserve">18.2851982116699</t>
@@ -77,64 +77,64 @@
     <t xml:space="preserve">18.0994262695312</t>
   </si>
   <si>
-    <t xml:space="preserve">17.63942527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5686531066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1878890991211</t>
+    <t xml:space="preserve">17.6394214630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5686511993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1878871917725</t>
   </si>
   <si>
     <t xml:space="preserve">18.4798145294189</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2232761383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7632694244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3913536071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6744346618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9578838348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2055835723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2586574554443</t>
+    <t xml:space="preserve">18.223274230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7632675170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3913555145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6744327545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9578857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2055816650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2586612701416</t>
   </si>
   <si>
     <t xml:space="preserve">18.0817356109619</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3563423156738</t>
+    <t xml:space="preserve">17.3563404083252</t>
   </si>
   <si>
     <t xml:space="preserve">16.9051837921143</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1617240905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6486415863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0201835632324</t>
+    <t xml:space="preserve">17.1617221832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6486434936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0201854705811</t>
   </si>
   <si>
     <t xml:space="preserve">17.4890365600586</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6305770874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4090461730957</t>
+    <t xml:space="preserve">17.6305732727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4090442657471</t>
   </si>
   <si>
     <t xml:space="preserve">18.4532775878906</t>
@@ -146,16 +146,16 @@
     <t xml:space="preserve">18.1348114013672</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3121089935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9048099517822</t>
+    <t xml:space="preserve">17.3121109008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9048080444336</t>
   </si>
   <si>
     <t xml:space="preserve">18.3471202850342</t>
   </si>
   <si>
-    <t xml:space="preserve">19.019437789917</t>
+    <t xml:space="preserve">19.0194358825684</t>
   </si>
   <si>
     <t xml:space="preserve">19.0017414093018</t>
@@ -170,10 +170,10 @@
     <t xml:space="preserve">19.9925231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9482936859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7271366119385</t>
+    <t xml:space="preserve">19.9482917785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7271327972412</t>
   </si>
   <si>
     <t xml:space="preserve">19.3379020690918</t>
@@ -182,67 +182,67 @@
     <t xml:space="preserve">19.647518157959</t>
   </si>
   <si>
-    <t xml:space="preserve">19.983678817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1167449951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4440574645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0367546081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1782932281494</t>
+    <t xml:space="preserve">19.9836769104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1167469024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.444055557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0367527008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1782970428467</t>
   </si>
   <si>
     <t xml:space="preserve">19.4971332550049</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4705963134766</t>
+    <t xml:space="preserve">19.4705944061279</t>
   </si>
   <si>
     <t xml:space="preserve">18.9663600921631</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4794425964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9129066467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8686771392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4175205230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8690509796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.833667755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5151996612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9309730529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8955898284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5240478515625</t>
+    <t xml:space="preserve">19.4794445037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9129085540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8686752319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4175186157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8690490722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8336658477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5152015686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9309749603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8955879211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5240497589111</t>
   </si>
   <si>
     <t xml:space="preserve">18.9486675262451</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7982769012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8778972625732</t>
+    <t xml:space="preserve">18.7982788085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8778991699219</t>
   </si>
   <si>
     <t xml:space="preserve">19.2936706542969</t>
@@ -251,46 +251,46 @@
     <t xml:space="preserve">18.8071269989014</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3205814361572</t>
+    <t xml:space="preserve">18.3205833435059</t>
   </si>
   <si>
     <t xml:space="preserve">18.3648128509521</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8251934051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0640430450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3117389678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.878267288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0021190643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7190380096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4447994232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1440296173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5509567260742</t>
+    <t xml:space="preserve">17.8251914978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0640392303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3117370605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8782691955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0021171569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7190399169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4448051452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1440315246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5509586334229</t>
   </si>
   <si>
     <t xml:space="preserve">17.9844245910645</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4182682037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9313488006592</t>
+    <t xml:space="preserve">17.4182643890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9313468933105</t>
   </si>
   <si>
     <t xml:space="preserve">17.7367286682129</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">17.648265838623</t>
   </si>
   <si>
-    <t xml:space="preserve">17.593936920166</t>
+    <t xml:space="preserve">17.5939388275146</t>
   </si>
   <si>
     <t xml:space="preserve">17.8112602233887</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">17.7025985717773</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6482639312744</t>
+    <t xml:space="preserve">17.6482677459717</t>
   </si>
   <si>
     <t xml:space="preserve">17.530553817749</t>
@@ -317,13 +317,13 @@
     <t xml:space="preserve">17.4128360748291</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3041744232178</t>
+    <t xml:space="preserve">17.3041763305664</t>
   </si>
   <si>
     <t xml:space="preserve">17.4762191772461</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4309482574463</t>
+    <t xml:space="preserve">17.4309425354004</t>
   </si>
   <si>
     <t xml:space="preserve">17.4852752685547</t>
@@ -332,13 +332,13 @@
     <t xml:space="preserve">17.7478733062744</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6844863891602</t>
+    <t xml:space="preserve">17.6844902038574</t>
   </si>
   <si>
     <t xml:space="preserve">17.1502418518066</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7155990600586</t>
+    <t xml:space="preserve">16.71559715271</t>
   </si>
   <si>
     <t xml:space="preserve">16.5435543060303</t>
@@ -347,37 +347,37 @@
     <t xml:space="preserve">17.0415802001953</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0777988433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8384265899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9380283355713</t>
+    <t xml:space="preserve">17.0778007507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8384246826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9380264282227</t>
   </si>
   <si>
     <t xml:space="preserve">17.7297649383545</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8655872344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1825141906738</t>
+    <t xml:space="preserve">17.8655910491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1825160980225</t>
   </si>
   <si>
     <t xml:space="preserve">16.8514251708984</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3896160125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6793804168701</t>
+    <t xml:space="preserve">16.3896179199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6793785095215</t>
   </si>
   <si>
     <t xml:space="preserve">16.262845993042</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5254402160645</t>
+    <t xml:space="preserve">16.5254459381104</t>
   </si>
   <si>
     <t xml:space="preserve">16.6069393157959</t>
@@ -386,7 +386,7 @@
     <t xml:space="preserve">16.8061485290527</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8242568969727</t>
+    <t xml:space="preserve">16.8242607116699</t>
   </si>
   <si>
     <t xml:space="preserve">16.0726909637451</t>
@@ -395,46 +395,46 @@
     <t xml:space="preserve">15.8734798431396</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3624515533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4439506530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.69748878479</t>
+    <t xml:space="preserve">16.3624496459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4439449310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6974906921387</t>
   </si>
   <si>
     <t xml:space="preserve">17.095911026001</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1321277618408</t>
+    <t xml:space="preserve">17.1321296691895</t>
   </si>
   <si>
     <t xml:space="preserve">17.0868549346924</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0325241088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3403949737549</t>
+    <t xml:space="preserve">17.0325260162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3403968811035</t>
   </si>
   <si>
     <t xml:space="preserve">17.9018096923828</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1372394561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9289741516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7710914611816</t>
+    <t xml:space="preserve">18.1372413635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9289722442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.771089553833</t>
   </si>
   <si>
     <t xml:space="preserve">18.6352672576904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0699100494385</t>
+    <t xml:space="preserve">19.0699062347412</t>
   </si>
   <si>
     <t xml:space="preserve">19.2147884368896</t>
@@ -443,10 +443,10 @@
     <t xml:space="preserve">18.6262111663818</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4994411468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2187366485596</t>
+    <t xml:space="preserve">18.4994430541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2187347412109</t>
   </si>
   <si>
     <t xml:space="preserve">18.7167625427246</t>
@@ -455,16 +455,16 @@
     <t xml:space="preserve">18.5809364318848</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7620334625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8073120117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.94313621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0427436828613</t>
+    <t xml:space="preserve">18.7620372772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8073139190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9431343078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.04274559021</t>
   </si>
   <si>
     <t xml:space="preserve">18.6624317169189</t>
@@ -473,10 +473,10 @@
     <t xml:space="preserve">18.4722766876221</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6171569824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7529811859131</t>
+    <t xml:space="preserve">18.6171550750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7529830932617</t>
   </si>
   <si>
     <t xml:space="preserve">18.9703044891357</t>
@@ -485,19 +485,19 @@
     <t xml:space="preserve">18.6805381774902</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6081008911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.653377532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5175533294678</t>
+    <t xml:space="preserve">18.6081027984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6533794403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5175514221191</t>
   </si>
   <si>
     <t xml:space="preserve">18.8707008361816</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6986522674561</t>
+    <t xml:space="preserve">18.6986541748047</t>
   </si>
   <si>
     <t xml:space="preserve">19.106128692627</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">19.9210815429688</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6947059631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5588817596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4592742919922</t>
+    <t xml:space="preserve">19.6947040557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5588779449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4592761993408</t>
   </si>
   <si>
     <t xml:space="preserve">19.3143939971924</t>
@@ -521,40 +521,40 @@
     <t xml:space="preserve">18.8888092041016</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1332931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.160457611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9391899108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4553260803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3557224273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3104476928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3919429779053</t>
+    <t xml:space="preserve">19.1332912445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1604557037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9391937255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4553279876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3557243347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3104515075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3919448852539</t>
   </si>
   <si>
     <t xml:space="preserve">20.4643840789795</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6907596588135</t>
+    <t xml:space="preserve">20.6907615661621</t>
   </si>
   <si>
     <t xml:space="preserve">20.8446979522705</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7994194030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4009990692139</t>
+    <t xml:space="preserve">20.7994213104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4010009765625</t>
   </si>
   <si>
     <t xml:space="preserve">20.1021823883057</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">20.3647766113281</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5458812713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7541446685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4191055297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0116348266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.265172958374</t>
+    <t xml:space="preserve">20.5458793640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7541465759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4191093444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0116329193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2651748657227</t>
   </si>
   <si>
     <t xml:space="preserve">20.3285598754883</t>
@@ -587,7 +587,7 @@
     <t xml:space="preserve">20.0387954711914</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1474590301514</t>
+    <t xml:space="preserve">20.1474571228027</t>
   </si>
   <si>
     <t xml:space="preserve">20.2289543151855</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">19.5498275756836</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4140033721924</t>
+    <t xml:space="preserve">19.4140014648438</t>
   </si>
   <si>
     <t xml:space="preserve">19.5045509338379</t>
@@ -632,19 +632,19 @@
     <t xml:space="preserve">18.0919628143311</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3002281188965</t>
+    <t xml:space="preserve">18.3002300262451</t>
   </si>
   <si>
     <t xml:space="preserve">18.3273944854736</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2458992004395</t>
+    <t xml:space="preserve">18.2459011077881</t>
   </si>
   <si>
     <t xml:space="preserve">18.0104694366455</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7388191223145</t>
+    <t xml:space="preserve">17.7388172149658</t>
   </si>
   <si>
     <t xml:space="preserve">17.8565330505371</t>
@@ -659,91 +659,91 @@
     <t xml:space="preserve">18.3455066680908</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3907814025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.151403427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2872276306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3958911895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3777770996094</t>
+    <t xml:space="preserve">18.3907794952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1514053344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2872295379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3958892822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3777828216553</t>
   </si>
   <si>
     <t xml:space="preserve">19.1151828765869</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5860481262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2600631713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.373836517334</t>
+    <t xml:space="preserve">19.5860443115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2600650787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3738346099854</t>
   </si>
   <si>
     <t xml:space="preserve">20.3466682434082</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2380084991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1293487548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1565132141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8084774017334</t>
+    <t xml:space="preserve">20.2380065917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1293468475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.15651512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8084735870361</t>
   </si>
   <si>
     <t xml:space="preserve">20.6183185577393</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4785461425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5328769683838</t>
+    <t xml:space="preserve">21.4785480499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5328788757324</t>
   </si>
   <si>
     <t xml:space="preserve">22.0671272277832</t>
   </si>
   <si>
-    <t xml:space="preserve">22.058069229126</t>
+    <t xml:space="preserve">22.0580711364746</t>
   </si>
   <si>
     <t xml:space="preserve">22.2572803497314</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2935028076172</t>
+    <t xml:space="preserve">22.2935009002686</t>
   </si>
   <si>
     <t xml:space="preserve">22.3025569915771</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3206672668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2753925323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2391738891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8186950683594</t>
+    <t xml:space="preserve">22.3206634521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.275390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2391700744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8186931610107</t>
   </si>
   <si>
     <t xml:space="preserve">23.0722351074219</t>
   </si>
   <si>
-    <t xml:space="preserve">22.891134262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1537284851074</t>
+    <t xml:space="preserve">22.8911361694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1537322998047</t>
   </si>
   <si>
     <t xml:space="preserve">23.099401473999</t>
@@ -752,22 +752,22 @@
     <t xml:space="preserve">22.5923175811768</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3568878173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9092426300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1757850646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1395664215088</t>
+    <t xml:space="preserve">22.3568897247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9092407226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1757888793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1395645141602</t>
   </si>
   <si>
     <t xml:space="preserve">23.606481552124</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7513637542725</t>
+    <t xml:space="preserve">23.7513618469238</t>
   </si>
   <si>
     <t xml:space="preserve">24.1226196289062</t>
@@ -776,43 +776,43 @@
     <t xml:space="preserve">23.6427040100098</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6879768371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.561206817627</t>
+    <t xml:space="preserve">23.6879806518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5612087249756</t>
   </si>
   <si>
     <t xml:space="preserve">23.7423057556152</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7241992950439</t>
+    <t xml:space="preserve">23.7241973876953</t>
   </si>
   <si>
     <t xml:space="preserve">23.6336479187012</t>
   </si>
   <si>
-    <t xml:space="preserve">23.823802947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6970329284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0139617919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.285608291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.068286895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9777393341064</t>
+    <t xml:space="preserve">23.8238048553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6970291137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0139598846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2856101989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0682888031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9777374267578</t>
   </si>
   <si>
     <t xml:space="preserve">24.2946643829346</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4304885864258</t>
+    <t xml:space="preserve">24.4304904937744</t>
   </si>
   <si>
     <t xml:space="preserve">24.6115913391113</t>
@@ -830,10 +830,10 @@
     <t xml:space="preserve">25.4265441894531</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6167049407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6710319519043</t>
+    <t xml:space="preserve">25.6167011260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6710300445557</t>
   </si>
   <si>
     <t xml:space="preserve">25.6529216766357</t>
@@ -842,13 +842,13 @@
     <t xml:space="preserve">25.7615814208984</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5352039337158</t>
+    <t xml:space="preserve">25.5352058410645</t>
   </si>
   <si>
     <t xml:space="preserve">24.955680847168</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9013538360596</t>
+    <t xml:space="preserve">24.9013519287109</t>
   </si>
   <si>
     <t xml:space="preserve">25.0643444061279</t>
@@ -857,19 +857,19 @@
     <t xml:space="preserve">24.8017482757568</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6206455230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.937572479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3722133636475</t>
+    <t xml:space="preserve">24.6206493377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9375762939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3722152709961</t>
   </si>
   <si>
     <t xml:space="preserve">25.6257553100586</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2273330688477</t>
+    <t xml:space="preserve">25.2273349761963</t>
   </si>
   <si>
     <t xml:space="preserve">25.173002243042</t>
@@ -890,16 +890,16 @@
     <t xml:space="preserve">25.1277294158936</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7434692382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5442562103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4808712005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5080375671387</t>
+    <t xml:space="preserve">25.7434711456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5442581176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4808731079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5080394744873</t>
   </si>
   <si>
     <t xml:space="preserve">25.2635536193848</t>
@@ -908,19 +908,19 @@
     <t xml:space="preserve">25.0824527740479</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7836360931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4214344024658</t>
+    <t xml:space="preserve">24.7836380004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4214324951172</t>
   </si>
   <si>
     <t xml:space="preserve">24.2674980163574</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5261516571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1237812042236</t>
+    <t xml:space="preserve">25.5261497497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1237831115723</t>
   </si>
   <si>
     <t xml:space="preserve">26.1871681213379</t>
@@ -929,7 +929,7 @@
     <t xml:space="preserve">26.6308631896973</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4859828948975</t>
+    <t xml:space="preserve">26.4859848022461</t>
   </si>
   <si>
     <t xml:space="preserve">26.3229923248291</t>
@@ -938,7 +938,7 @@
     <t xml:space="preserve">26.6761379241943</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8934631347656</t>
+    <t xml:space="preserve">26.893461227417</t>
   </si>
   <si>
     <t xml:space="preserve">26.2596073150635</t>
@@ -950,31 +950,31 @@
     <t xml:space="preserve">26.9115695953369</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6036987304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5946426391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3088283538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.326940536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8340225219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8984413146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0641078948975</t>
+    <t xml:space="preserve">26.6036968231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5946464538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3088321685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3269386291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.834020614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8984432220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0641059875488</t>
   </si>
   <si>
     <t xml:space="preserve">24.71120262146</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6159934997559</t>
+    <t xml:space="preserve">23.6159954071045</t>
   </si>
   <si>
     <t xml:space="preserve">23.2202472686768</t>
@@ -983,16 +983,16 @@
     <t xml:space="preserve">23.1282119750977</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9625511169434</t>
+    <t xml:space="preserve">22.962553024292</t>
   </si>
   <si>
     <t xml:space="preserve">22.8705196380615</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8613128662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.266263961792</t>
+    <t xml:space="preserve">22.8613147735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2662658691406</t>
   </si>
   <si>
     <t xml:space="preserve">23.238655090332</t>
@@ -1004,7 +1004,7 @@
     <t xml:space="preserve">22.8889236450195</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0882263183594</t>
+    <t xml:space="preserve">22.088228225708</t>
   </si>
   <si>
     <t xml:space="preserve">22.3183116912842</t>
@@ -1022,109 +1022,109 @@
     <t xml:space="preserve">22.7416687011719</t>
   </si>
   <si>
-    <t xml:space="preserve">22.95334815979</t>
+    <t xml:space="preserve">22.9533462524414</t>
   </si>
   <si>
     <t xml:space="preserve">22.8797206878662</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2846717834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4871463775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4319248199463</t>
+    <t xml:space="preserve">23.2846698760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4871482849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4319267272949</t>
   </si>
   <si>
     <t xml:space="preserve">22.8060932159424</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0269737243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6036205291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2538890838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.545223236084</t>
+    <t xml:space="preserve">23.0269756317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6036167144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2538871765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5452213287354</t>
   </si>
   <si>
     <t xml:space="preserve">21.4900035858154</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7200889587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5544281005859</t>
+    <t xml:space="preserve">21.7200870513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5544261932373</t>
   </si>
   <si>
     <t xml:space="preserve">21.674072265625</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6280536651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1678810119629</t>
+    <t xml:space="preserve">21.6280555725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1678829193115</t>
   </si>
   <si>
     <t xml:space="preserve">21.2046966552734</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1218681335449</t>
+    <t xml:space="preserve">21.1218662261963</t>
   </si>
   <si>
     <t xml:space="preserve">21.4163761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5084114074707</t>
+    <t xml:space="preserve">21.5084095001221</t>
   </si>
   <si>
     <t xml:space="preserve">21.9133605957031</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8857479095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9685802459717</t>
+    <t xml:space="preserve">21.8857517242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9685821533203</t>
   </si>
   <si>
     <t xml:space="preserve">22.6220245361328</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3735332489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2170734405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4103450775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5299873352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6312294006348</t>
+    <t xml:space="preserve">22.3735313415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2170715332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4103469848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.529993057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6312274932861</t>
   </si>
   <si>
     <t xml:space="preserve">22.6404323577881</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5575981140137</t>
+    <t xml:space="preserve">22.5576000213623</t>
   </si>
   <si>
     <t xml:space="preserve">21.4255790710449</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6556644439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.263090133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.539192199707</t>
+    <t xml:space="preserve">21.6556663513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2630920410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5391941070557</t>
   </si>
   <si>
     <t xml:space="preserve">22.3551254272461</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">22.0514125823975</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7876853942871</t>
+    <t xml:space="preserve">22.7876873016357</t>
   </si>
   <si>
     <t xml:space="preserve">22.3367195129395</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">22.0606136322021</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7569007873535</t>
+    <t xml:space="preserve">21.7568988800049</t>
   </si>
   <si>
     <t xml:space="preserve">21.9961910247803</t>
@@ -1163,19 +1163,19 @@
     <t xml:space="preserve">21.8765468597412</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1250400543213</t>
+    <t xml:space="preserve">22.1250419616699</t>
   </si>
   <si>
     <t xml:space="preserve">21.7753086090088</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0238037109375</t>
+    <t xml:space="preserve">22.0238018035889</t>
   </si>
   <si>
     <t xml:space="preserve">21.9041576385498</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6832752227783</t>
+    <t xml:space="preserve">21.6832733154297</t>
   </si>
   <si>
     <t xml:space="preserve">20.8273544311523</t>
@@ -1202,10 +1202,10 @@
     <t xml:space="preserve">21.950174331665</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0974292755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8581371307373</t>
+    <t xml:space="preserve">22.0974273681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8581428527832</t>
   </si>
   <si>
     <t xml:space="preserve">21.6372585296631</t>
@@ -1214,10 +1214,10 @@
     <t xml:space="preserve">21.2967300415039</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9746131896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9838161468506</t>
+    <t xml:space="preserve">20.9746112823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.983814239502</t>
   </si>
   <si>
     <t xml:space="preserve">21.1402721405029</t>
@@ -1229,13 +1229,13 @@
     <t xml:space="preserve">20.7077121734619</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0942573547363</t>
+    <t xml:space="preserve">21.0942554473877</t>
   </si>
   <si>
     <t xml:space="preserve">21.1586799621582</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0206279754639</t>
+    <t xml:space="preserve">21.0206260681152</t>
   </si>
   <si>
     <t xml:space="preserve">21.0022220611572</t>
@@ -1244,22 +1244,22 @@
     <t xml:space="preserve">20.6340847015381</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4500160217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.385591506958</t>
+    <t xml:space="preserve">20.4500141143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3855895996094</t>
   </si>
   <si>
     <t xml:space="preserve">20.3947944641113</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0082511901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9714393615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0634708404541</t>
+    <t xml:space="preserve">20.0082492828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9714374542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0634727478027</t>
   </si>
   <si>
     <t xml:space="preserve">20.4868297576904</t>
@@ -1271,16 +1271,16 @@
     <t xml:space="preserve">20.8917827606201</t>
   </si>
   <si>
-    <t xml:space="preserve">21.241512298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9285926818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2475395202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1647071838379</t>
+    <t xml:space="preserve">21.2415084838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9285945892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2475414276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1647090911865</t>
   </si>
   <si>
     <t xml:space="preserve">20.0910816192627</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">19.2719783782959</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6953315734863</t>
+    <t xml:space="preserve">19.6953353881836</t>
   </si>
   <si>
     <t xml:space="preserve">19.8057765960693</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">20.0450649261475</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2935581207275</t>
+    <t xml:space="preserve">20.2935562133789</t>
   </si>
   <si>
     <t xml:space="preserve">20.4316101074219</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">20.5696601867676</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6616954803467</t>
+    <t xml:space="preserve">20.6616973876953</t>
   </si>
   <si>
     <t xml:space="preserve">21.131067276001</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">21.0482387542725</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1954917907715</t>
+    <t xml:space="preserve">21.1954936981201</t>
   </si>
   <si>
     <t xml:space="preserve">21.4531898498535</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8089504241943</t>
+    <t xml:space="preserve">20.8089485168457</t>
   </si>
   <si>
     <t xml:space="preserve">20.6708965301514</t>
@@ -1337,10 +1337,10 @@
     <t xml:space="preserve">20.7721366882324</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4652481079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7965717315674</t>
+    <t xml:space="preserve">19.4652500152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.796573638916</t>
   </si>
   <si>
     <t xml:space="preserve">19.8609962463379</t>
@@ -1352,19 +1352,19 @@
     <t xml:space="preserve">20.2199287414551</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2291316986084</t>
+    <t xml:space="preserve">20.229133605957</t>
   </si>
   <si>
     <t xml:space="preserve">20.5236415863037</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6524925231934</t>
+    <t xml:space="preserve">20.652494430542</t>
   </si>
   <si>
     <t xml:space="preserve">20.9101867675781</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2659454345703</t>
+    <t xml:space="preserve">20.2659473419189</t>
   </si>
   <si>
     <t xml:space="preserve">20.4684219360352</t>
@@ -1376,10 +1376,10 @@
     <t xml:space="preserve">20.1739139556885</t>
   </si>
   <si>
-    <t xml:space="preserve">21.259916305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3703575134277</t>
+    <t xml:space="preserve">21.2599182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3703594207764</t>
   </si>
   <si>
     <t xml:space="preserve">21.5176124572754</t>
@@ -1388,16 +1388,16 @@
     <t xml:space="preserve">20.8549671173096</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9193916320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5052375793457</t>
+    <t xml:space="preserve">20.9193897247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5052356719971</t>
   </si>
   <si>
     <t xml:space="preserve">20.3487777709961</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0266571044922</t>
+    <t xml:space="preserve">20.0266609191895</t>
   </si>
   <si>
     <t xml:space="preserve">19.7229461669922</t>
@@ -1406,19 +1406,19 @@
     <t xml:space="preserve">19.9162158966064</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5604572296143</t>
+    <t xml:space="preserve">20.560453414917</t>
   </si>
   <si>
     <t xml:space="preserve">20.7169151306152</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9377975463867</t>
+    <t xml:space="preserve">20.9377956390381</t>
   </si>
   <si>
     <t xml:space="preserve">20.8365592956543</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6004428863525</t>
+    <t xml:space="preserve">21.6004447937012</t>
   </si>
   <si>
     <t xml:space="preserve">20.6248798370361</t>
@@ -1451,46 +1451,46 @@
     <t xml:space="preserve">20.5328464508057</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3027610778809</t>
+    <t xml:space="preserve">20.3027591705322</t>
   </si>
   <si>
     <t xml:space="preserve">20.6432876586914</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6156768798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7261161804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2783241271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3151359558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5360221862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7937164306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6496353149414</t>
+    <t xml:space="preserve">20.6156749725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7261180877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2783260345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3151378631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.536018371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7937145233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6496334075928</t>
   </si>
   <si>
     <t xml:space="preserve">22.548397064209</t>
   </si>
   <si>
-    <t xml:space="preserve">22.419548034668</t>
+    <t xml:space="preserve">22.4195499420166</t>
   </si>
   <si>
     <t xml:space="preserve">22.2078685760498</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5668029785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6128215789795</t>
+    <t xml:space="preserve">22.5668048858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6128196716309</t>
   </si>
   <si>
     <t xml:space="preserve">22.9165325164795</t>
@@ -1502,13 +1502,13 @@
     <t xml:space="preserve">22.7324657440186</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8337020874023</t>
+    <t xml:space="preserve">22.833703994751</t>
   </si>
   <si>
     <t xml:space="preserve">22.7692794799805</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9073295593262</t>
+    <t xml:space="preserve">22.9073314666748</t>
   </si>
   <si>
     <t xml:space="preserve">23.2754688262939</t>
@@ -1517,10 +1517,10 @@
     <t xml:space="preserve">22.991304397583</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3090686798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4118747711182</t>
+    <t xml:space="preserve">23.3090667724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4118766784668</t>
   </si>
   <si>
     <t xml:space="preserve">22.9071884155273</t>
@@ -1532,37 +1532,37 @@
     <t xml:space="preserve">22.7296123504639</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3557720184326</t>
+    <t xml:space="preserve">22.355770111084</t>
   </si>
   <si>
     <t xml:space="preserve">22.6174621582031</t>
   </si>
   <si>
-    <t xml:space="preserve">23.07541847229</t>
+    <t xml:space="preserve">23.0754165649414</t>
   </si>
   <si>
     <t xml:space="preserve">23.3557987213135</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1969184875488</t>
+    <t xml:space="preserve">23.1969146728516</t>
   </si>
   <si>
     <t xml:space="preserve">23.206262588501</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4586029052734</t>
+    <t xml:space="preserve">23.4586067199707</t>
   </si>
   <si>
     <t xml:space="preserve">22.6548461914062</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7389602661133</t>
+    <t xml:space="preserve">22.7389583587646</t>
   </si>
   <si>
     <t xml:space="preserve">23.1595325469971</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5053367614746</t>
+    <t xml:space="preserve">23.505334854126</t>
   </si>
   <si>
     <t xml:space="preserve">23.3838367462158</t>
@@ -1574,58 +1574,58 @@
     <t xml:space="preserve">23.2623386383057</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9258823394775</t>
+    <t xml:space="preserve">22.9258804321289</t>
   </si>
   <si>
     <t xml:space="preserve">20.9912452697754</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3370227813721</t>
+    <t xml:space="preserve">20.3370246887207</t>
   </si>
   <si>
     <t xml:space="preserve">19.9912166595459</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7388763427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5612983703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3089542388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.533260345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4958782196045</t>
+    <t xml:space="preserve">19.7388744354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.56130027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3089580535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5332622528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4958763122559</t>
   </si>
   <si>
     <t xml:space="preserve">19.346342086792</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0285758972168</t>
+    <t xml:space="preserve">19.0285720825195</t>
   </si>
   <si>
     <t xml:space="preserve">18.6266937255859</t>
   </si>
   <si>
-    <t xml:space="preserve">18.383695602417</t>
+    <t xml:space="preserve">18.3836975097656</t>
   </si>
   <si>
     <t xml:space="preserve">18.0752754211426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6220226287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0799503326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.603328704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6360397338867</t>
+    <t xml:space="preserve">18.6220188140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.079948425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6033306121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6360416412354</t>
   </si>
   <si>
     <t xml:space="preserve">18.794921875</t>
@@ -1637,10 +1637,10 @@
     <t xml:space="preserve">18.7201538085938</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5752906799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3930435180664</t>
+    <t xml:space="preserve">18.575288772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3930416107178</t>
   </si>
   <si>
     <t xml:space="preserve">18.5285606384277</t>
@@ -1649,19 +1649,19 @@
     <t xml:space="preserve">18.495849609375</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4350986480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3883686065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.491174697876</t>
+    <t xml:space="preserve">18.4351005554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.388370513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4911766052246</t>
   </si>
   <si>
     <t xml:space="preserve">18.2435054779053</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8042373657227</t>
+    <t xml:space="preserve">17.8042411804199</t>
   </si>
   <si>
     <t xml:space="preserve">17.7715282440186</t>
@@ -1670,16 +1670,16 @@
     <t xml:space="preserve">18.1079883575439</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6734237670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7575397491455</t>
+    <t xml:space="preserve">18.6734256744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7575378417969</t>
   </si>
   <si>
     <t xml:space="preserve">18.7295017242432</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2762184143066</t>
+    <t xml:space="preserve">18.276216506958</t>
   </si>
   <si>
     <t xml:space="preserve">18.2528533935547</t>
@@ -1688,28 +1688,28 @@
     <t xml:space="preserve">18.2107944488525</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3790225982666</t>
+    <t xml:space="preserve">18.3790264129639</t>
   </si>
   <si>
     <t xml:space="preserve">19.1407260894775</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4398021697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4024181365967</t>
+    <t xml:space="preserve">19.4397983551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.402416229248</t>
   </si>
   <si>
     <t xml:space="preserve">19.4117641448975</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4304542541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3650302886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1594181060791</t>
+    <t xml:space="preserve">19.430456161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3650321960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1594200134277</t>
   </si>
   <si>
     <t xml:space="preserve">19.1687660217285</t>
@@ -1724,40 +1724,40 @@
     <t xml:space="preserve">18.7388439178467</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0566101074219</t>
+    <t xml:space="preserve">19.0566120147705</t>
   </si>
   <si>
     <t xml:space="preserve">18.8416538238525</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6080303192139</t>
+    <t xml:space="preserve">19.6080284118652</t>
   </si>
   <si>
     <t xml:space="preserve">19.2528800964355</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5239162445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4211082458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8136444091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0753307342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7482204437256</t>
+    <t xml:space="preserve">19.5239143371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4211101531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8136463165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0753326416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.748218536377</t>
   </si>
   <si>
     <t xml:space="preserve">20.0192565917969</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7669124603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7856063842773</t>
+    <t xml:space="preserve">19.7669143676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7856044769287</t>
   </si>
   <si>
     <t xml:space="preserve">19.5706462860107</t>
@@ -1772,13 +1772,13 @@
     <t xml:space="preserve">18.8977298736572</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8042697906494</t>
+    <t xml:space="preserve">18.8042678833008</t>
   </si>
   <si>
     <t xml:space="preserve">18.8790378570557</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1780834197998</t>
+    <t xml:space="preserve">18.1780853271484</t>
   </si>
   <si>
     <t xml:space="preserve">18.6453857421875</t>
@@ -1790,10 +1790,10 @@
     <t xml:space="preserve">17.2528228759766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1546897888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9817867279053</t>
+    <t xml:space="preserve">17.1546878814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9817886352539</t>
   </si>
   <si>
     <t xml:space="preserve">18.1360263824463</t>
@@ -1805,7 +1805,7 @@
     <t xml:space="preserve">18.1173343658447</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2154655456543</t>
+    <t xml:space="preserve">18.2154693603516</t>
   </si>
   <si>
     <t xml:space="preserve">19.1874580383301</t>
@@ -1814,25 +1814,25 @@
     <t xml:space="preserve">19.0098819732666</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5986824035645</t>
+    <t xml:space="preserve">19.5986843109131</t>
   </si>
   <si>
     <t xml:space="preserve">19.5893363952637</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6454162597656</t>
+    <t xml:space="preserve">19.645414352417</t>
   </si>
   <si>
     <t xml:space="preserve">19.4771842956543</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5426063537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5799922943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0005626678467</t>
+    <t xml:space="preserve">19.542610168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5799942016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0005645751953</t>
   </si>
   <si>
     <t xml:space="preserve">19.6267204284668</t>
@@ -1844,7 +1844,7 @@
     <t xml:space="preserve">19.7014904022217</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3930683135986</t>
+    <t xml:space="preserve">19.3930702209473</t>
   </si>
   <si>
     <t xml:space="preserve">18.7481918334961</t>
@@ -1856,25 +1856,25 @@
     <t xml:space="preserve">19.0659580230713</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5145683288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2061500549316</t>
+    <t xml:space="preserve">19.5145664215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.206148147583</t>
   </si>
   <si>
     <t xml:space="preserve">17.0472087860107</t>
   </si>
   <si>
-    <t xml:space="preserve">16.710750579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8135566711426</t>
+    <t xml:space="preserve">16.7107524871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8135585784912</t>
   </si>
   <si>
     <t xml:space="preserve">16.5845813751221</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5471973419189</t>
+    <t xml:space="preserve">16.5471954345703</t>
   </si>
   <si>
     <t xml:space="preserve">16.5378494262695</t>
@@ -1886,7 +1886,7 @@
     <t xml:space="preserve">16.495792388916</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7528076171875</t>
+    <t xml:space="preserve">16.7528095245361</t>
   </si>
   <si>
     <t xml:space="preserve">16.5004653930664</t>
@@ -1913,10 +1913,10 @@
     <t xml:space="preserve">16.5331783294678</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5892524719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6827144622803</t>
+    <t xml:space="preserve">16.5892543792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6827125549316</t>
   </si>
   <si>
     <t xml:space="preserve">16.5986003875732</t>
@@ -1925,40 +1925,40 @@
     <t xml:space="preserve">16.4256973266602</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1266212463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1593360900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4490623474121</t>
+    <t xml:space="preserve">16.1266231536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1593341827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4490604400635</t>
   </si>
   <si>
     <t xml:space="preserve">16.1920471191406</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2154083251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4817733764648</t>
+    <t xml:space="preserve">16.2154102325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4817752838135</t>
   </si>
   <si>
     <t xml:space="preserve">16.5238304138184</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4023323059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.299524307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.579906463623</t>
+    <t xml:space="preserve">16.4023303985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2995262145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5799083709717</t>
   </si>
   <si>
     <t xml:space="preserve">17.1874008178711</t>
   </si>
   <si>
-    <t xml:space="preserve">17.785551071167</t>
+    <t xml:space="preserve">17.7855491638184</t>
   </si>
   <si>
     <t xml:space="preserve">17.1967468261719</t>
@@ -1973,7 +1973,7 @@
     <t xml:space="preserve">17.5518970489502</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4163780212402</t>
+    <t xml:space="preserve">17.4163799285889</t>
   </si>
   <si>
     <t xml:space="preserve">17.1079597473145</t>
@@ -2000,13 +2000,13 @@
     <t xml:space="preserve">17.6547031402588</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3369388580322</t>
+    <t xml:space="preserve">17.3369369506836</t>
   </si>
   <si>
     <t xml:space="preserve">17.1453418731689</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8462696075439</t>
+    <t xml:space="preserve">16.8462677001953</t>
   </si>
   <si>
     <t xml:space="preserve">17.1687107086182</t>
@@ -2015,7 +2015,7 @@
     <t xml:space="preserve">16.822904586792</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9911632537842</t>
+    <t xml:space="preserve">17.9911613464355</t>
   </si>
   <si>
     <t xml:space="preserve">17.9117221832275</t>
@@ -2030,10 +2030,10 @@
     <t xml:space="preserve">17.7948951721191</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6360111236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3275909423828</t>
+    <t xml:space="preserve">17.6360130310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3275928497314</t>
   </si>
   <si>
     <t xml:space="preserve">17.3976879119873</t>
@@ -2045,16 +2045,16 @@
     <t xml:space="preserve">17.5004940032959</t>
   </si>
   <si>
-    <t xml:space="preserve">17.869665145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3135986328125</t>
+    <t xml:space="preserve">17.8696632385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3136005401611</t>
   </si>
   <si>
     <t xml:space="preserve">18.056583404541</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2855625152588</t>
+    <t xml:space="preserve">18.2855606079102</t>
   </si>
   <si>
     <t xml:space="preserve">18.0192012786865</t>
@@ -2063,13 +2063,13 @@
     <t xml:space="preserve">17.9677982330322</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9070472717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.69211769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5051956176758</t>
+    <t xml:space="preserve">17.9070491790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6921157836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5051937103271</t>
   </si>
   <si>
     <t xml:space="preserve">18.3416385650635</t>
@@ -2078,7 +2078,7 @@
     <t xml:space="preserve">18.5565967559814</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4397716522217</t>
+    <t xml:space="preserve">18.4397735595703</t>
   </si>
   <si>
     <t xml:space="preserve">18.5472507476807</t>
@@ -2096,7 +2096,7 @@
     <t xml:space="preserve">18.5893096923828</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0238742828369</t>
+    <t xml:space="preserve">18.0238723754883</t>
   </si>
   <si>
     <t xml:space="preserve">17.8603172302246</t>
@@ -2111,10 +2111,10 @@
     <t xml:space="preserve">18.0939693450928</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8603744506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0472946166992</t>
+    <t xml:space="preserve">19.860372543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0472965240479</t>
   </si>
   <si>
     <t xml:space="preserve">19.9071025848389</t>
@@ -2123,25 +2123,25 @@
     <t xml:space="preserve">19.4607124328613</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9735870361328</t>
+    <t xml:space="preserve">19.9735889434814</t>
   </si>
   <si>
     <t xml:space="preserve">19.4132251739502</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2042751312256</t>
+    <t xml:space="preserve">19.2042770385742</t>
   </si>
   <si>
     <t xml:space="preserve">19.4892063140869</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1187973022461</t>
+    <t xml:space="preserve">19.1187953948975</t>
   </si>
   <si>
     <t xml:space="preserve">19.2327690124512</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9525871276855</t>
+    <t xml:space="preserve">18.9525890350342</t>
   </si>
   <si>
     <t xml:space="preserve">18.4397163391113</t>
@@ -2150,19 +2150,19 @@
     <t xml:space="preserve">17.7131423950195</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7273921966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8318614959717</t>
+    <t xml:space="preserve">17.7273902893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8318634033203</t>
   </si>
   <si>
     <t xml:space="preserve">18.3732299804688</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6534099578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1757850646973</t>
+    <t xml:space="preserve">18.6534118652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1757831573486</t>
   </si>
   <si>
     <t xml:space="preserve">19.3657360076904</t>
@@ -2174,13 +2174,13 @@
     <t xml:space="preserve">19.213773727417</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9810791015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9050998687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.033317565918</t>
+    <t xml:space="preserve">18.9810810089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.905101776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0333194732666</t>
   </si>
   <si>
     <t xml:space="preserve">19.6601657867432</t>
@@ -2195,46 +2195,46 @@
     <t xml:space="preserve">20.0210742950439</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8026294708252</t>
+    <t xml:space="preserve">19.8026275634766</t>
   </si>
   <si>
     <t xml:space="preserve">19.7171497344971</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8121280670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.745641708374</t>
+    <t xml:space="preserve">19.812126159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7456436157227</t>
   </si>
   <si>
     <t xml:space="preserve">19.926097869873</t>
   </si>
   <si>
-    <t xml:space="preserve">20.135046005249</t>
+    <t xml:space="preserve">20.1350498199463</t>
   </si>
   <si>
     <t xml:space="preserve">20.1920337677002</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4674663543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4864616394043</t>
+    <t xml:space="preserve">20.4674644470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4864597320557</t>
   </si>
   <si>
     <t xml:space="preserve">20.2870101928711</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2775135040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8406200408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.821626663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8501167297363</t>
+    <t xml:space="preserve">20.2775115966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8406181335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8216247558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.850118637085</t>
   </si>
   <si>
     <t xml:space="preserve">19.9545917510986</t>
@@ -2243,16 +2243,16 @@
     <t xml:space="preserve">19.8881092071533</t>
   </si>
   <si>
-    <t xml:space="preserve">20.030574798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8691139221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9640884399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0020809173584</t>
+    <t xml:space="preserve">20.0305728912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8691120147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.96409034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0020790100098</t>
   </si>
   <si>
     <t xml:space="preserve">19.9450931549072</t>
@@ -2264,19 +2264,19 @@
     <t xml:space="preserve">18.0218181610107</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9315872192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5754261016846</t>
+    <t xml:space="preserve">17.9315891265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5754241943359</t>
   </si>
   <si>
     <t xml:space="preserve">17.2952442169189</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2762489318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.266752243042</t>
+    <t xml:space="preserve">17.276252746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2667541503906</t>
   </si>
   <si>
     <t xml:space="preserve">17.3854732513428</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">16.8963451385498</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0150680541992</t>
+    <t xml:space="preserve">17.0150661468506</t>
   </si>
   <si>
     <t xml:space="preserve">16.59716796875</t>
@@ -2306,28 +2306,28 @@
     <t xml:space="preserve">17.0530548095703</t>
   </si>
   <si>
-    <t xml:space="preserve">16.915340423584</t>
+    <t xml:space="preserve">16.9153385162354</t>
   </si>
   <si>
     <t xml:space="preserve">16.6636505126953</t>
   </si>
   <si>
-    <t xml:space="preserve">16.734884262085</t>
+    <t xml:space="preserve">16.7348861694336</t>
   </si>
   <si>
     <t xml:space="preserve">16.948579788208</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7491302490234</t>
+    <t xml:space="preserve">16.7491321563721</t>
   </si>
   <si>
     <t xml:space="preserve">16.8441066741943</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4974422454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.668399810791</t>
+    <t xml:space="preserve">16.497444152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6683979034424</t>
   </si>
   <si>
     <t xml:space="preserve">16.6304092407227</t>
@@ -2336,7 +2336,7 @@
     <t xml:space="preserve">16.9248371124268</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4329624176025</t>
+    <t xml:space="preserve">17.4329605102539</t>
   </si>
   <si>
     <t xml:space="preserve">17.3807239532471</t>
@@ -2354,16 +2354,16 @@
     <t xml:space="preserve">17.2857475280762</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2002696990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6968936920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7538795471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2267570495605</t>
+    <t xml:space="preserve">17.2002716064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.696891784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7538776397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2267551422119</t>
   </si>
   <si>
     <t xml:space="preserve">16.1887664794922</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">16.1032905578613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0178089141846</t>
+    <t xml:space="preserve">16.0178108215332</t>
   </si>
   <si>
     <t xml:space="preserve">15.4811916351318</t>
@@ -2414,10 +2414,10 @@
     <t xml:space="preserve">15.4052095413208</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3244800567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2722434997559</t>
+    <t xml:space="preserve">15.324481010437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2722425460815</t>
   </si>
   <si>
     <t xml:space="preserve">15.2579975128174</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">15.1772661209106</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0680437088013</t>
+    <t xml:space="preserve">15.068042755127</t>
   </si>
   <si>
     <t xml:space="preserve">15.0348024368286</t>
@@ -2438,13 +2438,13 @@
     <t xml:space="preserve">15.9608240127563</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7661218643188</t>
+    <t xml:space="preserve">15.7661228179932</t>
   </si>
   <si>
     <t xml:space="preserve">15.8800926208496</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9085874557495</t>
+    <t xml:space="preserve">15.9085865020752</t>
   </si>
   <si>
     <t xml:space="preserve">15.922833442688</t>
@@ -2459,10 +2459,10 @@
     <t xml:space="preserve">16.4024639129639</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5781726837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5734233856201</t>
+    <t xml:space="preserve">16.5781707763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5734252929688</t>
   </si>
   <si>
     <t xml:space="preserve">16.6066665649414</t>
@@ -2471,10 +2471,10 @@
     <t xml:space="preserve">17.2809982299805</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9723262786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4404563903809</t>
+    <t xml:space="preserve">16.9723281860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4404544830322</t>
   </si>
   <si>
     <t xml:space="preserve">16.3074893951416</t>
@@ -2486,40 +2486,40 @@
     <t xml:space="preserve">16.3977165222168</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6209106445312</t>
+    <t xml:space="preserve">16.6209125518799</t>
   </si>
   <si>
     <t xml:space="preserve">17.3047428131104</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1290378570557</t>
+    <t xml:space="preserve">17.129035949707</t>
   </si>
   <si>
     <t xml:space="preserve">17.1860218048096</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6873970031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9695796966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1120452880859</t>
+    <t xml:space="preserve">16.6873950958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9695816040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1120433807373</t>
   </si>
   <si>
     <t xml:space="preserve">17.4282131195068</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3474826812744</t>
+    <t xml:space="preserve">17.3474807739258</t>
   </si>
   <si>
     <t xml:space="preserve">17.2477569580078</t>
   </si>
   <si>
-    <t xml:space="preserve">17.337984085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4092178344727</t>
+    <t xml:space="preserve">17.3379859924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.409215927124</t>
   </si>
   <si>
     <t xml:space="preserve">17.62766456604</t>
@@ -2531,19 +2531,19 @@
     <t xml:space="preserve">17.4804515838623</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8033714294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1167964935303</t>
+    <t xml:space="preserve">17.803373336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.116792678833</t>
   </si>
   <si>
     <t xml:space="preserve">17.8556079864502</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8081207275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0028228759766</t>
+    <t xml:space="preserve">17.8081188201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0028209686279</t>
   </si>
   <si>
     <t xml:space="preserve">17.6704025268555</t>
@@ -2552,31 +2552,31 @@
     <t xml:space="preserve">17.6229152679443</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6799030303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9885768890381</t>
+    <t xml:space="preserve">17.6799011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9885749816895</t>
   </si>
   <si>
     <t xml:space="preserve">18.4207191467285</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0930480957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.90309715271</t>
+    <t xml:space="preserve">18.0930500030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9030952453613</t>
   </si>
   <si>
     <t xml:space="preserve">17.8508586883545</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2620029449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.228759765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.095796585083</t>
+    <t xml:space="preserve">17.2620048522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2287616729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0957946777344</t>
   </si>
   <si>
     <t xml:space="preserve">16.8868465423584</t>
@@ -2585,13 +2585,13 @@
     <t xml:space="preserve">16.6161632537842</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5924186706543</t>
+    <t xml:space="preserve">16.5924167633057</t>
   </si>
   <si>
     <t xml:space="preserve">15.8611001968384</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2694969177246</t>
+    <t xml:space="preserve">16.2694988250732</t>
   </si>
   <si>
     <t xml:space="preserve">16.2979907989502</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">16.1175346374512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8468494415283</t>
+    <t xml:space="preserve">15.8468523025513</t>
   </si>
   <si>
     <t xml:space="preserve">16.3217353820801</t>
@@ -2615,10 +2615,10 @@
     <t xml:space="preserve">15.7186317443848</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3434762954712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9845685958862</t>
+    <t xml:space="preserve">15.3434772491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9845676422119</t>
   </si>
   <si>
     <t xml:space="preserve">15.7471265792847</t>
@@ -2627,37 +2627,37 @@
     <t xml:space="preserve">15.6046619415283</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7043867111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8848438262939</t>
+    <t xml:space="preserve">15.7043857574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8848428726196</t>
   </si>
   <si>
     <t xml:space="preserve">15.5429258346558</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1582717895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8096036911011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8665895462036</t>
+    <t xml:space="preserve">15.1582708358765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8096027374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8665885925293</t>
   </si>
   <si>
     <t xml:space="preserve">14.1420221328735</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6054039001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5721607208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0735340118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0497894287109</t>
+    <t xml:space="preserve">13.6054029464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5721616744995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0735349655151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0497903823853</t>
   </si>
   <si>
     <t xml:space="preserve">12.9738092422485</t>
@@ -2666,22 +2666,22 @@
     <t xml:space="preserve">12.3184700012207</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0477876663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2784757614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6563787460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7845973968506</t>
+    <t xml:space="preserve">12.0477867126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2784767150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.656379699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7845964431763</t>
   </si>
   <si>
     <t xml:space="preserve">9.08166599273682</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65437412261963</t>
+    <t xml:space="preserve">9.65437507629395</t>
   </si>
   <si>
     <t xml:space="preserve">10.0057888031006</t>
@@ -2690,13 +2690,13 @@
     <t xml:space="preserve">9.97254657745361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49766445159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6183891296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8625812530518</t>
+    <t xml:space="preserve">9.4976634979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6183881759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8625822067261</t>
   </si>
   <si>
     <t xml:space="preserve">12.1665077209473</t>
@@ -2705,28 +2705,28 @@
     <t xml:space="preserve">13.0877809524536</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3964548110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9690589904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2519865036011</t>
+    <t xml:space="preserve">13.3964538574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9690599441528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2519855499268</t>
   </si>
   <si>
     <t xml:space="preserve">11.9195680618286</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4921731948853</t>
+    <t xml:space="preserve">11.4921741485596</t>
   </si>
   <si>
     <t xml:space="preserve">11.2072429656982</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1597547531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1882467269897</t>
+    <t xml:space="preserve">11.1597557067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1882476806641</t>
   </si>
   <si>
     <t xml:space="preserve">11.5681552886963</t>
@@ -2735,10 +2735,10 @@
     <t xml:space="preserve">11.5586566925049</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6251401901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9765529632568</t>
+    <t xml:space="preserve">11.6251411437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9765539169312</t>
   </si>
   <si>
     <t xml:space="preserve">11.4541835784912</t>
@@ -2747,31 +2747,31 @@
     <t xml:space="preserve">11.2927227020264</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5396604537964</t>
+    <t xml:space="preserve">11.5396614074707</t>
   </si>
   <si>
     <t xml:space="preserve">10.8178396224976</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3999423980713</t>
+    <t xml:space="preserve">10.3999404907227</t>
   </si>
   <si>
     <t xml:space="preserve">10.4474306106567</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3809471130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7323608398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9128150939941</t>
+    <t xml:space="preserve">10.3809461593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7323598861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9128160476685</t>
   </si>
   <si>
     <t xml:space="preserve">10.7228622436523</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3049650192261</t>
+    <t xml:space="preserve">10.3049659729004</t>
   </si>
   <si>
     <t xml:space="preserve">10.3524532318115</t>
@@ -2780,37 +2780,37 @@
     <t xml:space="preserve">10.3144626617432</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3429574966431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4094390869141</t>
+    <t xml:space="preserve">10.3429555892944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4094400405884</t>
   </si>
   <si>
     <t xml:space="preserve">10.2574768066406</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0295333862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9060640335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89656639099121</t>
+    <t xml:space="preserve">10.0295324325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90606307983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89656543731689</t>
   </si>
   <si>
     <t xml:space="preserve">9.64962577819824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78259468078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4949188232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3469638824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9005727767944</t>
+    <t xml:space="preserve">9.78259372711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4949178695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.346962928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9005718231201</t>
   </si>
   <si>
     <t xml:space="preserve">12.2614841461182</t>
@@ -2825,28 +2825,28 @@
     <t xml:space="preserve">13.6576404571533</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2872314453125</t>
+    <t xml:space="preserve">13.2872304916382</t>
   </si>
   <si>
     <t xml:space="preserve">13.1542644500732</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8218460083008</t>
+    <t xml:space="preserve">12.8218469619751</t>
   </si>
   <si>
     <t xml:space="preserve">11.8815774917603</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7771024703979</t>
+    <t xml:space="preserve">11.7771034240723</t>
   </si>
   <si>
     <t xml:space="preserve">12.062032699585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1190185546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2899770736694</t>
+    <t xml:space="preserve">12.1190195083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2899761199951</t>
   </si>
   <si>
     <t xml:space="preserve">12.3089714050293</t>
@@ -2855,7 +2855,7 @@
     <t xml:space="preserve">12.7078742980957</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5749073028564</t>
+    <t xml:space="preserve">12.5749063491821</t>
   </si>
   <si>
     <t xml:space="preserve">12.5844049453735</t>
@@ -2867,7 +2867,7 @@
     <t xml:space="preserve">11.8055963516235</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5111684799194</t>
+    <t xml:space="preserve">11.5111694335938</t>
   </si>
   <si>
     <t xml:space="preserve">11.7296152114868</t>
@@ -2876,10 +2876,10 @@
     <t xml:space="preserve">11.4446849822998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5206670761108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7581071853638</t>
+    <t xml:space="preserve">11.5206661224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7581081390381</t>
   </si>
   <si>
     <t xml:space="preserve">11.5871496200562</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">11.4826755523682</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3402109146118</t>
+    <t xml:space="preserve">11.3402099609375</t>
   </si>
   <si>
     <t xml:space="preserve">10.9887962341309</t>
@@ -2897,19 +2897,19 @@
     <t xml:space="preserve">11.1787509918213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2262382507324</t>
+    <t xml:space="preserve">11.2262372970581</t>
   </si>
   <si>
     <t xml:space="preserve">11.2452335357666</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1027679443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1312618255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0267868041992</t>
+    <t xml:space="preserve">11.1027688980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1312627792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0267877578735</t>
   </si>
   <si>
     <t xml:space="preserve">11.0837736129761</t>
@@ -2918,10 +2918,10 @@
     <t xml:space="preserve">10.8368349075317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0552816390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2167406082153</t>
+    <t xml:space="preserve">11.0552806854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2167415618896</t>
   </si>
   <si>
     <t xml:space="preserve">10.5708999633789</t>
@@ -2936,7 +2936,7 @@
     <t xml:space="preserve">10.3619508743286</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6441354751587</t>
+    <t xml:space="preserve">11.644136428833</t>
   </si>
   <si>
     <t xml:space="preserve">11.3307132720947</t>
@@ -2945,46 +2945,46 @@
     <t xml:space="preserve">11.0932712554932</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9603042602539</t>
+    <t xml:space="preserve">10.9603033065796</t>
   </si>
   <si>
     <t xml:space="preserve">10.7608528137207</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7798480987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6753749847412</t>
+    <t xml:space="preserve">10.7798500061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6753740310669</t>
   </si>
   <si>
     <t xml:space="preserve">11.6156425476074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.463680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3971967697144</t>
+    <t xml:space="preserve">11.4636793136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3971977233887</t>
   </si>
   <si>
     <t xml:space="preserve">11.5016708374023</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7960996627808</t>
+    <t xml:space="preserve">11.7960987091064</t>
   </si>
   <si>
     <t xml:space="preserve">11.4731779098511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4256887435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5179214477539</t>
+    <t xml:space="preserve">11.4256896972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5179204940796</t>
   </si>
   <si>
     <t xml:space="preserve">12.565408706665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0810289382935</t>
+    <t xml:space="preserve">12.0810279846191</t>
   </si>
   <si>
     <t xml:space="preserve">11.6821269989014</t>
@@ -2993,16 +2993,16 @@
     <t xml:space="preserve">11.6061458587646</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1095209121704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0145454406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9385633468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.957558631897</t>
+    <t xml:space="preserve">12.1095218658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0145435333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9385623931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9575576782227</t>
   </si>
   <si>
     <t xml:space="preserve">11.9860515594482</t>
@@ -3023,19 +3023,19 @@
     <t xml:space="preserve">12.5464134216309</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2044973373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4039497375488</t>
+    <t xml:space="preserve">12.2044982910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4039487838745</t>
   </si>
   <si>
     <t xml:space="preserve">12.8978271484375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1950006484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8910751342773</t>
+    <t xml:space="preserve">12.1949996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8910760879517</t>
   </si>
   <si>
     <t xml:space="preserve">11.67262840271</t>
@@ -3047,43 +3047,43 @@
     <t xml:space="preserve">10.6943693161011</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5139141082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7988433837891</t>
+    <t xml:space="preserve">10.5139131546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7988443374634</t>
   </si>
   <si>
     <t xml:space="preserve">11.0647783279419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.359206199646</t>
+    <t xml:space="preserve">11.3592052459717</t>
   </si>
   <si>
     <t xml:space="preserve">12.3659582138062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7933540344238</t>
+    <t xml:space="preserve">12.7933530807495</t>
   </si>
   <si>
     <t xml:space="preserve">13.3537158966064</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7811098098755</t>
+    <t xml:space="preserve">13.7811107635498</t>
   </si>
   <si>
     <t xml:space="preserve">13.7146263122559</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9235754013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9330739974976</t>
+    <t xml:space="preserve">13.9235744476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9330730438232</t>
   </si>
   <si>
     <t xml:space="preserve">14.2369976043701</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3414716720581</t>
+    <t xml:space="preserve">14.3414726257324</t>
   </si>
   <si>
     <t xml:space="preserve">14.0470447540283</t>
@@ -3098,16 +3098,16 @@
     <t xml:space="preserve">14.1515197753906</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2464962005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4269514083862</t>
+    <t xml:space="preserve">14.2464952468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4269504547119</t>
   </si>
   <si>
     <t xml:space="preserve">14.4649410247803</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9113311767578</t>
+    <t xml:space="preserve">14.9113321304321</t>
   </si>
   <si>
     <t xml:space="preserve">14.4934358596802</t>
@@ -3116,16 +3116,16 @@
     <t xml:space="preserve">14.3509693145752</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5979099273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7498712539673</t>
+    <t xml:space="preserve">14.5979080200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7498722076416</t>
   </si>
   <si>
     <t xml:space="preserve">15.1487741470337</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8828392028809</t>
+    <t xml:space="preserve">14.8828401565552</t>
   </si>
   <si>
     <t xml:space="preserve">14.8543462753296</t>
@@ -3152,19 +3152,19 @@
     <t xml:space="preserve">15.0632944107056</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9493227005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7688674926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7118816375732</t>
+    <t xml:space="preserve">14.9493217468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7688684463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7118806838989</t>
   </si>
   <si>
     <t xml:space="preserve">14.5884113311768</t>
   </si>
   <si>
-    <t xml:space="preserve">14.578914642334</t>
+    <t xml:space="preserve">14.5789136886597</t>
   </si>
   <si>
     <t xml:space="preserve">14.4079561233521</t>
@@ -3173,16 +3173,16 @@
     <t xml:space="preserve">14.5504207611084</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5314254760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9615659713745</t>
+    <t xml:space="preserve">14.5314264297485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9615650177002</t>
   </si>
   <si>
     <t xml:space="preserve">14.2085056304932</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4459457397461</t>
+    <t xml:space="preserve">14.4459466934204</t>
   </si>
   <si>
     <t xml:space="preserve">15.29123878479</t>
@@ -3194,10 +3194,10 @@
     <t xml:space="preserve">15.0537977218628</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8041124343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6711444854736</t>
+    <t xml:space="preserve">15.8041133880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6711454391479</t>
   </si>
   <si>
     <t xml:space="preserve">15.2627458572388</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">14.9588203430176</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0443000793457</t>
+    <t xml:space="preserve">15.0442991256714</t>
   </si>
   <si>
     <t xml:space="preserve">14.721378326416</t>
@@ -3218,22 +3218,22 @@
     <t xml:space="preserve">14.4364490509033</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7403745651245</t>
+    <t xml:space="preserve">14.7403755187988</t>
   </si>
   <si>
     <t xml:space="preserve">15.006308555603</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0822906494141</t>
+    <t xml:space="preserve">15.0822896957397</t>
   </si>
   <si>
     <t xml:space="preserve">14.9778165817261</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6928863525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7783641815186</t>
+    <t xml:space="preserve">14.6928853988647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7783651351929</t>
   </si>
   <si>
     <t xml:space="preserve">14.8258533477783</t>
@@ -3242,7 +3242,7 @@
     <t xml:space="preserve">15.2057600021362</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1202802658081</t>
+    <t xml:space="preserve">15.1202812194824</t>
   </si>
   <si>
     <t xml:space="preserve">15.0917882919312</t>
@@ -3257,7 +3257,7 @@
     <t xml:space="preserve">14.9873132705688</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8705949783325</t>
+    <t xml:space="preserve">15.8705959320068</t>
   </si>
   <si>
     <t xml:space="preserve">16.0225601196289</t>
@@ -3266,13 +3266,13 @@
     <t xml:space="preserve">16.0320568084717</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8231086730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9370803833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7376270294189</t>
+    <t xml:space="preserve">15.8231077194214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9370794296265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7376279830933</t>
   </si>
   <si>
     <t xml:space="preserve">15.4906892776489</t>
@@ -3281,31 +3281,31 @@
     <t xml:space="preserve">15.7091360092163</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3102350234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3672208786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3387260437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6996402740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6853904724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6189069747925</t>
+    <t xml:space="preserve">15.3102340698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3672199249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3387269973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6996374130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6853914260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6189079284668</t>
   </si>
   <si>
     <t xml:space="preserve">15.428955078125</t>
   </si>
   <si>
-    <t xml:space="preserve">15.637903213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.739631652832</t>
+    <t xml:space="preserve">15.6379022598267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7396335601807</t>
   </si>
   <si>
     <t xml:space="preserve">16.8678512573242</t>
@@ -3314,7 +3314,7 @@
     <t xml:space="preserve">16.8725986480713</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4784488677979</t>
+    <t xml:space="preserve">16.4784469604492</t>
   </si>
   <si>
     <t xml:space="preserve">17.0340595245361</t>
@@ -3326,10 +3326,10 @@
     <t xml:space="preserve">17.4567050933838</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0388088226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2904987335205</t>
+    <t xml:space="preserve">17.0388107299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2904968261719</t>
   </si>
   <si>
     <t xml:space="preserve">17.0815486907959</t>
@@ -3338,31 +3338,31 @@
     <t xml:space="preserve">17.0245628356934</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9770736694336</t>
+    <t xml:space="preserve">16.9770755767822</t>
   </si>
   <si>
     <t xml:space="preserve">17.2572555541992</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4614562988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4187164306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2117691040039</t>
+    <t xml:space="preserve">17.4614543914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4187145233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2117710113525</t>
   </si>
   <si>
     <t xml:space="preserve">18.3589839935303</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1975231170654</t>
+    <t xml:space="preserve">18.1975250244141</t>
   </si>
   <si>
     <t xml:space="preserve">18.1500358581543</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2307662963867</t>
+    <t xml:space="preserve">18.2307643890381</t>
   </si>
   <si>
     <t xml:space="preserve">18.0360641479492</t>
@@ -3374,16 +3374,16 @@
     <t xml:space="preserve">17.9553356170654</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6846504211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0408115386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3304920196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3209934234619</t>
+    <t xml:space="preserve">17.6846523284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0408134460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3304901123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3209953308105</t>
   </si>
   <si>
     <t xml:space="preserve">18.368480682373</t>
@@ -3392,7 +3392,7 @@
     <t xml:space="preserve">18.3019981384277</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3542366027832</t>
+    <t xml:space="preserve">18.3542346954346</t>
   </si>
   <si>
     <t xml:space="preserve">18.3969745635986</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">18.1832790374756</t>
   </si>
   <si>
-    <t xml:space="preserve">18.444465637207</t>
+    <t xml:space="preserve">18.4444637298584</t>
   </si>
   <si>
     <t xml:space="preserve">18.8956031799316</t>
@@ -3419,10 +3419,10 @@
     <t xml:space="preserve">18.6961498260498</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5584373474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.335241317749</t>
+    <t xml:space="preserve">18.5584354400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3352394104004</t>
   </si>
   <si>
     <t xml:space="preserve">17.8461112976074</t>
@@ -3431,7 +3431,7 @@
     <t xml:space="preserve">17.1527805328369</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1812744140625</t>
+    <t xml:space="preserve">17.1812725067139</t>
   </si>
   <si>
     <t xml:space="preserve">17.0673007965088</t>
@@ -3440,22 +3440,22 @@
     <t xml:space="preserve">17.1575298309326</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6114120483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5021896362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7253856658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8773498535156</t>
+    <t xml:space="preserve">16.6114139556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5021915435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7253875732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.877347946167</t>
   </si>
   <si>
     <t xml:space="preserve">16.4214611053467</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9798192977905</t>
+    <t xml:space="preserve">15.9798202514648</t>
   </si>
   <si>
     <t xml:space="preserve">16.0985412597656</t>
@@ -3464,28 +3464,28 @@
     <t xml:space="preserve">16.0083122253418</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2505054473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4736976623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1697731018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0463027954102</t>
+    <t xml:space="preserve">16.2505035400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4736957550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.169771194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0463047027588</t>
   </si>
   <si>
     <t xml:space="preserve">16.0368061065674</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9988136291504</t>
+    <t xml:space="preserve">15.9988145828247</t>
   </si>
   <si>
     <t xml:space="preserve">16.2600021362305</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0652980804443</t>
+    <t xml:space="preserve">16.065299987793</t>
   </si>
   <si>
     <t xml:space="preserve">16.0510520935059</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">17.1100406646729</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3949699401855</t>
+    <t xml:space="preserve">17.3949718475342</t>
   </si>
   <si>
     <t xml:space="preserve">18.4919509887695</t>
@@ -3503,34 +3503,34 @@
     <t xml:space="preserve">17.5896739959717</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6609058380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0008163452148</t>
+    <t xml:space="preserve">17.6609039306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0008182525635</t>
   </si>
   <si>
     <t xml:space="preserve">16.6731491088867</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5164356231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7328796386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7423791885376</t>
+    <t xml:space="preserve">16.5164375305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7328805923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7423782348633</t>
   </si>
   <si>
     <t xml:space="preserve">16.1460285186768</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9275808334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9703226089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6541538238525</t>
+    <t xml:space="preserve">15.9275827407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9703216552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6541519165039</t>
   </si>
   <si>
     <t xml:space="preserve">16.7586288452148</t>
@@ -3551,13 +3551,13 @@
     <t xml:space="preserve">16.8251113891602</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7206363677979</t>
+    <t xml:space="preserve">16.7206382751465</t>
   </si>
   <si>
     <t xml:space="preserve">16.9628295898438</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9438323974609</t>
+    <t xml:space="preserve">16.9438304901123</t>
   </si>
   <si>
     <t xml:space="preserve">16.8298587799072</t>
@@ -3578,19 +3578,19 @@
     <t xml:space="preserve">16.7111377716064</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2145156860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4424591064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3427352905273</t>
+    <t xml:space="preserve">17.2145175933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4424610137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3427333831787</t>
   </si>
   <si>
     <t xml:space="preserve">17.4662036895752</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7178916931152</t>
+    <t xml:space="preserve">17.7178936004639</t>
   </si>
   <si>
     <t xml:space="preserve">17.7748775482178</t>
@@ -3608,22 +3608,22 @@
     <t xml:space="preserve">18.7911281585693</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9715824127197</t>
+    <t xml:space="preserve">18.9715843200684</t>
   </si>
   <si>
     <t xml:space="preserve">17.945837020874</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4302158355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5536880493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7626323699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0903034210205</t>
+    <t xml:space="preserve">18.4302177429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5536861419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7626342773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0903053283691</t>
   </si>
   <si>
     <t xml:space="preserve">19.3752346038818</t>
@@ -3641,28 +3641,28 @@
     <t xml:space="preserve">20.5529441833496</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6221733093262</t>
+    <t xml:space="preserve">19.6221752166748</t>
   </si>
   <si>
     <t xml:space="preserve">19.1377925872803</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6316699981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4579696655273</t>
+    <t xml:space="preserve">19.6316719055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4579677581787</t>
   </si>
   <si>
     <t xml:space="preserve">20.6289253234863</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0373249053955</t>
+    <t xml:space="preserve">21.0373229980469</t>
   </si>
   <si>
     <t xml:space="preserve">21.4457244873047</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9898376464844</t>
+    <t xml:space="preserve">20.9898357391357</t>
   </si>
   <si>
     <t xml:space="preserve">20.7523956298828</t>
@@ -3677,46 +3677,46 @@
     <t xml:space="preserve">20.0970573425293</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7903842926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7144050598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0278282165527</t>
+    <t xml:space="preserve">20.7903861999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7144031524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0278263092041</t>
   </si>
   <si>
     <t xml:space="preserve">21.0183296203613</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0943088531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4172325134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3982391357422</t>
+    <t xml:space="preserve">21.094310760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4172306060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3982372283936</t>
   </si>
   <si>
     <t xml:space="preserve">21.7021617889404</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5691947937012</t>
+    <t xml:space="preserve">21.5691928863525</t>
   </si>
   <si>
     <t xml:space="preserve">22.0820693969727</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5976867675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6261825561523</t>
+    <t xml:space="preserve">21.5976886749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6261806488037</t>
   </si>
   <si>
     <t xml:space="preserve">19.4797096252441</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0998020172119</t>
+    <t xml:space="preserve">19.0998001098633</t>
   </si>
   <si>
     <t xml:space="preserve">19.536693572998</t>
@@ -3731,13 +3731,13 @@
     <t xml:space="preserve">18.0550594329834</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4946956634521</t>
+    <t xml:space="preserve">17.4946975708008</t>
   </si>
   <si>
     <t xml:space="preserve">18.2212677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9743270874023</t>
+    <t xml:space="preserve">17.974328994751</t>
   </si>
   <si>
     <t xml:space="preserve">18.5916767120361</t>
@@ -3746,7 +3746,7 @@
     <t xml:space="preserve">18.5394401550293</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0977973937988</t>
+    <t xml:space="preserve">18.0977993011475</t>
   </si>
   <si>
     <t xml:space="preserve">18.0503082275391</t>
@@ -3767,7 +3767,7 @@
     <t xml:space="preserve">18.68190574646</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7721328735352</t>
+    <t xml:space="preserve">18.7721309661865</t>
   </si>
   <si>
     <t xml:space="preserve">18.8006267547607</t>
@@ -3785,40 +3785,40 @@
     <t xml:space="preserve">18.6581611633301</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4492111206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6324138641357</t>
+    <t xml:space="preserve">18.4492130279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6324119567871</t>
   </si>
   <si>
     <t xml:space="preserve">17.7368869781494</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1242904663086</t>
+    <t xml:space="preserve">17.12428855896</t>
   </si>
   <si>
     <t xml:space="preserve">15.1867637634277</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8306016921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5076818466187</t>
+    <t xml:space="preserve">14.8306007385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5076808929443</t>
   </si>
   <si>
     <t xml:space="preserve">15.9133348464966</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3529739379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.457447052002</t>
+    <t xml:space="preserve">15.3529748916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4574489593506</t>
   </si>
   <si>
     <t xml:space="preserve">14.8733415603638</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5856676101685</t>
+    <t xml:space="preserve">15.5856657028198</t>
   </si>
   <si>
     <t xml:space="preserve">15.81360912323</t>
@@ -3827,10 +3827,10 @@
     <t xml:space="preserve">15.5334281921387</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2390012741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2532482147217</t>
+    <t xml:space="preserve">15.2390022277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2532472610474</t>
   </si>
   <si>
     <t xml:space="preserve">15.5191822052002</t>
@@ -3839,7 +3839,7 @@
     <t xml:space="preserve">15.8278579711914</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7681274414062</t>
+    <t xml:space="preserve">16.7681255340576</t>
   </si>
   <si>
     <t xml:space="preserve">16.316987991333</t>
@@ -3854,13 +3854,13 @@
     <t xml:space="preserve">15.6331548690796</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6521482467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.889591217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5096845626831</t>
+    <t xml:space="preserve">15.6521492004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8895902633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5096855163574</t>
   </si>
   <si>
     <t xml:space="preserve">14.7308769226074</t>
@@ -3869,10 +3869,10 @@
     <t xml:space="preserve">14.8638439178467</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1392765045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7851181030273</t>
+    <t xml:space="preserve">15.1392755508423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7851190567017</t>
   </si>
   <si>
     <t xml:space="preserve">14.3034820556641</t>
@@ -3884,7 +3884,7 @@
     <t xml:space="preserve">13.8285989761353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.812349319458</t>
+    <t xml:space="preserve">12.8123483657837</t>
   </si>
   <si>
     <t xml:space="preserve">14.1040306091309</t>
@@ -3893,7 +3893,7 @@
     <t xml:space="preserve">14.1990070343018</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0158061981201</t>
+    <t xml:space="preserve">15.0158071517944</t>
   </si>
   <si>
     <t xml:space="preserve">14.5219278335571</t>
@@ -71282,7 +71282,7 @@
     </row>
     <row r="2500">
       <c r="A2500" s="1" t="n">
-        <v>45959.6930324074</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2500" t="n">
         <v>543530</v>
@@ -71303,6 +71303,32 @@
         <v>1842</v>
       </c>
       <c r="H2500" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" s="1" t="n">
+        <v>45960.6911226852</v>
+      </c>
+      <c r="B2501" t="n">
+        <v>462770</v>
+      </c>
+      <c r="C2501" t="n">
+        <v>7.32000017166138</v>
+      </c>
+      <c r="D2501" t="n">
+        <v>7.07000017166138</v>
+      </c>
+      <c r="E2501" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="F2501" t="n">
+        <v>7.19500017166138</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>1837</v>
+      </c>
+      <c r="H2501" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1994" uniqueCount="1994">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1995" uniqueCount="1995">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2763519287109</t>
+    <t xml:space="preserve">18.2763500213623</t>
   </si>
   <si>
     <t xml:space="preserve">SFER.MI</t>
@@ -47,16 +47,16 @@
     <t xml:space="preserve">18.0109634399414</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4978828430176</t>
+    <t xml:space="preserve">17.4978809356689</t>
   </si>
   <si>
     <t xml:space="preserve">17.9401950836182</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6836547851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2498149871826</t>
+    <t xml:space="preserve">17.683650970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.249813079834</t>
   </si>
   <si>
     <t xml:space="preserve">19.4086723327637</t>
@@ -65,73 +65,73 @@
     <t xml:space="preserve">19.1344375610352</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8425140380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4621238708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2852001190186</t>
+    <t xml:space="preserve">18.8425102233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.462121963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2851963043213</t>
   </si>
   <si>
     <t xml:space="preserve">18.0994262695312</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6394233703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5686550140381</t>
+    <t xml:space="preserve">17.6394195556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5686511993408</t>
   </si>
   <si>
     <t xml:space="preserve">18.1878871917725</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4798107147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2232723236084</t>
+    <t xml:space="preserve">18.4798126220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.223274230957</t>
   </si>
   <si>
     <t xml:space="preserve">17.7632675170898</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3913555145264</t>
+    <t xml:space="preserve">18.3913536071777</t>
   </si>
   <si>
     <t xml:space="preserve">18.6744346618652</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9578876495361</t>
+    <t xml:space="preserve">17.9578857421875</t>
   </si>
   <si>
     <t xml:space="preserve">18.2055816650391</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2586555480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0817337036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3563423156738</t>
+    <t xml:space="preserve">18.258659362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0817356109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3563404083252</t>
   </si>
   <si>
     <t xml:space="preserve">16.9051818847656</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1617202758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6486415863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0201835632324</t>
+    <t xml:space="preserve">17.1617259979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6486434936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0201854705811</t>
   </si>
   <si>
     <t xml:space="preserve">17.4890365600586</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6305751800537</t>
+    <t xml:space="preserve">17.6305732727051</t>
   </si>
   <si>
     <t xml:space="preserve">18.4090442657471</t>
@@ -140,34 +140,34 @@
     <t xml:space="preserve">18.453275680542</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9752044677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1348152160645</t>
+    <t xml:space="preserve">18.9752063751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1348094940186</t>
   </si>
   <si>
     <t xml:space="preserve">17.3121089935303</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9048099517822</t>
+    <t xml:space="preserve">17.9048080444336</t>
   </si>
   <si>
     <t xml:space="preserve">18.3471202850342</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0194358825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.001745223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8513603210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3113613128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9925231933594</t>
+    <t xml:space="preserve">19.019437789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0017433166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8513565063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3113632202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.992525100708</t>
   </si>
   <si>
     <t xml:space="preserve">19.9482917785645</t>
@@ -176,61 +176,61 @@
     <t xml:space="preserve">19.7271347045898</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3379020690918</t>
+    <t xml:space="preserve">19.3379039764404</t>
   </si>
   <si>
     <t xml:space="preserve">19.6475200653076</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9836769104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1167469024658</t>
+    <t xml:space="preserve">19.9836807250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1167449951172</t>
   </si>
   <si>
     <t xml:space="preserve">19.444055557251</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0367546081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1782932281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4971332550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4705924987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9663619995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4794387817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9129047393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8686771392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4175186157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8690509796143</t>
+    <t xml:space="preserve">20.0367565155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.178295135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4971351623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4705963134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9663581848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4794406890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9129085540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.868673324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.417516708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8690490722656</t>
   </si>
   <si>
     <t xml:space="preserve">18.8336658477783</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5151996612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9309730529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8955898284912</t>
+    <t xml:space="preserve">18.5152034759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9309711456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8955917358398</t>
   </si>
   <si>
     <t xml:space="preserve">18.5240478515625</t>
@@ -239,52 +239,52 @@
     <t xml:space="preserve">18.9486675262451</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7982807159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8778972625732</t>
+    <t xml:space="preserve">18.7982788085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8778991699219</t>
   </si>
   <si>
     <t xml:space="preserve">19.2936687469482</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8071250915527</t>
+    <t xml:space="preserve">18.80712890625</t>
   </si>
   <si>
     <t xml:space="preserve">18.3205814361572</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3648109436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8251914978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0640411376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3117351531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.878267288208</t>
+    <t xml:space="preserve">18.3648147583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8251895904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0640430450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3117370605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8782691955566</t>
   </si>
   <si>
     <t xml:space="preserve">18.0021171569824</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7190380096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4448051452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1440296173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5509605407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9844264984131</t>
+    <t xml:space="preserve">17.7190399169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.444803237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1440315246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5509586334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9844245910645</t>
   </si>
   <si>
     <t xml:space="preserve">17.4182682037354</t>
@@ -296,28 +296,28 @@
     <t xml:space="preserve">17.7367305755615</t>
   </si>
   <si>
-    <t xml:space="preserve">17.648265838623</t>
+    <t xml:space="preserve">17.6482715606689</t>
   </si>
   <si>
     <t xml:space="preserve">17.593936920166</t>
   </si>
   <si>
-    <t xml:space="preserve">17.81125831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7025947570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6482677459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.530553817749</t>
+    <t xml:space="preserve">17.8112564086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7025966644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6482696533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5305519104004</t>
   </si>
   <si>
     <t xml:space="preserve">17.4128360748291</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3041763305664</t>
+    <t xml:space="preserve">17.3041744232178</t>
   </si>
   <si>
     <t xml:space="preserve">17.4762210845947</t>
@@ -350,16 +350,16 @@
     <t xml:space="preserve">17.0778007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8384227752686</t>
+    <t xml:space="preserve">17.8384208679199</t>
   </si>
   <si>
     <t xml:space="preserve">17.9380302429199</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7297611236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8655891418457</t>
+    <t xml:space="preserve">17.7297630310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8655872344971</t>
   </si>
   <si>
     <t xml:space="preserve">18.1825141906738</t>
@@ -371,10 +371,10 @@
     <t xml:space="preserve">16.3896160125732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6793804168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2628440856934</t>
+    <t xml:space="preserve">16.6793785095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.262845993042</t>
   </si>
   <si>
     <t xml:space="preserve">16.5254440307617</t>
@@ -383,25 +383,25 @@
     <t xml:space="preserve">16.6069393157959</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8061485290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8242568969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0726909637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.873480796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3624515533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4439468383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6974906921387</t>
+    <t xml:space="preserve">16.8061466217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8242588043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0726890563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8734817504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3624496459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4439487457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.69748878479</t>
   </si>
   <si>
     <t xml:space="preserve">17.095911026001</t>
@@ -416,13 +416,13 @@
     <t xml:space="preserve">17.0325241088867</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3403949737549</t>
+    <t xml:space="preserve">17.3403968811035</t>
   </si>
   <si>
     <t xml:space="preserve">17.9018096923828</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1372394561768</t>
+    <t xml:space="preserve">18.1372413635254</t>
   </si>
   <si>
     <t xml:space="preserve">17.9289741516113</t>
@@ -431,31 +431,31 @@
     <t xml:space="preserve">18.771089553833</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6352653503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0699100494385</t>
+    <t xml:space="preserve">18.6352672576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0699081420898</t>
   </si>
   <si>
     <t xml:space="preserve">19.2147884368896</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6262092590332</t>
+    <t xml:space="preserve">18.6262130737305</t>
   </si>
   <si>
     <t xml:space="preserve">18.4994411468506</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2187366485596</t>
+    <t xml:space="preserve">18.2187328338623</t>
   </si>
   <si>
     <t xml:space="preserve">18.7167625427246</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5809345245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7620334625244</t>
+    <t xml:space="preserve">18.5809383392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.762035369873</t>
   </si>
   <si>
     <t xml:space="preserve">18.8073120117188</t>
@@ -473,7 +473,7 @@
     <t xml:space="preserve">18.4722747802734</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6171550750732</t>
+    <t xml:space="preserve">18.6171569824219</t>
   </si>
   <si>
     <t xml:space="preserve">18.7529792785645</t>
@@ -485,13 +485,13 @@
     <t xml:space="preserve">18.6805419921875</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6081008911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6533756256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5175514221191</t>
+    <t xml:space="preserve">18.6081027984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.653377532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5175495147705</t>
   </si>
   <si>
     <t xml:space="preserve">18.8706970214844</t>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">18.6986503601074</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1061305999756</t>
+    <t xml:space="preserve">19.1061267852783</t>
   </si>
   <si>
     <t xml:space="preserve">19.9210815429688</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">19.6947059631348</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5588817596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4592742919922</t>
+    <t xml:space="preserve">19.5588798522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4592761993408</t>
   </si>
   <si>
     <t xml:space="preserve">19.314395904541</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8888072967529</t>
+    <t xml:space="preserve">18.8888092041016</t>
   </si>
   <si>
     <t xml:space="preserve">19.1332931518555</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">19.1604614257812</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9391899108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4553279876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3557224273682</t>
+    <t xml:space="preserve">19.9391918182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4553298950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3557243347168</t>
   </si>
   <si>
     <t xml:space="preserve">20.3104496002197</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">20.6907596588135</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8446960449219</t>
+    <t xml:space="preserve">20.8446941375732</t>
   </si>
   <si>
     <t xml:space="preserve">20.7994194030762</t>
@@ -557,13 +557,13 @@
     <t xml:space="preserve">20.4009990692139</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1021823883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5277690887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3647785186768</t>
+    <t xml:space="preserve">20.1021842956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5277709960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3647766113281</t>
   </si>
   <si>
     <t xml:space="preserve">20.5458793640137</t>
@@ -572,7 +572,7 @@
     <t xml:space="preserve">20.7541465759277</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4191074371338</t>
+    <t xml:space="preserve">20.4191093444824</t>
   </si>
   <si>
     <t xml:space="preserve">20.0116329193115</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">20.265172958374</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3285598754883</t>
+    <t xml:space="preserve">20.3285617828369</t>
   </si>
   <si>
     <t xml:space="preserve">20.03879737854</t>
@@ -593,43 +593,43 @@
     <t xml:space="preserve">20.2289524078369</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5006046295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5639877319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1836814880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.549825668335</t>
+    <t xml:space="preserve">20.5006065368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5639896392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1836776733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5498275756836</t>
   </si>
   <si>
     <t xml:space="preserve">19.4140014648438</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5045490264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7218704223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7943115234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5226612091064</t>
+    <t xml:space="preserve">19.5045509338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7218723297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7943134307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5226631164551</t>
   </si>
   <si>
     <t xml:space="preserve">19.830530166626</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9120254516602</t>
+    <t xml:space="preserve">19.9120273590088</t>
   </si>
   <si>
     <t xml:space="preserve">19.7490348815918</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0919666290283</t>
+    <t xml:space="preserve">18.0919628143311</t>
   </si>
   <si>
     <t xml:space="preserve">18.3002281188965</t>
@@ -641,13 +641,13 @@
     <t xml:space="preserve">18.2458992004395</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0104675292969</t>
+    <t xml:space="preserve">18.0104694366455</t>
   </si>
   <si>
     <t xml:space="preserve">17.7388172149658</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8565330505371</t>
+    <t xml:space="preserve">17.8565311431885</t>
   </si>
   <si>
     <t xml:space="preserve">17.8203144073486</t>
@@ -656,40 +656,40 @@
     <t xml:space="preserve">17.6392116546631</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3455066680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3907814025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1514053344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2872314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3958911895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3777809143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1151866912842</t>
+    <t xml:space="preserve">18.3455047607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3907775878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.151403427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2872295379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3958892822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3777770996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1151847839355</t>
   </si>
   <si>
     <t xml:space="preserve">19.5860443115234</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2600650787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3738327026367</t>
+    <t xml:space="preserve">19.2600612640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3738346099854</t>
   </si>
   <si>
     <t xml:space="preserve">20.3466682434082</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2380104064941</t>
+    <t xml:space="preserve">20.2380084991455</t>
   </si>
   <si>
     <t xml:space="preserve">20.1293468475342</t>
@@ -707,13 +707,13 @@
     <t xml:space="preserve">21.4785480499268</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5328807830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0671272277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0580730438232</t>
+    <t xml:space="preserve">21.5328788757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0671253204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0580711364746</t>
   </si>
   <si>
     <t xml:space="preserve">22.2572803497314</t>
@@ -722,67 +722,67 @@
     <t xml:space="preserve">22.2935009002686</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3025531768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3206653594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2753925323486</t>
+    <t xml:space="preserve">22.3025569915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3206634521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.275390625</t>
   </si>
   <si>
     <t xml:space="preserve">22.2391719818115</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8186950683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0722332000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8911361694336</t>
+    <t xml:space="preserve">22.8186931610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0722351074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.891134262085</t>
   </si>
   <si>
     <t xml:space="preserve">23.1537303924561</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0993976593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5923156738281</t>
+    <t xml:space="preserve">23.0993995666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5923175811768</t>
   </si>
   <si>
     <t xml:space="preserve">22.3568859100342</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9092445373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1757850646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1395645141602</t>
+    <t xml:space="preserve">22.9092426300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1757888793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1395664215088</t>
   </si>
   <si>
     <t xml:space="preserve">23.6064834594727</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7513637542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1226177215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6427021026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6879768371582</t>
+    <t xml:space="preserve">23.7513618469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1226196289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6427059173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6879787445068</t>
   </si>
   <si>
     <t xml:space="preserve">23.561206817627</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7423076629639</t>
+    <t xml:space="preserve">23.7423057556152</t>
   </si>
   <si>
     <t xml:space="preserve">23.7241973876953</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">23.6336479187012</t>
   </si>
   <si>
-    <t xml:space="preserve">23.823802947998</t>
+    <t xml:space="preserve">23.8238010406494</t>
   </si>
   <si>
     <t xml:space="preserve">23.6970329284668</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">24.285608291626</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0682888031006</t>
+    <t xml:space="preserve">24.0682907104492</t>
   </si>
   <si>
     <t xml:space="preserve">23.9777374267578</t>
@@ -812,16 +812,16 @@
     <t xml:space="preserve">24.2946643829346</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4304904937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.61159324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7655277252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1911125183105</t>
+    <t xml:space="preserve">24.4304885864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6115913391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7655258178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1911144256592</t>
   </si>
   <si>
     <t xml:space="preserve">25.3903255462646</t>
@@ -836,25 +836,25 @@
     <t xml:space="preserve">25.6710319519043</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6529216766357</t>
+    <t xml:space="preserve">25.6529197692871</t>
   </si>
   <si>
     <t xml:space="preserve">25.7615814208984</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5352058410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9556789398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9013500213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0643444061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8017463684082</t>
+    <t xml:space="preserve">25.5352077484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9556827545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9013538360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0643463134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8017482757568</t>
   </si>
   <si>
     <t xml:space="preserve">24.6206474304199</t>
@@ -866,28 +866,28 @@
     <t xml:space="preserve">25.3722152709961</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6257572174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2273349761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1730041503906</t>
+    <t xml:space="preserve">25.62575340271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2273330688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.173002243042</t>
   </si>
   <si>
     <t xml:space="preserve">25.1639499664307</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3993797302246</t>
+    <t xml:space="preserve">25.399377822876</t>
   </si>
   <si>
     <t xml:space="preserve">25.7253608703613</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2907218933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1277275085449</t>
+    <t xml:space="preserve">25.2907180786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1277294158936</t>
   </si>
   <si>
     <t xml:space="preserve">25.7434711456299</t>
@@ -896,10 +896,10 @@
     <t xml:space="preserve">25.5442600250244</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4808750152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5080432891846</t>
+    <t xml:space="preserve">25.4808731079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5080394744873</t>
   </si>
   <si>
     <t xml:space="preserve">25.2635536193848</t>
@@ -908,13 +908,13 @@
     <t xml:space="preserve">25.0824546813965</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7836380004883</t>
+    <t xml:space="preserve">24.7836360931396</t>
   </si>
   <si>
     <t xml:space="preserve">24.4214344024658</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2674999237061</t>
+    <t xml:space="preserve">24.2674980163574</t>
   </si>
   <si>
     <t xml:space="preserve">25.5261516571045</t>
@@ -923,13 +923,13 @@
     <t xml:space="preserve">26.1237831115723</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1871662139893</t>
+    <t xml:space="preserve">26.1871643066406</t>
   </si>
   <si>
     <t xml:space="preserve">26.6308650970459</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4859848022461</t>
+    <t xml:space="preserve">26.4859828948975</t>
   </si>
   <si>
     <t xml:space="preserve">26.3229942321777</t>
@@ -938,37 +938,37 @@
     <t xml:space="preserve">26.6761379241943</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8934593200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2596073150635</t>
+    <t xml:space="preserve">26.893461227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2596092224121</t>
   </si>
   <si>
     <t xml:space="preserve">26.6670837402344</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9115695953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6036987304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5946445465088</t>
+    <t xml:space="preserve">26.9115676879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6037006378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5946464538574</t>
   </si>
   <si>
     <t xml:space="preserve">25.3088302612305</t>
   </si>
   <si>
-    <t xml:space="preserve">25.326940536499</t>
+    <t xml:space="preserve">25.3269367218018</t>
   </si>
   <si>
     <t xml:space="preserve">25.834020614624</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8984451293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0641059875488</t>
+    <t xml:space="preserve">25.8984413146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0641040802002</t>
   </si>
   <si>
     <t xml:space="preserve">24.7112045288086</t>
@@ -977,19 +977,19 @@
     <t xml:space="preserve">23.6159954071045</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2202472686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1282119750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9625492095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8705177307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8613128662109</t>
+    <t xml:space="preserve">23.2202453613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.128210067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9625511169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8705196380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8613147735596</t>
   </si>
   <si>
     <t xml:space="preserve">23.2662658691406</t>
@@ -998,31 +998,31 @@
     <t xml:space="preserve">23.2386531829834</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0453853607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8889236450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.088228225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3183116912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2262763977051</t>
+    <t xml:space="preserve">23.0453834533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8889255523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0882263183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3183135986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2262744903564</t>
   </si>
   <si>
     <t xml:space="preserve">22.3827342987061</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3643283843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7416667938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9533462524414</t>
+    <t xml:space="preserve">22.364330291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7416687011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.95334815979</t>
   </si>
   <si>
     <t xml:space="preserve">22.8797206878662</t>
@@ -1037,40 +1037,40 @@
     <t xml:space="preserve">23.4319248199463</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8060932159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0269756317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6036186218262</t>
+    <t xml:space="preserve">22.806095123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0269775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6036167144775</t>
   </si>
   <si>
     <t xml:space="preserve">22.2538871765137</t>
   </si>
   <si>
-    <t xml:space="preserve">21.545223236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4900035858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7200870513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5544281005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6740703582764</t>
+    <t xml:space="preserve">21.5452251434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4900016784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7200889587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5544261932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.674072265625</t>
   </si>
   <si>
     <t xml:space="preserve">21.6280555725098</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1678829193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2046966552734</t>
+    <t xml:space="preserve">21.1678848266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2046985626221</t>
   </si>
   <si>
     <t xml:space="preserve">21.1218662261963</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">21.4163761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5084095001221</t>
+    <t xml:space="preserve">21.5084114074707</t>
   </si>
   <si>
     <t xml:space="preserve">21.9133605957031</t>
@@ -1088,13 +1088,13 @@
     <t xml:space="preserve">21.8857517242432</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9685840606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6220226287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3735332489014</t>
+    <t xml:space="preserve">21.9685821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6220245361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3735313415527</t>
   </si>
   <si>
     <t xml:space="preserve">22.2170715332031</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">21.4255790710449</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6556644439697</t>
+    <t xml:space="preserve">21.6556663513184</t>
   </si>
   <si>
     <t xml:space="preserve">22.263090133667</t>
@@ -1133,37 +1133,37 @@
     <t xml:space="preserve">22.0514125823975</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7876853942871</t>
+    <t xml:space="preserve">22.7876873016357</t>
   </si>
   <si>
     <t xml:space="preserve">22.3367195129395</t>
   </si>
   <si>
-    <t xml:space="preserve">22.115837097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7661056518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0606155395508</t>
+    <t xml:space="preserve">22.1158390045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7661037445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0606136322021</t>
   </si>
   <si>
     <t xml:space="preserve">21.7569007873535</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9961910247803</t>
+    <t xml:space="preserve">21.9961891174316</t>
   </si>
   <si>
     <t xml:space="preserve">21.701681137085</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0053958892822</t>
+    <t xml:space="preserve">22.0053939819336</t>
   </si>
   <si>
     <t xml:space="preserve">21.8765468597412</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1250419616699</t>
+    <t xml:space="preserve">22.1250400543213</t>
   </si>
   <si>
     <t xml:space="preserve">21.7753086090088</t>
@@ -1178,16 +1178,16 @@
     <t xml:space="preserve">21.6832733154297</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8273544311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0574417114258</t>
+    <t xml:space="preserve">20.827356338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0574398040771</t>
   </si>
   <si>
     <t xml:space="preserve">20.94700050354</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7997455596924</t>
+    <t xml:space="preserve">20.7997436523438</t>
   </si>
   <si>
     <t xml:space="preserve">21.1034603118896</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">21.3243427276611</t>
   </si>
   <si>
-    <t xml:space="preserve">21.950174331665</t>
+    <t xml:space="preserve">21.9501762390137</t>
   </si>
   <si>
     <t xml:space="preserve">22.0974292755127</t>
@@ -1217,13 +1217,13 @@
     <t xml:space="preserve">20.9746112823486</t>
   </si>
   <si>
-    <t xml:space="preserve">20.983814239502</t>
+    <t xml:space="preserve">20.9838161468506</t>
   </si>
   <si>
     <t xml:space="preserve">21.1402721405029</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0666446685791</t>
+    <t xml:space="preserve">21.0666465759277</t>
   </si>
   <si>
     <t xml:space="preserve">20.7077121734619</t>
@@ -1235,7 +1235,7 @@
     <t xml:space="preserve">21.1586799621582</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0206279754639</t>
+    <t xml:space="preserve">21.0206260681152</t>
   </si>
   <si>
     <t xml:space="preserve">21.0022201538086</t>
@@ -1244,10 +1244,10 @@
     <t xml:space="preserve">20.6340847015381</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4500141143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3855895996094</t>
+    <t xml:space="preserve">20.4500160217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.385591506958</t>
   </si>
   <si>
     <t xml:space="preserve">20.3947944641113</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">19.9714374542236</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0634708404541</t>
+    <t xml:space="preserve">20.0634727478027</t>
   </si>
   <si>
     <t xml:space="preserve">20.4868278503418</t>
@@ -1268,19 +1268,19 @@
     <t xml:space="preserve">20.7445259094238</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8917808532715</t>
+    <t xml:space="preserve">20.8917789459229</t>
   </si>
   <si>
     <t xml:space="preserve">21.2415084838867</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9285945892334</t>
+    <t xml:space="preserve">20.9285926818848</t>
   </si>
   <si>
     <t xml:space="preserve">20.2475414276123</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1647090911865</t>
+    <t xml:space="preserve">20.1647109985352</t>
   </si>
   <si>
     <t xml:space="preserve">20.0910816192627</t>
@@ -1292,19 +1292,19 @@
     <t xml:space="preserve">19.6953353881836</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8057765960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7321510314941</t>
+    <t xml:space="preserve">19.8057746887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7321491241455</t>
   </si>
   <si>
     <t xml:space="preserve">20.1831169128418</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0450649261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2935562133789</t>
+    <t xml:space="preserve">20.0450630187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2935581207275</t>
   </si>
   <si>
     <t xml:space="preserve">20.4316082000732</t>
@@ -1316,31 +1316,31 @@
     <t xml:space="preserve">20.6616954803467</t>
   </si>
   <si>
-    <t xml:space="preserve">21.131067276001</t>
+    <t xml:space="preserve">21.1310691833496</t>
   </si>
   <si>
     <t xml:space="preserve">21.0482387542725</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1954936981201</t>
+    <t xml:space="preserve">21.1954956054688</t>
   </si>
   <si>
     <t xml:space="preserve">21.4531898498535</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8089504241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6708965301514</t>
+    <t xml:space="preserve">20.8089485168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6708984375</t>
   </si>
   <si>
     <t xml:space="preserve">20.7721347808838</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4652500152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7965717315674</t>
+    <t xml:space="preserve">19.4652481079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7965698242188</t>
   </si>
   <si>
     <t xml:space="preserve">19.8609962463379</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">20.2199287414551</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2291316986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5236415863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.652494430542</t>
+    <t xml:space="preserve">20.2291355133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5236434936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6524925231934</t>
   </si>
   <si>
     <t xml:space="preserve">20.9101867675781</t>
@@ -1370,13 +1370,13 @@
     <t xml:space="preserve">20.4684219360352</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1555042266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1739139556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2599182128906</t>
+    <t xml:space="preserve">20.1555061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1739120483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.259916305542</t>
   </si>
   <si>
     <t xml:space="preserve">21.3703575134277</t>
@@ -1385,13 +1385,13 @@
     <t xml:space="preserve">21.5176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8549690246582</t>
+    <t xml:space="preserve">20.8549671173096</t>
   </si>
   <si>
     <t xml:space="preserve">20.9193916320801</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5052375793457</t>
+    <t xml:space="preserve">20.5052356719971</t>
   </si>
   <si>
     <t xml:space="preserve">20.3487796783447</t>
@@ -1403,13 +1403,13 @@
     <t xml:space="preserve">19.7229461669922</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9162158966064</t>
+    <t xml:space="preserve">19.9162178039551</t>
   </si>
   <si>
     <t xml:space="preserve">20.5604553222656</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7169151306152</t>
+    <t xml:space="preserve">20.7169132232666</t>
   </si>
   <si>
     <t xml:space="preserve">20.9377975463867</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">20.8365592956543</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6004447937012</t>
+    <t xml:space="preserve">21.6004428863525</t>
   </si>
   <si>
     <t xml:space="preserve">20.6248817443848</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">19.6493186950684</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9990463256836</t>
+    <t xml:space="preserve">19.9990482330322</t>
   </si>
   <si>
     <t xml:space="preserve">20.1278972625732</t>
@@ -1445,7 +1445,7 @@
     <t xml:space="preserve">20.8733749389648</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3763866424561</t>
+    <t xml:space="preserve">20.3763885498047</t>
   </si>
   <si>
     <t xml:space="preserve">20.5328464508057</t>
@@ -1454,22 +1454,22 @@
     <t xml:space="preserve">20.3027591705322</t>
   </si>
   <si>
-    <t xml:space="preserve">20.64328956604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6156787872314</t>
+    <t xml:space="preserve">20.6432876586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6156768798828</t>
   </si>
   <si>
     <t xml:space="preserve">20.7261180877686</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2783241271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3151378631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5360164642334</t>
+    <t xml:space="preserve">21.2783260345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3151397705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.536018371582</t>
   </si>
   <si>
     <t xml:space="preserve">21.7937183380127</t>
@@ -1490,13 +1490,13 @@
     <t xml:space="preserve">22.5668048858643</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6128196716309</t>
+    <t xml:space="preserve">22.6128215789795</t>
   </si>
   <si>
     <t xml:space="preserve">22.9165325164795</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6864471435547</t>
+    <t xml:space="preserve">22.6864452362061</t>
   </si>
   <si>
     <t xml:space="preserve">22.7324638366699</t>
@@ -1511,13 +1511,13 @@
     <t xml:space="preserve">22.9073295593262</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2754707336426</t>
+    <t xml:space="preserve">23.2754688262939</t>
   </si>
   <si>
     <t xml:space="preserve">22.991304397583</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3090667724609</t>
+    <t xml:space="preserve">23.3090686798096</t>
   </si>
   <si>
     <t xml:space="preserve">23.4118766784668</t>
@@ -1553,34 +1553,34 @@
     <t xml:space="preserve">23.4586067199707</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6548461914062</t>
+    <t xml:space="preserve">22.6548442840576</t>
   </si>
   <si>
     <t xml:space="preserve">22.7389583587646</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1595325469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.505334854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3838367462158</t>
+    <t xml:space="preserve">23.1595344543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5053367614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3838386535645</t>
   </si>
   <si>
     <t xml:space="preserve">23.3931846618652</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2623386383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9258804321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9912452697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3370227813721</t>
+    <t xml:space="preserve">23.262336730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9258823394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.991247177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3370208740234</t>
   </si>
   <si>
     <t xml:space="preserve">19.9912166595459</t>
@@ -1604,10 +1604,10 @@
     <t xml:space="preserve">19.3463401794434</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0285739898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6266937255859</t>
+    <t xml:space="preserve">19.0285758972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6266956329346</t>
   </si>
   <si>
     <t xml:space="preserve">18.383695602417</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">18.6033306121826</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6360416412354</t>
+    <t xml:space="preserve">18.6360397338867</t>
   </si>
   <si>
     <t xml:space="preserve">18.7949237823486</t>
@@ -1634,19 +1634,19 @@
     <t xml:space="preserve">18.7762317657471</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7201538085938</t>
+    <t xml:space="preserve">18.7201557159424</t>
   </si>
   <si>
     <t xml:space="preserve">18.5752906799316</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3930416107178</t>
+    <t xml:space="preserve">18.3930435180664</t>
   </si>
   <si>
     <t xml:space="preserve">18.5285606384277</t>
   </si>
   <si>
-    <t xml:space="preserve">18.495849609375</t>
+    <t xml:space="preserve">18.4958515167236</t>
   </si>
   <si>
     <t xml:space="preserve">18.4351005554199</t>
@@ -1655,25 +1655,25 @@
     <t xml:space="preserve">18.3883686065674</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4911766052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2435054779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8042411804199</t>
+    <t xml:space="preserve">18.491174697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2435073852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8042392730713</t>
   </si>
   <si>
     <t xml:space="preserve">17.7715282440186</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1079883575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6734256744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7575378417969</t>
+    <t xml:space="preserve">18.1079864501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6734237670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7575359344482</t>
   </si>
   <si>
     <t xml:space="preserve">18.7295017242432</t>
@@ -1682,16 +1682,16 @@
     <t xml:space="preserve">18.276216506958</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2528533935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2107925415039</t>
+    <t xml:space="preserve">18.2528514862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2107944488525</t>
   </si>
   <si>
     <t xml:space="preserve">18.3790245056152</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1407260894775</t>
+    <t xml:space="preserve">19.1407241821289</t>
   </si>
   <si>
     <t xml:space="preserve">19.4398002624512</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">19.4117641448975</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4304580688477</t>
+    <t xml:space="preserve">19.430456161499</t>
   </si>
   <si>
     <t xml:space="preserve">19.3650302886963</t>
@@ -1718,13 +1718,13 @@
     <t xml:space="preserve">19.1126880645752</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0939960479736</t>
+    <t xml:space="preserve">19.0939979553223</t>
   </si>
   <si>
     <t xml:space="preserve">18.7388458251953</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0566120147705</t>
+    <t xml:space="preserve">19.0566101074219</t>
   </si>
   <si>
     <t xml:space="preserve">18.8416519165039</t>
@@ -1736,13 +1736,13 @@
     <t xml:space="preserve">19.2528800964355</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5239143371582</t>
+    <t xml:space="preserve">19.5239124298096</t>
   </si>
   <si>
     <t xml:space="preserve">19.4211101531982</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8136444091797</t>
+    <t xml:space="preserve">19.8136425018311</t>
   </si>
   <si>
     <t xml:space="preserve">20.0753326416016</t>
@@ -1775,16 +1775,16 @@
     <t xml:space="preserve">18.8042697906494</t>
   </si>
   <si>
-    <t xml:space="preserve">18.879035949707</t>
+    <t xml:space="preserve">18.8790378570557</t>
   </si>
   <si>
     <t xml:space="preserve">18.1780853271484</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6453838348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8556442260742</t>
+    <t xml:space="preserve">18.6453857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8556423187256</t>
   </si>
   <si>
     <t xml:space="preserve">17.2528228759766</t>
@@ -1805,13 +1805,13 @@
     <t xml:space="preserve">18.1173343658447</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2154693603516</t>
+    <t xml:space="preserve">18.2154674530029</t>
   </si>
   <si>
     <t xml:space="preserve">19.1874580383301</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0098819732666</t>
+    <t xml:space="preserve">19.0098838806152</t>
   </si>
   <si>
     <t xml:space="preserve">19.5986824035645</t>
@@ -1820,10 +1820,10 @@
     <t xml:space="preserve">19.589334487915</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6454124450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4771842956543</t>
+    <t xml:space="preserve">19.645414352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4771862030029</t>
   </si>
   <si>
     <t xml:space="preserve">19.5426082611084</t>
@@ -1835,7 +1835,7 @@
     <t xml:space="preserve">20.0005645751953</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6267204284668</t>
+    <t xml:space="preserve">19.6267223358154</t>
   </si>
   <si>
     <t xml:space="preserve">19.4865322113037</t>
@@ -1844,7 +1844,7 @@
     <t xml:space="preserve">19.7014904022217</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3930702209473</t>
+    <t xml:space="preserve">19.3930721282959</t>
   </si>
   <si>
     <t xml:space="preserve">18.7481937408447</t>
@@ -1853,16 +1853,16 @@
     <t xml:space="preserve">18.7855777740479</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0659561157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5145683288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2061500549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0472087860107</t>
+    <t xml:space="preserve">19.0659580230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5145702362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.206148147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0472106933594</t>
   </si>
   <si>
     <t xml:space="preserve">16.7107524871826</t>
@@ -1889,10 +1889,10 @@
     <t xml:space="preserve">16.7528076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5004653930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4630794525146</t>
+    <t xml:space="preserve">16.500467300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4630813598633</t>
   </si>
   <si>
     <t xml:space="preserve">16.0425090789795</t>
@@ -1904,7 +1904,7 @@
     <t xml:space="preserve">16.5425224304199</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8415966033936</t>
+    <t xml:space="preserve">16.8415946960449</t>
   </si>
   <si>
     <t xml:space="preserve">16.6640205383301</t>
@@ -1913,7 +1913,7 @@
     <t xml:space="preserve">16.5331783294678</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5892543792725</t>
+    <t xml:space="preserve">16.5892524719238</t>
   </si>
   <si>
     <t xml:space="preserve">16.6827125549316</t>
@@ -1925,19 +1925,19 @@
     <t xml:space="preserve">16.4256973266602</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1266231536865</t>
+    <t xml:space="preserve">16.1266212463379</t>
   </si>
   <si>
     <t xml:space="preserve">16.1593341827393</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4490623474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1920471191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2154102325439</t>
+    <t xml:space="preserve">16.4490642547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.192045211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2154121398926</t>
   </si>
   <si>
     <t xml:space="preserve">16.4817733764648</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">17.1313228607178</t>
   </si>
   <si>
-    <t xml:space="preserve">17.229455947876</t>
+    <t xml:space="preserve">17.2294578552246</t>
   </si>
   <si>
     <t xml:space="preserve">17.4911479949951</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">17.4537620544434</t>
   </si>
   <si>
-    <t xml:space="preserve">17.729471206665</t>
+    <t xml:space="preserve">17.7294731140137</t>
   </si>
   <si>
     <t xml:space="preserve">17.6547012329102</t>
@@ -2006,7 +2006,7 @@
     <t xml:space="preserve">17.1453437805176</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8462696075439</t>
+    <t xml:space="preserve">16.8462715148926</t>
   </si>
   <si>
     <t xml:space="preserve">17.1687088012695</t>
@@ -2015,7 +2015,7 @@
     <t xml:space="preserve">16.822904586792</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9911632537842</t>
+    <t xml:space="preserve">17.9911613464355</t>
   </si>
   <si>
     <t xml:space="preserve">17.9117202758789</t>
@@ -2024,10 +2024,10 @@
     <t xml:space="preserve">18.0378913879395</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6593780517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7948951721191</t>
+    <t xml:space="preserve">17.6593761444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7948970794678</t>
   </si>
   <si>
     <t xml:space="preserve">17.6360130310059</t>
@@ -2045,16 +2045,16 @@
     <t xml:space="preserve">17.5004940032959</t>
   </si>
   <si>
-    <t xml:space="preserve">17.869665145874</t>
+    <t xml:space="preserve">17.8696632385254</t>
   </si>
   <si>
     <t xml:space="preserve">18.3136024475098</t>
   </si>
   <si>
-    <t xml:space="preserve">18.056583404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2855606079102</t>
+    <t xml:space="preserve">18.0565814971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2855625152588</t>
   </si>
   <si>
     <t xml:space="preserve">18.0192012786865</t>
@@ -2063,25 +2063,25 @@
     <t xml:space="preserve">17.9677982330322</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9070472717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.69211769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5051956176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3416404724121</t>
+    <t xml:space="preserve">17.9070453643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6921157836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5051937103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3416385650635</t>
   </si>
   <si>
     <t xml:space="preserve">18.5565967559814</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4397735595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5472526550293</t>
+    <t xml:space="preserve">18.4397716522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5472545623779</t>
   </si>
   <si>
     <t xml:space="preserve">18.3089275360107</t>
@@ -2099,10 +2099,10 @@
     <t xml:space="preserve">18.0238723754883</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8603172302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.06125831604</t>
+    <t xml:space="preserve">17.8603191375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0612602233887</t>
   </si>
   <si>
     <t xml:space="preserve">17.5986270904541</t>
@@ -2111,13 +2111,13 @@
     <t xml:space="preserve">18.0939693450928</t>
   </si>
   <si>
-    <t xml:space="preserve">19.860372543335</t>
+    <t xml:space="preserve">19.8603744506836</t>
   </si>
   <si>
     <t xml:space="preserve">20.0472946166992</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9071044921875</t>
+    <t xml:space="preserve">19.9071025848389</t>
   </si>
   <si>
     <t xml:space="preserve">19.4607124328613</t>
@@ -5994,6 +5994,9 @@
   </si>
   <si>
     <t xml:space="preserve">7.66499996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49499988555908</t>
   </si>
 </sst>
 </file>
@@ -71618,7 +71621,7 @@
     </row>
     <row r="2512">
       <c r="A2512" s="1" t="n">
-        <v>45975.69125</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B2512" t="n">
         <v>470239</v>
@@ -71639,6 +71642,32 @@
         <v>1993</v>
       </c>
       <c r="H2512" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" s="1" t="n">
+        <v>45978.6912037037</v>
+      </c>
+      <c r="B2513" t="n">
+        <v>328725</v>
+      </c>
+      <c r="C2513" t="n">
+        <v>7.65000009536743</v>
+      </c>
+      <c r="D2513" t="n">
+        <v>7.45499992370605</v>
+      </c>
+      <c r="E2513" t="n">
+        <v>7.63000011444092</v>
+      </c>
+      <c r="F2513" t="n">
+        <v>7.49499988555908</v>
+      </c>
+      <c r="G2513" t="s">
+        <v>1994</v>
+      </c>
+      <c r="H2513" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1996" uniqueCount="1996">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1997" uniqueCount="1997">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2763500213623</t>
+    <t xml:space="preserve">18.2763519287109</t>
   </si>
   <si>
     <t xml:space="preserve">SFER.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">18.01096534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4978828430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9401931762695</t>
+    <t xml:space="preserve">18.0109634399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4978809356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9401950836182</t>
   </si>
   <si>
     <t xml:space="preserve">17.6836547851562</t>
@@ -59,10 +59,10 @@
     <t xml:space="preserve">18.249813079834</t>
   </si>
   <si>
-    <t xml:space="preserve">19.408670425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1344337463379</t>
+    <t xml:space="preserve">19.4086723327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1344375610352</t>
   </si>
   <si>
     <t xml:space="preserve">18.8425121307373</t>
@@ -74,103 +74,103 @@
     <t xml:space="preserve">18.2851982116699</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0994243621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6394233703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5686511993408</t>
+    <t xml:space="preserve">18.0994281768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6394214630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5686550140381</t>
   </si>
   <si>
     <t xml:space="preserve">18.1878871917725</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4798145294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2232761383057</t>
+    <t xml:space="preserve">18.4798126220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.223274230957</t>
   </si>
   <si>
     <t xml:space="preserve">17.7632713317871</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3913516998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6744327545166</t>
+    <t xml:space="preserve">18.3913536071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.674430847168</t>
   </si>
   <si>
     <t xml:space="preserve">17.9578857421875</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2055835723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.258659362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0817375183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3563442230225</t>
+    <t xml:space="preserve">18.2055816650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2586574554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0817337036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3563404083252</t>
   </si>
   <si>
     <t xml:space="preserve">16.9051837921143</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1617240905762</t>
+    <t xml:space="preserve">17.1617202758789</t>
   </si>
   <si>
     <t xml:space="preserve">16.6486415863037</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0201835632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.48903465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6305751800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4090461730957</t>
+    <t xml:space="preserve">17.0201854705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4890365600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6305732727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4090442657471</t>
   </si>
   <si>
     <t xml:space="preserve">18.453275680542</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9752044677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1348094940186</t>
+    <t xml:space="preserve">18.9752063751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1348133087158</t>
   </si>
   <si>
     <t xml:space="preserve">17.3121089935303</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9048118591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3471202850342</t>
+    <t xml:space="preserve">17.9048080444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3471221923828</t>
   </si>
   <si>
     <t xml:space="preserve">19.019437789917</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0017433166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8513565063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3113651275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.992525100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9482898712158</t>
+    <t xml:space="preserve">19.0017414093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8513584136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3113632202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9925231933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9482917785645</t>
   </si>
   <si>
     <t xml:space="preserve">19.7271347045898</t>
@@ -185,16 +185,16 @@
     <t xml:space="preserve">19.9836769104004</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1167430877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4440574645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0367546081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1782932281494</t>
+    <t xml:space="preserve">19.1167469024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.444055557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0367527008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1782970428467</t>
   </si>
   <si>
     <t xml:space="preserve">19.4971332550049</t>
@@ -206,73 +206,73 @@
     <t xml:space="preserve">18.9663600921631</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4794445037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9129085540771</t>
+    <t xml:space="preserve">19.4794425964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9129066467285</t>
   </si>
   <si>
     <t xml:space="preserve">19.8686752319336</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4175205230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8690490722656</t>
+    <t xml:space="preserve">19.4175186157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8690509796143</t>
   </si>
   <si>
     <t xml:space="preserve">18.8336658477783</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5152015686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9309711456299</t>
+    <t xml:space="preserve">18.5151996612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9309749603271</t>
   </si>
   <si>
     <t xml:space="preserve">18.8955879211426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5240478515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9486675262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7982807159424</t>
+    <t xml:space="preserve">18.5240459442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9486656188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7982788085938</t>
   </si>
   <si>
     <t xml:space="preserve">18.8778991699219</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2936706542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8071250915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3205795288086</t>
+    <t xml:space="preserve">19.2936687469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8071269989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3205833435059</t>
   </si>
   <si>
     <t xml:space="preserve">18.3648147583008</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8251934051514</t>
+    <t xml:space="preserve">17.8251914978027</t>
   </si>
   <si>
     <t xml:space="preserve">18.0640411376953</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3117370605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.878267288208</t>
+    <t xml:space="preserve">18.3117389678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8782691955566</t>
   </si>
   <si>
     <t xml:space="preserve">18.0021171569824</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7190380096436</t>
+    <t xml:space="preserve">17.7190399169922</t>
   </si>
   <si>
     <t xml:space="preserve">17.444803237915</t>
@@ -284,40 +284,40 @@
     <t xml:space="preserve">17.5509586334229</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9844245910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4182662963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9313507080078</t>
+    <t xml:space="preserve">17.9844264984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4182643890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9313468933105</t>
   </si>
   <si>
     <t xml:space="preserve">17.7367286682129</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6482696533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.593936920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.81125831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7025947570801</t>
+    <t xml:space="preserve">17.648265838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5939388275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8112602233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7025985717773</t>
   </si>
   <si>
     <t xml:space="preserve">17.6482677459717</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5305519104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4128379821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3041763305664</t>
+    <t xml:space="preserve">17.530553817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4128398895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.304178237915</t>
   </si>
   <si>
     <t xml:space="preserve">17.4762210845947</t>
@@ -329,31 +329,31 @@
     <t xml:space="preserve">17.4852752685547</t>
   </si>
   <si>
-    <t xml:space="preserve">17.747875213623</t>
+    <t xml:space="preserve">17.7478713989258</t>
   </si>
   <si>
     <t xml:space="preserve">17.6844882965088</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1502418518066</t>
+    <t xml:space="preserve">17.150239944458</t>
   </si>
   <si>
     <t xml:space="preserve">16.71559715271</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5435562133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0415821075439</t>
+    <t xml:space="preserve">16.5435523986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0415802001953</t>
   </si>
   <si>
     <t xml:space="preserve">17.0778007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8384265899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9380283355713</t>
+    <t xml:space="preserve">17.8384246826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9380264282227</t>
   </si>
   <si>
     <t xml:space="preserve">17.7297630310059</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">17.8655872344971</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1825141906738</t>
+    <t xml:space="preserve">18.1825180053711</t>
   </si>
   <si>
     <t xml:space="preserve">16.8514251708984</t>
@@ -374,34 +374,34 @@
     <t xml:space="preserve">16.6793785095215</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2628479003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5254421234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6069374084473</t>
+    <t xml:space="preserve">16.262845993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5254440307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6069393157959</t>
   </si>
   <si>
     <t xml:space="preserve">16.8061485290527</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8242607116699</t>
+    <t xml:space="preserve">16.8242588043213</t>
   </si>
   <si>
     <t xml:space="preserve">16.0726909637451</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8734798431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3624534606934</t>
+    <t xml:space="preserve">15.8734788894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3624515533447</t>
   </si>
   <si>
     <t xml:space="preserve">16.4439468383789</t>
   </si>
   <si>
-    <t xml:space="preserve">16.69748878479</t>
+    <t xml:space="preserve">16.6974906921387</t>
   </si>
   <si>
     <t xml:space="preserve">17.0959091186523</t>
@@ -410,19 +410,19 @@
     <t xml:space="preserve">17.1321315765381</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0868549346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0325222015381</t>
+    <t xml:space="preserve">17.086856842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0325260162354</t>
   </si>
   <si>
     <t xml:space="preserve">17.3403968811035</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9018077850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.137243270874</t>
+    <t xml:space="preserve">17.9018096923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1372413635254</t>
   </si>
   <si>
     <t xml:space="preserve">17.9289722442627</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">18.7710914611816</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6352691650391</t>
+    <t xml:space="preserve">18.6352653503418</t>
   </si>
   <si>
     <t xml:space="preserve">19.0699081420898</t>
@@ -443,40 +443,40 @@
     <t xml:space="preserve">18.6262092590332</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4994411468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2187366485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7167625427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5809364318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7620372772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8073139190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9431381225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0427436828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6624298095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4722728729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6171588897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7529792785645</t>
+    <t xml:space="preserve">18.4994430541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2187347412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.716760635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5809383392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.762035369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8073120117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.94313621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.04274559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6624317169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4722766876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6171550750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7529811859131</t>
   </si>
   <si>
     <t xml:space="preserve">18.9703044891357</t>
@@ -488,28 +488,28 @@
     <t xml:space="preserve">18.6081008911133</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6533794403076</t>
+    <t xml:space="preserve">18.653377532959</t>
   </si>
   <si>
     <t xml:space="preserve">18.5175514221191</t>
   </si>
   <si>
-    <t xml:space="preserve">18.870698928833</t>
+    <t xml:space="preserve">18.8707008361816</t>
   </si>
   <si>
     <t xml:space="preserve">18.6986522674561</t>
   </si>
   <si>
-    <t xml:space="preserve">19.106128692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9210834503174</t>
+    <t xml:space="preserve">19.1061267852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9210815429688</t>
   </si>
   <si>
     <t xml:space="preserve">19.6947059631348</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5588798522949</t>
+    <t xml:space="preserve">19.5588779449463</t>
   </si>
   <si>
     <t xml:space="preserve">19.4592742919922</t>
@@ -518,64 +518,64 @@
     <t xml:space="preserve">19.314395904541</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8888092041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1332950592041</t>
+    <t xml:space="preserve">18.8888072967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1332931518555</t>
   </si>
   <si>
     <t xml:space="preserve">19.160457611084</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9391918182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4553260803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3557243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3104515075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3919448852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4643859863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6907615661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8446941375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7994213104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4010009765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1021823883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5277709960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3647785186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5458793640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7541446685791</t>
+    <t xml:space="preserve">19.9391937255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4553279876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3557224273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3104496002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3919429779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4643840789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6907596588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8446960449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7994194030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4009990692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1021862030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5277690887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3647804260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.545877456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7541465759277</t>
   </si>
   <si>
     <t xml:space="preserve">20.4191074371338</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0116348266602</t>
+    <t xml:space="preserve">20.0116329193115</t>
   </si>
   <si>
     <t xml:space="preserve">20.265172958374</t>
@@ -587,19 +587,19 @@
     <t xml:space="preserve">20.0387954711914</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1474571228027</t>
+    <t xml:space="preserve">20.1474590301514</t>
   </si>
   <si>
     <t xml:space="preserve">20.2289543151855</t>
   </si>
   <si>
-    <t xml:space="preserve">20.500602722168</t>
+    <t xml:space="preserve">20.5006046295166</t>
   </si>
   <si>
     <t xml:space="preserve">20.5639877319336</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1836795806885</t>
+    <t xml:space="preserve">20.1836814880371</t>
   </si>
   <si>
     <t xml:space="preserve">19.549825668335</t>
@@ -608,13 +608,13 @@
     <t xml:space="preserve">19.4140014648438</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5045528411865</t>
+    <t xml:space="preserve">19.5045509338379</t>
   </si>
   <si>
     <t xml:space="preserve">19.7218723297119</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7943134307861</t>
+    <t xml:space="preserve">19.7943115234375</t>
   </si>
   <si>
     <t xml:space="preserve">19.5226593017578</t>
@@ -626,34 +626,34 @@
     <t xml:space="preserve">19.9120273590088</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7490367889404</t>
+    <t xml:space="preserve">19.7490348815918</t>
   </si>
   <si>
     <t xml:space="preserve">18.0919647216797</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3002281188965</t>
+    <t xml:space="preserve">18.3002300262451</t>
   </si>
   <si>
     <t xml:space="preserve">18.3273944854736</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2459011077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0104675292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7388191223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8565349578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8203144073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6392135620117</t>
+    <t xml:space="preserve">18.2458992004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0104694366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7388172149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8565311431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6392116546631</t>
   </si>
   <si>
     <t xml:space="preserve">18.3455047607422</t>
@@ -665,22 +665,22 @@
     <t xml:space="preserve">19.151403427124</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2872276306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3958930969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.377779006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1151866912842</t>
+    <t xml:space="preserve">19.2872295379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3958892822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3777828216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1151828765869</t>
   </si>
   <si>
     <t xml:space="preserve">19.5860443115234</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2600631713867</t>
+    <t xml:space="preserve">19.2600650787354</t>
   </si>
   <si>
     <t xml:space="preserve">20.3738346099854</t>
@@ -689,13 +689,13 @@
     <t xml:space="preserve">20.3466663360596</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2380065917969</t>
+    <t xml:space="preserve">20.2380084991455</t>
   </si>
   <si>
     <t xml:space="preserve">20.1293468475342</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1565093994141</t>
+    <t xml:space="preserve">20.15651512146</t>
   </si>
   <si>
     <t xml:space="preserve">20.8084735870361</t>
@@ -710,13 +710,13 @@
     <t xml:space="preserve">21.5328788757324</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0671272277832</t>
+    <t xml:space="preserve">22.0671291351318</t>
   </si>
   <si>
     <t xml:space="preserve">22.0580730438232</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2572822570801</t>
+    <t xml:space="preserve">22.2572803497314</t>
   </si>
   <si>
     <t xml:space="preserve">22.2935009002686</t>
@@ -728,13 +728,13 @@
     <t xml:space="preserve">22.3206653594971</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2753925323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2391719818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.818696975708</t>
+    <t xml:space="preserve">22.2753944396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2391700744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8186931610107</t>
   </si>
   <si>
     <t xml:space="preserve">23.0722332000732</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">22.8911361694336</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1537284851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0993976593018</t>
+    <t xml:space="preserve">23.1537303924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0993995666504</t>
   </si>
   <si>
     <t xml:space="preserve">22.5923175811768</t>
@@ -758,64 +758,64 @@
     <t xml:space="preserve">22.9092426300049</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1757831573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1395664215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.606481552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7513599395752</t>
+    <t xml:space="preserve">22.1757869720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1395645141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6064834594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7513618469238</t>
   </si>
   <si>
     <t xml:space="preserve">24.1226196289062</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6427021026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6879768371582</t>
+    <t xml:space="preserve">23.6427040100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6879787445068</t>
   </si>
   <si>
     <t xml:space="preserve">23.5612087249756</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7423076629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7241992950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6336479187012</t>
+    <t xml:space="preserve">23.7423095703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7242012023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6336498260498</t>
   </si>
   <si>
     <t xml:space="preserve">23.8238048553467</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6970329284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0139598846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.285608291626</t>
+    <t xml:space="preserve">23.6970310211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0139579772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2856101989746</t>
   </si>
   <si>
     <t xml:space="preserve">24.0682888031006</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9777393341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2946662902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4304885864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.61159324646</t>
+    <t xml:space="preserve">23.9777374267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2946643829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4304904937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6115894317627</t>
   </si>
   <si>
     <t xml:space="preserve">24.7655277252197</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">25.1911125183105</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3903274536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4265441894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6167011260986</t>
+    <t xml:space="preserve">25.3903255462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4265460968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6167030334473</t>
   </si>
   <si>
     <t xml:space="preserve">25.6710300445557</t>
@@ -839,16 +839,16 @@
     <t xml:space="preserve">25.6529216766357</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7615814208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5352058410645</t>
+    <t xml:space="preserve">25.7615795135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5352077484131</t>
   </si>
   <si>
     <t xml:space="preserve">24.9556827545166</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9013538360596</t>
+    <t xml:space="preserve">24.9013500213623</t>
   </si>
   <si>
     <t xml:space="preserve">25.0643424987793</t>
@@ -857,46 +857,46 @@
     <t xml:space="preserve">24.8017482757568</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6206474304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9375743865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3722152709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6257553100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2273330688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1730041503906</t>
+    <t xml:space="preserve">24.6206493377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.937572479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3722133636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6257572174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2273349761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.173002243042</t>
   </si>
   <si>
     <t xml:space="preserve">25.163948059082</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3993797302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7253589630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2907199859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1277256011963</t>
+    <t xml:space="preserve">25.399377822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.72536277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2907180786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1277294158936</t>
   </si>
   <si>
     <t xml:space="preserve">25.7434711456299</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5442600250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4808750152588</t>
+    <t xml:space="preserve">25.5442581176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4808731079102</t>
   </si>
   <si>
     <t xml:space="preserve">25.5080394744873</t>
@@ -908,16 +908,16 @@
     <t xml:space="preserve">25.0824527740479</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7836360931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4214363098145</t>
+    <t xml:space="preserve">24.7836380004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4214344024658</t>
   </si>
   <si>
     <t xml:space="preserve">24.2674961090088</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5261497497559</t>
+    <t xml:space="preserve">25.5261535644531</t>
   </si>
   <si>
     <t xml:space="preserve">26.1237831115723</t>
@@ -926,19 +926,19 @@
     <t xml:space="preserve">26.1871681213379</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6308631896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4859828948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3229923248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6761417388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8934593200684</t>
+    <t xml:space="preserve">26.6308650970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4859848022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3229942321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6761379241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.893461227417</t>
   </si>
   <si>
     <t xml:space="preserve">26.2596073150635</t>
@@ -950,25 +950,25 @@
     <t xml:space="preserve">26.9115695953369</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6036968231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5946464538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3088302612305</t>
+    <t xml:space="preserve">26.6036987304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5946483612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3088321685791</t>
   </si>
   <si>
     <t xml:space="preserve">25.3269386291504</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8340225219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8984432220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0641059875488</t>
+    <t xml:space="preserve">25.834020614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8984451293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0641078948975</t>
   </si>
   <si>
     <t xml:space="preserve">24.71120262146</t>
@@ -980,28 +980,28 @@
     <t xml:space="preserve">23.2202472686768</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1282119750977</t>
+    <t xml:space="preserve">23.128210067749</t>
   </si>
   <si>
     <t xml:space="preserve">22.9625511169434</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8705177307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8613147735596</t>
+    <t xml:space="preserve">22.8705196380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8613128662109</t>
   </si>
   <si>
     <t xml:space="preserve">23.2662658691406</t>
   </si>
   <si>
-    <t xml:space="preserve">23.238655090332</t>
+    <t xml:space="preserve">23.2386531829834</t>
   </si>
   <si>
     <t xml:space="preserve">23.0453834533691</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8889236450195</t>
+    <t xml:space="preserve">22.8889217376709</t>
   </si>
   <si>
     <t xml:space="preserve">22.0882263183594</t>
@@ -1013,43 +1013,43 @@
     <t xml:space="preserve">22.2262763977051</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3827342987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3643283843994</t>
+    <t xml:space="preserve">22.3827323913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.364330291748</t>
   </si>
   <si>
     <t xml:space="preserve">22.7416687011719</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9533500671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8797206878662</t>
+    <t xml:space="preserve">22.95334815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8797225952148</t>
   </si>
   <si>
     <t xml:space="preserve">23.2846698760986</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4871463775635</t>
+    <t xml:space="preserve">23.4871482849121</t>
   </si>
   <si>
     <t xml:space="preserve">23.4319248199463</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8060913085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0269756317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6036186218262</t>
+    <t xml:space="preserve">22.806095123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0269737243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6036167144775</t>
   </si>
   <si>
     <t xml:space="preserve">22.2538871765137</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5452213287354</t>
+    <t xml:space="preserve">21.545223236084</t>
   </si>
   <si>
     <t xml:space="preserve">21.4900035858154</t>
@@ -1058,13 +1058,13 @@
     <t xml:space="preserve">21.7200889587402</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5544281005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.674072265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6280536651611</t>
+    <t xml:space="preserve">21.5544261932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6740703582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6280555725098</t>
   </si>
   <si>
     <t xml:space="preserve">21.1678829193115</t>
@@ -1076,34 +1076,34 @@
     <t xml:space="preserve">21.1218662261963</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4163761138916</t>
+    <t xml:space="preserve">21.416374206543</t>
   </si>
   <si>
     <t xml:space="preserve">21.5084095001221</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9133625030518</t>
+    <t xml:space="preserve">21.9133605957031</t>
   </si>
   <si>
     <t xml:space="preserve">21.8857498168945</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9685821533203</t>
+    <t xml:space="preserve">21.9685840606689</t>
   </si>
   <si>
     <t xml:space="preserve">22.6220245361328</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3735332489014</t>
+    <t xml:space="preserve">22.3735313415527</t>
   </si>
   <si>
     <t xml:space="preserve">22.2170734405518</t>
   </si>
   <si>
-    <t xml:space="preserve">22.410343170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5299892425537</t>
+    <t xml:space="preserve">22.4103488922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5299911499023</t>
   </si>
   <si>
     <t xml:space="preserve">22.6312274932861</t>
@@ -1115,37 +1115,37 @@
     <t xml:space="preserve">22.5576000213623</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4255771636963</t>
+    <t xml:space="preserve">21.4255809783936</t>
   </si>
   <si>
     <t xml:space="preserve">21.6556644439697</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2630920410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.539192199707</t>
+    <t xml:space="preserve">22.263090133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5391941070557</t>
   </si>
   <si>
     <t xml:space="preserve">22.3551254272461</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0514125823975</t>
+    <t xml:space="preserve">22.0514106750488</t>
   </si>
   <si>
     <t xml:space="preserve">22.7876853942871</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3367176055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.115837097168</t>
+    <t xml:space="preserve">22.3367195129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1158351898193</t>
   </si>
   <si>
     <t xml:space="preserve">21.7661056518555</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0606136322021</t>
+    <t xml:space="preserve">22.0606155395508</t>
   </si>
   <si>
     <t xml:space="preserve">21.7569026947021</t>
@@ -1157,43 +1157,43 @@
     <t xml:space="preserve">21.701681137085</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0053939819336</t>
+    <t xml:space="preserve">22.0053958892822</t>
   </si>
   <si>
     <t xml:space="preserve">21.8765468597412</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1250400543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7753067016602</t>
+    <t xml:space="preserve">22.1250419616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7753086090088</t>
   </si>
   <si>
     <t xml:space="preserve">22.0238037109375</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9041557312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6832733154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8273544311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0574417114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.94700050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.799747467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.103458404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0758457183838</t>
+    <t xml:space="preserve">21.9041576385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6832752227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.827356338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0574436187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9470024108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7997455596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1034603118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0758476257324</t>
   </si>
   <si>
     <t xml:space="preserve">21.3243427276611</t>
@@ -1202,16 +1202,16 @@
     <t xml:space="preserve">21.950174331665</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0974273681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8581371307373</t>
+    <t xml:space="preserve">22.0974292755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8581409454346</t>
   </si>
   <si>
     <t xml:space="preserve">21.6372566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2967300415039</t>
+    <t xml:space="preserve">21.2967319488525</t>
   </si>
   <si>
     <t xml:space="preserve">20.9746112823486</t>
@@ -1220,25 +1220,25 @@
     <t xml:space="preserve">20.9838161468506</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1402721405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0666446685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7077102661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0942573547363</t>
+    <t xml:space="preserve">21.1402702331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0666427612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7077121734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0942554473877</t>
   </si>
   <si>
     <t xml:space="preserve">21.1586799621582</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0206298828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0022220611572</t>
+    <t xml:space="preserve">21.0206279754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0022201538086</t>
   </si>
   <si>
     <t xml:space="preserve">20.6340847015381</t>
@@ -1256,7 +1256,7 @@
     <t xml:space="preserve">20.0082511901855</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9714374542236</t>
+    <t xml:space="preserve">19.9714393615723</t>
   </si>
   <si>
     <t xml:space="preserve">20.0634708404541</t>
@@ -1268,10 +1268,10 @@
     <t xml:space="preserve">20.7445259094238</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8917827606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.241512298584</t>
+    <t xml:space="preserve">20.8917808532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2415084838867</t>
   </si>
   <si>
     <t xml:space="preserve">20.9285926818848</t>
@@ -1286,28 +1286,28 @@
     <t xml:space="preserve">20.0910816192627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2719783782959</t>
+    <t xml:space="preserve">19.2719764709473</t>
   </si>
   <si>
     <t xml:space="preserve">19.695333480835</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8057746887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7321491241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1831188201904</t>
+    <t xml:space="preserve">19.8057765960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7321510314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1831150054932</t>
   </si>
   <si>
     <t xml:space="preserve">20.0450649261475</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2935581207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4316101074219</t>
+    <t xml:space="preserve">20.2935562133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4316120147705</t>
   </si>
   <si>
     <t xml:space="preserve">20.5696601867676</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">21.0482387542725</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1954917907715</t>
+    <t xml:space="preserve">21.1954936981201</t>
   </si>
   <si>
     <t xml:space="preserve">21.4531898498535</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8089504241943</t>
+    <t xml:space="preserve">20.8089485168457</t>
   </si>
   <si>
     <t xml:space="preserve">20.6708965301514</t>
@@ -1337,10 +1337,10 @@
     <t xml:space="preserve">20.7721366882324</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4652481079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7965717315674</t>
+    <t xml:space="preserve">19.4652500152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.796573638916</t>
   </si>
   <si>
     <t xml:space="preserve">19.8609962463379</t>
@@ -1352,10 +1352,10 @@
     <t xml:space="preserve">20.2199287414551</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2291355133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5236415863037</t>
+    <t xml:space="preserve">20.2291316986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5236434936523</t>
   </si>
   <si>
     <t xml:space="preserve">20.6524925231934</t>
@@ -1364,16 +1364,16 @@
     <t xml:space="preserve">20.9101867675781</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2659473419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4684238433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1555042266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1739120483398</t>
+    <t xml:space="preserve">20.2659492492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4684219360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1555023193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1739139556885</t>
   </si>
   <si>
     <t xml:space="preserve">21.2599182128906</t>
@@ -1382,13 +1382,13 @@
     <t xml:space="preserve">21.3703575134277</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5176124572754</t>
+    <t xml:space="preserve">21.517614364624</t>
   </si>
   <si>
     <t xml:space="preserve">20.8549652099609</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9193897247314</t>
+    <t xml:space="preserve">20.9193916320801</t>
   </si>
   <si>
     <t xml:space="preserve">20.5052356719971</t>
@@ -1397,88 +1397,88 @@
     <t xml:space="preserve">20.3487777709961</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0266571044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7229461669922</t>
+    <t xml:space="preserve">20.0266590118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7229442596436</t>
   </si>
   <si>
     <t xml:space="preserve">19.9162158966064</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5604572296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7169151306152</t>
+    <t xml:space="preserve">20.5604553222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7169170379639</t>
   </si>
   <si>
     <t xml:space="preserve">20.9377975463867</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8365573883057</t>
+    <t xml:space="preserve">20.8365592956543</t>
   </si>
   <si>
     <t xml:space="preserve">21.6004428863525</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6248817443848</t>
+    <t xml:space="preserve">20.6248798370361</t>
   </si>
   <si>
     <t xml:space="preserve">20.2751502990723</t>
   </si>
   <si>
-    <t xml:space="preserve">20.109489440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6493167877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.999044418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1278953552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3303699493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8733730316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3763866424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5328483581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3027610778809</t>
+    <t xml:space="preserve">20.1094875335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6493148803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9990463256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1278972625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3303718566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8733749389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3763885498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5328464508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3027591705322</t>
   </si>
   <si>
     <t xml:space="preserve">20.64328956604</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6156749725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7261161804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2783241271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3151359558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5360202789307</t>
+    <t xml:space="preserve">20.6156768798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7261180877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2783260345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3151378631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5360164642334</t>
   </si>
   <si>
     <t xml:space="preserve">21.7937164306641</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6496334075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5483989715576</t>
+    <t xml:space="preserve">22.6496353149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.548397064209</t>
   </si>
   <si>
     <t xml:space="preserve">22.4195499420166</t>
@@ -1487,10 +1487,10 @@
     <t xml:space="preserve">22.2078685760498</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5668029785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6128196716309</t>
+    <t xml:space="preserve">22.5668048858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6128215789795</t>
   </si>
   <si>
     <t xml:space="preserve">22.9165344238281</t>
@@ -1502,10 +1502,10 @@
     <t xml:space="preserve">22.7324657440186</t>
   </si>
   <si>
-    <t xml:space="preserve">22.833703994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7692775726318</t>
+    <t xml:space="preserve">22.8337020874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7692794799805</t>
   </si>
   <si>
     <t xml:space="preserve">22.9073295593262</t>
@@ -1514,10 +1514,10 @@
     <t xml:space="preserve">23.2754688262939</t>
   </si>
   <si>
-    <t xml:space="preserve">22.991304397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3090705871582</t>
+    <t xml:space="preserve">22.9913024902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3090686798096</t>
   </si>
   <si>
     <t xml:space="preserve">23.4118747711182</t>
@@ -1532,34 +1532,34 @@
     <t xml:space="preserve">22.7296123504639</t>
   </si>
   <si>
-    <t xml:space="preserve">22.355770111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6174621582031</t>
+    <t xml:space="preserve">22.3557720184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6174602508545</t>
   </si>
   <si>
     <t xml:space="preserve">23.0754165649414</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3558006286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1969184875488</t>
+    <t xml:space="preserve">23.3557987213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1969146728516</t>
   </si>
   <si>
     <t xml:space="preserve">23.206262588501</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4586048126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6548461914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7389583587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1595325469971</t>
+    <t xml:space="preserve">23.4586067199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6548442840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7389602661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1595344543457</t>
   </si>
   <si>
     <t xml:space="preserve">23.5053367614746</t>
@@ -1571,10 +1571,10 @@
     <t xml:space="preserve">23.3931846618652</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2623386383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9258823394775</t>
+    <t xml:space="preserve">23.262336730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9258804321289</t>
   </si>
   <si>
     <t xml:space="preserve">20.9912452697754</t>
@@ -1583,16 +1583,16 @@
     <t xml:space="preserve">20.3370227813721</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9912166595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7388744354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5612983703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3089542388916</t>
+    <t xml:space="preserve">19.9912185668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7388763427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.56130027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3089561462402</t>
   </si>
   <si>
     <t xml:space="preserve">19.533260345459</t>
@@ -1604,34 +1604,34 @@
     <t xml:space="preserve">19.346342086792</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0285758972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6266937255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.383695602417</t>
+    <t xml:space="preserve">19.0285739898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6266918182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3836975097656</t>
   </si>
   <si>
     <t xml:space="preserve">18.0752754211426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6220226287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0799503326416</t>
+    <t xml:space="preserve">18.6220188140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.079948425293</t>
   </si>
   <si>
     <t xml:space="preserve">18.603328704834</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6360397338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.794921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7762298583984</t>
+    <t xml:space="preserve">18.6360416412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7949237823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7762317657471</t>
   </si>
   <si>
     <t xml:space="preserve">18.7201538085938</t>
@@ -1655,13 +1655,13 @@
     <t xml:space="preserve">18.3883686065674</t>
   </si>
   <si>
-    <t xml:space="preserve">18.491174697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2435073852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8042392730713</t>
+    <t xml:space="preserve">18.4911766052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2435054779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8042411804199</t>
   </si>
   <si>
     <t xml:space="preserve">17.7715282440186</t>
@@ -1673,13 +1673,13 @@
     <t xml:space="preserve">18.6734237670898</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7575397491455</t>
+    <t xml:space="preserve">18.7575378417969</t>
   </si>
   <si>
     <t xml:space="preserve">18.7295017242432</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2762184143066</t>
+    <t xml:space="preserve">18.276216506958</t>
   </si>
   <si>
     <t xml:space="preserve">18.2528533935547</t>
@@ -1688,13 +1688,13 @@
     <t xml:space="preserve">18.2107944488525</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3790225982666</t>
+    <t xml:space="preserve">18.3790264129639</t>
   </si>
   <si>
     <t xml:space="preserve">19.1407260894775</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4398021697998</t>
+    <t xml:space="preserve">19.4398002624512</t>
   </si>
   <si>
     <t xml:space="preserve">19.402416229248</t>
@@ -1715,7 +1715,7 @@
     <t xml:space="preserve">19.1687660217285</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1126899719238</t>
+    <t xml:space="preserve">19.1126880645752</t>
   </si>
   <si>
     <t xml:space="preserve">19.0939960479736</t>
@@ -1727,49 +1727,49 @@
     <t xml:space="preserve">19.0566120147705</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8416538238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6080303192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2528800964355</t>
+    <t xml:space="preserve">18.8416519165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6080284118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2528820037842</t>
   </si>
   <si>
     <t xml:space="preserve">19.5239162445068</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4211082458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8136425018311</t>
+    <t xml:space="preserve">19.4211101531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8136444091797</t>
   </si>
   <si>
     <t xml:space="preserve">20.0753307342529</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7482204437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0192565917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7669124603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7856063842773</t>
+    <t xml:space="preserve">19.748218536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0192546844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7669143676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7856044769287</t>
   </si>
   <si>
     <t xml:space="preserve">19.5706462860107</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2809181213379</t>
+    <t xml:space="preserve">19.2809162139893</t>
   </si>
   <si>
     <t xml:space="preserve">19.1500720977783</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8977298736572</t>
+    <t xml:space="preserve">18.8977279663086</t>
   </si>
   <si>
     <t xml:space="preserve">18.8042697906494</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">18.1780834197998</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6453876495361</t>
+    <t xml:space="preserve">18.6453857421875</t>
   </si>
   <si>
     <t xml:space="preserve">17.8556442260742</t>
@@ -1790,10 +1790,10 @@
     <t xml:space="preserve">17.2528228759766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1546897888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9817867279053</t>
+    <t xml:space="preserve">17.1546878814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9817886352539</t>
   </si>
   <si>
     <t xml:space="preserve">18.1360263824463</t>
@@ -1802,16 +1802,16 @@
     <t xml:space="preserve">17.949104309082</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1173343658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2154655456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1874599456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0098838806152</t>
+    <t xml:space="preserve">18.1173324584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2154693603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1874580383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0098819732666</t>
   </si>
   <si>
     <t xml:space="preserve">19.5986843109131</t>
@@ -1826,7 +1826,7 @@
     <t xml:space="preserve">19.4771842956543</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5426044464111</t>
+    <t xml:space="preserve">19.5426082611084</t>
   </si>
   <si>
     <t xml:space="preserve">19.5799922943115</t>
@@ -1850,7 +1850,7 @@
     <t xml:space="preserve">18.7481918334961</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7855796813965</t>
+    <t xml:space="preserve">18.7855777740479</t>
   </si>
   <si>
     <t xml:space="preserve">19.0659580230713</t>
@@ -1859,34 +1859,34 @@
     <t xml:space="preserve">19.5145683288574</t>
   </si>
   <si>
-    <t xml:space="preserve">19.206148147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0472106933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.710750579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8135566711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5845794677734</t>
+    <t xml:space="preserve">19.2061462402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0472087860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7107524871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8135585784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5845832824707</t>
   </si>
   <si>
     <t xml:space="preserve">16.5471954345703</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5378494262695</t>
+    <t xml:space="preserve">16.5378513336182</t>
   </si>
   <si>
     <t xml:space="preserve">16.7200965881348</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4957904815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7528076171875</t>
+    <t xml:space="preserve">16.495792388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7528095245361</t>
   </si>
   <si>
     <t xml:space="preserve">16.5004653930664</t>
@@ -1895,7 +1895,7 @@
     <t xml:space="preserve">16.4630813598633</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0425071716309</t>
+    <t xml:space="preserve">16.0425109863281</t>
   </si>
   <si>
     <t xml:space="preserve">16.3509292602539</t>
@@ -1907,31 +1907,31 @@
     <t xml:space="preserve">16.8415966033936</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6640224456787</t>
+    <t xml:space="preserve">16.6640205383301</t>
   </si>
   <si>
     <t xml:space="preserve">16.5331783294678</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5892524719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6827144622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5986003875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4256973266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1266212463379</t>
+    <t xml:space="preserve">16.5892543792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6827125549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5986022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4256992340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1266231536865</t>
   </si>
   <si>
     <t xml:space="preserve">16.1593341827393</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4490642547607</t>
+    <t xml:space="preserve">16.4490623474121</t>
   </si>
   <si>
     <t xml:space="preserve">16.1920471191406</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">16.2154102325439</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4817733764648</t>
+    <t xml:space="preserve">16.4817752838135</t>
   </si>
   <si>
     <t xml:space="preserve">16.5238304138184</t>
@@ -1949,10 +1949,10 @@
     <t xml:space="preserve">16.4023323059082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.299524307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.579906463623</t>
+    <t xml:space="preserve">16.2995262145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5799083709717</t>
   </si>
   <si>
     <t xml:space="preserve">17.1874008178711</t>
@@ -1967,19 +1967,19 @@
     <t xml:space="preserve">17.2201118469238</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5752601623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5518970489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4163780212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1079616546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1313228607178</t>
+    <t xml:space="preserve">17.5752620697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5518989562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4163799285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1079597473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1313247680664</t>
   </si>
   <si>
     <t xml:space="preserve">17.2294578552246</t>
@@ -1988,28 +1988,28 @@
     <t xml:space="preserve">17.4911479949951</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4397449493408</t>
+    <t xml:space="preserve">17.4397430419922</t>
   </si>
   <si>
     <t xml:space="preserve">17.453763961792</t>
   </si>
   <si>
-    <t xml:space="preserve">17.729471206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6547050476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3369369506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1453418731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8462696075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1687107086182</t>
+    <t xml:space="preserve">17.7294731140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6547031402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3369388580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1453437805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8462677001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1687088012695</t>
   </si>
   <si>
     <t xml:space="preserve">16.822904586792</t>
@@ -2018,43 +2018,43 @@
     <t xml:space="preserve">17.9911613464355</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9117202758789</t>
+    <t xml:space="preserve">17.9117221832275</t>
   </si>
   <si>
     <t xml:space="preserve">18.0378932952881</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6593761444092</t>
+    <t xml:space="preserve">17.6593780517578</t>
   </si>
   <si>
     <t xml:space="preserve">17.7948951721191</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6360111236572</t>
+    <t xml:space="preserve">17.6360130310059</t>
   </si>
   <si>
     <t xml:space="preserve">17.3275928497314</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3976879119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6266651153564</t>
+    <t xml:space="preserve">17.3976898193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6266670227051</t>
   </si>
   <si>
     <t xml:space="preserve">17.5004940032959</t>
   </si>
   <si>
-    <t xml:space="preserve">17.869665145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3135986328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0565814971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2855625152588</t>
+    <t xml:space="preserve">17.8696632385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3136005401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.056583404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2855606079102</t>
   </si>
   <si>
     <t xml:space="preserve">18.0192012786865</t>
@@ -2066,7 +2066,7 @@
     <t xml:space="preserve">17.9070472717285</t>
   </si>
   <si>
-    <t xml:space="preserve">18.69211769104</t>
+    <t xml:space="preserve">18.6921157836914</t>
   </si>
   <si>
     <t xml:space="preserve">18.5051937103271</t>
@@ -2078,10 +2078,10 @@
     <t xml:space="preserve">18.5565967559814</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4397716522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5472507476807</t>
+    <t xml:space="preserve">18.4397735595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5472526550293</t>
   </si>
   <si>
     <t xml:space="preserve">18.3089294433594</t>
@@ -2096,25 +2096,25 @@
     <t xml:space="preserve">18.5893096923828</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0238742828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8603191375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0612564086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5986289978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0939693450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8603744506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0472946166992</t>
+    <t xml:space="preserve">18.0238723754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8603172302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.06125831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5986270904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0939712524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.860372543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0472965240479</t>
   </si>
   <si>
     <t xml:space="preserve">19.9071025848389</t>
@@ -2123,7 +2123,7 @@
     <t xml:space="preserve">19.4607124328613</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9735870361328</t>
+    <t xml:space="preserve">19.9735889434814</t>
   </si>
   <si>
     <t xml:space="preserve">19.4132251739502</t>
@@ -2132,16 +2132,16 @@
     <t xml:space="preserve">19.2042751312256</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4892063140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1187973022461</t>
+    <t xml:space="preserve">19.4892082214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1187953948975</t>
   </si>
   <si>
     <t xml:space="preserve">19.2327690124512</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9525871276855</t>
+    <t xml:space="preserve">18.9525890350342</t>
   </si>
   <si>
     <t xml:space="preserve">18.4397163391113</t>
@@ -2162,7 +2162,7 @@
     <t xml:space="preserve">18.6534099578857</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1757850646973</t>
+    <t xml:space="preserve">19.1757831573486</t>
   </si>
   <si>
     <t xml:space="preserve">19.3657360076904</t>
@@ -2171,7 +2171,7 @@
     <t xml:space="preserve">19.2802562713623</t>
   </si>
   <si>
-    <t xml:space="preserve">19.213773727417</t>
+    <t xml:space="preserve">19.2137756347656</t>
   </si>
   <si>
     <t xml:space="preserve">18.9810791015625</t>
@@ -2180,7 +2180,7 @@
     <t xml:space="preserve">18.9050998687744</t>
   </si>
   <si>
-    <t xml:space="preserve">19.033317565918</t>
+    <t xml:space="preserve">19.0333194732666</t>
   </si>
   <si>
     <t xml:space="preserve">19.6601657867432</t>
@@ -2195,7 +2195,7 @@
     <t xml:space="preserve">20.0210742950439</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8026294708252</t>
+    <t xml:space="preserve">19.8026275634766</t>
   </si>
   <si>
     <t xml:space="preserve">19.7171497344971</t>
@@ -2210,13 +2210,13 @@
     <t xml:space="preserve">19.926097869873</t>
   </si>
   <si>
-    <t xml:space="preserve">20.135046005249</t>
+    <t xml:space="preserve">20.1350479125977</t>
   </si>
   <si>
     <t xml:space="preserve">20.1920337677002</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4674663543701</t>
+    <t xml:space="preserve">20.4674644470215</t>
   </si>
   <si>
     <t xml:space="preserve">20.4864616394043</t>
@@ -2225,13 +2225,13 @@
     <t xml:space="preserve">20.2870101928711</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2775135040283</t>
+    <t xml:space="preserve">20.2775115966797</t>
   </si>
   <si>
     <t xml:space="preserve">19.8406200408936</t>
   </si>
   <si>
-    <t xml:space="preserve">19.821626663208</t>
+    <t xml:space="preserve">19.8216247558594</t>
   </si>
   <si>
     <t xml:space="preserve">19.8501167297363</t>
@@ -2246,13 +2246,13 @@
     <t xml:space="preserve">20.030574798584</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8691139221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9640884399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0020809173584</t>
+    <t xml:space="preserve">19.8691120147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.96409034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0020790100098</t>
   </si>
   <si>
     <t xml:space="preserve">19.9450931549072</t>
@@ -2273,10 +2273,10 @@
     <t xml:space="preserve">17.2952442169189</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2762489318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.266752243042</t>
+    <t xml:space="preserve">17.2762508392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2667541503906</t>
   </si>
   <si>
     <t xml:space="preserve">17.3854732513428</t>
@@ -2285,22 +2285,22 @@
     <t xml:space="preserve">17.0198135375977</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8963451385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0150680541992</t>
+    <t xml:space="preserve">16.8963432312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0150661468506</t>
   </si>
   <si>
     <t xml:space="preserve">16.59716796875</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2837448120117</t>
+    <t xml:space="preserve">16.2837429046631</t>
   </si>
   <si>
     <t xml:space="preserve">16.8108654022217</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8536052703857</t>
+    <t xml:space="preserve">16.8536071777344</t>
   </si>
   <si>
     <t xml:space="preserve">17.0530548095703</t>
@@ -2318,7 +2318,7 @@
     <t xml:space="preserve">16.948579788208</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7491302490234</t>
+    <t xml:space="preserve">16.7491321563721</t>
   </si>
   <si>
     <t xml:space="preserve">16.8441066741943</t>
@@ -2330,13 +2330,13 @@
     <t xml:space="preserve">16.668399810791</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6304092407227</t>
+    <t xml:space="preserve">16.6304111480713</t>
   </si>
   <si>
     <t xml:space="preserve">16.9248371124268</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4329624176025</t>
+    <t xml:space="preserve">17.4329605102539</t>
   </si>
   <si>
     <t xml:space="preserve">17.3807239532471</t>
@@ -2357,10 +2357,10 @@
     <t xml:space="preserve">17.2002696990967</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6968936920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7538795471191</t>
+    <t xml:space="preserve">16.696891784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7538776397705</t>
   </si>
   <si>
     <t xml:space="preserve">16.2267570495605</t>
@@ -2384,13 +2384,13 @@
     <t xml:space="preserve">16.0178089141846</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4811916351318</t>
+    <t xml:space="preserve">15.4811906814575</t>
   </si>
   <si>
     <t xml:space="preserve">15.5381784439087</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5619220733643</t>
+    <t xml:space="preserve">15.5619230270386</t>
   </si>
   <si>
     <t xml:space="preserve">15.1725187301636</t>
@@ -2402,7 +2402,7 @@
     <t xml:space="preserve">15.3577222824097</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5904159545898</t>
+    <t xml:space="preserve">15.5904150009155</t>
   </si>
   <si>
     <t xml:space="preserve">15.4716949462891</t>
@@ -2411,22 +2411,22 @@
     <t xml:space="preserve">15.680643081665</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4052095413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3244800567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2722434997559</t>
+    <t xml:space="preserve">15.4052085876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.324481010437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2722425460815</t>
   </si>
   <si>
     <t xml:space="preserve">15.2579975128174</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1772661209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0680437088013</t>
+    <t xml:space="preserve">15.177267074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.068042755127</t>
   </si>
   <si>
     <t xml:space="preserve">15.0348024368286</t>
@@ -2531,16 +2531,16 @@
     <t xml:space="preserve">17.4804515838623</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8033714294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1167964935303</t>
+    <t xml:space="preserve">17.803373336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1167945861816</t>
   </si>
   <si>
     <t xml:space="preserve">17.8556079864502</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8081207275391</t>
+    <t xml:space="preserve">17.8081188201904</t>
   </si>
   <si>
     <t xml:space="preserve">18.0028228759766</t>
@@ -2549,25 +2549,25 @@
     <t xml:space="preserve">17.6704025268555</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6229152679443</t>
+    <t xml:space="preserve">17.622917175293</t>
   </si>
   <si>
     <t xml:space="preserve">17.6799030303955</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9885768890381</t>
+    <t xml:space="preserve">17.9885749816895</t>
   </si>
   <si>
     <t xml:space="preserve">18.4207191467285</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0930480957031</t>
+    <t xml:space="preserve">18.0930500030518</t>
   </si>
   <si>
     <t xml:space="preserve">17.90309715271</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8508586883545</t>
+    <t xml:space="preserve">17.8508605957031</t>
   </si>
   <si>
     <t xml:space="preserve">17.2620029449463</t>
@@ -2576,7 +2576,7 @@
     <t xml:space="preserve">17.228759765625</t>
   </si>
   <si>
-    <t xml:space="preserve">17.095796585083</t>
+    <t xml:space="preserve">17.0957946777344</t>
   </si>
   <si>
     <t xml:space="preserve">16.8868465423584</t>
@@ -2591,16 +2591,16 @@
     <t xml:space="preserve">15.8611001968384</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2694969177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2979907989502</t>
+    <t xml:space="preserve">16.2694988250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2979888916016</t>
   </si>
   <si>
     <t xml:space="preserve">16.1175346374512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8468494415283</t>
+    <t xml:space="preserve">15.846851348877</t>
   </si>
   <si>
     <t xml:space="preserve">16.3217353820801</t>
@@ -2612,7 +2612,7 @@
     <t xml:space="preserve">15.7803688049316</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7186317443848</t>
+    <t xml:space="preserve">15.7186336517334</t>
   </si>
   <si>
     <t xml:space="preserve">15.3434762954712</t>
@@ -2630,25 +2630,25 @@
     <t xml:space="preserve">15.7043867111206</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8848438262939</t>
+    <t xml:space="preserve">15.8848419189453</t>
   </si>
   <si>
     <t xml:space="preserve">15.5429258346558</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1582717895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8096036911011</t>
+    <t xml:space="preserve">15.1582708358765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8096027374268</t>
   </si>
   <si>
     <t xml:space="preserve">13.8665895462036</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1420221328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6054039001465</t>
+    <t xml:space="preserve">14.1420211791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6054029464722</t>
   </si>
   <si>
     <t xml:space="preserve">13.5721607208252</t>
@@ -2666,22 +2666,22 @@
     <t xml:space="preserve">12.3184700012207</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0477876663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2784757614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6563787460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7845973968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08166599273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65437412261963</t>
+    <t xml:space="preserve">12.0477867126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2784767150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.656379699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7845964431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08166694641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65437507629395</t>
   </si>
   <si>
     <t xml:space="preserve">10.0057888031006</t>
@@ -2690,13 +2690,13 @@
     <t xml:space="preserve">9.97254657745361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49766445159912</t>
+    <t xml:space="preserve">9.4976634979248</t>
   </si>
   <si>
     <t xml:space="preserve">10.6183891296387</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8625812530518</t>
+    <t xml:space="preserve">11.8625822067261</t>
   </si>
   <si>
     <t xml:space="preserve">12.1665077209473</t>
@@ -2705,13 +2705,13 @@
     <t xml:space="preserve">13.0877809524536</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3964548110962</t>
+    <t xml:space="preserve">13.3964538574219</t>
   </si>
   <si>
     <t xml:space="preserve">12.9690589904785</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2519865036011</t>
+    <t xml:space="preserve">12.2519855499268</t>
   </si>
   <si>
     <t xml:space="preserve">11.9195680618286</t>
@@ -2726,7 +2726,7 @@
     <t xml:space="preserve">11.1597547531128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1882467269897</t>
+    <t xml:space="preserve">11.1882476806641</t>
   </si>
   <si>
     <t xml:space="preserve">11.5681552886963</t>
@@ -2738,7 +2738,7 @@
     <t xml:space="preserve">11.6251401901245</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9765529632568</t>
+    <t xml:space="preserve">11.9765539169312</t>
   </si>
   <si>
     <t xml:space="preserve">11.4541835784912</t>
@@ -2747,16 +2747,16 @@
     <t xml:space="preserve">11.2927227020264</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5396604537964</t>
+    <t xml:space="preserve">11.5396614074707</t>
   </si>
   <si>
     <t xml:space="preserve">10.8178396224976</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3999423980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4474306106567</t>
+    <t xml:space="preserve">10.399941444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4474296569824</t>
   </si>
   <si>
     <t xml:space="preserve">10.3809471130371</t>
@@ -2768,10 +2768,10 @@
     <t xml:space="preserve">10.9128150939941</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7228622436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3049650192261</t>
+    <t xml:space="preserve">10.722861289978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3049659729004</t>
   </si>
   <si>
     <t xml:space="preserve">10.3524532318115</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">10.3144626617432</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3429574966431</t>
+    <t xml:space="preserve">10.3429565429688</t>
   </si>
   <si>
     <t xml:space="preserve">10.4094390869141</t>
@@ -2795,7 +2795,7 @@
     <t xml:space="preserve">9.9060640335083</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89656639099121</t>
+    <t xml:space="preserve">9.89656543731689</t>
   </si>
   <si>
     <t xml:space="preserve">9.64962577819824</t>
@@ -2807,10 +2807,10 @@
     <t xml:space="preserve">10.4949188232422</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3469638824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9005727767944</t>
+    <t xml:space="preserve">12.346962928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9005718231201</t>
   </si>
   <si>
     <t xml:space="preserve">12.2614841461182</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">13.2872314453125</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1542644500732</t>
+    <t xml:space="preserve">13.1542654037476</t>
   </si>
   <si>
     <t xml:space="preserve">12.8218460083008</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">11.8815774917603</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7771024703979</t>
+    <t xml:space="preserve">11.7771034240723</t>
   </si>
   <si>
     <t xml:space="preserve">12.062032699585</t>
@@ -2855,16 +2855,16 @@
     <t xml:space="preserve">12.7078742980957</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5749073028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5844049453735</t>
+    <t xml:space="preserve">12.5749063491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5844039916992</t>
   </si>
   <si>
     <t xml:space="preserve">11.9955492019653</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8055963516235</t>
+    <t xml:space="preserve">11.8055973052979</t>
   </si>
   <si>
     <t xml:space="preserve">11.5111684799194</t>
@@ -2876,7 +2876,7 @@
     <t xml:space="preserve">11.4446849822998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5206670761108</t>
+    <t xml:space="preserve">11.5206661224365</t>
   </si>
   <si>
     <t xml:space="preserve">11.7581071853638</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">11.4826755523682</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3402109146118</t>
+    <t xml:space="preserve">11.3402099609375</t>
   </si>
   <si>
     <t xml:space="preserve">10.9887962341309</t>
@@ -2903,10 +2903,10 @@
     <t xml:space="preserve">11.2452335357666</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1027679443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1312618255615</t>
+    <t xml:space="preserve">11.1027688980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1312627792358</t>
   </si>
   <si>
     <t xml:space="preserve">11.0267868041992</t>
@@ -2921,7 +2921,7 @@
     <t xml:space="preserve">11.0552816390991</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2167406082153</t>
+    <t xml:space="preserve">11.2167415618896</t>
   </si>
   <si>
     <t xml:space="preserve">10.5708999633789</t>
@@ -2939,28 +2939,28 @@
     <t xml:space="preserve">11.6441354751587</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3307132720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0932712554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9603042602539</t>
+    <t xml:space="preserve">11.330714225769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0932722091675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9603033065796</t>
   </si>
   <si>
     <t xml:space="preserve">10.7608528137207</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7798480987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6753749847412</t>
+    <t xml:space="preserve">10.7798490524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6753740310669</t>
   </si>
   <si>
     <t xml:space="preserve">11.6156425476074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.463680267334</t>
+    <t xml:space="preserve">11.4636793136597</t>
   </si>
   <si>
     <t xml:space="preserve">11.3971967697144</t>
@@ -2969,25 +2969,25 @@
     <t xml:space="preserve">11.5016708374023</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7960996627808</t>
+    <t xml:space="preserve">11.7960987091064</t>
   </si>
   <si>
     <t xml:space="preserve">11.4731779098511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4256887435913</t>
+    <t xml:space="preserve">11.4256896972656</t>
   </si>
   <si>
     <t xml:space="preserve">12.5179214477539</t>
   </si>
   <si>
-    <t xml:space="preserve">12.565408706665</t>
+    <t xml:space="preserve">12.5654096603394</t>
   </si>
   <si>
     <t xml:space="preserve">12.0810289382935</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6821269989014</t>
+    <t xml:space="preserve">11.6821260452271</t>
   </si>
   <si>
     <t xml:space="preserve">11.6061458587646</t>
@@ -2996,13 +2996,13 @@
     <t xml:space="preserve">12.1095209121704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0145454406738</t>
+    <t xml:space="preserve">12.0145444869995</t>
   </si>
   <si>
     <t xml:space="preserve">11.9385633468628</t>
   </si>
   <si>
-    <t xml:space="preserve">11.957558631897</t>
+    <t xml:space="preserve">11.9575576782227</t>
   </si>
   <si>
     <t xml:space="preserve">11.9860515594482</t>
@@ -3014,7 +3014,7 @@
     <t xml:space="preserve">12.2804794311523</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6793813705444</t>
+    <t xml:space="preserve">12.6793823242188</t>
   </si>
   <si>
     <t xml:space="preserve">12.6034002304077</t>
@@ -3023,7 +3023,7 @@
     <t xml:space="preserve">12.5464134216309</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2044973373413</t>
+    <t xml:space="preserve">12.2044982910156</t>
   </si>
   <si>
     <t xml:space="preserve">12.4039497375488</t>
@@ -3032,10 +3032,10 @@
     <t xml:space="preserve">12.8978271484375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1950006484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8910751342773</t>
+    <t xml:space="preserve">12.1949996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8910760879517</t>
   </si>
   <si>
     <t xml:space="preserve">11.67262840271</t>
@@ -3062,7 +3062,7 @@
     <t xml:space="preserve">12.3659582138062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7933540344238</t>
+    <t xml:space="preserve">12.7933530807495</t>
   </si>
   <si>
     <t xml:space="preserve">13.3537158966064</t>
@@ -3071,16 +3071,16 @@
     <t xml:space="preserve">13.7811098098755</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7146263122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9235754013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9330739974976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2369976043701</t>
+    <t xml:space="preserve">13.7146272659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9235744476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9330730438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2369985580444</t>
   </si>
   <si>
     <t xml:space="preserve">14.3414716720581</t>
@@ -3098,25 +3098,25 @@
     <t xml:space="preserve">14.1515197753906</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2464962005615</t>
+    <t xml:space="preserve">14.2464952468872</t>
   </si>
   <si>
     <t xml:space="preserve">14.4269514083862</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4649410247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9113311767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4934358596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3509693145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5979099273682</t>
+    <t xml:space="preserve">14.4649419784546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9113321304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4934349060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3509702682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5979089736938</t>
   </si>
   <si>
     <t xml:space="preserve">14.7498712539673</t>
@@ -3134,7 +3134,7 @@
     <t xml:space="preserve">14.7593698501587</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3794641494751</t>
+    <t xml:space="preserve">14.3794631958008</t>
   </si>
   <si>
     <t xml:space="preserve">14.5694160461426</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">15.1107835769653</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0632944107056</t>
+    <t xml:space="preserve">15.0632953643799</t>
   </si>
   <si>
     <t xml:space="preserve">14.9493227005005</t>
@@ -3164,7 +3164,7 @@
     <t xml:space="preserve">14.5884113311768</t>
   </si>
   <si>
-    <t xml:space="preserve">14.578914642334</t>
+    <t xml:space="preserve">14.5789136886597</t>
   </si>
   <si>
     <t xml:space="preserve">14.4079561233521</t>
@@ -3182,7 +3182,7 @@
     <t xml:space="preserve">14.2085056304932</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4459457397461</t>
+    <t xml:space="preserve">14.4459466934204</t>
   </si>
   <si>
     <t xml:space="preserve">15.29123878479</t>
@@ -3191,13 +3191,13 @@
     <t xml:space="preserve">14.6833877563477</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0537977218628</t>
+    <t xml:space="preserve">15.0537967681885</t>
   </si>
   <si>
     <t xml:space="preserve">15.8041124343872</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6711444854736</t>
+    <t xml:space="preserve">15.6711454391479</t>
   </si>
   <si>
     <t xml:space="preserve">15.2627458572388</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">14.9588203430176</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0443000793457</t>
+    <t xml:space="preserve">15.0442991256714</t>
   </si>
   <si>
     <t xml:space="preserve">14.721378326416</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">14.4364490509033</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7403745651245</t>
+    <t xml:space="preserve">14.7403755187988</t>
   </si>
   <si>
     <t xml:space="preserve">15.006308555603</t>
@@ -3230,7 +3230,7 @@
     <t xml:space="preserve">14.9778165817261</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6928863525391</t>
+    <t xml:space="preserve">14.6928853988647</t>
   </si>
   <si>
     <t xml:space="preserve">14.7783641815186</t>
@@ -3242,7 +3242,7 @@
     <t xml:space="preserve">15.2057600021362</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1202802658081</t>
+    <t xml:space="preserve">15.1202812194824</t>
   </si>
   <si>
     <t xml:space="preserve">15.0917882919312</t>
@@ -3257,25 +3257,25 @@
     <t xml:space="preserve">14.9873132705688</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8705949783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0225601196289</t>
+    <t xml:space="preserve">15.8705968856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0225582122803</t>
   </si>
   <si>
     <t xml:space="preserve">16.0320568084717</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8231086730957</t>
+    <t xml:space="preserve">15.8231067657471</t>
   </si>
   <si>
     <t xml:space="preserve">15.9370803833008</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7376270294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4906892776489</t>
+    <t xml:space="preserve">15.7376289367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4906883239746</t>
   </si>
   <si>
     <t xml:space="preserve">15.7091360092163</t>
@@ -3284,19 +3284,19 @@
     <t xml:space="preserve">15.3102350234985</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3672208786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3387260437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6996402740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6853904724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6189069747925</t>
+    <t xml:space="preserve">15.3672199249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3387269973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6996383666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6853923797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6189079284668</t>
   </si>
   <si>
     <t xml:space="preserve">15.428955078125</t>
@@ -3305,16 +3305,16 @@
     <t xml:space="preserve">15.637903213501</t>
   </si>
   <si>
-    <t xml:space="preserve">16.739631652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8678512573242</t>
+    <t xml:space="preserve">16.7396335601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8678531646729</t>
   </si>
   <si>
     <t xml:space="preserve">16.8725986480713</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4784488677979</t>
+    <t xml:space="preserve">16.4784469604492</t>
   </si>
   <si>
     <t xml:space="preserve">17.0340595245361</t>
@@ -3326,25 +3326,25 @@
     <t xml:space="preserve">17.4567050933838</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0388088226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2904987335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0815486907959</t>
+    <t xml:space="preserve">17.0388107299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2904968261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0815505981445</t>
   </si>
   <si>
     <t xml:space="preserve">17.0245628356934</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9770736694336</t>
+    <t xml:space="preserve">16.9770755767822</t>
   </si>
   <si>
     <t xml:space="preserve">17.2572555541992</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4614562988281</t>
+    <t xml:space="preserve">17.4614543914795</t>
   </si>
   <si>
     <t xml:space="preserve">17.4187164306641</t>
@@ -3368,16 +3368,16 @@
     <t xml:space="preserve">18.0360641479492</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9125938415527</t>
+    <t xml:space="preserve">17.9125957489014</t>
   </si>
   <si>
     <t xml:space="preserve">17.9553356170654</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6846504211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0408115386963</t>
+    <t xml:space="preserve">17.6846523284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0408134460449</t>
   </si>
   <si>
     <t xml:space="preserve">18.3304920196533</t>
@@ -3404,13 +3404,13 @@
     <t xml:space="preserve">18.297248840332</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1690311431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1832790374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.444465637207</t>
+    <t xml:space="preserve">18.1690292358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.183277130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4444637298584</t>
   </si>
   <si>
     <t xml:space="preserve">18.8956031799316</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">18.5584373474121</t>
   </si>
   <si>
-    <t xml:space="preserve">18.335241317749</t>
+    <t xml:space="preserve">18.3352394104004</t>
   </si>
   <si>
     <t xml:space="preserve">17.8461112976074</t>
@@ -3440,22 +3440,22 @@
     <t xml:space="preserve">17.1575298309326</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6114120483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5021896362305</t>
+    <t xml:space="preserve">16.6114139556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5021915435791</t>
   </si>
   <si>
     <t xml:space="preserve">16.7253856658936</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8773498535156</t>
+    <t xml:space="preserve">16.877347946167</t>
   </si>
   <si>
     <t xml:space="preserve">16.4214611053467</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9798192977905</t>
+    <t xml:space="preserve">15.9798212051392</t>
   </si>
   <si>
     <t xml:space="preserve">16.0985412597656</t>
@@ -3464,16 +3464,16 @@
     <t xml:space="preserve">16.0083122253418</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2505054473877</t>
+    <t xml:space="preserve">16.2505035400391</t>
   </si>
   <si>
     <t xml:space="preserve">16.4736976623535</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1697731018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0463027954102</t>
+    <t xml:space="preserve">16.169771194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0463047027588</t>
   </si>
   <si>
     <t xml:space="preserve">16.0368061065674</t>
@@ -3488,13 +3488,13 @@
     <t xml:space="preserve">16.0652980804443</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0510520935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1100406646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3949699401855</t>
+    <t xml:space="preserve">16.0510501861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1100387573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3949718475342</t>
   </si>
   <si>
     <t xml:space="preserve">18.4919509887695</t>
@@ -3503,7 +3503,7 @@
     <t xml:space="preserve">17.5896739959717</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6609058380127</t>
+    <t xml:space="preserve">17.6609039306641</t>
   </si>
   <si>
     <t xml:space="preserve">17.0008163452148</t>
@@ -3512,10 +3512,10 @@
     <t xml:space="preserve">16.6731491088867</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5164356231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7328796386719</t>
+    <t xml:space="preserve">16.5164375305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7328815460205</t>
   </si>
   <si>
     <t xml:space="preserve">15.7423791885376</t>
@@ -3524,7 +3524,7 @@
     <t xml:space="preserve">16.1460285186768</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9275808334351</t>
+    <t xml:space="preserve">15.9275827407837</t>
   </si>
   <si>
     <t xml:space="preserve">15.9703226089478</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">16.6541538238525</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7586288452148</t>
+    <t xml:space="preserve">16.7586269378662</t>
   </si>
   <si>
     <t xml:space="preserve">18.0123195648193</t>
@@ -3566,7 +3566,7 @@
     <t xml:space="preserve">16.9913196563721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8346099853516</t>
+    <t xml:space="preserve">16.8346080780029</t>
   </si>
   <si>
     <t xml:space="preserve">17.0435581207275</t>
@@ -3599,22 +3599,22 @@
     <t xml:space="preserve">17.6988964080811</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1405372619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7009010314941</t>
+    <t xml:space="preserve">18.1405391693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7008991241455</t>
   </si>
   <si>
     <t xml:space="preserve">18.7911281585693</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9715824127197</t>
+    <t xml:space="preserve">18.9715843200684</t>
   </si>
   <si>
     <t xml:space="preserve">17.945837020874</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4302158355713</t>
+    <t xml:space="preserve">18.4302177429199</t>
   </si>
   <si>
     <t xml:space="preserve">18.5536880493164</t>
@@ -3623,7 +3623,7 @@
     <t xml:space="preserve">18.7626323699951</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0903034210205</t>
+    <t xml:space="preserve">19.0903053283691</t>
   </si>
   <si>
     <t xml:space="preserve">19.3752346038818</t>
@@ -3650,7 +3650,7 @@
     <t xml:space="preserve">19.6316699981689</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4579696655273</t>
+    <t xml:space="preserve">20.4579677581787</t>
   </si>
   <si>
     <t xml:space="preserve">20.6289253234863</t>
@@ -3659,7 +3659,7 @@
     <t xml:space="preserve">21.0373249053955</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4457244873047</t>
+    <t xml:space="preserve">21.4457225799561</t>
   </si>
   <si>
     <t xml:space="preserve">20.9898376464844</t>
@@ -3668,16 +3668,16 @@
     <t xml:space="preserve">20.7523956298828</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6384220123291</t>
+    <t xml:space="preserve">20.6384239196777</t>
   </si>
   <si>
     <t xml:space="preserve">20.1635398864746</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0970573425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7903842926025</t>
+    <t xml:space="preserve">20.0970554351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7903861999512</t>
   </si>
   <si>
     <t xml:space="preserve">20.7144050598145</t>
@@ -3692,16 +3692,16 @@
     <t xml:space="preserve">21.0943088531494</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4172325134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3982391357422</t>
+    <t xml:space="preserve">21.4172306060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3982372283936</t>
   </si>
   <si>
     <t xml:space="preserve">21.7021617889404</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5691947937012</t>
+    <t xml:space="preserve">21.5691928863525</t>
   </si>
   <si>
     <t xml:space="preserve">22.0820693969727</t>
@@ -3710,7 +3710,7 @@
     <t xml:space="preserve">21.5976867675781</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6261825561523</t>
+    <t xml:space="preserve">21.6261806488037</t>
   </si>
   <si>
     <t xml:space="preserve">19.4797096252441</t>
@@ -3719,7 +3719,7 @@
     <t xml:space="preserve">19.0998020172119</t>
   </si>
   <si>
-    <t xml:space="preserve">19.536693572998</t>
+    <t xml:space="preserve">19.5366954803467</t>
   </si>
   <si>
     <t xml:space="preserve">19.2517642974854</t>
@@ -3737,7 +3737,7 @@
     <t xml:space="preserve">18.2212677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9743270874023</t>
+    <t xml:space="preserve">17.974328994751</t>
   </si>
   <si>
     <t xml:space="preserve">18.5916767120361</t>
@@ -3746,7 +3746,7 @@
     <t xml:space="preserve">18.5394401550293</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0977973937988</t>
+    <t xml:space="preserve">18.0977993011475</t>
   </si>
   <si>
     <t xml:space="preserve">18.0503082275391</t>
@@ -3761,7 +3761,7 @@
     <t xml:space="preserve">18.1452865600586</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5679321289062</t>
+    <t xml:space="preserve">18.5679340362549</t>
   </si>
   <si>
     <t xml:space="preserve">18.68190574646</t>
@@ -3785,25 +3785,25 @@
     <t xml:space="preserve">18.6581611633301</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4492111206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6324138641357</t>
+    <t xml:space="preserve">18.4492130279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6324119567871</t>
   </si>
   <si>
     <t xml:space="preserve">17.7368869781494</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1242904663086</t>
+    <t xml:space="preserve">17.12428855896</t>
   </si>
   <si>
     <t xml:space="preserve">15.1867637634277</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8306016921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5076818466187</t>
+    <t xml:space="preserve">14.8306007385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5076808929443</t>
   </si>
   <si>
     <t xml:space="preserve">15.9133348464966</t>
@@ -3812,13 +3812,13 @@
     <t xml:space="preserve">15.3529739379883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.457447052002</t>
+    <t xml:space="preserve">15.4574480056763</t>
   </si>
   <si>
     <t xml:space="preserve">14.8733415603638</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5856676101685</t>
+    <t xml:space="preserve">15.5856657028198</t>
   </si>
   <si>
     <t xml:space="preserve">15.81360912323</t>
@@ -3827,19 +3827,19 @@
     <t xml:space="preserve">15.5334281921387</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2390012741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2532482147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5191822052002</t>
+    <t xml:space="preserve">15.2390022277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2532472610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5191812515259</t>
   </si>
   <si>
     <t xml:space="preserve">15.8278579711914</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7681274414062</t>
+    <t xml:space="preserve">16.7681255340576</t>
   </si>
   <si>
     <t xml:space="preserve">16.316987991333</t>
@@ -3854,13 +3854,13 @@
     <t xml:space="preserve">15.6331548690796</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6521482467651</t>
+    <t xml:space="preserve">15.6521492004395</t>
   </si>
   <si>
     <t xml:space="preserve">15.889591217041</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5096845626831</t>
+    <t xml:space="preserve">15.5096855163574</t>
   </si>
   <si>
     <t xml:space="preserve">14.7308769226074</t>
@@ -3881,10 +3881,10 @@
     <t xml:space="preserve">14.3224773406982</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8285989761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.812349319458</t>
+    <t xml:space="preserve">13.8285999298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8123483657837</t>
   </si>
   <si>
     <t xml:space="preserve">14.1040306091309</t>
@@ -6000,6 +6000,9 @@
   </si>
   <si>
     <t xml:space="preserve">7.41499996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44500017166138</t>
   </si>
 </sst>
 </file>
@@ -71702,7 +71705,7 @@
     </row>
     <row r="2515">
       <c r="A2515" s="1" t="n">
-        <v>45980.6932407407</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B2515" t="n">
         <v>470241</v>
@@ -71723,6 +71726,32 @@
         <v>1995</v>
       </c>
       <c r="H2515" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" s="1" t="n">
+        <v>45981.6912268518</v>
+      </c>
+      <c r="B2516" t="n">
+        <v>339329</v>
+      </c>
+      <c r="C2516" t="n">
+        <v>7.59000015258789</v>
+      </c>
+      <c r="D2516" t="n">
+        <v>7.30999994277954</v>
+      </c>
+      <c r="E2516" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F2516" t="n">
+        <v>7.44500017166138</v>
+      </c>
+      <c r="G2516" t="s">
+        <v>1996</v>
+      </c>
+      <c r="H2516" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1999" uniqueCount="1999">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2000" uniqueCount="2000">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,130 +44,130 @@
     <t xml:space="preserve">SFER.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">18.01096534729</t>
+    <t xml:space="preserve">18.0109634399414</t>
   </si>
   <si>
     <t xml:space="preserve">17.4978828430176</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9401912689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6836528778076</t>
+    <t xml:space="preserve">17.9401931762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6836547851562</t>
   </si>
   <si>
     <t xml:space="preserve">18.2498111724854</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4086685180664</t>
+    <t xml:space="preserve">19.4086723327637</t>
   </si>
   <si>
     <t xml:space="preserve">19.1344375610352</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8425140380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4621238708496</t>
+    <t xml:space="preserve">18.8425121307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4621257781982</t>
   </si>
   <si>
     <t xml:space="preserve">18.2851963043213</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0994262695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6394233703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5686531066895</t>
+    <t xml:space="preserve">18.0994243621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6394195556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5686511993408</t>
   </si>
   <si>
     <t xml:space="preserve">18.1878890991211</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4798145294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.223274230957</t>
+    <t xml:space="preserve">18.4798126220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2232761383057</t>
   </si>
   <si>
     <t xml:space="preserve">17.7632675170898</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3913516998291</t>
+    <t xml:space="preserve">18.3913536071777</t>
   </si>
   <si>
     <t xml:space="preserve">18.6744346618652</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9578857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2055797576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2586574554443</t>
+    <t xml:space="preserve">17.9578876495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2055816650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.258659362793</t>
   </si>
   <si>
     <t xml:space="preserve">18.0817337036133</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3563423156738</t>
+    <t xml:space="preserve">17.3563442230225</t>
   </si>
   <si>
     <t xml:space="preserve">16.9051837921143</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1617240905762</t>
+    <t xml:space="preserve">17.1617221832275</t>
   </si>
   <si>
     <t xml:space="preserve">16.6486415863037</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0201835632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.48903465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6305770874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4090442657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4532775878906</t>
+    <t xml:space="preserve">17.0201854705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4890365600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6305751800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4090461730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.453275680542</t>
   </si>
   <si>
     <t xml:space="preserve">18.9752063751221</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1348094940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3121128082275</t>
+    <t xml:space="preserve">18.1348133087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3121109008789</t>
   </si>
   <si>
     <t xml:space="preserve">17.9048080444336</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3471183776855</t>
+    <t xml:space="preserve">18.3471202850342</t>
   </si>
   <si>
     <t xml:space="preserve">19.019437789917</t>
   </si>
   <si>
-    <t xml:space="preserve">19.001745223999</t>
+    <t xml:space="preserve">19.0017433166504</t>
   </si>
   <si>
     <t xml:space="preserve">18.8513584136963</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3113613128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.992525100708</t>
+    <t xml:space="preserve">19.3113632202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9925231933594</t>
   </si>
   <si>
     <t xml:space="preserve">19.9482917785645</t>
@@ -176,28 +176,28 @@
     <t xml:space="preserve">19.7271347045898</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3379001617432</t>
+    <t xml:space="preserve">19.3379020690918</t>
   </si>
   <si>
     <t xml:space="preserve">19.647518157959</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9836750030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1167449951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4440536499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0367565155029</t>
+    <t xml:space="preserve">19.9836769104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1167469024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.444055557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0367546081543</t>
   </si>
   <si>
     <t xml:space="preserve">20.178295135498</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4971313476562</t>
+    <t xml:space="preserve">19.4971351623535</t>
   </si>
   <si>
     <t xml:space="preserve">19.4705924987793</t>
@@ -209,13 +209,13 @@
     <t xml:space="preserve">19.4794406890869</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9129085540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8686771392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4175186157227</t>
+    <t xml:space="preserve">19.9129066467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8686752319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.417516708374</t>
   </si>
   <si>
     <t xml:space="preserve">18.8690528869629</t>
@@ -224,22 +224,22 @@
     <t xml:space="preserve">18.833667755127</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5152015686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9309749603271</t>
+    <t xml:space="preserve">18.5151996612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9309730529785</t>
   </si>
   <si>
     <t xml:space="preserve">18.8955898284912</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5240478515625</t>
+    <t xml:space="preserve">18.5240459442139</t>
   </si>
   <si>
     <t xml:space="preserve">18.9486675262451</t>
   </si>
   <si>
-    <t xml:space="preserve">18.798282623291</t>
+    <t xml:space="preserve">18.7982807159424</t>
   </si>
   <si>
     <t xml:space="preserve">18.8778972625732</t>
@@ -248,37 +248,37 @@
     <t xml:space="preserve">19.2936706542969</t>
   </si>
   <si>
-    <t xml:space="preserve">18.80712890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3205814361572</t>
+    <t xml:space="preserve">18.8071269989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3205795288086</t>
   </si>
   <si>
     <t xml:space="preserve">18.3648128509521</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8251934051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0640430450439</t>
+    <t xml:space="preserve">17.8251914978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0640411376953</t>
   </si>
   <si>
     <t xml:space="preserve">18.3117351531982</t>
   </si>
   <si>
-    <t xml:space="preserve">17.878267288208</t>
+    <t xml:space="preserve">17.8782653808594</t>
   </si>
   <si>
     <t xml:space="preserve">18.0021171569824</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7190380096436</t>
+    <t xml:space="preserve">17.7190399169922</t>
   </si>
   <si>
     <t xml:space="preserve">17.4448051452637</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1440296173096</t>
+    <t xml:space="preserve">17.1440315246582</t>
   </si>
   <si>
     <t xml:space="preserve">17.5509586334229</t>
@@ -290,31 +290,31 @@
     <t xml:space="preserve">17.4182662963867</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9313468933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7367305755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6482696533203</t>
+    <t xml:space="preserve">17.9313488006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7367286682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6482677459717</t>
   </si>
   <si>
     <t xml:space="preserve">17.593936920166</t>
   </si>
   <si>
-    <t xml:space="preserve">17.81125831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7025966644287</t>
+    <t xml:space="preserve">17.8112564086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7025985717773</t>
   </si>
   <si>
     <t xml:space="preserve">17.648265838623</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5305500030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4128360748291</t>
+    <t xml:space="preserve">17.5305519104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4128379821777</t>
   </si>
   <si>
     <t xml:space="preserve">17.304178237915</t>
@@ -323,22 +323,22 @@
     <t xml:space="preserve">17.4762210845947</t>
   </si>
   <si>
-    <t xml:space="preserve">17.430944442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4852752685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.747875213623</t>
+    <t xml:space="preserve">17.4309482574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.485279083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7478733062744</t>
   </si>
   <si>
     <t xml:space="preserve">17.6844882965088</t>
   </si>
   <si>
-    <t xml:space="preserve">17.150239944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7155990600586</t>
+    <t xml:space="preserve">17.1502418518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.71559715271</t>
   </si>
   <si>
     <t xml:space="preserve">16.5435543060303</t>
@@ -350,10 +350,10 @@
     <t xml:space="preserve">17.0778007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8384246826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9380283355713</t>
+    <t xml:space="preserve">17.8384227752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9380302429199</t>
   </si>
   <si>
     <t xml:space="preserve">17.7297630310059</t>
@@ -365,28 +365,28 @@
     <t xml:space="preserve">18.1825141906738</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8514270782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3896198272705</t>
+    <t xml:space="preserve">16.8514232635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3896179199219</t>
   </si>
   <si>
     <t xml:space="preserve">16.6793785095215</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2628440856934</t>
+    <t xml:space="preserve">16.262845993042</t>
   </si>
   <si>
     <t xml:space="preserve">16.5254459381104</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6069393157959</t>
+    <t xml:space="preserve">16.6069355010986</t>
   </si>
   <si>
     <t xml:space="preserve">16.8061504364014</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8242607116699</t>
+    <t xml:space="preserve">16.8242588043213</t>
   </si>
   <si>
     <t xml:space="preserve">16.0726909637451</t>
@@ -395,55 +395,55 @@
     <t xml:space="preserve">15.8734798431396</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3624496459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4439468383789</t>
+    <t xml:space="preserve">16.3624515533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4439487457275</t>
   </si>
   <si>
     <t xml:space="preserve">16.69748878479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0959072113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1321296691895</t>
+    <t xml:space="preserve">17.0959091186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1321315765381</t>
   </si>
   <si>
     <t xml:space="preserve">17.086856842041</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0325241088867</t>
+    <t xml:space="preserve">17.0325260162354</t>
   </si>
   <si>
     <t xml:space="preserve">17.3403949737549</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9018077850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1372394561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9289722442627</t>
+    <t xml:space="preserve">17.9018096923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1372413635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9289741516113</t>
   </si>
   <si>
     <t xml:space="preserve">18.771089553833</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6352653503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0699081420898</t>
+    <t xml:space="preserve">18.6352672576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0699100494385</t>
   </si>
   <si>
     <t xml:space="preserve">19.2147884368896</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6262092590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.499439239502</t>
+    <t xml:space="preserve">18.6262111663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4994411468506</t>
   </si>
   <si>
     <t xml:space="preserve">18.2187366485596</t>
@@ -458,7 +458,7 @@
     <t xml:space="preserve">18.762035369873</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8073120117188</t>
+    <t xml:space="preserve">18.8073139190674</t>
   </si>
   <si>
     <t xml:space="preserve">18.9431381225586</t>
@@ -467,16 +467,16 @@
     <t xml:space="preserve">19.0427436828613</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6624317169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4722766876221</t>
+    <t xml:space="preserve">18.6624336242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4722747802734</t>
   </si>
   <si>
     <t xml:space="preserve">18.6171569824219</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7529811859131</t>
+    <t xml:space="preserve">18.7529792785645</t>
   </si>
   <si>
     <t xml:space="preserve">18.9703044891357</t>
@@ -488,10 +488,10 @@
     <t xml:space="preserve">18.6081008911133</t>
   </si>
   <si>
-    <t xml:space="preserve">18.653377532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5175533294678</t>
+    <t xml:space="preserve">18.6533794403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5175514221191</t>
   </si>
   <si>
     <t xml:space="preserve">18.870698928833</t>
@@ -500,16 +500,16 @@
     <t xml:space="preserve">18.6986503601074</t>
   </si>
   <si>
-    <t xml:space="preserve">19.106128692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9210834503174</t>
+    <t xml:space="preserve">19.1061305999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9210815429688</t>
   </si>
   <si>
     <t xml:space="preserve">19.6947059631348</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5588798522949</t>
+    <t xml:space="preserve">19.5588836669922</t>
   </si>
   <si>
     <t xml:space="preserve">19.4592761993408</t>
@@ -518,31 +518,31 @@
     <t xml:space="preserve">19.314395904541</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8888092041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1332931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.160457611084</t>
+    <t xml:space="preserve">18.8888072967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1332893371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1604595184326</t>
   </si>
   <si>
     <t xml:space="preserve">19.9391918182373</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4553279876709</t>
+    <t xml:space="preserve">20.4553298950195</t>
   </si>
   <si>
     <t xml:space="preserve">20.3557224273682</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3104496002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3919429779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4643859863281</t>
+    <t xml:space="preserve">20.3104476928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3919448852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4643840789795</t>
   </si>
   <si>
     <t xml:space="preserve">20.6907596588135</t>
@@ -551,22 +551,22 @@
     <t xml:space="preserve">20.8446941375732</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7994174957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4009990692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1021842956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5277709960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3647785186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5458812713623</t>
+    <t xml:space="preserve">20.7994213104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4009971618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1021823883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5277690887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3647804260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5458793640137</t>
   </si>
   <si>
     <t xml:space="preserve">20.7541446685791</t>
@@ -575,22 +575,22 @@
     <t xml:space="preserve">20.4191093444824</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0116329193115</t>
+    <t xml:space="preserve">20.0116348266602</t>
   </si>
   <si>
     <t xml:space="preserve">20.2651710510254</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3285579681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0387935638428</t>
+    <t xml:space="preserve">20.3285598754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0387954711914</t>
   </si>
   <si>
     <t xml:space="preserve">20.1474590301514</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2289543151855</t>
+    <t xml:space="preserve">20.2289524078369</t>
   </si>
   <si>
     <t xml:space="preserve">20.5006046295166</t>
@@ -599,31 +599,31 @@
     <t xml:space="preserve">20.5639877319336</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1836814880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5498275756836</t>
+    <t xml:space="preserve">20.1836795806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.549825668335</t>
   </si>
   <si>
     <t xml:space="preserve">19.4140014648438</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5045528411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7218723297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7943115234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5226593017578</t>
+    <t xml:space="preserve">19.5045509338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7218685150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7943134307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5226631164551</t>
   </si>
   <si>
     <t xml:space="preserve">19.8305320739746</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9120254516602</t>
+    <t xml:space="preserve">19.9120273590088</t>
   </si>
   <si>
     <t xml:space="preserve">19.7490367889404</t>
@@ -632,31 +632,31 @@
     <t xml:space="preserve">18.0919628143311</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3002281188965</t>
+    <t xml:space="preserve">18.3002262115479</t>
   </si>
   <si>
     <t xml:space="preserve">18.3273944854736</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2459011077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0104694366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7388191223145</t>
+    <t xml:space="preserve">18.2458992004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0104675292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7388172149658</t>
   </si>
   <si>
     <t xml:space="preserve">17.8565330505371</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8203144073486</t>
+    <t xml:space="preserve">17.8203125</t>
   </si>
   <si>
     <t xml:space="preserve">17.6392116546631</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3455047607422</t>
+    <t xml:space="preserve">18.3455066680908</t>
   </si>
   <si>
     <t xml:space="preserve">18.3907814025879</t>
@@ -665,13 +665,13 @@
     <t xml:space="preserve">19.151403427124</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2872314453125</t>
+    <t xml:space="preserve">19.2872295379639</t>
   </si>
   <si>
     <t xml:space="preserve">19.3958892822266</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3777809143066</t>
+    <t xml:space="preserve">19.377779006958</t>
   </si>
   <si>
     <t xml:space="preserve">19.1151847839355</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">19.5860443115234</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2600650787354</t>
+    <t xml:space="preserve">19.2600631713867</t>
   </si>
   <si>
     <t xml:space="preserve">20.3738327026367</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">20.3466682434082</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2380084991455</t>
+    <t xml:space="preserve">20.2380104064941</t>
   </si>
   <si>
     <t xml:space="preserve">20.1293449401855</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">20.8084754943848</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6183223724365</t>
+    <t xml:space="preserve">20.6183185577393</t>
   </si>
   <si>
     <t xml:space="preserve">21.4785480499268</t>
@@ -710,19 +710,19 @@
     <t xml:space="preserve">21.5328807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0671253204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.058069229126</t>
+    <t xml:space="preserve">22.0671272277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0580711364746</t>
   </si>
   <si>
     <t xml:space="preserve">22.2572822570801</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2934989929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3025569915771</t>
+    <t xml:space="preserve">22.2935028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3025550842285</t>
   </si>
   <si>
     <t xml:space="preserve">22.3206653594971</t>
@@ -731,22 +731,22 @@
     <t xml:space="preserve">22.2753925323486</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2391700744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8186950683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0722351074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.891134262085</t>
+    <t xml:space="preserve">22.2391719818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8186931610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0722332000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8911361694336</t>
   </si>
   <si>
     <t xml:space="preserve">23.1537303924561</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0993995666504</t>
+    <t xml:space="preserve">23.0993976593018</t>
   </si>
   <si>
     <t xml:space="preserve">22.5923175811768</t>
@@ -761,34 +761,34 @@
     <t xml:space="preserve">22.1757869720459</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1395664215088</t>
+    <t xml:space="preserve">22.1395645141602</t>
   </si>
   <si>
     <t xml:space="preserve">23.6064834594727</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7513599395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1226177215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6427001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6879730224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5612087249756</t>
+    <t xml:space="preserve">23.7513618469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1226196289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6427040100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6879768371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.561206817627</t>
   </si>
   <si>
     <t xml:space="preserve">23.7423076629639</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7241954803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6336460113525</t>
+    <t xml:space="preserve">23.7241973876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6336498260498</t>
   </si>
   <si>
     <t xml:space="preserve">23.8238010406494</t>
@@ -800,16 +800,16 @@
     <t xml:space="preserve">24.0139598846436</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2856101989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0682888031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9777412414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2946643829346</t>
+    <t xml:space="preserve">24.285608291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0682907104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9777393341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2946662902832</t>
   </si>
   <si>
     <t xml:space="preserve">24.4304904937744</t>
@@ -824,16 +824,16 @@
     <t xml:space="preserve">25.1911144256592</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3903255462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4265460968018</t>
+    <t xml:space="preserve">25.390323638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4265441894531</t>
   </si>
   <si>
     <t xml:space="preserve">25.6167011260986</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6710300445557</t>
+    <t xml:space="preserve">25.6710319519043</t>
   </si>
   <si>
     <t xml:space="preserve">25.6529197692871</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">24.9013500213623</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0643444061279</t>
+    <t xml:space="preserve">25.0643463134766</t>
   </si>
   <si>
     <t xml:space="preserve">24.8017463684082</t>
@@ -866,19 +866,19 @@
     <t xml:space="preserve">25.3722152709961</t>
   </si>
   <si>
-    <t xml:space="preserve">25.62575340271</t>
+    <t xml:space="preserve">25.6257553100586</t>
   </si>
   <si>
     <t xml:space="preserve">25.2273349761963</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1730041503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1639499664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.399377822876</t>
+    <t xml:space="preserve">25.173002243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.163948059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3993797302246</t>
   </si>
   <si>
     <t xml:space="preserve">25.7253608703613</t>
@@ -890,13 +890,13 @@
     <t xml:space="preserve">25.1277275085449</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7434711456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.544261932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4808750152588</t>
+    <t xml:space="preserve">25.7434730529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5442600250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4808731079102</t>
   </si>
   <si>
     <t xml:space="preserve">25.5080413818359</t>
@@ -908,43 +908,43 @@
     <t xml:space="preserve">25.0824527740479</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7836380004883</t>
+    <t xml:space="preserve">24.7836399078369</t>
   </si>
   <si>
     <t xml:space="preserve">24.4214344024658</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2674999237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5261516571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1237812042236</t>
+    <t xml:space="preserve">24.2674980163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5261497497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1237831115723</t>
   </si>
   <si>
     <t xml:space="preserve">26.1871662139893</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6308631896973</t>
+    <t xml:space="preserve">26.6308650970459</t>
   </si>
   <si>
     <t xml:space="preserve">26.4859828948975</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3229942321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6761417388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8934593200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2596054077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.667085647583</t>
+    <t xml:space="preserve">26.3229923248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.676139831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.893461227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2596073150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6670837402344</t>
   </si>
   <si>
     <t xml:space="preserve">26.9115695953369</t>
@@ -953,19 +953,19 @@
     <t xml:space="preserve">26.6036987304688</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5946464538574</t>
+    <t xml:space="preserve">26.5946445465088</t>
   </si>
   <si>
     <t xml:space="preserve">25.3088302612305</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3269386291504</t>
+    <t xml:space="preserve">25.326940536499</t>
   </si>
   <si>
     <t xml:space="preserve">25.8340225219727</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8984451293945</t>
+    <t xml:space="preserve">25.8984432220459</t>
   </si>
   <si>
     <t xml:space="preserve">26.0641059875488</t>
@@ -977,37 +977,37 @@
     <t xml:space="preserve">23.6159954071045</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2202472686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1282119750977</t>
+    <t xml:space="preserve">23.2202453613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.128210067749</t>
   </si>
   <si>
     <t xml:space="preserve">22.9625511169434</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8705158233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8613128662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.266263961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.238655090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0453853607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8889217376709</t>
+    <t xml:space="preserve">22.8705196380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8613147735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2662658691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2386512756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0453834533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8889255523682</t>
   </si>
   <si>
     <t xml:space="preserve">22.0882263183594</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3183097839355</t>
+    <t xml:space="preserve">22.3183116912842</t>
   </si>
   <si>
     <t xml:space="preserve">22.2262763977051</t>
@@ -1016,40 +1016,40 @@
     <t xml:space="preserve">22.3827342987061</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3643264770508</t>
+    <t xml:space="preserve">22.3643283843994</t>
   </si>
   <si>
     <t xml:space="preserve">22.7416667938232</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9533500671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8797187805176</t>
+    <t xml:space="preserve">22.9533462524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8797206878662</t>
   </si>
   <si>
     <t xml:space="preserve">23.2846717834473</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4871482849121</t>
+    <t xml:space="preserve">23.4871444702148</t>
   </si>
   <si>
     <t xml:space="preserve">23.4319248199463</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8060932159424</t>
+    <t xml:space="preserve">22.806095123291</t>
   </si>
   <si>
     <t xml:space="preserve">23.0269756317139</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6036167144775</t>
+    <t xml:space="preserve">22.6036186218262</t>
   </si>
   <si>
     <t xml:space="preserve">22.2538871765137</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5452213287354</t>
+    <t xml:space="preserve">21.5452251434326</t>
   </si>
   <si>
     <t xml:space="preserve">21.4900035858154</t>
@@ -1061,16 +1061,16 @@
     <t xml:space="preserve">21.5544261932373</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6740703582764</t>
+    <t xml:space="preserve">21.674072265625</t>
   </si>
   <si>
     <t xml:space="preserve">21.6280536651611</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1678810119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2046966552734</t>
+    <t xml:space="preserve">21.1678829193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2046985626221</t>
   </si>
   <si>
     <t xml:space="preserve">21.1218662261963</t>
@@ -1079,10 +1079,10 @@
     <t xml:space="preserve">21.416374206543</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5084095001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9133605957031</t>
+    <t xml:space="preserve">21.5084114074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9133625030518</t>
   </si>
   <si>
     <t xml:space="preserve">21.8857517242432</t>
@@ -1094,16 +1094,16 @@
     <t xml:space="preserve">22.6220245361328</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3735313415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2170734405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4103450775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5299911499023</t>
+    <t xml:space="preserve">22.3735332489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2170715332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4103469848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5299892425537</t>
   </si>
   <si>
     <t xml:space="preserve">22.6312274932861</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">21.6556644439697</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2630920410156</t>
+    <t xml:space="preserve">22.263090133667</t>
   </si>
   <si>
     <t xml:space="preserve">22.5391941070557</t>
@@ -1130,10 +1130,10 @@
     <t xml:space="preserve">22.3551254272461</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0514106750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7876834869385</t>
+    <t xml:space="preserve">22.0514125823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7876853942871</t>
   </si>
   <si>
     <t xml:space="preserve">22.3367195129395</t>
@@ -1142,88 +1142,88 @@
     <t xml:space="preserve">22.115837097168</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7661075592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0606174468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7569026947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9961929321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.701681137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0053958892822</t>
+    <t xml:space="preserve">21.7661037445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0606155395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7569007873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9961891174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7016830444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0053939819336</t>
   </si>
   <si>
     <t xml:space="preserve">21.8765468597412</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1250400543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7753105163574</t>
+    <t xml:space="preserve">22.1250419616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7753086090088</t>
   </si>
   <si>
     <t xml:space="preserve">22.0238018035889</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9041576385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6832733154297</t>
+    <t xml:space="preserve">21.9041557312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6832752227783</t>
   </si>
   <si>
     <t xml:space="preserve">20.827356338501</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0574417114258</t>
+    <t xml:space="preserve">21.0574398040771</t>
   </si>
   <si>
     <t xml:space="preserve">20.94700050354</t>
   </si>
   <si>
-    <t xml:space="preserve">20.799747467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.103458404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0758476257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3243408203125</t>
+    <t xml:space="preserve">20.7997455596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1034622192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0758495330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3243427276611</t>
   </si>
   <si>
     <t xml:space="preserve">21.9501762390137</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0974311828613</t>
+    <t xml:space="preserve">22.0974292755127</t>
   </si>
   <si>
     <t xml:space="preserve">21.8581409454346</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6372566223145</t>
+    <t xml:space="preserve">21.6372585296631</t>
   </si>
   <si>
     <t xml:space="preserve">21.2967319488525</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9746112823486</t>
+    <t xml:space="preserve">20.9746131896973</t>
   </si>
   <si>
     <t xml:space="preserve">20.983814239502</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1402702331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0666446685791</t>
+    <t xml:space="preserve">21.1402740478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0666465759277</t>
   </si>
   <si>
     <t xml:space="preserve">20.7077102661133</t>
@@ -1235,10 +1235,10 @@
     <t xml:space="preserve">21.1586799621582</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0206298828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0022220611572</t>
+    <t xml:space="preserve">21.0206260681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0022201538086</t>
   </si>
   <si>
     <t xml:space="preserve">20.6340847015381</t>
@@ -1253,10 +1253,10 @@
     <t xml:space="preserve">20.3947944641113</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0082530975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9714393615723</t>
+    <t xml:space="preserve">20.0082511901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9714374542236</t>
   </si>
   <si>
     <t xml:space="preserve">20.0634708404541</t>
@@ -1271,25 +1271,25 @@
     <t xml:space="preserve">20.8917808532715</t>
   </si>
   <si>
-    <t xml:space="preserve">21.241512298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9285926818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2475414276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1647090911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0910816192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2719783782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6953353881836</t>
+    <t xml:space="preserve">21.2415084838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9285945892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2475395202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1647109985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0910835266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2719764709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.695333480835</t>
   </si>
   <si>
     <t xml:space="preserve">19.8057765960693</t>
@@ -1298,49 +1298,49 @@
     <t xml:space="preserve">19.7321491241455</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1831150054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0450668334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2935562133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4316101074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5696601867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.661693572998</t>
+    <t xml:space="preserve">20.1831169128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0450630187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2935581207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4316082000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5696620941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6616954803467</t>
   </si>
   <si>
     <t xml:space="preserve">21.131067276001</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0482406616211</t>
+    <t xml:space="preserve">21.0482387542725</t>
   </si>
   <si>
     <t xml:space="preserve">21.1954936981201</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4531879425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8089504241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6708984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7721347808838</t>
+    <t xml:space="preserve">21.4531898498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8089485168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6708965301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7721328735352</t>
   </si>
   <si>
     <t xml:space="preserve">19.4652481079102</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7965717315674</t>
+    <t xml:space="preserve">19.7965698242188</t>
   </si>
   <si>
     <t xml:space="preserve">19.8609962463379</t>
@@ -1349,10 +1349,10 @@
     <t xml:space="preserve">20.0174541473389</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2199268341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2291316986084</t>
+    <t xml:space="preserve">20.2199287414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.229133605957</t>
   </si>
   <si>
     <t xml:space="preserve">20.5236415863037</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">20.6524925231934</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9101886749268</t>
+    <t xml:space="preserve">20.9101867675781</t>
   </si>
   <si>
     <t xml:space="preserve">20.2659473419189</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">21.2599182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3703556060791</t>
+    <t xml:space="preserve">21.3703575134277</t>
   </si>
   <si>
     <t xml:space="preserve">21.5176105499268</t>
@@ -1388,28 +1388,28 @@
     <t xml:space="preserve">20.8549671173096</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9193916320801</t>
+    <t xml:space="preserve">20.9193897247314</t>
   </si>
   <si>
     <t xml:space="preserve">20.5052375793457</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3487777709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0266590118408</t>
+    <t xml:space="preserve">20.3487796783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0266571044922</t>
   </si>
   <si>
     <t xml:space="preserve">19.7229461669922</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9162158966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5604572296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7169170379639</t>
+    <t xml:space="preserve">19.9162178039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5604553222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7169151306152</t>
   </si>
   <si>
     <t xml:space="preserve">20.9377975463867</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">20.8365592956543</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6004428863525</t>
+    <t xml:space="preserve">21.6004447937012</t>
   </si>
   <si>
     <t xml:space="preserve">20.6248817443848</t>
@@ -1436,10 +1436,10 @@
     <t xml:space="preserve">19.9990463256836</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1278953552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3303680419922</t>
+    <t xml:space="preserve">20.1278991699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3303718566895</t>
   </si>
   <si>
     <t xml:space="preserve">20.8733749389648</t>
@@ -1448,52 +1448,52 @@
     <t xml:space="preserve">20.3763885498047</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5328483581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3027591705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.64328956604</t>
+    <t xml:space="preserve">20.5328464508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3027610778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6432876586914</t>
   </si>
   <si>
     <t xml:space="preserve">20.6156768798828</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7261180877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2783241271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3151378631592</t>
+    <t xml:space="preserve">20.7261199951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2783260345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3151397705078</t>
   </si>
   <si>
     <t xml:space="preserve">21.536018371582</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7937164306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6496353149414</t>
+    <t xml:space="preserve">21.7937183380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.64963722229</t>
   </si>
   <si>
     <t xml:space="preserve">22.5483989715576</t>
   </si>
   <si>
-    <t xml:space="preserve">22.419548034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2078704833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5668048858643</t>
+    <t xml:space="preserve">22.4195499420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2078685760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5668029785156</t>
   </si>
   <si>
     <t xml:space="preserve">22.6128215789795</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9165344238281</t>
+    <t xml:space="preserve">22.9165325164795</t>
   </si>
   <si>
     <t xml:space="preserve">22.6864471435547</t>
@@ -1502,25 +1502,25 @@
     <t xml:space="preserve">22.7324657440186</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8337001800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7692775726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9073314666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2754669189453</t>
+    <t xml:space="preserve">22.8337059020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7692813873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9073295593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2754688262939</t>
   </si>
   <si>
     <t xml:space="preserve">22.991304397583</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3090705871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4118747711182</t>
+    <t xml:space="preserve">23.3090686798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4118766784668</t>
   </si>
   <si>
     <t xml:space="preserve">22.9071884155273</t>
@@ -1541,7 +1541,7 @@
     <t xml:space="preserve">23.0754165649414</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3558006286621</t>
+    <t xml:space="preserve">23.3557987213135</t>
   </si>
   <si>
     <t xml:space="preserve">23.1969146728516</t>
@@ -1559,19 +1559,19 @@
     <t xml:space="preserve">22.7389583587646</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1595325469971</t>
+    <t xml:space="preserve">23.1595344543457</t>
   </si>
   <si>
     <t xml:space="preserve">23.5053367614746</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3838367462158</t>
+    <t xml:space="preserve">23.3838386535645</t>
   </si>
   <si>
     <t xml:space="preserve">23.3931846618652</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2623405456543</t>
+    <t xml:space="preserve">23.262336730957</t>
   </si>
   <si>
     <t xml:space="preserve">22.9258823394775</t>
@@ -1580,7 +1580,7 @@
     <t xml:space="preserve">20.991247177124</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3370246887207</t>
+    <t xml:space="preserve">20.3370208740234</t>
   </si>
   <si>
     <t xml:space="preserve">19.9912166595459</t>
@@ -1616,16 +1616,16 @@
     <t xml:space="preserve">18.0752754211426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6220207214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.079948425293</t>
+    <t xml:space="preserve">18.6220188140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0799503326416</t>
   </si>
   <si>
     <t xml:space="preserve">18.6033306121826</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6360416412354</t>
+    <t xml:space="preserve">18.6360397338867</t>
   </si>
   <si>
     <t xml:space="preserve">18.7949237823486</t>
@@ -1634,19 +1634,19 @@
     <t xml:space="preserve">18.7762317657471</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7201538085938</t>
+    <t xml:space="preserve">18.7201557159424</t>
   </si>
   <si>
     <t xml:space="preserve">18.5752906799316</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3930416107178</t>
+    <t xml:space="preserve">18.3930435180664</t>
   </si>
   <si>
     <t xml:space="preserve">18.5285606384277</t>
   </si>
   <si>
-    <t xml:space="preserve">18.495849609375</t>
+    <t xml:space="preserve">18.4958515167236</t>
   </si>
   <si>
     <t xml:space="preserve">18.4351005554199</t>
@@ -1673,16 +1673,16 @@
     <t xml:space="preserve">18.6734237670898</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7575378417969</t>
+    <t xml:space="preserve">18.7575359344482</t>
   </si>
   <si>
     <t xml:space="preserve">18.7295017242432</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2762184143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2528533935547</t>
+    <t xml:space="preserve">18.276216506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2528514862061</t>
   </si>
   <si>
     <t xml:space="preserve">18.2107944488525</t>
@@ -1691,13 +1691,13 @@
     <t xml:space="preserve">18.3790245056152</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1407279968262</t>
+    <t xml:space="preserve">19.1407241821289</t>
   </si>
   <si>
     <t xml:space="preserve">19.4398002624512</t>
   </si>
   <si>
-    <t xml:space="preserve">19.402416229248</t>
+    <t xml:space="preserve">19.4024143218994</t>
   </si>
   <si>
     <t xml:space="preserve">19.4117641448975</t>
@@ -1706,25 +1706,25 @@
     <t xml:space="preserve">19.430456161499</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3650321960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1594200134277</t>
+    <t xml:space="preserve">19.3650302886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1594219207764</t>
   </si>
   <si>
     <t xml:space="preserve">19.1687660217285</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1126899719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0939960479736</t>
+    <t xml:space="preserve">19.1126880645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0939979553223</t>
   </si>
   <si>
     <t xml:space="preserve">18.7388458251953</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0566120147705</t>
+    <t xml:space="preserve">19.0566101074219</t>
   </si>
   <si>
     <t xml:space="preserve">18.8416519165039</t>
@@ -1736,7 +1736,7 @@
     <t xml:space="preserve">19.2528800964355</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5239162445068</t>
+    <t xml:space="preserve">19.5239124298096</t>
   </si>
   <si>
     <t xml:space="preserve">19.4211101531982</t>
@@ -1748,13 +1748,13 @@
     <t xml:space="preserve">20.0753326416016</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7482204437256</t>
+    <t xml:space="preserve">19.748218536377</t>
   </si>
   <si>
     <t xml:space="preserve">20.0192565917969</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7669105529785</t>
+    <t xml:space="preserve">19.7669124603271</t>
   </si>
   <si>
     <t xml:space="preserve">19.7856044769287</t>
@@ -1763,7 +1763,7 @@
     <t xml:space="preserve">19.5706462860107</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2809162139893</t>
+    <t xml:space="preserve">19.2809181213379</t>
   </si>
   <si>
     <t xml:space="preserve">19.1500720977783</t>
@@ -1781,10 +1781,10 @@
     <t xml:space="preserve">18.1780853271484</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6453876495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8556442260742</t>
+    <t xml:space="preserve">18.6453857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8556423187256</t>
   </si>
   <si>
     <t xml:space="preserve">17.2528228759766</t>
@@ -1802,7 +1802,7 @@
     <t xml:space="preserve">17.949104309082</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1173324584961</t>
+    <t xml:space="preserve">18.1173343658447</t>
   </si>
   <si>
     <t xml:space="preserve">18.2154674530029</t>
@@ -1811,13 +1811,13 @@
     <t xml:space="preserve">19.1874580383301</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0098819732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5986843109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5893363952637</t>
+    <t xml:space="preserve">19.0098838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5986824035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.589334487915</t>
   </si>
   <si>
     <t xml:space="preserve">19.645414352417</t>
@@ -1835,7 +1835,7 @@
     <t xml:space="preserve">20.0005645751953</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6267204284668</t>
+    <t xml:space="preserve">19.6267223358154</t>
   </si>
   <si>
     <t xml:space="preserve">19.4865322113037</t>
@@ -1844,10 +1844,10 @@
     <t xml:space="preserve">19.7014904022217</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3930702209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7481918334961</t>
+    <t xml:space="preserve">19.3930721282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7481937408447</t>
   </si>
   <si>
     <t xml:space="preserve">18.7855777740479</t>
@@ -1856,7 +1856,7 @@
     <t xml:space="preserve">19.0659580230713</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5145683288574</t>
+    <t xml:space="preserve">19.5145702362061</t>
   </si>
   <si>
     <t xml:space="preserve">19.206148147583</t>
@@ -1868,16 +1868,16 @@
     <t xml:space="preserve">16.7107524871826</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8135566711426</t>
+    <t xml:space="preserve">16.8135585784912</t>
   </si>
   <si>
     <t xml:space="preserve">16.5845813751221</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5471973419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5378494262695</t>
+    <t xml:space="preserve">16.5471954345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5378475189209</t>
   </si>
   <si>
     <t xml:space="preserve">16.7200965881348</t>
@@ -1907,7 +1907,7 @@
     <t xml:space="preserve">16.8415946960449</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6640224456787</t>
+    <t xml:space="preserve">16.6640205383301</t>
   </si>
   <si>
     <t xml:space="preserve">16.5331783294678</t>
@@ -1919,28 +1919,28 @@
     <t xml:space="preserve">16.6827125549316</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5986003875732</t>
+    <t xml:space="preserve">16.5985984802246</t>
   </si>
   <si>
     <t xml:space="preserve">16.4256973266602</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1266231536865</t>
+    <t xml:space="preserve">16.1266212463379</t>
   </si>
   <si>
     <t xml:space="preserve">16.1593341827393</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4490623474121</t>
+    <t xml:space="preserve">16.4490642547607</t>
   </si>
   <si>
     <t xml:space="preserve">16.192045211792</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2154102325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4817752838135</t>
+    <t xml:space="preserve">16.2154121398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4817733764648</t>
   </si>
   <si>
     <t xml:space="preserve">16.5238304138184</t>
@@ -1949,7 +1949,7 @@
     <t xml:space="preserve">16.4023303985596</t>
   </si>
   <si>
-    <t xml:space="preserve">16.299524307251</t>
+    <t xml:space="preserve">16.2995262145996</t>
   </si>
   <si>
     <t xml:space="preserve">16.5799083709717</t>
@@ -1964,10 +1964,10 @@
     <t xml:space="preserve">17.1967468261719</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2201118469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5752601623535</t>
+    <t xml:space="preserve">17.2201099395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5752620697021</t>
   </si>
   <si>
     <t xml:space="preserve">17.5518970489502</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">17.1313228607178</t>
   </si>
   <si>
-    <t xml:space="preserve">17.229455947876</t>
+    <t xml:space="preserve">17.2294578552246</t>
   </si>
   <si>
     <t xml:space="preserve">17.4911479949951</t>
@@ -1991,22 +1991,22 @@
     <t xml:space="preserve">17.4397449493408</t>
   </si>
   <si>
-    <t xml:space="preserve">17.453763961792</t>
+    <t xml:space="preserve">17.4537620544434</t>
   </si>
   <si>
     <t xml:space="preserve">17.7294731140137</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6547031402588</t>
+    <t xml:space="preserve">17.6547012329102</t>
   </si>
   <si>
     <t xml:space="preserve">17.3369369506836</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1453418731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8462677001953</t>
+    <t xml:space="preserve">17.1453437805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8462715148926</t>
   </si>
   <si>
     <t xml:space="preserve">17.1687088012695</t>
@@ -2015,7 +2015,7 @@
     <t xml:space="preserve">16.822904586792</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9911594390869</t>
+    <t xml:space="preserve">17.9911613464355</t>
   </si>
   <si>
     <t xml:space="preserve">17.9117202758789</t>
@@ -2027,16 +2027,16 @@
     <t xml:space="preserve">17.6593761444092</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7948951721191</t>
+    <t xml:space="preserve">17.7948970794678</t>
   </si>
   <si>
     <t xml:space="preserve">17.6360130310059</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3275947570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3976898193359</t>
+    <t xml:space="preserve">17.3275928497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3976879119873</t>
   </si>
   <si>
     <t xml:space="preserve">17.6266651153564</t>
@@ -2045,13 +2045,13 @@
     <t xml:space="preserve">17.5004940032959</t>
   </si>
   <si>
-    <t xml:space="preserve">17.869665145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3136005401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.056583404541</t>
+    <t xml:space="preserve">17.8696632385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3136024475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0565814971924</t>
   </si>
   <si>
     <t xml:space="preserve">18.2855625152588</t>
@@ -2060,40 +2060,40 @@
     <t xml:space="preserve">18.0192012786865</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9677963256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9070491790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.69211769104</t>
+    <t xml:space="preserve">17.9677982330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9070453643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6921157836914</t>
   </si>
   <si>
     <t xml:space="preserve">18.5051937103271</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3416404724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5565986633301</t>
+    <t xml:space="preserve">18.3416385650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5565967559814</t>
   </si>
   <si>
     <t xml:space="preserve">18.4397716522217</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5472507476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3089294433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8603439331055</t>
+    <t xml:space="preserve">18.5472545623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3089275360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8603458404541</t>
   </si>
   <si>
     <t xml:space="preserve">18.3696784973145</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5893096923828</t>
+    <t xml:space="preserve">18.5893077850342</t>
   </si>
   <si>
     <t xml:space="preserve">18.0238723754883</t>
@@ -2102,28 +2102,28 @@
     <t xml:space="preserve">17.8603191375732</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0612564086914</t>
+    <t xml:space="preserve">18.0612602233887</t>
   </si>
   <si>
     <t xml:space="preserve">17.5986270904541</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0939674377441</t>
+    <t xml:space="preserve">18.0939693450928</t>
   </si>
   <si>
     <t xml:space="preserve">19.8603744506836</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0472965240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9071044921875</t>
+    <t xml:space="preserve">20.0472946166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9071025848389</t>
   </si>
   <si>
     <t xml:space="preserve">19.4607124328613</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9735870361328</t>
+    <t xml:space="preserve">19.9735889434814</t>
   </si>
   <si>
     <t xml:space="preserve">19.4132251739502</t>
@@ -2135,19 +2135,19 @@
     <t xml:space="preserve">19.4892063140869</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1187953948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2327690124512</t>
+    <t xml:space="preserve">19.1187973022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2327709197998</t>
   </si>
   <si>
     <t xml:space="preserve">18.9525890350342</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4397163391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7131443023682</t>
+    <t xml:space="preserve">18.4397144317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7131423950195</t>
   </si>
   <si>
     <t xml:space="preserve">17.7273902893066</t>
@@ -2156,19 +2156,19 @@
     <t xml:space="preserve">17.8318634033203</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3732299804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6534118652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1757850646973</t>
+    <t xml:space="preserve">18.3732318878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6534099578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1757831573486</t>
   </si>
   <si>
     <t xml:space="preserve">19.3657360076904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2802562713623</t>
+    <t xml:space="preserve">19.2802581787109</t>
   </si>
   <si>
     <t xml:space="preserve">19.2137718200684</t>
@@ -2198,22 +2198,22 @@
     <t xml:space="preserve">19.8026294708252</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7171497344971</t>
+    <t xml:space="preserve">19.7171478271484</t>
   </si>
   <si>
     <t xml:space="preserve">19.8121280670166</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7456436157227</t>
+    <t xml:space="preserve">19.7456455230713</t>
   </si>
   <si>
     <t xml:space="preserve">19.926097869873</t>
   </si>
   <si>
-    <t xml:space="preserve">20.135046005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1920337677002</t>
+    <t xml:space="preserve">20.1350479125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1920318603516</t>
   </si>
   <si>
     <t xml:space="preserve">20.4674644470215</t>
@@ -2222,13 +2222,13 @@
     <t xml:space="preserve">20.4864597320557</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2870101928711</t>
+    <t xml:space="preserve">20.2870121002197</t>
   </si>
   <si>
     <t xml:space="preserve">20.2775135040283</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8406200408936</t>
+    <t xml:space="preserve">19.8406181335449</t>
   </si>
   <si>
     <t xml:space="preserve">19.821626663208</t>
@@ -2237,10 +2237,10 @@
     <t xml:space="preserve">19.8501167297363</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9545917510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9071025848389</t>
+    <t xml:space="preserve">19.95458984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9071006774902</t>
   </si>
   <si>
     <t xml:space="preserve">19.8881092071533</t>
@@ -2249,13 +2249,13 @@
     <t xml:space="preserve">20.0305728912354</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8691139221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.96409034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0020790100098</t>
+    <t xml:space="preserve">19.8691120147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9640884399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0020809173584</t>
   </si>
   <si>
     <t xml:space="preserve">19.9450931549072</t>
@@ -2267,16 +2267,16 @@
     <t xml:space="preserve">18.0218181610107</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9315872192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5754261016846</t>
+    <t xml:space="preserve">17.9315891265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5754241943359</t>
   </si>
   <si>
     <t xml:space="preserve">17.2952442169189</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2762508392334</t>
+    <t xml:space="preserve">17.276252746582</t>
   </si>
   <si>
     <t xml:space="preserve">17.2667541503906</t>
@@ -2291,13 +2291,13 @@
     <t xml:space="preserve">16.8963451385498</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0150661468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5971660614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2837467193604</t>
+    <t xml:space="preserve">17.015064239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5971698760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2837448120117</t>
   </si>
   <si>
     <t xml:space="preserve">16.8108654022217</t>
@@ -2321,19 +2321,19 @@
     <t xml:space="preserve">16.9485816955566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7491321563721</t>
+    <t xml:space="preserve">16.7491302490234</t>
   </si>
   <si>
     <t xml:space="preserve">16.8441066741943</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4974422454834</t>
+    <t xml:space="preserve">16.497444152832</t>
   </si>
   <si>
     <t xml:space="preserve">16.6683979034424</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6304092407227</t>
+    <t xml:space="preserve">16.630407333374</t>
   </si>
   <si>
     <t xml:space="preserve">16.9248371124268</t>
@@ -2354,16 +2354,16 @@
     <t xml:space="preserve">17.5231895446777</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2857494354248</t>
+    <t xml:space="preserve">17.2857475280762</t>
   </si>
   <si>
     <t xml:space="preserve">17.2002696990967</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6968936920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7538795471191</t>
+    <t xml:space="preserve">16.696891784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7538776397705</t>
   </si>
   <si>
     <t xml:space="preserve">16.2267570495605</t>
@@ -2375,25 +2375,25 @@
     <t xml:space="preserve">16.1365299224854</t>
   </si>
   <si>
-    <t xml:space="preserve">16.34547996521</t>
+    <t xml:space="preserve">16.3454780578613</t>
   </si>
   <si>
     <t xml:space="preserve">16.1840190887451</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1032886505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0178108215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4811906814575</t>
+    <t xml:space="preserve">16.1032905578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0178089141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4811916351318</t>
   </si>
   <si>
     <t xml:space="preserve">15.538179397583</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5619230270386</t>
+    <t xml:space="preserve">15.5619211196899</t>
   </si>
   <si>
     <t xml:space="preserve">15.1725187301636</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">15.3577222824097</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5904159545898</t>
+    <t xml:space="preserve">15.5904169082642</t>
   </si>
   <si>
     <t xml:space="preserve">15.4716949462891</t>
@@ -2414,7 +2414,7 @@
     <t xml:space="preserve">15.680643081665</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4052095413208</t>
+    <t xml:space="preserve">15.4052104949951</t>
   </si>
   <si>
     <t xml:space="preserve">15.324481010437</t>
@@ -2432,37 +2432,37 @@
     <t xml:space="preserve">15.0680437088013</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0348014831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3197317123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.960823059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7661218643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8800916671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9085874557495</t>
+    <t xml:space="preserve">15.0348024368286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.319730758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9608240127563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7661228179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8800926208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9085865020752</t>
   </si>
   <si>
     <t xml:space="preserve">15.922833442688</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1412792205811</t>
+    <t xml:space="preserve">16.1412811279297</t>
   </si>
   <si>
     <t xml:space="preserve">16.1745204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4024658203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5781707763672</t>
+    <t xml:space="preserve">16.4024639129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5781726837158</t>
   </si>
   <si>
     <t xml:space="preserve">16.5734233856201</t>
@@ -2474,10 +2474,10 @@
     <t xml:space="preserve">17.2809982299805</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9723262786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4404563903809</t>
+    <t xml:space="preserve">16.9723281860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4404544830322</t>
   </si>
   <si>
     <t xml:space="preserve">16.3074893951416</t>
@@ -2489,7 +2489,7 @@
     <t xml:space="preserve">16.3977165222168</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6209106445312</t>
+    <t xml:space="preserve">16.6209125518799</t>
   </si>
   <si>
     <t xml:space="preserve">17.3047428131104</t>
@@ -2498,16 +2498,16 @@
     <t xml:space="preserve">17.1290378570557</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1860218048096</t>
+    <t xml:space="preserve">17.1860237121582</t>
   </si>
   <si>
     <t xml:space="preserve">16.6873950958252</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9695796966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1120452880859</t>
+    <t xml:space="preserve">17.9695816040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1120433807373</t>
   </si>
   <si>
     <t xml:space="preserve">17.4282131195068</t>
@@ -2528,10 +2528,10 @@
     <t xml:space="preserve">17.62766456604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5421829223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4804496765137</t>
+    <t xml:space="preserve">17.5421848297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4804515838623</t>
   </si>
   <si>
     <t xml:space="preserve">17.8033714294434</t>
@@ -2546,7 +2546,7 @@
     <t xml:space="preserve">17.8081207275391</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0028228759766</t>
+    <t xml:space="preserve">18.0028209686279</t>
   </si>
   <si>
     <t xml:space="preserve">17.6704025268555</t>
@@ -2555,19 +2555,19 @@
     <t xml:space="preserve">17.6229152679443</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6799030303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9885749816895</t>
+    <t xml:space="preserve">17.6799011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9885768890381</t>
   </si>
   <si>
     <t xml:space="preserve">18.4207191467285</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0930480957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.90309715271</t>
+    <t xml:space="preserve">18.0930500030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9030952453613</t>
   </si>
   <si>
     <t xml:space="preserve">17.8508586883545</t>
@@ -2588,82 +2588,82 @@
     <t xml:space="preserve">16.6161632537842</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5924186706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8611001968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2694969177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2979927062988</t>
+    <t xml:space="preserve">16.5924167633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8610982894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2694988250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2979907989502</t>
   </si>
   <si>
     <t xml:space="preserve">16.1175346374512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8468503952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3217353820801</t>
+    <t xml:space="preserve">15.8468523025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3217334747314</t>
   </si>
   <si>
     <t xml:space="preserve">16.0842933654785</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7803688049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7186326980591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3434772491455</t>
+    <t xml:space="preserve">15.780366897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7186336517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3434762954712</t>
   </si>
   <si>
     <t xml:space="preserve">15.9845676422119</t>
   </si>
   <si>
-    <t xml:space="preserve">15.747127532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.604660987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7043857574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8848428726196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5429267883301</t>
+    <t xml:space="preserve">15.7471265792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6046619415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7043876647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8848447799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5429258346558</t>
   </si>
   <si>
     <t xml:space="preserve">15.1582717895508</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8096036911011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8665895462036</t>
+    <t xml:space="preserve">13.8096027374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8665885925293</t>
   </si>
   <si>
     <t xml:space="preserve">14.1420221328735</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6054039001465</t>
+    <t xml:space="preserve">13.6054029464722</t>
   </si>
   <si>
     <t xml:space="preserve">13.5721616744995</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0735340118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0497894287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9738092422485</t>
+    <t xml:space="preserve">13.0735349655151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0497903823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9738082885742</t>
   </si>
   <si>
     <t xml:space="preserve">12.3184700012207</t>
@@ -2672,10 +2672,10 @@
     <t xml:space="preserve">12.0477876663208</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2784757614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6563787460327</t>
+    <t xml:space="preserve">11.2784767150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.656379699707</t>
   </si>
   <si>
     <t xml:space="preserve">10.7845964431763</t>
@@ -2702,7 +2702,7 @@
     <t xml:space="preserve">11.8625812530518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1665077209473</t>
+    <t xml:space="preserve">12.1665086746216</t>
   </si>
   <si>
     <t xml:space="preserve">13.0877799987793</t>
@@ -2711,7 +2711,7 @@
     <t xml:space="preserve">13.3964548110962</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9690599441528</t>
+    <t xml:space="preserve">12.9690589904785</t>
   </si>
   <si>
     <t xml:space="preserve">12.2519865036011</t>
@@ -2723,16 +2723,16 @@
     <t xml:space="preserve">11.4921731948853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2072439193726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1597547531128</t>
+    <t xml:space="preserve">11.2072429656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1597557067871</t>
   </si>
   <si>
     <t xml:space="preserve">11.1882476806641</t>
   </si>
   <si>
-    <t xml:space="preserve">11.568154335022</t>
+    <t xml:space="preserve">11.5681552886963</t>
   </si>
   <si>
     <t xml:space="preserve">11.5586566925049</t>
@@ -2750,13 +2750,13 @@
     <t xml:space="preserve">11.2927227020264</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5396604537964</t>
+    <t xml:space="preserve">11.5396614074707</t>
   </si>
   <si>
     <t xml:space="preserve">10.8178396224976</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3999423980713</t>
+    <t xml:space="preserve">10.399941444397</t>
   </si>
   <si>
     <t xml:space="preserve">10.4474306106567</t>
@@ -2765,16 +2765,16 @@
     <t xml:space="preserve">10.3809471130371</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7323608398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9128150939941</t>
+    <t xml:space="preserve">10.7323598861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9128160476685</t>
   </si>
   <si>
     <t xml:space="preserve">10.7228622436523</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3049659729004</t>
+    <t xml:space="preserve">10.3049650192261</t>
   </si>
   <si>
     <t xml:space="preserve">10.3524532318115</t>
@@ -2783,13 +2783,13 @@
     <t xml:space="preserve">10.3144626617432</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3429565429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4094390869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2574768066406</t>
+    <t xml:space="preserve">10.3429555892944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4094400405884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2574777603149</t>
   </si>
   <si>
     <t xml:space="preserve">10.0295333862305</t>
@@ -2798,10 +2798,10 @@
     <t xml:space="preserve">9.9060640335083</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89656639099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64962673187256</t>
+    <t xml:space="preserve">9.89656543731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64962577819824</t>
   </si>
   <si>
     <t xml:space="preserve">9.78259372711182</t>
@@ -2810,7 +2810,7 @@
     <t xml:space="preserve">10.4949188232422</t>
   </si>
   <si>
-    <t xml:space="preserve">12.346962928772</t>
+    <t xml:space="preserve">12.3469619750977</t>
   </si>
   <si>
     <t xml:space="preserve">11.9005727767944</t>
@@ -2840,16 +2840,16 @@
     <t xml:space="preserve">11.8815774917603</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7771024703979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0620336532593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1190195083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2899770736694</t>
+    <t xml:space="preserve">11.7771034240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.062032699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1190185546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2899761199951</t>
   </si>
   <si>
     <t xml:space="preserve">12.3089723587036</t>
@@ -2858,22 +2858,22 @@
     <t xml:space="preserve">12.7078742980957</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5749073028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5844049453735</t>
+    <t xml:space="preserve">12.5749063491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5844039916992</t>
   </si>
   <si>
     <t xml:space="preserve">11.9955492019653</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8055953979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5111684799194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7296152114868</t>
+    <t xml:space="preserve">11.8055963516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5111694335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7296142578125</t>
   </si>
   <si>
     <t xml:space="preserve">11.4446849822998</t>
@@ -2882,10 +2882,10 @@
     <t xml:space="preserve">11.5206661224365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7581071853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5871486663818</t>
+    <t xml:space="preserve">11.7581081390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5871496200562</t>
   </si>
   <si>
     <t xml:space="preserve">11.4826755523682</t>
@@ -2897,13 +2897,13 @@
     <t xml:space="preserve">10.9887971878052</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1787519454956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2262382507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2452335357666</t>
+    <t xml:space="preserve">11.1787509918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2262372970581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2452344894409</t>
   </si>
   <si>
     <t xml:space="preserve">11.1027679443359</t>
@@ -2912,13 +2912,13 @@
     <t xml:space="preserve">11.1312618255615</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0267868041992</t>
+    <t xml:space="preserve">11.0267877578735</t>
   </si>
   <si>
     <t xml:space="preserve">11.0837736129761</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8368349075317</t>
+    <t xml:space="preserve">10.8368339538574</t>
   </si>
   <si>
     <t xml:space="preserve">11.0552806854248</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">11.2167415618896</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5708999633789</t>
+    <t xml:space="preserve">10.5708990097046</t>
   </si>
   <si>
     <t xml:space="preserve">10.580397605896</t>
@@ -2948,10 +2948,10 @@
     <t xml:space="preserve">11.0932712554932</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9603052139282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7608528137207</t>
+    <t xml:space="preserve">10.9603033065796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.760853767395</t>
   </si>
   <si>
     <t xml:space="preserve">10.7798490524292</t>
@@ -2960,13 +2960,13 @@
     <t xml:space="preserve">10.6753740310669</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6156425476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.463680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3971967697144</t>
+    <t xml:space="preserve">11.6156415939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4636793136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3971977233887</t>
   </si>
   <si>
     <t xml:space="preserve">11.5016708374023</t>
@@ -2987,22 +2987,22 @@
     <t xml:space="preserve">12.565408706665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0810289382935</t>
+    <t xml:space="preserve">12.0810279846191</t>
   </si>
   <si>
     <t xml:space="preserve">11.6821269989014</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6061458587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1095218658447</t>
+    <t xml:space="preserve">11.6061449050903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1095209121704</t>
   </si>
   <si>
     <t xml:space="preserve">12.0145444869995</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9385633468628</t>
+    <t xml:space="preserve">11.9385623931885</t>
   </si>
   <si>
     <t xml:space="preserve">11.957558631897</t>
@@ -3011,7 +3011,7 @@
     <t xml:space="preserve">11.9860515594482</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1285171508789</t>
+    <t xml:space="preserve">12.1285181045532</t>
   </si>
   <si>
     <t xml:space="preserve">12.2804803848267</t>
@@ -3023,10 +3023,10 @@
     <t xml:space="preserve">12.6034002304077</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5464134216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2044973373413</t>
+    <t xml:space="preserve">12.5464143753052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2044982910156</t>
   </si>
   <si>
     <t xml:space="preserve">12.4039497375488</t>
@@ -3041,7 +3041,7 @@
     <t xml:space="preserve">11.8910760879517</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6726293563843</t>
+    <t xml:space="preserve">11.67262840271</t>
   </si>
   <si>
     <t xml:space="preserve">11.3117170333862</t>
@@ -3050,10 +3050,10 @@
     <t xml:space="preserve">10.6943693161011</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5139141082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7988433837891</t>
+    <t xml:space="preserve">10.5139131546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7988443374634</t>
   </si>
   <si>
     <t xml:space="preserve">11.0647783279419</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">13.7146253585815</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9235754013062</t>
+    <t xml:space="preserve">13.9235744476318</t>
   </si>
   <si>
     <t xml:space="preserve">13.9330730438232</t>
@@ -3092,28 +3092,28 @@
     <t xml:space="preserve">14.0470447540283</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6264009475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3129796981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1515188217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2464962005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4269514083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4649419784546</t>
+    <t xml:space="preserve">14.6264019012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3129787445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1515197753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2464952468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4269504547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4649410247803</t>
   </si>
   <si>
     <t xml:space="preserve">14.9113321304321</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4934358596802</t>
+    <t xml:space="preserve">14.4934349060059</t>
   </si>
   <si>
     <t xml:space="preserve">14.3509693145752</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">14.8828401565552</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8543472290039</t>
+    <t xml:space="preserve">14.8543462753296</t>
   </si>
   <si>
     <t xml:space="preserve">14.7593698501587</t>
@@ -3140,7 +3140,7 @@
     <t xml:space="preserve">14.3794631958008</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5694160461426</t>
+    <t xml:space="preserve">14.5694169998169</t>
   </si>
   <si>
     <t xml:space="preserve">14.6453981399536</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">14.6074066162109</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1107835769653</t>
+    <t xml:space="preserve">15.110782623291</t>
   </si>
   <si>
     <t xml:space="preserve">15.0632944107056</t>
@@ -3158,10 +3158,10 @@
     <t xml:space="preserve">14.9493227005005</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7688674926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7118816375732</t>
+    <t xml:space="preserve">14.7688684463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7118806838989</t>
   </si>
   <si>
     <t xml:space="preserve">14.5884113311768</t>
@@ -3170,13 +3170,13 @@
     <t xml:space="preserve">14.5789136886597</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4079551696777</t>
+    <t xml:space="preserve">14.4079561233521</t>
   </si>
   <si>
     <t xml:space="preserve">14.5504207611084</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5314254760742</t>
+    <t xml:space="preserve">14.5314264297485</t>
   </si>
   <si>
     <t xml:space="preserve">13.9615650177002</t>
@@ -3200,10 +3200,10 @@
     <t xml:space="preserve">15.8041114807129</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6711444854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2627449035645</t>
+    <t xml:space="preserve">15.6711454391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2627458572388</t>
   </si>
   <si>
     <t xml:space="preserve">14.9588203430176</t>
@@ -3215,10 +3215,10 @@
     <t xml:space="preserve">14.721378326416</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6359004974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4364500045776</t>
+    <t xml:space="preserve">14.6358995437622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4364490509033</t>
   </si>
   <si>
     <t xml:space="preserve">14.7403745651245</t>
@@ -3227,79 +3227,79 @@
     <t xml:space="preserve">15.006308555603</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0822906494141</t>
+    <t xml:space="preserve">15.0822896957397</t>
   </si>
   <si>
     <t xml:space="preserve">14.9778165817261</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6928863525391</t>
+    <t xml:space="preserve">14.6928853988647</t>
   </si>
   <si>
     <t xml:space="preserve">14.7783651351929</t>
   </si>
   <si>
-    <t xml:space="preserve">14.825852394104</t>
+    <t xml:space="preserve">14.8258533477783</t>
   </si>
   <si>
     <t xml:space="preserve">15.2057600021362</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1202812194824</t>
+    <t xml:space="preserve">15.1202802658081</t>
   </si>
   <si>
     <t xml:space="preserve">15.0917882919312</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1012859344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8448476791382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9873132705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8705949783325</t>
+    <t xml:space="preserve">15.1012849807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8448486328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9873123168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8705940246582</t>
   </si>
   <si>
     <t xml:space="preserve">16.0225601196289</t>
   </si>
   <si>
-    <t xml:space="preserve">16.032054901123</t>
+    <t xml:space="preserve">16.0320568084717</t>
   </si>
   <si>
     <t xml:space="preserve">15.8231077194214</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9370803833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7376289367676</t>
+    <t xml:space="preserve">15.9370794296265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7376298904419</t>
   </si>
   <si>
     <t xml:space="preserve">15.4906892776489</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7091369628906</t>
+    <t xml:space="preserve">15.7091379165649</t>
   </si>
   <si>
     <t xml:space="preserve">15.3102350234985</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3672208786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3387260437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6996393203735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6853904724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6189069747925</t>
+    <t xml:space="preserve">15.3672199249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3387269973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6996374130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6853914260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6189079284668</t>
   </si>
   <si>
     <t xml:space="preserve">15.428955078125</t>
@@ -3311,28 +3311,28 @@
     <t xml:space="preserve">16.739631652832</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8678512573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8725986480713</t>
+    <t xml:space="preserve">16.8678493499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8726005554199</t>
   </si>
   <si>
     <t xml:space="preserve">16.4784469604492</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0340576171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.513692855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4567031860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0388088226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2904987335205</t>
+    <t xml:space="preserve">17.0340595245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5136947631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4567070007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0388107299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2904968261719</t>
   </si>
   <si>
     <t xml:space="preserve">17.0815467834473</t>
@@ -3350,7 +3350,7 @@
     <t xml:space="preserve">17.4614543914795</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4187164306641</t>
+    <t xml:space="preserve">17.4187145233154</t>
   </si>
   <si>
     <t xml:space="preserve">18.2117691040039</t>
@@ -3359,13 +3359,13 @@
     <t xml:space="preserve">18.3589839935303</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1975250244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1500377655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2307662963867</t>
+    <t xml:space="preserve">18.1975231170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1500358581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2307643890381</t>
   </si>
   <si>
     <t xml:space="preserve">18.0360641479492</t>
@@ -3374,19 +3374,19 @@
     <t xml:space="preserve">17.9125938415527</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9553337097168</t>
+    <t xml:space="preserve">17.9553356170654</t>
   </si>
   <si>
     <t xml:space="preserve">17.6846504211426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0408134460449</t>
+    <t xml:space="preserve">18.0408115386963</t>
   </si>
   <si>
     <t xml:space="preserve">18.3304901123047</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3209934234619</t>
+    <t xml:space="preserve">18.3209953308105</t>
   </si>
   <si>
     <t xml:space="preserve">18.368480682373</t>
@@ -3395,10 +3395,10 @@
     <t xml:space="preserve">18.3019981384277</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3542346954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3969745635986</t>
+    <t xml:space="preserve">18.3542366027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3969764709473</t>
   </si>
   <si>
     <t xml:space="preserve">18.5299415588379</t>
@@ -3413,7 +3413,7 @@
     <t xml:space="preserve">18.1832790374756</t>
   </si>
   <si>
-    <t xml:space="preserve">18.444465637207</t>
+    <t xml:space="preserve">18.4444618225098</t>
   </si>
   <si>
     <t xml:space="preserve">18.8956031799316</t>
@@ -3422,28 +3422,28 @@
     <t xml:space="preserve">18.6961498260498</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5584373474121</t>
+    <t xml:space="preserve">18.5584354400635</t>
   </si>
   <si>
     <t xml:space="preserve">18.3352394104004</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8461093902588</t>
+    <t xml:space="preserve">17.8461112976074</t>
   </si>
   <si>
     <t xml:space="preserve">17.1527805328369</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1812744140625</t>
+    <t xml:space="preserve">17.1812725067139</t>
   </si>
   <si>
     <t xml:space="preserve">17.0673007965088</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1575317382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6114120483398</t>
+    <t xml:space="preserve">17.1575298309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6114139556885</t>
   </si>
   <si>
     <t xml:space="preserve">16.5021896362305</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">16.7253875732422</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8773498535156</t>
+    <t xml:space="preserve">16.877347946167</t>
   </si>
   <si>
     <t xml:space="preserve">16.4214611053467</t>
@@ -3461,10 +3461,10 @@
     <t xml:space="preserve">15.9798202514648</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0985412597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0083122253418</t>
+    <t xml:space="preserve">16.098539352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0083103179932</t>
   </si>
   <si>
     <t xml:space="preserve">16.2505035400391</t>
@@ -3479,10 +3479,10 @@
     <t xml:space="preserve">16.0463027954102</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0368061065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9988136291504</t>
+    <t xml:space="preserve">16.0368041992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9988145828247</t>
   </si>
   <si>
     <t xml:space="preserve">16.2600021362305</t>
@@ -3494,13 +3494,13 @@
     <t xml:space="preserve">16.0510520935059</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1100406646729</t>
+    <t xml:space="preserve">17.1100425720215</t>
   </si>
   <si>
     <t xml:space="preserve">17.3949718475342</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4919528961182</t>
+    <t xml:space="preserve">18.4919509887695</t>
   </si>
   <si>
     <t xml:space="preserve">17.5896739959717</t>
@@ -3509,7 +3509,7 @@
     <t xml:space="preserve">17.6609058380127</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0008163452148</t>
+    <t xml:space="preserve">17.0008182525635</t>
   </si>
   <si>
     <t xml:space="preserve">16.6731491088867</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">15.7328805923462</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7423791885376</t>
+    <t xml:space="preserve">15.7423782348633</t>
   </si>
   <si>
     <t xml:space="preserve">16.1460285186768</t>
@@ -3530,7 +3530,7 @@
     <t xml:space="preserve">15.9275808334351</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9703235626221</t>
+    <t xml:space="preserve">15.9703216552734</t>
   </si>
   <si>
     <t xml:space="preserve">16.6541538238525</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">18.0123195648193</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8698539733887</t>
+    <t xml:space="preserve">17.8698558807373</t>
   </si>
   <si>
     <t xml:space="preserve">18.0693054199219</t>
@@ -3554,25 +3554,25 @@
     <t xml:space="preserve">16.8251113891602</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7206382751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9628276824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9438323974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8298606872559</t>
+    <t xml:space="preserve">16.7206363677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9628295898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9438304901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8298587799072</t>
   </si>
   <si>
     <t xml:space="preserve">16.9913196563721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8346099853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0435581207275</t>
+    <t xml:space="preserve">16.8346118927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0435562133789</t>
   </si>
   <si>
     <t xml:space="preserve">16.8013687133789</t>
@@ -3593,7 +3593,7 @@
     <t xml:space="preserve">17.4662036895752</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7178916931152</t>
+    <t xml:space="preserve">17.7178936004639</t>
   </si>
   <si>
     <t xml:space="preserve">17.7748775482178</t>
@@ -3608,13 +3608,13 @@
     <t xml:space="preserve">18.7009010314941</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7911262512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9715843200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9458351135254</t>
+    <t xml:space="preserve">18.7911281585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9715824127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.945837020874</t>
   </si>
   <si>
     <t xml:space="preserve">18.4302177429199</t>
@@ -3629,13 +3629,13 @@
     <t xml:space="preserve">19.0903053283691</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3752346038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9240951538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1662845611572</t>
+    <t xml:space="preserve">19.3752326965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.92409324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1662864685059</t>
   </si>
   <si>
     <t xml:space="preserve">19.4037265777588</t>
@@ -3647,19 +3647,19 @@
     <t xml:space="preserve">19.6221733093262</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1377925872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6316699981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4579696655273</t>
+    <t xml:space="preserve">19.1377906799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6316719055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4579677581787</t>
   </si>
   <si>
     <t xml:space="preserve">20.6289253234863</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0373268127441</t>
+    <t xml:space="preserve">21.0373249053955</t>
   </si>
   <si>
     <t xml:space="preserve">21.4457244873047</t>
@@ -3674,22 +3674,22 @@
     <t xml:space="preserve">20.6384220123291</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1635417938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0970554351807</t>
+    <t xml:space="preserve">20.1635398864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0970573425293</t>
   </si>
   <si>
     <t xml:space="preserve">20.7903861999512</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7144050598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0278282165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0183277130127</t>
+    <t xml:space="preserve">20.7144031524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0278263092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0183296203613</t>
   </si>
   <si>
     <t xml:space="preserve">21.094310760498</t>
@@ -3710,10 +3710,10 @@
     <t xml:space="preserve">22.0820693969727</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5976867675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6261825561523</t>
+    <t xml:space="preserve">21.5976886749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6261806488037</t>
   </si>
   <si>
     <t xml:space="preserve">19.4797096252441</t>
@@ -3731,10 +3731,10 @@
     <t xml:space="preserve">18.7103977203369</t>
   </si>
   <si>
-    <t xml:space="preserve">18.055061340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4946956634521</t>
+    <t xml:space="preserve">18.0550594329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4946975708008</t>
   </si>
   <si>
     <t xml:space="preserve">18.2212677001953</t>
@@ -3743,19 +3743,19 @@
     <t xml:space="preserve">17.9743270874023</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5916767120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5394420623779</t>
+    <t xml:space="preserve">18.5916786193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5394401550293</t>
   </si>
   <si>
     <t xml:space="preserve">18.0977993011475</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0503101348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2830009460449</t>
+    <t xml:space="preserve">18.0503082275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2830047607422</t>
   </si>
   <si>
     <t xml:space="preserve">18.1927757263184</t>
@@ -3776,52 +3776,52 @@
     <t xml:space="preserve">18.8006248474121</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5964260101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7768802642822</t>
+    <t xml:space="preserve">18.5964241027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7768821716309</t>
   </si>
   <si>
     <t xml:space="preserve">17.9220924377441</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6581592559814</t>
+    <t xml:space="preserve">18.6581611633301</t>
   </si>
   <si>
     <t xml:space="preserve">18.4492111206055</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6324157714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7368869781494</t>
+    <t xml:space="preserve">17.6324138641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7368850708008</t>
   </si>
   <si>
     <t xml:space="preserve">17.12428855896</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1867637634277</t>
+    <t xml:space="preserve">15.1867647171021</t>
   </si>
   <si>
     <t xml:space="preserve">14.8306016921997</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5076808929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9133329391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3529748916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.457447052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8733415603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5856666564941</t>
+    <t xml:space="preserve">14.5076818466187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9133348464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3529739379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4574480056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8733406066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5856657028198</t>
   </si>
   <si>
     <t xml:space="preserve">15.81360912323</t>
@@ -3833,22 +3833,22 @@
     <t xml:space="preserve">15.2390012741089</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2532472610474</t>
+    <t xml:space="preserve">15.253246307373</t>
   </si>
   <si>
     <t xml:space="preserve">15.5191831588745</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8278579711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7681274414062</t>
+    <t xml:space="preserve">15.82785987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7681255340576</t>
   </si>
   <si>
     <t xml:space="preserve">16.316987991333</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9750709533691</t>
+    <t xml:space="preserve">15.9750719070435</t>
   </si>
   <si>
     <t xml:space="preserve">15.0253038406372</t>
@@ -3857,13 +3857,13 @@
     <t xml:space="preserve">15.6331539154053</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6521482467651</t>
+    <t xml:space="preserve">15.6521492004395</t>
   </si>
   <si>
     <t xml:space="preserve">15.8895902633667</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5096845626831</t>
+    <t xml:space="preserve">15.5096855163574</t>
   </si>
   <si>
     <t xml:space="preserve">14.7308769226074</t>
@@ -3875,7 +3875,7 @@
     <t xml:space="preserve">15.1392755508423</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7851181030273</t>
+    <t xml:space="preserve">15.7851190567017</t>
   </si>
   <si>
     <t xml:space="preserve">14.3034820556641</t>
@@ -3884,7 +3884,7 @@
     <t xml:space="preserve">14.3224773406982</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8285989761353</t>
+    <t xml:space="preserve">13.8285980224609</t>
   </si>
   <si>
     <t xml:space="preserve">12.8123483657837</t>
@@ -3893,10 +3893,10 @@
     <t xml:space="preserve">14.1040306091309</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1990079879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0158061981201</t>
+    <t xml:space="preserve">14.1990070343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0158071517944</t>
   </si>
   <si>
     <t xml:space="preserve">14.5219278335571</t>
@@ -6009,6 +6009,9 @@
   </si>
   <si>
     <t xml:space="preserve">7.65500020980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69999980926514</t>
   </si>
 </sst>
 </file>
@@ -71815,7 +71818,7 @@
     </row>
     <row r="2519">
       <c r="A2519" s="1" t="n">
-        <v>45986.6910532407</v>
+        <v>45986.3333333333</v>
       </c>
       <c r="B2519" t="n">
         <v>267612</v>
@@ -71836,6 +71839,32 @@
         <v>1998</v>
       </c>
       <c r="H2519" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2520">
+      <c r="A2520" s="1" t="n">
+        <v>45987.6909722222</v>
+      </c>
+      <c r="B2520" t="n">
+        <v>298767</v>
+      </c>
+      <c r="C2520" t="n">
+        <v>7.81500005722046</v>
+      </c>
+      <c r="D2520" t="n">
+        <v>7.64499998092651</v>
+      </c>
+      <c r="E2520" t="n">
+        <v>7.71500015258789</v>
+      </c>
+      <c r="F2520" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="G2520" t="s">
+        <v>1999</v>
+      </c>
+      <c r="H2520" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2003" uniqueCount="2003">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2004" uniqueCount="2004">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,22 +44,22 @@
     <t xml:space="preserve">SFER.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">18.01096534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4978828430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9401931762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.683650970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2498092651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4086723327637</t>
+    <t xml:space="preserve">18.0109634399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4978809356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9401950836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6836528778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2498111724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4086742401123</t>
   </si>
   <si>
     <t xml:space="preserve">19.1344356536865</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">18.8425102233887</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4621238708496</t>
+    <t xml:space="preserve">18.462121963501</t>
   </si>
   <si>
     <t xml:space="preserve">18.2851963043213</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">18.0994243621826</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6394214630127</t>
+    <t xml:space="preserve">17.6394195556641</t>
   </si>
   <si>
     <t xml:space="preserve">17.5686531066895</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">18.1878871917725</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4798164367676</t>
+    <t xml:space="preserve">18.4798145294189</t>
   </si>
   <si>
     <t xml:space="preserve">18.223274230957</t>
@@ -95,16 +95,16 @@
     <t xml:space="preserve">17.7632694244385</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3913536071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6744346618652</t>
+    <t xml:space="preserve">18.3913516998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6744327545166</t>
   </si>
   <si>
     <t xml:space="preserve">17.9578857421875</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2055835723877</t>
+    <t xml:space="preserve">18.2055816650391</t>
   </si>
   <si>
     <t xml:space="preserve">18.258659362793</t>
@@ -113,13 +113,13 @@
     <t xml:space="preserve">18.0817337036133</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3563442230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9051818847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1617202758789</t>
+    <t xml:space="preserve">17.3563423156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9051837921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1617221832275</t>
   </si>
   <si>
     <t xml:space="preserve">16.6486415863037</t>
@@ -128,28 +128,28 @@
     <t xml:space="preserve">17.0201835632324</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4890365600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6305732727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4090442657471</t>
+    <t xml:space="preserve">17.4890384674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6305751800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4090461730957</t>
   </si>
   <si>
     <t xml:space="preserve">18.453275680542</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9752063751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1348152160645</t>
+    <t xml:space="preserve">18.9752044677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1348114013672</t>
   </si>
   <si>
     <t xml:space="preserve">17.3121089935303</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9048099517822</t>
+    <t xml:space="preserve">17.9048080444336</t>
   </si>
   <si>
     <t xml:space="preserve">18.3471202850342</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">19.0194358825684</t>
   </si>
   <si>
-    <t xml:space="preserve">19.001745223999</t>
+    <t xml:space="preserve">19.0017433166504</t>
   </si>
   <si>
     <t xml:space="preserve">18.8513584136963</t>
@@ -173,16 +173,16 @@
     <t xml:space="preserve">19.9482917785645</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7271366119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3379001617432</t>
+    <t xml:space="preserve">19.7271347045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3379020690918</t>
   </si>
   <si>
     <t xml:space="preserve">19.6475200653076</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9836769104004</t>
+    <t xml:space="preserve">19.9836750030518</t>
   </si>
   <si>
     <t xml:space="preserve">19.1167449951172</t>
@@ -194,13 +194,13 @@
     <t xml:space="preserve">20.0367546081543</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1782913208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4971370697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4705963134766</t>
+    <t xml:space="preserve">20.1782970428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4971351623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4705944061279</t>
   </si>
   <si>
     <t xml:space="preserve">18.9663600921631</t>
@@ -209,22 +209,22 @@
     <t xml:space="preserve">19.4794445037842</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9129085540771</t>
+    <t xml:space="preserve">19.9129066467285</t>
   </si>
   <si>
     <t xml:space="preserve">19.8686752319336</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4175186157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8690528869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.833667755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5151996612549</t>
+    <t xml:space="preserve">19.417516708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8690509796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8336658477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5152015686035</t>
   </si>
   <si>
     <t xml:space="preserve">18.9309730529785</t>
@@ -233,76 +233,76 @@
     <t xml:space="preserve">18.8955898284912</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5240440368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9486656188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.798282623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8778953552246</t>
+    <t xml:space="preserve">18.5240459442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9486637115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7982807159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8778972625732</t>
   </si>
   <si>
     <t xml:space="preserve">19.2936706542969</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8071250915527</t>
+    <t xml:space="preserve">18.8071269989014</t>
   </si>
   <si>
     <t xml:space="preserve">18.3205814361572</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3648166656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8251914978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0640411376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3117370605469</t>
+    <t xml:space="preserve">18.3648147583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8251934051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0640392303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3117389678955</t>
   </si>
   <si>
     <t xml:space="preserve">17.878267288208</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0021171569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7190361022949</t>
+    <t xml:space="preserve">18.0021209716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7190380096436</t>
   </si>
   <si>
     <t xml:space="preserve">17.4448051452637</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1440315246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5509586334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9844264984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4182662963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9313488006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7367305755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6482677459717</t>
+    <t xml:space="preserve">17.1440296173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5509567260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9844284057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4182643890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9313468933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7367267608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6482696533203</t>
   </si>
   <si>
     <t xml:space="preserve">17.593936920166</t>
   </si>
   <si>
-    <t xml:space="preserve">17.81125831604</t>
+    <t xml:space="preserve">17.8112564086914</t>
   </si>
   <si>
     <t xml:space="preserve">17.7025985717773</t>
@@ -317,10 +317,10 @@
     <t xml:space="preserve">17.304178237915</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4762229919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4309482574463</t>
+    <t xml:space="preserve">17.4762191772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.430944442749</t>
   </si>
   <si>
     <t xml:space="preserve">17.4852752685547</t>
@@ -329,34 +329,34 @@
     <t xml:space="preserve">17.747875213623</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6844902038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1502380371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7155990600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5435543060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0415782928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0778007507324</t>
+    <t xml:space="preserve">17.6844882965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.150239944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.71559715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5435523986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0415802001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0778026580811</t>
   </si>
   <si>
     <t xml:space="preserve">17.8384246826172</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9380302429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7297630310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8655872344971</t>
+    <t xml:space="preserve">17.9380283355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7297611236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8655891418457</t>
   </si>
   <si>
     <t xml:space="preserve">18.1825141906738</t>
@@ -368,10 +368,10 @@
     <t xml:space="preserve">16.3896198272705</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6793785095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.262845993042</t>
+    <t xml:space="preserve">16.6793804168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2628440856934</t>
   </si>
   <si>
     <t xml:space="preserve">16.5254440307617</t>
@@ -383,37 +383,37 @@
     <t xml:space="preserve">16.8061504364014</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8242588043213</t>
+    <t xml:space="preserve">16.8242607116699</t>
   </si>
   <si>
     <t xml:space="preserve">16.0726909637451</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8734798431396</t>
+    <t xml:space="preserve">15.8734817504883</t>
   </si>
   <si>
     <t xml:space="preserve">16.3624496459961</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4439487457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.69748878479</t>
+    <t xml:space="preserve">16.4439468383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6974868774414</t>
   </si>
   <si>
     <t xml:space="preserve">17.0959091186523</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1321296691895</t>
+    <t xml:space="preserve">17.1321315765381</t>
   </si>
   <si>
     <t xml:space="preserve">17.086856842041</t>
   </si>
   <si>
-    <t xml:space="preserve">17.032527923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3403949737549</t>
+    <t xml:space="preserve">17.0325241088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3403968811035</t>
   </si>
   <si>
     <t xml:space="preserve">17.9018096923828</t>
@@ -422,7 +422,7 @@
     <t xml:space="preserve">18.1372413635254</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9289703369141</t>
+    <t xml:space="preserve">17.9289722442627</t>
   </si>
   <si>
     <t xml:space="preserve">18.7710914611816</t>
@@ -431,16 +431,16 @@
     <t xml:space="preserve">18.6352672576904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0699100494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2147884368896</t>
+    <t xml:space="preserve">19.0699081420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2147903442383</t>
   </si>
   <si>
     <t xml:space="preserve">18.6262111663818</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4994430541992</t>
+    <t xml:space="preserve">18.499439239502</t>
   </si>
   <si>
     <t xml:space="preserve">18.2187347412109</t>
@@ -452,28 +452,28 @@
     <t xml:space="preserve">18.5809364318848</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7620391845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8073120117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.94313621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0427436828613</t>
+    <t xml:space="preserve">18.7620372772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8073139190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9431343078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.04274559021</t>
   </si>
   <si>
     <t xml:space="preserve">18.6624298095703</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4722747802734</t>
+    <t xml:space="preserve">18.4722766876221</t>
   </si>
   <si>
     <t xml:space="preserve">18.6171550750732</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7529811859131</t>
+    <t xml:space="preserve">18.7529830932617</t>
   </si>
   <si>
     <t xml:space="preserve">18.9703044891357</t>
@@ -482,10 +482,10 @@
     <t xml:space="preserve">18.6805400848389</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6081008911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6533794403076</t>
+    <t xml:space="preserve">18.6080989837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6533756256104</t>
   </si>
   <si>
     <t xml:space="preserve">18.5175514221191</t>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">19.1061267852783</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9210815429688</t>
+    <t xml:space="preserve">19.9210834503174</t>
   </si>
   <si>
     <t xml:space="preserve">19.6947059631348</t>
@@ -509,19 +509,19 @@
     <t xml:space="preserve">19.5588817596436</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4592742919922</t>
+    <t xml:space="preserve">19.4592723846436</t>
   </si>
   <si>
     <t xml:space="preserve">19.3143939971924</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8888072967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1332931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.160457611084</t>
+    <t xml:space="preserve">18.8888053894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1332912445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1604595184326</t>
   </si>
   <si>
     <t xml:space="preserve">19.9391937255859</t>
@@ -530,28 +530,28 @@
     <t xml:space="preserve">20.4553279876709</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3557224273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3104496002197</t>
+    <t xml:space="preserve">20.3557205200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3104476928711</t>
   </si>
   <si>
     <t xml:space="preserve">20.3919429779053</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4643859863281</t>
+    <t xml:space="preserve">20.4643840789795</t>
   </si>
   <si>
     <t xml:space="preserve">20.6907596588135</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8446941375732</t>
+    <t xml:space="preserve">20.8446960449219</t>
   </si>
   <si>
     <t xml:space="preserve">20.7994194030762</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4009971618652</t>
+    <t xml:space="preserve">20.4010009765625</t>
   </si>
   <si>
     <t xml:space="preserve">20.1021842956543</t>
@@ -563,55 +563,55 @@
     <t xml:space="preserve">20.3647785186768</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5458793640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7541446685791</t>
+    <t xml:space="preserve">20.5458812713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7541465759277</t>
   </si>
   <si>
     <t xml:space="preserve">20.4191074371338</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0116329193115</t>
+    <t xml:space="preserve">20.0116310119629</t>
   </si>
   <si>
     <t xml:space="preserve">20.265172958374</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3285598754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0387954711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1474571228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2289524078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5006046295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5639877319336</t>
+    <t xml:space="preserve">20.3285617828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.03879737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1474590301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2289543151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.500602722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5639896392822</t>
   </si>
   <si>
     <t xml:space="preserve">20.1836795806885</t>
   </si>
   <si>
-    <t xml:space="preserve">19.549825668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4139995574951</t>
+    <t xml:space="preserve">19.5498275756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4140014648438</t>
   </si>
   <si>
     <t xml:space="preserve">19.5045490264893</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7218704223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7943115234375</t>
+    <t xml:space="preserve">19.7218685150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7943096160889</t>
   </si>
   <si>
     <t xml:space="preserve">19.5226593017578</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">19.7490367889404</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0919628143311</t>
+    <t xml:space="preserve">18.0919647216797</t>
   </si>
   <si>
     <t xml:space="preserve">18.3002281188965</t>
@@ -635,10 +635,10 @@
     <t xml:space="preserve">18.327392578125</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2458992004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0104675292969</t>
+    <t xml:space="preserve">18.2459011077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0104694366455</t>
   </si>
   <si>
     <t xml:space="preserve">17.7388172149658</t>
@@ -647,13 +647,13 @@
     <t xml:space="preserve">17.8565349578857</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8203125</t>
+    <t xml:space="preserve">17.8203144073486</t>
   </si>
   <si>
     <t xml:space="preserve">17.6392135620117</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3455047607422</t>
+    <t xml:space="preserve">18.3455066680908</t>
   </si>
   <si>
     <t xml:space="preserve">18.3907794952393</t>
@@ -668,10 +668,10 @@
     <t xml:space="preserve">19.3958892822266</t>
   </si>
   <si>
-    <t xml:space="preserve">19.377779006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1151828765869</t>
+    <t xml:space="preserve">19.3777809143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1151847839355</t>
   </si>
   <si>
     <t xml:space="preserve">19.5860462188721</t>
@@ -680,13 +680,13 @@
     <t xml:space="preserve">19.2600650787354</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3738327026367</t>
+    <t xml:space="preserve">20.3738346099854</t>
   </si>
   <si>
     <t xml:space="preserve">20.3466682434082</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2380084991455</t>
+    <t xml:space="preserve">20.2380065917969</t>
   </si>
   <si>
     <t xml:space="preserve">20.1293468475342</t>
@@ -698,31 +698,31 @@
     <t xml:space="preserve">20.8084754943848</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6183204650879</t>
+    <t xml:space="preserve">20.6183185577393</t>
   </si>
   <si>
     <t xml:space="preserve">21.4785480499268</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5328769683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0671291351318</t>
+    <t xml:space="preserve">21.5328788757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0671272277832</t>
   </si>
   <si>
     <t xml:space="preserve">22.0580711364746</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2572822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2935009002686</t>
+    <t xml:space="preserve">22.2572841644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2935047149658</t>
   </si>
   <si>
     <t xml:space="preserve">22.3025550842285</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3206672668457</t>
+    <t xml:space="preserve">22.3206653594971</t>
   </si>
   <si>
     <t xml:space="preserve">22.2753925323486</t>
@@ -731,31 +731,31 @@
     <t xml:space="preserve">22.2391719818115</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8186950683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0722351074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8911361694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1537303924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.099401473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5923194885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3568840026855</t>
+    <t xml:space="preserve">22.8186931610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0722370147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.891134262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1537284851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0993995666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5923175811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3568859100342</t>
   </si>
   <si>
     <t xml:space="preserve">22.9092426300049</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1757888793945</t>
+    <t xml:space="preserve">22.1757869720459</t>
   </si>
   <si>
     <t xml:space="preserve">22.1395664215088</t>
@@ -764,13 +764,13 @@
     <t xml:space="preserve">23.606481552124</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7513599395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1226196289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6427040100098</t>
+    <t xml:space="preserve">23.7513618469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1226177215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6427021026611</t>
   </si>
   <si>
     <t xml:space="preserve">23.6879787445068</t>
@@ -779,22 +779,22 @@
     <t xml:space="preserve">23.561206817627</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7423076629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7241992950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6336498260498</t>
+    <t xml:space="preserve">23.7423057556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7241973876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6336479187012</t>
   </si>
   <si>
     <t xml:space="preserve">23.8238010406494</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6970310211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0139579772949</t>
+    <t xml:space="preserve">23.6970329284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0139617919922</t>
   </si>
   <si>
     <t xml:space="preserve">24.2856101989746</t>
@@ -803,13 +803,13 @@
     <t xml:space="preserve">24.0682888031006</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9777393341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2946681976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4304866790771</t>
+    <t xml:space="preserve">23.9777374267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2946662902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4304885864258</t>
   </si>
   <si>
     <t xml:space="preserve">24.61159324646</t>
@@ -821,43 +821,43 @@
     <t xml:space="preserve">25.1911125183105</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3903255462646</t>
+    <t xml:space="preserve">25.3903274536133</t>
   </si>
   <si>
     <t xml:space="preserve">25.4265460968018</t>
   </si>
   <si>
-    <t xml:space="preserve">25.61669921875</t>
+    <t xml:space="preserve">25.6167011260986</t>
   </si>
   <si>
     <t xml:space="preserve">25.6710319519043</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6529197692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7615814208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5352077484131</t>
+    <t xml:space="preserve">25.6529216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7615833282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5352058410645</t>
   </si>
   <si>
     <t xml:space="preserve">24.955680847168</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9013538360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0643444061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8017501831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6206455230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9375705718994</t>
+    <t xml:space="preserve">24.9013519287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0643424987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8017463684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6206474304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9375743865967</t>
   </si>
   <si>
     <t xml:space="preserve">25.3722152709961</t>
@@ -872,25 +872,25 @@
     <t xml:space="preserve">25.1730041503906</t>
   </si>
   <si>
-    <t xml:space="preserve">25.163948059082</t>
+    <t xml:space="preserve">25.1639499664307</t>
   </si>
   <si>
     <t xml:space="preserve">25.399377822876</t>
   </si>
   <si>
-    <t xml:space="preserve">25.72536277771</t>
+    <t xml:space="preserve">25.7253608703613</t>
   </si>
   <si>
     <t xml:space="preserve">25.2907180786133</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1277275085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7434730529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5442581176758</t>
+    <t xml:space="preserve">25.1277313232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7434711456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5442562103271</t>
   </si>
   <si>
     <t xml:space="preserve">25.4808750152588</t>
@@ -899,13 +899,13 @@
     <t xml:space="preserve">25.5080394744873</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2635536193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0824546813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7836399078369</t>
+    <t xml:space="preserve">25.2635517120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0824565887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7836380004883</t>
   </si>
   <si>
     <t xml:space="preserve">24.4214344024658</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">24.2674980163574</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5261497497559</t>
+    <t xml:space="preserve">25.5261516571045</t>
   </si>
   <si>
     <t xml:space="preserve">26.1237831115723</t>
@@ -929,34 +929,34 @@
     <t xml:space="preserve">26.4859828948975</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3229923248291</t>
+    <t xml:space="preserve">26.3229904174805</t>
   </si>
   <si>
     <t xml:space="preserve">26.6761379241943</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8934631347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2596092224121</t>
+    <t xml:space="preserve">26.893461227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2596111297607</t>
   </si>
   <si>
     <t xml:space="preserve">26.667085647583</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9115715026855</t>
+    <t xml:space="preserve">26.9115695953369</t>
   </si>
   <si>
     <t xml:space="preserve">26.6036987304688</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5946464538574</t>
+    <t xml:space="preserve">26.5946483612061</t>
   </si>
   <si>
     <t xml:space="preserve">25.3088302612305</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3269386291504</t>
+    <t xml:space="preserve">25.3269367218018</t>
   </si>
   <si>
     <t xml:space="preserve">25.8340225219727</t>
@@ -968,7 +968,7 @@
     <t xml:space="preserve">26.0641078948975</t>
   </si>
   <si>
-    <t xml:space="preserve">24.71120262146</t>
+    <t xml:space="preserve">24.7112007141113</t>
   </si>
   <si>
     <t xml:space="preserve">23.6159954071045</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">23.2202472686768</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1282119750977</t>
+    <t xml:space="preserve">23.128210067749</t>
   </si>
   <si>
     <t xml:space="preserve">22.9625511169434</t>
@@ -986,43 +986,43 @@
     <t xml:space="preserve">22.8705196380615</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8613147735596</t>
+    <t xml:space="preserve">22.8613166809082</t>
   </si>
   <si>
     <t xml:space="preserve">23.2662658691406</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2386512756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0453815460205</t>
+    <t xml:space="preserve">23.2386531829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0453834533691</t>
   </si>
   <si>
     <t xml:space="preserve">22.8889236450195</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0882263183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3183097839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2262783050537</t>
+    <t xml:space="preserve">22.088228225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3183116912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2262763977051</t>
   </si>
   <si>
     <t xml:space="preserve">22.3827342987061</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3643264770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7416687011719</t>
+    <t xml:space="preserve">22.3643283843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7416667938232</t>
   </si>
   <si>
     <t xml:space="preserve">22.95334815979</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8797206878662</t>
+    <t xml:space="preserve">22.8797225952148</t>
   </si>
   <si>
     <t xml:space="preserve">23.2846698760986</t>
@@ -1037,19 +1037,19 @@
     <t xml:space="preserve">22.806095123291</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0269737243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6036167144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2538871765137</t>
+    <t xml:space="preserve">23.0269756317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6036148071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2538890838623</t>
   </si>
   <si>
     <t xml:space="preserve">21.545223236084</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4900054931641</t>
+    <t xml:space="preserve">21.4900035858154</t>
   </si>
   <si>
     <t xml:space="preserve">21.7200889587402</t>
@@ -1058,10 +1058,10 @@
     <t xml:space="preserve">21.5544261932373</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6740703582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6280536651611</t>
+    <t xml:space="preserve">21.674072265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6280555725098</t>
   </si>
   <si>
     <t xml:space="preserve">21.1678829193115</t>
@@ -1073,25 +1073,25 @@
     <t xml:space="preserve">21.1218662261963</t>
   </si>
   <si>
-    <t xml:space="preserve">21.416374206543</t>
+    <t xml:space="preserve">21.4163761138916</t>
   </si>
   <si>
     <t xml:space="preserve">21.5084114074707</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9133625030518</t>
+    <t xml:space="preserve">21.9133605957031</t>
   </si>
   <si>
     <t xml:space="preserve">21.8857498168945</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9685840606689</t>
+    <t xml:space="preserve">21.9685821533203</t>
   </si>
   <si>
     <t xml:space="preserve">22.6220245361328</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3735332489014</t>
+    <t xml:space="preserve">22.3735313415527</t>
   </si>
   <si>
     <t xml:space="preserve">22.2170734405518</t>
@@ -1103,10 +1103,10 @@
     <t xml:space="preserve">22.5299892425537</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6312294006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6404323577881</t>
+    <t xml:space="preserve">22.6312274932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6404304504395</t>
   </si>
   <si>
     <t xml:space="preserve">22.5576000213623</t>
@@ -1121,19 +1121,19 @@
     <t xml:space="preserve">22.2630920410156</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5391941070557</t>
+    <t xml:space="preserve">22.539192199707</t>
   </si>
   <si>
     <t xml:space="preserve">22.3551254272461</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0514106750488</t>
+    <t xml:space="preserve">22.0514125823975</t>
   </si>
   <si>
     <t xml:space="preserve">22.7876853942871</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3367176055908</t>
+    <t xml:space="preserve">22.3367195129395</t>
   </si>
   <si>
     <t xml:space="preserve">22.115837097168</t>
@@ -1151,13 +1151,13 @@
     <t xml:space="preserve">21.9961891174316</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7016830444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0053958892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8765468597412</t>
+    <t xml:space="preserve">21.701681137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0053939819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8765487670898</t>
   </si>
   <si>
     <t xml:space="preserve">22.1250419616699</t>
@@ -1169,13 +1169,13 @@
     <t xml:space="preserve">22.0238037109375</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9041576385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6832752227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.827356338501</t>
+    <t xml:space="preserve">21.9041557312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6832733154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8273582458496</t>
   </si>
   <si>
     <t xml:space="preserve">21.0574417114258</t>
@@ -1184,7 +1184,7 @@
     <t xml:space="preserve">20.94700050354</t>
   </si>
   <si>
-    <t xml:space="preserve">20.799747467041</t>
+    <t xml:space="preserve">20.7997455596924</t>
   </si>
   <si>
     <t xml:space="preserve">21.1034603118896</t>
@@ -1196,7 +1196,7 @@
     <t xml:space="preserve">21.3243427276611</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9501762390137</t>
+    <t xml:space="preserve">21.950174331665</t>
   </si>
   <si>
     <t xml:space="preserve">22.0974292755127</t>
@@ -1205,7 +1205,7 @@
     <t xml:space="preserve">21.8581409454346</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6372585296631</t>
+    <t xml:space="preserve">21.6372566223145</t>
   </si>
   <si>
     <t xml:space="preserve">21.2967300415039</t>
@@ -1214,16 +1214,16 @@
     <t xml:space="preserve">20.9746131896973</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9838123321533</t>
+    <t xml:space="preserve">20.983814239502</t>
   </si>
   <si>
     <t xml:space="preserve">21.1402721405029</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0666465759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7077102661133</t>
+    <t xml:space="preserve">21.0666446685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7077121734619</t>
   </si>
   <si>
     <t xml:space="preserve">21.0942535400391</t>
@@ -1238,7 +1238,7 @@
     <t xml:space="preserve">21.0022220611572</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6340827941895</t>
+    <t xml:space="preserve">20.6340847015381</t>
   </si>
   <si>
     <t xml:space="preserve">20.4500141143799</t>
@@ -1247,10 +1247,10 @@
     <t xml:space="preserve">20.3855895996094</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3947944641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0082511901855</t>
+    <t xml:space="preserve">20.3947925567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0082492828369</t>
   </si>
   <si>
     <t xml:space="preserve">19.9714393615723</t>
@@ -1259,10 +1259,10 @@
     <t xml:space="preserve">20.0634708404541</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4868316650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7445278167725</t>
+    <t xml:space="preserve">20.4868278503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7445259094238</t>
   </si>
   <si>
     <t xml:space="preserve">20.8917827606201</t>
@@ -1277,13 +1277,13 @@
     <t xml:space="preserve">20.2475395202637</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1647109985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0910835266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2719745635986</t>
+    <t xml:space="preserve">20.1647090911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0910816192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2719764709473</t>
   </si>
   <si>
     <t xml:space="preserve">19.695333480835</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">20.0450630187988</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2935581207275</t>
+    <t xml:space="preserve">20.2935562133789</t>
   </si>
   <si>
     <t xml:space="preserve">20.4316101074219</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">20.5696601867676</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6616954803467</t>
+    <t xml:space="preserve">20.6616973876953</t>
   </si>
   <si>
     <t xml:space="preserve">21.131067276001</t>
@@ -1319,7 +1319,7 @@
     <t xml:space="preserve">21.0482387542725</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1954936981201</t>
+    <t xml:space="preserve">21.1954917907715</t>
   </si>
   <si>
     <t xml:space="preserve">21.4531898498535</t>
@@ -1328,22 +1328,22 @@
     <t xml:space="preserve">20.8089504241943</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6708946228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7721347808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4652481079102</t>
+    <t xml:space="preserve">20.6708965301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7721366882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4652500152588</t>
   </si>
   <si>
     <t xml:space="preserve">19.7965717315674</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8609981536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0174541473389</t>
+    <t xml:space="preserve">19.8609962463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0174560546875</t>
   </si>
   <si>
     <t xml:space="preserve">20.2199287414551</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">20.229133605957</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5236415863037</t>
+    <t xml:space="preserve">20.5236434936523</t>
   </si>
   <si>
     <t xml:space="preserve">20.6524925231934</t>
@@ -1373,22 +1373,22 @@
     <t xml:space="preserve">20.1739120483398</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2599182128906</t>
+    <t xml:space="preserve">21.259916305542</t>
   </si>
   <si>
     <t xml:space="preserve">21.3703575134277</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5176124572754</t>
+    <t xml:space="preserve">21.517614364624</t>
   </si>
   <si>
     <t xml:space="preserve">20.8549652099609</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9193878173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5052375793457</t>
+    <t xml:space="preserve">20.9193897247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5052356719971</t>
   </si>
   <si>
     <t xml:space="preserve">20.3487777709961</t>
@@ -1403,7 +1403,7 @@
     <t xml:space="preserve">19.9162178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5604553222656</t>
+    <t xml:space="preserve">20.5604572296143</t>
   </si>
   <si>
     <t xml:space="preserve">20.7169170379639</t>
@@ -1415,10 +1415,10 @@
     <t xml:space="preserve">20.8365592956543</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6004447937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6248798370361</t>
+    <t xml:space="preserve">21.6004428863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6248817443848</t>
   </si>
   <si>
     <t xml:space="preserve">20.2751502990723</t>
@@ -1427,10 +1427,10 @@
     <t xml:space="preserve">20.1094875335693</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6493186950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.999044418335</t>
+    <t xml:space="preserve">19.6493148803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9990463256836</t>
   </si>
   <si>
     <t xml:space="preserve">20.1278972625732</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">20.8733749389648</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3763904571533</t>
+    <t xml:space="preserve">20.3763885498047</t>
   </si>
   <si>
     <t xml:space="preserve">20.5328464508057</t>
@@ -1457,19 +1457,19 @@
     <t xml:space="preserve">20.6156768798828</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7261180877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2783279418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3151378631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5360202789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7937183380127</t>
+    <t xml:space="preserve">20.7261199951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2783260345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3151397705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.536018371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7937164306641</t>
   </si>
   <si>
     <t xml:space="preserve">22.64963722229</t>
@@ -1478,22 +1478,22 @@
     <t xml:space="preserve">22.548397064209</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4195499420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2078666687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5668029785156</t>
+    <t xml:space="preserve">22.4195518493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2078685760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5668048858643</t>
   </si>
   <si>
     <t xml:space="preserve">22.6128215789795</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9165325164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6864490509033</t>
+    <t xml:space="preserve">22.9165344238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6864471435547</t>
   </si>
   <si>
     <t xml:space="preserve">22.7324657440186</t>
@@ -1508,7 +1508,7 @@
     <t xml:space="preserve">22.9073314666748</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2754688262939</t>
+    <t xml:space="preserve">23.2754669189453</t>
   </si>
   <si>
     <t xml:space="preserve">22.991304397583</t>
@@ -6021,6 +6021,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.17000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
   </si>
 </sst>
 </file>
@@ -72009,7 +72012,7 @@
     </row>
     <row r="2526">
       <c r="A2526" s="1" t="n">
-        <v>45995.6909837963</v>
+        <v>45995.3333333333</v>
       </c>
       <c r="B2526" t="n">
         <v>373913</v>
@@ -72030,6 +72033,32 @@
         <v>2002</v>
       </c>
       <c r="H2526" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2527">
+      <c r="A2527" s="1" t="n">
+        <v>45996.6912037037</v>
+      </c>
+      <c r="B2527" t="n">
+        <v>277565</v>
+      </c>
+      <c r="C2527" t="n">
+        <v>8.19999980926514</v>
+      </c>
+      <c r="D2527" t="n">
+        <v>7.94500017166138</v>
+      </c>
+      <c r="E2527" t="n">
+        <v>8.19999980926514</v>
+      </c>
+      <c r="F2527" t="n">
+        <v>8</v>
+      </c>
+      <c r="G2527" t="s">
+        <v>2003</v>
+      </c>
+      <c r="H2527" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2763519287109</t>
+    <t xml:space="preserve">18.2763500213623</t>
   </si>
   <si>
     <t xml:space="preserve">SFER.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">18.01096534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4978809356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9401950836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6836528778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.249813079834</t>
+    <t xml:space="preserve">18.0109672546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4978828430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9401969909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.683650970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2498111724854</t>
   </si>
   <si>
     <t xml:space="preserve">19.4086723327637</t>
@@ -65,19 +65,19 @@
     <t xml:space="preserve">19.1344375610352</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8425102233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4621238708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2852001190186</t>
+    <t xml:space="preserve">18.8425121307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4621257781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2851963043213</t>
   </si>
   <si>
     <t xml:space="preserve">18.0994262695312</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6394233703613</t>
+    <t xml:space="preserve">17.6394195556641</t>
   </si>
   <si>
     <t xml:space="preserve">17.5686531066895</t>
@@ -86,22 +86,22 @@
     <t xml:space="preserve">18.1878890991211</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4798145294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2232704162598</t>
+    <t xml:space="preserve">18.4798164367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.223274230957</t>
   </si>
   <si>
     <t xml:space="preserve">17.7632675170898</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3913555145264</t>
+    <t xml:space="preserve">18.3913516998291</t>
   </si>
   <si>
     <t xml:space="preserve">18.6744327545166</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9578819274902</t>
+    <t xml:space="preserve">17.9578857421875</t>
   </si>
   <si>
     <t xml:space="preserve">18.2055816650391</t>
@@ -113,28 +113,28 @@
     <t xml:space="preserve">18.0817337036133</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3563423156738</t>
+    <t xml:space="preserve">17.3563404083252</t>
   </si>
   <si>
     <t xml:space="preserve">16.9051837921143</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1617221832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6486415863037</t>
+    <t xml:space="preserve">17.1617259979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.648645401001</t>
   </si>
   <si>
     <t xml:space="preserve">17.0201835632324</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4890365600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6305751800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4090442657471</t>
+    <t xml:space="preserve">17.48903465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6305770874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4090461730957</t>
   </si>
   <si>
     <t xml:space="preserve">18.4532775878906</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">18.9752063751221</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1348114013672</t>
+    <t xml:space="preserve">18.1348094940186</t>
   </si>
   <si>
     <t xml:space="preserve">17.3121089935303</t>
@@ -152,64 +152,64 @@
     <t xml:space="preserve">17.9048099517822</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3471221923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0194339752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.001745223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8513584136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3113613128662</t>
+    <t xml:space="preserve">18.3471202850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0194358825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0017433166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8513565063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3113632202148</t>
   </si>
   <si>
     <t xml:space="preserve">19.992525100708</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9482936859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7271366119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3379020690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6475200653076</t>
+    <t xml:space="preserve">19.9482917785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7271347045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3379039764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.647518157959</t>
   </si>
   <si>
     <t xml:space="preserve">19.9836769104004</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1167469024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.444055557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0367565155029</t>
+    <t xml:space="preserve">19.1167449951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4440536499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0367546081543</t>
   </si>
   <si>
     <t xml:space="preserve">20.1782932281494</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4971351623535</t>
+    <t xml:space="preserve">19.4971332550049</t>
   </si>
   <si>
     <t xml:space="preserve">19.4705944061279</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9663619995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4794406890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9129066467285</t>
+    <t xml:space="preserve">18.9663600921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4794425964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9129085540771</t>
   </si>
   <si>
     <t xml:space="preserve">19.8686752319336</t>
@@ -221,31 +221,31 @@
     <t xml:space="preserve">18.8690509796143</t>
   </si>
   <si>
-    <t xml:space="preserve">18.833667755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5151996612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9309711456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8955879211426</t>
+    <t xml:space="preserve">18.8336658477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5152015686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9309749603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8955898284912</t>
   </si>
   <si>
     <t xml:space="preserve">18.5240478515625</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9486656188965</t>
+    <t xml:space="preserve">18.9486675262451</t>
   </si>
   <si>
     <t xml:space="preserve">18.7982788085938</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8778991699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2936687469482</t>
+    <t xml:space="preserve">18.8778953552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2936706542969</t>
   </si>
   <si>
     <t xml:space="preserve">18.8071269989014</t>
@@ -254,13 +254,13 @@
     <t xml:space="preserve">18.3205833435059</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3648128509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8251895904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0640430450439</t>
+    <t xml:space="preserve">18.3648147583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8251934051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0640411376953</t>
   </si>
   <si>
     <t xml:space="preserve">18.3117370605469</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">17.8782691955566</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0021171569824</t>
+    <t xml:space="preserve">18.0021190643311</t>
   </si>
   <si>
     <t xml:space="preserve">17.7190399169922</t>
@@ -278,52 +278,52 @@
     <t xml:space="preserve">17.4448051452637</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1440296173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5509586334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9844264984131</t>
+    <t xml:space="preserve">17.1440334320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5509605407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9844245910645</t>
   </si>
   <si>
     <t xml:space="preserve">17.4182662963867</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9313507080078</t>
+    <t xml:space="preserve">17.9313488006592</t>
   </si>
   <si>
     <t xml:space="preserve">17.7367286682129</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6482639312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.593936920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.81125831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7025947570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6482677459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.530553817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4128379821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.304178237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4762229919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4309463500977</t>
+    <t xml:space="preserve">17.6482696533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5939388275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8112564086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7025966644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.648265838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5305519104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4128360748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3041763305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4762210845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.430944442749</t>
   </si>
   <si>
     <t xml:space="preserve">17.4852771759033</t>
@@ -335,16 +335,16 @@
     <t xml:space="preserve">17.6844882965088</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1502418518066</t>
+    <t xml:space="preserve">17.150239944458</t>
   </si>
   <si>
     <t xml:space="preserve">16.71559715271</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5435543060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0415782928467</t>
+    <t xml:space="preserve">16.5435562133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0415821075439</t>
   </si>
   <si>
     <t xml:space="preserve">17.0778007507324</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">17.8384227752686</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9380302429199</t>
+    <t xml:space="preserve">17.9380283355713</t>
   </si>
   <si>
     <t xml:space="preserve">17.7297611236572</t>
@@ -365,19 +365,19 @@
     <t xml:space="preserve">18.1825141906738</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8514232635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3896198272705</t>
+    <t xml:space="preserve">16.8514251708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3896179199219</t>
   </si>
   <si>
     <t xml:space="preserve">16.6793804168701</t>
   </si>
   <si>
-    <t xml:space="preserve">16.262845993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5254459381104</t>
+    <t xml:space="preserve">16.2628440856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5254440307617</t>
   </si>
   <si>
     <t xml:space="preserve">16.6069412231445</t>
@@ -386,13 +386,13 @@
     <t xml:space="preserve">16.8061485290527</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8242588043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0726909637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8734827041626</t>
+    <t xml:space="preserve">16.8242607116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0726890563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8734817504883</t>
   </si>
   <si>
     <t xml:space="preserve">16.3624496459961</t>
@@ -401,22 +401,22 @@
     <t xml:space="preserve">16.4439468383789</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6974906921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0959091186523</t>
+    <t xml:space="preserve">16.69748878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.095911026001</t>
   </si>
   <si>
     <t xml:space="preserve">17.1321315765381</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0868549346924</t>
+    <t xml:space="preserve">17.086856842041</t>
   </si>
   <si>
     <t xml:space="preserve">17.0325260162354</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3403968811035</t>
+    <t xml:space="preserve">17.3403949737549</t>
   </si>
   <si>
     <t xml:space="preserve">17.9018077850342</t>
@@ -425,28 +425,28 @@
     <t xml:space="preserve">18.1372413635254</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9289703369141</t>
+    <t xml:space="preserve">17.9289741516113</t>
   </si>
   <si>
     <t xml:space="preserve">18.7710914611816</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6352653503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0699081420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2147903442383</t>
+    <t xml:space="preserve">18.6352672576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0699062347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2147884368896</t>
   </si>
   <si>
     <t xml:space="preserve">18.6262111663818</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4994411468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2187385559082</t>
+    <t xml:space="preserve">18.4994430541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2187366485596</t>
   </si>
   <si>
     <t xml:space="preserve">18.7167625427246</t>
@@ -458,28 +458,28 @@
     <t xml:space="preserve">18.7620372772217</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8073120117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9431381225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0427436828613</t>
+    <t xml:space="preserve">18.8073139190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9431400299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0427417755127</t>
   </si>
   <si>
     <t xml:space="preserve">18.6624317169189</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4722747802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6171569824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7529811859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9703044891357</t>
+    <t xml:space="preserve">18.4722766876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6171550750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7529830932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9703025817871</t>
   </si>
   <si>
     <t xml:space="preserve">18.6805400848389</t>
@@ -488,28 +488,28 @@
     <t xml:space="preserve">18.6081008911133</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6533737182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5175514221191</t>
+    <t xml:space="preserve">18.653377532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5175495147705</t>
   </si>
   <si>
     <t xml:space="preserve">18.870698928833</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6986503601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.106128692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9210834503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6947078704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5588817596436</t>
+    <t xml:space="preserve">18.6986522674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1061267852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9210815429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6947059631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5588798522949</t>
   </si>
   <si>
     <t xml:space="preserve">19.4592742919922</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">18.8888092041016</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1332912445068</t>
+    <t xml:space="preserve">19.1332931518555</t>
   </si>
   <si>
     <t xml:space="preserve">19.1604595184326</t>
@@ -530,52 +530,52 @@
     <t xml:space="preserve">19.9391918182373</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4553279876709</t>
+    <t xml:space="preserve">20.4553298950195</t>
   </si>
   <si>
     <t xml:space="preserve">20.3557224273682</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3104496002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3919429779053</t>
+    <t xml:space="preserve">20.3104515075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3919448852539</t>
   </si>
   <si>
     <t xml:space="preserve">20.4643840789795</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6907596588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8446960449219</t>
+    <t xml:space="preserve">20.6907615661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8446941375732</t>
   </si>
   <si>
     <t xml:space="preserve">20.7994194030762</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4009990692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1021862030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5277690887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3647785186768</t>
+    <t xml:space="preserve">20.4010009765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1021842956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5277709960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3647766113281</t>
   </si>
   <si>
     <t xml:space="preserve">20.5458793640137</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7541446685791</t>
+    <t xml:space="preserve">20.7541484832764</t>
   </si>
   <si>
     <t xml:space="preserve">20.4191074371338</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0116310119629</t>
+    <t xml:space="preserve">20.0116348266602</t>
   </si>
   <si>
     <t xml:space="preserve">20.265172958374</t>
@@ -587,19 +587,19 @@
     <t xml:space="preserve">20.03879737854</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1474571228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2289562225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5006046295166</t>
+    <t xml:space="preserve">20.1474590301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2289543151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.500602722168</t>
   </si>
   <si>
     <t xml:space="preserve">20.5639877319336</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1836776733398</t>
+    <t xml:space="preserve">20.1836795806885</t>
   </si>
   <si>
     <t xml:space="preserve">19.549825668335</t>
@@ -608,37 +608,37 @@
     <t xml:space="preserve">19.4140014648438</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5045490264893</t>
+    <t xml:space="preserve">19.5045528411865</t>
   </si>
   <si>
     <t xml:space="preserve">19.7218723297119</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7943115234375</t>
+    <t xml:space="preserve">19.7943134307861</t>
   </si>
   <si>
     <t xml:space="preserve">19.5226593017578</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8305339813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9120254516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7490348815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0919647216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3002300262451</t>
+    <t xml:space="preserve">19.8305320739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9120235443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7490367889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0919609069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3002281188965</t>
   </si>
   <si>
     <t xml:space="preserve">18.3273963928223</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2458972930908</t>
+    <t xml:space="preserve">18.2459011077881</t>
   </si>
   <si>
     <t xml:space="preserve">18.0104694366455</t>
@@ -650,19 +650,19 @@
     <t xml:space="preserve">17.8565330505371</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8203125</t>
+    <t xml:space="preserve">17.8203144073486</t>
   </si>
   <si>
     <t xml:space="preserve">17.6392116546631</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3455066680908</t>
+    <t xml:space="preserve">18.3455047607422</t>
   </si>
   <si>
     <t xml:space="preserve">18.3907814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">19.151403427124</t>
+    <t xml:space="preserve">19.1514015197754</t>
   </si>
   <si>
     <t xml:space="preserve">19.2872295379639</t>
@@ -677,40 +677,40 @@
     <t xml:space="preserve">19.1151847839355</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5860443115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2600650787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3738346099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3466663360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2380104064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1293487548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.15651512146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8084754943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6183185577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4785461425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5328807830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0671291351318</t>
+    <t xml:space="preserve">19.5860462188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2600631713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3738327026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3466682434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2380084991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1293449401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1565132141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8084735870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6183223724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4785480499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5328788757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0671272277832</t>
   </si>
   <si>
     <t xml:space="preserve">22.0580711364746</t>
@@ -722,76 +722,76 @@
     <t xml:space="preserve">22.2935009002686</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3025550842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3206672668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.275390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2391681671143</t>
+    <t xml:space="preserve">22.3025569915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3206653594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2753925323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2391700744629</t>
   </si>
   <si>
     <t xml:space="preserve">22.8186950683594</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0722332000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8911361694336</t>
+    <t xml:space="preserve">23.0722351074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.891134262085</t>
   </si>
   <si>
     <t xml:space="preserve">23.1537303924561</t>
   </si>
   <si>
-    <t xml:space="preserve">23.099401473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5923194885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3568840026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9092426300049</t>
+    <t xml:space="preserve">23.0993976593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5923175811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3568878173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9092445373535</t>
   </si>
   <si>
     <t xml:space="preserve">22.1757850646973</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1395664215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6064834594727</t>
+    <t xml:space="preserve">22.1395683288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.606481552124</t>
   </si>
   <si>
     <t xml:space="preserve">23.7513618469238</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1226196289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6427040100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6879768371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.561206817627</t>
+    <t xml:space="preserve">24.1226177215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6427021026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6879749298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5612087249756</t>
   </si>
   <si>
     <t xml:space="preserve">23.7423076629639</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7241992950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6336479187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.823802947998</t>
+    <t xml:space="preserve">23.7241973876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6336460113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8238010406494</t>
   </si>
   <si>
     <t xml:space="preserve">23.6970329284668</t>
@@ -806,22 +806,22 @@
     <t xml:space="preserve">24.0682888031006</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9777374267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2946643829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4304904937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.61159324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7655296325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1911125183105</t>
+    <t xml:space="preserve">23.9777393341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2946624755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.430492401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6115913391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7655277252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1911144256592</t>
   </si>
   <si>
     <t xml:space="preserve">25.3903255462646</t>
@@ -830,55 +830,55 @@
     <t xml:space="preserve">25.4265441894531</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6167049407959</t>
+    <t xml:space="preserve">25.6167030334473</t>
   </si>
   <si>
     <t xml:space="preserve">25.6710300445557</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6529216766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7615795135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5352039337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9556827545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9013519287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0643424987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8017501831055</t>
+    <t xml:space="preserve">25.6529197692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7615833282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5352058410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.955680847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9013538360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0643444061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8017463684082</t>
   </si>
   <si>
     <t xml:space="preserve">24.6206474304199</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9375762939453</t>
+    <t xml:space="preserve">24.9375743865967</t>
   </si>
   <si>
     <t xml:space="preserve">25.3722133636475</t>
   </si>
   <si>
-    <t xml:space="preserve">25.62575340271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2273349761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.173002243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1639499664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3993759155273</t>
+    <t xml:space="preserve">25.6257553100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2273330688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1730041503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.163948059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.399377822876</t>
   </si>
   <si>
     <t xml:space="preserve">25.7253608703613</t>
@@ -887,25 +887,25 @@
     <t xml:space="preserve">25.2907199859619</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1277256011963</t>
+    <t xml:space="preserve">25.1277294158936</t>
   </si>
   <si>
     <t xml:space="preserve">25.7434711456299</t>
   </si>
   <si>
-    <t xml:space="preserve">25.544261932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4808769226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5080394744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2635517120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0824527740479</t>
+    <t xml:space="preserve">25.5442600250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4808750152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5080375671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2635555267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0824508666992</t>
   </si>
   <si>
     <t xml:space="preserve">24.7836380004883</t>
@@ -926,13 +926,13 @@
     <t xml:space="preserve">26.1871681213379</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6308650970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4859848022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3229942321777</t>
+    <t xml:space="preserve">26.6308631896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4859828948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3229923248291</t>
   </si>
   <si>
     <t xml:space="preserve">26.6761379241943</t>
@@ -944,13 +944,13 @@
     <t xml:space="preserve">26.2596073150635</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6670837402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9115695953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6037006378174</t>
+    <t xml:space="preserve">26.667085647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9115676879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6036987304688</t>
   </si>
   <si>
     <t xml:space="preserve">26.5946464538574</t>
@@ -959,16 +959,16 @@
     <t xml:space="preserve">25.3088302612305</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3269367218018</t>
+    <t xml:space="preserve">25.326940536499</t>
   </si>
   <si>
     <t xml:space="preserve">25.834020614624</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8984451293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0641078948975</t>
+    <t xml:space="preserve">25.8984432220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0641059875488</t>
   </si>
   <si>
     <t xml:space="preserve">24.7112045288086</t>
@@ -980,25 +980,25 @@
     <t xml:space="preserve">23.2202472686768</t>
   </si>
   <si>
-    <t xml:space="preserve">23.128210067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9625511169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8705196380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8613128662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2662658691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2386512756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0453853607178</t>
+    <t xml:space="preserve">23.1282119750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.962553024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8705177307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8613147735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.266263961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.238655090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0453834533691</t>
   </si>
   <si>
     <t xml:space="preserve">22.8889236450195</t>
@@ -1013,28 +1013,28 @@
     <t xml:space="preserve">22.2262763977051</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3827342987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3643283843994</t>
+    <t xml:space="preserve">22.3827362060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3643264770508</t>
   </si>
   <si>
     <t xml:space="preserve">22.7416667938232</t>
   </si>
   <si>
-    <t xml:space="preserve">22.95334815979</t>
+    <t xml:space="preserve">22.9533500671387</t>
   </si>
   <si>
     <t xml:space="preserve">22.8797206878662</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2846717834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4871463775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4319229125977</t>
+    <t xml:space="preserve">23.2846736907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4871482849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4319248199463</t>
   </si>
   <si>
     <t xml:space="preserve">22.8060932159424</t>
@@ -1046,34 +1046,34 @@
     <t xml:space="preserve">22.6036167144775</t>
   </si>
   <si>
-    <t xml:space="preserve">22.253885269165</t>
+    <t xml:space="preserve">22.2538871765137</t>
   </si>
   <si>
     <t xml:space="preserve">21.545223236084</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4900016784668</t>
+    <t xml:space="preserve">21.4900035858154</t>
   </si>
   <si>
     <t xml:space="preserve">21.7200889587402</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5544281005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6740703582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6280555725098</t>
+    <t xml:space="preserve">21.5544261932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.674072265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6280536651611</t>
   </si>
   <si>
     <t xml:space="preserve">21.1678829193115</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2046966552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1218681335449</t>
+    <t xml:space="preserve">21.2046985626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1218662261963</t>
   </si>
   <si>
     <t xml:space="preserve">21.4163761138916</t>
@@ -1082,7 +1082,7 @@
     <t xml:space="preserve">21.5084095001221</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9133605957031</t>
+    <t xml:space="preserve">21.9133625030518</t>
   </si>
   <si>
     <t xml:space="preserve">21.8857517242432</t>
@@ -1097,28 +1097,28 @@
     <t xml:space="preserve">22.3735313415527</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2170715332031</t>
+    <t xml:space="preserve">22.2170734405518</t>
   </si>
   <si>
     <t xml:space="preserve">22.4103469848633</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5299892425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6312255859375</t>
+    <t xml:space="preserve">22.5299911499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6312274932861</t>
   </si>
   <si>
     <t xml:space="preserve">22.6404323577881</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5576019287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4255809783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6556663513184</t>
+    <t xml:space="preserve">22.5576000213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4255790710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6556644439697</t>
   </si>
   <si>
     <t xml:space="preserve">22.2630920410156</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">22.0514106750488</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7876853942871</t>
+    <t xml:space="preserve">22.7876873016357</t>
   </si>
   <si>
     <t xml:space="preserve">22.3367195129395</t>
@@ -1151,22 +1151,22 @@
     <t xml:space="preserve">21.7569007873535</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9961891174316</t>
+    <t xml:space="preserve">21.9961929321289</t>
   </si>
   <si>
     <t xml:space="preserve">21.701681137085</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0053958892822</t>
+    <t xml:space="preserve">22.0053939819336</t>
   </si>
   <si>
     <t xml:space="preserve">21.8765468597412</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1250419616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7753086090088</t>
+    <t xml:space="preserve">22.1250381469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7753105163574</t>
   </si>
   <si>
     <t xml:space="preserve">22.0238018035889</t>
@@ -1175,31 +1175,31 @@
     <t xml:space="preserve">21.9041576385498</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6832733154297</t>
+    <t xml:space="preserve">21.6832714080811</t>
   </si>
   <si>
     <t xml:space="preserve">20.827356338501</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0574417114258</t>
+    <t xml:space="preserve">21.0574398040771</t>
   </si>
   <si>
     <t xml:space="preserve">20.94700050354</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7997436523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1034603118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0758495330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3243427276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.950174331665</t>
+    <t xml:space="preserve">20.799747467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.103458404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0758476257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3243408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9501762390137</t>
   </si>
   <si>
     <t xml:space="preserve">22.0974292755127</t>
@@ -1220,28 +1220,28 @@
     <t xml:space="preserve">20.983814239502</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1402721405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0666446685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7077121734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0942554473877</t>
+    <t xml:space="preserve">21.1402702331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0666465759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7077102661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0942573547363</t>
   </si>
   <si>
     <t xml:space="preserve">21.1586799621582</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0206298828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0022201538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6340847015381</t>
+    <t xml:space="preserve">21.0206279754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0022220611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6340827941895</t>
   </si>
   <si>
     <t xml:space="preserve">20.4500160217285</t>
@@ -1259,25 +1259,25 @@
     <t xml:space="preserve">19.9714374542236</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0634708404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4868278503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7445259094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8917789459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2415084838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9285945892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2475395202637</t>
+    <t xml:space="preserve">20.0634727478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4868297576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7445278167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8917808532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.241512298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9285926818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2475433349609</t>
   </si>
   <si>
     <t xml:space="preserve">20.1647090911865</t>
@@ -1286,7 +1286,7 @@
     <t xml:space="preserve">20.0910816192627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2719764709473</t>
+    <t xml:space="preserve">19.2719783782959</t>
   </si>
   <si>
     <t xml:space="preserve">19.695333480835</t>
@@ -1304,55 +1304,55 @@
     <t xml:space="preserve">20.0450649261475</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2935562133789</t>
+    <t xml:space="preserve">20.2935581207275</t>
   </si>
   <si>
     <t xml:space="preserve">20.4316101074219</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5696620941162</t>
+    <t xml:space="preserve">20.5696601867676</t>
   </si>
   <si>
     <t xml:space="preserve">20.661693572998</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1310691833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0482387542725</t>
+    <t xml:space="preserve">21.131067276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0482406616211</t>
   </si>
   <si>
     <t xml:space="preserve">21.1954936981201</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4531898498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8089485168457</t>
+    <t xml:space="preserve">21.4531879425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8089466094971</t>
   </si>
   <si>
     <t xml:space="preserve">20.6708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7721347808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4652500152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7965698242188</t>
+    <t xml:space="preserve">20.7721366882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4652462005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7965717315674</t>
   </si>
   <si>
     <t xml:space="preserve">19.8609981536865</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0174541473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2199287414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2291316986084</t>
+    <t xml:space="preserve">20.0174522399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2199268341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.229133605957</t>
   </si>
   <si>
     <t xml:space="preserve">20.5236415863037</t>
@@ -1361,49 +1361,49 @@
     <t xml:space="preserve">20.6524925231934</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9101867675781</t>
+    <t xml:space="preserve">20.9101886749268</t>
   </si>
   <si>
     <t xml:space="preserve">20.2659473419189</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4684238433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1555061340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1739139556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2599182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3703575134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5176124572754</t>
+    <t xml:space="preserve">20.4684219360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1555080413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1739120483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.259916305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3703556060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5176105499268</t>
   </si>
   <si>
     <t xml:space="preserve">20.8549671173096</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9193897247314</t>
+    <t xml:space="preserve">20.9193916320801</t>
   </si>
   <si>
     <t xml:space="preserve">20.5052356719971</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3487796783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0266571044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7229461669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9162158966064</t>
+    <t xml:space="preserve">20.3487777709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0266590118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7229442596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9162178039551</t>
   </si>
   <si>
     <t xml:space="preserve">20.5604553222656</t>
@@ -1415,13 +1415,13 @@
     <t xml:space="preserve">20.9377956390381</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8365592956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6004447937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6248798370361</t>
+    <t xml:space="preserve">20.8365573883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6004428863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6248817443848</t>
   </si>
   <si>
     <t xml:space="preserve">20.2751522064209</t>
@@ -1430,52 +1430,52 @@
     <t xml:space="preserve">20.109489440918</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6493167877197</t>
+    <t xml:space="preserve">19.6493186950684</t>
   </si>
   <si>
     <t xml:space="preserve">19.9990463256836</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1278972625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3303737640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8733749389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3763885498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5328464508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3027591705322</t>
+    <t xml:space="preserve">20.1278953552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3303699493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8733730316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3763866424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5328483581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3027610778809</t>
   </si>
   <si>
     <t xml:space="preserve">20.6432876586914</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6156787872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7261199951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2783260345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3151397705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.536018371582</t>
+    <t xml:space="preserve">20.6156768798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7261180877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2783241271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3151378631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5360202789307</t>
   </si>
   <si>
     <t xml:space="preserve">21.7937164306641</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6496353149414</t>
+    <t xml:space="preserve">22.6496334075928</t>
   </si>
   <si>
     <t xml:space="preserve">22.548397064209</t>
@@ -1490,13 +1490,13 @@
     <t xml:space="preserve">22.5668048858643</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6128234863281</t>
+    <t xml:space="preserve">22.6128215789795</t>
   </si>
   <si>
     <t xml:space="preserve">22.9165344238281</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6864452362061</t>
+    <t xml:space="preserve">22.6864471435547</t>
   </si>
   <si>
     <t xml:space="preserve">22.7324657440186</t>
@@ -1505,31 +1505,31 @@
     <t xml:space="preserve">22.8337020874023</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7692813873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9073314666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2754707336426</t>
+    <t xml:space="preserve">22.7692775726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9073333740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2754669189453</t>
   </si>
   <si>
     <t xml:space="preserve">22.991304397583</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3090686798096</t>
+    <t xml:space="preserve">23.3090705871582</t>
   </si>
   <si>
     <t xml:space="preserve">23.4118747711182</t>
   </si>
   <si>
-    <t xml:space="preserve">22.907190322876</t>
+    <t xml:space="preserve">22.9071884155273</t>
   </si>
   <si>
     <t xml:space="preserve">22.9819564819336</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7296123504639</t>
+    <t xml:space="preserve">22.7296142578125</t>
   </si>
   <si>
     <t xml:space="preserve">22.355770111084</t>
@@ -1538,13 +1538,13 @@
     <t xml:space="preserve">22.6174602508545</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0754165649414</t>
+    <t xml:space="preserve">23.07541847229</t>
   </si>
   <si>
     <t xml:space="preserve">23.3557987213135</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1969146728516</t>
+    <t xml:space="preserve">23.1969165802002</t>
   </si>
   <si>
     <t xml:space="preserve">23.206262588501</t>
@@ -1562,34 +1562,34 @@
     <t xml:space="preserve">23.1595325469971</t>
   </si>
   <si>
-    <t xml:space="preserve">23.505334854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3838386535645</t>
+    <t xml:space="preserve">23.5053367614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3838367462158</t>
   </si>
   <si>
     <t xml:space="preserve">23.3931846618652</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2623386383057</t>
+    <t xml:space="preserve">23.2623405456543</t>
   </si>
   <si>
     <t xml:space="preserve">22.9258823394775</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9912452697754</t>
+    <t xml:space="preserve">20.991247177124</t>
   </si>
   <si>
     <t xml:space="preserve">20.3370227813721</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9912166595459</t>
+    <t xml:space="preserve">19.9912185668945</t>
   </si>
   <si>
     <t xml:space="preserve">19.7388763427734</t>
   </si>
   <si>
-    <t xml:space="preserve">19.56130027771</t>
+    <t xml:space="preserve">19.5612983703613</t>
   </si>
   <si>
     <t xml:space="preserve">19.3089561462402</t>
@@ -1598,16 +1598,16 @@
     <t xml:space="preserve">19.533260345459</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4958782196045</t>
+    <t xml:space="preserve">19.4958763122559</t>
   </si>
   <si>
     <t xml:space="preserve">19.3463401794434</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0285739898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6266937255859</t>
+    <t xml:space="preserve">19.0285758972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6266956329346</t>
   </si>
   <si>
     <t xml:space="preserve">18.383695602417</t>
@@ -1622,7 +1622,7 @@
     <t xml:space="preserve">18.079948425293</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6033306121826</t>
+    <t xml:space="preserve">18.603328704834</t>
   </si>
   <si>
     <t xml:space="preserve">18.6360397338867</t>
@@ -1640,10 +1640,10 @@
     <t xml:space="preserve">18.5752906799316</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3930416107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5285587310791</t>
+    <t xml:space="preserve">18.3930435180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5285606384277</t>
   </si>
   <si>
     <t xml:space="preserve">18.495849609375</t>
@@ -1652,25 +1652,25 @@
     <t xml:space="preserve">18.4351005554199</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3883686065674</t>
+    <t xml:space="preserve">18.388370513916</t>
   </si>
   <si>
     <t xml:space="preserve">18.491174697876</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2435054779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8042411804199</t>
+    <t xml:space="preserve">18.2435073852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8042373657227</t>
   </si>
   <si>
     <t xml:space="preserve">17.7715282440186</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1079883575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6734256744385</t>
+    <t xml:space="preserve">18.1079864501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6734237670898</t>
   </si>
   <si>
     <t xml:space="preserve">18.7575378417969</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">18.276216506958</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2528533935547</t>
+    <t xml:space="preserve">18.2528514862061</t>
   </si>
   <si>
     <t xml:space="preserve">18.2107944488525</t>
@@ -1694,19 +1694,19 @@
     <t xml:space="preserve">19.1407260894775</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4398021697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4024143218994</t>
+    <t xml:space="preserve">19.4397983551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4024181365967</t>
   </si>
   <si>
     <t xml:space="preserve">19.4117641448975</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4304580688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3650302886963</t>
+    <t xml:space="preserve">19.4304542541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3650341033936</t>
   </si>
   <si>
     <t xml:space="preserve">19.1594200134277</t>
@@ -1724,19 +1724,19 @@
     <t xml:space="preserve">18.7388458251953</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0566120147705</t>
+    <t xml:space="preserve">19.0566101074219</t>
   </si>
   <si>
     <t xml:space="preserve">18.8416519165039</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6080284118652</t>
+    <t xml:space="preserve">19.6080303192139</t>
   </si>
   <si>
     <t xml:space="preserve">19.2528800964355</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5239162445068</t>
+    <t xml:space="preserve">19.5239143371582</t>
   </si>
   <si>
     <t xml:space="preserve">19.4211101531982</t>
@@ -1745,43 +1745,43 @@
     <t xml:space="preserve">19.8136425018311</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0753307342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.748218536377</t>
+    <t xml:space="preserve">20.0753326416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7482204437256</t>
   </si>
   <si>
     <t xml:space="preserve">20.0192565917969</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7669124603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7856044769287</t>
+    <t xml:space="preserve">19.7669105529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7856063842773</t>
   </si>
   <si>
     <t xml:space="preserve">19.5706462860107</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2809162139893</t>
+    <t xml:space="preserve">19.2809181213379</t>
   </si>
   <si>
     <t xml:space="preserve">19.1500720977783</t>
   </si>
   <si>
-    <t xml:space="preserve">18.89772605896</t>
+    <t xml:space="preserve">18.8977298736572</t>
   </si>
   <si>
     <t xml:space="preserve">18.8042697906494</t>
   </si>
   <si>
-    <t xml:space="preserve">18.879035949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1780853271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6453857421875</t>
+    <t xml:space="preserve">18.8790378570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1780834197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6453876495361</t>
   </si>
   <si>
     <t xml:space="preserve">17.8556442260742</t>
@@ -1793,19 +1793,19 @@
     <t xml:space="preserve">17.1546878814697</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9817886352539</t>
+    <t xml:space="preserve">16.9817867279053</t>
   </si>
   <si>
     <t xml:space="preserve">18.1360263824463</t>
   </si>
   <si>
-    <t xml:space="preserve">17.949104309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1173324584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2154693603516</t>
+    <t xml:space="preserve">17.9491062164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1173343658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2154674530029</t>
   </si>
   <si>
     <t xml:space="preserve">19.1874580383301</t>
@@ -1814,13 +1814,13 @@
     <t xml:space="preserve">19.0098819732666</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5986824035645</t>
+    <t xml:space="preserve">19.5986843109131</t>
   </si>
   <si>
     <t xml:space="preserve">19.5893363952637</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6454124450684</t>
+    <t xml:space="preserve">19.645414352417</t>
   </si>
   <si>
     <t xml:space="preserve">19.4771862030029</t>
@@ -1832,7 +1832,7 @@
     <t xml:space="preserve">19.5799922943115</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0005645751953</t>
+    <t xml:space="preserve">20.0005626678467</t>
   </si>
   <si>
     <t xml:space="preserve">19.6267204284668</t>
@@ -1862,34 +1862,34 @@
     <t xml:space="preserve">19.206148147583</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0472087860107</t>
+    <t xml:space="preserve">17.0472106933594</t>
   </si>
   <si>
     <t xml:space="preserve">16.7107524871826</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8135566711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5845813751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5471954345703</t>
+    <t xml:space="preserve">16.8135585784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5845794677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5471973419189</t>
   </si>
   <si>
     <t xml:space="preserve">16.5378494262695</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7200965881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4957942962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7528076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5004653930664</t>
+    <t xml:space="preserve">16.7200984954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4957904815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7528095245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.500467300415</t>
   </si>
   <si>
     <t xml:space="preserve">16.4630813598633</t>
@@ -1907,10 +1907,10 @@
     <t xml:space="preserve">16.8415966033936</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6640205383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5331783294678</t>
+    <t xml:space="preserve">16.6640224456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5331764221191</t>
   </si>
   <si>
     <t xml:space="preserve">16.5892524719238</t>
@@ -1919,37 +1919,37 @@
     <t xml:space="preserve">16.6827125549316</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5986003875732</t>
+    <t xml:space="preserve">16.5985984802246</t>
   </si>
   <si>
     <t xml:space="preserve">16.4256973266602</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1266250610352</t>
+    <t xml:space="preserve">16.1266212463379</t>
   </si>
   <si>
     <t xml:space="preserve">16.1593341827393</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4490642547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1920471191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2154102325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4817733764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5238304138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4023303985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2995262145996</t>
+    <t xml:space="preserve">16.4490623474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.192045211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2154121398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4817752838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.523832321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4023323059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.299524307251</t>
   </si>
   <si>
     <t xml:space="preserve">16.5799083709717</t>
@@ -1964,25 +1964,25 @@
     <t xml:space="preserve">17.1967468261719</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2201099395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5752620697021</t>
+    <t xml:space="preserve">17.2201118469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5752601623535</t>
   </si>
   <si>
     <t xml:space="preserve">17.5518970489502</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4163799285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1079616546631</t>
+    <t xml:space="preserve">17.4163780212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1079597473145</t>
   </si>
   <si>
     <t xml:space="preserve">17.1313228607178</t>
   </si>
   <si>
-    <t xml:space="preserve">17.229455947876</t>
+    <t xml:space="preserve">17.2294578552246</t>
   </si>
   <si>
     <t xml:space="preserve">17.4911479949951</t>
@@ -1991,19 +1991,19 @@
     <t xml:space="preserve">17.4397449493408</t>
   </si>
   <si>
-    <t xml:space="preserve">17.453763961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7294731140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6547012329102</t>
+    <t xml:space="preserve">17.4537620544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.729471206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6547031402588</t>
   </si>
   <si>
     <t xml:space="preserve">17.3369369506836</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1453437805176</t>
+    <t xml:space="preserve">17.1453418731689</t>
   </si>
   <si>
     <t xml:space="preserve">16.8462696075439</t>
@@ -2015,13 +2015,13 @@
     <t xml:space="preserve">16.822904586792</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9911613464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9117221832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0378913879395</t>
+    <t xml:space="preserve">17.9911594390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9117202758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0378932952881</t>
   </si>
   <si>
     <t xml:space="preserve">17.6593761444092</t>
@@ -2030,7 +2030,7 @@
     <t xml:space="preserve">17.7948951721191</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6360111236572</t>
+    <t xml:space="preserve">17.6360130310059</t>
   </si>
   <si>
     <t xml:space="preserve">17.3275928497314</t>
@@ -2042,10 +2042,10 @@
     <t xml:space="preserve">17.6266651153564</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5004940032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.869665145874</t>
+    <t xml:space="preserve">17.5004959106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8696632385254</t>
   </si>
   <si>
     <t xml:space="preserve">18.3136005401611</t>
@@ -2063,16 +2063,16 @@
     <t xml:space="preserve">17.9677963256836</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9070472717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.69211769104</t>
+    <t xml:space="preserve">17.9070491790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6921157836914</t>
   </si>
   <si>
     <t xml:space="preserve">18.5051937103271</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3416404724121</t>
+    <t xml:space="preserve">18.3416385650635</t>
   </si>
   <si>
     <t xml:space="preserve">18.5565986633301</t>
@@ -2081,13 +2081,13 @@
     <t xml:space="preserve">18.4397716522217</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5472526550293</t>
+    <t xml:space="preserve">18.5472507476807</t>
   </si>
   <si>
     <t xml:space="preserve">18.3089275360107</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8603439331055</t>
+    <t xml:space="preserve">18.8603458404541</t>
   </si>
   <si>
     <t xml:space="preserve">18.3696784973145</t>
@@ -2108,10 +2108,10 @@
     <t xml:space="preserve">17.5986270904541</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0939674377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.860372543335</t>
+    <t xml:space="preserve">18.0939693450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8603744506836</t>
   </si>
   <si>
     <t xml:space="preserve">20.0472965240479</t>
@@ -2123,16 +2123,16 @@
     <t xml:space="preserve">19.4607124328613</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9735889434814</t>
+    <t xml:space="preserve">19.9735870361328</t>
   </si>
   <si>
     <t xml:space="preserve">19.4132251739502</t>
   </si>
   <si>
-    <t xml:space="preserve">19.204273223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4892082214355</t>
+    <t xml:space="preserve">19.2042751312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4892063140869</t>
   </si>
   <si>
     <t xml:space="preserve">19.1187953948975</t>
@@ -2153,16 +2153,16 @@
     <t xml:space="preserve">17.7273902893066</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8318614959717</t>
+    <t xml:space="preserve">17.8318634033203</t>
   </si>
   <si>
     <t xml:space="preserve">18.3732299804688</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6534099578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1757831573486</t>
+    <t xml:space="preserve">18.6534118652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1757850646973</t>
   </si>
   <si>
     <t xml:space="preserve">19.3657360076904</t>
@@ -2174,7 +2174,7 @@
     <t xml:space="preserve">19.2137718200684</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9810829162598</t>
+    <t xml:space="preserve">18.9810810089111</t>
   </si>
   <si>
     <t xml:space="preserve">18.905101776123</t>
@@ -2189,22 +2189,22 @@
     <t xml:space="preserve">19.6886558532715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9355945587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0210762023926</t>
+    <t xml:space="preserve">19.9355964660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0210742950439</t>
   </si>
   <si>
     <t xml:space="preserve">19.8026294708252</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7171478271484</t>
+    <t xml:space="preserve">19.7171497344971</t>
   </si>
   <si>
     <t xml:space="preserve">19.8121280670166</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7456455230713</t>
+    <t xml:space="preserve">19.7456436157227</t>
   </si>
   <si>
     <t xml:space="preserve">19.926097869873</t>
@@ -2216,13 +2216,13 @@
     <t xml:space="preserve">20.1920337677002</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4674625396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4864616394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2870121002197</t>
+    <t xml:space="preserve">20.4674644470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4864597320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2870101928711</t>
   </si>
   <si>
     <t xml:space="preserve">20.2775135040283</t>
@@ -2249,10 +2249,10 @@
     <t xml:space="preserve">20.0305728912354</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8691120147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9640884399414</t>
+    <t xml:space="preserve">19.8691139221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.96409034729</t>
   </si>
   <si>
     <t xml:space="preserve">20.0020790100098</t>
@@ -2273,7 +2273,7 @@
     <t xml:space="preserve">17.5754261016846</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2952461242676</t>
+    <t xml:space="preserve">17.2952442169189</t>
   </si>
   <si>
     <t xml:space="preserve">17.2762508392334</t>
@@ -2282,7 +2282,7 @@
     <t xml:space="preserve">17.2667541503906</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3854751586914</t>
+    <t xml:space="preserve">17.3854732513428</t>
   </si>
   <si>
     <t xml:space="preserve">17.0198135375977</t>
@@ -2291,13 +2291,13 @@
     <t xml:space="preserve">16.8963451385498</t>
   </si>
   <si>
-    <t xml:space="preserve">17.015064239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.59716796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2837448120117</t>
+    <t xml:space="preserve">17.0150661468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5971660614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2837467193604</t>
   </si>
   <si>
     <t xml:space="preserve">16.8108654022217</t>
@@ -2318,16 +2318,16 @@
     <t xml:space="preserve">16.7348861694336</t>
   </si>
   <si>
-    <t xml:space="preserve">16.948579788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7491302490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.844108581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.497444152832</t>
+    <t xml:space="preserve">16.9485816955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7491321563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8441066741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4974422454834</t>
   </si>
   <si>
     <t xml:space="preserve">16.6683979034424</t>
@@ -2336,7 +2336,7 @@
     <t xml:space="preserve">16.6304092407227</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9248352050781</t>
+    <t xml:space="preserve">16.9248371124268</t>
   </si>
   <si>
     <t xml:space="preserve">17.4329605102539</t>
@@ -2348,7 +2348,7 @@
     <t xml:space="preserve">17.2097682952881</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1385364532471</t>
+    <t xml:space="preserve">17.1385345458984</t>
   </si>
   <si>
     <t xml:space="preserve">17.5231895446777</t>
@@ -2369,13 +2369,13 @@
     <t xml:space="preserve">16.2267570495605</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1887683868408</t>
+    <t xml:space="preserve">16.1887664794922</t>
   </si>
   <si>
     <t xml:space="preserve">16.1365299224854</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3454780578613</t>
+    <t xml:space="preserve">16.34547996521</t>
   </si>
   <si>
     <t xml:space="preserve">16.1840190887451</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">16.1032886505127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0178089141846</t>
+    <t xml:space="preserve">16.0178108215332</t>
   </si>
   <si>
     <t xml:space="preserve">15.4811906814575</t>
@@ -2393,7 +2393,7 @@
     <t xml:space="preserve">15.538179397583</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5619220733643</t>
+    <t xml:space="preserve">15.5619230270386</t>
   </si>
   <si>
     <t xml:space="preserve">15.1725187301636</t>
@@ -2405,16 +2405,16 @@
     <t xml:space="preserve">15.3577222824097</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5904169082642</t>
+    <t xml:space="preserve">15.5904159545898</t>
   </si>
   <si>
     <t xml:space="preserve">15.4716949462891</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6806421279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4052104949951</t>
+    <t xml:space="preserve">15.680643081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4052095413208</t>
   </si>
   <si>
     <t xml:space="preserve">15.324481010437</t>
@@ -2435,25 +2435,25 @@
     <t xml:space="preserve">15.0348014831543</t>
   </si>
   <si>
-    <t xml:space="preserve">15.319730758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9608249664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7661228179932</t>
+    <t xml:space="preserve">15.3197317123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.960823059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7661218643188</t>
   </si>
   <si>
     <t xml:space="preserve">15.8800916671753</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9085855484009</t>
+    <t xml:space="preserve">15.9085874557495</t>
   </si>
   <si>
     <t xml:space="preserve">15.922833442688</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1412811279297</t>
+    <t xml:space="preserve">16.1412792205811</t>
   </si>
   <si>
     <t xml:space="preserve">16.1745204925537</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">16.4024658203125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5781726837158</t>
+    <t xml:space="preserve">16.5781707763672</t>
   </si>
   <si>
     <t xml:space="preserve">16.5734233856201</t>
@@ -2477,7 +2477,7 @@
     <t xml:space="preserve">16.9723262786865</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4404544830322</t>
+    <t xml:space="preserve">16.4404563903809</t>
   </si>
   <si>
     <t xml:space="preserve">16.3074893951416</t>
@@ -2498,7 +2498,7 @@
     <t xml:space="preserve">17.1290378570557</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1860237121582</t>
+    <t xml:space="preserve">17.1860218048096</t>
   </si>
   <si>
     <t xml:space="preserve">16.6873950958252</t>
@@ -2516,7 +2516,7 @@
     <t xml:space="preserve">17.3474826812744</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2477588653564</t>
+    <t xml:space="preserve">17.2477569580078</t>
   </si>
   <si>
     <t xml:space="preserve">17.3379859924316</t>
@@ -2537,25 +2537,25 @@
     <t xml:space="preserve">17.8033714294434</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1167964935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8556060791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8081188201904</t>
+    <t xml:space="preserve">18.1167945861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8556079864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8081207275391</t>
   </si>
   <si>
     <t xml:space="preserve">18.0028228759766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6704044342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.622917175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6799011230469</t>
+    <t xml:space="preserve">17.6704025268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6229152679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6799030303955</t>
   </si>
   <si>
     <t xml:space="preserve">17.9885749816895</t>
@@ -2564,19 +2564,19 @@
     <t xml:space="preserve">18.4207191467285</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0930500030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9030952453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8508605957031</t>
+    <t xml:space="preserve">18.0930480957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.90309715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8508586883545</t>
   </si>
   <si>
     <t xml:space="preserve">17.2620029449463</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2287635803223</t>
+    <t xml:space="preserve">17.2287616729736</t>
   </si>
   <si>
     <t xml:space="preserve">17.0957946777344</t>
@@ -2588,13 +2588,13 @@
     <t xml:space="preserve">16.6161632537842</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5924167633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8610982894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2694988250732</t>
+    <t xml:space="preserve">16.5924186706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8611001968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2694969177246</t>
   </si>
   <si>
     <t xml:space="preserve">16.2979927062988</t>
@@ -2603,7 +2603,7 @@
     <t xml:space="preserve">16.1175346374512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8468523025513</t>
+    <t xml:space="preserve">15.8468503952026</t>
   </si>
   <si>
     <t xml:space="preserve">16.3217353820801</t>
@@ -2612,31 +2612,31 @@
     <t xml:space="preserve">16.0842933654785</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7803678512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7186336517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3434762954712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9845695495605</t>
+    <t xml:space="preserve">15.7803688049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7186326980591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3434772491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9845676422119</t>
   </si>
   <si>
     <t xml:space="preserve">15.747127532959</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6046619415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7043867111206</t>
+    <t xml:space="preserve">15.604660987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7043857574463</t>
   </si>
   <si>
     <t xml:space="preserve">15.8848428726196</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5429258346558</t>
+    <t xml:space="preserve">15.5429267883301</t>
   </si>
   <si>
     <t xml:space="preserve">15.1582717895508</t>
@@ -2651,7 +2651,7 @@
     <t xml:space="preserve">14.1420221328735</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6054029464722</t>
+    <t xml:space="preserve">13.6054039001465</t>
   </si>
   <si>
     <t xml:space="preserve">13.5721616744995</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">13.0497894287109</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9738082885742</t>
+    <t xml:space="preserve">12.9738092422485</t>
   </si>
   <si>
     <t xml:space="preserve">12.3184700012207</t>
@@ -2678,13 +2678,13 @@
     <t xml:space="preserve">10.6563787460327</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7845973968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08166694641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65437602996826</t>
+    <t xml:space="preserve">10.7845964431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08166599273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65437507629395</t>
   </si>
   <si>
     <t xml:space="preserve">10.0057888031006</t>
@@ -2744,34 +2744,34 @@
     <t xml:space="preserve">11.9765529632568</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4541826248169</t>
+    <t xml:space="preserve">11.4541835784912</t>
   </si>
   <si>
     <t xml:space="preserve">11.2927227020264</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5396614074707</t>
+    <t xml:space="preserve">11.5396604537964</t>
   </si>
   <si>
     <t xml:space="preserve">10.8178396224976</t>
   </si>
   <si>
-    <t xml:space="preserve">10.399941444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4474296569824</t>
+    <t xml:space="preserve">10.3999423980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4474306106567</t>
   </si>
   <si>
     <t xml:space="preserve">10.3809471130371</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7323598861694</t>
+    <t xml:space="preserve">10.7323608398438</t>
   </si>
   <si>
     <t xml:space="preserve">10.9128150939941</t>
   </si>
   <si>
-    <t xml:space="preserve">10.722861289978</t>
+    <t xml:space="preserve">10.7228622436523</t>
   </si>
   <si>
     <t xml:space="preserve">10.3049659729004</t>
@@ -2786,7 +2786,7 @@
     <t xml:space="preserve">10.3429565429688</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4094400405884</t>
+    <t xml:space="preserve">10.4094390869141</t>
   </si>
   <si>
     <t xml:space="preserve">10.2574768066406</t>
@@ -2831,22 +2831,22 @@
     <t xml:space="preserve">13.2872314453125</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1542654037476</t>
+    <t xml:space="preserve">13.1542644500732</t>
   </si>
   <si>
     <t xml:space="preserve">12.8218460083008</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8815784454346</t>
+    <t xml:space="preserve">11.8815774917603</t>
   </si>
   <si>
     <t xml:space="preserve">11.7771024703979</t>
   </si>
   <si>
-    <t xml:space="preserve">12.062032699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1190185546875</t>
+    <t xml:space="preserve">12.0620336532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1190195083618</t>
   </si>
   <si>
     <t xml:space="preserve">12.2899770736694</t>
@@ -2858,22 +2858,22 @@
     <t xml:space="preserve">12.7078742980957</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5749063491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5844039916992</t>
+    <t xml:space="preserve">12.5749073028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5844049453735</t>
   </si>
   <si>
     <t xml:space="preserve">11.9955492019653</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8055963516235</t>
+    <t xml:space="preserve">11.8055953979492</t>
   </si>
   <si>
     <t xml:space="preserve">11.5111684799194</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7296142578125</t>
+    <t xml:space="preserve">11.7296152114868</t>
   </si>
   <si>
     <t xml:space="preserve">11.4446849822998</t>
@@ -2882,7 +2882,7 @@
     <t xml:space="preserve">11.5206661224365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7581081390381</t>
+    <t xml:space="preserve">11.7581071853638</t>
   </si>
   <si>
     <t xml:space="preserve">11.5871486663818</t>
@@ -2897,13 +2897,13 @@
     <t xml:space="preserve">10.9887971878052</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1787509918213</t>
+    <t xml:space="preserve">11.1787519454956</t>
   </si>
   <si>
     <t xml:space="preserve">11.2262382507324</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2452344894409</t>
+    <t xml:space="preserve">11.2452335357666</t>
   </si>
   <si>
     <t xml:space="preserve">11.1027679443359</t>
@@ -2912,13 +2912,13 @@
     <t xml:space="preserve">11.1312618255615</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0267877578735</t>
+    <t xml:space="preserve">11.0267868041992</t>
   </si>
   <si>
     <t xml:space="preserve">11.0837736129761</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8368339538574</t>
+    <t xml:space="preserve">10.8368349075317</t>
   </si>
   <si>
     <t xml:space="preserve">11.0552806854248</t>
@@ -2936,22 +2936,22 @@
     <t xml:space="preserve">10.4379320144653</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3619518280029</t>
+    <t xml:space="preserve">10.3619508743286</t>
   </si>
   <si>
     <t xml:space="preserve">11.644136428833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3307123184204</t>
+    <t xml:space="preserve">11.3307132720947</t>
   </si>
   <si>
     <t xml:space="preserve">11.0932712554932</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9603042602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.760853767395</t>
+    <t xml:space="preserve">10.9603052139282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7608528137207</t>
   </si>
   <si>
     <t xml:space="preserve">10.7798490524292</t>
@@ -2963,7 +2963,7 @@
     <t xml:space="preserve">11.6156425476074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4636793136597</t>
+    <t xml:space="preserve">11.463680267334</t>
   </si>
   <si>
     <t xml:space="preserve">11.3971967697144</t>
@@ -2972,7 +2972,7 @@
     <t xml:space="preserve">11.5016708374023</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7960977554321</t>
+    <t xml:space="preserve">11.7960987091064</t>
   </si>
   <si>
     <t xml:space="preserve">11.4731779098511</t>
@@ -2996,7 +2996,7 @@
     <t xml:space="preserve">11.6061458587646</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1095209121704</t>
+    <t xml:space="preserve">12.1095218658447</t>
   </si>
   <si>
     <t xml:space="preserve">12.0145444869995</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">11.957558631897</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9860506057739</t>
+    <t xml:space="preserve">11.9860515594482</t>
   </si>
   <si>
     <t xml:space="preserve">12.1285171508789</t>
@@ -3023,10 +3023,10 @@
     <t xml:space="preserve">12.6034002304077</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5464143753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2044982910156</t>
+    <t xml:space="preserve">12.5464134216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2044973373413</t>
   </si>
   <si>
     <t xml:space="preserve">12.4039497375488</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">12.8978281021118</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1949996948242</t>
+    <t xml:space="preserve">12.1950006484985</t>
   </si>
   <si>
     <t xml:space="preserve">11.8910760879517</t>
@@ -3056,7 +3056,7 @@
     <t xml:space="preserve">10.7988433837891</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0647773742676</t>
+    <t xml:space="preserve">11.0647783279419</t>
   </si>
   <si>
     <t xml:space="preserve">11.3592052459717</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">13.7146253585815</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9235744476318</t>
+    <t xml:space="preserve">13.9235754013062</t>
   </si>
   <si>
     <t xml:space="preserve">13.9330730438232</t>
@@ -3095,13 +3095,13 @@
     <t xml:space="preserve">14.6264009475708</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3129787445068</t>
+    <t xml:space="preserve">14.3129796981812</t>
   </si>
   <si>
     <t xml:space="preserve">14.1515188217163</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2464952468872</t>
+    <t xml:space="preserve">14.2464962005615</t>
   </si>
   <si>
     <t xml:space="preserve">14.4269514083862</t>
@@ -3113,7 +3113,7 @@
     <t xml:space="preserve">14.9113321304321</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4934349060059</t>
+    <t xml:space="preserve">14.4934358596802</t>
   </si>
   <si>
     <t xml:space="preserve">14.3509693145752</t>
@@ -3131,13 +3131,13 @@
     <t xml:space="preserve">14.8828401565552</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8543462753296</t>
+    <t xml:space="preserve">14.8543472290039</t>
   </si>
   <si>
     <t xml:space="preserve">14.7593698501587</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3794622421265</t>
+    <t xml:space="preserve">14.3794631958008</t>
   </si>
   <si>
     <t xml:space="preserve">14.5694160461426</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">14.6074066162109</t>
   </si>
   <si>
-    <t xml:space="preserve">15.110782623291</t>
+    <t xml:space="preserve">15.1107835769653</t>
   </si>
   <si>
     <t xml:space="preserve">15.0632944107056</t>
@@ -3161,22 +3161,22 @@
     <t xml:space="preserve">14.7688674926758</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7118806838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5884103775024</t>
+    <t xml:space="preserve">14.7118816375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5884113311768</t>
   </si>
   <si>
     <t xml:space="preserve">14.5789136886597</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4079561233521</t>
+    <t xml:space="preserve">14.4079551696777</t>
   </si>
   <si>
     <t xml:space="preserve">14.5504207611084</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5314264297485</t>
+    <t xml:space="preserve">14.5314254760742</t>
   </si>
   <si>
     <t xml:space="preserve">13.9615650177002</t>
@@ -3188,22 +3188,22 @@
     <t xml:space="preserve">14.4459466934204</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2912397384644</t>
+    <t xml:space="preserve">15.29123878479</t>
   </si>
   <si>
     <t xml:space="preserve">14.683388710022</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0537967681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8041124343872</t>
+    <t xml:space="preserve">15.0537977218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8041114807129</t>
   </si>
   <si>
     <t xml:space="preserve">15.6711444854736</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2627458572388</t>
+    <t xml:space="preserve">15.2627449035645</t>
   </si>
   <si>
     <t xml:space="preserve">14.9588203430176</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">14.6359004974365</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4364490509033</t>
+    <t xml:space="preserve">14.4364500045776</t>
   </si>
   <si>
     <t xml:space="preserve">14.7403745651245</t>
@@ -3230,7 +3230,7 @@
     <t xml:space="preserve">15.0822906494141</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9778156280518</t>
+    <t xml:space="preserve">14.9778165817261</t>
   </si>
   <si>
     <t xml:space="preserve">14.6928863525391</t>
@@ -3245,19 +3245,19 @@
     <t xml:space="preserve">15.2057600021362</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1202802658081</t>
+    <t xml:space="preserve">15.1202812194824</t>
   </si>
   <si>
     <t xml:space="preserve">15.0917882919312</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1012849807739</t>
+    <t xml:space="preserve">15.1012859344482</t>
   </si>
   <si>
     <t xml:space="preserve">14.8448476791382</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9873123168945</t>
+    <t xml:space="preserve">14.9873132705688</t>
   </si>
   <si>
     <t xml:space="preserve">15.8705949783325</t>
@@ -3266,7 +3266,7 @@
     <t xml:space="preserve">16.0225601196289</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0320568084717</t>
+    <t xml:space="preserve">16.032054901123</t>
   </si>
   <si>
     <t xml:space="preserve">15.8231077194214</t>
@@ -3275,7 +3275,7 @@
     <t xml:space="preserve">15.9370803833008</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7376298904419</t>
+    <t xml:space="preserve">15.7376289367676</t>
   </si>
   <si>
     <t xml:space="preserve">15.4906892776489</t>
@@ -3287,34 +3287,34 @@
     <t xml:space="preserve">15.3102350234985</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3672199249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3387269973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6996374130249</t>
+    <t xml:space="preserve">15.3672208786011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3387260437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6996393203735</t>
   </si>
   <si>
     <t xml:space="preserve">15.6853904724121</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6189079284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4289560317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6379041671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7396335601807</t>
+    <t xml:space="preserve">15.6189069747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.428955078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.637903213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.739631652832</t>
   </si>
   <si>
     <t xml:space="preserve">16.8678512573242</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8726005554199</t>
+    <t xml:space="preserve">16.8725986480713</t>
   </si>
   <si>
     <t xml:space="preserve">16.4784469604492</t>
@@ -3326,13 +3326,13 @@
     <t xml:space="preserve">17.513692855835</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4567050933838</t>
+    <t xml:space="preserve">17.4567031860352</t>
   </si>
   <si>
     <t xml:space="preserve">17.0388088226318</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2904968261719</t>
+    <t xml:space="preserve">17.2904987335205</t>
   </si>
   <si>
     <t xml:space="preserve">17.0815467834473</t>
@@ -3350,7 +3350,7 @@
     <t xml:space="preserve">17.4614543914795</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4187145233154</t>
+    <t xml:space="preserve">17.4187164306641</t>
   </si>
   <si>
     <t xml:space="preserve">18.2117691040039</t>
@@ -3359,13 +3359,13 @@
     <t xml:space="preserve">18.3589839935303</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1975231170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1500358581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2307643890381</t>
+    <t xml:space="preserve">18.1975250244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1500377655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2307662963867</t>
   </si>
   <si>
     <t xml:space="preserve">18.0360641479492</t>
@@ -3395,25 +3395,25 @@
     <t xml:space="preserve">18.3019981384277</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3542366027832</t>
+    <t xml:space="preserve">18.3542346954346</t>
   </si>
   <si>
     <t xml:space="preserve">18.3969745635986</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5299434661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2972469329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1690292358398</t>
+    <t xml:space="preserve">18.5299415588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.297248840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1690311431885</t>
   </si>
   <si>
     <t xml:space="preserve">18.1832790374756</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4444637298584</t>
+    <t xml:space="preserve">18.444465637207</t>
   </si>
   <si>
     <t xml:space="preserve">18.8956031799316</t>
@@ -3428,7 +3428,7 @@
     <t xml:space="preserve">18.3352394104004</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8461112976074</t>
+    <t xml:space="preserve">17.8461093902588</t>
   </si>
   <si>
     <t xml:space="preserve">17.1527805328369</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">16.7253875732422</t>
   </si>
   <si>
-    <t xml:space="preserve">16.877347946167</t>
+    <t xml:space="preserve">16.8773498535156</t>
   </si>
   <si>
     <t xml:space="preserve">16.4214611053467</t>
@@ -3473,13 +3473,13 @@
     <t xml:space="preserve">16.4736976623535</t>
   </si>
   <si>
-    <t xml:space="preserve">16.169771194458</t>
+    <t xml:space="preserve">16.1697731018066</t>
   </si>
   <si>
     <t xml:space="preserve">16.0463027954102</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0368041992188</t>
+    <t xml:space="preserve">16.0368061065674</t>
   </si>
   <si>
     <t xml:space="preserve">15.9988136291504</t>
@@ -3488,7 +3488,7 @@
     <t xml:space="preserve">16.2600021362305</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0652980804443</t>
+    <t xml:space="preserve">16.065299987793</t>
   </si>
   <si>
     <t xml:space="preserve">16.0510520935059</t>
@@ -3509,28 +3509,28 @@
     <t xml:space="preserve">17.6609058380127</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0008182525635</t>
+    <t xml:space="preserve">17.0008163452148</t>
   </si>
   <si>
     <t xml:space="preserve">16.6731491088867</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5164375305176</t>
+    <t xml:space="preserve">16.5164356231689</t>
   </si>
   <si>
     <t xml:space="preserve">15.7328805923462</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7423782348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1460266113281</t>
+    <t xml:space="preserve">15.7423791885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1460285186768</t>
   </si>
   <si>
     <t xml:space="preserve">15.9275808334351</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9703216552734</t>
+    <t xml:space="preserve">15.9703235626221</t>
   </si>
   <si>
     <t xml:space="preserve">16.6541538238525</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">18.0123195648193</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8698558807373</t>
+    <t xml:space="preserve">17.8698539733887</t>
   </si>
   <si>
     <t xml:space="preserve">18.0693054199219</t>
@@ -3557,10 +3557,10 @@
     <t xml:space="preserve">16.7206382751465</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9628295898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9438304901123</t>
+    <t xml:space="preserve">16.9628276824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9438323974609</t>
   </si>
   <si>
     <t xml:space="preserve">16.8298606872559</t>
@@ -3572,7 +3572,7 @@
     <t xml:space="preserve">16.8346099853516</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0435562133789</t>
+    <t xml:space="preserve">17.0435581207275</t>
   </si>
   <si>
     <t xml:space="preserve">16.8013687133789</t>
@@ -3593,7 +3593,7 @@
     <t xml:space="preserve">17.4662036895752</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7178936004639</t>
+    <t xml:space="preserve">17.7178916931152</t>
   </si>
   <si>
     <t xml:space="preserve">17.7748775482178</t>
@@ -3605,7 +3605,7 @@
     <t xml:space="preserve">18.1405372619629</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7008991241455</t>
+    <t xml:space="preserve">18.7009010314941</t>
   </si>
   <si>
     <t xml:space="preserve">18.7911262512207</t>
@@ -3623,7 +3623,7 @@
     <t xml:space="preserve">18.5536861419678</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7626323699951</t>
+    <t xml:space="preserve">18.7626342773438</t>
   </si>
   <si>
     <t xml:space="preserve">19.0903053283691</t>
@@ -3647,13 +3647,13 @@
     <t xml:space="preserve">19.6221733093262</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1377906799316</t>
+    <t xml:space="preserve">19.1377925872803</t>
   </si>
   <si>
     <t xml:space="preserve">19.6316699981689</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4579677581787</t>
+    <t xml:space="preserve">20.4579696655273</t>
   </si>
   <si>
     <t xml:space="preserve">20.6289253234863</t>
@@ -3662,19 +3662,19 @@
     <t xml:space="preserve">21.0373268127441</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4457225799561</t>
+    <t xml:space="preserve">21.4457244873047</t>
   </si>
   <si>
     <t xml:space="preserve">20.9898376464844</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7523975372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6384239196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1635398864746</t>
+    <t xml:space="preserve">20.7523956298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6384220123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1635417938232</t>
   </si>
   <si>
     <t xml:space="preserve">20.0970554351807</t>
@@ -3683,13 +3683,13 @@
     <t xml:space="preserve">20.7903861999512</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7144031524658</t>
+    <t xml:space="preserve">20.7144050598145</t>
   </si>
   <si>
     <t xml:space="preserve">21.0278282165527</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0183296203613</t>
+    <t xml:space="preserve">21.0183277130127</t>
   </si>
   <si>
     <t xml:space="preserve">21.094310760498</t>
@@ -3698,13 +3698,13 @@
     <t xml:space="preserve">21.4172306060791</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3982353210449</t>
+    <t xml:space="preserve">21.3982372283936</t>
   </si>
   <si>
     <t xml:space="preserve">21.7021617889404</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5691947937012</t>
+    <t xml:space="preserve">21.5691928863525</t>
   </si>
   <si>
     <t xml:space="preserve">22.0820693969727</t>
@@ -3713,7 +3713,7 @@
     <t xml:space="preserve">21.5976867675781</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6261806488037</t>
+    <t xml:space="preserve">21.6261825561523</t>
   </si>
   <si>
     <t xml:space="preserve">19.4797096252441</t>
@@ -3731,10 +3731,10 @@
     <t xml:space="preserve">18.7103977203369</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0550594329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4946975708008</t>
+    <t xml:space="preserve">18.055061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4946956634521</t>
   </si>
   <si>
     <t xml:space="preserve">18.2212677001953</t>
@@ -3743,10 +3743,10 @@
     <t xml:space="preserve">17.9743270874023</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5916786193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5394401550293</t>
+    <t xml:space="preserve">18.5916767120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5394420623779</t>
   </si>
   <si>
     <t xml:space="preserve">18.0977993011475</t>
@@ -3755,7 +3755,7 @@
     <t xml:space="preserve">18.0503101348877</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2830028533936</t>
+    <t xml:space="preserve">18.2830009460449</t>
   </si>
   <si>
     <t xml:space="preserve">18.1927757263184</t>
@@ -3779,19 +3779,19 @@
     <t xml:space="preserve">18.5964260101318</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7768821716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9220905303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6581611633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4492130279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6324138641357</t>
+    <t xml:space="preserve">18.7768802642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9220924377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6581592559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4492111206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6324157714844</t>
   </si>
   <si>
     <t xml:space="preserve">17.7368869781494</t>
@@ -3806,13 +3806,13 @@
     <t xml:space="preserve">14.8306016921997</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5076818466187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9133348464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3529739379883</t>
+    <t xml:space="preserve">14.5076808929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9133329391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3529748916626</t>
   </si>
   <si>
     <t xml:space="preserve">15.457447052002</t>
@@ -3821,10 +3821,10 @@
     <t xml:space="preserve">14.8733415603638</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5856657028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8136100769043</t>
+    <t xml:space="preserve">15.5856666564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.81360912323</t>
   </si>
   <si>
     <t xml:space="preserve">15.5334281921387</t>
@@ -3833,16 +3833,16 @@
     <t xml:space="preserve">15.2390012741089</t>
   </si>
   <si>
-    <t xml:space="preserve">15.253246307373</t>
+    <t xml:space="preserve">15.2532472610474</t>
   </si>
   <si>
     <t xml:space="preserve">15.5191831588745</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8278589248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7681255340576</t>
+    <t xml:space="preserve">15.8278579711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7681274414062</t>
   </si>
   <si>
     <t xml:space="preserve">16.316987991333</t>
@@ -3854,7 +3854,7 @@
     <t xml:space="preserve">15.0253038406372</t>
   </si>
   <si>
-    <t xml:space="preserve">15.633152961731</t>
+    <t xml:space="preserve">15.6331539154053</t>
   </si>
   <si>
     <t xml:space="preserve">15.6521482467651</t>
@@ -3863,7 +3863,7 @@
     <t xml:space="preserve">15.8895902633667</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5096855163574</t>
+    <t xml:space="preserve">15.5096845626831</t>
   </si>
   <si>
     <t xml:space="preserve">14.7308769226074</t>
@@ -3872,7 +3872,7 @@
     <t xml:space="preserve">14.8638439178467</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1392765045166</t>
+    <t xml:space="preserve">15.1392755508423</t>
   </si>
   <si>
     <t xml:space="preserve">15.7851181030273</t>
@@ -3881,7 +3881,7 @@
     <t xml:space="preserve">14.3034820556641</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3224763870239</t>
+    <t xml:space="preserve">14.3224773406982</t>
   </si>
   <si>
     <t xml:space="preserve">13.8285989761353</t>
@@ -3896,7 +3896,7 @@
     <t xml:space="preserve">14.1990079879761</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0158071517944</t>
+    <t xml:space="preserve">15.0158061981201</t>
   </si>
   <si>
     <t xml:space="preserve">14.5219278335571</t>
@@ -72186,7 +72186,7 @@
     </row>
     <row r="2532">
       <c r="A2532" s="1" t="n">
-        <v>46003.6937384259</v>
+        <v>46003.3333333333</v>
       </c>
       <c r="B2532" t="n">
         <v>347101</v>
@@ -72207,6 +72207,32 @@
         <v>2009</v>
       </c>
       <c r="H2532" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2533">
+      <c r="A2533" s="1" t="n">
+        <v>46006.6910300926</v>
+      </c>
+      <c r="B2533" t="n">
+        <v>793066</v>
+      </c>
+      <c r="C2533" t="n">
+        <v>8.42000007629395</v>
+      </c>
+      <c r="D2533" t="n">
+        <v>7.99499988555908</v>
+      </c>
+      <c r="E2533" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2533" t="n">
+        <v>8.08500003814697</v>
+      </c>
+      <c r="G2533" t="s">
+        <v>1844</v>
+      </c>
+      <c r="H2533" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2763519287109</t>
+    <t xml:space="preserve">18.2763500213623</t>
   </si>
   <si>
     <t xml:space="preserve">SFER.MI</t>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">17.4978828430176</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9401931762695</t>
+    <t xml:space="preserve">17.9401950836182</t>
   </si>
   <si>
     <t xml:space="preserve">17.683650970459</t>
@@ -62,34 +62,34 @@
     <t xml:space="preserve">19.4086723327637</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1344356536865</t>
+    <t xml:space="preserve">19.1344375610352</t>
   </si>
   <si>
     <t xml:space="preserve">18.8425121307373</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4621257781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2851982116699</t>
+    <t xml:space="preserve">18.4621238708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2851963043213</t>
   </si>
   <si>
     <t xml:space="preserve">18.0994262695312</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6394195556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5686492919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1878871917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4798126220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2232761383057</t>
+    <t xml:space="preserve">17.6394233703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5686531066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1878890991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4798164367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.223274230957</t>
   </si>
   <si>
     <t xml:space="preserve">17.7632675170898</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">18.3913516998291</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6744346618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9578857421875</t>
+    <t xml:space="preserve">18.6744327545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9578838348389</t>
   </si>
   <si>
     <t xml:space="preserve">18.2055816650391</t>
@@ -113,25 +113,25 @@
     <t xml:space="preserve">18.0817356109619</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3563423156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9051837921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1617240905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6486415863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0201854705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4890365600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6305751800537</t>
+    <t xml:space="preserve">17.3563404083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9051856994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1617221832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6486434936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0201835632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.48903465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6305770874023</t>
   </si>
   <si>
     <t xml:space="preserve">18.4090442657471</t>
@@ -161,10 +161,10 @@
     <t xml:space="preserve">19.0017433166504</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8513584136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3113613128662</t>
+    <t xml:space="preserve">18.8513565063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3113632202148</t>
   </si>
   <si>
     <t xml:space="preserve">19.992525100708</t>
@@ -176,10 +176,10 @@
     <t xml:space="preserve">19.7271347045898</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3379001617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6475162506104</t>
+    <t xml:space="preserve">19.3379039764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.647518157959</t>
   </si>
   <si>
     <t xml:space="preserve">19.9836769104004</t>
@@ -188,10 +188,10 @@
     <t xml:space="preserve">19.1167449951172</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4440536499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0367546081543</t>
+    <t xml:space="preserve">19.444055557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0367565155029</t>
   </si>
   <si>
     <t xml:space="preserve">20.1782932281494</t>
@@ -200,22 +200,22 @@
     <t xml:space="preserve">19.4971332550049</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4705944061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9663581848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4794445037842</t>
+    <t xml:space="preserve">19.4705963134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9663600921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4794425964355</t>
   </si>
   <si>
     <t xml:space="preserve">19.9129085540771</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8686752319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4175186157227</t>
+    <t xml:space="preserve">19.8686771392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4175205230713</t>
   </si>
   <si>
     <t xml:space="preserve">18.8690509796143</t>
@@ -224,10 +224,10 @@
     <t xml:space="preserve">18.8336658477783</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5152015686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9309768676758</t>
+    <t xml:space="preserve">18.5151996612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9309730529785</t>
   </si>
   <si>
     <t xml:space="preserve">18.8955898284912</t>
@@ -236,7 +236,7 @@
     <t xml:space="preserve">18.5240478515625</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9486675262451</t>
+    <t xml:space="preserve">18.9486656188965</t>
   </si>
   <si>
     <t xml:space="preserve">18.7982807159424</t>
@@ -245,22 +245,22 @@
     <t xml:space="preserve">18.8778972625732</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2936668395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8071250915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3205795288086</t>
+    <t xml:space="preserve">19.2936706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8071269989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3205814361572</t>
   </si>
   <si>
     <t xml:space="preserve">18.3648128509521</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8251953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0640411376953</t>
+    <t xml:space="preserve">17.8251914978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0640392303467</t>
   </si>
   <si>
     <t xml:space="preserve">18.3117370605469</t>
@@ -275,22 +275,22 @@
     <t xml:space="preserve">17.7190380096436</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4448051452637</t>
+    <t xml:space="preserve">17.444803237915</t>
   </si>
   <si>
     <t xml:space="preserve">17.1440315246582</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5509586334229</t>
+    <t xml:space="preserve">17.5509605407715</t>
   </si>
   <si>
     <t xml:space="preserve">17.9844245910645</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4182682037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9313488006592</t>
+    <t xml:space="preserve">17.4182662963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9313468933105</t>
   </si>
   <si>
     <t xml:space="preserve">17.7367286682129</t>
@@ -302,16 +302,16 @@
     <t xml:space="preserve">17.5939388275146</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8112602233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7025985717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6482677459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.530553817749</t>
+    <t xml:space="preserve">17.8112564086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7025966644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.648265838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5305519104004</t>
   </si>
   <si>
     <t xml:space="preserve">17.4128360748291</t>
@@ -320,10 +320,10 @@
     <t xml:space="preserve">17.3041763305664</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4762229919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4309463500977</t>
+    <t xml:space="preserve">17.4762210845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.430944442749</t>
   </si>
   <si>
     <t xml:space="preserve">17.4852771759033</t>
@@ -338,13 +338,13 @@
     <t xml:space="preserve">17.150239944458</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7155990600586</t>
+    <t xml:space="preserve">16.71559715271</t>
   </si>
   <si>
     <t xml:space="preserve">16.5435562133789</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0415802001953</t>
+    <t xml:space="preserve">17.0415821075439</t>
   </si>
   <si>
     <t xml:space="preserve">17.0778007507324</t>
@@ -368,34 +368,34 @@
     <t xml:space="preserve">16.8514251708984</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3896198272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6793785095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.262845993042</t>
+    <t xml:space="preserve">16.3896179199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6793804168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2628440856934</t>
   </si>
   <si>
     <t xml:space="preserve">16.5254440307617</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6069374084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8061504364014</t>
+    <t xml:space="preserve">16.6069412231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8061485290527</t>
   </si>
   <si>
     <t xml:space="preserve">16.8242607116699</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0726909637451</t>
+    <t xml:space="preserve">16.0726890563965</t>
   </si>
   <si>
     <t xml:space="preserve">15.8734817504883</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3624515533447</t>
+    <t xml:space="preserve">16.3624496459961</t>
   </si>
   <si>
     <t xml:space="preserve">16.4439468383789</t>
@@ -404,10 +404,10 @@
     <t xml:space="preserve">16.69748878479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0959072113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1321296691895</t>
+    <t xml:space="preserve">17.095911026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1321315765381</t>
   </si>
   <si>
     <t xml:space="preserve">17.086856842041</t>
@@ -419,37 +419,37 @@
     <t xml:space="preserve">17.3403949737549</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9018096923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1372394561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9289722442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.771089553833</t>
+    <t xml:space="preserve">17.9018077850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1372413635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9289741516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7710914611816</t>
   </si>
   <si>
     <t xml:space="preserve">18.6352672576904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0699081420898</t>
+    <t xml:space="preserve">19.0699062347412</t>
   </si>
   <si>
     <t xml:space="preserve">19.2147884368896</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6262092590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.499439239502</t>
+    <t xml:space="preserve">18.6262111663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4994430541992</t>
   </si>
   <si>
     <t xml:space="preserve">18.2187366485596</t>
   </si>
   <si>
-    <t xml:space="preserve">18.716760635376</t>
+    <t xml:space="preserve">18.7167625427246</t>
   </si>
   <si>
     <t xml:space="preserve">18.5809364318848</t>
@@ -461,10 +461,10 @@
     <t xml:space="preserve">18.8073139190674</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9431381225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0427436828613</t>
+    <t xml:space="preserve">18.9431400299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0427417755127</t>
   </si>
   <si>
     <t xml:space="preserve">18.6624317169189</t>
@@ -476,22 +476,22 @@
     <t xml:space="preserve">18.6171550750732</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7529811859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9703044891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6805419921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6080989837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6533794403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5175514221191</t>
+    <t xml:space="preserve">18.7529830932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9703025817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6805400848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6081008911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.653377532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5175495147705</t>
   </si>
   <si>
     <t xml:space="preserve">18.870698928833</t>
@@ -500,22 +500,22 @@
     <t xml:space="preserve">18.6986522674561</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1061305999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9210834503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6947040557861</t>
+    <t xml:space="preserve">19.1061267852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9210815429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6947059631348</t>
   </si>
   <si>
     <t xml:space="preserve">19.5588798522949</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4592781066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3143939971924</t>
+    <t xml:space="preserve">19.4592742919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.314395904541</t>
   </si>
   <si>
     <t xml:space="preserve">18.8888092041016</t>
@@ -527,22 +527,22 @@
     <t xml:space="preserve">19.1604595184326</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9391937255859</t>
+    <t xml:space="preserve">19.9391918182373</t>
   </si>
   <si>
     <t xml:space="preserve">20.4553298950195</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3557262420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3104476928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3919429779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4643859863281</t>
+    <t xml:space="preserve">20.3557224273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3104515075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3919448852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4643840789795</t>
   </si>
   <si>
     <t xml:space="preserve">20.6907615661621</t>
@@ -557,31 +557,31 @@
     <t xml:space="preserve">20.4010009765625</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1021823883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5277690887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3647804260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.545877456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7541427612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4191093444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0116329193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2651710510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3285579681396</t>
+    <t xml:space="preserve">20.1021842956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5277709960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3647766113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5458793640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7541484832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4191074371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0116348266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.265172958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3285598754883</t>
   </si>
   <si>
     <t xml:space="preserve">20.03879737854</t>
@@ -590,19 +590,19 @@
     <t xml:space="preserve">20.1474590301514</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2289524078369</t>
+    <t xml:space="preserve">20.2289543151855</t>
   </si>
   <si>
     <t xml:space="preserve">20.500602722168</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5639896392822</t>
+    <t xml:space="preserve">20.5639877319336</t>
   </si>
   <si>
     <t xml:space="preserve">20.1836795806885</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5498275756836</t>
+    <t xml:space="preserve">19.549825668335</t>
   </si>
   <si>
     <t xml:space="preserve">19.4140014648438</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">19.5045528411865</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7218742370605</t>
+    <t xml:space="preserve">19.7218723297119</t>
   </si>
   <si>
     <t xml:space="preserve">19.7943134307861</t>
@@ -620,28 +620,28 @@
     <t xml:space="preserve">19.5226593017578</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8305339813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9120254516602</t>
+    <t xml:space="preserve">19.8305320739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9120235443115</t>
   </si>
   <si>
     <t xml:space="preserve">19.7490367889404</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0919628143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3002300262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3273944854736</t>
+    <t xml:space="preserve">18.0919609069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3002281188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3273963928223</t>
   </si>
   <si>
     <t xml:space="preserve">18.2459011077881</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0104675292969</t>
+    <t xml:space="preserve">18.0104694366455</t>
   </si>
   <si>
     <t xml:space="preserve">17.7388191223145</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">17.8565330505371</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8203125</t>
+    <t xml:space="preserve">17.8203144073486</t>
   </si>
   <si>
     <t xml:space="preserve">17.6392116546631</t>
@@ -662,13 +662,13 @@
     <t xml:space="preserve">18.3907814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">19.151403427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2872314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3958892822266</t>
+    <t xml:space="preserve">19.1514015197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2872295379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3958911895752</t>
   </si>
   <si>
     <t xml:space="preserve">19.3777809143066</t>
@@ -677,49 +677,49 @@
     <t xml:space="preserve">19.1151847839355</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5860443115234</t>
+    <t xml:space="preserve">19.5860462188721</t>
   </si>
   <si>
     <t xml:space="preserve">19.2600631713867</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3738346099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3466663360596</t>
+    <t xml:space="preserve">20.3738327026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3466682434082</t>
   </si>
   <si>
     <t xml:space="preserve">20.2380084991455</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1293468475342</t>
+    <t xml:space="preserve">20.1293449401855</t>
   </si>
   <si>
     <t xml:space="preserve">20.1565132141113</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8084754943848</t>
+    <t xml:space="preserve">20.8084735870361</t>
   </si>
   <si>
     <t xml:space="preserve">20.6183223724365</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4785461425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5328807830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0671253204346</t>
+    <t xml:space="preserve">21.4785480499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5328788757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0671272277832</t>
   </si>
   <si>
     <t xml:space="preserve">22.0580711364746</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2572822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2935028076172</t>
+    <t xml:space="preserve">22.2572803497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2935009002686</t>
   </si>
   <si>
     <t xml:space="preserve">22.3025569915771</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">22.891134262085</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1537322998047</t>
+    <t xml:space="preserve">23.1537303924561</t>
   </si>
   <si>
     <t xml:space="preserve">23.0993976593018</t>
@@ -752,34 +752,34 @@
     <t xml:space="preserve">22.5923175811768</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3568859100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9092464447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1757869720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1395664215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6064834594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7513637542725</t>
+    <t xml:space="preserve">22.3568878173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9092445373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1757850646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1395683288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.606481552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7513618469238</t>
   </si>
   <si>
     <t xml:space="preserve">24.1226177215576</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6427040100098</t>
+    <t xml:space="preserve">23.6427021026611</t>
   </si>
   <si>
     <t xml:space="preserve">23.6879749298096</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5612106323242</t>
+    <t xml:space="preserve">23.5612087249756</t>
   </si>
   <si>
     <t xml:space="preserve">23.7423076629639</t>
@@ -791,37 +791,37 @@
     <t xml:space="preserve">23.6336460113525</t>
   </si>
   <si>
-    <t xml:space="preserve">23.823802947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6970348358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0139617919922</t>
+    <t xml:space="preserve">23.8238010406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6970329284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0139579772949</t>
   </si>
   <si>
     <t xml:space="preserve">24.2856101989746</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0682907104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9777412414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2946643829346</t>
+    <t xml:space="preserve">24.0682888031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9777393341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2946624755859</t>
   </si>
   <si>
     <t xml:space="preserve">24.430492401123</t>
   </si>
   <si>
-    <t xml:space="preserve">24.61159324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7655258178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1911125183105</t>
+    <t xml:space="preserve">24.6115913391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7655277252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1911144256592</t>
   </si>
   <si>
     <t xml:space="preserve">25.3903255462646</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">25.4265441894531</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6167011260986</t>
+    <t xml:space="preserve">25.6167030334473</t>
   </si>
   <si>
     <t xml:space="preserve">25.6710300445557</t>
@@ -839,16 +839,16 @@
     <t xml:space="preserve">25.6529197692871</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7615814208984</t>
+    <t xml:space="preserve">25.7615833282471</t>
   </si>
   <si>
     <t xml:space="preserve">25.5352058410645</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9556846618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9013519287109</t>
+    <t xml:space="preserve">24.955680847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9013538360596</t>
   </si>
   <si>
     <t xml:space="preserve">25.0643444061279</t>
@@ -857,28 +857,28 @@
     <t xml:space="preserve">24.8017463684082</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6206455230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.937572479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3722171783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.62575340271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2273349761963</t>
+    <t xml:space="preserve">24.6206474304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9375743865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3722133636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6257553100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2273330688477</t>
   </si>
   <si>
     <t xml:space="preserve">25.1730041503906</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1639499664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3993759155273</t>
+    <t xml:space="preserve">25.163948059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.399377822876</t>
   </si>
   <si>
     <t xml:space="preserve">25.7253608703613</t>
@@ -887,37 +887,37 @@
     <t xml:space="preserve">25.2907199859619</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1277275085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7434730529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.544261932373</t>
+    <t xml:space="preserve">25.1277294158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7434711456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5442600250244</t>
   </si>
   <si>
     <t xml:space="preserve">25.4808750152588</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5080413818359</t>
+    <t xml:space="preserve">25.5080375671387</t>
   </si>
   <si>
     <t xml:space="preserve">25.2635555267334</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0824527740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7836360931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4214363098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2674999237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5261516571045</t>
+    <t xml:space="preserve">25.0824508666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7836380004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4214344024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2674980163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5261497497559</t>
   </si>
   <si>
     <t xml:space="preserve">26.1237831115723</t>
@@ -932,19 +932,19 @@
     <t xml:space="preserve">26.4859828948975</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3229942321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.676139831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8934593200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2596054077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6670837402344</t>
+    <t xml:space="preserve">26.3229923248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6761379241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.893461227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2596073150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.667085647583</t>
   </si>
   <si>
     <t xml:space="preserve">26.9115676879883</t>
@@ -953,43 +953,43 @@
     <t xml:space="preserve">26.6036987304688</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5946445465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3088283538818</t>
+    <t xml:space="preserve">26.5946464538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3088302612305</t>
   </si>
   <si>
     <t xml:space="preserve">25.326940536499</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8340225219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8984451293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0641040802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.71120262146</t>
+    <t xml:space="preserve">25.834020614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8984432220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0641059875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7112045288086</t>
   </si>
   <si>
     <t xml:space="preserve">23.6159954071045</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2202453613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1282138824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9625511169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8705196380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8613166809082</t>
+    <t xml:space="preserve">23.2202472686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1282119750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.962553024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8705177307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8613147735596</t>
   </si>
   <si>
     <t xml:space="preserve">23.266263961792</t>
@@ -998,10 +998,10 @@
     <t xml:space="preserve">23.238655090332</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0453815460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8889255523682</t>
+    <t xml:space="preserve">23.0453834533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8889236450195</t>
   </si>
   <si>
     <t xml:space="preserve">22.0882263183594</t>
@@ -1010,10 +1010,10 @@
     <t xml:space="preserve">22.3183116912842</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2262783050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3827342987061</t>
+    <t xml:space="preserve">22.2262763977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3827362060547</t>
   </si>
   <si>
     <t xml:space="preserve">22.3643264770508</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">22.7416667938232</t>
   </si>
   <si>
-    <t xml:space="preserve">22.95334815979</t>
+    <t xml:space="preserve">22.9533500671387</t>
   </si>
   <si>
     <t xml:space="preserve">22.8797206878662</t>
@@ -1031,10 +1031,10 @@
     <t xml:space="preserve">23.2846736907959</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4871463775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4319229125977</t>
+    <t xml:space="preserve">23.4871482849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4319248199463</t>
   </si>
   <si>
     <t xml:space="preserve">22.8060932159424</t>
@@ -1055,13 +1055,13 @@
     <t xml:space="preserve">21.4900035858154</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7200870513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5544281005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6740703582764</t>
+    <t xml:space="preserve">21.7200889587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5544261932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.674072265625</t>
   </si>
   <si>
     <t xml:space="preserve">21.6280536651611</t>
@@ -1070,25 +1070,25 @@
     <t xml:space="preserve">21.1678829193115</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2046966552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1218681335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.416374206543</t>
+    <t xml:space="preserve">21.2046985626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1218662261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4163761138916</t>
   </si>
   <si>
     <t xml:space="preserve">21.5084095001221</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9133605957031</t>
+    <t xml:space="preserve">21.9133625030518</t>
   </si>
   <si>
     <t xml:space="preserve">21.8857517242432</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9685802459717</t>
+    <t xml:space="preserve">21.9685821533203</t>
   </si>
   <si>
     <t xml:space="preserve">22.6220245361328</t>
@@ -1115,10 +1115,10 @@
     <t xml:space="preserve">22.5576000213623</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4255809783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6556663513184</t>
+    <t xml:space="preserve">21.4255790710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6556644439697</t>
   </si>
   <si>
     <t xml:space="preserve">22.2630920410156</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">22.0514106750488</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7876853942871</t>
+    <t xml:space="preserve">22.7876873016357</t>
   </si>
   <si>
     <t xml:space="preserve">22.3367195129395</t>
@@ -1145,7 +1145,7 @@
     <t xml:space="preserve">21.7661056518555</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0606136322021</t>
+    <t xml:space="preserve">22.0606155395508</t>
   </si>
   <si>
     <t xml:space="preserve">21.7569007873535</t>
@@ -1163,7 +1163,7 @@
     <t xml:space="preserve">21.8765468597412</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1250400543213</t>
+    <t xml:space="preserve">22.1250381469727</t>
   </si>
   <si>
     <t xml:space="preserve">21.7753105163574</t>
@@ -1178,19 +1178,19 @@
     <t xml:space="preserve">21.6832714080811</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8273544311523</t>
+    <t xml:space="preserve">20.827356338501</t>
   </si>
   <si>
     <t xml:space="preserve">21.0574398040771</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9470024108887</t>
+    <t xml:space="preserve">20.94700050354</t>
   </si>
   <si>
     <t xml:space="preserve">20.799747467041</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1034564971924</t>
+    <t xml:space="preserve">21.103458404541</t>
   </si>
   <si>
     <t xml:space="preserve">21.0758476257324</t>
@@ -1199,19 +1199,19 @@
     <t xml:space="preserve">21.3243408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">21.950174331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0974273681641</t>
+    <t xml:space="preserve">21.9501762390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0974292755127</t>
   </si>
   <si>
     <t xml:space="preserve">21.8581409454346</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6372585296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2967300415039</t>
+    <t xml:space="preserve">21.6372566223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2967319488525</t>
   </si>
   <si>
     <t xml:space="preserve">20.9746112823486</t>
@@ -1220,16 +1220,16 @@
     <t xml:space="preserve">20.983814239502</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1402721405029</t>
+    <t xml:space="preserve">21.1402702331543</t>
   </si>
   <si>
     <t xml:space="preserve">21.0666465759277</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7077121734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0942535400391</t>
+    <t xml:space="preserve">20.7077102661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0942573547363</t>
   </si>
   <si>
     <t xml:space="preserve">21.1586799621582</t>
@@ -1241,10 +1241,10 @@
     <t xml:space="preserve">21.0022220611572</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6340847015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4500141143799</t>
+    <t xml:space="preserve">20.6340827941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4500160217285</t>
   </si>
   <si>
     <t xml:space="preserve">20.385591506958</t>
@@ -1253,10 +1253,10 @@
     <t xml:space="preserve">20.3947944641113</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0082492828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.971435546875</t>
+    <t xml:space="preserve">20.0082511901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9714374542236</t>
   </si>
   <si>
     <t xml:space="preserve">20.0634727478027</t>
@@ -1268,16 +1268,16 @@
     <t xml:space="preserve">20.7445278167725</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8917789459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2415103912354</t>
+    <t xml:space="preserve">20.8917808532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.241512298584</t>
   </si>
   <si>
     <t xml:space="preserve">20.9285926818848</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2475414276123</t>
+    <t xml:space="preserve">20.2475433349609</t>
   </si>
   <si>
     <t xml:space="preserve">20.1647090911865</t>
@@ -1289,25 +1289,25 @@
     <t xml:space="preserve">19.2719783782959</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6953353881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8057746887207</t>
+    <t xml:space="preserve">19.695333480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8057765960693</t>
   </si>
   <si>
     <t xml:space="preserve">19.7321491241455</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1831150054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0450687408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2935562133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4316082000732</t>
+    <t xml:space="preserve">20.1831169128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0450649261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2935581207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4316101074219</t>
   </si>
   <si>
     <t xml:space="preserve">20.5696601867676</t>
@@ -1316,10 +1316,10 @@
     <t xml:space="preserve">20.661693572998</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1310691833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0482387542725</t>
+    <t xml:space="preserve">21.131067276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0482406616211</t>
   </si>
   <si>
     <t xml:space="preserve">21.1954936981201</t>
@@ -1328,22 +1328,22 @@
     <t xml:space="preserve">21.4531879425049</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8089485168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6708965301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7721347808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4652481079102</t>
+    <t xml:space="preserve">20.8089466094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6708984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7721366882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4652462005615</t>
   </si>
   <si>
     <t xml:space="preserve">19.7965717315674</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8609962463379</t>
+    <t xml:space="preserve">19.8609981536865</t>
   </si>
   <si>
     <t xml:space="preserve">20.0174522399902</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">20.229133605957</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5236434936523</t>
+    <t xml:space="preserve">20.5236415863037</t>
   </si>
   <si>
     <t xml:space="preserve">20.6524925231934</t>
@@ -1364,7 +1364,7 @@
     <t xml:space="preserve">20.9101886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2659492492676</t>
+    <t xml:space="preserve">20.2659473419189</t>
   </si>
   <si>
     <t xml:space="preserve">20.4684219360352</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">21.259916305542</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3703575134277</t>
+    <t xml:space="preserve">21.3703556060791</t>
   </si>
   <si>
     <t xml:space="preserve">21.5176105499268</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">20.8549671173096</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9193897247314</t>
+    <t xml:space="preserve">20.9193916320801</t>
   </si>
   <si>
     <t xml:space="preserve">20.5052356719971</t>
@@ -1403,7 +1403,7 @@
     <t xml:space="preserve">19.7229442596436</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9162158966064</t>
+    <t xml:space="preserve">19.9162178039551</t>
   </si>
   <si>
     <t xml:space="preserve">20.5604553222656</t>
@@ -1418,10 +1418,10 @@
     <t xml:space="preserve">20.8365573883057</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6004447937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6248798370361</t>
+    <t xml:space="preserve">21.6004428863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6248817443848</t>
   </si>
   <si>
     <t xml:space="preserve">20.2751522064209</t>
@@ -1439,31 +1439,31 @@
     <t xml:space="preserve">20.1278953552246</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3303718566895</t>
+    <t xml:space="preserve">20.3303699493408</t>
   </si>
   <si>
     <t xml:space="preserve">20.8733730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3763885498047</t>
+    <t xml:space="preserve">20.3763866424561</t>
   </si>
   <si>
     <t xml:space="preserve">20.5328483581543</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3027591705322</t>
+    <t xml:space="preserve">20.3027610778809</t>
   </si>
   <si>
     <t xml:space="preserve">20.6432876586914</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6156749725342</t>
+    <t xml:space="preserve">20.6156768798828</t>
   </si>
   <si>
     <t xml:space="preserve">20.7261180877686</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2783260345459</t>
+    <t xml:space="preserve">21.2783241271973</t>
   </si>
   <si>
     <t xml:space="preserve">21.3151378631592</t>
@@ -1472,13 +1472,13 @@
     <t xml:space="preserve">21.5360202789307</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7937145233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6496353149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5483989715576</t>
+    <t xml:space="preserve">21.7937164306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6496334075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.548397064209</t>
   </si>
   <si>
     <t xml:space="preserve">22.4195499420166</t>
@@ -1490,7 +1490,7 @@
     <t xml:space="preserve">22.5668048858643</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6128196716309</t>
+    <t xml:space="preserve">22.6128215789795</t>
   </si>
   <si>
     <t xml:space="preserve">22.9165344238281</t>
@@ -1508,7 +1508,7 @@
     <t xml:space="preserve">22.7692775726318</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9073314666748</t>
+    <t xml:space="preserve">22.9073333740234</t>
   </si>
   <si>
     <t xml:space="preserve">23.2754669189453</t>
@@ -1517,10 +1517,10 @@
     <t xml:space="preserve">22.991304397583</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3090686798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4118728637695</t>
+    <t xml:space="preserve">23.3090705871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4118747711182</t>
   </si>
   <si>
     <t xml:space="preserve">22.9071884155273</t>
@@ -1529,16 +1529,16 @@
     <t xml:space="preserve">22.9819564819336</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7296123504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3557720184326</t>
+    <t xml:space="preserve">22.7296142578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.355770111084</t>
   </si>
   <si>
     <t xml:space="preserve">22.6174602508545</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0754165649414</t>
+    <t xml:space="preserve">23.07541847229</t>
   </si>
   <si>
     <t xml:space="preserve">23.3557987213135</t>
@@ -1571,25 +1571,25 @@
     <t xml:space="preserve">23.3931846618652</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2623386383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9258804321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9912452697754</t>
+    <t xml:space="preserve">23.2623405456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9258823394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.991247177124</t>
   </si>
   <si>
     <t xml:space="preserve">20.3370227813721</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9912166595459</t>
+    <t xml:space="preserve">19.9912185668945</t>
   </si>
   <si>
     <t xml:space="preserve">19.7388763427734</t>
   </si>
   <si>
-    <t xml:space="preserve">19.56130027771</t>
+    <t xml:space="preserve">19.5612983703613</t>
   </si>
   <si>
     <t xml:space="preserve">19.3089561462402</t>
@@ -1598,25 +1598,25 @@
     <t xml:space="preserve">19.533260345459</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4958782196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.346342086792</t>
+    <t xml:space="preserve">19.4958763122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3463401794434</t>
   </si>
   <si>
     <t xml:space="preserve">19.0285758972168</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6266937255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3836975097656</t>
+    <t xml:space="preserve">18.6266956329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.383695602417</t>
   </si>
   <si>
     <t xml:space="preserve">18.0752754211426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6220188140869</t>
+    <t xml:space="preserve">18.6220207214355</t>
   </si>
   <si>
     <t xml:space="preserve">18.079948425293</t>
@@ -1625,25 +1625,25 @@
     <t xml:space="preserve">18.603328704834</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6360416412354</t>
+    <t xml:space="preserve">18.6360397338867</t>
   </si>
   <si>
     <t xml:space="preserve">18.7949237823486</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7762298583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7201538085938</t>
+    <t xml:space="preserve">18.7762317657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7201557159424</t>
   </si>
   <si>
     <t xml:space="preserve">18.5752906799316</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3930416107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5285625457764</t>
+    <t xml:space="preserve">18.3930435180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5285606384277</t>
   </si>
   <si>
     <t xml:space="preserve">18.495849609375</t>
@@ -1652,22 +1652,22 @@
     <t xml:space="preserve">18.4351005554199</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3883686065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4911766052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2435054779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8042392730713</t>
+    <t xml:space="preserve">18.388370513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.491174697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2435073852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8042373657227</t>
   </si>
   <si>
     <t xml:space="preserve">17.7715282440186</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1079883575439</t>
+    <t xml:space="preserve">18.1079864501953</t>
   </si>
   <si>
     <t xml:space="preserve">18.6734237670898</t>
@@ -1676,13 +1676,13 @@
     <t xml:space="preserve">18.7575378417969</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7294998168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2762184143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2528533935547</t>
+    <t xml:space="preserve">18.7295017242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.276216506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2528514862061</t>
   </si>
   <si>
     <t xml:space="preserve">18.2107944488525</t>
@@ -1691,13 +1691,13 @@
     <t xml:space="preserve">18.3790245056152</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1407279968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4398002624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.402416229248</t>
+    <t xml:space="preserve">19.1407260894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4397983551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4024181365967</t>
   </si>
   <si>
     <t xml:space="preserve">19.4117641448975</t>
@@ -1706,16 +1706,16 @@
     <t xml:space="preserve">19.4304542541504</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3650321960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1594181060791</t>
+    <t xml:space="preserve">19.3650341033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1594200134277</t>
   </si>
   <si>
     <t xml:space="preserve">19.1687660217285</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1126880645752</t>
+    <t xml:space="preserve">19.1126899719238</t>
   </si>
   <si>
     <t xml:space="preserve">19.0939960479736</t>
@@ -1724,28 +1724,28 @@
     <t xml:space="preserve">18.7388458251953</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0566120147705</t>
+    <t xml:space="preserve">19.0566101074219</t>
   </si>
   <si>
     <t xml:space="preserve">18.8416519165039</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6080284118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2528820037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5239162445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4211082458496</t>
+    <t xml:space="preserve">19.6080303192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2528800964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5239143371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4211101531982</t>
   </si>
   <si>
     <t xml:space="preserve">19.8136425018311</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0753307342529</t>
+    <t xml:space="preserve">20.0753326416016</t>
   </si>
   <si>
     <t xml:space="preserve">19.7482204437256</t>
@@ -1754,10 +1754,10 @@
     <t xml:space="preserve">20.0192565917969</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7669124603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7856044769287</t>
+    <t xml:space="preserve">19.7669105529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7856063842773</t>
   </si>
   <si>
     <t xml:space="preserve">19.5706462860107</t>
@@ -1769,16 +1769,16 @@
     <t xml:space="preserve">19.1500720977783</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8977279663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.804271697998</t>
+    <t xml:space="preserve">18.8977298736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8042697906494</t>
   </si>
   <si>
     <t xml:space="preserve">18.8790378570557</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1780853271484</t>
+    <t xml:space="preserve">18.1780834197998</t>
   </si>
   <si>
     <t xml:space="preserve">18.6453876495361</t>
@@ -1790,16 +1790,16 @@
     <t xml:space="preserve">17.2528228759766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1546897888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9817886352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1360244750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.949104309082</t>
+    <t xml:space="preserve">17.1546878814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9817867279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1360263824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9491062164307</t>
   </si>
   <si>
     <t xml:space="preserve">18.1173343658447</t>
@@ -1814,25 +1814,25 @@
     <t xml:space="preserve">19.0098819732666</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5986824035645</t>
+    <t xml:space="preserve">19.5986843109131</t>
   </si>
   <si>
     <t xml:space="preserve">19.5893363952637</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6454124450684</t>
+    <t xml:space="preserve">19.645414352417</t>
   </si>
   <si>
     <t xml:space="preserve">19.4771862030029</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5426063537598</t>
+    <t xml:space="preserve">19.5426082611084</t>
   </si>
   <si>
     <t xml:space="preserve">19.5799922943115</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0005645751953</t>
+    <t xml:space="preserve">20.0005626678467</t>
   </si>
   <si>
     <t xml:space="preserve">19.6267204284668</t>
@@ -1850,7 +1850,7 @@
     <t xml:space="preserve">18.7481918334961</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7855758666992</t>
+    <t xml:space="preserve">18.7855777740479</t>
   </si>
   <si>
     <t xml:space="preserve">19.0659580230713</t>
@@ -1859,7 +1859,7 @@
     <t xml:space="preserve">19.5145683288574</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2061462402344</t>
+    <t xml:space="preserve">19.206148147583</t>
   </si>
   <si>
     <t xml:space="preserve">17.0472106933594</t>
@@ -1868,10 +1868,10 @@
     <t xml:space="preserve">16.7107524871826</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8135566711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5845813751221</t>
+    <t xml:space="preserve">16.8135585784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5845794677734</t>
   </si>
   <si>
     <t xml:space="preserve">16.5471973419189</t>
@@ -1880,10 +1880,10 @@
     <t xml:space="preserve">16.5378494262695</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7200965881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.495792388916</t>
+    <t xml:space="preserve">16.7200984954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4957904815674</t>
   </si>
   <si>
     <t xml:space="preserve">16.7528095245361</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">16.500467300415</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4630794525146</t>
+    <t xml:space="preserve">16.4630813598633</t>
   </si>
   <si>
     <t xml:space="preserve">16.0425090789795</t>
@@ -1910,7 +1910,7 @@
     <t xml:space="preserve">16.6640224456787</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5331783294678</t>
+    <t xml:space="preserve">16.5331764221191</t>
   </si>
   <si>
     <t xml:space="preserve">16.5892524719238</t>
@@ -1919,13 +1919,13 @@
     <t xml:space="preserve">16.6827125549316</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5986003875732</t>
+    <t xml:space="preserve">16.5985984802246</t>
   </si>
   <si>
     <t xml:space="preserve">16.4256973266602</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1266231536865</t>
+    <t xml:space="preserve">16.1266212463379</t>
   </si>
   <si>
     <t xml:space="preserve">16.1593341827393</t>
@@ -1940,10 +1940,10 @@
     <t xml:space="preserve">16.2154121398926</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4817733764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5238285064697</t>
+    <t xml:space="preserve">16.4817752838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.523832321167</t>
   </si>
   <si>
     <t xml:space="preserve">16.4023323059082</t>
@@ -1970,16 +1970,16 @@
     <t xml:space="preserve">17.5752601623535</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5518989562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4163799285889</t>
+    <t xml:space="preserve">17.5518970489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4163780212402</t>
   </si>
   <si>
     <t xml:space="preserve">17.1079597473145</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1313247680664</t>
+    <t xml:space="preserve">17.1313228607178</t>
   </si>
   <si>
     <t xml:space="preserve">17.2294578552246</t>
@@ -1988,13 +1988,13 @@
     <t xml:space="preserve">17.4911479949951</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4397430419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.453763961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7294731140137</t>
+    <t xml:space="preserve">17.4397449493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4537620544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.729471206665</t>
   </si>
   <si>
     <t xml:space="preserve">17.6547031402588</t>
@@ -2006,16 +2006,16 @@
     <t xml:space="preserve">17.1453418731689</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8462677001953</t>
+    <t xml:space="preserve">16.8462696075439</t>
   </si>
   <si>
     <t xml:space="preserve">17.1687088012695</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8229064941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9911613464355</t>
+    <t xml:space="preserve">16.822904586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9911594390869</t>
   </si>
   <si>
     <t xml:space="preserve">17.9117202758789</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">18.0378932952881</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6593780517578</t>
+    <t xml:space="preserve">17.6593761444092</t>
   </si>
   <si>
     <t xml:space="preserve">17.7948951721191</t>
@@ -2036,13 +2036,13 @@
     <t xml:space="preserve">17.3275928497314</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3976898193359</t>
+    <t xml:space="preserve">17.3976879119873</t>
   </si>
   <si>
     <t xml:space="preserve">17.6266651153564</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5004940032959</t>
+    <t xml:space="preserve">17.5004959106445</t>
   </si>
   <si>
     <t xml:space="preserve">17.8696632385254</t>
@@ -2063,28 +2063,28 @@
     <t xml:space="preserve">17.9677963256836</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9070472717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.69211769104</t>
+    <t xml:space="preserve">17.9070491790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6921157836914</t>
   </si>
   <si>
     <t xml:space="preserve">18.5051937103271</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3416404724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5565967559814</t>
+    <t xml:space="preserve">18.3416385650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5565986633301</t>
   </si>
   <si>
     <t xml:space="preserve">18.4397716522217</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5472526550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3089294433594</t>
+    <t xml:space="preserve">18.5472507476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3089275360107</t>
   </si>
   <si>
     <t xml:space="preserve">18.8603458404541</t>
@@ -2096,7 +2096,7 @@
     <t xml:space="preserve">18.5893096923828</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0238704681396</t>
+    <t xml:space="preserve">18.0238723754883</t>
   </si>
   <si>
     <t xml:space="preserve">17.8603172302246</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">18.0939693450928</t>
   </si>
   <si>
-    <t xml:space="preserve">19.860372543335</t>
+    <t xml:space="preserve">19.8603744506836</t>
   </si>
   <si>
     <t xml:space="preserve">20.0472965240479</t>
@@ -2135,31 +2135,31 @@
     <t xml:space="preserve">19.4892063140869</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1187973022461</t>
+    <t xml:space="preserve">19.1187953948975</t>
   </si>
   <si>
     <t xml:space="preserve">19.2327690124512</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9525871276855</t>
+    <t xml:space="preserve">18.9525890350342</t>
   </si>
   <si>
     <t xml:space="preserve">18.4397163391113</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7131423950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7273921966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8318614959717</t>
+    <t xml:space="preserve">17.7131443023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7273902893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8318634033203</t>
   </si>
   <si>
     <t xml:space="preserve">18.3732299804688</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6534099578857</t>
+    <t xml:space="preserve">18.6534118652344</t>
   </si>
   <si>
     <t xml:space="preserve">19.1757850646973</t>
@@ -2171,19 +2171,19 @@
     <t xml:space="preserve">19.2802562713623</t>
   </si>
   <si>
-    <t xml:space="preserve">19.213773727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9810791015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9050998687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.033317565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6601657867432</t>
+    <t xml:space="preserve">19.2137718200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9810810089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.905101776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0333194732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6601638793945</t>
   </si>
   <si>
     <t xml:space="preserve">19.6886558532715</t>
@@ -2204,7 +2204,7 @@
     <t xml:space="preserve">19.8121280670166</t>
   </si>
   <si>
-    <t xml:space="preserve">19.745641708374</t>
+    <t xml:space="preserve">19.7456436157227</t>
   </si>
   <si>
     <t xml:space="preserve">19.926097869873</t>
@@ -2216,10 +2216,10 @@
     <t xml:space="preserve">20.1920337677002</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4674663543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4864616394043</t>
+    <t xml:space="preserve">20.4674644470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4864597320557</t>
   </si>
   <si>
     <t xml:space="preserve">20.2870101928711</t>
@@ -2246,16 +2246,16 @@
     <t xml:space="preserve">19.8881092071533</t>
   </si>
   <si>
-    <t xml:space="preserve">20.030574798584</t>
+    <t xml:space="preserve">20.0305728912354</t>
   </si>
   <si>
     <t xml:space="preserve">19.8691139221191</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9640884399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0020809173584</t>
+    <t xml:space="preserve">19.96409034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0020790100098</t>
   </si>
   <si>
     <t xml:space="preserve">19.9450931549072</t>
@@ -2276,10 +2276,10 @@
     <t xml:space="preserve">17.2952442169189</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2762489318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.266752243042</t>
+    <t xml:space="preserve">17.2762508392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2667541503906</t>
   </si>
   <si>
     <t xml:space="preserve">17.3854732513428</t>
@@ -2291,13 +2291,13 @@
     <t xml:space="preserve">16.8963451385498</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0150680541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.59716796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2837448120117</t>
+    <t xml:space="preserve">17.0150661468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5971660614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2837467193604</t>
   </si>
   <si>
     <t xml:space="preserve">16.8108654022217</t>
@@ -2309,19 +2309,19 @@
     <t xml:space="preserve">17.0530548095703</t>
   </si>
   <si>
-    <t xml:space="preserve">16.915340423584</t>
+    <t xml:space="preserve">16.9153385162354</t>
   </si>
   <si>
     <t xml:space="preserve">16.6636505126953</t>
   </si>
   <si>
-    <t xml:space="preserve">16.734884262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.948579788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7491302490234</t>
+    <t xml:space="preserve">16.7348861694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9485816955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7491321563721</t>
   </si>
   <si>
     <t xml:space="preserve">16.8441066741943</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">16.4974422454834</t>
   </si>
   <si>
-    <t xml:space="preserve">16.668399810791</t>
+    <t xml:space="preserve">16.6683979034424</t>
   </si>
   <si>
     <t xml:space="preserve">16.6304092407227</t>
@@ -2339,7 +2339,7 @@
     <t xml:space="preserve">16.9248371124268</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4329624176025</t>
+    <t xml:space="preserve">17.4329605102539</t>
   </si>
   <si>
     <t xml:space="preserve">17.3807239532471</t>
@@ -2354,7 +2354,7 @@
     <t xml:space="preserve">17.5231895446777</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2857475280762</t>
+    <t xml:space="preserve">17.2857494354248</t>
   </si>
   <si>
     <t xml:space="preserve">17.2002696990967</t>
@@ -2375,25 +2375,25 @@
     <t xml:space="preserve">16.1365299224854</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3454780578613</t>
+    <t xml:space="preserve">16.34547996521</t>
   </si>
   <si>
     <t xml:space="preserve">16.1840190887451</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1032905578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0178089141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4811916351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5381784439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5619220733643</t>
+    <t xml:space="preserve">16.1032886505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0178108215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4811906814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.538179397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5619230270386</t>
   </si>
   <si>
     <t xml:space="preserve">15.1725187301636</t>
@@ -2417,13 +2417,13 @@
     <t xml:space="preserve">15.4052095413208</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3244800567627</t>
+    <t xml:space="preserve">15.324481010437</t>
   </si>
   <si>
     <t xml:space="preserve">15.2722434997559</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2579975128174</t>
+    <t xml:space="preserve">15.2579965591431</t>
   </si>
   <si>
     <t xml:space="preserve">15.1772661209106</t>
@@ -2432,19 +2432,19 @@
     <t xml:space="preserve">15.0680437088013</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0348024368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.319730758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9608240127563</t>
+    <t xml:space="preserve">15.0348014831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3197317123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.960823059082</t>
   </si>
   <si>
     <t xml:space="preserve">15.7661218643188</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8800926208496</t>
+    <t xml:space="preserve">15.8800916671753</t>
   </si>
   <si>
     <t xml:space="preserve">15.9085874557495</t>
@@ -2453,16 +2453,16 @@
     <t xml:space="preserve">15.922833442688</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1412811279297</t>
+    <t xml:space="preserve">16.1412792205811</t>
   </si>
   <si>
     <t xml:space="preserve">16.1745204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4024639129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5781726837158</t>
+    <t xml:space="preserve">16.4024658203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5781707763672</t>
   </si>
   <si>
     <t xml:space="preserve">16.5734233856201</t>
@@ -2501,7 +2501,7 @@
     <t xml:space="preserve">17.1860218048096</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6873970031738</t>
+    <t xml:space="preserve">16.6873950958252</t>
   </si>
   <si>
     <t xml:space="preserve">17.9695796966553</t>
@@ -2519,25 +2519,25 @@
     <t xml:space="preserve">17.2477569580078</t>
   </si>
   <si>
-    <t xml:space="preserve">17.337984085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4092178344727</t>
+    <t xml:space="preserve">17.3379859924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.409215927124</t>
   </si>
   <si>
     <t xml:space="preserve">17.62766456604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5421848297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4804515838623</t>
+    <t xml:space="preserve">17.5421829223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4804496765137</t>
   </si>
   <si>
     <t xml:space="preserve">17.8033714294434</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1167964935303</t>
+    <t xml:space="preserve">18.1167945861816</t>
   </si>
   <si>
     <t xml:space="preserve">17.8556079864502</t>
@@ -2558,7 +2558,7 @@
     <t xml:space="preserve">17.6799030303955</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9885768890381</t>
+    <t xml:space="preserve">17.9885749816895</t>
   </si>
   <si>
     <t xml:space="preserve">18.4207191467285</t>
@@ -2576,10 +2576,10 @@
     <t xml:space="preserve">17.2620029449463</t>
   </si>
   <si>
-    <t xml:space="preserve">17.228759765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.095796585083</t>
+    <t xml:space="preserve">17.2287616729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0957946777344</t>
   </si>
   <si>
     <t xml:space="preserve">16.8868465423584</t>
@@ -2597,13 +2597,13 @@
     <t xml:space="preserve">16.2694969177246</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2979907989502</t>
+    <t xml:space="preserve">16.2979927062988</t>
   </si>
   <si>
     <t xml:space="preserve">16.1175346374512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8468494415283</t>
+    <t xml:space="preserve">15.8468503952026</t>
   </si>
   <si>
     <t xml:space="preserve">16.3217353820801</t>
@@ -2615,28 +2615,28 @@
     <t xml:space="preserve">15.7803688049316</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7186317443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3434762954712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9845685958862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7471265792847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6046619415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7043867111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8848438262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5429258346558</t>
+    <t xml:space="preserve">15.7186326980591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3434772491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9845676422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.747127532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.604660987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7043857574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8848428726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5429267883301</t>
   </si>
   <si>
     <t xml:space="preserve">15.1582717895508</t>
@@ -2654,7 +2654,7 @@
     <t xml:space="preserve">13.6054039001465</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5721607208252</t>
+    <t xml:space="preserve">13.5721616744995</t>
   </si>
   <si>
     <t xml:space="preserve">13.0735340118408</t>
@@ -2678,13 +2678,13 @@
     <t xml:space="preserve">10.6563787460327</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7845973968506</t>
+    <t xml:space="preserve">10.7845964431763</t>
   </si>
   <si>
     <t xml:space="preserve">9.08166599273682</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65437412261963</t>
+    <t xml:space="preserve">9.65437507629395</t>
   </si>
   <si>
     <t xml:space="preserve">10.0057888031006</t>
@@ -2705,13 +2705,13 @@
     <t xml:space="preserve">12.1665077209473</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0877809524536</t>
+    <t xml:space="preserve">13.0877799987793</t>
   </si>
   <si>
     <t xml:space="preserve">13.3964548110962</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9690589904785</t>
+    <t xml:space="preserve">12.9690599441528</t>
   </si>
   <si>
     <t xml:space="preserve">12.2519865036011</t>
@@ -2723,22 +2723,22 @@
     <t xml:space="preserve">11.4921731948853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2072429656982</t>
+    <t xml:space="preserve">11.2072439193726</t>
   </si>
   <si>
     <t xml:space="preserve">11.1597547531128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1882467269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5681552886963</t>
+    <t xml:space="preserve">11.1882476806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.568154335022</t>
   </si>
   <si>
     <t xml:space="preserve">11.5586566925049</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6251401901245</t>
+    <t xml:space="preserve">11.6251411437988</t>
   </si>
   <si>
     <t xml:space="preserve">11.9765529632568</t>
@@ -2774,7 +2774,7 @@
     <t xml:space="preserve">10.7228622436523</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3049650192261</t>
+    <t xml:space="preserve">10.3049659729004</t>
   </si>
   <si>
     <t xml:space="preserve">10.3524532318115</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">10.3144626617432</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3429574966431</t>
+    <t xml:space="preserve">10.3429565429688</t>
   </si>
   <si>
     <t xml:space="preserve">10.4094390869141</t>
@@ -2801,16 +2801,16 @@
     <t xml:space="preserve">9.89656639099121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64962577819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78259468078613</t>
+    <t xml:space="preserve">9.64962673187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78259372711182</t>
   </si>
   <si>
     <t xml:space="preserve">10.4949188232422</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3469638824463</t>
+    <t xml:space="preserve">12.346962928772</t>
   </si>
   <si>
     <t xml:space="preserve">11.9005727767944</t>
@@ -2843,16 +2843,16 @@
     <t xml:space="preserve">11.7771024703979</t>
   </si>
   <si>
-    <t xml:space="preserve">12.062032699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1190185546875</t>
+    <t xml:space="preserve">12.0620336532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1190195083618</t>
   </si>
   <si>
     <t xml:space="preserve">12.2899770736694</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3089714050293</t>
+    <t xml:space="preserve">12.3089723587036</t>
   </si>
   <si>
     <t xml:space="preserve">12.7078742980957</t>
@@ -2867,7 +2867,7 @@
     <t xml:space="preserve">11.9955492019653</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8055963516235</t>
+    <t xml:space="preserve">11.8055953979492</t>
   </si>
   <si>
     <t xml:space="preserve">11.5111684799194</t>
@@ -2879,25 +2879,25 @@
     <t xml:space="preserve">11.4446849822998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5206670761108</t>
+    <t xml:space="preserve">11.5206661224365</t>
   </si>
   <si>
     <t xml:space="preserve">11.7581071853638</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5871496200562</t>
+    <t xml:space="preserve">11.5871486663818</t>
   </si>
   <si>
     <t xml:space="preserve">11.4826755523682</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3402109146118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9887962341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1787509918213</t>
+    <t xml:space="preserve">11.3402099609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9887971878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1787519454956</t>
   </si>
   <si>
     <t xml:space="preserve">11.2262382507324</t>
@@ -2921,10 +2921,10 @@
     <t xml:space="preserve">10.8368349075317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0552816390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2167406082153</t>
+    <t xml:space="preserve">11.0552806854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2167415618896</t>
   </si>
   <si>
     <t xml:space="preserve">10.5708999633789</t>
@@ -2939,7 +2939,7 @@
     <t xml:space="preserve">10.3619508743286</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6441354751587</t>
+    <t xml:space="preserve">11.644136428833</t>
   </si>
   <si>
     <t xml:space="preserve">11.3307132720947</t>
@@ -2948,16 +2948,16 @@
     <t xml:space="preserve">11.0932712554932</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9603042602539</t>
+    <t xml:space="preserve">10.9603052139282</t>
   </si>
   <si>
     <t xml:space="preserve">10.7608528137207</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7798480987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6753749847412</t>
+    <t xml:space="preserve">10.7798490524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6753740310669</t>
   </si>
   <si>
     <t xml:space="preserve">11.6156425476074</t>
@@ -2972,13 +2972,13 @@
     <t xml:space="preserve">11.5016708374023</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7960996627808</t>
+    <t xml:space="preserve">11.7960987091064</t>
   </si>
   <si>
     <t xml:space="preserve">11.4731779098511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4256887435913</t>
+    <t xml:space="preserve">11.4256896972656</t>
   </si>
   <si>
     <t xml:space="preserve">12.5179214477539</t>
@@ -2996,10 +2996,10 @@
     <t xml:space="preserve">11.6061458587646</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1095209121704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0145454406738</t>
+    <t xml:space="preserve">12.1095218658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0145444869995</t>
   </si>
   <si>
     <t xml:space="preserve">11.9385633468628</t>
@@ -3011,10 +3011,10 @@
     <t xml:space="preserve">11.9860515594482</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1285181045532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2804794311523</t>
+    <t xml:space="preserve">12.1285171508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2804803848267</t>
   </si>
   <si>
     <t xml:space="preserve">12.6793813705444</t>
@@ -3032,16 +3032,16 @@
     <t xml:space="preserve">12.4039497375488</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8978271484375</t>
+    <t xml:space="preserve">12.8978281021118</t>
   </si>
   <si>
     <t xml:space="preserve">12.1950006484985</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8910751342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.67262840271</t>
+    <t xml:space="preserve">11.8910760879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6726293563843</t>
   </si>
   <si>
     <t xml:space="preserve">11.3117170333862</t>
@@ -3059,46 +3059,46 @@
     <t xml:space="preserve">11.0647783279419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.359206199646</t>
+    <t xml:space="preserve">11.3592052459717</t>
   </si>
   <si>
     <t xml:space="preserve">12.3659582138062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7933540344238</t>
+    <t xml:space="preserve">12.7933530807495</t>
   </si>
   <si>
     <t xml:space="preserve">13.3537158966064</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7811098098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7146263122559</t>
+    <t xml:space="preserve">13.7811107635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7146253585815</t>
   </si>
   <si>
     <t xml:space="preserve">13.9235754013062</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9330739974976</t>
+    <t xml:space="preserve">13.9330730438232</t>
   </si>
   <si>
     <t xml:space="preserve">14.2369976043701</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3414716720581</t>
+    <t xml:space="preserve">14.3414726257324</t>
   </si>
   <si>
     <t xml:space="preserve">14.0470447540283</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6264019012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3129787445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1515197753906</t>
+    <t xml:space="preserve">14.6264009475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3129796981812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1515188217163</t>
   </si>
   <si>
     <t xml:space="preserve">14.2464962005615</t>
@@ -3107,10 +3107,10 @@
     <t xml:space="preserve">14.4269514083862</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4649410247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9113311767578</t>
+    <t xml:space="preserve">14.4649419784546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9113321304321</t>
   </si>
   <si>
     <t xml:space="preserve">14.4934358596802</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">14.3509693145752</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5979099273682</t>
+    <t xml:space="preserve">14.5979089736938</t>
   </si>
   <si>
     <t xml:space="preserve">14.7498712539673</t>
@@ -3128,16 +3128,16 @@
     <t xml:space="preserve">15.1487741470337</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8828392028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8543462753296</t>
+    <t xml:space="preserve">14.8828401565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8543472290039</t>
   </si>
   <si>
     <t xml:space="preserve">14.7593698501587</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3794641494751</t>
+    <t xml:space="preserve">14.3794631958008</t>
   </si>
   <si>
     <t xml:space="preserve">14.5694160461426</t>
@@ -3167,10 +3167,10 @@
     <t xml:space="preserve">14.5884113311768</t>
   </si>
   <si>
-    <t xml:space="preserve">14.578914642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4079561233521</t>
+    <t xml:space="preserve">14.5789136886597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4079551696777</t>
   </si>
   <si>
     <t xml:space="preserve">14.5504207611084</t>
@@ -3179,46 +3179,46 @@
     <t xml:space="preserve">14.5314254760742</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9615659713745</t>
+    <t xml:space="preserve">13.9615650177002</t>
   </si>
   <si>
     <t xml:space="preserve">14.2085056304932</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4459457397461</t>
+    <t xml:space="preserve">14.4459466934204</t>
   </si>
   <si>
     <t xml:space="preserve">15.29123878479</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6833877563477</t>
+    <t xml:space="preserve">14.683388710022</t>
   </si>
   <si>
     <t xml:space="preserve">15.0537977218628</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8041124343872</t>
+    <t xml:space="preserve">15.8041114807129</t>
   </si>
   <si>
     <t xml:space="preserve">15.6711444854736</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2627458572388</t>
+    <t xml:space="preserve">15.2627449035645</t>
   </si>
   <si>
     <t xml:space="preserve">14.9588203430176</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0443000793457</t>
+    <t xml:space="preserve">15.0442991256714</t>
   </si>
   <si>
     <t xml:space="preserve">14.721378326416</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6358995437622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4364490509033</t>
+    <t xml:space="preserve">14.6359004974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4364500045776</t>
   </si>
   <si>
     <t xml:space="preserve">14.7403745651245</t>
@@ -3236,25 +3236,25 @@
     <t xml:space="preserve">14.6928863525391</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7783641815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8258533477783</t>
+    <t xml:space="preserve">14.7783651351929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.825852394104</t>
   </si>
   <si>
     <t xml:space="preserve">15.2057600021362</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1202802658081</t>
+    <t xml:space="preserve">15.1202812194824</t>
   </si>
   <si>
     <t xml:space="preserve">15.0917882919312</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1012849807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8448486328125</t>
+    <t xml:space="preserve">15.1012859344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8448476791382</t>
   </si>
   <si>
     <t xml:space="preserve">14.9873132705688</t>
@@ -3266,22 +3266,22 @@
     <t xml:space="preserve">16.0225601196289</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0320568084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8231086730957</t>
+    <t xml:space="preserve">16.032054901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8231077194214</t>
   </si>
   <si>
     <t xml:space="preserve">15.9370803833008</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7376270294189</t>
+    <t xml:space="preserve">15.7376289367676</t>
   </si>
   <si>
     <t xml:space="preserve">15.4906892776489</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7091360092163</t>
+    <t xml:space="preserve">15.7091369628906</t>
   </si>
   <si>
     <t xml:space="preserve">15.3102350234985</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">15.3387260437012</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6996402740479</t>
+    <t xml:space="preserve">15.6996393203735</t>
   </si>
   <si>
     <t xml:space="preserve">15.6853904724121</t>
@@ -3317,16 +3317,16 @@
     <t xml:space="preserve">16.8725986480713</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4784488677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0340595245361</t>
+    <t xml:space="preserve">16.4784469604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0340576171875</t>
   </si>
   <si>
     <t xml:space="preserve">17.513692855835</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4567050933838</t>
+    <t xml:space="preserve">17.4567031860352</t>
   </si>
   <si>
     <t xml:space="preserve">17.0388088226318</t>
@@ -3335,10 +3335,10 @@
     <t xml:space="preserve">17.2904987335205</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0815486907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0245628356934</t>
+    <t xml:space="preserve">17.0815467834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0245609283447</t>
   </si>
   <si>
     <t xml:space="preserve">16.9770736694336</t>
@@ -3347,7 +3347,7 @@
     <t xml:space="preserve">17.2572555541992</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4614562988281</t>
+    <t xml:space="preserve">17.4614543914795</t>
   </si>
   <si>
     <t xml:space="preserve">17.4187164306641</t>
@@ -3359,10 +3359,10 @@
     <t xml:space="preserve">18.3589839935303</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1975231170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1500358581543</t>
+    <t xml:space="preserve">18.1975250244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1500377655029</t>
   </si>
   <si>
     <t xml:space="preserve">18.2307662963867</t>
@@ -3374,16 +3374,16 @@
     <t xml:space="preserve">17.9125938415527</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9553356170654</t>
+    <t xml:space="preserve">17.9553337097168</t>
   </si>
   <si>
     <t xml:space="preserve">17.6846504211426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0408115386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3304920196533</t>
+    <t xml:space="preserve">18.0408134460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3304901123047</t>
   </si>
   <si>
     <t xml:space="preserve">18.3209934234619</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">18.3019981384277</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3542366027832</t>
+    <t xml:space="preserve">18.3542346954346</t>
   </si>
   <si>
     <t xml:space="preserve">18.3969745635986</t>
@@ -3425,10 +3425,10 @@
     <t xml:space="preserve">18.5584373474121</t>
   </si>
   <si>
-    <t xml:space="preserve">18.335241317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8461112976074</t>
+    <t xml:space="preserve">18.3352394104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8461093902588</t>
   </si>
   <si>
     <t xml:space="preserve">17.1527805328369</t>
@@ -3440,7 +3440,7 @@
     <t xml:space="preserve">17.0673007965088</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1575298309326</t>
+    <t xml:space="preserve">17.1575317382812</t>
   </si>
   <si>
     <t xml:space="preserve">16.6114120483398</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">16.5021896362305</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7253856658936</t>
+    <t xml:space="preserve">16.7253875732422</t>
   </si>
   <si>
     <t xml:space="preserve">16.8773498535156</t>
@@ -3458,7 +3458,7 @@
     <t xml:space="preserve">16.4214611053467</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9798192977905</t>
+    <t xml:space="preserve">15.9798202514648</t>
   </si>
   <si>
     <t xml:space="preserve">16.0985412597656</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">16.0083122253418</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2505054473877</t>
+    <t xml:space="preserve">16.2505035400391</t>
   </si>
   <si>
     <t xml:space="preserve">16.4736976623535</t>
@@ -3488,7 +3488,7 @@
     <t xml:space="preserve">16.2600021362305</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0652980804443</t>
+    <t xml:space="preserve">16.065299987793</t>
   </si>
   <si>
     <t xml:space="preserve">16.0510520935059</t>
@@ -3497,10 +3497,10 @@
     <t xml:space="preserve">17.1100406646729</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3949699401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4919509887695</t>
+    <t xml:space="preserve">17.3949718475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4919528961182</t>
   </si>
   <si>
     <t xml:space="preserve">17.5896739959717</t>
@@ -3518,7 +3518,7 @@
     <t xml:space="preserve">16.5164356231689</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7328796386719</t>
+    <t xml:space="preserve">15.7328805923462</t>
   </si>
   <si>
     <t xml:space="preserve">15.7423791885376</t>
@@ -3530,7 +3530,7 @@
     <t xml:space="preserve">15.9275808334351</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9703226089478</t>
+    <t xml:space="preserve">15.9703235626221</t>
   </si>
   <si>
     <t xml:space="preserve">16.6541538238525</t>
@@ -3554,16 +3554,16 @@
     <t xml:space="preserve">16.8251113891602</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7206363677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9628295898438</t>
+    <t xml:space="preserve">16.7206382751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9628276824951</t>
   </si>
   <si>
     <t xml:space="preserve">16.9438323974609</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8298587799072</t>
+    <t xml:space="preserve">16.8298606872559</t>
   </si>
   <si>
     <t xml:space="preserve">16.9913196563721</t>
@@ -3578,7 +3578,7 @@
     <t xml:space="preserve">16.8013687133789</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7111377716064</t>
+    <t xml:space="preserve">16.7111396789551</t>
   </si>
   <si>
     <t xml:space="preserve">17.2145156860352</t>
@@ -3587,7 +3587,7 @@
     <t xml:space="preserve">17.4424591064453</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3427352905273</t>
+    <t xml:space="preserve">17.3427333831787</t>
   </si>
   <si>
     <t xml:space="preserve">17.4662036895752</t>
@@ -3608,34 +3608,34 @@
     <t xml:space="preserve">18.7009010314941</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7911281585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9715824127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.945837020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4302158355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5536880493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7626323699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0903034210205</t>
+    <t xml:space="preserve">18.7911262512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9715843200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9458351135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4302177429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5536861419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7626342773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0903053283691</t>
   </si>
   <si>
     <t xml:space="preserve">19.3752346038818</t>
   </si>
   <si>
-    <t xml:space="preserve">18.92409324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1662864685059</t>
+    <t xml:space="preserve">18.9240951538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1662845611572</t>
   </si>
   <si>
     <t xml:space="preserve">19.4037265777588</t>
@@ -3659,7 +3659,7 @@
     <t xml:space="preserve">20.6289253234863</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0373249053955</t>
+    <t xml:space="preserve">21.0373268127441</t>
   </si>
   <si>
     <t xml:space="preserve">21.4457244873047</t>
@@ -3674,13 +3674,13 @@
     <t xml:space="preserve">20.6384220123291</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1635398864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0970573425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7903842926025</t>
+    <t xml:space="preserve">20.1635417938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0970554351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7903861999512</t>
   </si>
   <si>
     <t xml:space="preserve">20.7144050598145</t>
@@ -3689,22 +3689,22 @@
     <t xml:space="preserve">21.0278282165527</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0183296203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0943088531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4172325134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3982391357422</t>
+    <t xml:space="preserve">21.0183277130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.094310760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4172306060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3982372283936</t>
   </si>
   <si>
     <t xml:space="preserve">21.7021617889404</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5691947937012</t>
+    <t xml:space="preserve">21.5691928863525</t>
   </si>
   <si>
     <t xml:space="preserve">22.0820693969727</t>
@@ -3731,7 +3731,7 @@
     <t xml:space="preserve">18.7103977203369</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0550594329834</t>
+    <t xml:space="preserve">18.055061340332</t>
   </si>
   <si>
     <t xml:space="preserve">17.4946956634521</t>
@@ -3746,16 +3746,16 @@
     <t xml:space="preserve">18.5916767120361</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5394401550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0977973937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0503082275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2830028533936</t>
+    <t xml:space="preserve">18.5394420623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0977993011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0503101348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2830009460449</t>
   </si>
   <si>
     <t xml:space="preserve">18.1927757263184</t>
@@ -3767,37 +3767,37 @@
     <t xml:space="preserve">18.5679321289062</t>
   </si>
   <si>
-    <t xml:space="preserve">18.68190574646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7721328735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8006267547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5964241027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7768821716309</t>
+    <t xml:space="preserve">18.6819038391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7721309661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8006248474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5964260101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7768802642822</t>
   </si>
   <si>
     <t xml:space="preserve">17.9220924377441</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6581611633301</t>
+    <t xml:space="preserve">18.6581592559814</t>
   </si>
   <si>
     <t xml:space="preserve">18.4492111206055</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6324138641357</t>
+    <t xml:space="preserve">17.6324157714844</t>
   </si>
   <si>
     <t xml:space="preserve">17.7368869781494</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1242904663086</t>
+    <t xml:space="preserve">17.12428855896</t>
   </si>
   <si>
     <t xml:space="preserve">15.1867637634277</t>
@@ -3806,13 +3806,13 @@
     <t xml:space="preserve">14.8306016921997</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5076818466187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9133348464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3529739379883</t>
+    <t xml:space="preserve">14.5076808929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9133329391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3529748916626</t>
   </si>
   <si>
     <t xml:space="preserve">15.457447052002</t>
@@ -3821,7 +3821,7 @@
     <t xml:space="preserve">14.8733415603638</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5856676101685</t>
+    <t xml:space="preserve">15.5856666564941</t>
   </si>
   <si>
     <t xml:space="preserve">15.81360912323</t>
@@ -3833,10 +3833,10 @@
     <t xml:space="preserve">15.2390012741089</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2532482147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5191822052002</t>
+    <t xml:space="preserve">15.2532472610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5191831588745</t>
   </si>
   <si>
     <t xml:space="preserve">15.8278579711914</t>
@@ -3848,19 +3848,19 @@
     <t xml:space="preserve">16.316987991333</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9750699996948</t>
+    <t xml:space="preserve">15.9750709533691</t>
   </si>
   <si>
     <t xml:space="preserve">15.0253038406372</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6331548690796</t>
+    <t xml:space="preserve">15.6331539154053</t>
   </si>
   <si>
     <t xml:space="preserve">15.6521482467651</t>
   </si>
   <si>
-    <t xml:space="preserve">15.889591217041</t>
+    <t xml:space="preserve">15.8895902633667</t>
   </si>
   <si>
     <t xml:space="preserve">15.5096845626831</t>
@@ -3872,7 +3872,7 @@
     <t xml:space="preserve">14.8638439178467</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1392765045166</t>
+    <t xml:space="preserve">15.1392755508423</t>
   </si>
   <si>
     <t xml:space="preserve">15.7851181030273</t>
@@ -3887,13 +3887,13 @@
     <t xml:space="preserve">13.8285989761353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.812349319458</t>
+    <t xml:space="preserve">12.8123483657837</t>
   </si>
   <si>
     <t xml:space="preserve">14.1040306091309</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1990070343018</t>
+    <t xml:space="preserve">14.1990079879761</t>
   </si>
   <si>
     <t xml:space="preserve">15.0158061981201</t>
@@ -3902,16 +3902,16 @@
     <t xml:space="preserve">14.5219278335571</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8327665328979</t>
+    <t xml:space="preserve">14.8327655792236</t>
   </si>
   <si>
     <t xml:space="preserve">14.7744836807251</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6870594024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.075608253479</t>
+    <t xml:space="preserve">14.6870603561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0756072998047</t>
   </si>
   <si>
     <t xml:space="preserve">15.4932947158813</t>
@@ -3923,16 +3923,16 @@
     <t xml:space="preserve">15.7944183349609</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8915548324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9886913299561</t>
+    <t xml:space="preserve">15.8915557861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9886903762817</t>
   </si>
   <si>
     <t xml:space="preserve">15.8332719802856</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9692649841309</t>
+    <t xml:space="preserve">15.9692640304565</t>
   </si>
   <si>
     <t xml:space="preserve">15.949836730957</t>
@@ -3947,7 +3947,7 @@
     <t xml:space="preserve">14.492787361145</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7545490264893</t>
+    <t xml:space="preserve">13.7545480728149</t>
   </si>
   <si>
     <t xml:space="preserve">13.3465747833252</t>
@@ -3956,13 +3956,13 @@
     <t xml:space="preserve">13.8808259963989</t>
   </si>
   <si>
-    <t xml:space="preserve">13.366003036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7254085540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9391078948975</t>
+    <t xml:space="preserve">13.3660020828247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7254076004028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9391088485718</t>
   </si>
   <si>
     <t xml:space="preserve">14.1722364425659</t>
@@ -4019,13 +4019,13 @@
     <t xml:space="preserve">15.8235597610474</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6972818374634</t>
+    <t xml:space="preserve">15.6972808837891</t>
   </si>
   <si>
     <t xml:space="preserve">16.0178318023682</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2315330505371</t>
+    <t xml:space="preserve">16.2315311431885</t>
   </si>
   <si>
     <t xml:space="preserve">16.2703876495361</t>
@@ -4034,7 +4034,7 @@
     <t xml:space="preserve">15.6389999389648</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8721265792847</t>
+    <t xml:space="preserve">15.872127532959</t>
   </si>
   <si>
     <t xml:space="preserve">16.6783618927002</t>
@@ -4046,7 +4046,7 @@
     <t xml:space="preserve">16.9406318664551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4646625518799</t>
+    <t xml:space="preserve">16.4646606445312</t>
   </si>
   <si>
     <t xml:space="preserve">16.9794845581055</t>
@@ -4073,10 +4073,10 @@
     <t xml:space="preserve">17.2223262786865</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0960483551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.950345993042</t>
+    <t xml:space="preserve">17.0960502624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9503440856934</t>
   </si>
   <si>
     <t xml:space="preserve">17.0377674102783</t>
@@ -4097,13 +4097,13 @@
     <t xml:space="preserve">16.620080947876</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0664005279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6487131118774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6001443862915</t>
+    <t xml:space="preserve">16.0664024353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6487140655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6001434326172</t>
   </si>
   <si>
     <t xml:space="preserve">15.2990207672119</t>
@@ -4121,7 +4121,7 @@
     <t xml:space="preserve">15.2795934677124</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1727428436279</t>
+    <t xml:space="preserve">15.1727437973022</t>
   </si>
   <si>
     <t xml:space="preserve">14.4830732345581</t>
@@ -4133,7 +4133,7 @@
     <t xml:space="preserve">13.8905401229858</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3276538848877</t>
+    <t xml:space="preserve">14.327654838562</t>
   </si>
   <si>
     <t xml:space="preserve">14.4636468887329</t>
@@ -4148,7 +4148,7 @@
     <t xml:space="preserve">13.7156944274902</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5408477783203</t>
+    <t xml:space="preserve">13.540846824646</t>
   </si>
   <si>
     <t xml:space="preserve">13.9002542495728</t>
@@ -4202,7 +4202,7 @@
     <t xml:space="preserve">14.8910474777222</t>
   </si>
   <si>
-    <t xml:space="preserve">14.823052406311</t>
+    <t xml:space="preserve">14.8230514526367</t>
   </si>
   <si>
     <t xml:space="preserve">15.1241750717163</t>
@@ -4217,22 +4217,22 @@
     <t xml:space="preserve">16.4840869903564</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9304103851318</t>
+    <t xml:space="preserve">15.9304094314575</t>
   </si>
   <si>
     <t xml:space="preserve">16.1052551269531</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9789791107178</t>
+    <t xml:space="preserve">15.9789781570435</t>
   </si>
   <si>
     <t xml:space="preserve">15.8527002334595</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7652759552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5229434967041</t>
+    <t xml:space="preserve">15.7652769088745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5229415893555</t>
   </si>
   <si>
     <t xml:space="preserve">16.8046379089355</t>
@@ -4241,7 +4241,7 @@
     <t xml:space="preserve">16.8532085418701</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8434925079346</t>
+    <t xml:space="preserve">16.8434944152832</t>
   </si>
   <si>
     <t xml:space="preserve">16.5617961883545</t>
@@ -4280,7 +4280,7 @@
     <t xml:space="preserve">16.2121067047119</t>
   </si>
   <si>
-    <t xml:space="preserve">16.163537979126</t>
+    <t xml:space="preserve">16.1635360717773</t>
   </si>
   <si>
     <t xml:space="preserve">16.2995281219482</t>
@@ -4319,13 +4319,13 @@
     <t xml:space="preserve">17.8051452636719</t>
   </si>
   <si>
-    <t xml:space="preserve">17.795431137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9119968414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.038272857666</t>
+    <t xml:space="preserve">17.7954330444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9119987487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0382747650146</t>
   </si>
   <si>
     <t xml:space="preserve">17.9508514404297</t>
@@ -4403,10 +4403,10 @@
     <t xml:space="preserve">16.9017753601074</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3189544677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5812244415283</t>
+    <t xml:space="preserve">16.3189563751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.581226348877</t>
   </si>
   <si>
     <t xml:space="preserve">16.3869533538818</t>
@@ -4424,7 +4424,7 @@
     <t xml:space="preserve">15.8624143600464</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0761127471924</t>
+    <t xml:space="preserve">16.076114654541</t>
   </si>
   <si>
     <t xml:space="preserve">16.2412452697754</t>
@@ -4442,10 +4442,10 @@
     <t xml:space="preserve">16.6395072937012</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8818407058716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7361373901367</t>
+    <t xml:space="preserve">15.8818416595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7361364364624</t>
   </si>
   <si>
     <t xml:space="preserve">15.5612907409668</t>
@@ -4463,10 +4463,10 @@
     <t xml:space="preserve">15.4447259902954</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6778526306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0853204727173</t>
+    <t xml:space="preserve">15.6778535842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.085319519043</t>
   </si>
   <si>
     <t xml:space="preserve">15.1824569702148</t>
@@ -4478,7 +4478,7 @@
     <t xml:space="preserve">15.1436023712158</t>
   </si>
   <si>
-    <t xml:space="preserve">14.706488609314</t>
+    <t xml:space="preserve">14.7064876556396</t>
   </si>
   <si>
     <t xml:space="preserve">14.9440088272095</t>
@@ -4544,9 +4544,6 @@
     <t xml:space="preserve">14.7460746765137</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7064876556396</t>
-  </si>
-  <si>
     <t xml:space="preserve">14.6075210571289</t>
   </si>
   <si>
@@ -6071,7 +6068,10 @@
     <t xml:space="preserve">8.14000034332275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69999980926514</t>
+    <t xml:space="preserve">8.65999984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43000030517578</t>
   </si>
 </sst>
 </file>
@@ -55906,7 +55906,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G1904" t="s">
-        <v>1510</v>
+        <v>1488</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -55958,7 +55958,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G1906" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -55984,7 +55984,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G1907" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -56010,7 +56010,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G1908" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -56036,7 +56036,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G1909" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -56088,7 +56088,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1911" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -56140,7 +56140,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1913" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -56166,7 +56166,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1914" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -56192,7 +56192,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G1915" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -56218,7 +56218,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G1916" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -56244,7 +56244,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G1917" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -56270,7 +56270,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G1918" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -56322,7 +56322,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1920" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -56348,7 +56348,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G1921" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -56374,7 +56374,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G1922" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -56400,7 +56400,7 @@
         <v>14.4099998474121</v>
       </c>
       <c r="G1923" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -56426,7 +56426,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1924" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -56452,7 +56452,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G1925" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -56478,7 +56478,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G1926" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -56504,7 +56504,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1927" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -56530,7 +56530,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1928" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -56556,7 +56556,7 @@
         <v>14.6300001144409</v>
       </c>
       <c r="G1929" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -56582,7 +56582,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G1930" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -56608,7 +56608,7 @@
         <v>14.6099996566772</v>
       </c>
       <c r="G1931" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -56634,7 +56634,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G1932" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -56660,7 +56660,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G1933" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -56686,7 +56686,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G1934" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -56712,7 +56712,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1935" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -56738,7 +56738,7 @@
         <v>14.4099998474121</v>
       </c>
       <c r="G1936" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -56764,7 +56764,7 @@
         <v>14.2700004577637</v>
       </c>
       <c r="G1937" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -56790,7 +56790,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1938" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -56816,7 +56816,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G1939" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -56842,7 +56842,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G1940" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -56868,7 +56868,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G1941" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -56894,7 +56894,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G1942" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -56920,7 +56920,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G1943" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -56946,7 +56946,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G1944" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -56972,7 +56972,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G1945" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -56998,7 +56998,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1946" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -57024,7 +57024,7 @@
         <v>14.2700004577637</v>
       </c>
       <c r="G1947" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -57050,7 +57050,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G1948" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -57076,7 +57076,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1949" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -57102,7 +57102,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1950" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -57128,7 +57128,7 @@
         <v>14.6300001144409</v>
       </c>
       <c r="G1951" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -57154,7 +57154,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G1952" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -57180,7 +57180,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G1953" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -57206,7 +57206,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G1954" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -57232,7 +57232,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G1955" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -57258,7 +57258,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G1956" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -57284,7 +57284,7 @@
         <v>14.0299997329712</v>
       </c>
       <c r="G1957" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -57310,7 +57310,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G1958" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -57336,7 +57336,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1959" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -57362,7 +57362,7 @@
         <v>14.25</v>
       </c>
       <c r="G1960" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -57388,7 +57388,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G1961" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -57414,7 +57414,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G1962" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -57440,7 +57440,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1963" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -57466,7 +57466,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1964" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -57492,7 +57492,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G1965" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -57518,7 +57518,7 @@
         <v>14</v>
       </c>
       <c r="G1966" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -57544,7 +57544,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1967" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -57570,7 +57570,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G1968" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -57596,7 +57596,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1969" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -57622,7 +57622,7 @@
         <v>12.6099996566772</v>
       </c>
       <c r="G1970" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -57648,7 +57648,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1971" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -57674,7 +57674,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1972" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -57700,7 +57700,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G1973" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -57726,7 +57726,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G1974" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -57752,7 +57752,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G1975" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -57778,7 +57778,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1976" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -57804,7 +57804,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G1977" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -57830,7 +57830,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1978" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -57856,7 +57856,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G1979" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -57882,7 +57882,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G1980" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -57908,7 +57908,7 @@
         <v>12.0299997329712</v>
       </c>
       <c r="G1981" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -57934,7 +57934,7 @@
         <v>12</v>
       </c>
       <c r="G1982" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -57960,7 +57960,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G1983" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -57986,7 +57986,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G1984" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -58012,7 +58012,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1985" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -58038,7 +58038,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G1986" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -58064,7 +58064,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G1987" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -58090,7 +58090,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1988" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -58116,7 +58116,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1989" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -58142,7 +58142,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G1990" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -58168,7 +58168,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G1991" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -58194,7 +58194,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G1992" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -58220,7 +58220,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G1993" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -58246,7 +58246,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G1994" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -58272,7 +58272,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1995" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -58298,7 +58298,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1996" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -58324,7 +58324,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G1997" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -58350,7 +58350,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1998" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -58376,7 +58376,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1999" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -58402,7 +58402,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G2000" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -58428,7 +58428,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2001" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -58454,7 +58454,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G2002" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -58480,7 +58480,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G2003" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -58506,7 +58506,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G2004" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -58532,7 +58532,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G2005" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -58558,7 +58558,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G2006" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -58584,7 +58584,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G2007" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -58610,7 +58610,7 @@
         <v>12.25</v>
       </c>
       <c r="G2008" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -58636,7 +58636,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G2009" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -58662,7 +58662,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G2010" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -58688,7 +58688,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G2011" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -58714,7 +58714,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G2012" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -58740,7 +58740,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G2013" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -58766,7 +58766,7 @@
         <v>11.75</v>
       </c>
       <c r="G2014" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -58792,7 +58792,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G2015" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -58818,7 +58818,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2016" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -58844,7 +58844,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2017" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -58870,7 +58870,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2018" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -58896,7 +58896,7 @@
         <v>11.75</v>
       </c>
       <c r="G2019" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -58922,7 +58922,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2020" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -58948,7 +58948,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G2021" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -58974,7 +58974,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2022" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -59000,7 +59000,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G2023" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -59026,7 +59026,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2024" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -59052,7 +59052,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G2025" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -59078,7 +59078,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G2026" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -59104,7 +59104,7 @@
         <v>12.710000038147</v>
       </c>
       <c r="G2027" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -59130,7 +59130,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G2028" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -59156,7 +59156,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2029" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -59182,7 +59182,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G2030" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -59208,7 +59208,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2031" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -59234,7 +59234,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2032" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -59260,7 +59260,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G2033" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -59286,7 +59286,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2034" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -59312,7 +59312,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2035" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -59338,7 +59338,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G2036" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -59364,7 +59364,7 @@
         <v>12.1700000762939</v>
       </c>
       <c r="G2037" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -59390,7 +59390,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G2038" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -59416,7 +59416,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2039" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -59442,7 +59442,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G2040" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -59468,7 +59468,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G2041" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -59494,7 +59494,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G2042" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -59520,7 +59520,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G2043" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -59546,7 +59546,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G2044" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -59572,7 +59572,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G2045" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -59598,7 +59598,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G2046" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -59624,7 +59624,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G2047" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -59650,7 +59650,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G2048" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -59676,7 +59676,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G2049" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -59702,7 +59702,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2050" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -59728,7 +59728,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G2051" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -59754,7 +59754,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2052" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -59780,7 +59780,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G2053" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -59806,7 +59806,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G2054" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -59832,7 +59832,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G2055" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -59858,7 +59858,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G2056" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -59884,7 +59884,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G2057" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -59910,7 +59910,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G2058" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -59936,7 +59936,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G2059" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -59962,7 +59962,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G2060" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -59988,7 +59988,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G2061" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -60014,7 +60014,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G2062" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -60040,7 +60040,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G2063" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -60066,7 +60066,7 @@
         <v>12.25</v>
       </c>
       <c r="G2064" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -60092,7 +60092,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G2065" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -60118,7 +60118,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G2066" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -60144,7 +60144,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G2067" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -60170,7 +60170,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G2068" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -60196,7 +60196,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G2069" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -60222,7 +60222,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G2070" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -60248,7 +60248,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G2071" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -60274,7 +60274,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2072" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -60300,7 +60300,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G2073" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -60326,7 +60326,7 @@
         <v>12.75</v>
       </c>
       <c r="G2074" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -60352,7 +60352,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G2075" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -60378,7 +60378,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G2076" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -60404,7 +60404,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G2077" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -60430,7 +60430,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G2078" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -60456,7 +60456,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G2079" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -60482,7 +60482,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G2080" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -60508,7 +60508,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2081" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -60534,7 +60534,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G2082" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -60560,7 +60560,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G2083" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -60586,7 +60586,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G2084" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -60612,7 +60612,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2085" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -60638,7 +60638,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G2086" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -60664,7 +60664,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2087" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -60690,7 +60690,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2088" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -60716,7 +60716,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G2089" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -60742,7 +60742,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G2090" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -60768,7 +60768,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G2091" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -60794,7 +60794,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G2092" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -60820,7 +60820,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G2093" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -60846,7 +60846,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G2094" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -60872,7 +60872,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G2095" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -60898,7 +60898,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G2096" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -60924,7 +60924,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G2097" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -60950,7 +60950,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G2098" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -60976,7 +60976,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G2099" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -61002,7 +61002,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G2100" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -61028,7 +61028,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G2101" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -61054,7 +61054,7 @@
         <v>11</v>
       </c>
       <c r="G2102" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -61080,7 +61080,7 @@
         <v>10.75</v>
       </c>
       <c r="G2103" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -61106,7 +61106,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G2104" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -61132,7 +61132,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G2105" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -61158,7 +61158,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2106" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -61184,7 +61184,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G2107" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -61210,7 +61210,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G2108" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -61236,7 +61236,7 @@
         <v>9.25500011444092</v>
       </c>
       <c r="G2109" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -61262,7 +61262,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G2110" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -61288,7 +61288,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G2111" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -61314,7 +61314,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G2112" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -61340,7 +61340,7 @@
         <v>9.05500030517578</v>
       </c>
       <c r="G2113" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -61366,7 +61366,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G2114" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -61392,7 +61392,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G2115" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -61418,7 +61418,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G2116" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -61444,7 +61444,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G2117" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -61470,7 +61470,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G2118" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -61496,7 +61496,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G2119" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -61522,7 +61522,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G2120" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -61548,7 +61548,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G2121" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -61574,7 +61574,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G2122" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -61600,7 +61600,7 @@
         <v>9.44499969482422</v>
       </c>
       <c r="G2123" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -61626,7 +61626,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G2124" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -61652,7 +61652,7 @@
         <v>9.48499965667725</v>
       </c>
       <c r="G2125" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -61678,7 +61678,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G2126" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -61704,7 +61704,7 @@
         <v>9.64500045776367</v>
       </c>
       <c r="G2127" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -61730,7 +61730,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G2128" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -61756,7 +61756,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G2129" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -61782,7 +61782,7 @@
         <v>9.76500034332275</v>
       </c>
       <c r="G2130" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -61808,7 +61808,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G2131" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -61834,7 +61834,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G2132" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -61860,7 +61860,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G2133" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -61886,7 +61886,7 @@
         <v>9.24499988555908</v>
       </c>
       <c r="G2134" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -61912,7 +61912,7 @@
         <v>9.35499954223633</v>
       </c>
       <c r="G2135" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -61938,7 +61938,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G2136" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -61964,7 +61964,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G2137" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -61990,7 +61990,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G2138" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -62016,7 +62016,7 @@
         <v>9.34500026702881</v>
       </c>
       <c r="G2139" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -62042,7 +62042,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G2140" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -62068,7 +62068,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G2141" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -62094,7 +62094,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G2142" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -62120,7 +62120,7 @@
         <v>9.46500015258789</v>
       </c>
       <c r="G2143" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -62146,7 +62146,7 @@
         <v>9.4350004196167</v>
       </c>
       <c r="G2144" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -62172,7 +62172,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G2145" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -62198,7 +62198,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G2146" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -62224,7 +62224,7 @@
         <v>9.34500026702881</v>
       </c>
       <c r="G2147" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -62250,7 +62250,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G2148" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -62276,7 +62276,7 @@
         <v>9.10499954223633</v>
       </c>
       <c r="G2149" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -62302,7 +62302,7 @@
         <v>9.1850004196167</v>
       </c>
       <c r="G2150" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -62328,7 +62328,7 @@
         <v>9.00500011444092</v>
       </c>
       <c r="G2151" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -62354,7 +62354,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G2152" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -62380,7 +62380,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G2153" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -62406,7 +62406,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G2154" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -62432,7 +62432,7 @@
         <v>8.92500019073486</v>
       </c>
       <c r="G2155" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -62458,7 +62458,7 @@
         <v>8.89500045776367</v>
       </c>
       <c r="G2156" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -62484,7 +62484,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G2157" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -62510,7 +62510,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G2158" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -62536,7 +62536,7 @@
         <v>9.13500022888184</v>
       </c>
       <c r="G2159" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -62562,7 +62562,7 @@
         <v>9.125</v>
       </c>
       <c r="G2160" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -62588,7 +62588,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G2161" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -62614,7 +62614,7 @@
         <v>7.90500020980835</v>
       </c>
       <c r="G2162" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -62640,7 +62640,7 @@
         <v>7.84499979019165</v>
       </c>
       <c r="G2163" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -62666,7 +62666,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G2164" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -62692,7 +62692,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G2165" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -62718,7 +62718,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G2166" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -62744,7 +62744,7 @@
         <v>8.57499980926514</v>
       </c>
       <c r="G2167" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -62770,7 +62770,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G2168" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -62796,7 +62796,7 @@
         <v>8.35499954223633</v>
       </c>
       <c r="G2169" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -62822,7 +62822,7 @@
         <v>8.57499980926514</v>
       </c>
       <c r="G2170" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -62848,7 +62848,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G2171" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -62874,7 +62874,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G2172" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -62900,7 +62900,7 @@
         <v>8.25</v>
       </c>
       <c r="G2173" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -62926,7 +62926,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G2174" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -62952,7 +62952,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G2175" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -62978,7 +62978,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G2176" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -63004,7 +63004,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G2177" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -63030,7 +63030,7 @@
         <v>8.34500026702881</v>
       </c>
       <c r="G2178" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -63056,7 +63056,7 @@
         <v>8.23499965667725</v>
       </c>
       <c r="G2179" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -63082,7 +63082,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G2180" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -63108,7 +63108,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2181" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -63134,7 +63134,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G2182" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -63160,7 +63160,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2183" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -63186,7 +63186,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G2184" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -63212,7 +63212,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2185" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -63238,7 +63238,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G2186" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -63264,7 +63264,7 @@
         <v>7.9850001335144</v>
       </c>
       <c r="G2187" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -63290,7 +63290,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G2188" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -63316,7 +63316,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G2189" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -63342,7 +63342,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G2190" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -63368,7 +63368,7 @@
         <v>7.5</v>
       </c>
       <c r="G2191" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -63394,7 +63394,7 @@
         <v>7.375</v>
       </c>
       <c r="G2192" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -63420,7 +63420,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G2193" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -63446,7 +63446,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G2194" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -63472,7 +63472,7 @@
         <v>7.24499988555908</v>
       </c>
       <c r="G2195" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -63498,7 +63498,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G2196" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -63524,7 +63524,7 @@
         <v>7.5</v>
       </c>
       <c r="G2197" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -63550,7 +63550,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G2198" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -63576,7 +63576,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G2199" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -63602,7 +63602,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G2200" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -63628,7 +63628,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G2201" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -63654,7 +63654,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G2202" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -63680,7 +63680,7 @@
         <v>7.58500003814697</v>
       </c>
       <c r="G2203" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -63706,7 +63706,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2204" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -63732,7 +63732,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G2205" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -63758,7 +63758,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G2206" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -63784,7 +63784,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G2207" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -63810,7 +63810,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G2208" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -63836,7 +63836,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2209" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -63862,7 +63862,7 @@
         <v>7.09499979019165</v>
       </c>
       <c r="G2210" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -63888,7 +63888,7 @@
         <v>6.84499979019165</v>
       </c>
       <c r="G2211" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -63914,7 +63914,7 @@
         <v>6.65500020980835</v>
       </c>
       <c r="G2212" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -63940,7 +63940,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G2213" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -63966,7 +63966,7 @@
         <v>6.58500003814697</v>
       </c>
       <c r="G2214" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -63992,7 +63992,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G2215" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -64018,7 +64018,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G2216" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -64044,7 +64044,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G2217" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -64070,7 +64070,7 @@
         <v>6.35500001907349</v>
       </c>
       <c r="G2218" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -64096,7 +64096,7 @@
         <v>6.24499988555908</v>
       </c>
       <c r="G2219" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -64122,7 +64122,7 @@
         <v>6.47499990463257</v>
       </c>
       <c r="G2220" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -64148,7 +64148,7 @@
         <v>6.07499980926514</v>
       </c>
       <c r="G2221" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -64174,7 +64174,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G2222" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -64200,7 +64200,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G2223" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -64226,7 +64226,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G2224" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -64252,7 +64252,7 @@
         <v>6.72499990463257</v>
       </c>
       <c r="G2225" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -64278,7 +64278,7 @@
         <v>7.06500005722046</v>
       </c>
       <c r="G2226" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -64304,7 +64304,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G2227" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -64330,7 +64330,7 @@
         <v>6.9850001335144</v>
       </c>
       <c r="G2228" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -64356,7 +64356,7 @@
         <v>6.93499994277954</v>
       </c>
       <c r="G2229" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -64382,7 +64382,7 @@
         <v>6.69500017166138</v>
       </c>
       <c r="G2230" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -64408,7 +64408,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G2231" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -64434,7 +64434,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G2232" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -64460,7 +64460,7 @@
         <v>6.69500017166138</v>
       </c>
       <c r="G2233" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -64486,7 +64486,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G2234" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -64512,7 +64512,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G2235" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -64538,7 +64538,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G2236" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -64564,7 +64564,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G2237" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -64590,7 +64590,7 @@
         <v>6.47499990463257</v>
       </c>
       <c r="G2238" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -64616,7 +64616,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G2239" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -64642,7 +64642,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G2240" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -64668,7 +64668,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G2241" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -64694,7 +64694,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G2242" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -64720,7 +64720,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G2243" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -64746,7 +64746,7 @@
         <v>6.56500005722046</v>
       </c>
       <c r="G2244" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -64772,7 +64772,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G2245" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -64798,7 +64798,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G2246" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -64824,7 +64824,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G2247" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -64850,7 +64850,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G2248" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -64876,7 +64876,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G2249" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -64902,7 +64902,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G2250" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -64928,7 +64928,7 @@
         <v>6.18499994277954</v>
       </c>
       <c r="G2251" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -64954,7 +64954,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G2252" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -64980,7 +64980,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G2253" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -65006,7 +65006,7 @@
         <v>6.0149998664856</v>
       </c>
       <c r="G2254" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -65032,7 +65032,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G2255" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -65058,7 +65058,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G2256" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -65084,7 +65084,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G2257" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -65110,7 +65110,7 @@
         <v>5.7350001335144</v>
       </c>
       <c r="G2258" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -65136,7 +65136,7 @@
         <v>5.79500007629395</v>
       </c>
       <c r="G2259" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -65162,7 +65162,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G2260" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -65188,7 +65188,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G2261" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -65214,7 +65214,7 @@
         <v>6.17500019073486</v>
       </c>
       <c r="G2262" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -65240,7 +65240,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G2263" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -65266,7 +65266,7 @@
         <v>5.7350001335144</v>
       </c>
       <c r="G2264" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -65292,7 +65292,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G2265" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -65318,7 +65318,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G2266" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -65344,7 +65344,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G2267" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -65370,7 +65370,7 @@
         <v>5.80499982833862</v>
       </c>
       <c r="G2268" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -65396,7 +65396,7 @@
         <v>5.7350001335144</v>
       </c>
       <c r="G2269" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -65422,7 +65422,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2270" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -65448,7 +65448,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G2271" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -65474,7 +65474,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G2272" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -65500,7 +65500,7 @@
         <v>6.125</v>
       </c>
       <c r="G2273" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -65526,7 +65526,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G2274" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -65552,7 +65552,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G2275" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -65578,7 +65578,7 @@
         <v>6.34499979019165</v>
       </c>
       <c r="G2276" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -65604,7 +65604,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G2277" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -65630,7 +65630,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G2278" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -65656,7 +65656,7 @@
         <v>6.81500005722046</v>
       </c>
       <c r="G2279" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -65682,7 +65682,7 @@
         <v>6.75500011444092</v>
       </c>
       <c r="G2280" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -65708,7 +65708,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G2281" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -65734,7 +65734,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G2282" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -65760,7 +65760,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G2283" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -65786,7 +65786,7 @@
         <v>6.64499998092651</v>
       </c>
       <c r="G2284" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -65812,7 +65812,7 @@
         <v>6.64499998092651</v>
       </c>
       <c r="G2285" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -65838,7 +65838,7 @@
         <v>6.71500015258789</v>
       </c>
       <c r="G2286" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -65864,7 +65864,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G2287" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -65890,7 +65890,7 @@
         <v>6.81500005722046</v>
       </c>
       <c r="G2288" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -65916,7 +65916,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G2289" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -65942,7 +65942,7 @@
         <v>6.78499984741211</v>
       </c>
       <c r="G2290" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -65968,7 +65968,7 @@
         <v>6.58500003814697</v>
       </c>
       <c r="G2291" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -65994,7 +65994,7 @@
         <v>6.75500011444092</v>
       </c>
       <c r="G2292" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -66020,7 +66020,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G2293" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -66046,7 +66046,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G2294" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -66072,7 +66072,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G2295" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -66098,7 +66098,7 @@
         <v>6.78499984741211</v>
       </c>
       <c r="G2296" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -66124,7 +66124,7 @@
         <v>6.79500007629395</v>
       </c>
       <c r="G2297" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -66150,7 +66150,7 @@
         <v>6.65500020980835</v>
       </c>
       <c r="G2298" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -66176,7 +66176,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G2299" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -66202,7 +66202,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G2300" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -66228,7 +66228,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G2301" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -66254,7 +66254,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G2302" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -66280,7 +66280,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G2303" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -66306,7 +66306,7 @@
         <v>6.875</v>
       </c>
       <c r="G2304" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -66332,7 +66332,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G2305" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -66358,7 +66358,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G2306" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -66384,7 +66384,7 @@
         <v>7.2350001335144</v>
       </c>
       <c r="G2307" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -66410,7 +66410,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G2308" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -66436,7 +66436,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G2309" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -66462,7 +66462,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G2310" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -66488,7 +66488,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G2311" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -66514,7 +66514,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G2312" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -66540,7 +66540,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G2313" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -66566,7 +66566,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G2314" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -66592,7 +66592,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G2315" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -66618,7 +66618,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G2316" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -66644,7 +66644,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G2317" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -66670,7 +66670,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G2318" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -66696,7 +66696,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G2319" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -66722,7 +66722,7 @@
         <v>7.875</v>
       </c>
       <c r="G2320" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -66748,7 +66748,7 @@
         <v>8.08500003814697</v>
       </c>
       <c r="G2321" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -66774,7 +66774,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2322" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -66800,7 +66800,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G2323" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -66826,7 +66826,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G2324" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -66852,7 +66852,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G2325" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -66878,7 +66878,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G2326" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -66904,7 +66904,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G2327" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -66930,7 +66930,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G2328" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -66956,7 +66956,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G2329" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -66982,7 +66982,7 @@
         <v>7.86499977111816</v>
       </c>
       <c r="G2330" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -67008,7 +67008,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G2331" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -67034,7 +67034,7 @@
         <v>7.82499980926514</v>
       </c>
       <c r="G2332" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -67060,7 +67060,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G2333" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -67086,7 +67086,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G2334" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -67112,7 +67112,7 @@
         <v>7.5149998664856</v>
       </c>
       <c r="G2335" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -67138,7 +67138,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G2336" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -67164,7 +67164,7 @@
         <v>6.80499982833862</v>
       </c>
       <c r="G2337" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -67190,7 +67190,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G2338" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -67216,7 +67216,7 @@
         <v>6.61499977111816</v>
       </c>
       <c r="G2339" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -67242,7 +67242,7 @@
         <v>6.79500007629395</v>
       </c>
       <c r="G2340" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -67268,7 +67268,7 @@
         <v>6.875</v>
       </c>
       <c r="G2341" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -67294,7 +67294,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G2342" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -67320,7 +67320,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G2343" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -67346,7 +67346,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2344" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -67372,7 +67372,7 @@
         <v>6.80499982833862</v>
       </c>
       <c r="G2345" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -67398,7 +67398,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G2346" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -67424,7 +67424,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G2347" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -67450,7 +67450,7 @@
         <v>6.58500003814697</v>
       </c>
       <c r="G2348" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -67476,7 +67476,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G2349" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -67502,7 +67502,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G2350" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -67528,7 +67528,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G2351" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -67554,7 +67554,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G2352" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -67580,7 +67580,7 @@
         <v>6.125</v>
       </c>
       <c r="G2353" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -67606,7 +67606,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G2354" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -67632,7 +67632,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G2355" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -67658,7 +67658,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G2356" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -67684,7 +67684,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G2357" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -67710,7 +67710,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G2358" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -67736,7 +67736,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G2359" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -67762,7 +67762,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2360" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -67788,7 +67788,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G2361" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -67814,7 +67814,7 @@
         <v>5.18499994277954</v>
       </c>
       <c r="G2362" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -67840,7 +67840,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G2363" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -67866,7 +67866,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G2364" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -67892,7 +67892,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G2365" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -67918,7 +67918,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G2366" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -67944,7 +67944,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G2367" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -67970,7 +67970,7 @@
         <v>5.5</v>
       </c>
       <c r="G2368" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -67996,7 +67996,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G2369" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -68022,7 +68022,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G2370" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -68048,7 +68048,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G2371" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -68074,7 +68074,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G2372" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -68100,7 +68100,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G2373" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -68126,7 +68126,7 @@
         <v>5.58500003814697</v>
       </c>
       <c r="G2374" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -68152,7 +68152,7 @@
         <v>5.56500005722046</v>
       </c>
       <c r="G2375" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -68178,7 +68178,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G2376" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -68204,7 +68204,7 @@
         <v>5.66499996185303</v>
       </c>
       <c r="G2377" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -68230,7 +68230,7 @@
         <v>5.625</v>
       </c>
       <c r="G2378" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -68256,7 +68256,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G2379" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -68282,7 +68282,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G2380" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -68308,7 +68308,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G2381" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -68334,7 +68334,7 @@
         <v>5.86499977111816</v>
       </c>
       <c r="G2382" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -68360,7 +68360,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G2383" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -68386,7 +68386,7 @@
         <v>5.875</v>
       </c>
       <c r="G2384" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -68412,7 +68412,7 @@
         <v>5.97499990463257</v>
       </c>
       <c r="G2385" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -68438,7 +68438,7 @@
         <v>5.86499977111816</v>
       </c>
       <c r="G2386" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -68464,7 +68464,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G2387" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -68490,7 +68490,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G2388" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -68516,7 +68516,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2389" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -68542,7 +68542,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2390" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -68568,7 +68568,7 @@
         <v>5.625</v>
       </c>
       <c r="G2391" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -68594,7 +68594,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G2392" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -68620,7 +68620,7 @@
         <v>5.71500015258789</v>
       </c>
       <c r="G2393" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -68646,7 +68646,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2394" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -68672,7 +68672,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G2395" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -68698,7 +68698,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G2396" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -68724,7 +68724,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G2397" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -68750,7 +68750,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G2398" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -68776,7 +68776,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G2399" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -68802,7 +68802,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G2400" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -68828,7 +68828,7 @@
         <v>5.47499990463257</v>
       </c>
       <c r="G2401" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -68854,7 +68854,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G2402" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -68880,7 +68880,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G2403" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -68906,7 +68906,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2404" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -68932,7 +68932,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G2405" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -68958,7 +68958,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G2406" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -68984,7 +68984,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G2407" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -69010,7 +69010,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G2408" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -69036,7 +69036,7 @@
         <v>4.93400001525879</v>
       </c>
       <c r="G2409" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -69062,7 +69062,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G2410" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -69088,7 +69088,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G2411" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -69114,7 +69114,7 @@
         <v>4.91200017929077</v>
       </c>
       <c r="G2412" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -69140,7 +69140,7 @@
         <v>4.99200010299683</v>
       </c>
       <c r="G2413" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -69166,7 +69166,7 @@
         <v>5</v>
       </c>
       <c r="G2414" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -69192,7 +69192,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G2415" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -69218,7 +69218,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G2416" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -69244,7 +69244,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G2417" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -69270,7 +69270,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G2418" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -69296,7 +69296,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G2419" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -69322,7 +69322,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G2420" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -69348,7 +69348,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G2421" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -69374,7 +69374,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G2422" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -69400,7 +69400,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G2423" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -69426,7 +69426,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G2424" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -69452,7 +69452,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G2425" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -69478,7 +69478,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G2426" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -69504,7 +69504,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G2427" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -69530,7 +69530,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G2428" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -69556,7 +69556,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G2429" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -69582,7 +69582,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G2430" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -69608,7 +69608,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G2431" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -69634,7 +69634,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G2432" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -69660,7 +69660,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G2433" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -69686,7 +69686,7 @@
         <v>5.25</v>
       </c>
       <c r="G2434" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -69712,7 +69712,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G2435" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -69738,7 +69738,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G2436" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -69764,7 +69764,7 @@
         <v>4.98400020599365</v>
       </c>
       <c r="G2437" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -69790,7 +69790,7 @@
         <v>4.91200017929077</v>
       </c>
       <c r="G2438" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -69816,7 +69816,7 @@
         <v>4.77400016784668</v>
       </c>
       <c r="G2439" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -69842,7 +69842,7 @@
         <v>4.64400005340576</v>
       </c>
       <c r="G2440" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -69868,7 +69868,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G2441" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -69894,7 +69894,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G2442" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -69920,7 +69920,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2443" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -69946,7 +69946,7 @@
         <v>4.44199991226196</v>
       </c>
       <c r="G2444" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -69972,7 +69972,7 @@
         <v>4.47200012207031</v>
       </c>
       <c r="G2445" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -69998,7 +69998,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G2446" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -70024,7 +70024,7 @@
         <v>4.52799987792969</v>
       </c>
       <c r="G2447" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -70050,7 +70050,7 @@
         <v>4.50600004196167</v>
       </c>
       <c r="G2448" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -70076,7 +70076,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G2449" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -70102,7 +70102,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G2450" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -70128,7 +70128,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G2451" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -70154,7 +70154,7 @@
         <v>4.79199981689453</v>
       </c>
       <c r="G2452" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -70180,7 +70180,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G2453" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -70206,7 +70206,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G2454" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -70232,7 +70232,7 @@
         <v>4.88600015640259</v>
       </c>
       <c r="G2455" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -70258,7 +70258,7 @@
         <v>4.88600015640259</v>
       </c>
       <c r="G2456" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -70284,7 +70284,7 @@
         <v>4.7020001411438</v>
       </c>
       <c r="G2457" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -70310,7 +70310,7 @@
         <v>4.62799978256226</v>
       </c>
       <c r="G2458" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -70336,7 +70336,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G2459" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -70362,7 +70362,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G2460" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -70388,7 +70388,7 @@
         <v>4.64200019836426</v>
       </c>
       <c r="G2461" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -70414,7 +70414,7 @@
         <v>4.62200021743774</v>
       </c>
       <c r="G2462" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -70440,7 +70440,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G2463" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -70466,7 +70466,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2464" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -70492,7 +70492,7 @@
         <v>4.69600009918213</v>
       </c>
       <c r="G2465" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -70518,7 +70518,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G2466" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -70544,7 +70544,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G2467" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -70570,7 +70570,7 @@
         <v>4.6560001373291</v>
       </c>
       <c r="G2468" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -70596,7 +70596,7 @@
         <v>4.72399997711182</v>
       </c>
       <c r="G2469" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -70622,7 +70622,7 @@
         <v>4.85799980163574</v>
       </c>
       <c r="G2470" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -70648,7 +70648,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G2471" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -70674,7 +70674,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G2472" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -70700,7 +70700,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G2473" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -70726,7 +70726,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G2474" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -70752,7 +70752,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2475" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -70778,7 +70778,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G2476" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -70804,7 +70804,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2477" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -70830,7 +70830,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G2478" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -70856,7 +70856,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G2479" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -70882,7 +70882,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G2480" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -70908,7 +70908,7 @@
         <v>5.56500005722046</v>
       </c>
       <c r="G2481" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -70934,7 +70934,7 @@
         <v>5.97499990463257</v>
       </c>
       <c r="G2482" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -70960,7 +70960,7 @@
         <v>5.7649998664856</v>
       </c>
       <c r="G2483" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -70986,7 +70986,7 @@
         <v>5.875</v>
       </c>
       <c r="G2484" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -71012,7 +71012,7 @@
         <v>6.18499994277954</v>
       </c>
       <c r="G2485" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -71038,7 +71038,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G2486" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -71064,7 +71064,7 @@
         <v>5.80499982833862</v>
       </c>
       <c r="G2487" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -71090,7 +71090,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G2488" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -71116,7 +71116,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G2489" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -71142,7 +71142,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G2490" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -71168,7 +71168,7 @@
         <v>5.94500017166138</v>
       </c>
       <c r="G2491" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -71194,7 +71194,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G2492" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -71220,7 +71220,7 @@
         <v>6.17500019073486</v>
       </c>
       <c r="G2493" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -71246,7 +71246,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G2494" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -71272,7 +71272,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G2495" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -71298,7 +71298,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G2496" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -71324,7 +71324,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G2497" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -71350,7 +71350,7 @@
         <v>7.25</v>
       </c>
       <c r="G2498" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -71376,7 +71376,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G2499" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -71402,7 +71402,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G2500" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -71428,7 +71428,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G2501" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -71454,7 +71454,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2502" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -71480,7 +71480,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G2503" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -71506,7 +71506,7 @@
         <v>6.74499988555908</v>
       </c>
       <c r="G2504" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -71532,7 +71532,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G2505" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -71558,7 +71558,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G2506" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -71584,7 +71584,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G2507" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -71610,7 +71610,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G2508" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -71636,7 +71636,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G2509" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -71662,7 +71662,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G2510" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -71688,7 +71688,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2511" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -71714,7 +71714,7 @@
         <v>7.66499996185303</v>
       </c>
       <c r="G2512" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -71740,7 +71740,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G2513" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -71766,7 +71766,7 @@
         <v>7.25</v>
       </c>
       <c r="G2514" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -71792,7 +71792,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G2515" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -71818,7 +71818,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G2516" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -71844,7 +71844,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G2517" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -71870,7 +71870,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G2518" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -71896,7 +71896,7 @@
         <v>7.65500020980835</v>
       </c>
       <c r="G2519" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -71922,7 +71922,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G2520" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -71948,7 +71948,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G2521" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -71974,7 +71974,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G2522" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -72000,7 +72000,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G2523" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -72026,7 +72026,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G2524" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -72052,7 +72052,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G2525" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="H2525" t="s">
         <v>9</v>
@@ -72078,7 +72078,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G2526" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H2526" t="s">
         <v>9</v>
@@ -72104,7 +72104,7 @@
         <v>8</v>
       </c>
       <c r="G2527" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H2527" t="s">
         <v>9</v>
@@ -72130,7 +72130,7 @@
         <v>7.77500009536743</v>
       </c>
       <c r="G2528" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H2528" t="s">
         <v>9</v>
@@ -72156,7 +72156,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G2529" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H2529" t="s">
         <v>9</v>
@@ -72182,7 +72182,7 @@
         <v>7.75</v>
       </c>
       <c r="G2530" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H2530" t="s">
         <v>9</v>
@@ -72208,7 +72208,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G2531" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H2531" t="s">
         <v>9</v>
@@ -72234,7 +72234,7 @@
         <v>7.99499988555908</v>
       </c>
       <c r="G2532" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H2532" t="s">
         <v>9</v>
@@ -72260,7 +72260,7 @@
         <v>8.08500003814697</v>
       </c>
       <c r="G2533" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="H2533" t="s">
         <v>9</v>
@@ -72286,7 +72286,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G2534" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H2534" t="s">
         <v>9</v>
@@ -72312,7 +72312,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G2535" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H2535" t="s">
         <v>9</v>
@@ -72338,7 +72338,7 @@
         <v>8.14500045776367</v>
       </c>
       <c r="G2536" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H2536" t="s">
         <v>9</v>
@@ -72364,7 +72364,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2537" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H2537" t="s">
         <v>9</v>
@@ -72390,7 +72390,7 @@
         <v>8.07499980926514</v>
       </c>
       <c r="G2538" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H2538" t="s">
         <v>9</v>
@@ -72416,7 +72416,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G2539" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H2539" t="s">
         <v>9</v>
@@ -72442,7 +72442,7 @@
         <v>8.22500038146973</v>
       </c>
       <c r="G2540" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="H2540" t="s">
         <v>9</v>
@@ -72468,7 +72468,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G2541" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H2541" t="s">
         <v>9</v>
@@ -72494,7 +72494,7 @@
         <v>8.34500026702881</v>
       </c>
       <c r="G2542" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="H2542" t="s">
         <v>9</v>
@@ -72520,7 +72520,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G2543" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H2543" t="s">
         <v>9</v>
@@ -72528,13 +72528,13 @@
     </row>
     <row r="2544">
       <c r="A2544" s="1" t="n">
-        <v>46028.6874884259</v>
+        <v>46028.3333333333</v>
       </c>
       <c r="B2544" t="n">
-        <v>558662</v>
+        <v>700340</v>
       </c>
       <c r="C2544" t="n">
-        <v>8.69499969482422</v>
+        <v>8.71000003814697</v>
       </c>
       <c r="D2544" t="n">
         <v>8.0600004196167</v>
@@ -72543,12 +72543,38 @@
         <v>8.10499954223633</v>
       </c>
       <c r="F2544" t="n">
-        <v>8.69999980926514</v>
+        <v>8.65999984741211</v>
       </c>
       <c r="G2544" t="s">
+        <v>2018</v>
+      </c>
+      <c r="H2544" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2545">
+      <c r="A2545" s="1" t="n">
+        <v>46029.6911574074</v>
+      </c>
+      <c r="B2545" t="n">
+        <v>628470</v>
+      </c>
+      <c r="C2545" t="n">
+        <v>8.65999984741211</v>
+      </c>
+      <c r="D2545" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="E2545" t="n">
+        <v>8.65999984741211</v>
+      </c>
+      <c r="F2545" t="n">
+        <v>8.43000030517578</v>
+      </c>
+      <c r="G2545" t="s">
         <v>2019</v>
       </c>
-      <c r="H2544" t="s">
+      <c r="H2545" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2023" uniqueCount="2023">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2024" uniqueCount="2024">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2763500213623</t>
+    <t xml:space="preserve">18.2763519287109</t>
   </si>
   <si>
     <t xml:space="preserve">SFER.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0109615325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4978828430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9401931762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.683650970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2498111724854</t>
+    <t xml:space="preserve">18.0109672546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4978809356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9401950836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6836547851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.249813079834</t>
   </si>
   <si>
     <t xml:space="preserve">19.4086723327637</t>
@@ -65,19 +65,19 @@
     <t xml:space="preserve">19.1344375610352</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8425121307373</t>
+    <t xml:space="preserve">18.8425102233887</t>
   </si>
   <si>
     <t xml:space="preserve">18.4621257781982</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2851982116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0994262695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6394214630127</t>
+    <t xml:space="preserve">18.2851943969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0994243621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6394233703613</t>
   </si>
   <si>
     <t xml:space="preserve">17.5686511993408</t>
@@ -86,31 +86,31 @@
     <t xml:space="preserve">18.1878871917725</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4798145294189</t>
+    <t xml:space="preserve">18.4798164367676</t>
   </si>
   <si>
     <t xml:space="preserve">18.223274230957</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7632675170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3913555145264</t>
+    <t xml:space="preserve">17.7632694244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3913536071777</t>
   </si>
   <si>
     <t xml:space="preserve">18.6744327545166</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9578857421875</t>
+    <t xml:space="preserve">17.9578838348389</t>
   </si>
   <si>
     <t xml:space="preserve">18.2055816650391</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2586574554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0817317962646</t>
+    <t xml:space="preserve">18.258659362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0817375183105</t>
   </si>
   <si>
     <t xml:space="preserve">17.3563423156738</t>
@@ -128,22 +128,22 @@
     <t xml:space="preserve">17.0201854705811</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4890384674072</t>
+    <t xml:space="preserve">17.48903465271</t>
   </si>
   <si>
     <t xml:space="preserve">17.6305751800537</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4090461730957</t>
+    <t xml:space="preserve">18.4090442657471</t>
   </si>
   <si>
     <t xml:space="preserve">18.4532775878906</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9752063751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1348133087158</t>
+    <t xml:space="preserve">18.9752044677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1348075866699</t>
   </si>
   <si>
     <t xml:space="preserve">17.3121109008789</t>
@@ -152,31 +152,31 @@
     <t xml:space="preserve">17.9048099517822</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3471183776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0194358825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0017414093018</t>
+    <t xml:space="preserve">18.3471202850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.019437789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0017433166504</t>
   </si>
   <si>
     <t xml:space="preserve">18.8513584136963</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3113632202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9925231933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9482898712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7271366119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3379001617432</t>
+    <t xml:space="preserve">19.3113651275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.992525100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9482917785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7271327972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3379039764404</t>
   </si>
   <si>
     <t xml:space="preserve">19.647518157959</t>
@@ -185,70 +185,70 @@
     <t xml:space="preserve">19.9836769104004</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1167469024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4440517425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0367546081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1782932281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4971351623535</t>
+    <t xml:space="preserve">19.1167449951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.444055557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0367565155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.178295135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4971332550049</t>
   </si>
   <si>
     <t xml:space="preserve">19.4705944061279</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9663581848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4794406890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9129066467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8686771392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4175205230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8690528869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8336639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5151996612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9309749603271</t>
+    <t xml:space="preserve">18.9663600921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4794445037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9129085540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8686752319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4175186157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8690490722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.833667755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5152015686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9309711456299</t>
   </si>
   <si>
     <t xml:space="preserve">18.8955898284912</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5240459442139</t>
+    <t xml:space="preserve">18.5240497589111</t>
   </si>
   <si>
     <t xml:space="preserve">18.9486675262451</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7982807159424</t>
+    <t xml:space="preserve">18.7982788085938</t>
   </si>
   <si>
     <t xml:space="preserve">18.8778972625732</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2936668395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8071269989014</t>
+    <t xml:space="preserve">19.2936687469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.80712890625</t>
   </si>
   <si>
     <t xml:space="preserve">18.3205814361572</t>
@@ -263,31 +263,31 @@
     <t xml:space="preserve">18.0640411376953</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3117351531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.878267288208</t>
+    <t xml:space="preserve">18.3117370605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8782711029053</t>
   </si>
   <si>
     <t xml:space="preserve">18.0021152496338</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7190380096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4448051452637</t>
+    <t xml:space="preserve">17.7190399169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.444803237915</t>
   </si>
   <si>
     <t xml:space="preserve">17.1440315246582</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5509586334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9844264984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4182643890381</t>
+    <t xml:space="preserve">17.5509605407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9844245910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4182662963867</t>
   </si>
   <si>
     <t xml:space="preserve">17.9313488006592</t>
@@ -296,13 +296,13 @@
     <t xml:space="preserve">17.7367305755615</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6482677459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5939350128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.81125831604</t>
+    <t xml:space="preserve">17.6482715606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5939388275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8112564086914</t>
   </si>
   <si>
     <t xml:space="preserve">17.7025985717773</t>
@@ -314,28 +314,28 @@
     <t xml:space="preserve">17.530553817749</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4128360748291</t>
+    <t xml:space="preserve">17.4128379821777</t>
   </si>
   <si>
     <t xml:space="preserve">17.3041763305664</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4762210845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4309463500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4852771759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7478733062744</t>
+    <t xml:space="preserve">17.4762229919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.430944442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4852752685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7478713989258</t>
   </si>
   <si>
     <t xml:space="preserve">17.6844882965088</t>
   </si>
   <si>
-    <t xml:space="preserve">17.150239944458</t>
+    <t xml:space="preserve">17.1502418518066</t>
   </si>
   <si>
     <t xml:space="preserve">16.7155990600586</t>
@@ -344,19 +344,19 @@
     <t xml:space="preserve">16.5435543060303</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0415802001953</t>
+    <t xml:space="preserve">17.0415821075439</t>
   </si>
   <si>
     <t xml:space="preserve">17.0778007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8384246826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9380302429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7297630310059</t>
+    <t xml:space="preserve">17.8384227752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9380264282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7297611236572</t>
   </si>
   <si>
     <t xml:space="preserve">17.8655872344971</t>
@@ -365,22 +365,22 @@
     <t xml:space="preserve">18.1825141906738</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8514232635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3896179199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6793804168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.262845993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5254421234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6069355010986</t>
+    <t xml:space="preserve">16.8514251708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3896160125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6793785095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2628440856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5254440307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6069412231445</t>
   </si>
   <si>
     <t xml:space="preserve">16.8061504364014</t>
@@ -389,28 +389,28 @@
     <t xml:space="preserve">16.8242588043213</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0726909637451</t>
+    <t xml:space="preserve">16.0726890563965</t>
   </si>
   <si>
     <t xml:space="preserve">15.8734798431396</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3624515533447</t>
+    <t xml:space="preserve">16.3624496459961</t>
   </si>
   <si>
     <t xml:space="preserve">16.4439468383789</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6974868774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0959091186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1321315765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0868549346924</t>
+    <t xml:space="preserve">16.6974906921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.095911026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1321296691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.086856842041</t>
   </si>
   <si>
     <t xml:space="preserve">17.0325260162354</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">17.3403949737549</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9018115997314</t>
+    <t xml:space="preserve">17.9018077850342</t>
   </si>
   <si>
     <t xml:space="preserve">18.1372413635254</t>
@@ -428,97 +428,97 @@
     <t xml:space="preserve">17.9289722442627</t>
   </si>
   <si>
-    <t xml:space="preserve">18.771089553833</t>
+    <t xml:space="preserve">18.7710914611816</t>
   </si>
   <si>
     <t xml:space="preserve">18.6352672576904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0699081420898</t>
+    <t xml:space="preserve">19.0699062347412</t>
   </si>
   <si>
     <t xml:space="preserve">19.2147884368896</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6262092590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.499439239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2187366485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7167625427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5809383392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.762035369873</t>
+    <t xml:space="preserve">18.6262130737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4994411468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2187347412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.716760635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5809345245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7620391845703</t>
   </si>
   <si>
     <t xml:space="preserve">18.8073139190674</t>
   </si>
   <si>
-    <t xml:space="preserve">18.94313621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.04274559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6624336242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4722766876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6171550750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7529811859131</t>
+    <t xml:space="preserve">18.9431400299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0427436828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6624317169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4722747802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6171569824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7529830932617</t>
   </si>
   <si>
     <t xml:space="preserve">18.9703044891357</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6805400848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6081027984619</t>
+    <t xml:space="preserve">18.6805419921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6081008911133</t>
   </si>
   <si>
     <t xml:space="preserve">18.653377532959</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5175533294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8707008361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6986503601074</t>
+    <t xml:space="preserve">18.5175514221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.870698928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6986522674561</t>
   </si>
   <si>
     <t xml:space="preserve">19.106128692627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9210815429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6947059631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5588817596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4592742919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3143939971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8888092041016</t>
+    <t xml:space="preserve">19.9210834503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6947040557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5588798522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4592781066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.314395904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8888072967529</t>
   </si>
   <si>
     <t xml:space="preserve">19.1332931518555</t>
@@ -536,40 +536,40 @@
     <t xml:space="preserve">20.3557224273682</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3104476928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3919429779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4643840789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6907596588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8446960449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7994174957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4009990692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1021823883057</t>
+    <t xml:space="preserve">20.3104496002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3919448852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4643859863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6907615661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8446941375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7994194030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4010009765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1021842956543</t>
   </si>
   <si>
     <t xml:space="preserve">20.5277709960938</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3647785186768</t>
+    <t xml:space="preserve">20.3647766113281</t>
   </si>
   <si>
     <t xml:space="preserve">20.5458793640137</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7541446685791</t>
+    <t xml:space="preserve">20.7541484832764</t>
   </si>
   <si>
     <t xml:space="preserve">20.4191074371338</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">20.265172958374</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3285598754883</t>
+    <t xml:space="preserve">20.3285579681396</t>
   </si>
   <si>
     <t xml:space="preserve">20.0387954711914</t>
@@ -593,10 +593,10 @@
     <t xml:space="preserve">20.2289524078369</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5006046295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5639896392822</t>
+    <t xml:space="preserve">20.500602722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5639877319336</t>
   </si>
   <si>
     <t xml:space="preserve">20.1836776733398</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">19.5045528411865</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7218685150146</t>
+    <t xml:space="preserve">19.7218704223633</t>
   </si>
   <si>
     <t xml:space="preserve">19.7943134307861</t>
@@ -620,10 +620,10 @@
     <t xml:space="preserve">19.5226593017578</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8305339813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9120273590088</t>
+    <t xml:space="preserve">19.8305320739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9120254516602</t>
   </si>
   <si>
     <t xml:space="preserve">19.7490348815918</t>
@@ -635,112 +635,112 @@
     <t xml:space="preserve">18.3002281188965</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3273944854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2458992004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0104656219482</t>
+    <t xml:space="preserve">18.3273963928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2459011077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0104694366455</t>
   </si>
   <si>
     <t xml:space="preserve">17.7388172149658</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8565330505371</t>
+    <t xml:space="preserve">17.8565292358398</t>
   </si>
   <si>
     <t xml:space="preserve">17.8203144073486</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6392116546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3455085754395</t>
+    <t xml:space="preserve">17.6392135620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3455028533936</t>
   </si>
   <si>
     <t xml:space="preserve">18.3907814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">19.151403427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2872295379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3958873748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3777809143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1151847839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5860443115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2600631713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3738346099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3466663360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2380084991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1293468475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1565113067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8084774017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6183185577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4785480499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5328807830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0671272277832</t>
+    <t xml:space="preserve">19.1514015197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2872314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3958911895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.377779006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1151866912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5860462188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2600650787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3738327026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3466701507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2380065917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1293449401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1565132141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8084754943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6183204650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4785461425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5328788757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0671253204346</t>
   </si>
   <si>
     <t xml:space="preserve">22.0580711364746</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2572841644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2935028076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3025550842285</t>
+    <t xml:space="preserve">22.2572803497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2935009002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3025588989258</t>
   </si>
   <si>
     <t xml:space="preserve">22.3206653594971</t>
   </si>
   <si>
-    <t xml:space="preserve">22.275390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2391700744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8186931610107</t>
+    <t xml:space="preserve">22.2753925323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2391719818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.818696975708</t>
   </si>
   <si>
     <t xml:space="preserve">23.0722351074219</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8911361694336</t>
+    <t xml:space="preserve">22.891134262085</t>
   </si>
   <si>
     <t xml:space="preserve">23.1537322998047</t>
@@ -749,13 +749,13 @@
     <t xml:space="preserve">23.0993995666504</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5923156738281</t>
+    <t xml:space="preserve">22.5923194885254</t>
   </si>
   <si>
     <t xml:space="preserve">22.3568878173828</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9092445373535</t>
+    <t xml:space="preserve">22.9092464447021</t>
   </si>
   <si>
     <t xml:space="preserve">22.1757869720459</t>
@@ -764,7 +764,7 @@
     <t xml:space="preserve">22.1395645141602</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6064853668213</t>
+    <t xml:space="preserve">23.606481552124</t>
   </si>
   <si>
     <t xml:space="preserve">23.7513618469238</t>
@@ -779,31 +779,31 @@
     <t xml:space="preserve">23.6879768371582</t>
   </si>
   <si>
-    <t xml:space="preserve">23.561206817627</t>
+    <t xml:space="preserve">23.5612087249756</t>
   </si>
   <si>
     <t xml:space="preserve">23.7423076629639</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7241992950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6336479187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8238010406494</t>
+    <t xml:space="preserve">23.7241954803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6336460113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.823802947998</t>
   </si>
   <si>
     <t xml:space="preserve">23.6970329284668</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0139598846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.285608291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0682907104492</t>
+    <t xml:space="preserve">24.0139560699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2856101989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0682888031006</t>
   </si>
   <si>
     <t xml:space="preserve">23.9777393341064</t>
@@ -812,13 +812,13 @@
     <t xml:space="preserve">24.2946643829346</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4304904937744</t>
+    <t xml:space="preserve">24.430492401123</t>
   </si>
   <si>
     <t xml:space="preserve">24.6115913391113</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7655277252197</t>
+    <t xml:space="preserve">24.7655258178711</t>
   </si>
   <si>
     <t xml:space="preserve">25.1911125183105</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">25.4265441894531</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6167011260986</t>
+    <t xml:space="preserve">25.6167030334473</t>
   </si>
   <si>
     <t xml:space="preserve">25.6710300445557</t>
@@ -839,22 +839,22 @@
     <t xml:space="preserve">25.6529197692871</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7615814208984</t>
+    <t xml:space="preserve">25.7615833282471</t>
   </si>
   <si>
     <t xml:space="preserve">25.5352058410645</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9556846618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9013500213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0643424987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8017463684082</t>
+    <t xml:space="preserve">24.9556827545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9013519287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0643463134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8017482757568</t>
   </si>
   <si>
     <t xml:space="preserve">24.6206474304199</t>
@@ -863,19 +863,19 @@
     <t xml:space="preserve">24.9375743865967</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3722171783447</t>
+    <t xml:space="preserve">25.3722133636475</t>
   </si>
   <si>
     <t xml:space="preserve">25.62575340271</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2273349761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.173002243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1639499664307</t>
+    <t xml:space="preserve">25.2273330688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1730041503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.163948059082</t>
   </si>
   <si>
     <t xml:space="preserve">25.399377822876</t>
@@ -884,43 +884,43 @@
     <t xml:space="preserve">25.7253608703613</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2907218933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1277275085449</t>
+    <t xml:space="preserve">25.2907199859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1277294158936</t>
   </si>
   <si>
     <t xml:space="preserve">25.7434711456299</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5442600250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4808712005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5080413818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2635555267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0824565887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7836360931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4214382171631</t>
+    <t xml:space="preserve">25.5442581176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4808731079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5080375671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2635536193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0824527740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7836399078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4214344024658</t>
   </si>
   <si>
     <t xml:space="preserve">24.2674980163574</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5261497497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1237812042236</t>
+    <t xml:space="preserve">25.5261516571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1237831115723</t>
   </si>
   <si>
     <t xml:space="preserve">26.1871681213379</t>
@@ -929,22 +929,22 @@
     <t xml:space="preserve">26.6308631896973</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4859848022461</t>
+    <t xml:space="preserve">26.4859828948975</t>
   </si>
   <si>
     <t xml:space="preserve">26.3229942321777</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6761379241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8934593200684</t>
+    <t xml:space="preserve">26.676139831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.893461227417</t>
   </si>
   <si>
     <t xml:space="preserve">26.2596073150635</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6670837402344</t>
+    <t xml:space="preserve">26.667085647583</t>
   </si>
   <si>
     <t xml:space="preserve">26.9115695953369</t>
@@ -953,55 +953,55 @@
     <t xml:space="preserve">26.6036987304688</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5946445465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3088302612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.326940536499</t>
+    <t xml:space="preserve">26.5946483612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3088283538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3269386291504</t>
   </si>
   <si>
     <t xml:space="preserve">25.8340225219727</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8984413146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0641040802002</t>
+    <t xml:space="preserve">25.8984432220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0641059875488</t>
   </si>
   <si>
     <t xml:space="preserve">24.7112045288086</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6159934997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2202453613281</t>
+    <t xml:space="preserve">23.6159954071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2202472686768</t>
   </si>
   <si>
     <t xml:space="preserve">23.1282119750977</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9625492095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8705196380615</t>
+    <t xml:space="preserve">22.962553024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8705177307129</t>
   </si>
   <si>
     <t xml:space="preserve">22.8613147735596</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2662658691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2386531829834</t>
+    <t xml:space="preserve">23.266263961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.238655090332</t>
   </si>
   <si>
     <t xml:space="preserve">23.0453834533691</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8889255523682</t>
+    <t xml:space="preserve">22.8889236450195</t>
   </si>
   <si>
     <t xml:space="preserve">22.0882263183594</t>
@@ -1010,16 +1010,16 @@
     <t xml:space="preserve">22.3183116912842</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2262744903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3827342987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.364330291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7416687011719</t>
+    <t xml:space="preserve">22.2262763977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3827362060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3643264770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7416667938232</t>
   </si>
   <si>
     <t xml:space="preserve">22.9533500671387</t>
@@ -1028,16 +1028,16 @@
     <t xml:space="preserve">22.8797206878662</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2846717834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4871463775635</t>
+    <t xml:space="preserve">23.2846736907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4871482849121</t>
   </si>
   <si>
     <t xml:space="preserve">23.4319248199463</t>
   </si>
   <si>
-    <t xml:space="preserve">22.806095123291</t>
+    <t xml:space="preserve">22.8060932159424</t>
   </si>
   <si>
     <t xml:space="preserve">23.0269756317139</t>
@@ -1046,13 +1046,13 @@
     <t xml:space="preserve">22.6036167144775</t>
   </si>
   <si>
-    <t xml:space="preserve">22.253885269165</t>
+    <t xml:space="preserve">22.2538871765137</t>
   </si>
   <si>
     <t xml:space="preserve">21.545223236084</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4900016784668</t>
+    <t xml:space="preserve">21.4900035858154</t>
   </si>
   <si>
     <t xml:space="preserve">21.7200889587402</t>
@@ -1061,28 +1061,28 @@
     <t xml:space="preserve">21.5544261932373</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6740703582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6280555725098</t>
+    <t xml:space="preserve">21.674072265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6280536651611</t>
   </si>
   <si>
     <t xml:space="preserve">21.1678829193115</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2046966552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1218681335449</t>
+    <t xml:space="preserve">21.2046985626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1218662261963</t>
   </si>
   <si>
     <t xml:space="preserve">21.4163761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5084114074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9133605957031</t>
+    <t xml:space="preserve">21.5084095001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9133625030518</t>
   </si>
   <si>
     <t xml:space="preserve">21.8857517242432</t>
@@ -1091,10 +1091,10 @@
     <t xml:space="preserve">21.9685821533203</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6220264434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3735294342041</t>
+    <t xml:space="preserve">22.6220245361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3735313415527</t>
   </si>
   <si>
     <t xml:space="preserve">22.2170734405518</t>
@@ -1106,22 +1106,22 @@
     <t xml:space="preserve">22.5299911499023</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6312294006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6404304504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5576019287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4255809783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6556663513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.263090133667</t>
+    <t xml:space="preserve">22.6312274932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6404323577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5576000213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4255790710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6556644439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2630920410156</t>
   </si>
   <si>
     <t xml:space="preserve">22.5391941070557</t>
@@ -1142,16 +1142,16 @@
     <t xml:space="preserve">22.115837097168</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7661037445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0606136322021</t>
+    <t xml:space="preserve">21.7661056518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0606155395508</t>
   </si>
   <si>
     <t xml:space="preserve">21.7569007873535</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9961891174316</t>
+    <t xml:space="preserve">21.9961929321289</t>
   </si>
   <si>
     <t xml:space="preserve">21.701681137085</t>
@@ -1163,7 +1163,7 @@
     <t xml:space="preserve">21.8765468597412</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1250400543213</t>
+    <t xml:space="preserve">22.1250381469727</t>
   </si>
   <si>
     <t xml:space="preserve">21.7753105163574</t>
@@ -1175,19 +1175,19 @@
     <t xml:space="preserve">21.9041576385498</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6832733154297</t>
+    <t xml:space="preserve">21.6832714080811</t>
   </si>
   <si>
     <t xml:space="preserve">20.827356338501</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0574417114258</t>
+    <t xml:space="preserve">21.0574398040771</t>
   </si>
   <si>
     <t xml:space="preserve">20.94700050354</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7997455596924</t>
+    <t xml:space="preserve">20.799747467041</t>
   </si>
   <si>
     <t xml:space="preserve">21.103458404541</t>
@@ -1196,13 +1196,13 @@
     <t xml:space="preserve">21.0758476257324</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3243427276611</t>
+    <t xml:space="preserve">21.3243408203125</t>
   </si>
   <si>
     <t xml:space="preserve">21.9501762390137</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0974311828613</t>
+    <t xml:space="preserve">22.0974292755127</t>
   </si>
   <si>
     <t xml:space="preserve">21.8581409454346</t>
@@ -1223,19 +1223,19 @@
     <t xml:space="preserve">21.1402702331543</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0666484832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7077121734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0942554473877</t>
+    <t xml:space="preserve">21.0666465759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7077102661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0942573547363</t>
   </si>
   <si>
     <t xml:space="preserve">21.1586799621582</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0206260681152</t>
+    <t xml:space="preserve">21.0206279754639</t>
   </si>
   <si>
     <t xml:space="preserve">21.0022220611572</t>
@@ -1262,37 +1262,37 @@
     <t xml:space="preserve">20.0634727478027</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4868278503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7445259094238</t>
+    <t xml:space="preserve">20.4868297576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7445278167725</t>
   </si>
   <si>
     <t xml:space="preserve">20.8917808532715</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2415103912354</t>
+    <t xml:space="preserve">21.241512298584</t>
   </si>
   <si>
     <t xml:space="preserve">20.9285926818848</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2475395202637</t>
+    <t xml:space="preserve">20.2475433349609</t>
   </si>
   <si>
     <t xml:space="preserve">20.1647090911865</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0910835266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2719764709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6953353881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8057746887207</t>
+    <t xml:space="preserve">20.0910816192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2719783782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.695333480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8057765960693</t>
   </si>
   <si>
     <t xml:space="preserve">19.7321491241455</t>
@@ -1301,31 +1301,31 @@
     <t xml:space="preserve">20.1831169128418</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0450630187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2935562133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4316082000732</t>
+    <t xml:space="preserve">20.0450649261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2935581207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4316101074219</t>
   </si>
   <si>
     <t xml:space="preserve">20.5696601867676</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6616954803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1310691833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0482387542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1954956054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4531898498535</t>
+    <t xml:space="preserve">20.661693572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.131067276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0482406616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1954936981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4531879425049</t>
   </si>
   <si>
     <t xml:space="preserve">20.8089466094971</t>
@@ -1337,31 +1337,31 @@
     <t xml:space="preserve">20.7721366882324</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4652481079102</t>
+    <t xml:space="preserve">19.4652462005615</t>
   </si>
   <si>
     <t xml:space="preserve">19.7965717315674</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8609962463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0174541473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2199287414551</t>
+    <t xml:space="preserve">19.8609981536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0174522399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2199268341064</t>
   </si>
   <si>
     <t xml:space="preserve">20.229133605957</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5236434936523</t>
+    <t xml:space="preserve">20.5236415863037</t>
   </si>
   <si>
     <t xml:space="preserve">20.6524925231934</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9101867675781</t>
+    <t xml:space="preserve">20.9101886749268</t>
   </si>
   <si>
     <t xml:space="preserve">20.2659473419189</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">21.259916305542</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3703575134277</t>
+    <t xml:space="preserve">21.3703556060791</t>
   </si>
   <si>
     <t xml:space="preserve">21.5176105499268</t>
@@ -1394,7 +1394,7 @@
     <t xml:space="preserve">20.5052356719971</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3487796783447</t>
+    <t xml:space="preserve">20.3487777709961</t>
   </si>
   <si>
     <t xml:space="preserve">20.0266590118408</t>
@@ -1412,10 +1412,10 @@
     <t xml:space="preserve">20.7169151306152</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9377975463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8365592956543</t>
+    <t xml:space="preserve">20.9377956390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8365573883057</t>
   </si>
   <si>
     <t xml:space="preserve">21.6004428863525</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">20.6248817443848</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2751502990723</t>
+    <t xml:space="preserve">20.2751522064209</t>
   </si>
   <si>
     <t xml:space="preserve">20.109489440918</t>
@@ -1433,25 +1433,25 @@
     <t xml:space="preserve">19.6493186950684</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9990482330322</t>
+    <t xml:space="preserve">19.9990463256836</t>
   </si>
   <si>
     <t xml:space="preserve">20.1278953552246</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3303737640381</t>
+    <t xml:space="preserve">20.3303699493408</t>
   </si>
   <si>
     <t xml:space="preserve">20.8733730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3763885498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5328464508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3027591705322</t>
+    <t xml:space="preserve">20.3763866424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5328483581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3027610778809</t>
   </si>
   <si>
     <t xml:space="preserve">20.6432876586914</t>
@@ -1463,13 +1463,13 @@
     <t xml:space="preserve">20.7261180877686</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2783260345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3151397705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.536018371582</t>
+    <t xml:space="preserve">21.2783241271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3151378631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5360202789307</t>
   </si>
   <si>
     <t xml:space="preserve">21.7937164306641</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">22.4195499420166</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2078685760498</t>
+    <t xml:space="preserve">22.2078704833984</t>
   </si>
   <si>
     <t xml:space="preserve">22.5668048858643</t>
@@ -1493,28 +1493,28 @@
     <t xml:space="preserve">22.6128215789795</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9165325164795</t>
+    <t xml:space="preserve">22.9165344238281</t>
   </si>
   <si>
     <t xml:space="preserve">22.6864471435547</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7324638366699</t>
+    <t xml:space="preserve">22.7324657440186</t>
   </si>
   <si>
     <t xml:space="preserve">22.8337020874023</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7692794799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9073295593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2754688262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9913024902344</t>
+    <t xml:space="preserve">22.7692775726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9073333740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2754669189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.991304397583</t>
   </si>
   <si>
     <t xml:space="preserve">23.3090705871582</t>
@@ -1523,13 +1523,13 @@
     <t xml:space="preserve">23.4118747711182</t>
   </si>
   <si>
-    <t xml:space="preserve">22.907190322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9819583892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7296123504639</t>
+    <t xml:space="preserve">22.9071884155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9819564819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7296142578125</t>
   </si>
   <si>
     <t xml:space="preserve">22.355770111084</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">22.7389583587646</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1595344543457</t>
+    <t xml:space="preserve">23.1595325469971</t>
   </si>
   <si>
     <t xml:space="preserve">23.5053367614746</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">23.3931846618652</t>
   </si>
   <si>
-    <t xml:space="preserve">23.262336730957</t>
+    <t xml:space="preserve">23.2623405456543</t>
   </si>
   <si>
     <t xml:space="preserve">22.9258823394775</t>
@@ -1583,22 +1583,22 @@
     <t xml:space="preserve">20.3370227813721</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9912166595459</t>
+    <t xml:space="preserve">19.9912185668945</t>
   </si>
   <si>
     <t xml:space="preserve">19.7388763427734</t>
   </si>
   <si>
-    <t xml:space="preserve">19.56130027771</t>
+    <t xml:space="preserve">19.5612983703613</t>
   </si>
   <si>
     <t xml:space="preserve">19.3089561462402</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5332622528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4958782196045</t>
+    <t xml:space="preserve">19.533260345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4958763122559</t>
   </si>
   <si>
     <t xml:space="preserve">19.3463401794434</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">19.0285758972168</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6266937255859</t>
+    <t xml:space="preserve">18.6266956329346</t>
   </si>
   <si>
     <t xml:space="preserve">18.383695602417</t>
@@ -1616,13 +1616,13 @@
     <t xml:space="preserve">18.0752754211426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6220188140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0799503326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6033306121826</t>
+    <t xml:space="preserve">18.6220207214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.079948425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.603328704834</t>
   </si>
   <si>
     <t xml:space="preserve">18.6360397338867</t>
@@ -1649,22 +1649,22 @@
     <t xml:space="preserve">18.495849609375</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4350986480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3883686065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4911727905273</t>
+    <t xml:space="preserve">18.4351005554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.388370513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.491174697876</t>
   </si>
   <si>
     <t xml:space="preserve">18.2435073852539</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8042392730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7715263366699</t>
+    <t xml:space="preserve">17.8042373657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7715282440186</t>
   </si>
   <si>
     <t xml:space="preserve">18.1079864501953</t>
@@ -1685,7 +1685,7 @@
     <t xml:space="preserve">18.2528514862061</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2107963562012</t>
+    <t xml:space="preserve">18.2107944488525</t>
   </si>
   <si>
     <t xml:space="preserve">18.3790245056152</t>
@@ -1694,19 +1694,19 @@
     <t xml:space="preserve">19.1407260894775</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4398002624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.402416229248</t>
+    <t xml:space="preserve">19.4397983551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4024181365967</t>
   </si>
   <si>
     <t xml:space="preserve">19.4117641448975</t>
   </si>
   <si>
-    <t xml:space="preserve">19.430456161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3650302886963</t>
+    <t xml:space="preserve">19.4304542541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3650341033936</t>
   </si>
   <si>
     <t xml:space="preserve">19.1594200134277</t>
@@ -1724,13 +1724,13 @@
     <t xml:space="preserve">18.7388458251953</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0566120147705</t>
+    <t xml:space="preserve">19.0566101074219</t>
   </si>
   <si>
     <t xml:space="preserve">18.8416519165039</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6080284118652</t>
+    <t xml:space="preserve">19.6080303192139</t>
   </si>
   <si>
     <t xml:space="preserve">19.2528800964355</t>
@@ -1739,7 +1739,7 @@
     <t xml:space="preserve">19.5239143371582</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4211082458496</t>
+    <t xml:space="preserve">19.4211101531982</t>
   </si>
   <si>
     <t xml:space="preserve">19.8136425018311</t>
@@ -1751,25 +1751,25 @@
     <t xml:space="preserve">19.7482204437256</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0192546844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7669124603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7856044769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5706443786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2809162139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1500701904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8977279663086</t>
+    <t xml:space="preserve">20.0192565917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7669105529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7856063842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5706462860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2809181213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1500720977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8977298736572</t>
   </si>
   <si>
     <t xml:space="preserve">18.8042697906494</t>
@@ -1778,10 +1778,10 @@
     <t xml:space="preserve">18.8790378570557</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1780853271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6453857421875</t>
+    <t xml:space="preserve">18.1780834197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6453876495361</t>
   </si>
   <si>
     <t xml:space="preserve">17.8556442260742</t>
@@ -1790,10 +1790,10 @@
     <t xml:space="preserve">17.2528228759766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1546897888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9817886352539</t>
+    <t xml:space="preserve">17.1546878814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9817867279053</t>
   </si>
   <si>
     <t xml:space="preserve">18.1360263824463</t>
@@ -1805,13 +1805,13 @@
     <t xml:space="preserve">18.1173343658447</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2154693603516</t>
+    <t xml:space="preserve">18.2154674530029</t>
   </si>
   <si>
     <t xml:space="preserve">19.1874580383301</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0098838806152</t>
+    <t xml:space="preserve">19.0098819732666</t>
   </si>
   <si>
     <t xml:space="preserve">19.5986843109131</t>
@@ -1823,7 +1823,7 @@
     <t xml:space="preserve">19.645414352417</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4771881103516</t>
+    <t xml:space="preserve">19.4771862030029</t>
   </si>
   <si>
     <t xml:space="preserve">19.5426082611084</t>
@@ -1832,13 +1832,13 @@
     <t xml:space="preserve">19.5799922943115</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0005645751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6267223358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4865303039551</t>
+    <t xml:space="preserve">20.0005626678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6267204284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4865322113037</t>
   </si>
   <si>
     <t xml:space="preserve">19.7014904022217</t>
@@ -1847,7 +1847,7 @@
     <t xml:space="preserve">19.3930702209473</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7481937408447</t>
+    <t xml:space="preserve">18.7481918334961</t>
   </si>
   <si>
     <t xml:space="preserve">18.7855777740479</t>
@@ -1859,34 +1859,34 @@
     <t xml:space="preserve">19.5145683288574</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2061500549316</t>
+    <t xml:space="preserve">19.206148147583</t>
   </si>
   <si>
     <t xml:space="preserve">17.0472106933594</t>
   </si>
   <si>
-    <t xml:space="preserve">16.710750579834</t>
+    <t xml:space="preserve">16.7107524871826</t>
   </si>
   <si>
     <t xml:space="preserve">16.8135585784912</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5845813751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5471954345703</t>
+    <t xml:space="preserve">16.5845794677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5471973419189</t>
   </si>
   <si>
     <t xml:space="preserve">16.5378494262695</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7200965881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4957942962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7528076171875</t>
+    <t xml:space="preserve">16.7200984954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4957904815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7528095245361</t>
   </si>
   <si>
     <t xml:space="preserve">16.500467300415</t>
@@ -1895,31 +1895,31 @@
     <t xml:space="preserve">16.4630813598633</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0425071716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3509311676025</t>
+    <t xml:space="preserve">16.0425090789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3509292602539</t>
   </si>
   <si>
     <t xml:space="preserve">16.5425224304199</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8415946960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6640205383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5331783294678</t>
+    <t xml:space="preserve">16.8415966033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6640224456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5331764221191</t>
   </si>
   <si>
     <t xml:space="preserve">16.5892524719238</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6827144622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5986003875732</t>
+    <t xml:space="preserve">16.6827125549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5985984802246</t>
   </si>
   <si>
     <t xml:space="preserve">16.4256973266602</t>
@@ -1931,7 +1931,7 @@
     <t xml:space="preserve">16.1593341827393</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4490642547607</t>
+    <t xml:space="preserve">16.4490623474121</t>
   </si>
   <si>
     <t xml:space="preserve">16.192045211792</t>
@@ -1940,19 +1940,19 @@
     <t xml:space="preserve">16.2154121398926</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4817733764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5238304138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4023303985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2995262145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.579906463623</t>
+    <t xml:space="preserve">16.4817752838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.523832321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4023323059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.299524307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5799083709717</t>
   </si>
   <si>
     <t xml:space="preserve">17.1874008178711</t>
@@ -1961,25 +1961,25 @@
     <t xml:space="preserve">17.7855491638184</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1967487335205</t>
+    <t xml:space="preserve">17.1967468261719</t>
   </si>
   <si>
     <t xml:space="preserve">17.2201118469238</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5752620697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5518989562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4163799285889</t>
+    <t xml:space="preserve">17.5752601623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5518970489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4163780212402</t>
   </si>
   <si>
     <t xml:space="preserve">17.1079597473145</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1313247680664</t>
+    <t xml:space="preserve">17.1313228607178</t>
   </si>
   <si>
     <t xml:space="preserve">17.2294578552246</t>
@@ -1988,22 +1988,22 @@
     <t xml:space="preserve">17.4911479949951</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4397430419922</t>
+    <t xml:space="preserve">17.4397449493408</t>
   </si>
   <si>
     <t xml:space="preserve">17.4537620544434</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7294731140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6547012329102</t>
+    <t xml:space="preserve">17.729471206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6547031402588</t>
   </si>
   <si>
     <t xml:space="preserve">17.3369369506836</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1453437805176</t>
+    <t xml:space="preserve">17.1453418731689</t>
   </si>
   <si>
     <t xml:space="preserve">16.8462696075439</t>
@@ -2015,22 +2015,22 @@
     <t xml:space="preserve">16.822904586792</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9911613464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9117221832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0378913879395</t>
+    <t xml:space="preserve">17.9911594390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9117202758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0378932952881</t>
   </si>
   <si>
     <t xml:space="preserve">17.6593761444092</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7948970794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6360111236572</t>
+    <t xml:space="preserve">17.7948951721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6360130310059</t>
   </si>
   <si>
     <t xml:space="preserve">17.3275928497314</t>
@@ -2042,7 +2042,7 @@
     <t xml:space="preserve">17.6266651153564</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5004920959473</t>
+    <t xml:space="preserve">17.5004959106445</t>
   </si>
   <si>
     <t xml:space="preserve">17.8696632385254</t>
@@ -2063,7 +2063,7 @@
     <t xml:space="preserve">17.9677963256836</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9070453643799</t>
+    <t xml:space="preserve">17.9070491790771</t>
   </si>
   <si>
     <t xml:space="preserve">18.6921157836914</t>
@@ -2075,13 +2075,13 @@
     <t xml:space="preserve">18.3416385650635</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5565967559814</t>
+    <t xml:space="preserve">18.5565986633301</t>
   </si>
   <si>
     <t xml:space="preserve">18.4397716522217</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5472545623779</t>
+    <t xml:space="preserve">18.5472507476807</t>
   </si>
   <si>
     <t xml:space="preserve">18.3089275360107</t>
@@ -2090,19 +2090,19 @@
     <t xml:space="preserve">18.8603458404541</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3696765899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5893077850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0238704681396</t>
+    <t xml:space="preserve">18.3696784973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5893096923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0238723754883</t>
   </si>
   <si>
     <t xml:space="preserve">17.8603172302246</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0612602233887</t>
+    <t xml:space="preserve">18.06125831604</t>
   </si>
   <si>
     <t xml:space="preserve">17.5986270904541</t>
@@ -2117,145 +2117,145 @@
     <t xml:space="preserve">20.0472965240479</t>
   </si>
   <si>
+    <t xml:space="preserve">19.9071044921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4607124328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9735870361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4132251739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2042751312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4892063140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1187953948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2327690124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9525890350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4397163391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7131443023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7273902893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8318634033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3732299804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6534118652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1757850646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3657360076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2802562713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2137718200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9810810089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.905101776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0333194732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6601638793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6886558532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9355964660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0210742950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8026294708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7171497344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8121280670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7456436157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.926097869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.135046005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1920337677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4674644470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4864597320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2870101928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2775135040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8406200408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.821626663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8501167297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9545917510986</t>
+  </si>
+  <si>
     <t xml:space="preserve">19.9071025848389</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4607124328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9735889434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4132251739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2042751312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4892063140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1187973022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2327709197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9525890350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4397144317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7131423950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7273902893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8318634033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3732318878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6534099578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1757831573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3657360076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2802581787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2137718200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9810810089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.905101776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0333194732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6601638793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6886558532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9355964660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0210742950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8026294708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7171478271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8121280670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7456455230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.926097869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1350479125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1920318603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4674644470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4864597320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2870121002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2775135040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8406181335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.821626663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8501167297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.95458984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9071006774902</t>
-  </si>
-  <si>
     <t xml:space="preserve">19.8881092071533</t>
   </si>
   <si>
     <t xml:space="preserve">20.0305728912354</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8691120147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9640884399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0020809173584</t>
+    <t xml:space="preserve">19.8691139221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.96409034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0020790100098</t>
   </si>
   <si>
     <t xml:space="preserve">19.9450931549072</t>
@@ -2267,16 +2267,16 @@
     <t xml:space="preserve">18.0218181610107</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9315891265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5754241943359</t>
+    <t xml:space="preserve">17.9315872192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5754261016846</t>
   </si>
   <si>
     <t xml:space="preserve">17.2952442169189</t>
   </si>
   <si>
-    <t xml:space="preserve">17.276252746582</t>
+    <t xml:space="preserve">17.2762508392334</t>
   </si>
   <si>
     <t xml:space="preserve">17.2667541503906</t>
@@ -2291,13 +2291,13 @@
     <t xml:space="preserve">16.8963451385498</t>
   </si>
   <si>
-    <t xml:space="preserve">17.015064239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5971698760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2837448120117</t>
+    <t xml:space="preserve">17.0150661468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5971660614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2837467193604</t>
   </si>
   <si>
     <t xml:space="preserve">16.8108654022217</t>
@@ -2321,19 +2321,19 @@
     <t xml:space="preserve">16.9485816955566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7491302490234</t>
+    <t xml:space="preserve">16.7491321563721</t>
   </si>
   <si>
     <t xml:space="preserve">16.8441066741943</t>
   </si>
   <si>
-    <t xml:space="preserve">16.497444152832</t>
+    <t xml:space="preserve">16.4974422454834</t>
   </si>
   <si>
     <t xml:space="preserve">16.6683979034424</t>
   </si>
   <si>
-    <t xml:space="preserve">16.630407333374</t>
+    <t xml:space="preserve">16.6304092407227</t>
   </si>
   <si>
     <t xml:space="preserve">16.9248371124268</t>
@@ -2354,16 +2354,16 @@
     <t xml:space="preserve">17.5231895446777</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2857475280762</t>
+    <t xml:space="preserve">17.2857494354248</t>
   </si>
   <si>
     <t xml:space="preserve">17.2002696990967</t>
   </si>
   <si>
-    <t xml:space="preserve">16.696891784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7538776397705</t>
+    <t xml:space="preserve">16.6968936920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7538795471191</t>
   </si>
   <si>
     <t xml:space="preserve">16.2267570495605</t>
@@ -2375,25 +2375,25 @@
     <t xml:space="preserve">16.1365299224854</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3454780578613</t>
+    <t xml:space="preserve">16.34547996521</t>
   </si>
   <si>
     <t xml:space="preserve">16.1840190887451</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1032905578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0178089141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4811916351318</t>
+    <t xml:space="preserve">16.1032886505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0178108215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4811906814575</t>
   </si>
   <si>
     <t xml:space="preserve">15.538179397583</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5619211196899</t>
+    <t xml:space="preserve">15.5619230270386</t>
   </si>
   <si>
     <t xml:space="preserve">15.1725187301636</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">15.3577222824097</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5904169082642</t>
+    <t xml:space="preserve">15.5904159545898</t>
   </si>
   <si>
     <t xml:space="preserve">15.4716949462891</t>
@@ -2414,7 +2414,7 @@
     <t xml:space="preserve">15.680643081665</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4052104949951</t>
+    <t xml:space="preserve">15.4052095413208</t>
   </si>
   <si>
     <t xml:space="preserve">15.324481010437</t>
@@ -2432,37 +2432,37 @@
     <t xml:space="preserve">15.0680437088013</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0348024368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.319730758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9608240127563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7661228179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8800926208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9085865020752</t>
+    <t xml:space="preserve">15.0348014831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3197317123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.960823059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7661218643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8800916671753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9085874557495</t>
   </si>
   <si>
     <t xml:space="preserve">15.922833442688</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1412811279297</t>
+    <t xml:space="preserve">16.1412792205811</t>
   </si>
   <si>
     <t xml:space="preserve">16.1745204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4024639129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5781726837158</t>
+    <t xml:space="preserve">16.4024658203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5781707763672</t>
   </si>
   <si>
     <t xml:space="preserve">16.5734233856201</t>
@@ -2474,10 +2474,10 @@
     <t xml:space="preserve">17.2809982299805</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9723281860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4404544830322</t>
+    <t xml:space="preserve">16.9723262786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4404563903809</t>
   </si>
   <si>
     <t xml:space="preserve">16.3074893951416</t>
@@ -2489,7 +2489,7 @@
     <t xml:space="preserve">16.3977165222168</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6209125518799</t>
+    <t xml:space="preserve">16.6209106445312</t>
   </si>
   <si>
     <t xml:space="preserve">17.3047428131104</t>
@@ -2498,16 +2498,16 @@
     <t xml:space="preserve">17.1290378570557</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1860237121582</t>
+    <t xml:space="preserve">17.1860218048096</t>
   </si>
   <si>
     <t xml:space="preserve">16.6873950958252</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9695816040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1120433807373</t>
+    <t xml:space="preserve">17.9695796966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1120452880859</t>
   </si>
   <si>
     <t xml:space="preserve">17.4282131195068</t>
@@ -2528,10 +2528,10 @@
     <t xml:space="preserve">17.62766456604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5421848297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4804515838623</t>
+    <t xml:space="preserve">17.5421829223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4804496765137</t>
   </si>
   <si>
     <t xml:space="preserve">17.8033714294434</t>
@@ -2546,7 +2546,7 @@
     <t xml:space="preserve">17.8081207275391</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0028209686279</t>
+    <t xml:space="preserve">18.0028228759766</t>
   </si>
   <si>
     <t xml:space="preserve">17.6704025268555</t>
@@ -2555,19 +2555,19 @@
     <t xml:space="preserve">17.6229152679443</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6799011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9885768890381</t>
+    <t xml:space="preserve">17.6799030303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9885749816895</t>
   </si>
   <si>
     <t xml:space="preserve">18.4207191467285</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0930500030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9030952453613</t>
+    <t xml:space="preserve">18.0930480957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.90309715271</t>
   </si>
   <si>
     <t xml:space="preserve">17.8508586883545</t>
@@ -2588,82 +2588,82 @@
     <t xml:space="preserve">16.6161632537842</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5924167633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8610982894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2694988250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2979907989502</t>
+    <t xml:space="preserve">16.5924186706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8611001968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2694969177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2979927062988</t>
   </si>
   <si>
     <t xml:space="preserve">16.1175346374512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8468523025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3217334747314</t>
+    <t xml:space="preserve">15.8468503952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3217353820801</t>
   </si>
   <si>
     <t xml:space="preserve">16.0842933654785</t>
   </si>
   <si>
-    <t xml:space="preserve">15.780366897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7186336517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3434762954712</t>
+    <t xml:space="preserve">15.7803688049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7186326980591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3434772491455</t>
   </si>
   <si>
     <t xml:space="preserve">15.9845676422119</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7471265792847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6046619415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7043876647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8848447799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5429258346558</t>
+    <t xml:space="preserve">15.747127532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.604660987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7043857574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8848428726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5429267883301</t>
   </si>
   <si>
     <t xml:space="preserve">15.1582717895508</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8096027374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8665885925293</t>
+    <t xml:space="preserve">13.8096036911011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8665895462036</t>
   </si>
   <si>
     <t xml:space="preserve">14.1420221328735</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6054029464722</t>
+    <t xml:space="preserve">13.6054039001465</t>
   </si>
   <si>
     <t xml:space="preserve">13.5721616744995</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0735349655151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0497903823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9738082885742</t>
+    <t xml:space="preserve">13.0735340118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0497894287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9738092422485</t>
   </si>
   <si>
     <t xml:space="preserve">12.3184700012207</t>
@@ -2672,10 +2672,10 @@
     <t xml:space="preserve">12.0477876663208</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2784767150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.656379699707</t>
+    <t xml:space="preserve">11.2784757614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6563787460327</t>
   </si>
   <si>
     <t xml:space="preserve">10.7845964431763</t>
@@ -2702,7 +2702,7 @@
     <t xml:space="preserve">11.8625812530518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1665086746216</t>
+    <t xml:space="preserve">12.1665077209473</t>
   </si>
   <si>
     <t xml:space="preserve">13.0877799987793</t>
@@ -2711,7 +2711,7 @@
     <t xml:space="preserve">13.3964548110962</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9690589904785</t>
+    <t xml:space="preserve">12.9690599441528</t>
   </si>
   <si>
     <t xml:space="preserve">12.2519865036011</t>
@@ -2723,16 +2723,16 @@
     <t xml:space="preserve">11.4921731948853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2072429656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1597557067871</t>
+    <t xml:space="preserve">11.2072439193726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1597547531128</t>
   </si>
   <si>
     <t xml:space="preserve">11.1882476806641</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5681552886963</t>
+    <t xml:space="preserve">11.568154335022</t>
   </si>
   <si>
     <t xml:space="preserve">11.5586566925049</t>
@@ -2750,13 +2750,13 @@
     <t xml:space="preserve">11.2927227020264</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5396614074707</t>
+    <t xml:space="preserve">11.5396604537964</t>
   </si>
   <si>
     <t xml:space="preserve">10.8178396224976</t>
   </si>
   <si>
-    <t xml:space="preserve">10.399941444397</t>
+    <t xml:space="preserve">10.3999423980713</t>
   </si>
   <si>
     <t xml:space="preserve">10.4474306106567</t>
@@ -2765,16 +2765,16 @@
     <t xml:space="preserve">10.3809471130371</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7323598861694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9128160476685</t>
+    <t xml:space="preserve">10.7323608398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9128150939941</t>
   </si>
   <si>
     <t xml:space="preserve">10.7228622436523</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3049650192261</t>
+    <t xml:space="preserve">10.3049659729004</t>
   </si>
   <si>
     <t xml:space="preserve">10.3524532318115</t>
@@ -2783,13 +2783,13 @@
     <t xml:space="preserve">10.3144626617432</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3429555892944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4094400405884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2574777603149</t>
+    <t xml:space="preserve">10.3429565429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4094390869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2574768066406</t>
   </si>
   <si>
     <t xml:space="preserve">10.0295333862305</t>
@@ -2798,10 +2798,10 @@
     <t xml:space="preserve">9.9060640335083</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89656543731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64962577819824</t>
+    <t xml:space="preserve">9.89656639099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64962673187256</t>
   </si>
   <si>
     <t xml:space="preserve">9.78259372711182</t>
@@ -2810,7 +2810,7 @@
     <t xml:space="preserve">10.4949188232422</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3469619750977</t>
+    <t xml:space="preserve">12.346962928772</t>
   </si>
   <si>
     <t xml:space="preserve">11.9005727767944</t>
@@ -2840,16 +2840,16 @@
     <t xml:space="preserve">11.8815774917603</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7771034240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.062032699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1190185546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2899761199951</t>
+    <t xml:space="preserve">11.7771024703979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0620336532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1190195083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2899770736694</t>
   </si>
   <si>
     <t xml:space="preserve">12.3089723587036</t>
@@ -2858,22 +2858,22 @@
     <t xml:space="preserve">12.7078742980957</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5749063491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5844039916992</t>
+    <t xml:space="preserve">12.5749073028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5844049453735</t>
   </si>
   <si>
     <t xml:space="preserve">11.9955492019653</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8055963516235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5111694335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7296142578125</t>
+    <t xml:space="preserve">11.8055953979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5111684799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7296152114868</t>
   </si>
   <si>
     <t xml:space="preserve">11.4446849822998</t>
@@ -2882,10 +2882,10 @@
     <t xml:space="preserve">11.5206661224365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7581081390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5871496200562</t>
+    <t xml:space="preserve">11.7581071853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5871486663818</t>
   </si>
   <si>
     <t xml:space="preserve">11.4826755523682</t>
@@ -2897,13 +2897,13 @@
     <t xml:space="preserve">10.9887971878052</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1787509918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2262372970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2452344894409</t>
+    <t xml:space="preserve">11.1787519454956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2262382507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2452335357666</t>
   </si>
   <si>
     <t xml:space="preserve">11.1027679443359</t>
@@ -2912,13 +2912,13 @@
     <t xml:space="preserve">11.1312618255615</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0267877578735</t>
+    <t xml:space="preserve">11.0267868041992</t>
   </si>
   <si>
     <t xml:space="preserve">11.0837736129761</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8368339538574</t>
+    <t xml:space="preserve">10.8368349075317</t>
   </si>
   <si>
     <t xml:space="preserve">11.0552806854248</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">11.2167415618896</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5708990097046</t>
+    <t xml:space="preserve">10.5708999633789</t>
   </si>
   <si>
     <t xml:space="preserve">10.580397605896</t>
@@ -2948,10 +2948,10 @@
     <t xml:space="preserve">11.0932712554932</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9603033065796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.760853767395</t>
+    <t xml:space="preserve">10.9603052139282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7608528137207</t>
   </si>
   <si>
     <t xml:space="preserve">10.7798490524292</t>
@@ -2960,13 +2960,13 @@
     <t xml:space="preserve">10.6753740310669</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6156415939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4636793136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3971977233887</t>
+    <t xml:space="preserve">11.6156425476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.463680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3971967697144</t>
   </si>
   <si>
     <t xml:space="preserve">11.5016708374023</t>
@@ -2987,22 +2987,22 @@
     <t xml:space="preserve">12.565408706665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0810279846191</t>
+    <t xml:space="preserve">12.0810289382935</t>
   </si>
   <si>
     <t xml:space="preserve">11.6821269989014</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6061449050903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1095209121704</t>
+    <t xml:space="preserve">11.6061458587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1095218658447</t>
   </si>
   <si>
     <t xml:space="preserve">12.0145444869995</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9385623931885</t>
+    <t xml:space="preserve">11.9385633468628</t>
   </si>
   <si>
     <t xml:space="preserve">11.957558631897</t>
@@ -3011,7 +3011,7 @@
     <t xml:space="preserve">11.9860515594482</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1285181045532</t>
+    <t xml:space="preserve">12.1285171508789</t>
   </si>
   <si>
     <t xml:space="preserve">12.2804803848267</t>
@@ -3023,10 +3023,10 @@
     <t xml:space="preserve">12.6034002304077</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5464143753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2044982910156</t>
+    <t xml:space="preserve">12.5464134216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2044973373413</t>
   </si>
   <si>
     <t xml:space="preserve">12.4039497375488</t>
@@ -3041,7 +3041,7 @@
     <t xml:space="preserve">11.8910760879517</t>
   </si>
   <si>
-    <t xml:space="preserve">11.67262840271</t>
+    <t xml:space="preserve">11.6726293563843</t>
   </si>
   <si>
     <t xml:space="preserve">11.3117170333862</t>
@@ -3050,10 +3050,10 @@
     <t xml:space="preserve">10.6943693161011</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5139131546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7988443374634</t>
+    <t xml:space="preserve">10.5139141082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7988433837891</t>
   </si>
   <si>
     <t xml:space="preserve">11.0647783279419</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">13.7146253585815</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9235744476318</t>
+    <t xml:space="preserve">13.9235754013062</t>
   </si>
   <si>
     <t xml:space="preserve">13.9330730438232</t>
@@ -3092,28 +3092,28 @@
     <t xml:space="preserve">14.0470447540283</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6264019012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3129787445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1515197753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2464952468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4269504547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4649410247803</t>
+    <t xml:space="preserve">14.6264009475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3129796981812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1515188217163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2464962005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4269514083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4649419784546</t>
   </si>
   <si>
     <t xml:space="preserve">14.9113321304321</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4934349060059</t>
+    <t xml:space="preserve">14.4934358596802</t>
   </si>
   <si>
     <t xml:space="preserve">14.3509693145752</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">14.8828401565552</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8543462753296</t>
+    <t xml:space="preserve">14.8543472290039</t>
   </si>
   <si>
     <t xml:space="preserve">14.7593698501587</t>
@@ -3140,7 +3140,7 @@
     <t xml:space="preserve">14.3794631958008</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5694169998169</t>
+    <t xml:space="preserve">14.5694160461426</t>
   </si>
   <si>
     <t xml:space="preserve">14.6453981399536</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">14.6074066162109</t>
   </si>
   <si>
-    <t xml:space="preserve">15.110782623291</t>
+    <t xml:space="preserve">15.1107835769653</t>
   </si>
   <si>
     <t xml:space="preserve">15.0632944107056</t>
@@ -3158,10 +3158,10 @@
     <t xml:space="preserve">14.9493227005005</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7688684463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7118806838989</t>
+    <t xml:space="preserve">14.7688674926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7118816375732</t>
   </si>
   <si>
     <t xml:space="preserve">14.5884113311768</t>
@@ -3170,13 +3170,13 @@
     <t xml:space="preserve">14.5789136886597</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4079561233521</t>
+    <t xml:space="preserve">14.4079551696777</t>
   </si>
   <si>
     <t xml:space="preserve">14.5504207611084</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5314264297485</t>
+    <t xml:space="preserve">14.5314254760742</t>
   </si>
   <si>
     <t xml:space="preserve">13.9615650177002</t>
@@ -3200,10 +3200,10 @@
     <t xml:space="preserve">15.8041114807129</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6711454391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2627458572388</t>
+    <t xml:space="preserve">15.6711444854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2627449035645</t>
   </si>
   <si>
     <t xml:space="preserve">14.9588203430176</t>
@@ -3215,10 +3215,10 @@
     <t xml:space="preserve">14.721378326416</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6358995437622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4364490509033</t>
+    <t xml:space="preserve">14.6359004974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4364500045776</t>
   </si>
   <si>
     <t xml:space="preserve">14.7403745651245</t>
@@ -3227,79 +3227,79 @@
     <t xml:space="preserve">15.006308555603</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0822896957397</t>
+    <t xml:space="preserve">15.0822906494141</t>
   </si>
   <si>
     <t xml:space="preserve">14.9778165817261</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6928853988647</t>
+    <t xml:space="preserve">14.6928863525391</t>
   </si>
   <si>
     <t xml:space="preserve">14.7783651351929</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8258533477783</t>
+    <t xml:space="preserve">14.825852394104</t>
   </si>
   <si>
     <t xml:space="preserve">15.2057600021362</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1202802658081</t>
+    <t xml:space="preserve">15.1202812194824</t>
   </si>
   <si>
     <t xml:space="preserve">15.0917882919312</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1012849807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8448486328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9873123168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8705940246582</t>
+    <t xml:space="preserve">15.1012859344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8448476791382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9873132705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8705949783325</t>
   </si>
   <si>
     <t xml:space="preserve">16.0225601196289</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0320568084717</t>
+    <t xml:space="preserve">16.032054901123</t>
   </si>
   <si>
     <t xml:space="preserve">15.8231077194214</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9370794296265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7376298904419</t>
+    <t xml:space="preserve">15.9370803833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7376289367676</t>
   </si>
   <si>
     <t xml:space="preserve">15.4906892776489</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7091379165649</t>
+    <t xml:space="preserve">15.7091369628906</t>
   </si>
   <si>
     <t xml:space="preserve">15.3102350234985</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3672199249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3387269973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6996374130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6853914260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6189079284668</t>
+    <t xml:space="preserve">15.3672208786011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3387260437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6996393203735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6853904724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6189069747925</t>
   </si>
   <si>
     <t xml:space="preserve">15.428955078125</t>
@@ -3311,28 +3311,28 @@
     <t xml:space="preserve">16.739631652832</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8678493499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8726005554199</t>
+    <t xml:space="preserve">16.8678512573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8725986480713</t>
   </si>
   <si>
     <t xml:space="preserve">16.4784469604492</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0340595245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5136947631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4567070007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0388107299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2904968261719</t>
+    <t xml:space="preserve">17.0340576171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.513692855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4567031860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0388088226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2904987335205</t>
   </si>
   <si>
     <t xml:space="preserve">17.0815467834473</t>
@@ -3350,7 +3350,7 @@
     <t xml:space="preserve">17.4614543914795</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4187145233154</t>
+    <t xml:space="preserve">17.4187164306641</t>
   </si>
   <si>
     <t xml:space="preserve">18.2117691040039</t>
@@ -3359,13 +3359,13 @@
     <t xml:space="preserve">18.3589839935303</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1975231170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1500358581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2307643890381</t>
+    <t xml:space="preserve">18.1975250244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1500377655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2307662963867</t>
   </si>
   <si>
     <t xml:space="preserve">18.0360641479492</t>
@@ -3374,19 +3374,19 @@
     <t xml:space="preserve">17.9125938415527</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9553356170654</t>
+    <t xml:space="preserve">17.9553337097168</t>
   </si>
   <si>
     <t xml:space="preserve">17.6846504211426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0408115386963</t>
+    <t xml:space="preserve">18.0408134460449</t>
   </si>
   <si>
     <t xml:space="preserve">18.3304901123047</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3209953308105</t>
+    <t xml:space="preserve">18.3209934234619</t>
   </si>
   <si>
     <t xml:space="preserve">18.368480682373</t>
@@ -3395,10 +3395,10 @@
     <t xml:space="preserve">18.3019981384277</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3542366027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3969764709473</t>
+    <t xml:space="preserve">18.3542346954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3969745635986</t>
   </si>
   <si>
     <t xml:space="preserve">18.5299415588379</t>
@@ -3413,7 +3413,7 @@
     <t xml:space="preserve">18.1832790374756</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4444618225098</t>
+    <t xml:space="preserve">18.444465637207</t>
   </si>
   <si>
     <t xml:space="preserve">18.8956031799316</t>
@@ -3422,28 +3422,28 @@
     <t xml:space="preserve">18.6961498260498</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5584354400635</t>
+    <t xml:space="preserve">18.5584373474121</t>
   </si>
   <si>
     <t xml:space="preserve">18.3352394104004</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8461112976074</t>
+    <t xml:space="preserve">17.8461093902588</t>
   </si>
   <si>
     <t xml:space="preserve">17.1527805328369</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1812725067139</t>
+    <t xml:space="preserve">17.1812744140625</t>
   </si>
   <si>
     <t xml:space="preserve">17.0673007965088</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1575298309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6114139556885</t>
+    <t xml:space="preserve">17.1575317382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6114120483398</t>
   </si>
   <si>
     <t xml:space="preserve">16.5021896362305</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">16.7253875732422</t>
   </si>
   <si>
-    <t xml:space="preserve">16.877347946167</t>
+    <t xml:space="preserve">16.8773498535156</t>
   </si>
   <si>
     <t xml:space="preserve">16.4214611053467</t>
@@ -3461,10 +3461,10 @@
     <t xml:space="preserve">15.9798202514648</t>
   </si>
   <si>
-    <t xml:space="preserve">16.098539352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0083103179932</t>
+    <t xml:space="preserve">16.0985412597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0083122253418</t>
   </si>
   <si>
     <t xml:space="preserve">16.2505035400391</t>
@@ -3479,10 +3479,10 @@
     <t xml:space="preserve">16.0463027954102</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0368041992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9988145828247</t>
+    <t xml:space="preserve">16.0368061065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9988136291504</t>
   </si>
   <si>
     <t xml:space="preserve">16.2600021362305</t>
@@ -3494,13 +3494,13 @@
     <t xml:space="preserve">16.0510520935059</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1100425720215</t>
+    <t xml:space="preserve">17.1100406646729</t>
   </si>
   <si>
     <t xml:space="preserve">17.3949718475342</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4919509887695</t>
+    <t xml:space="preserve">18.4919528961182</t>
   </si>
   <si>
     <t xml:space="preserve">17.5896739959717</t>
@@ -3509,7 +3509,7 @@
     <t xml:space="preserve">17.6609058380127</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0008182525635</t>
+    <t xml:space="preserve">17.0008163452148</t>
   </si>
   <si>
     <t xml:space="preserve">16.6731491088867</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">15.7328805923462</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7423782348633</t>
+    <t xml:space="preserve">15.7423791885376</t>
   </si>
   <si>
     <t xml:space="preserve">16.1460285186768</t>
@@ -3530,7 +3530,7 @@
     <t xml:space="preserve">15.9275808334351</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9703216552734</t>
+    <t xml:space="preserve">15.9703235626221</t>
   </si>
   <si>
     <t xml:space="preserve">16.6541538238525</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">18.0123195648193</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8698558807373</t>
+    <t xml:space="preserve">17.8698539733887</t>
   </si>
   <si>
     <t xml:space="preserve">18.0693054199219</t>
@@ -3554,25 +3554,25 @@
     <t xml:space="preserve">16.8251113891602</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7206363677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9628295898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9438304901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8298587799072</t>
+    <t xml:space="preserve">16.7206382751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9628276824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9438323974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8298606872559</t>
   </si>
   <si>
     <t xml:space="preserve">16.9913196563721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8346118927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0435562133789</t>
+    <t xml:space="preserve">16.8346099853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0435581207275</t>
   </si>
   <si>
     <t xml:space="preserve">16.8013687133789</t>
@@ -3593,7 +3593,7 @@
     <t xml:space="preserve">17.4662036895752</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7178936004639</t>
+    <t xml:space="preserve">17.7178916931152</t>
   </si>
   <si>
     <t xml:space="preserve">17.7748775482178</t>
@@ -3608,13 +3608,13 @@
     <t xml:space="preserve">18.7009010314941</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7911281585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9715824127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.945837020874</t>
+    <t xml:space="preserve">18.7911262512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9715843200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9458351135254</t>
   </si>
   <si>
     <t xml:space="preserve">18.4302177429199</t>
@@ -3629,13 +3629,13 @@
     <t xml:space="preserve">19.0903053283691</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3752326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.92409324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1662864685059</t>
+    <t xml:space="preserve">19.3752346038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9240951538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1662845611572</t>
   </si>
   <si>
     <t xml:space="preserve">19.4037265777588</t>
@@ -3647,19 +3647,19 @@
     <t xml:space="preserve">19.6221733093262</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1377906799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6316719055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4579677581787</t>
+    <t xml:space="preserve">19.1377925872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6316699981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4579696655273</t>
   </si>
   <si>
     <t xml:space="preserve">20.6289253234863</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0373249053955</t>
+    <t xml:space="preserve">21.0373268127441</t>
   </si>
   <si>
     <t xml:space="preserve">21.4457244873047</t>
@@ -3674,22 +3674,22 @@
     <t xml:space="preserve">20.6384220123291</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1635398864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0970573425293</t>
+    <t xml:space="preserve">20.1635417938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0970554351807</t>
   </si>
   <si>
     <t xml:space="preserve">20.7903861999512</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7144031524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0278263092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0183296203613</t>
+    <t xml:space="preserve">20.7144050598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0278282165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0183277130127</t>
   </si>
   <si>
     <t xml:space="preserve">21.094310760498</t>
@@ -3710,10 +3710,10 @@
     <t xml:space="preserve">22.0820693969727</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5976886749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6261806488037</t>
+    <t xml:space="preserve">21.5976867675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6261825561523</t>
   </si>
   <si>
     <t xml:space="preserve">19.4797096252441</t>
@@ -3731,10 +3731,10 @@
     <t xml:space="preserve">18.7103977203369</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0550594329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4946975708008</t>
+    <t xml:space="preserve">18.055061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4946956634521</t>
   </si>
   <si>
     <t xml:space="preserve">18.2212677001953</t>
@@ -3743,19 +3743,19 @@
     <t xml:space="preserve">17.9743270874023</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5916786193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5394401550293</t>
+    <t xml:space="preserve">18.5916767120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5394420623779</t>
   </si>
   <si>
     <t xml:space="preserve">18.0977993011475</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0503082275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2830047607422</t>
+    <t xml:space="preserve">18.0503101348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2830009460449</t>
   </si>
   <si>
     <t xml:space="preserve">18.1927757263184</t>
@@ -3776,52 +3776,52 @@
     <t xml:space="preserve">18.8006248474121</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5964241027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7768821716309</t>
+    <t xml:space="preserve">18.5964260101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7768802642822</t>
   </si>
   <si>
     <t xml:space="preserve">17.9220924377441</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6581611633301</t>
+    <t xml:space="preserve">18.6581592559814</t>
   </si>
   <si>
     <t xml:space="preserve">18.4492111206055</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6324138641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7368850708008</t>
+    <t xml:space="preserve">17.6324157714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7368869781494</t>
   </si>
   <si>
     <t xml:space="preserve">17.12428855896</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1867647171021</t>
+    <t xml:space="preserve">15.1867637634277</t>
   </si>
   <si>
     <t xml:space="preserve">14.8306016921997</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5076818466187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9133348464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3529739379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4574480056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8733406066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5856657028198</t>
+    <t xml:space="preserve">14.5076808929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9133329391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3529748916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.457447052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8733415603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5856666564941</t>
   </si>
   <si>
     <t xml:space="preserve">15.81360912323</t>
@@ -3833,22 +3833,22 @@
     <t xml:space="preserve">15.2390012741089</t>
   </si>
   <si>
-    <t xml:space="preserve">15.253246307373</t>
+    <t xml:space="preserve">15.2532472610474</t>
   </si>
   <si>
     <t xml:space="preserve">15.5191831588745</t>
   </si>
   <si>
-    <t xml:space="preserve">15.82785987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7681255340576</t>
+    <t xml:space="preserve">15.8278579711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7681274414062</t>
   </si>
   <si>
     <t xml:space="preserve">16.316987991333</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9750719070435</t>
+    <t xml:space="preserve">15.9750709533691</t>
   </si>
   <si>
     <t xml:space="preserve">15.0253038406372</t>
@@ -3857,13 +3857,13 @@
     <t xml:space="preserve">15.6331539154053</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6521492004395</t>
+    <t xml:space="preserve">15.6521482467651</t>
   </si>
   <si>
     <t xml:space="preserve">15.8895902633667</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5096855163574</t>
+    <t xml:space="preserve">15.5096845626831</t>
   </si>
   <si>
     <t xml:space="preserve">14.7308769226074</t>
@@ -3875,7 +3875,7 @@
     <t xml:space="preserve">15.1392755508423</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7851190567017</t>
+    <t xml:space="preserve">15.7851181030273</t>
   </si>
   <si>
     <t xml:space="preserve">14.3034820556641</t>
@@ -3884,7 +3884,7 @@
     <t xml:space="preserve">14.3224773406982</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8285980224609</t>
+    <t xml:space="preserve">13.8285989761353</t>
   </si>
   <si>
     <t xml:space="preserve">12.8123483657837</t>
@@ -3893,10 +3893,10 @@
     <t xml:space="preserve">14.1040306091309</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1990070343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0158071517944</t>
+    <t xml:space="preserve">14.1990079879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0158061981201</t>
   </si>
   <si>
     <t xml:space="preserve">14.5219278335571</t>
@@ -6081,6 +6081,9 @@
   </si>
   <si>
     <t xml:space="preserve">7.78000020980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09000015258789</t>
   </si>
 </sst>
 </file>
@@ -72745,7 +72748,7 @@
     </row>
     <row r="2552">
       <c r="A2552" s="1" t="n">
-        <v>46038.6917824074</v>
+        <v>46038.3333333333</v>
       </c>
       <c r="B2552" t="n">
         <v>872161</v>
@@ -72766,6 +72769,32 @@
         <v>1842</v>
       </c>
       <c r="H2552" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2553">
+      <c r="A2553" s="1" t="n">
+        <v>46041.6912037037</v>
+      </c>
+      <c r="B2553" t="n">
+        <v>485238</v>
+      </c>
+      <c r="C2553" t="n">
+        <v>7.19000005722046</v>
+      </c>
+      <c r="D2553" t="n">
+        <v>7.03000020980835</v>
+      </c>
+      <c r="E2553" t="n">
+        <v>7.13500022888184</v>
+      </c>
+      <c r="F2553" t="n">
+        <v>7.09000015258789</v>
+      </c>
+      <c r="G2553" t="s">
+        <v>2023</v>
+      </c>
+      <c r="H2553" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2029" uniqueCount="2029">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2030" uniqueCount="2030">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,43 +38,43 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2763519287109</t>
+    <t xml:space="preserve">18.2763481140137</t>
   </si>
   <si>
     <t xml:space="preserve">SFER.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">18.01096534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4978809356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9401969909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6836528778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2498111724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4086723327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1344394683838</t>
+    <t xml:space="preserve">18.0109634399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4978828430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9401950836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6836547851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2498149871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.408670425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1344375610352</t>
   </si>
   <si>
     <t xml:space="preserve">18.8425102233887</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4621238708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2851982116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0994262695312</t>
+    <t xml:space="preserve">18.462121963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2851963043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0994243621826</t>
   </si>
   <si>
     <t xml:space="preserve">17.6394214630127</t>
@@ -83,19 +83,19 @@
     <t xml:space="preserve">17.5686531066895</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1878890991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4798164367676</t>
+    <t xml:space="preserve">18.1878910064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4798145294189</t>
   </si>
   <si>
     <t xml:space="preserve">18.223274230957</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7632675170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3913536071777</t>
+    <t xml:space="preserve">17.7632694244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3913555145264</t>
   </si>
   <si>
     <t xml:space="preserve">18.6744346618652</t>
@@ -104,37 +104,37 @@
     <t xml:space="preserve">17.9578838348389</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2055816650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.258659362793</t>
+    <t xml:space="preserve">18.2055835723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2586574554443</t>
   </si>
   <si>
     <t xml:space="preserve">18.0817356109619</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3563404083252</t>
+    <t xml:space="preserve">17.3563423156738</t>
   </si>
   <si>
     <t xml:space="preserve">16.9051818847656</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1617221832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6486396789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0201835632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.48903465271</t>
+    <t xml:space="preserve">17.1617259979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6486415863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0201854705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4890365600586</t>
   </si>
   <si>
     <t xml:space="preserve">17.6305751800537</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4090423583984</t>
+    <t xml:space="preserve">18.4090461730957</t>
   </si>
   <si>
     <t xml:space="preserve">18.4532794952393</t>
@@ -143,97 +143,97 @@
     <t xml:space="preserve">18.9752063751221</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1348094940186</t>
+    <t xml:space="preserve">18.1348133087158</t>
   </si>
   <si>
     <t xml:space="preserve">17.3121109008789</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9048080444336</t>
+    <t xml:space="preserve">17.9048099517822</t>
   </si>
   <si>
     <t xml:space="preserve">18.3471202850342</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0194396972656</t>
+    <t xml:space="preserve">19.0194358825684</t>
   </si>
   <si>
     <t xml:space="preserve">19.0017414093018</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8513565063477</t>
+    <t xml:space="preserve">18.8513584136963</t>
   </si>
   <si>
     <t xml:space="preserve">19.3113632202148</t>
   </si>
   <si>
-    <t xml:space="preserve">19.992525100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9482898712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7271347045898</t>
+    <t xml:space="preserve">19.9925212860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9482917785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7271366119385</t>
   </si>
   <si>
     <t xml:space="preserve">19.3379020690918</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6475200653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.983678817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1167469024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.444055557251</t>
+    <t xml:space="preserve">19.647518157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9836807250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1167449951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4440574645996</t>
   </si>
   <si>
     <t xml:space="preserve">20.0367546081543</t>
   </si>
   <si>
-    <t xml:space="preserve">20.178295135498</t>
+    <t xml:space="preserve">20.1782932281494</t>
   </si>
   <si>
     <t xml:space="preserve">19.4971351623535</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4705963134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9663619995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4794406890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9129085540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.868673324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4175205230713</t>
+    <t xml:space="preserve">19.4705944061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9663581848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4794445037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9129047393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8686752319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4175186157227</t>
   </si>
   <si>
     <t xml:space="preserve">18.8690490722656</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8336658477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5152034759521</t>
+    <t xml:space="preserve">18.833667755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5151996612549</t>
   </si>
   <si>
     <t xml:space="preserve">18.9309730529785</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8955898284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5240440368652</t>
+    <t xml:space="preserve">18.8955917358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5240459442139</t>
   </si>
   <si>
     <t xml:space="preserve">18.9486675262451</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">18.7982788085938</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8778991699219</t>
+    <t xml:space="preserve">18.8778972625732</t>
   </si>
   <si>
     <t xml:space="preserve">19.2936687469482</t>
@@ -251,37 +251,37 @@
     <t xml:space="preserve">18.8071269989014</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3205814361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3648147583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8251934051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0640392303467</t>
+    <t xml:space="preserve">18.3205795288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3648128509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8251914978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0640411376953</t>
   </si>
   <si>
     <t xml:space="preserve">18.3117389678955</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8782691955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0021171569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7190399169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.444803237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1440334320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5509586334229</t>
+    <t xml:space="preserve">17.878267288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0021190643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7190380096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4448051452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1440296173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5509567260742</t>
   </si>
   <si>
     <t xml:space="preserve">17.9844245910645</t>
@@ -290,40 +290,40 @@
     <t xml:space="preserve">17.4182662963867</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9313449859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7367305755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6482696533203</t>
+    <t xml:space="preserve">17.9313488006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7367286682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.648265838623</t>
   </si>
   <si>
     <t xml:space="preserve">17.593936920166</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8112564086914</t>
+    <t xml:space="preserve">17.81125831604</t>
   </si>
   <si>
     <t xml:space="preserve">17.7025966644287</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5305519104004</t>
+    <t xml:space="preserve">17.530553817749</t>
   </si>
   <si>
     <t xml:space="preserve">17.4128341674805</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3041763305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4762191772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4309463500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4852752685547</t>
+    <t xml:space="preserve">17.3041744232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4762210845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4309482574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4852771759033</t>
   </si>
   <si>
     <t xml:space="preserve">17.7478733062744</t>
@@ -335,22 +335,22 @@
     <t xml:space="preserve">17.1502418518066</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7155990600586</t>
+    <t xml:space="preserve">16.71559715271</t>
   </si>
   <si>
     <t xml:space="preserve">16.5435543060303</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0415782928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0778007507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8384227752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9380283355713</t>
+    <t xml:space="preserve">17.0415802001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0778026580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8384246826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9380302429199</t>
   </si>
   <si>
     <t xml:space="preserve">17.7297630310059</t>
@@ -365,37 +365,37 @@
     <t xml:space="preserve">16.8514251708984</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3896179199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6793785095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2628440856934</t>
+    <t xml:space="preserve">16.3896160125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6793804168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2628479003906</t>
   </si>
   <si>
     <t xml:space="preserve">16.5254402160645</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6069412231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8061466217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8242607116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0726890563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8734817504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3624515533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4439468383789</t>
+    <t xml:space="preserve">16.6069374084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8061485290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8242588043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0726909637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.873477935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3624534606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4439487457275</t>
   </si>
   <si>
     <t xml:space="preserve">16.69748878479</t>
@@ -404,10 +404,10 @@
     <t xml:space="preserve">17.095911026001</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1321277618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.086856842041</t>
+    <t xml:space="preserve">17.1321296691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0868549346924</t>
   </si>
   <si>
     <t xml:space="preserve">17.0325241088867</t>
@@ -416,13 +416,13 @@
     <t xml:space="preserve">17.3403968811035</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9018077850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1372413635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9289741516113</t>
+    <t xml:space="preserve">17.9018096923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1372394561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9289703369141</t>
   </si>
   <si>
     <t xml:space="preserve">18.7710914611816</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">18.6352672576904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0699062347412</t>
+    <t xml:space="preserve">19.0699100494385</t>
   </si>
   <si>
     <t xml:space="preserve">19.2147884368896</t>
@@ -440,13 +440,13 @@
     <t xml:space="preserve">18.6262111663818</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4994430541992</t>
+    <t xml:space="preserve">18.4994411468506</t>
   </si>
   <si>
     <t xml:space="preserve">18.2187366485596</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7167625427246</t>
+    <t xml:space="preserve">18.716760635376</t>
   </si>
   <si>
     <t xml:space="preserve">18.5809364318848</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">18.762035369873</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8073139190674</t>
+    <t xml:space="preserve">18.8073120117188</t>
   </si>
   <si>
     <t xml:space="preserve">18.94313621521</t>
@@ -464,34 +464,34 @@
     <t xml:space="preserve">19.0427436828613</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6624317169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4722728729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6171569824219</t>
+    <t xml:space="preserve">18.6624336242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4722766876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6171588897705</t>
   </si>
   <si>
     <t xml:space="preserve">18.7529811859131</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9703025817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6805400848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6081027984619</t>
+    <t xml:space="preserve">18.9703063964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6805419921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6081008911133</t>
   </si>
   <si>
     <t xml:space="preserve">18.653377532959</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5175514221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8706970214844</t>
+    <t xml:space="preserve">18.5175533294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.870698928833</t>
   </si>
   <si>
     <t xml:space="preserve">18.6986522674561</t>
@@ -506,67 +506,67 @@
     <t xml:space="preserve">19.6947059631348</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5588798522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4592723846436</t>
+    <t xml:space="preserve">19.5588779449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4592704772949</t>
   </si>
   <si>
     <t xml:space="preserve">19.314395904541</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8888111114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1332912445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1604595184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9391899108887</t>
+    <t xml:space="preserve">18.8888092041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1332931518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.160457611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9391937255859</t>
   </si>
   <si>
     <t xml:space="preserve">20.4553298950195</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3557243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3104476928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3919429779053</t>
+    <t xml:space="preserve">20.3557205200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3104496002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3919448852539</t>
   </si>
   <si>
     <t xml:space="preserve">20.4643840789795</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6907596588135</t>
+    <t xml:space="preserve">20.6907615661621</t>
   </si>
   <si>
     <t xml:space="preserve">20.8446979522705</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7994174957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4010009765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1021823883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5277709960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3647766113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5458812713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7541484832764</t>
+    <t xml:space="preserve">20.7994194030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4009990692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1021842956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5277690887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3647785186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5458793640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7541427612305</t>
   </si>
   <si>
     <t xml:space="preserve">20.4191074371338</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">20.3285598754883</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0387954711914</t>
+    <t xml:space="preserve">20.03879737854</t>
   </si>
   <si>
     <t xml:space="preserve">20.1474590301514</t>
@@ -596,19 +596,19 @@
     <t xml:space="preserve">20.5639896392822</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1836795806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5498237609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4140033721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5045528411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7218704223633</t>
+    <t xml:space="preserve">20.1836814880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.549825668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4140014648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5045509338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7218723297119</t>
   </si>
   <si>
     <t xml:space="preserve">19.7943134307861</t>
@@ -620,13 +620,13 @@
     <t xml:space="preserve">19.830530166626</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9120254516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7490348815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0919609069824</t>
+    <t xml:space="preserve">19.9120273590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7490367889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0919628143311</t>
   </si>
   <si>
     <t xml:space="preserve">18.3002281188965</t>
@@ -635,7 +635,7 @@
     <t xml:space="preserve">18.3273944854736</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2459011077881</t>
+    <t xml:space="preserve">18.2458992004395</t>
   </si>
   <si>
     <t xml:space="preserve">18.0104675292969</t>
@@ -644,10 +644,10 @@
     <t xml:space="preserve">17.7388191223145</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8565330505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8203163146973</t>
+    <t xml:space="preserve">17.8565349578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8203144073486</t>
   </si>
   <si>
     <t xml:space="preserve">17.6392135620117</t>
@@ -656,13 +656,13 @@
     <t xml:space="preserve">18.3455047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3907794952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1514015197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2872314453125</t>
+    <t xml:space="preserve">18.3907814025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1514053344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2872295379639</t>
   </si>
   <si>
     <t xml:space="preserve">19.3958911895752</t>
@@ -677,19 +677,19 @@
     <t xml:space="preserve">19.5860462188721</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2600631713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3738346099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3466701507568</t>
+    <t xml:space="preserve">19.2600650787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.373836517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3466682434082</t>
   </si>
   <si>
     <t xml:space="preserve">20.2380084991455</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1293449401855</t>
+    <t xml:space="preserve">20.1293506622314</t>
   </si>
   <si>
     <t xml:space="preserve">20.1565132141113</t>
@@ -698,43 +698,43 @@
     <t xml:space="preserve">20.8084754943848</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6183185577393</t>
+    <t xml:space="preserve">20.6183204650879</t>
   </si>
   <si>
     <t xml:space="preserve">21.4785480499268</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5328769683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0671253204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.058069229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2572784423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2935028076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3025588989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3206634521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2753944396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2391719818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8186950683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0722332000732</t>
+    <t xml:space="preserve">21.5328807830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0671272277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0580711364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2572803497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2935009002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3025550842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3206672668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2753925323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2391700744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8186931610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0722370147705</t>
   </si>
   <si>
     <t xml:space="preserve">22.891134262085</t>
@@ -743,55 +743,55 @@
     <t xml:space="preserve">23.1537303924561</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0993995666504</t>
+    <t xml:space="preserve">23.099401473999</t>
   </si>
   <si>
     <t xml:space="preserve">22.5923175811768</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3568878173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9092445373535</t>
+    <t xml:space="preserve">22.3568859100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9092426300049</t>
   </si>
   <si>
     <t xml:space="preserve">22.1757869720459</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1395645141602</t>
+    <t xml:space="preserve">22.1395683288574</t>
   </si>
   <si>
     <t xml:space="preserve">23.606481552124</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7513637542725</t>
+    <t xml:space="preserve">23.7513618469238</t>
   </si>
   <si>
     <t xml:space="preserve">24.1226196289062</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6427059173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6879768371582</t>
+    <t xml:space="preserve">23.6427040100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6879787445068</t>
   </si>
   <si>
     <t xml:space="preserve">23.5612087249756</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7423057556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7241992950439</t>
+    <t xml:space="preserve">23.7423076629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7241973876953</t>
   </si>
   <si>
     <t xml:space="preserve">23.6336479187012</t>
   </si>
   <si>
-    <t xml:space="preserve">23.823802947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6970329284668</t>
+    <t xml:space="preserve">23.8238048553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6970310211182</t>
   </si>
   <si>
     <t xml:space="preserve">24.0139598846436</t>
@@ -800,10 +800,10 @@
     <t xml:space="preserve">24.2856101989746</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0682888031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9777374267578</t>
+    <t xml:space="preserve">24.068286895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9777393341064</t>
   </si>
   <si>
     <t xml:space="preserve">24.2946643829346</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">24.6115913391113</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7655239105225</t>
+    <t xml:space="preserve">24.7655277252197</t>
   </si>
   <si>
     <t xml:space="preserve">25.1911144256592</t>
@@ -827,28 +827,28 @@
     <t xml:space="preserve">25.4265441894531</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6167030334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6710319519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6529216766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7615814208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5352077484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9556827545166</t>
+    <t xml:space="preserve">25.61669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.671028137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6529197692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7615795135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5352058410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.955680847168</t>
   </si>
   <si>
     <t xml:space="preserve">24.9013538360596</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0643463134766</t>
+    <t xml:space="preserve">25.0643405914307</t>
   </si>
   <si>
     <t xml:space="preserve">24.8017482757568</t>
@@ -857,40 +857,40 @@
     <t xml:space="preserve">24.6206474304199</t>
   </si>
   <si>
-    <t xml:space="preserve">24.937572479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3722152709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6257553100586</t>
+    <t xml:space="preserve">24.9375743865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3722133636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.62575340271</t>
   </si>
   <si>
     <t xml:space="preserve">25.2273330688477</t>
   </si>
   <si>
-    <t xml:space="preserve">25.173002243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1639499664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.399377822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7253589630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2907199859619</t>
+    <t xml:space="preserve">25.1730041503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.163948059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3993797302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7253608703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2907180786133</t>
   </si>
   <si>
     <t xml:space="preserve">25.1277294158936</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7434711456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5442581176758</t>
+    <t xml:space="preserve">25.7434692382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5442600250244</t>
   </si>
   <si>
     <t xml:space="preserve">25.4808731079102</t>
@@ -899,55 +899,55 @@
     <t xml:space="preserve">25.5080394744873</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2635555267334</t>
+    <t xml:space="preserve">25.2635517120361</t>
   </si>
   <si>
     <t xml:space="preserve">25.0824527740479</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7836380004883</t>
+    <t xml:space="preserve">24.783634185791</t>
   </si>
   <si>
     <t xml:space="preserve">24.4214363098145</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2674961090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5261497497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1237812042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1871662139893</t>
+    <t xml:space="preserve">24.2674980163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5261516571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1237831115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1871681213379</t>
   </si>
   <si>
     <t xml:space="preserve">26.6308650970459</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4859809875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3229961395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6761379241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8934593200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2596092224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6670837402344</t>
+    <t xml:space="preserve">26.4859828948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3229904174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.676139831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8934631347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2596073150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.667085647583</t>
   </si>
   <si>
     <t xml:space="preserve">26.9115695953369</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6036987304688</t>
+    <t xml:space="preserve">26.6036968231201</t>
   </si>
   <si>
     <t xml:space="preserve">26.5946445465088</t>
@@ -956,10 +956,10 @@
     <t xml:space="preserve">25.3088302612305</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3269367218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.834020614624</t>
+    <t xml:space="preserve">25.3269386291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8340225219727</t>
   </si>
   <si>
     <t xml:space="preserve">25.8984432220459</t>
@@ -968,25 +968,25 @@
     <t xml:space="preserve">26.0641059875488</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7112045288086</t>
+    <t xml:space="preserve">24.71120262146</t>
   </si>
   <si>
     <t xml:space="preserve">23.6159954071045</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2202453613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1282119750977</t>
+    <t xml:space="preserve">23.2202472686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.128210067749</t>
   </si>
   <si>
     <t xml:space="preserve">22.9625511169434</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8705196380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8613128662109</t>
+    <t xml:space="preserve">22.8705177307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8613147735596</t>
   </si>
   <si>
     <t xml:space="preserve">23.266263961792</t>
@@ -995,25 +995,25 @@
     <t xml:space="preserve">23.2386531829834</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0453834533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8889255523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0882244110107</t>
+    <t xml:space="preserve">23.0453815460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8889236450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0882263183594</t>
   </si>
   <si>
     <t xml:space="preserve">22.3183116912842</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2262763977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3827342987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.364330291748</t>
+    <t xml:space="preserve">22.2262744903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3827362060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3643283843994</t>
   </si>
   <si>
     <t xml:space="preserve">22.7416687011719</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">23.2846717834473</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4871482849121</t>
+    <t xml:space="preserve">23.4871463775635</t>
   </si>
   <si>
     <t xml:space="preserve">23.4319248199463</t>
@@ -1049,13 +1049,13 @@
     <t xml:space="preserve">21.545223236084</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4900035858154</t>
+    <t xml:space="preserve">21.4900016784668</t>
   </si>
   <si>
     <t xml:space="preserve">21.7200889587402</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5544261932373</t>
+    <t xml:space="preserve">21.5544281005859</t>
   </si>
   <si>
     <t xml:space="preserve">21.6740703582764</t>
@@ -1064,7 +1064,7 @@
     <t xml:space="preserve">21.6280536651611</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1678829193115</t>
+    <t xml:space="preserve">21.1678848266602</t>
   </si>
   <si>
     <t xml:space="preserve">21.2046966552734</t>
@@ -1076,13 +1076,13 @@
     <t xml:space="preserve">21.4163761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5084114074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9133586883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8857498168945</t>
+    <t xml:space="preserve">21.5084095001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9133605957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8857517242432</t>
   </si>
   <si>
     <t xml:space="preserve">21.9685821533203</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">22.5299892425537</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6312294006348</t>
+    <t xml:space="preserve">22.6312274932861</t>
   </si>
   <si>
     <t xml:space="preserve">22.6404323577881</t>
@@ -1112,16 +1112,16 @@
     <t xml:space="preserve">22.5576000213623</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4255809783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6556663513184</t>
+    <t xml:space="preserve">21.4255771636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6556644439697</t>
   </si>
   <si>
     <t xml:space="preserve">22.2630920410156</t>
   </si>
   <si>
-    <t xml:space="preserve">22.539192199707</t>
+    <t xml:space="preserve">22.5391941070557</t>
   </si>
   <si>
     <t xml:space="preserve">22.3551254272461</t>
@@ -1136,19 +1136,19 @@
     <t xml:space="preserve">22.3367176055908</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1158390045166</t>
+    <t xml:space="preserve">22.1158351898193</t>
   </si>
   <si>
     <t xml:space="preserve">21.7661037445068</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0606117248535</t>
+    <t xml:space="preserve">22.0606136322021</t>
   </si>
   <si>
     <t xml:space="preserve">21.7569007873535</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9961891174316</t>
+    <t xml:space="preserve">21.9961910247803</t>
   </si>
   <si>
     <t xml:space="preserve">21.701681137085</t>
@@ -1157,28 +1157,28 @@
     <t xml:space="preserve">22.0053939819336</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8765468597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1250381469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7753124237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0238018035889</t>
+    <t xml:space="preserve">21.8765487670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1250400543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7753086090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0238056182861</t>
   </si>
   <si>
     <t xml:space="preserve">21.9041576385498</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6832752227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.827356338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0574398040771</t>
+    <t xml:space="preserve">21.6832733154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8273544311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0574417114258</t>
   </si>
   <si>
     <t xml:space="preserve">20.94700050354</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">20.7997455596924</t>
   </si>
   <si>
-    <t xml:space="preserve">21.103458404541</t>
+    <t xml:space="preserve">21.1034603118896</t>
   </si>
   <si>
     <t xml:space="preserve">21.0758476257324</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">21.3243408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9501762390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0974311828613</t>
+    <t xml:space="preserve">21.950174331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0974273681641</t>
   </si>
   <si>
     <t xml:space="preserve">21.8581409454346</t>
@@ -1208,19 +1208,19 @@
     <t xml:space="preserve">21.6372566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2967319488525</t>
+    <t xml:space="preserve">21.2967300415039</t>
   </si>
   <si>
     <t xml:space="preserve">20.9746112823486</t>
   </si>
   <si>
-    <t xml:space="preserve">20.983814239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1402702331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0666465759277</t>
+    <t xml:space="preserve">20.9838161468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1402721405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0666427612305</t>
   </si>
   <si>
     <t xml:space="preserve">20.7077121734619</t>
@@ -1235,13 +1235,13 @@
     <t xml:space="preserve">21.0206279754639</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0022239685059</t>
+    <t xml:space="preserve">21.0022220611572</t>
   </si>
   <si>
     <t xml:space="preserve">20.6340827941895</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4500141143799</t>
+    <t xml:space="preserve">20.4500160217285</t>
   </si>
   <si>
     <t xml:space="preserve">20.3855895996094</t>
@@ -1250,40 +1250,40 @@
     <t xml:space="preserve">20.3947944641113</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0082511901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9714393615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0634727478027</t>
+    <t xml:space="preserve">20.0082492828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9714374542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0634708404541</t>
   </si>
   <si>
     <t xml:space="preserve">20.4868297576904</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7445278167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8917808532715</t>
+    <t xml:space="preserve">20.7445259094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8917827606201</t>
   </si>
   <si>
     <t xml:space="preserve">21.2415103912354</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9285926818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2475414276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1647109985352</t>
+    <t xml:space="preserve">20.9285945892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2475395202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1647071838379</t>
   </si>
   <si>
     <t xml:space="preserve">20.0910816192627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2719764709473</t>
+    <t xml:space="preserve">19.2719783782959</t>
   </si>
   <si>
     <t xml:space="preserve">19.695333480835</t>
@@ -1292,19 +1292,19 @@
     <t xml:space="preserve">19.8057746887207</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7321510314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1831169128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0450630187988</t>
+    <t xml:space="preserve">19.7321491241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1831188201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0450649261475</t>
   </si>
   <si>
     <t xml:space="preserve">20.2935581207275</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4316082000732</t>
+    <t xml:space="preserve">20.4316120147705</t>
   </si>
   <si>
     <t xml:space="preserve">20.5696601867676</t>
@@ -1319,10 +1319,10 @@
     <t xml:space="preserve">21.0482387542725</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1954956054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4531898498535</t>
+    <t xml:space="preserve">21.1954936981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4531879425049</t>
   </si>
   <si>
     <t xml:space="preserve">20.8089504241943</t>
@@ -1331,22 +1331,22 @@
     <t xml:space="preserve">20.6708965301514</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7721366882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4652481079102</t>
+    <t xml:space="preserve">20.7721347808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4652500152588</t>
   </si>
   <si>
     <t xml:space="preserve">19.7965717315674</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8609962463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0174522399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2199287414551</t>
+    <t xml:space="preserve">19.8609943389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0174541473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2199306488037</t>
   </si>
   <si>
     <t xml:space="preserve">20.229133605957</t>
@@ -1358,31 +1358,31 @@
     <t xml:space="preserve">20.6524925231934</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9101848602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2659473419189</t>
+    <t xml:space="preserve">20.9101867675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2659492492676</t>
   </si>
   <si>
     <t xml:space="preserve">20.4684219360352</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1555061340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1739120483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.259916305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3703575134277</t>
+    <t xml:space="preserve">20.1555042266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1739139556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2599182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3703556060791</t>
   </si>
   <si>
     <t xml:space="preserve">21.5176124572754</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8549671173096</t>
+    <t xml:space="preserve">20.8549652099609</t>
   </si>
   <si>
     <t xml:space="preserve">20.9193897247314</t>
@@ -1391,22 +1391,22 @@
     <t xml:space="preserve">20.5052375793457</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3487777709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0266590118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7229442596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9162178039551</t>
+    <t xml:space="preserve">20.3487796783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0266571044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7229461669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9162139892578</t>
   </si>
   <si>
     <t xml:space="preserve">20.5604572296143</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7169151306152</t>
+    <t xml:space="preserve">20.7169132232666</t>
   </si>
   <si>
     <t xml:space="preserve">20.9377975463867</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">21.6004428863525</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6248817443848</t>
+    <t xml:space="preserve">20.6248798370361</t>
   </si>
   <si>
     <t xml:space="preserve">20.2751502990723</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">19.6493186950684</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9990482330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1278953552246</t>
+    <t xml:space="preserve">19.9990463256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1278972625732</t>
   </si>
   <si>
     <t xml:space="preserve">20.3303718566895</t>
@@ -1448,34 +1448,34 @@
     <t xml:space="preserve">20.5328464508057</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3027591705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6432857513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6156787872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7261161804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2783279418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3151378631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5360202789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7937164306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6496334075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5483989715576</t>
+    <t xml:space="preserve">20.3027610778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.64328956604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6156749725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7261180877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2783260345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3151359558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5360164642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7937183380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.64963722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.548397064209</t>
   </si>
   <si>
     <t xml:space="preserve">22.4195499420166</t>
@@ -1490,34 +1490,34 @@
     <t xml:space="preserve">22.6128215789795</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9165325164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6864452362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7324657440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8337001800537</t>
+    <t xml:space="preserve">22.9165306091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6864471435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7324695587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.833703994751</t>
   </si>
   <si>
     <t xml:space="preserve">22.7692775726318</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9073314666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2754669189453</t>
+    <t xml:space="preserve">22.9073276519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2754688262939</t>
   </si>
   <si>
     <t xml:space="preserve">22.991304397583</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3090686798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4118747711182</t>
+    <t xml:space="preserve">23.3090705871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4118766784668</t>
   </si>
   <si>
     <t xml:space="preserve">22.9071884155273</t>
@@ -1529,16 +1529,16 @@
     <t xml:space="preserve">22.7296123504639</t>
   </si>
   <si>
-    <t xml:space="preserve">22.355770111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6174583435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.07541847229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3558006286621</t>
+    <t xml:space="preserve">22.3557720184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6174621582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0754165649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3557987213135</t>
   </si>
   <si>
     <t xml:space="preserve">23.1969165802002</t>
@@ -1547,10 +1547,10 @@
     <t xml:space="preserve">23.206262588501</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4586067199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6548442840576</t>
+    <t xml:space="preserve">23.4586048126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6548461914062</t>
   </si>
   <si>
     <t xml:space="preserve">22.7389602661133</t>
@@ -1562,7 +1562,7 @@
     <t xml:space="preserve">23.5053367614746</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3838367462158</t>
+    <t xml:space="preserve">23.3838386535645</t>
   </si>
   <si>
     <t xml:space="preserve">23.3931846618652</t>
@@ -1571,10 +1571,10 @@
     <t xml:space="preserve">23.2623386383057</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9258823394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9912452697754</t>
+    <t xml:space="preserve">22.9258804321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9912433624268</t>
   </si>
   <si>
     <t xml:space="preserve">20.3370227813721</t>
@@ -1583,25 +1583,25 @@
     <t xml:space="preserve">19.9912166595459</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7388744354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5613021850586</t>
+    <t xml:space="preserve">19.7388763427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5612983703613</t>
   </si>
   <si>
     <t xml:space="preserve">19.3089561462402</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5332622528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4958801269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.346342086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0285758972168</t>
+    <t xml:space="preserve">19.533260345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4958782196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3463401794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0285739898682</t>
   </si>
   <si>
     <t xml:space="preserve">18.6266937255859</t>
@@ -1613,31 +1613,31 @@
     <t xml:space="preserve">18.0752754211426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6220207214355</t>
+    <t xml:space="preserve">18.6220188140869</t>
   </si>
   <si>
     <t xml:space="preserve">18.0799503326416</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6033306121826</t>
+    <t xml:space="preserve">18.603328704834</t>
   </si>
   <si>
     <t xml:space="preserve">18.6360397338867</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7949237823486</t>
+    <t xml:space="preserve">18.794921875</t>
   </si>
   <si>
     <t xml:space="preserve">18.7762317657471</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7201538085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5752906799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3930435180664</t>
+    <t xml:space="preserve">18.7201557159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.575288772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3930416107178</t>
   </si>
   <si>
     <t xml:space="preserve">18.5285606384277</t>
@@ -1646,13 +1646,13 @@
     <t xml:space="preserve">18.495849609375</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4350986480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3883686065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.491174697876</t>
+    <t xml:space="preserve">18.4351005554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.388370513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4911766052246</t>
   </si>
   <si>
     <t xml:space="preserve">18.2435073852539</t>
@@ -1664,52 +1664,52 @@
     <t xml:space="preserve">17.7715282440186</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1079845428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6734218597412</t>
+    <t xml:space="preserve">18.1079883575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6734256744385</t>
   </si>
   <si>
     <t xml:space="preserve">18.7575378417969</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7295017242432</t>
+    <t xml:space="preserve">18.7295036315918</t>
   </si>
   <si>
     <t xml:space="preserve">18.276216506958</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2528514862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2107963562012</t>
+    <t xml:space="preserve">18.2528533935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2107944488525</t>
   </si>
   <si>
     <t xml:space="preserve">18.3790245056152</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1407260894775</t>
+    <t xml:space="preserve">19.1407241821289</t>
   </si>
   <si>
     <t xml:space="preserve">19.4398002624512</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4024181365967</t>
+    <t xml:space="preserve">19.402416229248</t>
   </si>
   <si>
     <t xml:space="preserve">19.4117622375488</t>
   </si>
   <si>
-    <t xml:space="preserve">19.430456161499</t>
+    <t xml:space="preserve">19.4304542541504</t>
   </si>
   <si>
     <t xml:space="preserve">19.3650321960449</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1594181060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1687660217285</t>
+    <t xml:space="preserve">19.1594200134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1687641143799</t>
   </si>
   <si>
     <t xml:space="preserve">19.1126899719238</t>
@@ -1733,28 +1733,28 @@
     <t xml:space="preserve">19.2528820037842</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5239143371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4211082458496</t>
+    <t xml:space="preserve">19.5239162445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4211101531982</t>
   </si>
   <si>
     <t xml:space="preserve">19.8136444091797</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0753326416016</t>
+    <t xml:space="preserve">20.0753307342529</t>
   </si>
   <si>
     <t xml:space="preserve">19.7482204437256</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0192565917969</t>
+    <t xml:space="preserve">20.0192546844482</t>
   </si>
   <si>
     <t xml:space="preserve">19.7669124603271</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7856044769287</t>
+    <t xml:space="preserve">19.7856063842773</t>
   </si>
   <si>
     <t xml:space="preserve">19.5706443786621</t>
@@ -1763,25 +1763,25 @@
     <t xml:space="preserve">19.2809162139893</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1500720977783</t>
+    <t xml:space="preserve">19.150074005127</t>
   </si>
   <si>
     <t xml:space="preserve">18.8977298736572</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8042697906494</t>
+    <t xml:space="preserve">18.8042678833008</t>
   </si>
   <si>
     <t xml:space="preserve">18.8790378570557</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1780853271484</t>
+    <t xml:space="preserve">18.1780834197998</t>
   </si>
   <si>
     <t xml:space="preserve">18.6453876495361</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8556423187256</t>
+    <t xml:space="preserve">17.8556461334229</t>
   </si>
   <si>
     <t xml:space="preserve">17.2528228759766</t>
@@ -1790,7 +1790,7 @@
     <t xml:space="preserve">17.1546897888184</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9817886352539</t>
+    <t xml:space="preserve">16.9817867279053</t>
   </si>
   <si>
     <t xml:space="preserve">18.1360263824463</t>
@@ -1808,7 +1808,7 @@
     <t xml:space="preserve">19.1874580383301</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0098819732666</t>
+    <t xml:space="preserve">19.0098838806152</t>
   </si>
   <si>
     <t xml:space="preserve">19.5986843109131</t>
@@ -1820,37 +1820,37 @@
     <t xml:space="preserve">19.6454162597656</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4771842956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5426063537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5799922943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0005626678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6267242431641</t>
+    <t xml:space="preserve">19.4771862030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5426082611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5799942016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0005645751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6267223358154</t>
   </si>
   <si>
     <t xml:space="preserve">19.4865303039551</t>
   </si>
   <si>
-    <t xml:space="preserve">19.701488494873</t>
+    <t xml:space="preserve">19.7014923095703</t>
   </si>
   <si>
     <t xml:space="preserve">19.3930702209473</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7481937408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7855758666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0659561157227</t>
+    <t xml:space="preserve">18.7481918334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7855777740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0659580230713</t>
   </si>
   <si>
     <t xml:space="preserve">19.5145683288574</t>
@@ -1862,7 +1862,7 @@
     <t xml:space="preserve">17.0472106933594</t>
   </si>
   <si>
-    <t xml:space="preserve">16.710750579834</t>
+    <t xml:space="preserve">16.7107524871826</t>
   </si>
   <si>
     <t xml:space="preserve">16.8135585784912</t>
@@ -1871,22 +1871,22 @@
     <t xml:space="preserve">16.5845813751221</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5471973419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5378475189209</t>
+    <t xml:space="preserve">16.5471954345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5378513336182</t>
   </si>
   <si>
     <t xml:space="preserve">16.7200965881348</t>
   </si>
   <si>
-    <t xml:space="preserve">16.495792388916</t>
+    <t xml:space="preserve">16.4957904815674</t>
   </si>
   <si>
     <t xml:space="preserve">16.7528076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">16.500467300415</t>
+    <t xml:space="preserve">16.5004653930664</t>
   </si>
   <si>
     <t xml:space="preserve">16.4630832672119</t>
@@ -1898,16 +1898,16 @@
     <t xml:space="preserve">16.3509292602539</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5425224304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8415946960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6640224456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5331783294678</t>
+    <t xml:space="preserve">16.5425243377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8415966033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6640205383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5331764221191</t>
   </si>
   <si>
     <t xml:space="preserve">16.5892524719238</t>
@@ -1916,28 +1916,28 @@
     <t xml:space="preserve">16.6827144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5986003875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4256954193115</t>
+    <t xml:space="preserve">16.5986022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4256992340088</t>
   </si>
   <si>
     <t xml:space="preserve">16.1266212463379</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1593360900879</t>
+    <t xml:space="preserve">16.1593341827393</t>
   </si>
   <si>
     <t xml:space="preserve">16.4490623474121</t>
   </si>
   <si>
-    <t xml:space="preserve">16.192045211792</t>
+    <t xml:space="preserve">16.1920471191406</t>
   </si>
   <si>
     <t xml:space="preserve">16.2154102325439</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4817733764648</t>
+    <t xml:space="preserve">16.4817752838135</t>
   </si>
   <si>
     <t xml:space="preserve">16.5238304138184</t>
@@ -1946,10 +1946,10 @@
     <t xml:space="preserve">16.4023323059082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.299524307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5799083709717</t>
+    <t xml:space="preserve">16.2995262145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.579906463623</t>
   </si>
   <si>
     <t xml:space="preserve">17.1874008178711</t>
@@ -1964,22 +1964,22 @@
     <t xml:space="preserve">17.2201118469238</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5752620697021</t>
+    <t xml:space="preserve">17.5752639770508</t>
   </si>
   <si>
     <t xml:space="preserve">17.5518989562988</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4163780212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1079578399658</t>
+    <t xml:space="preserve">17.4163799285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1079616546631</t>
   </si>
   <si>
     <t xml:space="preserve">17.1313247680664</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2294578552246</t>
+    <t xml:space="preserve">17.2294597625732</t>
   </si>
   <si>
     <t xml:space="preserve">17.4911479949951</t>
@@ -1988,40 +1988,40 @@
     <t xml:space="preserve">17.4397430419922</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4537620544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7294731140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6547012329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3369369506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1453418731689</t>
+    <t xml:space="preserve">17.453763961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.729471206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6547050476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3369388580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1453437805176</t>
   </si>
   <si>
     <t xml:space="preserve">16.8462696075439</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1687088012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.822904586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9911632537842</t>
+    <t xml:space="preserve">17.1687107086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8229064941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9911613464355</t>
   </si>
   <si>
     <t xml:space="preserve">17.9117221832275</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0378913879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6593780517578</t>
+    <t xml:space="preserve">18.0378932952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6593761444092</t>
   </si>
   <si>
     <t xml:space="preserve">17.7948970794678</t>
@@ -2036,25 +2036,25 @@
     <t xml:space="preserve">17.3976879119873</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6266651153564</t>
+    <t xml:space="preserve">17.6266670227051</t>
   </si>
   <si>
     <t xml:space="preserve">17.5004940032959</t>
   </si>
   <si>
-    <t xml:space="preserve">17.869665145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3136005401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0565853118896</t>
+    <t xml:space="preserve">17.8696632385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3135986328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.056583404541</t>
   </si>
   <si>
     <t xml:space="preserve">18.2855625152588</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0191993713379</t>
+    <t xml:space="preserve">18.0192012786865</t>
   </si>
   <si>
     <t xml:space="preserve">17.9677982330322</t>
@@ -2072,31 +2072,31 @@
     <t xml:space="preserve">18.3416385650635</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5565967559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.439769744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5472507476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3089275360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8603458404541</t>
+    <t xml:space="preserve">18.5565986633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4397716522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5472526550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3089294433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8603439331055</t>
   </si>
   <si>
     <t xml:space="preserve">18.3696765899658</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5893077850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0238723754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8603191375732</t>
+    <t xml:space="preserve">18.5893096923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0238742828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8603172302246</t>
   </si>
   <si>
     <t xml:space="preserve">18.06125831604</t>
@@ -2126,10 +2126,10 @@
     <t xml:space="preserve">19.4132251739502</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2042770385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4892063140869</t>
+    <t xml:space="preserve">19.2042751312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4892082214355</t>
   </si>
   <si>
     <t xml:space="preserve">19.1187953948975</t>
@@ -2147,16 +2147,16 @@
     <t xml:space="preserve">17.7131423950195</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7273902893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8318634033203</t>
+    <t xml:space="preserve">17.7273921966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8318614959717</t>
   </si>
   <si>
     <t xml:space="preserve">18.3732299804688</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6534118652344</t>
+    <t xml:space="preserve">18.6534099578857</t>
   </si>
   <si>
     <t xml:space="preserve">19.1757831573486</t>
@@ -2168,13 +2168,13 @@
     <t xml:space="preserve">19.2802562713623</t>
   </si>
   <si>
-    <t xml:space="preserve">19.213773727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9810810089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.905101776123</t>
+    <t xml:space="preserve">19.2137756347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9810791015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9050998687744</t>
   </si>
   <si>
     <t xml:space="preserve">19.0333194732666</t>
@@ -2198,16 +2198,16 @@
     <t xml:space="preserve">19.7171497344971</t>
   </si>
   <si>
-    <t xml:space="preserve">19.812126159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7456436157227</t>
+    <t xml:space="preserve">19.8121280670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.745641708374</t>
   </si>
   <si>
     <t xml:space="preserve">19.926097869873</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1350498199463</t>
+    <t xml:space="preserve">20.1350479125977</t>
   </si>
   <si>
     <t xml:space="preserve">20.1920337677002</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">20.4674644470215</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4864597320557</t>
+    <t xml:space="preserve">20.4864616394043</t>
   </si>
   <si>
     <t xml:space="preserve">20.2870101928711</t>
@@ -2225,13 +2225,13 @@
     <t xml:space="preserve">20.2775115966797</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8406181335449</t>
+    <t xml:space="preserve">19.8406200408936</t>
   </si>
   <si>
     <t xml:space="preserve">19.8216247558594</t>
   </si>
   <si>
-    <t xml:space="preserve">19.850118637085</t>
+    <t xml:space="preserve">19.8501167297363</t>
   </si>
   <si>
     <t xml:space="preserve">19.9545917510986</t>
@@ -2240,7 +2240,7 @@
     <t xml:space="preserve">19.8881092071533</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0305728912354</t>
+    <t xml:space="preserve">20.030574798584</t>
   </si>
   <si>
     <t xml:space="preserve">19.8691120147705</t>
@@ -2261,16 +2261,16 @@
     <t xml:space="preserve">18.0218181610107</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9315891265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5754241943359</t>
+    <t xml:space="preserve">17.9315872192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5754261016846</t>
   </si>
   <si>
     <t xml:space="preserve">17.2952442169189</t>
   </si>
   <si>
-    <t xml:space="preserve">17.276252746582</t>
+    <t xml:space="preserve">17.2762508392334</t>
   </si>
   <si>
     <t xml:space="preserve">17.2667541503906</t>
@@ -2282,7 +2282,7 @@
     <t xml:space="preserve">17.0198135375977</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8963451385498</t>
+    <t xml:space="preserve">16.8963432312012</t>
   </si>
   <si>
     <t xml:space="preserve">17.0150661468506</t>
@@ -2291,25 +2291,25 @@
     <t xml:space="preserve">16.59716796875</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2837448120117</t>
+    <t xml:space="preserve">16.2837429046631</t>
   </si>
   <si>
     <t xml:space="preserve">16.8108654022217</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8536052703857</t>
+    <t xml:space="preserve">16.8536071777344</t>
   </si>
   <si>
     <t xml:space="preserve">17.0530548095703</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9153385162354</t>
+    <t xml:space="preserve">16.915340423584</t>
   </si>
   <si>
     <t xml:space="preserve">16.6636505126953</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7348861694336</t>
+    <t xml:space="preserve">16.734884262085</t>
   </si>
   <si>
     <t xml:space="preserve">16.948579788208</t>
@@ -2321,13 +2321,13 @@
     <t xml:space="preserve">16.8441066741943</t>
   </si>
   <si>
-    <t xml:space="preserve">16.497444152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6683979034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6304092407227</t>
+    <t xml:space="preserve">16.4974422454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.668399810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6304111480713</t>
   </si>
   <si>
     <t xml:space="preserve">16.9248371124268</t>
@@ -2351,7 +2351,7 @@
     <t xml:space="preserve">17.2857475280762</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2002716064453</t>
+    <t xml:space="preserve">17.2002696990967</t>
   </si>
   <si>
     <t xml:space="preserve">16.696891784668</t>
@@ -2360,7 +2360,7 @@
     <t xml:space="preserve">16.7538776397705</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2267551422119</t>
+    <t xml:space="preserve">16.2267570495605</t>
   </si>
   <si>
     <t xml:space="preserve">16.1887664794922</t>
@@ -2378,16 +2378,16 @@
     <t xml:space="preserve">16.1032905578613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0178108215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4811916351318</t>
+    <t xml:space="preserve">16.0178089141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4811906814575</t>
   </si>
   <si>
     <t xml:space="preserve">15.5381784439087</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5619220733643</t>
+    <t xml:space="preserve">15.5619230270386</t>
   </si>
   <si>
     <t xml:space="preserve">15.1725187301636</t>
@@ -2399,7 +2399,7 @@
     <t xml:space="preserve">15.3577222824097</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5904159545898</t>
+    <t xml:space="preserve">15.5904150009155</t>
   </si>
   <si>
     <t xml:space="preserve">15.4716949462891</t>
@@ -2408,7 +2408,7 @@
     <t xml:space="preserve">15.680643081665</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4052095413208</t>
+    <t xml:space="preserve">15.4052085876465</t>
   </si>
   <si>
     <t xml:space="preserve">15.324481010437</t>
@@ -2420,7 +2420,7 @@
     <t xml:space="preserve">15.2579975128174</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1772661209106</t>
+    <t xml:space="preserve">15.177267074585</t>
   </si>
   <si>
     <t xml:space="preserve">15.068042755127</t>
@@ -2435,13 +2435,13 @@
     <t xml:space="preserve">15.9608240127563</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7661228179932</t>
+    <t xml:space="preserve">15.7661218643188</t>
   </si>
   <si>
     <t xml:space="preserve">15.8800926208496</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9085865020752</t>
+    <t xml:space="preserve">15.9085874557495</t>
   </si>
   <si>
     <t xml:space="preserve">15.922833442688</t>
@@ -2456,10 +2456,10 @@
     <t xml:space="preserve">16.4024639129639</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5781707763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5734252929688</t>
+    <t xml:space="preserve">16.5781726837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5734233856201</t>
   </si>
   <si>
     <t xml:space="preserve">16.6066665649414</t>
@@ -2468,10 +2468,10 @@
     <t xml:space="preserve">17.2809982299805</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9723281860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4404544830322</t>
+    <t xml:space="preserve">16.9723262786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4404563903809</t>
   </si>
   <si>
     <t xml:space="preserve">16.3074893951416</t>
@@ -2483,40 +2483,40 @@
     <t xml:space="preserve">16.3977165222168</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6209125518799</t>
+    <t xml:space="preserve">16.6209106445312</t>
   </si>
   <si>
     <t xml:space="preserve">17.3047428131104</t>
   </si>
   <si>
-    <t xml:space="preserve">17.129035949707</t>
+    <t xml:space="preserve">17.1290378570557</t>
   </si>
   <si>
     <t xml:space="preserve">17.1860218048096</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6873950958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9695816040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1120433807373</t>
+    <t xml:space="preserve">16.6873970031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9695796966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1120452880859</t>
   </si>
   <si>
     <t xml:space="preserve">17.4282131195068</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3474807739258</t>
+    <t xml:space="preserve">17.3474826812744</t>
   </si>
   <si>
     <t xml:space="preserve">17.2477569580078</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3379859924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.409215927124</t>
+    <t xml:space="preserve">17.337984085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4092178344727</t>
   </si>
   <si>
     <t xml:space="preserve">17.62766456604</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">17.803373336792</t>
   </si>
   <si>
-    <t xml:space="preserve">18.116792678833</t>
+    <t xml:space="preserve">18.1167945861816</t>
   </si>
   <si>
     <t xml:space="preserve">17.8556079864502</t>
@@ -2540,16 +2540,16 @@
     <t xml:space="preserve">17.8081188201904</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0028209686279</t>
+    <t xml:space="preserve">18.0028228759766</t>
   </si>
   <si>
     <t xml:space="preserve">17.6704025268555</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6229152679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6799011230469</t>
+    <t xml:space="preserve">17.622917175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6799030303955</t>
   </si>
   <si>
     <t xml:space="preserve">17.9885749816895</t>
@@ -2561,16 +2561,16 @@
     <t xml:space="preserve">18.0930500030518</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9030952453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8508586883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2620048522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2287616729736</t>
+    <t xml:space="preserve">17.90309715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8508605957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2620029449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.228759765625</t>
   </si>
   <si>
     <t xml:space="preserve">17.0957946777344</t>
@@ -2582,7 +2582,7 @@
     <t xml:space="preserve">16.6161632537842</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5924167633057</t>
+    <t xml:space="preserve">16.5924186706543</t>
   </si>
   <si>
     <t xml:space="preserve">15.8611001968384</t>
@@ -2591,13 +2591,13 @@
     <t xml:space="preserve">16.2694988250732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2979907989502</t>
+    <t xml:space="preserve">16.2979888916016</t>
   </si>
   <si>
     <t xml:space="preserve">16.1175346374512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8468523025513</t>
+    <t xml:space="preserve">15.846851348877</t>
   </si>
   <si>
     <t xml:space="preserve">16.3217353820801</t>
@@ -2609,13 +2609,13 @@
     <t xml:space="preserve">15.7803688049316</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7186317443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3434772491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9845676422119</t>
+    <t xml:space="preserve">15.7186336517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3434762954712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9845685958862</t>
   </si>
   <si>
     <t xml:space="preserve">15.7471265792847</t>
@@ -2624,10 +2624,10 @@
     <t xml:space="preserve">15.6046619415283</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7043857574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8848428726196</t>
+    <t xml:space="preserve">15.7043867111206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8848419189453</t>
   </si>
   <si>
     <t xml:space="preserve">15.5429258346558</t>
@@ -2639,22 +2639,22 @@
     <t xml:space="preserve">13.8096027374268</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8665885925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1420221328735</t>
+    <t xml:space="preserve">13.8665895462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1420211791992</t>
   </si>
   <si>
     <t xml:space="preserve">13.6054029464722</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5721616744995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0735349655151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0497903823853</t>
+    <t xml:space="preserve">13.5721607208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0735340118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0497894287109</t>
   </si>
   <si>
     <t xml:space="preserve">12.9738092422485</t>
@@ -2675,7 +2675,7 @@
     <t xml:space="preserve">10.7845964431763</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08166599273682</t>
+    <t xml:space="preserve">9.08166694641113</t>
   </si>
   <si>
     <t xml:space="preserve">9.65437507629395</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">9.4976634979248</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6183881759644</t>
+    <t xml:space="preserve">10.6183891296387</t>
   </si>
   <si>
     <t xml:space="preserve">11.8625822067261</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">13.3964538574219</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9690599441528</t>
+    <t xml:space="preserve">12.9690589904785</t>
   </si>
   <si>
     <t xml:space="preserve">12.2519855499268</t>
@@ -2714,13 +2714,13 @@
     <t xml:space="preserve">11.9195680618286</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4921741485596</t>
+    <t xml:space="preserve">11.4921731948853</t>
   </si>
   <si>
     <t xml:space="preserve">11.2072429656982</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1597557067871</t>
+    <t xml:space="preserve">11.1597547531128</t>
   </si>
   <si>
     <t xml:space="preserve">11.1882476806641</t>
@@ -2732,7 +2732,7 @@
     <t xml:space="preserve">11.5586566925049</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6251411437988</t>
+    <t xml:space="preserve">11.6251401901245</t>
   </si>
   <si>
     <t xml:space="preserve">11.9765539169312</t>
@@ -2750,22 +2750,22 @@
     <t xml:space="preserve">10.8178396224976</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3999404907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4474306106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3809461593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7323598861694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9128160476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7228622436523</t>
+    <t xml:space="preserve">10.399941444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4474296569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3809471130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7323608398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9128150939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.722861289978</t>
   </si>
   <si>
     <t xml:space="preserve">10.3049659729004</t>
@@ -2777,19 +2777,19 @@
     <t xml:space="preserve">10.3144626617432</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3429555892944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4094400405884</t>
+    <t xml:space="preserve">10.3429565429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4094390869141</t>
   </si>
   <si>
     <t xml:space="preserve">10.2574768066406</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0295324325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90606307983398</t>
+    <t xml:space="preserve">10.0295333862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9060640335083</t>
   </si>
   <si>
     <t xml:space="preserve">9.89656543731689</t>
@@ -2798,10 +2798,10 @@
     <t xml:space="preserve">9.64962577819824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78259372711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4949178695679</t>
+    <t xml:space="preserve">9.78259468078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4949188232422</t>
   </si>
   <si>
     <t xml:space="preserve">12.346962928772</t>
@@ -2822,13 +2822,13 @@
     <t xml:space="preserve">13.6576404571533</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2872304916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1542644500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8218469619751</t>
+    <t xml:space="preserve">13.2872314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1542654037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8218460083008</t>
   </si>
   <si>
     <t xml:space="preserve">11.8815774917603</t>
@@ -2840,10 +2840,10 @@
     <t xml:space="preserve">12.062032699585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1190195083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2899761199951</t>
+    <t xml:space="preserve">12.1190185546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2899770736694</t>
   </si>
   <si>
     <t xml:space="preserve">12.3089714050293</t>
@@ -2855,16 +2855,16 @@
     <t xml:space="preserve">12.5749063491821</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5844049453735</t>
+    <t xml:space="preserve">12.5844039916992</t>
   </si>
   <si>
     <t xml:space="preserve">11.9955492019653</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8055963516235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5111694335938</t>
+    <t xml:space="preserve">11.8055973052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5111684799194</t>
   </si>
   <si>
     <t xml:space="preserve">11.7296152114868</t>
@@ -2876,7 +2876,7 @@
     <t xml:space="preserve">11.5206661224365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7581081390381</t>
+    <t xml:space="preserve">11.7581071853638</t>
   </si>
   <si>
     <t xml:space="preserve">11.5871496200562</t>
@@ -2894,7 +2894,7 @@
     <t xml:space="preserve">11.1787509918213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2262372970581</t>
+    <t xml:space="preserve">11.2262382507324</t>
   </si>
   <si>
     <t xml:space="preserve">11.2452335357666</t>
@@ -2906,7 +2906,7 @@
     <t xml:space="preserve">11.1312627792358</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0267877578735</t>
+    <t xml:space="preserve">11.0267868041992</t>
   </si>
   <si>
     <t xml:space="preserve">11.0837736129761</t>
@@ -2915,7 +2915,7 @@
     <t xml:space="preserve">10.8368349075317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0552806854248</t>
+    <t xml:space="preserve">11.0552816390991</t>
   </si>
   <si>
     <t xml:space="preserve">11.2167415618896</t>
@@ -2933,13 +2933,13 @@
     <t xml:space="preserve">10.3619508743286</t>
   </si>
   <si>
-    <t xml:space="preserve">11.644136428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3307132720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0932712554932</t>
+    <t xml:space="preserve">11.6441354751587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.330714225769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0932722091675</t>
   </si>
   <si>
     <t xml:space="preserve">10.9603033065796</t>
@@ -2948,7 +2948,7 @@
     <t xml:space="preserve">10.7608528137207</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7798500061035</t>
+    <t xml:space="preserve">10.7798490524292</t>
   </si>
   <si>
     <t xml:space="preserve">10.6753740310669</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">11.4636793136597</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3971977233887</t>
+    <t xml:space="preserve">11.3971967697144</t>
   </si>
   <si>
     <t xml:space="preserve">11.5016708374023</t>
@@ -2975,28 +2975,28 @@
     <t xml:space="preserve">11.4256896972656</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5179204940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.565408706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0810279846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6821269989014</t>
+    <t xml:space="preserve">12.5179214477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5654096603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0810289382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6821260452271</t>
   </si>
   <si>
     <t xml:space="preserve">11.6061458587646</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1095218658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0145435333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9385623931885</t>
+    <t xml:space="preserve">12.1095209121704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0145444869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9385633468628</t>
   </si>
   <si>
     <t xml:space="preserve">11.9575576782227</t>
@@ -3011,7 +3011,7 @@
     <t xml:space="preserve">12.2804794311523</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6793813705444</t>
+    <t xml:space="preserve">12.6793823242188</t>
   </si>
   <si>
     <t xml:space="preserve">12.6034002304077</t>
@@ -3023,7 +3023,7 @@
     <t xml:space="preserve">12.2044982910156</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4039487838745</t>
+    <t xml:space="preserve">12.4039497375488</t>
   </si>
   <si>
     <t xml:space="preserve">12.8978271484375</t>
@@ -3044,16 +3044,16 @@
     <t xml:space="preserve">10.6943693161011</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5139131546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7988443374634</t>
+    <t xml:space="preserve">10.5139141082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7988433837891</t>
   </si>
   <si>
     <t xml:space="preserve">11.0647783279419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3592052459717</t>
+    <t xml:space="preserve">11.359206199646</t>
   </si>
   <si>
     <t xml:space="preserve">12.3659582138062</t>
@@ -3065,10 +3065,10 @@
     <t xml:space="preserve">13.3537158966064</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7811107635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7146263122559</t>
+    <t xml:space="preserve">13.7811098098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7146272659302</t>
   </si>
   <si>
     <t xml:space="preserve">13.9235744476318</t>
@@ -3077,10 +3077,10 @@
     <t xml:space="preserve">13.9330730438232</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2369976043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3414726257324</t>
+    <t xml:space="preserve">14.2369985580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3414716720581</t>
   </si>
   <si>
     <t xml:space="preserve">14.0470447540283</t>
@@ -3098,31 +3098,31 @@
     <t xml:space="preserve">14.2464952468872</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4269504547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4649410247803</t>
+    <t xml:space="preserve">14.4269514083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4649419784546</t>
   </si>
   <si>
     <t xml:space="preserve">14.9113321304321</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4934358596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3509693145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5979080200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7498722076416</t>
+    <t xml:space="preserve">14.4934349060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3509702682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5979089736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7498712539673</t>
   </si>
   <si>
     <t xml:space="preserve">15.1487741470337</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8828401565552</t>
+    <t xml:space="preserve">14.8828392028809</t>
   </si>
   <si>
     <t xml:space="preserve">14.8543462753296</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">14.7593698501587</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3794641494751</t>
+    <t xml:space="preserve">14.3794631958008</t>
   </si>
   <si>
     <t xml:space="preserve">14.5694160461426</t>
@@ -3146,16 +3146,16 @@
     <t xml:space="preserve">15.1107835769653</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0632944107056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9493217468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7688684463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7118806838989</t>
+    <t xml:space="preserve">15.0632953643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9493227005005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7688674926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7118816375732</t>
   </si>
   <si>
     <t xml:space="preserve">14.5884113311768</t>
@@ -3170,10 +3170,10 @@
     <t xml:space="preserve">14.5504207611084</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5314264297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9615650177002</t>
+    <t xml:space="preserve">14.5314254760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9615659713745</t>
   </si>
   <si>
     <t xml:space="preserve">14.2085056304932</t>
@@ -3188,10 +3188,10 @@
     <t xml:space="preserve">14.6833877563477</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0537977218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8041133880615</t>
+    <t xml:space="preserve">15.0537967681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8041124343872</t>
   </si>
   <si>
     <t xml:space="preserve">15.6711454391479</t>
@@ -3221,7 +3221,7 @@
     <t xml:space="preserve">15.006308555603</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0822896957397</t>
+    <t xml:space="preserve">15.0822906494141</t>
   </si>
   <si>
     <t xml:space="preserve">14.9778165817261</t>
@@ -3230,7 +3230,7 @@
     <t xml:space="preserve">14.6928853988647</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7783651351929</t>
+    <t xml:space="preserve">14.7783641815186</t>
   </si>
   <si>
     <t xml:space="preserve">14.8258533477783</t>
@@ -3254,31 +3254,31 @@
     <t xml:space="preserve">14.9873132705688</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8705959320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0225601196289</t>
+    <t xml:space="preserve">15.8705968856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0225582122803</t>
   </si>
   <si>
     <t xml:space="preserve">16.0320568084717</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8231077194214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9370794296265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7376279830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4906892776489</t>
+    <t xml:space="preserve">15.8231067657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9370803833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7376289367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4906883239746</t>
   </si>
   <si>
     <t xml:space="preserve">15.7091360092163</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3102340698242</t>
+    <t xml:space="preserve">15.3102350234985</t>
   </si>
   <si>
     <t xml:space="preserve">15.3672199249268</t>
@@ -3287,10 +3287,10 @@
     <t xml:space="preserve">15.3387269973755</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6996374130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6853914260864</t>
+    <t xml:space="preserve">15.6996383666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6853923797607</t>
   </si>
   <si>
     <t xml:space="preserve">15.6189079284668</t>
@@ -3299,13 +3299,13 @@
     <t xml:space="preserve">15.428955078125</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6379022598267</t>
+    <t xml:space="preserve">15.637903213501</t>
   </si>
   <si>
     <t xml:space="preserve">16.7396335601807</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8678512573242</t>
+    <t xml:space="preserve">16.8678531646729</t>
   </si>
   <si>
     <t xml:space="preserve">16.8725986480713</t>
@@ -3329,7 +3329,7 @@
     <t xml:space="preserve">17.2904968261719</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0815486907959</t>
+    <t xml:space="preserve">17.0815505981445</t>
   </si>
   <si>
     <t xml:space="preserve">17.0245628356934</t>
@@ -3344,28 +3344,28 @@
     <t xml:space="preserve">17.4614543914795</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4187145233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2117710113525</t>
+    <t xml:space="preserve">17.4187164306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2117691040039</t>
   </si>
   <si>
     <t xml:space="preserve">18.3589839935303</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1975250244141</t>
+    <t xml:space="preserve">18.1975231170654</t>
   </si>
   <si>
     <t xml:space="preserve">18.1500358581543</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2307643890381</t>
+    <t xml:space="preserve">18.2307662963867</t>
   </si>
   <si>
     <t xml:space="preserve">18.0360641479492</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9125938415527</t>
+    <t xml:space="preserve">17.9125957489014</t>
   </si>
   <si>
     <t xml:space="preserve">17.9553356170654</t>
@@ -3377,10 +3377,10 @@
     <t xml:space="preserve">18.0408134460449</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3304901123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3209953308105</t>
+    <t xml:space="preserve">18.3304920196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3209934234619</t>
   </si>
   <si>
     <t xml:space="preserve">18.368480682373</t>
@@ -3389,7 +3389,7 @@
     <t xml:space="preserve">18.3019981384277</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3542346954346</t>
+    <t xml:space="preserve">18.3542366027832</t>
   </si>
   <si>
     <t xml:space="preserve">18.3969745635986</t>
@@ -3401,10 +3401,10 @@
     <t xml:space="preserve">18.297248840332</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1690311431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1832790374756</t>
+    <t xml:space="preserve">18.1690292358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.183277130127</t>
   </si>
   <si>
     <t xml:space="preserve">18.4444637298584</t>
@@ -3416,7 +3416,7 @@
     <t xml:space="preserve">18.6961498260498</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5584354400635</t>
+    <t xml:space="preserve">18.5584373474121</t>
   </si>
   <si>
     <t xml:space="preserve">18.3352394104004</t>
@@ -3428,7 +3428,7 @@
     <t xml:space="preserve">17.1527805328369</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1812725067139</t>
+    <t xml:space="preserve">17.1812744140625</t>
   </si>
   <si>
     <t xml:space="preserve">17.0673007965088</t>
@@ -3443,7 +3443,7 @@
     <t xml:space="preserve">16.5021915435791</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7253875732422</t>
+    <t xml:space="preserve">16.7253856658936</t>
   </si>
   <si>
     <t xml:space="preserve">16.877347946167</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">16.4214611053467</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9798202514648</t>
+    <t xml:space="preserve">15.9798212051392</t>
   </si>
   <si>
     <t xml:space="preserve">16.0985412597656</t>
@@ -3464,7 +3464,7 @@
     <t xml:space="preserve">16.2505035400391</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4736957550049</t>
+    <t xml:space="preserve">16.4736976623535</t>
   </si>
   <si>
     <t xml:space="preserve">16.169771194458</t>
@@ -3476,19 +3476,19 @@
     <t xml:space="preserve">16.0368061065674</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9988145828247</t>
+    <t xml:space="preserve">15.9988136291504</t>
   </si>
   <si>
     <t xml:space="preserve">16.2600021362305</t>
   </si>
   <si>
-    <t xml:space="preserve">16.065299987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0510520935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1100406646729</t>
+    <t xml:space="preserve">16.0652980804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0510501861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1100387573242</t>
   </si>
   <si>
     <t xml:space="preserve">17.3949718475342</t>
@@ -3503,7 +3503,7 @@
     <t xml:space="preserve">17.6609039306641</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0008182525635</t>
+    <t xml:space="preserve">17.0008163452148</t>
   </si>
   <si>
     <t xml:space="preserve">16.6731491088867</t>
@@ -3512,10 +3512,10 @@
     <t xml:space="preserve">16.5164375305176</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7328805923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7423782348633</t>
+    <t xml:space="preserve">15.7328815460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7423791885376</t>
   </si>
   <si>
     <t xml:space="preserve">16.1460285186768</t>
@@ -3524,13 +3524,13 @@
     <t xml:space="preserve">15.9275827407837</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9703216552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6541519165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7586288452148</t>
+    <t xml:space="preserve">15.9703226089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6541538238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7586269378662</t>
   </si>
   <si>
     <t xml:space="preserve">18.0123195648193</t>
@@ -3548,13 +3548,13 @@
     <t xml:space="preserve">16.8251113891602</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7206382751465</t>
+    <t xml:space="preserve">16.7206363677979</t>
   </si>
   <si>
     <t xml:space="preserve">16.9628295898438</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9438304901123</t>
+    <t xml:space="preserve">16.9438323974609</t>
   </si>
   <si>
     <t xml:space="preserve">16.8298587799072</t>
@@ -3563,7 +3563,7 @@
     <t xml:space="preserve">16.9913196563721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8346099853516</t>
+    <t xml:space="preserve">16.8346080780029</t>
   </si>
   <si>
     <t xml:space="preserve">17.0435581207275</t>
@@ -3575,19 +3575,19 @@
     <t xml:space="preserve">16.7111377716064</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2145175933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4424610137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3427333831787</t>
+    <t xml:space="preserve">17.2145156860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4424591064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3427352905273</t>
   </si>
   <si>
     <t xml:space="preserve">17.4662036895752</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7178936004639</t>
+    <t xml:space="preserve">17.7178916931152</t>
   </si>
   <si>
     <t xml:space="preserve">17.7748775482178</t>
@@ -3596,10 +3596,10 @@
     <t xml:space="preserve">17.6988964080811</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1405372619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7009010314941</t>
+    <t xml:space="preserve">18.1405391693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7008991241455</t>
   </si>
   <si>
     <t xml:space="preserve">18.7911281585693</t>
@@ -3614,10 +3614,10 @@
     <t xml:space="preserve">18.4302177429199</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5536861419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7626342773438</t>
+    <t xml:space="preserve">18.5536880493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7626323699951</t>
   </si>
   <si>
     <t xml:space="preserve">19.0903053283691</t>
@@ -3638,13 +3638,13 @@
     <t xml:space="preserve">20.5529441833496</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6221752166748</t>
+    <t xml:space="preserve">19.6221733093262</t>
   </si>
   <si>
     <t xml:space="preserve">19.1377925872803</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6316719055176</t>
+    <t xml:space="preserve">19.6316699981689</t>
   </si>
   <si>
     <t xml:space="preserve">20.4579677581787</t>
@@ -3653,40 +3653,40 @@
     <t xml:space="preserve">20.6289253234863</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0373229980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4457244873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9898357391357</t>
+    <t xml:space="preserve">21.0373249053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4457225799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9898376464844</t>
   </si>
   <si>
     <t xml:space="preserve">20.7523956298828</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6384220123291</t>
+    <t xml:space="preserve">20.6384239196777</t>
   </si>
   <si>
     <t xml:space="preserve">20.1635398864746</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0970573425293</t>
+    <t xml:space="preserve">20.0970554351807</t>
   </si>
   <si>
     <t xml:space="preserve">20.7903861999512</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7144031524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0278263092041</t>
+    <t xml:space="preserve">20.7144050598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0278282165527</t>
   </si>
   <si>
     <t xml:space="preserve">21.0183296203613</t>
   </si>
   <si>
-    <t xml:space="preserve">21.094310760498</t>
+    <t xml:space="preserve">21.0943088531494</t>
   </si>
   <si>
     <t xml:space="preserve">21.4172306060791</t>
@@ -3704,7 +3704,7 @@
     <t xml:space="preserve">22.0820693969727</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5976886749268</t>
+    <t xml:space="preserve">21.5976867675781</t>
   </si>
   <si>
     <t xml:space="preserve">21.6261806488037</t>
@@ -3713,10 +3713,10 @@
     <t xml:space="preserve">19.4797096252441</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0998001098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.536693572998</t>
+    <t xml:space="preserve">19.0998020172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5366954803467</t>
   </si>
   <si>
     <t xml:space="preserve">19.2517642974854</t>
@@ -3728,7 +3728,7 @@
     <t xml:space="preserve">18.0550594329834</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4946975708008</t>
+    <t xml:space="preserve">17.4946956634521</t>
   </si>
   <si>
     <t xml:space="preserve">18.2212677001953</t>
@@ -3758,13 +3758,13 @@
     <t xml:space="preserve">18.1452865600586</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5679321289062</t>
+    <t xml:space="preserve">18.5679340362549</t>
   </si>
   <si>
     <t xml:space="preserve">18.68190574646</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7721309661865</t>
+    <t xml:space="preserve">18.7721328735352</t>
   </si>
   <si>
     <t xml:space="preserve">18.8006267547607</t>
@@ -3806,10 +3806,10 @@
     <t xml:space="preserve">15.9133348464966</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3529748916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4574489593506</t>
+    <t xml:space="preserve">15.3529739379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4574480056763</t>
   </si>
   <si>
     <t xml:space="preserve">14.8733415603638</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">15.2532472610474</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5191822052002</t>
+    <t xml:space="preserve">15.5191812515259</t>
   </si>
   <si>
     <t xml:space="preserve">15.8278579711914</t>
@@ -3854,7 +3854,7 @@
     <t xml:space="preserve">15.6521492004395</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8895902633667</t>
+    <t xml:space="preserve">15.889591217041</t>
   </si>
   <si>
     <t xml:space="preserve">15.5096855163574</t>
@@ -3866,10 +3866,10 @@
     <t xml:space="preserve">14.8638439178467</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1392755508423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7851190567017</t>
+    <t xml:space="preserve">15.1392765045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7851181030273</t>
   </si>
   <si>
     <t xml:space="preserve">14.3034820556641</t>
@@ -3878,7 +3878,7 @@
     <t xml:space="preserve">14.3224773406982</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8285989761353</t>
+    <t xml:space="preserve">13.8285999298096</t>
   </si>
   <si>
     <t xml:space="preserve">12.8123483657837</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">14.1990070343018</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0158071517944</t>
+    <t xml:space="preserve">15.0158061981201</t>
   </si>
   <si>
     <t xml:space="preserve">14.5219278335571</t>
@@ -6099,6 +6099,9 @@
   </si>
   <si>
     <t xml:space="preserve">6.43499994277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6100001335144</t>
   </si>
 </sst>
 </file>
@@ -73101,7 +73104,7 @@
     </row>
     <row r="2565">
       <c r="A2565" s="1" t="n">
-        <v>46057.6911574074</v>
+        <v>46057.3333333333</v>
       </c>
       <c r="B2565" t="n">
         <v>245839</v>
@@ -73122,6 +73125,32 @@
         <v>1863</v>
       </c>
       <c r="H2565" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2566">
+      <c r="A2566" s="1" t="n">
+        <v>46058.6910648148</v>
+      </c>
+      <c r="B2566" t="n">
+        <v>228788</v>
+      </c>
+      <c r="C2566" t="n">
+        <v>6.64499998092651</v>
+      </c>
+      <c r="D2566" t="n">
+        <v>6.46500015258789</v>
+      </c>
+      <c r="E2566" t="n">
+        <v>6.48999977111816</v>
+      </c>
+      <c r="F2566" t="n">
+        <v>6.6100001335144</v>
+      </c>
+      <c r="G2566" t="s">
+        <v>2029</v>
+      </c>
+      <c r="H2566" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2763481140137</t>
+    <t xml:space="preserve">18.2763500213623</t>
   </si>
   <si>
     <t xml:space="preserve">SFER.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0109672546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4978809356689</t>
+    <t xml:space="preserve">18.0109634399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4978828430176</t>
   </si>
   <si>
     <t xml:space="preserve">17.9401950836182</t>
@@ -56,19 +56,19 @@
     <t xml:space="preserve">17.6836528778076</t>
   </si>
   <si>
-    <t xml:space="preserve">18.249813079834</t>
+    <t xml:space="preserve">18.2498111724854</t>
   </si>
   <si>
     <t xml:space="preserve">19.4086723327637</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1344356536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8425121307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4621238708496</t>
+    <t xml:space="preserve">19.1344375610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8425102233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.462121963501</t>
   </si>
   <si>
     <t xml:space="preserve">18.2852001190186</t>
@@ -77,10 +77,10 @@
     <t xml:space="preserve">18.0994262695312</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6394214630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5686550140381</t>
+    <t xml:space="preserve">17.6394233703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5686511993408</t>
   </si>
   <si>
     <t xml:space="preserve">18.1878890991211</t>
@@ -89,28 +89,28 @@
     <t xml:space="preserve">18.4798145294189</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2232761383057</t>
+    <t xml:space="preserve">18.223274230957</t>
   </si>
   <si>
     <t xml:space="preserve">17.7632694244385</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3913555145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6744346618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9578838348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2055854797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2586555480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0817337036133</t>
+    <t xml:space="preserve">18.3913536071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6744327545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9578857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2055816650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2586574554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0817356109619</t>
   </si>
   <si>
     <t xml:space="preserve">17.3563404083252</t>
@@ -119,28 +119,28 @@
     <t xml:space="preserve">16.9051837921143</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1617221832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6486415863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0201854705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4890384674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6305770874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4090423583984</t>
+    <t xml:space="preserve">17.1617240905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6486434936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0201835632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.48903465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6305751800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4090442657471</t>
   </si>
   <si>
     <t xml:space="preserve">18.453275680542</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9752044677734</t>
+    <t xml:space="preserve">18.9752063751221</t>
   </si>
   <si>
     <t xml:space="preserve">18.1348114013672</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">18.3471202850342</t>
   </si>
   <si>
-    <t xml:space="preserve">19.019437789917</t>
+    <t xml:space="preserve">19.0194358825684</t>
   </si>
   <si>
     <t xml:space="preserve">19.0017433166504</t>
@@ -164,13 +164,13 @@
     <t xml:space="preserve">18.8513584136963</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3113613128662</t>
+    <t xml:space="preserve">19.3113632202148</t>
   </si>
   <si>
     <t xml:space="preserve">19.9925231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9482936859131</t>
+    <t xml:space="preserve">19.9482917785645</t>
   </si>
   <si>
     <t xml:space="preserve">19.7271327972412</t>
@@ -179,10 +179,10 @@
     <t xml:space="preserve">19.3379020690918</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6475200653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9836769104004</t>
+    <t xml:space="preserve">19.647518157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.983678817749</t>
   </si>
   <si>
     <t xml:space="preserve">19.1167469024658</t>
@@ -194,28 +194,28 @@
     <t xml:space="preserve">20.0367546081543</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1782913208008</t>
+    <t xml:space="preserve">20.178295135498</t>
   </si>
   <si>
     <t xml:space="preserve">19.4971351623535</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4705963134766</t>
+    <t xml:space="preserve">19.4705944061279</t>
   </si>
   <si>
     <t xml:space="preserve">18.9663619995117</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4794425964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9129066467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8686771392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4175205230713</t>
+    <t xml:space="preserve">19.4794445037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9129085540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.868673324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4175186157227</t>
   </si>
   <si>
     <t xml:space="preserve">18.8690490722656</t>
@@ -224,13 +224,13 @@
     <t xml:space="preserve">18.8336658477783</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5151996612549</t>
+    <t xml:space="preserve">18.5152015686035</t>
   </si>
   <si>
     <t xml:space="preserve">18.9309730529785</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8955860137939</t>
+    <t xml:space="preserve">18.8955898284912</t>
   </si>
   <si>
     <t xml:space="preserve">18.5240478515625</t>
@@ -239,76 +239,76 @@
     <t xml:space="preserve">18.9486675262451</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7982807159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8778953552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2936687469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8071269989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3205814361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3648128509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8251953125</t>
+    <t xml:space="preserve">18.7982788085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8778972625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2936706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.80712890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3205833435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3648147583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8251895904541</t>
   </si>
   <si>
     <t xml:space="preserve">18.0640411376953</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3117370605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8782653808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0021171569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7190380096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.444803237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1440315246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5509567260742</t>
+    <t xml:space="preserve">18.3117351531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8782691955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0021190643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7190399169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4448013305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1440296173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5509586334229</t>
   </si>
   <si>
     <t xml:space="preserve">17.9844245910645</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4182682037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9313488006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7367305755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6482677459717</t>
+    <t xml:space="preserve">17.4182662963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9313449859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7367324829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6482696533203</t>
   </si>
   <si>
     <t xml:space="preserve">17.5939388275146</t>
   </si>
   <si>
-    <t xml:space="preserve">17.81125831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7025947570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5305500030518</t>
+    <t xml:space="preserve">17.8112564086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7025966644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5305519104004</t>
   </si>
   <si>
     <t xml:space="preserve">17.4128341674805</t>
@@ -320,28 +320,28 @@
     <t xml:space="preserve">17.4762210845947</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4309463500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4852771759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7478733062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6844844818115</t>
+    <t xml:space="preserve">17.430944442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4852752685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.747875213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6844882965088</t>
   </si>
   <si>
     <t xml:space="preserve">17.1502418518066</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7155990600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5435562133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0415782928467</t>
+    <t xml:space="preserve">16.71559715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5435543060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0415802001953</t>
   </si>
   <si>
     <t xml:space="preserve">17.0778007507324</t>
@@ -359,25 +359,25 @@
     <t xml:space="preserve">17.8655891418457</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1825141906738</t>
+    <t xml:space="preserve">18.1825160980225</t>
   </si>
   <si>
     <t xml:space="preserve">16.8514232635498</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3896198272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6793804168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.262845993042</t>
+    <t xml:space="preserve">16.3896179199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6793785095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2628440856934</t>
   </si>
   <si>
     <t xml:space="preserve">16.5254440307617</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6069393157959</t>
+    <t xml:space="preserve">16.6069412231445</t>
   </si>
   <si>
     <t xml:space="preserve">16.8061466217041</t>
@@ -386,31 +386,31 @@
     <t xml:space="preserve">16.8242588043213</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0726909637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.873480796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3624496459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4439487457275</t>
+    <t xml:space="preserve">16.0726890563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8734798431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3624515533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4439468383789</t>
   </si>
   <si>
     <t xml:space="preserve">16.69748878479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0959072113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1321296691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.086856842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0325260162354</t>
+    <t xml:space="preserve">17.095911026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1321277618408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0868587493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0325241088867</t>
   </si>
   <si>
     <t xml:space="preserve">17.3403968811035</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">17.9018077850342</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1372394561768</t>
+    <t xml:space="preserve">18.137243270874</t>
   </si>
   <si>
     <t xml:space="preserve">17.9289741516113</t>
@@ -428,31 +428,31 @@
     <t xml:space="preserve">18.771089553833</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6352653503418</t>
+    <t xml:space="preserve">18.6352672576904</t>
   </si>
   <si>
     <t xml:space="preserve">19.0699081420898</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2147903442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6262092590332</t>
+    <t xml:space="preserve">19.2147884368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6262111663818</t>
   </si>
   <si>
     <t xml:space="preserve">18.4994411468506</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2187366485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.716760635376</t>
+    <t xml:space="preserve">18.2187347412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7167644500732</t>
   </si>
   <si>
     <t xml:space="preserve">18.5809364318848</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7620372772217</t>
+    <t xml:space="preserve">18.762035369873</t>
   </si>
   <si>
     <t xml:space="preserve">18.8073120117188</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">18.94313621521</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0427417755127</t>
+    <t xml:space="preserve">19.0427436828613</t>
   </si>
   <si>
     <t xml:space="preserve">18.6624317169189</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4722766876221</t>
+    <t xml:space="preserve">18.4722747802734</t>
   </si>
   <si>
     <t xml:space="preserve">18.6171569824219</t>
@@ -479,46 +479,46 @@
     <t xml:space="preserve">18.9703025817871</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6805419921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6080989837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6533737182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5175514221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.870698928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6986503601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1061305999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9210834503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6947040557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5588817596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4592761993408</t>
+    <t xml:space="preserve">18.6805400848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6081027984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6533756256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5175495147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8706970214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6986522674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.106128692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9210815429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6947059631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5588798522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4592742919922</t>
   </si>
   <si>
     <t xml:space="preserve">19.314395904541</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8888072967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1332931518555</t>
+    <t xml:space="preserve">18.8888092041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1332912445068</t>
   </si>
   <si>
     <t xml:space="preserve">19.1604595184326</t>
@@ -527,22 +527,22 @@
     <t xml:space="preserve">19.9391918182373</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4553279876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3557205200195</t>
+    <t xml:space="preserve">20.4553318023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3557224273682</t>
   </si>
   <si>
     <t xml:space="preserve">20.3104496002197</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3919429779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4643859863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6907634735107</t>
+    <t xml:space="preserve">20.3919448852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4643840789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6907615661621</t>
   </si>
   <si>
     <t xml:space="preserve">20.8446960449219</t>
@@ -551,13 +551,13 @@
     <t xml:space="preserve">20.7994194030762</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4009990692139</t>
+    <t xml:space="preserve">20.4010009765625</t>
   </si>
   <si>
     <t xml:space="preserve">20.1021842956543</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5277671813965</t>
+    <t xml:space="preserve">20.5277709960938</t>
   </si>
   <si>
     <t xml:space="preserve">20.3647785186768</t>
@@ -578,13 +578,13 @@
     <t xml:space="preserve">20.2651748657227</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3285579681396</t>
+    <t xml:space="preserve">20.3285598754883</t>
   </si>
   <si>
     <t xml:space="preserve">20.0387954711914</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1474590301514</t>
+    <t xml:space="preserve">20.1474571228027</t>
   </si>
   <si>
     <t xml:space="preserve">20.2289543151855</t>
@@ -593,61 +593,61 @@
     <t xml:space="preserve">20.5006046295166</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5639877319336</t>
+    <t xml:space="preserve">20.5639896392822</t>
   </si>
   <si>
     <t xml:space="preserve">20.1836795806885</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5498237609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4140014648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5045490264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7218704223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7943115234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5226593017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8305320739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9120273590088</t>
+    <t xml:space="preserve">19.549825668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4140033721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5045509338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7218723297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7943134307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5226612091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.830530166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9120254516602</t>
   </si>
   <si>
     <t xml:space="preserve">19.7490348815918</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0919628143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3002300262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3273983001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2458992004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0104694366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7388172149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8565330505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8203125</t>
+    <t xml:space="preserve">18.0919609069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3002281188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3273963928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2458972930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0104675292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7388191223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8565311431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8203144073486</t>
   </si>
   <si>
     <t xml:space="preserve">17.6392116546631</t>
@@ -656,82 +656,82 @@
     <t xml:space="preserve">18.3455066680908</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3907833099365</t>
+    <t xml:space="preserve">18.3907775878906</t>
   </si>
   <si>
     <t xml:space="preserve">19.151403427124</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2872276306152</t>
+    <t xml:space="preserve">19.2872295379639</t>
   </si>
   <si>
     <t xml:space="preserve">19.3958911895752</t>
   </si>
   <si>
-    <t xml:space="preserve">19.377779006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1151828765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5860443115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2600650787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3738327026367</t>
+    <t xml:space="preserve">19.3777809143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1151847839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5860462188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2600612640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3738346099854</t>
   </si>
   <si>
     <t xml:space="preserve">20.3466701507568</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2380104064941</t>
+    <t xml:space="preserve">20.2380084991455</t>
   </si>
   <si>
     <t xml:space="preserve">20.1293468475342</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1565132141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8084774017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6183204650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4785480499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5328788757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0671291351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0580711364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2572822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2935009002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3025550842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3206672668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.275390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2391681671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8186950683594</t>
+    <t xml:space="preserve">20.15651512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8084754943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6183185577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4785461425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5328769683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0671253204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.058069229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2572784423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2935028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3025569915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3206653594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2753925323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2391700744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8186931610107</t>
   </si>
   <si>
     <t xml:space="preserve">23.0722332000732</t>
@@ -740,28 +740,28 @@
     <t xml:space="preserve">22.891134262085</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1537284851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.099401473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5923194885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3568840026855</t>
+    <t xml:space="preserve">23.1537303924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0993995666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5923175811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3568859100342</t>
   </si>
   <si>
     <t xml:space="preserve">22.9092445373535</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1757850646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1395664215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6064834594727</t>
+    <t xml:space="preserve">22.1757869720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1395645141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6064796447754</t>
   </si>
   <si>
     <t xml:space="preserve">23.7513618469238</t>
@@ -770,43 +770,43 @@
     <t xml:space="preserve">24.1226196289062</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6427021026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6879787445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.561206817627</t>
+    <t xml:space="preserve">23.6427040100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6879768371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5612087249756</t>
   </si>
   <si>
     <t xml:space="preserve">23.7423076629639</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7242012023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6336479187012</t>
+    <t xml:space="preserve">23.7241973876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6336460113525</t>
   </si>
   <si>
     <t xml:space="preserve">23.823802947998</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6970348358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0139598846436</t>
+    <t xml:space="preserve">23.6970329284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0139579772949</t>
   </si>
   <si>
     <t xml:space="preserve">24.285608291626</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0682888031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9777374267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2946643829346</t>
+    <t xml:space="preserve">24.0682907104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9777355194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2946662902832</t>
   </si>
   <si>
     <t xml:space="preserve">24.4304885864258</t>
@@ -815,22 +815,22 @@
     <t xml:space="preserve">24.61159324646</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7655296325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1911125183105</t>
+    <t xml:space="preserve">24.7655258178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1911144256592</t>
   </si>
   <si>
     <t xml:space="preserve">25.3903255462646</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4265460968018</t>
+    <t xml:space="preserve">25.4265441894531</t>
   </si>
   <si>
     <t xml:space="preserve">25.6167030334473</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6710319519043</t>
+    <t xml:space="preserve">25.6710300445557</t>
   </si>
   <si>
     <t xml:space="preserve">25.6529216766357</t>
@@ -845,16 +845,16 @@
     <t xml:space="preserve">24.9556827545166</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9013519287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0643424987793</t>
+    <t xml:space="preserve">24.9013538360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0643463134766</t>
   </si>
   <si>
     <t xml:space="preserve">24.8017482757568</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6206474304199</t>
+    <t xml:space="preserve">24.6206455230713</t>
   </si>
   <si>
     <t xml:space="preserve">24.9375743865967</t>
@@ -869,13 +869,13 @@
     <t xml:space="preserve">25.2273349761963</t>
   </si>
   <si>
-    <t xml:space="preserve">25.173002243042</t>
+    <t xml:space="preserve">25.1730041503906</t>
   </si>
   <si>
     <t xml:space="preserve">25.1639499664307</t>
   </si>
   <si>
-    <t xml:space="preserve">25.399377822876</t>
+    <t xml:space="preserve">25.3993759155273</t>
   </si>
   <si>
     <t xml:space="preserve">25.7253608703613</t>
@@ -890,34 +890,34 @@
     <t xml:space="preserve">25.7434711456299</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5442600250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4808769226074</t>
+    <t xml:space="preserve">25.5442581176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4808750152588</t>
   </si>
   <si>
     <t xml:space="preserve">25.5080394744873</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2635517120361</t>
+    <t xml:space="preserve">25.2635536193848</t>
   </si>
   <si>
     <t xml:space="preserve">25.0824546813965</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7836399078369</t>
+    <t xml:space="preserve">24.7836380004883</t>
   </si>
   <si>
     <t xml:space="preserve">24.4214363098145</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2674999237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5261497497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1237831115723</t>
+    <t xml:space="preserve">24.2674980163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5261478424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1237812042236</t>
   </si>
   <si>
     <t xml:space="preserve">26.1871662139893</t>
@@ -926,16 +926,16 @@
     <t xml:space="preserve">26.6308650970459</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4859867095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3229923248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6761360168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8934631347656</t>
+    <t xml:space="preserve">26.4859828948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3229942321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6761379241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.893461227417</t>
   </si>
   <si>
     <t xml:space="preserve">26.2596092224121</t>
@@ -947,7 +947,7 @@
     <t xml:space="preserve">26.9115676879883</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6037006378174</t>
+    <t xml:space="preserve">26.6036987304688</t>
   </si>
   <si>
     <t xml:space="preserve">26.5946445465088</t>
@@ -956,85 +956,85 @@
     <t xml:space="preserve">25.3088302612305</t>
   </si>
   <si>
-    <t xml:space="preserve">25.326940536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8340225219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8984451293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0641078948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.71120262146</t>
+    <t xml:space="preserve">25.3269386291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.834020614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8984432220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0641059875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7112045288086</t>
   </si>
   <si>
     <t xml:space="preserve">23.6159954071045</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2202472686768</t>
+    <t xml:space="preserve">23.2202453613281</t>
   </si>
   <si>
     <t xml:space="preserve">23.1282119750977</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9625492095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8705177307129</t>
+    <t xml:space="preserve">22.9625511169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8705196380615</t>
   </si>
   <si>
     <t xml:space="preserve">22.8613128662109</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2662658691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.238655090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0453853607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8889217376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0882263183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3183097839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2262783050537</t>
+    <t xml:space="preserve">23.266263961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2386531829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0453834533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8889255523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0882244110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3183116912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2262763977051</t>
   </si>
   <si>
     <t xml:space="preserve">22.3827342987061</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3643283843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7416667938232</t>
+    <t xml:space="preserve">22.364330291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7416687011719</t>
   </si>
   <si>
     <t xml:space="preserve">22.95334815979</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8797225952148</t>
+    <t xml:space="preserve">22.8797206878662</t>
   </si>
   <si>
     <t xml:space="preserve">23.2846717834473</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4871463775635</t>
+    <t xml:space="preserve">23.4871482849121</t>
   </si>
   <si>
     <t xml:space="preserve">23.4319248199463</t>
   </si>
   <si>
-    <t xml:space="preserve">22.806095123291</t>
+    <t xml:space="preserve">22.8060932159424</t>
   </si>
   <si>
     <t xml:space="preserve">23.0269756317139</t>
@@ -1052,13 +1052,13 @@
     <t xml:space="preserve">21.4900035858154</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7200870513916</t>
+    <t xml:space="preserve">21.7200889587402</t>
   </si>
   <si>
     <t xml:space="preserve">21.5544261932373</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6740684509277</t>
+    <t xml:space="preserve">21.6740703582764</t>
   </si>
   <si>
     <t xml:space="preserve">21.6280536651611</t>
@@ -1070,31 +1070,31 @@
     <t xml:space="preserve">21.2046966552734</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1218662261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.416374206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5084095001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9133605957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8857517242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9685840606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6220226287842</t>
+    <t xml:space="preserve">21.1218681335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4163761138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5084114074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9133586883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8857498168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9685821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6220245361328</t>
   </si>
   <si>
     <t xml:space="preserve">22.3735313415527</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2170715332031</t>
+    <t xml:space="preserve">22.2170734405518</t>
   </si>
   <si>
     <t xml:space="preserve">22.4103469848633</t>
@@ -1103,10 +1103,10 @@
     <t xml:space="preserve">22.5299892425537</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6312274932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6404304504395</t>
+    <t xml:space="preserve">22.6312294006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6404323577881</t>
   </si>
   <si>
     <t xml:space="preserve">22.5576000213623</t>
@@ -1115,76 +1115,76 @@
     <t xml:space="preserve">21.4255809783936</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6556644439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.263090133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5391941070557</t>
+    <t xml:space="preserve">21.6556663513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2630920410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.539192199707</t>
   </si>
   <si>
     <t xml:space="preserve">22.3551254272461</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0514106750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7876834869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3367195129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.115837097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7661075592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0606155395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7569026947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9961910247803</t>
+    <t xml:space="preserve">22.0514125823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7876873016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3367176055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1158390045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7661037445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0606117248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7569007873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9961891174316</t>
   </si>
   <si>
     <t xml:space="preserve">21.701681137085</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0053958892822</t>
+    <t xml:space="preserve">22.0053939819336</t>
   </si>
   <si>
     <t xml:space="preserve">21.8765468597412</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1250419616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7753086090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0238037109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9041595458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6832733154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8273544311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0574436187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9470024108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.799747467041</t>
+    <t xml:space="preserve">22.1250381469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7753124237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0238018035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9041576385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6832752227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.827356338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0574398040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.94700050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7997455596924</t>
   </si>
   <si>
     <t xml:space="preserve">21.103458404541</t>
@@ -1193,22 +1193,22 @@
     <t xml:space="preserve">21.0758476257324</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3243427276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.950174331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0974292755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8581428527832</t>
+    <t xml:space="preserve">21.3243408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9501762390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0974311828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8581409454346</t>
   </si>
   <si>
     <t xml:space="preserve">21.6372566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2967300415039</t>
+    <t xml:space="preserve">21.2967319488525</t>
   </si>
   <si>
     <t xml:space="preserve">20.9746112823486</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">21.1402702331543</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0666446685791</t>
+    <t xml:space="preserve">21.0666465759277</t>
   </si>
   <si>
     <t xml:space="preserve">20.7077121734619</t>
@@ -1229,16 +1229,16 @@
     <t xml:space="preserve">21.0942554473877</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1586799621582</t>
+    <t xml:space="preserve">21.1586780548096</t>
   </si>
   <si>
     <t xml:space="preserve">21.0206279754639</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0022220611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6340847015381</t>
+    <t xml:space="preserve">21.0022239685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6340827941895</t>
   </si>
   <si>
     <t xml:space="preserve">20.4500141143799</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">20.3855895996094</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3947925567627</t>
+    <t xml:space="preserve">20.3947944641113</t>
   </si>
   <si>
     <t xml:space="preserve">20.0082511901855</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">19.9714393615723</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0634708404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4868278503418</t>
+    <t xml:space="preserve">20.0634727478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4868297576904</t>
   </si>
   <si>
     <t xml:space="preserve">20.7445278167725</t>
@@ -1268,43 +1268,43 @@
     <t xml:space="preserve">20.8917808532715</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2415084838867</t>
+    <t xml:space="preserve">21.2415103912354</t>
   </si>
   <si>
     <t xml:space="preserve">20.9285926818848</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2475395202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1647090911865</t>
+    <t xml:space="preserve">20.2475414276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1647109985352</t>
   </si>
   <si>
     <t xml:space="preserve">20.0910816192627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2719783782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6953353881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.805778503418</t>
+    <t xml:space="preserve">19.2719764709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.695333480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8057746887207</t>
   </si>
   <si>
     <t xml:space="preserve">19.7321510314941</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1831150054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0450668334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2935543060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4316101074219</t>
+    <t xml:space="preserve">20.1831169128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0450630187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2935581207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4316082000732</t>
   </si>
   <si>
     <t xml:space="preserve">20.5696601867676</t>
@@ -1313,13 +1313,13 @@
     <t xml:space="preserve">20.6616954803467</t>
   </si>
   <si>
-    <t xml:space="preserve">21.131067276001</t>
+    <t xml:space="preserve">21.1310691833496</t>
   </si>
   <si>
     <t xml:space="preserve">21.0482387542725</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1954936981201</t>
+    <t xml:space="preserve">21.1954956054688</t>
   </si>
   <si>
     <t xml:space="preserve">21.4531898498535</t>
@@ -1334,40 +1334,40 @@
     <t xml:space="preserve">20.7721366882324</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4652519226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.796573638916</t>
+    <t xml:space="preserve">19.4652481079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7965717315674</t>
   </si>
   <si>
     <t xml:space="preserve">19.8609962463379</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0174541473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2199268341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2291316986084</t>
+    <t xml:space="preserve">20.0174522399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2199287414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.229133605957</t>
   </si>
   <si>
     <t xml:space="preserve">20.5236434936523</t>
   </si>
   <si>
-    <t xml:space="preserve">20.652494430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9101867675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2659492492676</t>
+    <t xml:space="preserve">20.6524925231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9101848602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2659473419189</t>
   </si>
   <si>
     <t xml:space="preserve">20.4684219360352</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1555042266846</t>
+    <t xml:space="preserve">20.1555061340332</t>
   </si>
   <si>
     <t xml:space="preserve">20.1739120483398</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">21.259916305542</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3703556060791</t>
+    <t xml:space="preserve">21.3703575134277</t>
   </si>
   <si>
     <t xml:space="preserve">21.5176124572754</t>
@@ -1385,7 +1385,7 @@
     <t xml:space="preserve">20.8549671173096</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9193916320801</t>
+    <t xml:space="preserve">20.9193897247314</t>
   </si>
   <si>
     <t xml:space="preserve">20.5052375793457</t>
@@ -1394,19 +1394,19 @@
     <t xml:space="preserve">20.3487777709961</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0266571044922</t>
+    <t xml:space="preserve">20.0266590118408</t>
   </si>
   <si>
     <t xml:space="preserve">19.7229442596436</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9162158966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5604553222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7169170379639</t>
+    <t xml:space="preserve">19.9162178039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5604572296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7169151306152</t>
   </si>
   <si>
     <t xml:space="preserve">20.9377975463867</t>
@@ -1418,16 +1418,16 @@
     <t xml:space="preserve">21.6004428863525</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6248798370361</t>
+    <t xml:space="preserve">20.6248817443848</t>
   </si>
   <si>
     <t xml:space="preserve">20.2751502990723</t>
   </si>
   <si>
-    <t xml:space="preserve">20.109489440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6493167877197</t>
+    <t xml:space="preserve">20.1094875335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6493186950684</t>
   </si>
   <si>
     <t xml:space="preserve">19.9990482330322</t>
@@ -1436,46 +1436,46 @@
     <t xml:space="preserve">20.1278953552246</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3303699493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8733730316162</t>
+    <t xml:space="preserve">20.3303718566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8733749389648</t>
   </si>
   <si>
     <t xml:space="preserve">20.3763885498047</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5328483581543</t>
+    <t xml:space="preserve">20.5328464508057</t>
   </si>
   <si>
     <t xml:space="preserve">20.3027591705322</t>
   </si>
   <si>
-    <t xml:space="preserve">20.64328956604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6156768798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7261180877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2783260345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3151359558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.536018371582</t>
+    <t xml:space="preserve">20.6432857513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6156787872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7261161804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2783279418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3151378631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5360202789307</t>
   </si>
   <si>
     <t xml:space="preserve">21.7937164306641</t>
   </si>
   <si>
-    <t xml:space="preserve">22.64963722229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.548397064209</t>
+    <t xml:space="preserve">22.6496334075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5483989715576</t>
   </si>
   <si>
     <t xml:space="preserve">22.4195499420166</t>
@@ -1484,16 +1484,16 @@
     <t xml:space="preserve">22.2078685760498</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5668029785156</t>
+    <t xml:space="preserve">22.5668048858643</t>
   </si>
   <si>
     <t xml:space="preserve">22.6128215789795</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9165344238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6864471435547</t>
+    <t xml:space="preserve">22.9165325164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6864452362061</t>
   </si>
   <si>
     <t xml:space="preserve">22.7324657440186</t>
@@ -1502,16 +1502,16 @@
     <t xml:space="preserve">22.8337001800537</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7692794799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9073276519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2754688262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9913024902344</t>
+    <t xml:space="preserve">22.7692775726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9073314666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2754669189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.991304397583</t>
   </si>
   <si>
     <t xml:space="preserve">23.3090686798096</t>
@@ -1523,25 +1523,25 @@
     <t xml:space="preserve">22.9071884155273</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9819564819336</t>
+    <t xml:space="preserve">22.9819583892822</t>
   </si>
   <si>
     <t xml:space="preserve">22.7296123504639</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3557720184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6174602508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0754165649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3557987213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1969146728516</t>
+    <t xml:space="preserve">22.355770111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6174583435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.07541847229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3558006286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1969165802002</t>
   </si>
   <si>
     <t xml:space="preserve">23.206262588501</t>
@@ -1556,7 +1556,7 @@
     <t xml:space="preserve">22.7389602661133</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1595344543457</t>
+    <t xml:space="preserve">23.1595325469971</t>
   </si>
   <si>
     <t xml:space="preserve">23.5053367614746</t>
@@ -1568,10 +1568,10 @@
     <t xml:space="preserve">23.3931846618652</t>
   </si>
   <si>
-    <t xml:space="preserve">23.262336730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9258804321289</t>
+    <t xml:space="preserve">23.2623386383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9258823394775</t>
   </si>
   <si>
     <t xml:space="preserve">20.9912452697754</t>
@@ -1580,31 +1580,31 @@
     <t xml:space="preserve">20.3370227813721</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9912185668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7388763427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.56130027771</t>
+    <t xml:space="preserve">19.9912166595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7388744354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5613021850586</t>
   </si>
   <si>
     <t xml:space="preserve">19.3089561462402</t>
   </si>
   <si>
-    <t xml:space="preserve">19.533260345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4958782196045</t>
+    <t xml:space="preserve">19.5332622528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4958801269531</t>
   </si>
   <si>
     <t xml:space="preserve">19.346342086792</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0285739898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6266918182373</t>
+    <t xml:space="preserve">19.0285758972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6266937255859</t>
   </si>
   <si>
     <t xml:space="preserve">18.3836975097656</t>
@@ -1613,16 +1613,16 @@
     <t xml:space="preserve">18.0752754211426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6220188140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.079948425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.603328704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6360416412354</t>
+    <t xml:space="preserve">18.6220207214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0799503326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6033306121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6360397338867</t>
   </si>
   <si>
     <t xml:space="preserve">18.7949237823486</t>
@@ -1637,37 +1637,37 @@
     <t xml:space="preserve">18.5752906799316</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3930416107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5285625457764</t>
+    <t xml:space="preserve">18.3930435180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5285606384277</t>
   </si>
   <si>
     <t xml:space="preserve">18.495849609375</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4351005554199</t>
+    <t xml:space="preserve">18.4350986480713</t>
   </si>
   <si>
     <t xml:space="preserve">18.3883686065674</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4911766052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2435054779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8042411804199</t>
+    <t xml:space="preserve">18.491174697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2435073852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8042392730713</t>
   </si>
   <si>
     <t xml:space="preserve">17.7715282440186</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1079883575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6734237670898</t>
+    <t xml:space="preserve">18.1079845428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6734218597412</t>
   </si>
   <si>
     <t xml:space="preserve">18.7575378417969</t>
@@ -1679,13 +1679,13 @@
     <t xml:space="preserve">18.276216506958</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2528533935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2107944488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3790264129639</t>
+    <t xml:space="preserve">18.2528514862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2107963562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3790245056152</t>
   </si>
   <si>
     <t xml:space="preserve">19.1407260894775</t>
@@ -1694,13 +1694,13 @@
     <t xml:space="preserve">19.4398002624512</t>
   </si>
   <si>
-    <t xml:space="preserve">19.402416229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4117641448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4304542541504</t>
+    <t xml:space="preserve">19.4024181365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4117622375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.430456161499</t>
   </si>
   <si>
     <t xml:space="preserve">19.3650321960449</t>
@@ -1712,19 +1712,19 @@
     <t xml:space="preserve">19.1687660217285</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1126880645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0939960479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7388458251953</t>
+    <t xml:space="preserve">19.1126899719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0939979553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7388439178467</t>
   </si>
   <si>
     <t xml:space="preserve">19.0566120147705</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8416519165039</t>
+    <t xml:space="preserve">18.8416538238525</t>
   </si>
   <si>
     <t xml:space="preserve">19.6080284118652</t>
@@ -1733,31 +1733,31 @@
     <t xml:space="preserve">19.2528820037842</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5239162445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4211101531982</t>
+    <t xml:space="preserve">19.5239143371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4211082458496</t>
   </si>
   <si>
     <t xml:space="preserve">19.8136444091797</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0753307342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.748218536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0192546844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7669143676758</t>
+    <t xml:space="preserve">20.0753326416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7482204437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0192565917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7669124603271</t>
   </si>
   <si>
     <t xml:space="preserve">19.7856044769287</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5706462860107</t>
+    <t xml:space="preserve">19.5706443786621</t>
   </si>
   <si>
     <t xml:space="preserve">19.2809162139893</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">19.1500720977783</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8977279663086</t>
+    <t xml:space="preserve">18.8977298736572</t>
   </si>
   <si>
     <t xml:space="preserve">18.8042697906494</t>
@@ -1775,19 +1775,19 @@
     <t xml:space="preserve">18.8790378570557</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1780834197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6453857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8556442260742</t>
+    <t xml:space="preserve">18.1780853271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6453876495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8556423187256</t>
   </si>
   <si>
     <t xml:space="preserve">17.2528228759766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1546878814697</t>
+    <t xml:space="preserve">17.1546897888184</t>
   </si>
   <si>
     <t xml:space="preserve">16.9817886352539</t>
@@ -1799,10 +1799,10 @@
     <t xml:space="preserve">17.949104309082</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1173324584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2154693603516</t>
+    <t xml:space="preserve">18.1173343658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2154674530029</t>
   </si>
   <si>
     <t xml:space="preserve">19.1874580383301</t>
@@ -1817,64 +1817,64 @@
     <t xml:space="preserve">19.5893363952637</t>
   </si>
   <si>
-    <t xml:space="preserve">19.645414352417</t>
+    <t xml:space="preserve">19.6454162597656</t>
   </si>
   <si>
     <t xml:space="preserve">19.4771842956543</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5426082611084</t>
+    <t xml:space="preserve">19.5426063537598</t>
   </si>
   <si>
     <t xml:space="preserve">19.5799922943115</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0005645751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6267204284668</t>
+    <t xml:space="preserve">20.0005626678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6267242431641</t>
   </si>
   <si>
     <t xml:space="preserve">19.4865303039551</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7014904022217</t>
+    <t xml:space="preserve">19.701488494873</t>
   </si>
   <si>
     <t xml:space="preserve">19.3930702209473</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7481918334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7855777740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0659580230713</t>
+    <t xml:space="preserve">18.7481937408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7855758666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0659561157227</t>
   </si>
   <si>
     <t xml:space="preserve">19.5145683288574</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2061462402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0472087860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7107524871826</t>
+    <t xml:space="preserve">19.206148147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0472106933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.710750579834</t>
   </si>
   <si>
     <t xml:space="preserve">16.8135585784912</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5845832824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5471954345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5378513336182</t>
+    <t xml:space="preserve">16.5845813751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5471973419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5378475189209</t>
   </si>
   <si>
     <t xml:space="preserve">16.7200965881348</t>
@@ -1883,16 +1883,16 @@
     <t xml:space="preserve">16.495792388916</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7528095245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5004653930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4630813598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0425109863281</t>
+    <t xml:space="preserve">16.7528076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.500467300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4630832672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0425090789795</t>
   </si>
   <si>
     <t xml:space="preserve">16.3509292602539</t>
@@ -1901,43 +1901,43 @@
     <t xml:space="preserve">16.5425224304199</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8415966033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6640205383301</t>
+    <t xml:space="preserve">16.8415946960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6640224456787</t>
   </si>
   <si>
     <t xml:space="preserve">16.5331783294678</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5892543792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6827125549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5986022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4256992340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1266231536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1593341827393</t>
+    <t xml:space="preserve">16.5892524719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6827144622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5986003875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4256954193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1266212463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1593360900879</t>
   </si>
   <si>
     <t xml:space="preserve">16.4490623474121</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1920471191406</t>
+    <t xml:space="preserve">16.192045211792</t>
   </si>
   <si>
     <t xml:space="preserve">16.2154102325439</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4817752838135</t>
+    <t xml:space="preserve">16.4817733764648</t>
   </si>
   <si>
     <t xml:space="preserve">16.5238304138184</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">16.4023323059082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2995262145996</t>
+    <t xml:space="preserve">16.299524307251</t>
   </si>
   <si>
     <t xml:space="preserve">16.5799083709717</t>
@@ -1970,10 +1970,10 @@
     <t xml:space="preserve">17.5518989562988</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4163799285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1079597473145</t>
+    <t xml:space="preserve">17.4163780212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1079578399658</t>
   </si>
   <si>
     <t xml:space="preserve">17.1313247680664</t>
@@ -1988,22 +1988,22 @@
     <t xml:space="preserve">17.4397430419922</t>
   </si>
   <si>
-    <t xml:space="preserve">17.453763961792</t>
+    <t xml:space="preserve">17.4537620544434</t>
   </si>
   <si>
     <t xml:space="preserve">17.7294731140137</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6547031402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3369388580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1453437805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8462677001953</t>
+    <t xml:space="preserve">17.6547012329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3369369506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1453418731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8462696075439</t>
   </si>
   <si>
     <t xml:space="preserve">17.1687088012695</t>
@@ -2012,19 +2012,19 @@
     <t xml:space="preserve">16.822904586792</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9911613464355</t>
+    <t xml:space="preserve">17.9911632537842</t>
   </si>
   <si>
     <t xml:space="preserve">17.9117221832275</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0378932952881</t>
+    <t xml:space="preserve">18.0378913879395</t>
   </si>
   <si>
     <t xml:space="preserve">17.6593780517578</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7948951721191</t>
+    <t xml:space="preserve">17.7948970794678</t>
   </si>
   <si>
     <t xml:space="preserve">17.6360130310059</t>
@@ -2033,31 +2033,31 @@
     <t xml:space="preserve">17.3275928497314</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3976898193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6266670227051</t>
+    <t xml:space="preserve">17.3976879119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6266651153564</t>
   </si>
   <si>
     <t xml:space="preserve">17.5004940032959</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8696632385254</t>
+    <t xml:space="preserve">17.869665145874</t>
   </si>
   <si>
     <t xml:space="preserve">18.3136005401611</t>
   </si>
   <si>
-    <t xml:space="preserve">18.056583404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2855606079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0192012786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9677963256836</t>
+    <t xml:space="preserve">18.0565853118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2855625152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0191993713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9677982330322</t>
   </si>
   <si>
     <t xml:space="preserve">17.9070472717285</t>
@@ -2075,28 +2075,28 @@
     <t xml:space="preserve">18.5565967559814</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4397735595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5472526550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3089294433594</t>
+    <t xml:space="preserve">18.439769744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5472507476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3089275360107</t>
   </si>
   <si>
     <t xml:space="preserve">18.8603458404541</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3696784973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5893096923828</t>
+    <t xml:space="preserve">18.3696765899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5893077850342</t>
   </si>
   <si>
     <t xml:space="preserve">18.0238723754883</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8603172302246</t>
+    <t xml:space="preserve">17.8603191375732</t>
   </si>
   <si>
     <t xml:space="preserve">18.06125831604</t>
@@ -2105,13 +2105,13 @@
     <t xml:space="preserve">17.5986270904541</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0939712524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.860372543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0472965240479</t>
+    <t xml:space="preserve">18.0939693450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8603744506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0472946166992</t>
   </si>
   <si>
     <t xml:space="preserve">19.9071025848389</t>
@@ -2126,10 +2126,10 @@
     <t xml:space="preserve">19.4132251739502</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2042751312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4892082214355</t>
+    <t xml:space="preserve">19.2042770385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4892063140869</t>
   </si>
   <si>
     <t xml:space="preserve">19.1187953948975</t>
@@ -2147,16 +2147,16 @@
     <t xml:space="preserve">17.7131423950195</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7273921966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8318614959717</t>
+    <t xml:space="preserve">17.7273902893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8318634033203</t>
   </si>
   <si>
     <t xml:space="preserve">18.3732299804688</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6534099578857</t>
+    <t xml:space="preserve">18.6534118652344</t>
   </si>
   <si>
     <t xml:space="preserve">19.1757831573486</t>
@@ -2168,13 +2168,13 @@
     <t xml:space="preserve">19.2802562713623</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2137756347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9810791015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9050998687744</t>
+    <t xml:space="preserve">19.213773727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9810810089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.905101776123</t>
   </si>
   <si>
     <t xml:space="preserve">19.0333194732666</t>
@@ -2198,16 +2198,16 @@
     <t xml:space="preserve">19.7171497344971</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8121280670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.745641708374</t>
+    <t xml:space="preserve">19.812126159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7456436157227</t>
   </si>
   <si>
     <t xml:space="preserve">19.926097869873</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1350479125977</t>
+    <t xml:space="preserve">20.1350498199463</t>
   </si>
   <si>
     <t xml:space="preserve">20.1920337677002</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">20.4674644470215</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4864616394043</t>
+    <t xml:space="preserve">20.4864597320557</t>
   </si>
   <si>
     <t xml:space="preserve">20.2870101928711</t>
@@ -2225,13 +2225,13 @@
     <t xml:space="preserve">20.2775115966797</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8406200408936</t>
+    <t xml:space="preserve">19.8406181335449</t>
   </si>
   <si>
     <t xml:space="preserve">19.8216247558594</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8501167297363</t>
+    <t xml:space="preserve">19.850118637085</t>
   </si>
   <si>
     <t xml:space="preserve">19.9545917510986</t>
@@ -2240,7 +2240,7 @@
     <t xml:space="preserve">19.8881092071533</t>
   </si>
   <si>
-    <t xml:space="preserve">20.030574798584</t>
+    <t xml:space="preserve">20.0305728912354</t>
   </si>
   <si>
     <t xml:space="preserve">19.8691120147705</t>
@@ -2261,16 +2261,16 @@
     <t xml:space="preserve">18.0218181610107</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9315872192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5754261016846</t>
+    <t xml:space="preserve">17.9315891265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5754241943359</t>
   </si>
   <si>
     <t xml:space="preserve">17.2952442169189</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2762508392334</t>
+    <t xml:space="preserve">17.276252746582</t>
   </si>
   <si>
     <t xml:space="preserve">17.2667541503906</t>
@@ -2282,7 +2282,7 @@
     <t xml:space="preserve">17.0198135375977</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8963432312012</t>
+    <t xml:space="preserve">16.8963451385498</t>
   </si>
   <si>
     <t xml:space="preserve">17.0150661468506</t>
@@ -2291,25 +2291,25 @@
     <t xml:space="preserve">16.59716796875</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2837429046631</t>
+    <t xml:space="preserve">16.2837448120117</t>
   </si>
   <si>
     <t xml:space="preserve">16.8108654022217</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8536071777344</t>
+    <t xml:space="preserve">16.8536052703857</t>
   </si>
   <si>
     <t xml:space="preserve">17.0530548095703</t>
   </si>
   <si>
-    <t xml:space="preserve">16.915340423584</t>
+    <t xml:space="preserve">16.9153385162354</t>
   </si>
   <si>
     <t xml:space="preserve">16.6636505126953</t>
   </si>
   <si>
-    <t xml:space="preserve">16.734884262085</t>
+    <t xml:space="preserve">16.7348861694336</t>
   </si>
   <si>
     <t xml:space="preserve">16.948579788208</t>
@@ -2321,13 +2321,13 @@
     <t xml:space="preserve">16.8441066741943</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4974422454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.668399810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6304111480713</t>
+    <t xml:space="preserve">16.497444152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6683979034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6304092407227</t>
   </si>
   <si>
     <t xml:space="preserve">16.9248371124268</t>
@@ -2351,7 +2351,7 @@
     <t xml:space="preserve">17.2857475280762</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2002696990967</t>
+    <t xml:space="preserve">17.2002716064453</t>
   </si>
   <si>
     <t xml:space="preserve">16.696891784668</t>
@@ -2360,7 +2360,7 @@
     <t xml:space="preserve">16.7538776397705</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2267570495605</t>
+    <t xml:space="preserve">16.2267551422119</t>
   </si>
   <si>
     <t xml:space="preserve">16.1887664794922</t>
@@ -2378,16 +2378,16 @@
     <t xml:space="preserve">16.1032905578613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0178089141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4811906814575</t>
+    <t xml:space="preserve">16.0178108215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4811916351318</t>
   </si>
   <si>
     <t xml:space="preserve">15.5381784439087</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5619230270386</t>
+    <t xml:space="preserve">15.5619220733643</t>
   </si>
   <si>
     <t xml:space="preserve">15.1725187301636</t>
@@ -2399,7 +2399,7 @@
     <t xml:space="preserve">15.3577222824097</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5904150009155</t>
+    <t xml:space="preserve">15.5904159545898</t>
   </si>
   <si>
     <t xml:space="preserve">15.4716949462891</t>
@@ -2408,7 +2408,7 @@
     <t xml:space="preserve">15.680643081665</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4052085876465</t>
+    <t xml:space="preserve">15.4052095413208</t>
   </si>
   <si>
     <t xml:space="preserve">15.324481010437</t>
@@ -2420,7 +2420,7 @@
     <t xml:space="preserve">15.2579975128174</t>
   </si>
   <si>
-    <t xml:space="preserve">15.177267074585</t>
+    <t xml:space="preserve">15.1772661209106</t>
   </si>
   <si>
     <t xml:space="preserve">15.068042755127</t>
@@ -2435,13 +2435,13 @@
     <t xml:space="preserve">15.9608240127563</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7661218643188</t>
+    <t xml:space="preserve">15.7661228179932</t>
   </si>
   <si>
     <t xml:space="preserve">15.8800926208496</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9085874557495</t>
+    <t xml:space="preserve">15.9085865020752</t>
   </si>
   <si>
     <t xml:space="preserve">15.922833442688</t>
@@ -2456,10 +2456,10 @@
     <t xml:space="preserve">16.4024639129639</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5781726837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5734233856201</t>
+    <t xml:space="preserve">16.5781707763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5734252929688</t>
   </si>
   <si>
     <t xml:space="preserve">16.6066665649414</t>
@@ -2468,10 +2468,10 @@
     <t xml:space="preserve">17.2809982299805</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9723262786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4404563903809</t>
+    <t xml:space="preserve">16.9723281860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4404544830322</t>
   </si>
   <si>
     <t xml:space="preserve">16.3074893951416</t>
@@ -2483,40 +2483,40 @@
     <t xml:space="preserve">16.3977165222168</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6209106445312</t>
+    <t xml:space="preserve">16.6209125518799</t>
   </si>
   <si>
     <t xml:space="preserve">17.3047428131104</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1290378570557</t>
+    <t xml:space="preserve">17.129035949707</t>
   </si>
   <si>
     <t xml:space="preserve">17.1860218048096</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6873970031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9695796966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1120452880859</t>
+    <t xml:space="preserve">16.6873950958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9695816040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1120433807373</t>
   </si>
   <si>
     <t xml:space="preserve">17.4282131195068</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3474826812744</t>
+    <t xml:space="preserve">17.3474807739258</t>
   </si>
   <si>
     <t xml:space="preserve">17.2477569580078</t>
   </si>
   <si>
-    <t xml:space="preserve">17.337984085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4092178344727</t>
+    <t xml:space="preserve">17.3379859924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.409215927124</t>
   </si>
   <si>
     <t xml:space="preserve">17.62766456604</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">17.803373336792</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1167945861816</t>
+    <t xml:space="preserve">18.116792678833</t>
   </si>
   <si>
     <t xml:space="preserve">17.8556079864502</t>
@@ -2540,16 +2540,16 @@
     <t xml:space="preserve">17.8081188201904</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0028228759766</t>
+    <t xml:space="preserve">18.0028209686279</t>
   </si>
   <si>
     <t xml:space="preserve">17.6704025268555</t>
   </si>
   <si>
-    <t xml:space="preserve">17.622917175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6799030303955</t>
+    <t xml:space="preserve">17.6229152679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6799011230469</t>
   </si>
   <si>
     <t xml:space="preserve">17.9885749816895</t>
@@ -2561,16 +2561,16 @@
     <t xml:space="preserve">18.0930500030518</t>
   </si>
   <si>
-    <t xml:space="preserve">17.90309715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8508605957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2620029449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.228759765625</t>
+    <t xml:space="preserve">17.9030952453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8508586883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2620048522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2287616729736</t>
   </si>
   <si>
     <t xml:space="preserve">17.0957946777344</t>
@@ -2582,7 +2582,7 @@
     <t xml:space="preserve">16.6161632537842</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5924186706543</t>
+    <t xml:space="preserve">16.5924167633057</t>
   </si>
   <si>
     <t xml:space="preserve">15.8611001968384</t>
@@ -2591,13 +2591,13 @@
     <t xml:space="preserve">16.2694988250732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2979888916016</t>
+    <t xml:space="preserve">16.2979907989502</t>
   </si>
   <si>
     <t xml:space="preserve">16.1175346374512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.846851348877</t>
+    <t xml:space="preserve">15.8468523025513</t>
   </si>
   <si>
     <t xml:space="preserve">16.3217353820801</t>
@@ -2609,13 +2609,13 @@
     <t xml:space="preserve">15.7803688049316</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7186336517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3434762954712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9845685958862</t>
+    <t xml:space="preserve">15.7186317443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3434772491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9845676422119</t>
   </si>
   <si>
     <t xml:space="preserve">15.7471265792847</t>
@@ -2624,10 +2624,10 @@
     <t xml:space="preserve">15.6046619415283</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7043867111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8848419189453</t>
+    <t xml:space="preserve">15.7043857574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8848428726196</t>
   </si>
   <si>
     <t xml:space="preserve">15.5429258346558</t>
@@ -2639,22 +2639,22 @@
     <t xml:space="preserve">13.8096027374268</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8665895462036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1420211791992</t>
+    <t xml:space="preserve">13.8665885925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1420221328735</t>
   </si>
   <si>
     <t xml:space="preserve">13.6054029464722</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5721607208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0735340118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0497894287109</t>
+    <t xml:space="preserve">13.5721616744995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0735349655151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0497903823853</t>
   </si>
   <si>
     <t xml:space="preserve">12.9738092422485</t>
@@ -2675,7 +2675,7 @@
     <t xml:space="preserve">10.7845964431763</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08166694641113</t>
+    <t xml:space="preserve">9.08166599273682</t>
   </si>
   <si>
     <t xml:space="preserve">9.65437507629395</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">9.4976634979248</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6183891296387</t>
+    <t xml:space="preserve">10.6183881759644</t>
   </si>
   <si>
     <t xml:space="preserve">11.8625822067261</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">13.3964538574219</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9690589904785</t>
+    <t xml:space="preserve">12.9690599441528</t>
   </si>
   <si>
     <t xml:space="preserve">12.2519855499268</t>
@@ -2714,13 +2714,13 @@
     <t xml:space="preserve">11.9195680618286</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4921731948853</t>
+    <t xml:space="preserve">11.4921741485596</t>
   </si>
   <si>
     <t xml:space="preserve">11.2072429656982</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1597547531128</t>
+    <t xml:space="preserve">11.1597557067871</t>
   </si>
   <si>
     <t xml:space="preserve">11.1882476806641</t>
@@ -2732,7 +2732,7 @@
     <t xml:space="preserve">11.5586566925049</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6251401901245</t>
+    <t xml:space="preserve">11.6251411437988</t>
   </si>
   <si>
     <t xml:space="preserve">11.9765539169312</t>
@@ -2750,22 +2750,22 @@
     <t xml:space="preserve">10.8178396224976</t>
   </si>
   <si>
-    <t xml:space="preserve">10.399941444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4474296569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3809471130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7323608398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9128150939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.722861289978</t>
+    <t xml:space="preserve">10.3999404907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4474306106567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3809461593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7323598861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9128160476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7228622436523</t>
   </si>
   <si>
     <t xml:space="preserve">10.3049659729004</t>
@@ -2777,19 +2777,19 @@
     <t xml:space="preserve">10.3144626617432</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3429565429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4094390869141</t>
+    <t xml:space="preserve">10.3429555892944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4094400405884</t>
   </si>
   <si>
     <t xml:space="preserve">10.2574768066406</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0295333862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9060640335083</t>
+    <t xml:space="preserve">10.0295324325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90606307983398</t>
   </si>
   <si>
     <t xml:space="preserve">9.89656543731689</t>
@@ -2798,10 +2798,10 @@
     <t xml:space="preserve">9.64962577819824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78259468078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4949188232422</t>
+    <t xml:space="preserve">9.78259372711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4949178695679</t>
   </si>
   <si>
     <t xml:space="preserve">12.346962928772</t>
@@ -2822,13 +2822,13 @@
     <t xml:space="preserve">13.6576404571533</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2872314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1542654037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8218460083008</t>
+    <t xml:space="preserve">13.2872304916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1542644500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8218469619751</t>
   </si>
   <si>
     <t xml:space="preserve">11.8815774917603</t>
@@ -2840,10 +2840,10 @@
     <t xml:space="preserve">12.062032699585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1190185546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2899770736694</t>
+    <t xml:space="preserve">12.1190195083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2899761199951</t>
   </si>
   <si>
     <t xml:space="preserve">12.3089714050293</t>
@@ -2855,16 +2855,16 @@
     <t xml:space="preserve">12.5749063491821</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5844039916992</t>
+    <t xml:space="preserve">12.5844049453735</t>
   </si>
   <si>
     <t xml:space="preserve">11.9955492019653</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8055973052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5111684799194</t>
+    <t xml:space="preserve">11.8055963516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5111694335938</t>
   </si>
   <si>
     <t xml:space="preserve">11.7296152114868</t>
@@ -2876,7 +2876,7 @@
     <t xml:space="preserve">11.5206661224365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7581071853638</t>
+    <t xml:space="preserve">11.7581081390381</t>
   </si>
   <si>
     <t xml:space="preserve">11.5871496200562</t>
@@ -2894,7 +2894,7 @@
     <t xml:space="preserve">11.1787509918213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2262382507324</t>
+    <t xml:space="preserve">11.2262372970581</t>
   </si>
   <si>
     <t xml:space="preserve">11.2452335357666</t>
@@ -2906,7 +2906,7 @@
     <t xml:space="preserve">11.1312627792358</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0267868041992</t>
+    <t xml:space="preserve">11.0267877578735</t>
   </si>
   <si>
     <t xml:space="preserve">11.0837736129761</t>
@@ -2915,7 +2915,7 @@
     <t xml:space="preserve">10.8368349075317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0552816390991</t>
+    <t xml:space="preserve">11.0552806854248</t>
   </si>
   <si>
     <t xml:space="preserve">11.2167415618896</t>
@@ -2933,13 +2933,13 @@
     <t xml:space="preserve">10.3619508743286</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6441354751587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.330714225769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0932722091675</t>
+    <t xml:space="preserve">11.644136428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3307132720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0932712554932</t>
   </si>
   <si>
     <t xml:space="preserve">10.9603033065796</t>
@@ -2948,7 +2948,7 @@
     <t xml:space="preserve">10.7608528137207</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7798490524292</t>
+    <t xml:space="preserve">10.7798500061035</t>
   </si>
   <si>
     <t xml:space="preserve">10.6753740310669</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">11.4636793136597</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3971967697144</t>
+    <t xml:space="preserve">11.3971977233887</t>
   </si>
   <si>
     <t xml:space="preserve">11.5016708374023</t>
@@ -2975,28 +2975,28 @@
     <t xml:space="preserve">11.4256896972656</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5179214477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5654096603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0810289382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6821260452271</t>
+    <t xml:space="preserve">12.5179204940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.565408706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0810279846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6821269989014</t>
   </si>
   <si>
     <t xml:space="preserve">11.6061458587646</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1095209121704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0145444869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9385633468628</t>
+    <t xml:space="preserve">12.1095218658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0145435333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9385623931885</t>
   </si>
   <si>
     <t xml:space="preserve">11.9575576782227</t>
@@ -3011,7 +3011,7 @@
     <t xml:space="preserve">12.2804794311523</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6793823242188</t>
+    <t xml:space="preserve">12.6793813705444</t>
   </si>
   <si>
     <t xml:space="preserve">12.6034002304077</t>
@@ -3023,7 +3023,7 @@
     <t xml:space="preserve">12.2044982910156</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4039497375488</t>
+    <t xml:space="preserve">12.4039487838745</t>
   </si>
   <si>
     <t xml:space="preserve">12.8978271484375</t>
@@ -3044,16 +3044,16 @@
     <t xml:space="preserve">10.6943693161011</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5139141082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7988433837891</t>
+    <t xml:space="preserve">10.5139131546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7988443374634</t>
   </si>
   <si>
     <t xml:space="preserve">11.0647783279419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.359206199646</t>
+    <t xml:space="preserve">11.3592052459717</t>
   </si>
   <si>
     <t xml:space="preserve">12.3659582138062</t>
@@ -3065,10 +3065,10 @@
     <t xml:space="preserve">13.3537158966064</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7811098098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7146272659302</t>
+    <t xml:space="preserve">13.7811107635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7146263122559</t>
   </si>
   <si>
     <t xml:space="preserve">13.9235744476318</t>
@@ -3077,10 +3077,10 @@
     <t xml:space="preserve">13.9330730438232</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2369985580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3414716720581</t>
+    <t xml:space="preserve">14.2369976043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3414726257324</t>
   </si>
   <si>
     <t xml:space="preserve">14.0470447540283</t>
@@ -3098,31 +3098,31 @@
     <t xml:space="preserve">14.2464952468872</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4269514083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4649419784546</t>
+    <t xml:space="preserve">14.4269504547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4649410247803</t>
   </si>
   <si>
     <t xml:space="preserve">14.9113321304321</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4934349060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3509702682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5979089736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7498712539673</t>
+    <t xml:space="preserve">14.4934358596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3509693145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5979080200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7498722076416</t>
   </si>
   <si>
     <t xml:space="preserve">15.1487741470337</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8828392028809</t>
+    <t xml:space="preserve">14.8828401565552</t>
   </si>
   <si>
     <t xml:space="preserve">14.8543462753296</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">14.7593698501587</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3794631958008</t>
+    <t xml:space="preserve">14.3794641494751</t>
   </si>
   <si>
     <t xml:space="preserve">14.5694160461426</t>
@@ -3146,16 +3146,16 @@
     <t xml:space="preserve">15.1107835769653</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0632953643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9493227005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7688674926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7118816375732</t>
+    <t xml:space="preserve">15.0632944107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9493217468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7688684463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7118806838989</t>
   </si>
   <si>
     <t xml:space="preserve">14.5884113311768</t>
@@ -3170,10 +3170,10 @@
     <t xml:space="preserve">14.5504207611084</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5314254760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9615659713745</t>
+    <t xml:space="preserve">14.5314264297485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9615650177002</t>
   </si>
   <si>
     <t xml:space="preserve">14.2085056304932</t>
@@ -3188,10 +3188,10 @@
     <t xml:space="preserve">14.6833877563477</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0537967681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8041124343872</t>
+    <t xml:space="preserve">15.0537977218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8041133880615</t>
   </si>
   <si>
     <t xml:space="preserve">15.6711454391479</t>
@@ -3221,7 +3221,7 @@
     <t xml:space="preserve">15.006308555603</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0822906494141</t>
+    <t xml:space="preserve">15.0822896957397</t>
   </si>
   <si>
     <t xml:space="preserve">14.9778165817261</t>
@@ -3230,7 +3230,7 @@
     <t xml:space="preserve">14.6928853988647</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7783641815186</t>
+    <t xml:space="preserve">14.7783651351929</t>
   </si>
   <si>
     <t xml:space="preserve">14.8258533477783</t>
@@ -3254,31 +3254,31 @@
     <t xml:space="preserve">14.9873132705688</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8705968856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0225582122803</t>
+    <t xml:space="preserve">15.8705959320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0225601196289</t>
   </si>
   <si>
     <t xml:space="preserve">16.0320568084717</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8231067657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9370803833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7376289367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4906883239746</t>
+    <t xml:space="preserve">15.8231077194214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9370794296265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7376279830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4906892776489</t>
   </si>
   <si>
     <t xml:space="preserve">15.7091360092163</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3102350234985</t>
+    <t xml:space="preserve">15.3102340698242</t>
   </si>
   <si>
     <t xml:space="preserve">15.3672199249268</t>
@@ -3287,10 +3287,10 @@
     <t xml:space="preserve">15.3387269973755</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6996383666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6853923797607</t>
+    <t xml:space="preserve">15.6996374130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6853914260864</t>
   </si>
   <si>
     <t xml:space="preserve">15.6189079284668</t>
@@ -3299,13 +3299,13 @@
     <t xml:space="preserve">15.428955078125</t>
   </si>
   <si>
-    <t xml:space="preserve">15.637903213501</t>
+    <t xml:space="preserve">15.6379022598267</t>
   </si>
   <si>
     <t xml:space="preserve">16.7396335601807</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8678531646729</t>
+    <t xml:space="preserve">16.8678512573242</t>
   </si>
   <si>
     <t xml:space="preserve">16.8725986480713</t>
@@ -3329,7 +3329,7 @@
     <t xml:space="preserve">17.2904968261719</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0815505981445</t>
+    <t xml:space="preserve">17.0815486907959</t>
   </si>
   <si>
     <t xml:space="preserve">17.0245628356934</t>
@@ -3344,28 +3344,28 @@
     <t xml:space="preserve">17.4614543914795</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4187164306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2117691040039</t>
+    <t xml:space="preserve">17.4187145233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2117710113525</t>
   </si>
   <si>
     <t xml:space="preserve">18.3589839935303</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1975231170654</t>
+    <t xml:space="preserve">18.1975250244141</t>
   </si>
   <si>
     <t xml:space="preserve">18.1500358581543</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2307662963867</t>
+    <t xml:space="preserve">18.2307643890381</t>
   </si>
   <si>
     <t xml:space="preserve">18.0360641479492</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9125957489014</t>
+    <t xml:space="preserve">17.9125938415527</t>
   </si>
   <si>
     <t xml:space="preserve">17.9553356170654</t>
@@ -3377,10 +3377,10 @@
     <t xml:space="preserve">18.0408134460449</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3304920196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3209934234619</t>
+    <t xml:space="preserve">18.3304901123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3209953308105</t>
   </si>
   <si>
     <t xml:space="preserve">18.368480682373</t>
@@ -3389,7 +3389,7 @@
     <t xml:space="preserve">18.3019981384277</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3542366027832</t>
+    <t xml:space="preserve">18.3542346954346</t>
   </si>
   <si>
     <t xml:space="preserve">18.3969745635986</t>
@@ -3401,10 +3401,10 @@
     <t xml:space="preserve">18.297248840332</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1690292358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.183277130127</t>
+    <t xml:space="preserve">18.1690311431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1832790374756</t>
   </si>
   <si>
     <t xml:space="preserve">18.4444637298584</t>
@@ -3416,7 +3416,7 @@
     <t xml:space="preserve">18.6961498260498</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5584373474121</t>
+    <t xml:space="preserve">18.5584354400635</t>
   </si>
   <si>
     <t xml:space="preserve">18.3352394104004</t>
@@ -3428,7 +3428,7 @@
     <t xml:space="preserve">17.1527805328369</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1812744140625</t>
+    <t xml:space="preserve">17.1812725067139</t>
   </si>
   <si>
     <t xml:space="preserve">17.0673007965088</t>
@@ -3443,7 +3443,7 @@
     <t xml:space="preserve">16.5021915435791</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7253856658936</t>
+    <t xml:space="preserve">16.7253875732422</t>
   </si>
   <si>
     <t xml:space="preserve">16.877347946167</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">16.4214611053467</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9798212051392</t>
+    <t xml:space="preserve">15.9798202514648</t>
   </si>
   <si>
     <t xml:space="preserve">16.0985412597656</t>
@@ -3464,7 +3464,7 @@
     <t xml:space="preserve">16.2505035400391</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4736976623535</t>
+    <t xml:space="preserve">16.4736957550049</t>
   </si>
   <si>
     <t xml:space="preserve">16.169771194458</t>
@@ -3476,19 +3476,19 @@
     <t xml:space="preserve">16.0368061065674</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9988136291504</t>
+    <t xml:space="preserve">15.9988145828247</t>
   </si>
   <si>
     <t xml:space="preserve">16.2600021362305</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0652980804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0510501861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1100387573242</t>
+    <t xml:space="preserve">16.065299987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0510520935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1100406646729</t>
   </si>
   <si>
     <t xml:space="preserve">17.3949718475342</t>
@@ -3503,7 +3503,7 @@
     <t xml:space="preserve">17.6609039306641</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0008163452148</t>
+    <t xml:space="preserve">17.0008182525635</t>
   </si>
   <si>
     <t xml:space="preserve">16.6731491088867</t>
@@ -3512,10 +3512,10 @@
     <t xml:space="preserve">16.5164375305176</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7328815460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7423791885376</t>
+    <t xml:space="preserve">15.7328805923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7423782348633</t>
   </si>
   <si>
     <t xml:space="preserve">16.1460285186768</t>
@@ -3524,13 +3524,13 @@
     <t xml:space="preserve">15.9275827407837</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9703226089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6541538238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7586269378662</t>
+    <t xml:space="preserve">15.9703216552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6541519165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7586288452148</t>
   </si>
   <si>
     <t xml:space="preserve">18.0123195648193</t>
@@ -3548,13 +3548,13 @@
     <t xml:space="preserve">16.8251113891602</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7206363677979</t>
+    <t xml:space="preserve">16.7206382751465</t>
   </si>
   <si>
     <t xml:space="preserve">16.9628295898438</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9438323974609</t>
+    <t xml:space="preserve">16.9438304901123</t>
   </si>
   <si>
     <t xml:space="preserve">16.8298587799072</t>
@@ -3563,7 +3563,7 @@
     <t xml:space="preserve">16.9913196563721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8346080780029</t>
+    <t xml:space="preserve">16.8346099853516</t>
   </si>
   <si>
     <t xml:space="preserve">17.0435581207275</t>
@@ -3575,19 +3575,19 @@
     <t xml:space="preserve">16.7111377716064</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2145156860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4424591064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3427352905273</t>
+    <t xml:space="preserve">17.2145175933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4424610137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3427333831787</t>
   </si>
   <si>
     <t xml:space="preserve">17.4662036895752</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7178916931152</t>
+    <t xml:space="preserve">17.7178936004639</t>
   </si>
   <si>
     <t xml:space="preserve">17.7748775482178</t>
@@ -3596,10 +3596,10 @@
     <t xml:space="preserve">17.6988964080811</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1405391693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7008991241455</t>
+    <t xml:space="preserve">18.1405372619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7009010314941</t>
   </si>
   <si>
     <t xml:space="preserve">18.7911281585693</t>
@@ -3614,10 +3614,10 @@
     <t xml:space="preserve">18.4302177429199</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5536880493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7626323699951</t>
+    <t xml:space="preserve">18.5536861419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7626342773438</t>
   </si>
   <si>
     <t xml:space="preserve">19.0903053283691</t>
@@ -3638,13 +3638,13 @@
     <t xml:space="preserve">20.5529441833496</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6221733093262</t>
+    <t xml:space="preserve">19.6221752166748</t>
   </si>
   <si>
     <t xml:space="preserve">19.1377925872803</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6316699981689</t>
+    <t xml:space="preserve">19.6316719055176</t>
   </si>
   <si>
     <t xml:space="preserve">20.4579677581787</t>
@@ -3653,40 +3653,40 @@
     <t xml:space="preserve">20.6289253234863</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0373249053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4457225799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9898376464844</t>
+    <t xml:space="preserve">21.0373229980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4457244873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9898357391357</t>
   </si>
   <si>
     <t xml:space="preserve">20.7523956298828</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6384239196777</t>
+    <t xml:space="preserve">20.6384220123291</t>
   </si>
   <si>
     <t xml:space="preserve">20.1635398864746</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0970554351807</t>
+    <t xml:space="preserve">20.0970573425293</t>
   </si>
   <si>
     <t xml:space="preserve">20.7903861999512</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7144050598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0278282165527</t>
+    <t xml:space="preserve">20.7144031524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0278263092041</t>
   </si>
   <si>
     <t xml:space="preserve">21.0183296203613</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0943088531494</t>
+    <t xml:space="preserve">21.094310760498</t>
   </si>
   <si>
     <t xml:space="preserve">21.4172306060791</t>
@@ -3704,7 +3704,7 @@
     <t xml:space="preserve">22.0820693969727</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5976867675781</t>
+    <t xml:space="preserve">21.5976886749268</t>
   </si>
   <si>
     <t xml:space="preserve">21.6261806488037</t>
@@ -3713,10 +3713,10 @@
     <t xml:space="preserve">19.4797096252441</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0998020172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5366954803467</t>
+    <t xml:space="preserve">19.0998001098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.536693572998</t>
   </si>
   <si>
     <t xml:space="preserve">19.2517642974854</t>
@@ -3728,7 +3728,7 @@
     <t xml:space="preserve">18.0550594329834</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4946956634521</t>
+    <t xml:space="preserve">17.4946975708008</t>
   </si>
   <si>
     <t xml:space="preserve">18.2212677001953</t>
@@ -3758,13 +3758,13 @@
     <t xml:space="preserve">18.1452865600586</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5679340362549</t>
+    <t xml:space="preserve">18.5679321289062</t>
   </si>
   <si>
     <t xml:space="preserve">18.68190574646</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7721328735352</t>
+    <t xml:space="preserve">18.7721309661865</t>
   </si>
   <si>
     <t xml:space="preserve">18.8006267547607</t>
@@ -3806,10 +3806,10 @@
     <t xml:space="preserve">15.9133348464966</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3529739379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4574480056763</t>
+    <t xml:space="preserve">15.3529748916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4574489593506</t>
   </si>
   <si>
     <t xml:space="preserve">14.8733415603638</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">15.2532472610474</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5191812515259</t>
+    <t xml:space="preserve">15.5191822052002</t>
   </si>
   <si>
     <t xml:space="preserve">15.8278579711914</t>
@@ -3854,7 +3854,7 @@
     <t xml:space="preserve">15.6521492004395</t>
   </si>
   <si>
-    <t xml:space="preserve">15.889591217041</t>
+    <t xml:space="preserve">15.8895902633667</t>
   </si>
   <si>
     <t xml:space="preserve">15.5096855163574</t>
@@ -3866,10 +3866,10 @@
     <t xml:space="preserve">14.8638439178467</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1392765045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7851181030273</t>
+    <t xml:space="preserve">15.1392755508423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7851190567017</t>
   </si>
   <si>
     <t xml:space="preserve">14.3034820556641</t>
@@ -3878,7 +3878,7 @@
     <t xml:space="preserve">14.3224773406982</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8285999298096</t>
+    <t xml:space="preserve">13.8285989761353</t>
   </si>
   <si>
     <t xml:space="preserve">12.8123483657837</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">14.1990070343018</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0158061981201</t>
+    <t xml:space="preserve">15.0158071517944</t>
   </si>
   <si>
     <t xml:space="preserve">14.5219278335571</t>
@@ -73214,7 +73214,7 @@
     </row>
     <row r="2569">
       <c r="A2569" s="1" t="n">
-        <v>46063.6922685185</v>
+        <v>46063.3333333333</v>
       </c>
       <c r="B2569" t="n">
         <v>523435</v>
@@ -73235,6 +73235,32 @@
         <v>2031</v>
       </c>
       <c r="H2569" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2570">
+      <c r="A2570" s="1" t="n">
+        <v>46064.6912962963</v>
+      </c>
+      <c r="B2570" t="n">
+        <v>180662</v>
+      </c>
+      <c r="C2570" t="n">
+        <v>6.92999982833862</v>
+      </c>
+      <c r="D2570" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="E2570" t="n">
+        <v>6.92000007629395</v>
+      </c>
+      <c r="F2570" t="n">
+        <v>6.82000017166138</v>
+      </c>
+      <c r="G2570" t="s">
+        <v>1816</v>
+      </c>
+      <c r="H2570" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2763519287109</t>
+    <t xml:space="preserve">18.2763500213623</t>
   </si>
   <si>
     <t xml:space="preserve">SFER.MI</t>
@@ -50,55 +50,55 @@
     <t xml:space="preserve">17.4978828430176</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9401950836182</t>
+    <t xml:space="preserve">17.9401931762695</t>
   </si>
   <si>
     <t xml:space="preserve">17.683650970459</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2498111724854</t>
+    <t xml:space="preserve">18.249813079834</t>
   </si>
   <si>
     <t xml:space="preserve">19.4086723327637</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1344356536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.84250831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4621238708496</t>
+    <t xml:space="preserve">19.1344375610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8425121307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4621257781982</t>
   </si>
   <si>
     <t xml:space="preserve">18.2851963043213</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0994243621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6394214630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5686531066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1878871917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4798145294189</t>
+    <t xml:space="preserve">18.0994281768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6394233703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5686492919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1878910064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4798164367676</t>
   </si>
   <si>
     <t xml:space="preserve">18.2232761383057</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7632694244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3913536071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6744327545166</t>
+    <t xml:space="preserve">17.7632675170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3913516998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6744346618652</t>
   </si>
   <si>
     <t xml:space="preserve">17.9578857421875</t>
@@ -107,37 +107,37 @@
     <t xml:space="preserve">18.2055816650391</t>
   </si>
   <si>
-    <t xml:space="preserve">18.258659362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0817337036133</t>
+    <t xml:space="preserve">18.2586574554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0817356109619</t>
   </si>
   <si>
     <t xml:space="preserve">17.3563423156738</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9051837921143</t>
+    <t xml:space="preserve">16.9051818847656</t>
   </si>
   <si>
     <t xml:space="preserve">17.1617221832275</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6486396789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0201835632324</t>
+    <t xml:space="preserve">16.6486415863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0201816558838</t>
   </si>
   <si>
     <t xml:space="preserve">17.4890365600586</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6305751800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4090461730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.453275680542</t>
+    <t xml:space="preserve">17.6305732727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4090442657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4532775878906</t>
   </si>
   <si>
     <t xml:space="preserve">18.9752063751221</t>
@@ -146,10 +146,10 @@
     <t xml:space="preserve">18.1348133087158</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3121070861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9048080444336</t>
+    <t xml:space="preserve">17.3121109008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9048099517822</t>
   </si>
   <si>
     <t xml:space="preserve">18.3471202850342</t>
@@ -158,10 +158,10 @@
     <t xml:space="preserve">19.0194358825684</t>
   </si>
   <si>
-    <t xml:space="preserve">19.001745223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8513565063477</t>
+    <t xml:space="preserve">19.0017433166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8513584136963</t>
   </si>
   <si>
     <t xml:space="preserve">19.3113632202148</t>
@@ -176,10 +176,10 @@
     <t xml:space="preserve">19.7271366119385</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3379001617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.647518157959</t>
+    <t xml:space="preserve">19.3379039764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6475200653076</t>
   </si>
   <si>
     <t xml:space="preserve">19.9836750030518</t>
@@ -188,40 +188,40 @@
     <t xml:space="preserve">19.1167449951172</t>
   </si>
   <si>
-    <t xml:space="preserve">19.444055557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0367546081543</t>
+    <t xml:space="preserve">19.4440574645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0367565155029</t>
   </si>
   <si>
     <t xml:space="preserve">20.178295135498</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4971332550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4705944061279</t>
+    <t xml:space="preserve">19.4971351623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4705963134766</t>
   </si>
   <si>
     <t xml:space="preserve">18.9663600921631</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4794445037842</t>
+    <t xml:space="preserve">19.4794406890869</t>
   </si>
   <si>
     <t xml:space="preserve">19.9129066467285</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8686752319336</t>
+    <t xml:space="preserve">19.868673324585</t>
   </si>
   <si>
     <t xml:space="preserve">19.417516708374</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8690528869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8336658477783</t>
+    <t xml:space="preserve">18.8690490722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8336639404297</t>
   </si>
   <si>
     <t xml:space="preserve">18.5151996612549</t>
@@ -233,13 +233,13 @@
     <t xml:space="preserve">18.8955879211426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5240459442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9486656188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.798282623291</t>
+    <t xml:space="preserve">18.5240440368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9486675262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7982788085938</t>
   </si>
   <si>
     <t xml:space="preserve">18.8778972625732</t>
@@ -248,13 +248,13 @@
     <t xml:space="preserve">19.2936687469482</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8071250915527</t>
+    <t xml:space="preserve">18.80712890625</t>
   </si>
   <si>
     <t xml:space="preserve">18.3205814361572</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3648109436035</t>
+    <t xml:space="preserve">18.3648166656494</t>
   </si>
   <si>
     <t xml:space="preserve">17.8251914978027</t>
@@ -263,37 +263,37 @@
     <t xml:space="preserve">18.0640411376953</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3117389678955</t>
+    <t xml:space="preserve">18.3117370605469</t>
   </si>
   <si>
     <t xml:space="preserve">17.878267288208</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0021171569824</t>
+    <t xml:space="preserve">18.0021190643311</t>
   </si>
   <si>
     <t xml:space="preserve">17.7190380096436</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4448051452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1440315246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5509567260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9844284057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4182662963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9313507080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7367286682129</t>
+    <t xml:space="preserve">17.4448070526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1440296173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5509586334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9844264984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4182682037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9313488006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7367305755615</t>
   </si>
   <si>
     <t xml:space="preserve">17.6482677459717</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">17.5939388275146</t>
   </si>
   <si>
-    <t xml:space="preserve">17.81125831604</t>
+    <t xml:space="preserve">17.8112602233887</t>
   </si>
   <si>
     <t xml:space="preserve">17.7025966644287</t>
@@ -311,28 +311,28 @@
     <t xml:space="preserve">17.530553817749</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4128379821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3041763305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4762191772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4309463500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4852752685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7478733062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6844902038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.150239944458</t>
+    <t xml:space="preserve">17.4128360748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3041744232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4762210845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.430944442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4852771759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7478713989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6844882965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1502418518066</t>
   </si>
   <si>
     <t xml:space="preserve">16.7155990600586</t>
@@ -347,16 +347,16 @@
     <t xml:space="preserve">17.0778007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8384265899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9380264282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7297611236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8655891418457</t>
+    <t xml:space="preserve">17.8384246826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9380283355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7297630310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8655872344971</t>
   </si>
   <si>
     <t xml:space="preserve">18.1825141906738</t>
@@ -371,7 +371,7 @@
     <t xml:space="preserve">16.6793785095215</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2628440856934</t>
+    <t xml:space="preserve">16.2628479003906</t>
   </si>
   <si>
     <t xml:space="preserve">16.5254421234131</t>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">16.6069374084473</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8061504364014</t>
+    <t xml:space="preserve">16.8061466217041</t>
   </si>
   <si>
     <t xml:space="preserve">16.8242568969727</t>
@@ -392,7 +392,7 @@
     <t xml:space="preserve">15.8734798431396</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3624496459961</t>
+    <t xml:space="preserve">16.3624534606934</t>
   </si>
   <si>
     <t xml:space="preserve">16.4439487457275</t>
@@ -404,10 +404,10 @@
     <t xml:space="preserve">17.0959091186523</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1321296691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0868549346924</t>
+    <t xml:space="preserve">17.1321315765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.086856842041</t>
   </si>
   <si>
     <t xml:space="preserve">17.0325260162354</t>
@@ -419,58 +419,58 @@
     <t xml:space="preserve">17.9018096923828</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1372413635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9289722442627</t>
+    <t xml:space="preserve">18.1372394561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9289703369141</t>
   </si>
   <si>
     <t xml:space="preserve">18.7710914611816</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6352653503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0699062347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2147884368896</t>
+    <t xml:space="preserve">18.6352672576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0699081420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2147903442383</t>
   </si>
   <si>
     <t xml:space="preserve">18.6262111663818</t>
   </si>
   <si>
-    <t xml:space="preserve">18.499439239502</t>
+    <t xml:space="preserve">18.4994411468506</t>
   </si>
   <si>
     <t xml:space="preserve">18.2187347412109</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7167625427246</t>
+    <t xml:space="preserve">18.716760635376</t>
   </si>
   <si>
     <t xml:space="preserve">18.5809364318848</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7620372772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.807315826416</t>
+    <t xml:space="preserve">18.762035369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8073101043701</t>
   </si>
   <si>
     <t xml:space="preserve">18.9431381225586</t>
   </si>
   <si>
-    <t xml:space="preserve">19.04274559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6624298095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4722785949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6171550750732</t>
+    <t xml:space="preserve">19.0427417755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6624336242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4722766876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6171588897705</t>
   </si>
   <si>
     <t xml:space="preserve">18.7529811859131</t>
@@ -479,43 +479,43 @@
     <t xml:space="preserve">18.9703044891357</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6805400848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6080989837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6533756256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5175514221191</t>
+    <t xml:space="preserve">18.6805419921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6081008911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6533794403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5175533294678</t>
   </si>
   <si>
     <t xml:space="preserve">18.8706970214844</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6986541748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1061267852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9210834503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6947078704834</t>
+    <t xml:space="preserve">18.6986522674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.106128692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9210815429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6947059631348</t>
   </si>
   <si>
     <t xml:space="preserve">19.5588798522949</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4592761993408</t>
+    <t xml:space="preserve">19.4592723846436</t>
   </si>
   <si>
     <t xml:space="preserve">19.3143939971924</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8888072967529</t>
+    <t xml:space="preserve">18.8888092041016</t>
   </si>
   <si>
     <t xml:space="preserve">19.1332931518555</t>
@@ -524,61 +524,61 @@
     <t xml:space="preserve">19.160457611084</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9391937255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4553279876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3557224273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3104496002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3919429779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4643840789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6907577514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8446941375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7994213104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4009990692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1021862030029</t>
+    <t xml:space="preserve">19.9391918182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4553260803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3557205200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3104476928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3919448852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4643859863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6907596588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8446979522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7994194030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4009971618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1021823883057</t>
   </si>
   <si>
     <t xml:space="preserve">20.5277709960938</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3647785186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5458812713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7541484832764</t>
+    <t xml:space="preserve">20.3647766113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5458793640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7541446685791</t>
   </si>
   <si>
     <t xml:space="preserve">20.4191074371338</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0116310119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.265172958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3285617828369</t>
+    <t xml:space="preserve">20.0116329193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2651710510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3285598754883</t>
   </si>
   <si>
     <t xml:space="preserve">20.0387954711914</t>
@@ -587,19 +587,19 @@
     <t xml:space="preserve">20.1474590301514</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2289524078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5006046295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5639896392822</t>
+    <t xml:space="preserve">20.2289543151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.500602722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5639877319336</t>
   </si>
   <si>
     <t xml:space="preserve">20.1836795806885</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5498237609863</t>
+    <t xml:space="preserve">19.549825668335</t>
   </si>
   <si>
     <t xml:space="preserve">19.4140014648438</t>
@@ -608,19 +608,19 @@
     <t xml:space="preserve">19.5045509338379</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7218704223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7943115234375</t>
+    <t xml:space="preserve">19.7218723297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7943134307861</t>
   </si>
   <si>
     <t xml:space="preserve">19.5226593017578</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8305282592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9120273590088</t>
+    <t xml:space="preserve">19.830530166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9120292663574</t>
   </si>
   <si>
     <t xml:space="preserve">19.7490348815918</t>
@@ -629,31 +629,31 @@
     <t xml:space="preserve">18.0919647216797</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3002300262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3273944854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2459030151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0104713439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7388172149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8565330505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8203144073486</t>
+    <t xml:space="preserve">18.3002281188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3273963928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2458992004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0104675292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7388210296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8565368652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8203163146973</t>
   </si>
   <si>
     <t xml:space="preserve">17.6392135620117</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3455028533936</t>
+    <t xml:space="preserve">18.3455047607422</t>
   </si>
   <si>
     <t xml:space="preserve">18.3907794952393</t>
@@ -665,22 +665,22 @@
     <t xml:space="preserve">19.2872295379639</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3958892822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3777809143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1151847839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5860443115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2600631713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3738346099854</t>
+    <t xml:space="preserve">19.3958911895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.377779006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1151866912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5860462188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2600650787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.373836517334</t>
   </si>
   <si>
     <t xml:space="preserve">20.3466682434082</t>
@@ -692,31 +692,31 @@
     <t xml:space="preserve">20.1293468475342</t>
   </si>
   <si>
-    <t xml:space="preserve">20.15651512146</t>
+    <t xml:space="preserve">20.1565132141113</t>
   </si>
   <si>
     <t xml:space="preserve">20.8084754943848</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6183185577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4785499572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5328788757324</t>
+    <t xml:space="preserve">20.6183204650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4785461425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5328807830811</t>
   </si>
   <si>
     <t xml:space="preserve">22.0671253204346</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0580711364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2572803497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2934989929199</t>
+    <t xml:space="preserve">22.0580730438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2572822570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2935047149658</t>
   </si>
   <si>
     <t xml:space="preserve">22.3025550842285</t>
@@ -728,43 +728,43 @@
     <t xml:space="preserve">22.2753925323486</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2391700744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8186931610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0722370147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8911361694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1537303924561</t>
+    <t xml:space="preserve">22.2391719818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8186950683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0722351074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.891134262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1537284851074</t>
   </si>
   <si>
     <t xml:space="preserve">23.099401473999</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5923194885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3568859100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9092445373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1757888793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1395645141602</t>
+    <t xml:space="preserve">22.5923175811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3568878173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9092426300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1757869720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1395683288574</t>
   </si>
   <si>
     <t xml:space="preserve">23.606481552124</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7513618469238</t>
+    <t xml:space="preserve">23.7513637542725</t>
   </si>
   <si>
     <t xml:space="preserve">24.1226196289062</t>
@@ -776,73 +776,73 @@
     <t xml:space="preserve">23.6879768371582</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5612087249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7423095703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7241992950439</t>
+    <t xml:space="preserve">23.561206817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7423076629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7242012023926</t>
   </si>
   <si>
     <t xml:space="preserve">23.6336498260498</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8238010406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6970310211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0139617919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2856121063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0682888031006</t>
+    <t xml:space="preserve">23.823802947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6970329284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0139598846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.285608291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.068286895752</t>
   </si>
   <si>
     <t xml:space="preserve">23.9777393341064</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2946662902832</t>
+    <t xml:space="preserve">24.2946643829346</t>
   </si>
   <si>
     <t xml:space="preserve">24.4304904937744</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6115913391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7655258178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1911144256592</t>
+    <t xml:space="preserve">24.61159324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7655277252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1911125183105</t>
   </si>
   <si>
     <t xml:space="preserve">25.3903255462646</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4265460968018</t>
+    <t xml:space="preserve">25.4265441894531</t>
   </si>
   <si>
     <t xml:space="preserve">25.6167011260986</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6710319519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6529216766357</t>
+    <t xml:space="preserve">25.6710300445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6529197692871</t>
   </si>
   <si>
     <t xml:space="preserve">25.7615795135498</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5352058410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9556827545166</t>
+    <t xml:space="preserve">25.5352077484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.955680847168</t>
   </si>
   <si>
     <t xml:space="preserve">24.9013538360596</t>
@@ -857,10 +857,10 @@
     <t xml:space="preserve">24.6206474304199</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9375743865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3722133636475</t>
+    <t xml:space="preserve">24.937572479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3722152709961</t>
   </si>
   <si>
     <t xml:space="preserve">25.62575340271</t>
@@ -869,13 +869,13 @@
     <t xml:space="preserve">25.2273349761963</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1730041503906</t>
+    <t xml:space="preserve">25.173002243042</t>
   </si>
   <si>
     <t xml:space="preserve">25.1639499664307</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3993797302246</t>
+    <t xml:space="preserve">25.3993816375732</t>
   </si>
   <si>
     <t xml:space="preserve">25.7253608703613</t>
@@ -884,19 +884,19 @@
     <t xml:space="preserve">25.2907180786133</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1277294158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7434711456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5442581176758</t>
+    <t xml:space="preserve">25.1277275085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7434692382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5442600250244</t>
   </si>
   <si>
     <t xml:space="preserve">25.4808731079102</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5080394744873</t>
+    <t xml:space="preserve">25.5080413818359</t>
   </si>
   <si>
     <t xml:space="preserve">25.2635536193848</t>
@@ -905,13 +905,13 @@
     <t xml:space="preserve">25.0824546813965</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7836399078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4214344024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2674980163574</t>
+    <t xml:space="preserve">24.7836360931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4214363098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2674961090088</t>
   </si>
   <si>
     <t xml:space="preserve">25.5261497497559</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">26.1237831115723</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1871662139893</t>
+    <t xml:space="preserve">26.1871700286865</t>
   </si>
   <si>
     <t xml:space="preserve">26.6308650970459</t>
@@ -929,22 +929,22 @@
     <t xml:space="preserve">26.4859828948975</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3229923248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6761379241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.893461227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2596111297607</t>
+    <t xml:space="preserve">26.3229904174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.676139831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8934650421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2596073150635</t>
   </si>
   <si>
     <t xml:space="preserve">26.667085647583</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9115695953369</t>
+    <t xml:space="preserve">26.9115715026855</t>
   </si>
   <si>
     <t xml:space="preserve">26.6036987304688</t>
@@ -965,13 +965,13 @@
     <t xml:space="preserve">25.8984432220459</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0641078948975</t>
+    <t xml:space="preserve">26.0641059875488</t>
   </si>
   <si>
     <t xml:space="preserve">24.71120262146</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6159934997559</t>
+    <t xml:space="preserve">23.6159954071045</t>
   </si>
   <si>
     <t xml:space="preserve">23.2202472686768</t>
@@ -983,7 +983,7 @@
     <t xml:space="preserve">22.9625511169434</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8705177307129</t>
+    <t xml:space="preserve">22.8705158233643</t>
   </si>
   <si>
     <t xml:space="preserve">22.8613147735596</t>
@@ -998,28 +998,28 @@
     <t xml:space="preserve">23.0453834533691</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8889217376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.088228225708</t>
+    <t xml:space="preserve">22.8889255523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0882263183594</t>
   </si>
   <si>
     <t xml:space="preserve">22.3183116912842</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2262763977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3827342987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3643264770508</t>
+    <t xml:space="preserve">22.2262744903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3827362060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3643283843994</t>
   </si>
   <si>
     <t xml:space="preserve">22.7416687011719</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9533462524414</t>
+    <t xml:space="preserve">22.95334815979</t>
   </si>
   <si>
     <t xml:space="preserve">22.8797206878662</t>
@@ -1031,31 +1031,31 @@
     <t xml:space="preserve">23.4871463775635</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4319267272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.806095123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0269756317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6036167144775</t>
+    <t xml:space="preserve">23.4319248199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8060932159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0269737243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6036186218262</t>
   </si>
   <si>
     <t xml:space="preserve">22.2538871765137</t>
   </si>
   <si>
-    <t xml:space="preserve">21.545223236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4900035858154</t>
+    <t xml:space="preserve">21.5452213287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4900016784668</t>
   </si>
   <si>
     <t xml:space="preserve">21.7200889587402</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5544261932373</t>
+    <t xml:space="preserve">21.5544281005859</t>
   </si>
   <si>
     <t xml:space="preserve">21.6740703582764</t>
@@ -1076,7 +1076,7 @@
     <t xml:space="preserve">21.4163761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5084095001221</t>
+    <t xml:space="preserve">21.5084114074707</t>
   </si>
   <si>
     <t xml:space="preserve">21.9133625030518</t>
@@ -1094,52 +1094,52 @@
     <t xml:space="preserve">22.3735313415527</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2170715332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4103469848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5299892425537</t>
+    <t xml:space="preserve">22.2170734405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4103450775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5299911499023</t>
   </si>
   <si>
     <t xml:space="preserve">22.6312274932861</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6404323577881</t>
+    <t xml:space="preserve">22.6404342651367</t>
   </si>
   <si>
     <t xml:space="preserve">22.5576000213623</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4255809783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6556644439697</t>
+    <t xml:space="preserve">21.4255771636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6556663513184</t>
   </si>
   <si>
     <t xml:space="preserve">22.2630920410156</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5391941070557</t>
+    <t xml:space="preserve">22.539192199707</t>
   </si>
   <si>
     <t xml:space="preserve">22.3551254272461</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0514125823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7876853942871</t>
+    <t xml:space="preserve">22.0514106750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7876873016357</t>
   </si>
   <si>
     <t xml:space="preserve">22.3367176055908</t>
   </si>
   <si>
-    <t xml:space="preserve">22.115837097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7661037445068</t>
+    <t xml:space="preserve">22.1158332824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7661056518555</t>
   </si>
   <si>
     <t xml:space="preserve">22.0606155395508</t>
@@ -1148,43 +1148,43 @@
     <t xml:space="preserve">21.7569007873535</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9961891174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.701681137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.005392074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8765487670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1250419616699</t>
+    <t xml:space="preserve">21.9961910247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7016830444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0053939819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8765468597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1250400543213</t>
   </si>
   <si>
     <t xml:space="preserve">21.7753086090088</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0238018035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9041557312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6832752227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.827356338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0574417114258</t>
+    <t xml:space="preserve">22.0238037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9041576385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6832733154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8273544311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0574398040771</t>
   </si>
   <si>
     <t xml:space="preserve">20.94700050354</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7997455596924</t>
+    <t xml:space="preserve">20.799747467041</t>
   </si>
   <si>
     <t xml:space="preserve">21.1034603118896</t>
@@ -1202,25 +1202,25 @@
     <t xml:space="preserve">22.0974292755127</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8581409454346</t>
+    <t xml:space="preserve">21.8581390380859</t>
   </si>
   <si>
     <t xml:space="preserve">21.6372566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2967281341553</t>
+    <t xml:space="preserve">21.2967319488525</t>
   </si>
   <si>
     <t xml:space="preserve">20.9746112823486</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9838123321533</t>
+    <t xml:space="preserve">20.9838161468506</t>
   </si>
   <si>
     <t xml:space="preserve">21.1402721405029</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0666446685791</t>
+    <t xml:space="preserve">21.0666427612305</t>
   </si>
   <si>
     <t xml:space="preserve">20.7077121734619</t>
@@ -1244,19 +1244,19 @@
     <t xml:space="preserve">20.4500141143799</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3855895996094</t>
+    <t xml:space="preserve">20.385591506958</t>
   </si>
   <si>
     <t xml:space="preserve">20.3947944641113</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0082511901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9714393615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0634708404541</t>
+    <t xml:space="preserve">20.0082492828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9714374542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0634727478027</t>
   </si>
   <si>
     <t xml:space="preserve">20.4868297576904</t>
@@ -1268,85 +1268,85 @@
     <t xml:space="preserve">20.8917827606201</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2415084838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9285945892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2475395202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1647109985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0910816192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2719783782959</t>
+    <t xml:space="preserve">21.2415103912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9285926818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2475414276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1647090911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0910835266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2719764709473</t>
   </si>
   <si>
     <t xml:space="preserve">19.695333480835</t>
   </si>
   <si>
-    <t xml:space="preserve">19.805778503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7321491241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1831169128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0450630187988</t>
+    <t xml:space="preserve">19.8057765960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7321510314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1831188201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0450649261475</t>
   </si>
   <si>
     <t xml:space="preserve">20.2935581207275</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4316101074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5696582794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6616973876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.131067276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0482387542725</t>
+    <t xml:space="preserve">20.4316120147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5696601867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6616954803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1310691833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0482406616211</t>
   </si>
   <si>
     <t xml:space="preserve">21.1954936981201</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4531898498535</t>
+    <t xml:space="preserve">21.4531879425049</t>
   </si>
   <si>
     <t xml:space="preserve">20.8089485168457</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6708965301514</t>
+    <t xml:space="preserve">20.6708984375</t>
   </si>
   <si>
     <t xml:space="preserve">20.7721347808838</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4652500152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7965717315674</t>
+    <t xml:space="preserve">19.4652462005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7965698242188</t>
   </si>
   <si>
     <t xml:space="preserve">19.8609962463379</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0174560546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2199268341064</t>
+    <t xml:space="preserve">20.0174541473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2199287414551</t>
   </si>
   <si>
     <t xml:space="preserve">20.229133605957</t>
@@ -1355,16 +1355,16 @@
     <t xml:space="preserve">20.5236434936523</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6524925231934</t>
+    <t xml:space="preserve">20.6524906158447</t>
   </si>
   <si>
     <t xml:space="preserve">20.9101867675781</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2659492492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4684219360352</t>
+    <t xml:space="preserve">20.2659454345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4684238433838</t>
   </si>
   <si>
     <t xml:space="preserve">20.1555042266846</t>
@@ -1382,49 +1382,49 @@
     <t xml:space="preserve">21.5176124572754</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8549652099609</t>
+    <t xml:space="preserve">20.8549671173096</t>
   </si>
   <si>
     <t xml:space="preserve">20.9193897247314</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5052375793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3487777709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0266590118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7229442596436</t>
+    <t xml:space="preserve">20.5052356719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3487796783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0266571044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7229461669922</t>
   </si>
   <si>
     <t xml:space="preserve">19.9162158966064</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5604572296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7169170379639</t>
+    <t xml:space="preserve">20.5604553222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7169151306152</t>
   </si>
   <si>
     <t xml:space="preserve">20.9377975463867</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8365592956543</t>
+    <t xml:space="preserve">20.8365573883057</t>
   </si>
   <si>
     <t xml:space="preserve">21.6004447937012</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6248798370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2751502990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1094875335693</t>
+    <t xml:space="preserve">20.6248779296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2751522064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.109489440918</t>
   </si>
   <si>
     <t xml:space="preserve">19.6493167877197</t>
@@ -1433,19 +1433,19 @@
     <t xml:space="preserve">19.9990482330322</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1278972625732</t>
+    <t xml:space="preserve">20.1278953552246</t>
   </si>
   <si>
     <t xml:space="preserve">20.3303718566895</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8733749389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3763885498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5328464508057</t>
+    <t xml:space="preserve">20.8733730316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3763866424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5328483581543</t>
   </si>
   <si>
     <t xml:space="preserve">20.3027610778809</t>
@@ -1454,16 +1454,16 @@
     <t xml:space="preserve">20.6432876586914</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6156749725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7261199951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2783241271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3151378631592</t>
+    <t xml:space="preserve">20.6156768798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7261180877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2783260345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3151359558105</t>
   </si>
   <si>
     <t xml:space="preserve">21.536018371582</t>
@@ -1484,28 +1484,28 @@
     <t xml:space="preserve">22.2078685760498</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5668029785156</t>
+    <t xml:space="preserve">22.5668048858643</t>
   </si>
   <si>
     <t xml:space="preserve">22.6128215789795</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9165325164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6864490509033</t>
+    <t xml:space="preserve">22.9165306091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6864471435547</t>
   </si>
   <si>
     <t xml:space="preserve">22.7324657440186</t>
   </si>
   <si>
-    <t xml:space="preserve">22.833703994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7692813873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9073295593262</t>
+    <t xml:space="preserve">22.8337059020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7692794799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9073276519775</t>
   </si>
   <si>
     <t xml:space="preserve">23.2754688262939</t>
@@ -1514,10 +1514,10 @@
     <t xml:space="preserve">22.991304397583</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3090686798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4118766784668</t>
+    <t xml:space="preserve">23.3090705871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4118728637695</t>
   </si>
   <si>
     <t xml:space="preserve">22.9071884155273</t>
@@ -1535,46 +1535,46 @@
     <t xml:space="preserve">22.6174621582031</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0754165649414</t>
+    <t xml:space="preserve">23.07541847229</t>
   </si>
   <si>
     <t xml:space="preserve">23.3557987213135</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1969146728516</t>
+    <t xml:space="preserve">23.1969184875488</t>
   </si>
   <si>
     <t xml:space="preserve">23.206262588501</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4586067199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6548442840576</t>
+    <t xml:space="preserve">23.4586048126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6548461914062</t>
   </si>
   <si>
     <t xml:space="preserve">22.7389583587646</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1595344543457</t>
+    <t xml:space="preserve">23.1595325469971</t>
   </si>
   <si>
     <t xml:space="preserve">23.5053367614746</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3838386535645</t>
+    <t xml:space="preserve">23.3838367462158</t>
   </si>
   <si>
     <t xml:space="preserve">23.3931846618652</t>
   </si>
   <si>
-    <t xml:space="preserve">23.262336730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9258823394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.991247177124</t>
+    <t xml:space="preserve">23.2623386383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9258804321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9912452697754</t>
   </si>
   <si>
     <t xml:space="preserve">20.3370227813721</t>
@@ -1586,25 +1586,25 @@
     <t xml:space="preserve">19.7388744354248</t>
   </si>
   <si>
-    <t xml:space="preserve">19.56130027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3089580535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5332622528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4958763122559</t>
+    <t xml:space="preserve">19.5612983703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3089561462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.533260345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4958782196045</t>
   </si>
   <si>
     <t xml:space="preserve">19.346342086792</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0285739898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6266956329346</t>
+    <t xml:space="preserve">19.0285758972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6266937255859</t>
   </si>
   <si>
     <t xml:space="preserve">18.3836975097656</t>
@@ -1613,13 +1613,13 @@
     <t xml:space="preserve">18.0752754211426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6220188140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.079948425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6033306121826</t>
+    <t xml:space="preserve">18.6220207214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0799503326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.603328704834</t>
   </si>
   <si>
     <t xml:space="preserve">18.6360397338867</t>
@@ -1628,31 +1628,31 @@
     <t xml:space="preserve">18.794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7762317657471</t>
+    <t xml:space="preserve">18.7762298583984</t>
   </si>
   <si>
     <t xml:space="preserve">18.7201557159424</t>
   </si>
   <si>
-    <t xml:space="preserve">18.575288772583</t>
+    <t xml:space="preserve">18.5752906799316</t>
   </si>
   <si>
     <t xml:space="preserve">18.3930435180664</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5285606384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4958515167236</t>
+    <t xml:space="preserve">18.5285625457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.495849609375</t>
   </si>
   <si>
     <t xml:space="preserve">18.4351005554199</t>
   </si>
   <si>
-    <t xml:space="preserve">18.388370513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.491174697876</t>
+    <t xml:space="preserve">18.3883686065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4911766052246</t>
   </si>
   <si>
     <t xml:space="preserve">18.2435073852539</t>
@@ -1664,34 +1664,34 @@
     <t xml:space="preserve">17.7715282440186</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1079864501953</t>
+    <t xml:space="preserve">18.1079883575439</t>
   </si>
   <si>
     <t xml:space="preserve">18.6734237670898</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7575359344482</t>
+    <t xml:space="preserve">18.7575397491455</t>
   </si>
   <si>
     <t xml:space="preserve">18.7295017242432</t>
   </si>
   <si>
-    <t xml:space="preserve">18.276216506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2528514862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2107963562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3790264129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1407241821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4397983551025</t>
+    <t xml:space="preserve">18.2762184143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2528533935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2107944488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3790225982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1407260894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4398002624512</t>
   </si>
   <si>
     <t xml:space="preserve">19.402416229248</t>
@@ -1706,19 +1706,19 @@
     <t xml:space="preserve">19.3650321960449</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1594200134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1687660217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1126899719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0939979553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7388439178467</t>
+    <t xml:space="preserve">19.1594181060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1687641143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1126880645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0939960479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7388458251953</t>
   </si>
   <si>
     <t xml:space="preserve">19.0566120147705</t>
@@ -1733,34 +1733,34 @@
     <t xml:space="preserve">19.2528800964355</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5239124298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4211101531982</t>
+    <t xml:space="preserve">19.5239162445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4211082458496</t>
   </si>
   <si>
     <t xml:space="preserve">19.8136444091797</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0753326416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.748218536377</t>
+    <t xml:space="preserve">20.0753307342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7482204437256</t>
   </si>
   <si>
     <t xml:space="preserve">20.0192565917969</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7669143676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7856044769287</t>
+    <t xml:space="preserve">19.7669105529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7856063842773</t>
   </si>
   <si>
     <t xml:space="preserve">19.5706462860107</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2809162139893</t>
+    <t xml:space="preserve">19.2809181213379</t>
   </si>
   <si>
     <t xml:space="preserve">19.1500720977783</t>
@@ -1769,10 +1769,10 @@
     <t xml:space="preserve">18.8977298736572</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8042678833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8790397644043</t>
+    <t xml:space="preserve">18.804271697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8790378570557</t>
   </si>
   <si>
     <t xml:space="preserve">18.1780853271484</t>
@@ -1781,16 +1781,16 @@
     <t xml:space="preserve">18.6453876495361</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8556423187256</t>
+    <t xml:space="preserve">17.8556442260742</t>
   </si>
   <si>
     <t xml:space="preserve">17.2528228759766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1546878814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9817886352539</t>
+    <t xml:space="preserve">17.1546897888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9817867279053</t>
   </si>
   <si>
     <t xml:space="preserve">18.1360263824463</t>
@@ -1808,40 +1808,40 @@
     <t xml:space="preserve">19.1874580383301</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0098838806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5986843109131</t>
+    <t xml:space="preserve">19.0098819732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5986824035645</t>
   </si>
   <si>
     <t xml:space="preserve">19.5893363952637</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6454162597656</t>
+    <t xml:space="preserve">19.645414352417</t>
   </si>
   <si>
     <t xml:space="preserve">19.4771862030029</t>
   </si>
   <si>
-    <t xml:space="preserve">19.542610168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5799942016602</t>
+    <t xml:space="preserve">19.5426063537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5799922943115</t>
   </si>
   <si>
     <t xml:space="preserve">20.0005645751953</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6267223358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4865303039551</t>
+    <t xml:space="preserve">19.6267204284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4865322113037</t>
   </si>
   <si>
     <t xml:space="preserve">19.7014904022217</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3930721282959</t>
+    <t xml:space="preserve">19.3930702209473</t>
   </si>
   <si>
     <t xml:space="preserve">18.7481918334961</t>
@@ -1850,7 +1850,7 @@
     <t xml:space="preserve">18.7855777740479</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0659599304199</t>
+    <t xml:space="preserve">19.0659580230713</t>
   </si>
   <si>
     <t xml:space="preserve">19.5145683288574</t>
@@ -1865,13 +1865,13 @@
     <t xml:space="preserve">16.7107524871826</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8135585784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5845813751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5471954345703</t>
+    <t xml:space="preserve">16.8135566711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5845794677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5471973419189</t>
   </si>
   <si>
     <t xml:space="preserve">16.5378494262695</t>
@@ -1880,40 +1880,40 @@
     <t xml:space="preserve">16.7200965881348</t>
   </si>
   <si>
-    <t xml:space="preserve">16.495792388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7528095245361</t>
+    <t xml:space="preserve">16.4957904815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7528076171875</t>
   </si>
   <si>
     <t xml:space="preserve">16.500467300415</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4630832672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0425090789795</t>
+    <t xml:space="preserve">16.4630813598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0425071716309</t>
   </si>
   <si>
     <t xml:space="preserve">16.3509292602539</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5425224304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8415946960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6640205383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5331783294678</t>
+    <t xml:space="preserve">16.5425243377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8415966033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6640224456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5331764221191</t>
   </si>
   <si>
     <t xml:space="preserve">16.5892524719238</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6827125549316</t>
+    <t xml:space="preserve">16.6827144622803</t>
   </si>
   <si>
     <t xml:space="preserve">16.5986003875732</t>
@@ -1937,19 +1937,19 @@
     <t xml:space="preserve">16.2154121398926</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4817752838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5238304138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4023303985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2995262145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5799083709717</t>
+    <t xml:space="preserve">16.4817733764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5238285064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4023323059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.299524307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.579906463623</t>
   </si>
   <si>
     <t xml:space="preserve">17.1874008178711</t>
@@ -1964,7 +1964,7 @@
     <t xml:space="preserve">17.2201118469238</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5752620697021</t>
+    <t xml:space="preserve">17.5752601623535</t>
   </si>
   <si>
     <t xml:space="preserve">17.5518970489502</t>
@@ -1976,16 +1976,16 @@
     <t xml:space="preserve">17.1079597473145</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1313228607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2294597625732</t>
+    <t xml:space="preserve">17.1313247680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2294578552246</t>
   </si>
   <si>
     <t xml:space="preserve">17.4911479949951</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4397449493408</t>
+    <t xml:space="preserve">17.4397430419922</t>
   </si>
   <si>
     <t xml:space="preserve">17.453763961792</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">17.7294731140137</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6547031402588</t>
+    <t xml:space="preserve">17.6547050476074</t>
   </si>
   <si>
     <t xml:space="preserve">17.3369369506836</t>
@@ -2009,10 +2009,10 @@
     <t xml:space="preserve">17.1687107086182</t>
   </si>
   <si>
-    <t xml:space="preserve">16.822904586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9911594390869</t>
+    <t xml:space="preserve">16.8229064941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9911613464355</t>
   </si>
   <si>
     <t xml:space="preserve">17.9117221832275</t>
@@ -2033,19 +2033,19 @@
     <t xml:space="preserve">17.3275928497314</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3976879119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6266651153564</t>
+    <t xml:space="preserve">17.3976898193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6266670227051</t>
   </si>
   <si>
     <t xml:space="preserve">17.5004940032959</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8696613311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3136005401611</t>
+    <t xml:space="preserve">17.8696632385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3135986328125</t>
   </si>
   <si>
     <t xml:space="preserve">18.0565814971924</t>
@@ -2066,13 +2066,13 @@
     <t xml:space="preserve">18.6921157836914</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5051918029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3416366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5565967559814</t>
+    <t xml:space="preserve">18.5051937103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3416385650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5565986633301</t>
   </si>
   <si>
     <t xml:space="preserve">18.4397716522217</t>
@@ -2081,13 +2081,13 @@
     <t xml:space="preserve">18.5472526550293</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3089275360107</t>
+    <t xml:space="preserve">18.3089294433594</t>
   </si>
   <si>
     <t xml:space="preserve">18.8603458404541</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3696784973145</t>
+    <t xml:space="preserve">18.3696765899658</t>
   </si>
   <si>
     <t xml:space="preserve">18.5893096923828</t>
@@ -2096,7 +2096,7 @@
     <t xml:space="preserve">18.0238723754883</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8603191375732</t>
+    <t xml:space="preserve">17.8603172302246</t>
   </si>
   <si>
     <t xml:space="preserve">18.06125831604</t>
@@ -2105,40 +2105,40 @@
     <t xml:space="preserve">17.5986270904541</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0939693450928</t>
+    <t xml:space="preserve">18.0939674377441</t>
   </si>
   <si>
     <t xml:space="preserve">19.8603744506836</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0472965240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9071006774902</t>
+    <t xml:space="preserve">20.0472946166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9071044921875</t>
   </si>
   <si>
     <t xml:space="preserve">19.4607124328613</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9735889434814</t>
+    <t xml:space="preserve">19.9735870361328</t>
   </si>
   <si>
     <t xml:space="preserve">19.4132251739502</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2042770385742</t>
+    <t xml:space="preserve">19.2042751312256</t>
   </si>
   <si>
     <t xml:space="preserve">19.4892063140869</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1187953948975</t>
+    <t xml:space="preserve">19.1187973022461</t>
   </si>
   <si>
     <t xml:space="preserve">19.2327690124512</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9525890350342</t>
+    <t xml:space="preserve">18.9525871276855</t>
   </si>
   <si>
     <t xml:space="preserve">18.4397163391113</t>
@@ -2147,19 +2147,19 @@
     <t xml:space="preserve">17.7131423950195</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7273902893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8318634033203</t>
+    <t xml:space="preserve">17.7273921966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8318614959717</t>
   </si>
   <si>
     <t xml:space="preserve">18.3732299804688</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6534118652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1757831573486</t>
+    <t xml:space="preserve">18.6534099578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1757850646973</t>
   </si>
   <si>
     <t xml:space="preserve">19.3657360076904</t>
@@ -2171,13 +2171,13 @@
     <t xml:space="preserve">19.213773727417</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9810810089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.905101776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0333194732666</t>
+    <t xml:space="preserve">18.9810791015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9050998687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.033317565918</t>
   </si>
   <si>
     <t xml:space="preserve">19.6601657867432</t>
@@ -2192,46 +2192,46 @@
     <t xml:space="preserve">20.0210742950439</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8026275634766</t>
+    <t xml:space="preserve">19.8026294708252</t>
   </si>
   <si>
     <t xml:space="preserve">19.7171497344971</t>
   </si>
   <si>
-    <t xml:space="preserve">19.812126159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7456436157227</t>
+    <t xml:space="preserve">19.8121280670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.745641708374</t>
   </si>
   <si>
     <t xml:space="preserve">19.926097869873</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1350498199463</t>
+    <t xml:space="preserve">20.135046005249</t>
   </si>
   <si>
     <t xml:space="preserve">20.1920337677002</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4674644470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4864597320557</t>
+    <t xml:space="preserve">20.4674663543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4864616394043</t>
   </si>
   <si>
     <t xml:space="preserve">20.2870101928711</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2775115966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8406181335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8216247558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.850118637085</t>
+    <t xml:space="preserve">20.2775135040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8406200408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.821626663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8501167297363</t>
   </si>
   <si>
     <t xml:space="preserve">19.9545917510986</t>
@@ -2243,16 +2243,16 @@
     <t xml:space="preserve">19.8881092071533</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0305728912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8691120147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.96409034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0020790100098</t>
+    <t xml:space="preserve">20.030574798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8691139221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9640884399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0020809173584</t>
   </si>
   <si>
     <t xml:space="preserve">19.9450931549072</t>
@@ -2264,19 +2264,19 @@
     <t xml:space="preserve">18.0218181610107</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9315891265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5754241943359</t>
+    <t xml:space="preserve">17.9315872192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5754261016846</t>
   </si>
   <si>
     <t xml:space="preserve">17.2952442169189</t>
   </si>
   <si>
-    <t xml:space="preserve">17.276252746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2667541503906</t>
+    <t xml:space="preserve">17.2762489318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.266752243042</t>
   </si>
   <si>
     <t xml:space="preserve">17.3854732513428</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">16.8963451385498</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0150661468506</t>
+    <t xml:space="preserve">17.0150680541992</t>
   </si>
   <si>
     <t xml:space="preserve">16.59716796875</t>
@@ -2306,28 +2306,28 @@
     <t xml:space="preserve">17.0530548095703</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9153385162354</t>
+    <t xml:space="preserve">16.915340423584</t>
   </si>
   <si>
     <t xml:space="preserve">16.6636505126953</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7348861694336</t>
+    <t xml:space="preserve">16.734884262085</t>
   </si>
   <si>
     <t xml:space="preserve">16.948579788208</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7491321563721</t>
+    <t xml:space="preserve">16.7491302490234</t>
   </si>
   <si>
     <t xml:space="preserve">16.8441066741943</t>
   </si>
   <si>
-    <t xml:space="preserve">16.497444152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6683979034424</t>
+    <t xml:space="preserve">16.4974422454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.668399810791</t>
   </si>
   <si>
     <t xml:space="preserve">16.6304092407227</t>
@@ -2336,7 +2336,7 @@
     <t xml:space="preserve">16.9248371124268</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4329605102539</t>
+    <t xml:space="preserve">17.4329624176025</t>
   </si>
   <si>
     <t xml:space="preserve">17.3807239532471</t>
@@ -2354,16 +2354,16 @@
     <t xml:space="preserve">17.2857475280762</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2002716064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.696891784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7538776397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2267551422119</t>
+    <t xml:space="preserve">17.2002696990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6968936920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7538795471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2267570495605</t>
   </si>
   <si>
     <t xml:space="preserve">16.1887664794922</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">16.1032905578613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0178108215332</t>
+    <t xml:space="preserve">16.0178089141846</t>
   </si>
   <si>
     <t xml:space="preserve">15.4811916351318</t>
@@ -2414,10 +2414,10 @@
     <t xml:space="preserve">15.4052095413208</t>
   </si>
   <si>
-    <t xml:space="preserve">15.324481010437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2722425460815</t>
+    <t xml:space="preserve">15.3244800567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2722434997559</t>
   </si>
   <si>
     <t xml:space="preserve">15.2579975128174</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">15.1772661209106</t>
   </si>
   <si>
-    <t xml:space="preserve">15.068042755127</t>
+    <t xml:space="preserve">15.0680437088013</t>
   </si>
   <si>
     <t xml:space="preserve">15.0348024368286</t>
@@ -2438,13 +2438,13 @@
     <t xml:space="preserve">15.9608240127563</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7661228179932</t>
+    <t xml:space="preserve">15.7661218643188</t>
   </si>
   <si>
     <t xml:space="preserve">15.8800926208496</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9085865020752</t>
+    <t xml:space="preserve">15.9085874557495</t>
   </si>
   <si>
     <t xml:space="preserve">15.922833442688</t>
@@ -2459,10 +2459,10 @@
     <t xml:space="preserve">16.4024639129639</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5781707763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5734252929688</t>
+    <t xml:space="preserve">16.5781726837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5734233856201</t>
   </si>
   <si>
     <t xml:space="preserve">16.6066665649414</t>
@@ -2471,10 +2471,10 @@
     <t xml:space="preserve">17.2809982299805</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9723281860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4404544830322</t>
+    <t xml:space="preserve">16.9723262786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4404563903809</t>
   </si>
   <si>
     <t xml:space="preserve">16.3074893951416</t>
@@ -2486,40 +2486,40 @@
     <t xml:space="preserve">16.3977165222168</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6209125518799</t>
+    <t xml:space="preserve">16.6209106445312</t>
   </si>
   <si>
     <t xml:space="preserve">17.3047428131104</t>
   </si>
   <si>
-    <t xml:space="preserve">17.129035949707</t>
+    <t xml:space="preserve">17.1290378570557</t>
   </si>
   <si>
     <t xml:space="preserve">17.1860218048096</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6873950958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9695816040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1120433807373</t>
+    <t xml:space="preserve">16.6873970031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9695796966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1120452880859</t>
   </si>
   <si>
     <t xml:space="preserve">17.4282131195068</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3474807739258</t>
+    <t xml:space="preserve">17.3474826812744</t>
   </si>
   <si>
     <t xml:space="preserve">17.2477569580078</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3379859924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.409215927124</t>
+    <t xml:space="preserve">17.337984085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4092178344727</t>
   </si>
   <si>
     <t xml:space="preserve">17.62766456604</t>
@@ -2531,19 +2531,19 @@
     <t xml:space="preserve">17.4804515838623</t>
   </si>
   <si>
-    <t xml:space="preserve">17.803373336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.116792678833</t>
+    <t xml:space="preserve">17.8033714294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1167964935303</t>
   </si>
   <si>
     <t xml:space="preserve">17.8556079864502</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8081188201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0028209686279</t>
+    <t xml:space="preserve">17.8081207275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0028228759766</t>
   </si>
   <si>
     <t xml:space="preserve">17.6704025268555</t>
@@ -2552,31 +2552,31 @@
     <t xml:space="preserve">17.6229152679443</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6799011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9885749816895</t>
+    <t xml:space="preserve">17.6799030303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9885768890381</t>
   </si>
   <si>
     <t xml:space="preserve">18.4207191467285</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0930500030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9030952453613</t>
+    <t xml:space="preserve">18.0930480957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.90309715271</t>
   </si>
   <si>
     <t xml:space="preserve">17.8508586883545</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2620048522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2287616729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0957946777344</t>
+    <t xml:space="preserve">17.2620029449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.228759765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.095796585083</t>
   </si>
   <si>
     <t xml:space="preserve">16.8868465423584</t>
@@ -2585,13 +2585,13 @@
     <t xml:space="preserve">16.6161632537842</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5924167633057</t>
+    <t xml:space="preserve">16.5924186706543</t>
   </si>
   <si>
     <t xml:space="preserve">15.8611001968384</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2694988250732</t>
+    <t xml:space="preserve">16.2694969177246</t>
   </si>
   <si>
     <t xml:space="preserve">16.2979907989502</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">16.1175346374512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8468523025513</t>
+    <t xml:space="preserve">15.8468494415283</t>
   </si>
   <si>
     <t xml:space="preserve">16.3217353820801</t>
@@ -2615,10 +2615,10 @@
     <t xml:space="preserve">15.7186317443848</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3434772491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9845676422119</t>
+    <t xml:space="preserve">15.3434762954712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9845685958862</t>
   </si>
   <si>
     <t xml:space="preserve">15.7471265792847</t>
@@ -2627,37 +2627,37 @@
     <t xml:space="preserve">15.6046619415283</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7043857574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8848428726196</t>
+    <t xml:space="preserve">15.7043867111206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8848438262939</t>
   </si>
   <si>
     <t xml:space="preserve">15.5429258346558</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1582708358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8096027374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8665885925293</t>
+    <t xml:space="preserve">15.1582717895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8096036911011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8665895462036</t>
   </si>
   <si>
     <t xml:space="preserve">14.1420221328735</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6054029464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5721616744995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0735349655151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0497903823853</t>
+    <t xml:space="preserve">13.6054039001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5721607208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0735340118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0497894287109</t>
   </si>
   <si>
     <t xml:space="preserve">12.9738092422485</t>
@@ -2666,22 +2666,22 @@
     <t xml:space="preserve">12.3184700012207</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0477867126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2784767150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.656379699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7845964431763</t>
+    <t xml:space="preserve">12.0477876663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2784757614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6563787460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7845973968506</t>
   </si>
   <si>
     <t xml:space="preserve">9.08166599273682</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65437507629395</t>
+    <t xml:space="preserve">9.65437412261963</t>
   </si>
   <si>
     <t xml:space="preserve">10.0057888031006</t>
@@ -2690,13 +2690,13 @@
     <t xml:space="preserve">9.97254657745361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4976634979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6183881759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8625822067261</t>
+    <t xml:space="preserve">9.49766445159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6183891296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8625812530518</t>
   </si>
   <si>
     <t xml:space="preserve">12.1665077209473</t>
@@ -2705,28 +2705,28 @@
     <t xml:space="preserve">13.0877809524536</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3964538574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9690599441528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2519855499268</t>
+    <t xml:space="preserve">13.3964548110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9690589904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2519865036011</t>
   </si>
   <si>
     <t xml:space="preserve">11.9195680618286</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4921741485596</t>
+    <t xml:space="preserve">11.4921731948853</t>
   </si>
   <si>
     <t xml:space="preserve">11.2072429656982</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1597557067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1882476806641</t>
+    <t xml:space="preserve">11.1597547531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1882467269897</t>
   </si>
   <si>
     <t xml:space="preserve">11.5681552886963</t>
@@ -2735,10 +2735,10 @@
     <t xml:space="preserve">11.5586566925049</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6251411437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9765539169312</t>
+    <t xml:space="preserve">11.6251401901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9765529632568</t>
   </si>
   <si>
     <t xml:space="preserve">11.4541835784912</t>
@@ -2747,31 +2747,31 @@
     <t xml:space="preserve">11.2927227020264</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5396614074707</t>
+    <t xml:space="preserve">11.5396604537964</t>
   </si>
   <si>
     <t xml:space="preserve">10.8178396224976</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3999404907227</t>
+    <t xml:space="preserve">10.3999423980713</t>
   </si>
   <si>
     <t xml:space="preserve">10.4474306106567</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3809461593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7323598861694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9128160476685</t>
+    <t xml:space="preserve">10.3809471130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7323608398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9128150939941</t>
   </si>
   <si>
     <t xml:space="preserve">10.7228622436523</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3049659729004</t>
+    <t xml:space="preserve">10.3049650192261</t>
   </si>
   <si>
     <t xml:space="preserve">10.3524532318115</t>
@@ -2780,37 +2780,37 @@
     <t xml:space="preserve">10.3144626617432</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3429555892944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4094400405884</t>
+    <t xml:space="preserve">10.3429574966431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4094390869141</t>
   </si>
   <si>
     <t xml:space="preserve">10.2574768066406</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0295324325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90606307983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89656543731689</t>
+    <t xml:space="preserve">10.0295333862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9060640335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89656639099121</t>
   </si>
   <si>
     <t xml:space="preserve">9.64962577819824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78259372711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4949178695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.346962928772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9005718231201</t>
+    <t xml:space="preserve">9.78259468078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4949188232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3469638824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9005727767944</t>
   </si>
   <si>
     <t xml:space="preserve">12.2614841461182</t>
@@ -2825,28 +2825,28 @@
     <t xml:space="preserve">13.6576404571533</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2872304916382</t>
+    <t xml:space="preserve">13.2872314453125</t>
   </si>
   <si>
     <t xml:space="preserve">13.1542644500732</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8218469619751</t>
+    <t xml:space="preserve">12.8218460083008</t>
   </si>
   <si>
     <t xml:space="preserve">11.8815774917603</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7771034240723</t>
+    <t xml:space="preserve">11.7771024703979</t>
   </si>
   <si>
     <t xml:space="preserve">12.062032699585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1190195083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2899761199951</t>
+    <t xml:space="preserve">12.1190185546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2899770736694</t>
   </si>
   <si>
     <t xml:space="preserve">12.3089714050293</t>
@@ -2855,7 +2855,7 @@
     <t xml:space="preserve">12.7078742980957</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5749063491821</t>
+    <t xml:space="preserve">12.5749073028564</t>
   </si>
   <si>
     <t xml:space="preserve">12.5844049453735</t>
@@ -2867,7 +2867,7 @@
     <t xml:space="preserve">11.8055963516235</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5111694335938</t>
+    <t xml:space="preserve">11.5111684799194</t>
   </si>
   <si>
     <t xml:space="preserve">11.7296152114868</t>
@@ -2876,10 +2876,10 @@
     <t xml:space="preserve">11.4446849822998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5206661224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7581081390381</t>
+    <t xml:space="preserve">11.5206670761108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7581071853638</t>
   </si>
   <si>
     <t xml:space="preserve">11.5871496200562</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">11.4826755523682</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3402099609375</t>
+    <t xml:space="preserve">11.3402109146118</t>
   </si>
   <si>
     <t xml:space="preserve">10.9887962341309</t>
@@ -2897,19 +2897,19 @@
     <t xml:space="preserve">11.1787509918213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2262372970581</t>
+    <t xml:space="preserve">11.2262382507324</t>
   </si>
   <si>
     <t xml:space="preserve">11.2452335357666</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1027688980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1312627792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0267877578735</t>
+    <t xml:space="preserve">11.1027679443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1312618255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0267868041992</t>
   </si>
   <si>
     <t xml:space="preserve">11.0837736129761</t>
@@ -2918,10 +2918,10 @@
     <t xml:space="preserve">10.8368349075317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0552806854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2167415618896</t>
+    <t xml:space="preserve">11.0552816390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2167406082153</t>
   </si>
   <si>
     <t xml:space="preserve">10.5708999633789</t>
@@ -2936,7 +2936,7 @@
     <t xml:space="preserve">10.3619508743286</t>
   </si>
   <si>
-    <t xml:space="preserve">11.644136428833</t>
+    <t xml:space="preserve">11.6441354751587</t>
   </si>
   <si>
     <t xml:space="preserve">11.3307132720947</t>
@@ -2945,46 +2945,46 @@
     <t xml:space="preserve">11.0932712554932</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9603033065796</t>
+    <t xml:space="preserve">10.9603042602539</t>
   </si>
   <si>
     <t xml:space="preserve">10.7608528137207</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7798500061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6753740310669</t>
+    <t xml:space="preserve">10.7798480987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6753749847412</t>
   </si>
   <si>
     <t xml:space="preserve">11.6156425476074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4636793136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3971977233887</t>
+    <t xml:space="preserve">11.463680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3971967697144</t>
   </si>
   <si>
     <t xml:space="preserve">11.5016708374023</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7960987091064</t>
+    <t xml:space="preserve">11.7960996627808</t>
   </si>
   <si>
     <t xml:space="preserve">11.4731779098511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4256896972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5179204940796</t>
+    <t xml:space="preserve">11.4256887435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5179214477539</t>
   </si>
   <si>
     <t xml:space="preserve">12.565408706665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0810279846191</t>
+    <t xml:space="preserve">12.0810289382935</t>
   </si>
   <si>
     <t xml:space="preserve">11.6821269989014</t>
@@ -2993,16 +2993,16 @@
     <t xml:space="preserve">11.6061458587646</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1095218658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0145435333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9385623931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9575576782227</t>
+    <t xml:space="preserve">12.1095209121704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0145454406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9385633468628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.957558631897</t>
   </si>
   <si>
     <t xml:space="preserve">11.9860515594482</t>
@@ -3023,19 +3023,19 @@
     <t xml:space="preserve">12.5464134216309</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2044982910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4039487838745</t>
+    <t xml:space="preserve">12.2044973373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4039497375488</t>
   </si>
   <si>
     <t xml:space="preserve">12.8978271484375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1949996948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8910760879517</t>
+    <t xml:space="preserve">12.1950006484985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8910751342773</t>
   </si>
   <si>
     <t xml:space="preserve">11.67262840271</t>
@@ -3047,43 +3047,43 @@
     <t xml:space="preserve">10.6943693161011</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5139131546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7988443374634</t>
+    <t xml:space="preserve">10.5139141082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7988433837891</t>
   </si>
   <si>
     <t xml:space="preserve">11.0647783279419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3592052459717</t>
+    <t xml:space="preserve">11.359206199646</t>
   </si>
   <si>
     <t xml:space="preserve">12.3659582138062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7933530807495</t>
+    <t xml:space="preserve">12.7933540344238</t>
   </si>
   <si>
     <t xml:space="preserve">13.3537158966064</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7811107635498</t>
+    <t xml:space="preserve">13.7811098098755</t>
   </si>
   <si>
     <t xml:space="preserve">13.7146263122559</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9235744476318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9330730438232</t>
+    <t xml:space="preserve">13.9235754013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9330739974976</t>
   </si>
   <si>
     <t xml:space="preserve">14.2369976043701</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3414726257324</t>
+    <t xml:space="preserve">14.3414716720581</t>
   </si>
   <si>
     <t xml:space="preserve">14.0470447540283</t>
@@ -3098,16 +3098,16 @@
     <t xml:space="preserve">14.1515197753906</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2464952468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4269504547119</t>
+    <t xml:space="preserve">14.2464962005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4269514083862</t>
   </si>
   <si>
     <t xml:space="preserve">14.4649410247803</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9113321304321</t>
+    <t xml:space="preserve">14.9113311767578</t>
   </si>
   <si>
     <t xml:space="preserve">14.4934358596802</t>
@@ -3116,16 +3116,16 @@
     <t xml:space="preserve">14.3509693145752</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5979080200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7498722076416</t>
+    <t xml:space="preserve">14.5979099273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7498712539673</t>
   </si>
   <si>
     <t xml:space="preserve">15.1487741470337</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8828401565552</t>
+    <t xml:space="preserve">14.8828392028809</t>
   </si>
   <si>
     <t xml:space="preserve">14.8543462753296</t>
@@ -3152,19 +3152,19 @@
     <t xml:space="preserve">15.0632944107056</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9493217468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7688684463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7118806838989</t>
+    <t xml:space="preserve">14.9493227005005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7688674926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7118816375732</t>
   </si>
   <si>
     <t xml:space="preserve">14.5884113311768</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5789136886597</t>
+    <t xml:space="preserve">14.578914642334</t>
   </si>
   <si>
     <t xml:space="preserve">14.4079561233521</t>
@@ -3173,16 +3173,16 @@
     <t xml:space="preserve">14.5504207611084</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5314264297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9615650177002</t>
+    <t xml:space="preserve">14.5314254760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9615659713745</t>
   </si>
   <si>
     <t xml:space="preserve">14.2085056304932</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4459466934204</t>
+    <t xml:space="preserve">14.4459457397461</t>
   </si>
   <si>
     <t xml:space="preserve">15.29123878479</t>
@@ -3194,10 +3194,10 @@
     <t xml:space="preserve">15.0537977218628</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8041133880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6711454391479</t>
+    <t xml:space="preserve">15.8041124343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6711444854736</t>
   </si>
   <si>
     <t xml:space="preserve">15.2627458572388</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">14.9588203430176</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0442991256714</t>
+    <t xml:space="preserve">15.0443000793457</t>
   </si>
   <si>
     <t xml:space="preserve">14.721378326416</t>
@@ -3218,22 +3218,22 @@
     <t xml:space="preserve">14.4364490509033</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7403755187988</t>
+    <t xml:space="preserve">14.7403745651245</t>
   </si>
   <si>
     <t xml:space="preserve">15.006308555603</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0822896957397</t>
+    <t xml:space="preserve">15.0822906494141</t>
   </si>
   <si>
     <t xml:space="preserve">14.9778165817261</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6928853988647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7783651351929</t>
+    <t xml:space="preserve">14.6928863525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7783641815186</t>
   </si>
   <si>
     <t xml:space="preserve">14.8258533477783</t>
@@ -3242,7 +3242,7 @@
     <t xml:space="preserve">15.2057600021362</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1202812194824</t>
+    <t xml:space="preserve">15.1202802658081</t>
   </si>
   <si>
     <t xml:space="preserve">15.0917882919312</t>
@@ -3257,7 +3257,7 @@
     <t xml:space="preserve">14.9873132705688</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8705959320068</t>
+    <t xml:space="preserve">15.8705949783325</t>
   </si>
   <si>
     <t xml:space="preserve">16.0225601196289</t>
@@ -3266,13 +3266,13 @@
     <t xml:space="preserve">16.0320568084717</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8231077194214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9370794296265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7376279830933</t>
+    <t xml:space="preserve">15.8231086730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9370803833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7376270294189</t>
   </si>
   <si>
     <t xml:space="preserve">15.4906892776489</t>
@@ -3281,31 +3281,31 @@
     <t xml:space="preserve">15.7091360092163</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3102340698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3672199249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3387269973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6996374130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6853914260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6189079284668</t>
+    <t xml:space="preserve">15.3102350234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3672208786011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3387260437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6996402740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6853904724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6189069747925</t>
   </si>
   <si>
     <t xml:space="preserve">15.428955078125</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6379022598267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7396335601807</t>
+    <t xml:space="preserve">15.637903213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.739631652832</t>
   </si>
   <si>
     <t xml:space="preserve">16.8678512573242</t>
@@ -3314,7 +3314,7 @@
     <t xml:space="preserve">16.8725986480713</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4784469604492</t>
+    <t xml:space="preserve">16.4784488677979</t>
   </si>
   <si>
     <t xml:space="preserve">17.0340595245361</t>
@@ -3326,10 +3326,10 @@
     <t xml:space="preserve">17.4567050933838</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0388107299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2904968261719</t>
+    <t xml:space="preserve">17.0388088226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2904987335205</t>
   </si>
   <si>
     <t xml:space="preserve">17.0815486907959</t>
@@ -3338,31 +3338,31 @@
     <t xml:space="preserve">17.0245628356934</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9770755767822</t>
+    <t xml:space="preserve">16.9770736694336</t>
   </si>
   <si>
     <t xml:space="preserve">17.2572555541992</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4614543914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4187145233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2117710113525</t>
+    <t xml:space="preserve">17.4614562988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4187164306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2117691040039</t>
   </si>
   <si>
     <t xml:space="preserve">18.3589839935303</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1975250244141</t>
+    <t xml:space="preserve">18.1975231170654</t>
   </si>
   <si>
     <t xml:space="preserve">18.1500358581543</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2307643890381</t>
+    <t xml:space="preserve">18.2307662963867</t>
   </si>
   <si>
     <t xml:space="preserve">18.0360641479492</t>
@@ -3374,16 +3374,16 @@
     <t xml:space="preserve">17.9553356170654</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6846523284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0408134460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3304901123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3209953308105</t>
+    <t xml:space="preserve">17.6846504211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0408115386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3304920196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3209934234619</t>
   </si>
   <si>
     <t xml:space="preserve">18.368480682373</t>
@@ -3392,7 +3392,7 @@
     <t xml:space="preserve">18.3019981384277</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3542346954346</t>
+    <t xml:space="preserve">18.3542366027832</t>
   </si>
   <si>
     <t xml:space="preserve">18.3969745635986</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">18.1832790374756</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4444637298584</t>
+    <t xml:space="preserve">18.444465637207</t>
   </si>
   <si>
     <t xml:space="preserve">18.8956031799316</t>
@@ -3419,10 +3419,10 @@
     <t xml:space="preserve">18.6961498260498</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5584354400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3352394104004</t>
+    <t xml:space="preserve">18.5584373474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.335241317749</t>
   </si>
   <si>
     <t xml:space="preserve">17.8461112976074</t>
@@ -3431,7 +3431,7 @@
     <t xml:space="preserve">17.1527805328369</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1812725067139</t>
+    <t xml:space="preserve">17.1812744140625</t>
   </si>
   <si>
     <t xml:space="preserve">17.0673007965088</t>
@@ -3440,22 +3440,22 @@
     <t xml:space="preserve">17.1575298309326</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6114139556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5021915435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7253875732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.877347946167</t>
+    <t xml:space="preserve">16.6114120483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5021896362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7253856658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8773498535156</t>
   </si>
   <si>
     <t xml:space="preserve">16.4214611053467</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9798202514648</t>
+    <t xml:space="preserve">15.9798192977905</t>
   </si>
   <si>
     <t xml:space="preserve">16.0985412597656</t>
@@ -3464,28 +3464,28 @@
     <t xml:space="preserve">16.0083122253418</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2505035400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4736957550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.169771194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0463047027588</t>
+    <t xml:space="preserve">16.2505054473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4736976623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1697731018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0463027954102</t>
   </si>
   <si>
     <t xml:space="preserve">16.0368061065674</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9988145828247</t>
+    <t xml:space="preserve">15.9988136291504</t>
   </si>
   <si>
     <t xml:space="preserve">16.2600021362305</t>
   </si>
   <si>
-    <t xml:space="preserve">16.065299987793</t>
+    <t xml:space="preserve">16.0652980804443</t>
   </si>
   <si>
     <t xml:space="preserve">16.0510520935059</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">17.1100406646729</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3949718475342</t>
+    <t xml:space="preserve">17.3949699401855</t>
   </si>
   <si>
     <t xml:space="preserve">18.4919509887695</t>
@@ -3503,34 +3503,34 @@
     <t xml:space="preserve">17.5896739959717</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6609039306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0008182525635</t>
+    <t xml:space="preserve">17.6609058380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0008163452148</t>
   </si>
   <si>
     <t xml:space="preserve">16.6731491088867</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5164375305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7328805923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7423782348633</t>
+    <t xml:space="preserve">16.5164356231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7328796386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7423791885376</t>
   </si>
   <si>
     <t xml:space="preserve">16.1460285186768</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9275827407837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9703216552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6541519165039</t>
+    <t xml:space="preserve">15.9275808334351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9703226089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6541538238525</t>
   </si>
   <si>
     <t xml:space="preserve">16.7586288452148</t>
@@ -3551,13 +3551,13 @@
     <t xml:space="preserve">16.8251113891602</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7206382751465</t>
+    <t xml:space="preserve">16.7206363677979</t>
   </si>
   <si>
     <t xml:space="preserve">16.9628295898438</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9438304901123</t>
+    <t xml:space="preserve">16.9438323974609</t>
   </si>
   <si>
     <t xml:space="preserve">16.8298587799072</t>
@@ -3578,19 +3578,19 @@
     <t xml:space="preserve">16.7111377716064</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2145175933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4424610137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3427333831787</t>
+    <t xml:space="preserve">17.2145156860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4424591064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3427352905273</t>
   </si>
   <si>
     <t xml:space="preserve">17.4662036895752</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7178936004639</t>
+    <t xml:space="preserve">17.7178916931152</t>
   </si>
   <si>
     <t xml:space="preserve">17.7748775482178</t>
@@ -3608,22 +3608,22 @@
     <t xml:space="preserve">18.7911281585693</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9715843200684</t>
+    <t xml:space="preserve">18.9715824127197</t>
   </si>
   <si>
     <t xml:space="preserve">17.945837020874</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4302177429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5536861419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7626342773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0903053283691</t>
+    <t xml:space="preserve">18.4302158355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5536880493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7626323699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0903034210205</t>
   </si>
   <si>
     <t xml:space="preserve">19.3752346038818</t>
@@ -3641,28 +3641,28 @@
     <t xml:space="preserve">20.5529441833496</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6221752166748</t>
+    <t xml:space="preserve">19.6221733093262</t>
   </si>
   <si>
     <t xml:space="preserve">19.1377925872803</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6316719055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4579677581787</t>
+    <t xml:space="preserve">19.6316699981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4579696655273</t>
   </si>
   <si>
     <t xml:space="preserve">20.6289253234863</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0373229980469</t>
+    <t xml:space="preserve">21.0373249053955</t>
   </si>
   <si>
     <t xml:space="preserve">21.4457244873047</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9898357391357</t>
+    <t xml:space="preserve">20.9898376464844</t>
   </si>
   <si>
     <t xml:space="preserve">20.7523956298828</t>
@@ -3677,46 +3677,46 @@
     <t xml:space="preserve">20.0970573425293</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7903861999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7144031524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0278263092041</t>
+    <t xml:space="preserve">20.7903842926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7144050598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0278282165527</t>
   </si>
   <si>
     <t xml:space="preserve">21.0183296203613</t>
   </si>
   <si>
-    <t xml:space="preserve">21.094310760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4172306060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3982372283936</t>
+    <t xml:space="preserve">21.0943088531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4172325134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3982391357422</t>
   </si>
   <si>
     <t xml:space="preserve">21.7021617889404</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5691928863525</t>
+    <t xml:space="preserve">21.5691947937012</t>
   </si>
   <si>
     <t xml:space="preserve">22.0820693969727</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5976886749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6261806488037</t>
+    <t xml:space="preserve">21.5976867675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6261825561523</t>
   </si>
   <si>
     <t xml:space="preserve">19.4797096252441</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0998001098633</t>
+    <t xml:space="preserve">19.0998020172119</t>
   </si>
   <si>
     <t xml:space="preserve">19.536693572998</t>
@@ -3731,13 +3731,13 @@
     <t xml:space="preserve">18.0550594329834</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4946975708008</t>
+    <t xml:space="preserve">17.4946956634521</t>
   </si>
   <si>
     <t xml:space="preserve">18.2212677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">17.974328994751</t>
+    <t xml:space="preserve">17.9743270874023</t>
   </si>
   <si>
     <t xml:space="preserve">18.5916767120361</t>
@@ -3746,7 +3746,7 @@
     <t xml:space="preserve">18.5394401550293</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0977993011475</t>
+    <t xml:space="preserve">18.0977973937988</t>
   </si>
   <si>
     <t xml:space="preserve">18.0503082275391</t>
@@ -3767,7 +3767,7 @@
     <t xml:space="preserve">18.68190574646</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7721309661865</t>
+    <t xml:space="preserve">18.7721328735352</t>
   </si>
   <si>
     <t xml:space="preserve">18.8006267547607</t>
@@ -3785,40 +3785,40 @@
     <t xml:space="preserve">18.6581611633301</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4492130279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6324119567871</t>
+    <t xml:space="preserve">18.4492111206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6324138641357</t>
   </si>
   <si>
     <t xml:space="preserve">17.7368869781494</t>
   </si>
   <si>
-    <t xml:space="preserve">17.12428855896</t>
+    <t xml:space="preserve">17.1242904663086</t>
   </si>
   <si>
     <t xml:space="preserve">15.1867637634277</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8306007385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5076808929443</t>
+    <t xml:space="preserve">14.8306016921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5076818466187</t>
   </si>
   <si>
     <t xml:space="preserve">15.9133348464966</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3529748916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4574489593506</t>
+    <t xml:space="preserve">15.3529739379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.457447052002</t>
   </si>
   <si>
     <t xml:space="preserve">14.8733415603638</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5856657028198</t>
+    <t xml:space="preserve">15.5856676101685</t>
   </si>
   <si>
     <t xml:space="preserve">15.81360912323</t>
@@ -3827,10 +3827,10 @@
     <t xml:space="preserve">15.5334281921387</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2390022277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2532472610474</t>
+    <t xml:space="preserve">15.2390012741089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2532482147217</t>
   </si>
   <si>
     <t xml:space="preserve">15.5191822052002</t>
@@ -3839,7 +3839,7 @@
     <t xml:space="preserve">15.8278579711914</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7681255340576</t>
+    <t xml:space="preserve">16.7681274414062</t>
   </si>
   <si>
     <t xml:space="preserve">16.316987991333</t>
@@ -3854,13 +3854,13 @@
     <t xml:space="preserve">15.6331548690796</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6521492004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8895902633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5096855163574</t>
+    <t xml:space="preserve">15.6521482467651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.889591217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5096845626831</t>
   </si>
   <si>
     <t xml:space="preserve">14.7308769226074</t>
@@ -3869,10 +3869,10 @@
     <t xml:space="preserve">14.8638439178467</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1392755508423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7851190567017</t>
+    <t xml:space="preserve">15.1392765045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7851181030273</t>
   </si>
   <si>
     <t xml:space="preserve">14.3034820556641</t>
@@ -3884,7 +3884,7 @@
     <t xml:space="preserve">13.8285989761353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8123483657837</t>
+    <t xml:space="preserve">12.812349319458</t>
   </si>
   <si>
     <t xml:space="preserve">14.1040306091309</t>
@@ -3893,7 +3893,7 @@
     <t xml:space="preserve">14.1990070343018</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0158071517944</t>
+    <t xml:space="preserve">15.0158061981201</t>
   </si>
   <si>
     <t xml:space="preserve">14.5219278335571</t>
@@ -73382,7 +73382,7 @@
     </row>
     <row r="2575">
       <c r="A2575" s="1" t="n">
-        <v>46071.6911226852</v>
+        <v>46071.3333333333</v>
       </c>
       <c r="B2575" t="n">
         <v>242061</v>
@@ -73403,6 +73403,32 @@
         <v>2035</v>
       </c>
       <c r="H2575" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2576">
+      <c r="A2576" s="1" t="n">
+        <v>46072.6910185185</v>
+      </c>
+      <c r="B2576" t="n">
+        <v>173440</v>
+      </c>
+      <c r="C2576" t="n">
+        <v>6.69500017166138</v>
+      </c>
+      <c r="D2576" t="n">
+        <v>6.53999996185303</v>
+      </c>
+      <c r="E2576" t="n">
+        <v>6.67500019073486</v>
+      </c>
+      <c r="F2576" t="n">
+        <v>6.69000005722046</v>
+      </c>
+      <c r="G2576" t="s">
+        <v>2031</v>
+      </c>
+      <c r="H2576" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2043" uniqueCount="2043">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2044" uniqueCount="2044">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,37 +44,37 @@
     <t xml:space="preserve">SFER.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0109634399414</t>
+    <t xml:space="preserve">18.01096534729</t>
   </si>
   <si>
     <t xml:space="preserve">17.4978828430176</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9401950836182</t>
+    <t xml:space="preserve">17.9401969909668</t>
   </si>
   <si>
     <t xml:space="preserve">17.6836528778076</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2498092651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.408670425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1344413757324</t>
+    <t xml:space="preserve">18.2498111724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4086723327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1344375610352</t>
   </si>
   <si>
     <t xml:space="preserve">18.8425102233887</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4621257781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2851982116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0994243621826</t>
+    <t xml:space="preserve">18.462121963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2852001190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0994262695312</t>
   </si>
   <si>
     <t xml:space="preserve">17.6394214630127</t>
@@ -83,22 +83,22 @@
     <t xml:space="preserve">17.5686531066895</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1878890991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4798164367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2232761383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7632675170898</t>
+    <t xml:space="preserve">18.1878871917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4798145294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.223274230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7632694244385</t>
   </si>
   <si>
     <t xml:space="preserve">18.3913536071777</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6744327545166</t>
+    <t xml:space="preserve">18.6744346618652</t>
   </si>
   <si>
     <t xml:space="preserve">17.9578857421875</t>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">18.0817337036133</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3563423156738</t>
+    <t xml:space="preserve">17.3563404083252</t>
   </si>
   <si>
     <t xml:space="preserve">16.9051818847656</t>
@@ -128,19 +128,19 @@
     <t xml:space="preserve">17.0201835632324</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4890384674072</t>
+    <t xml:space="preserve">17.4890365600586</t>
   </si>
   <si>
     <t xml:space="preserve">17.6305751800537</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4090442657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4532775878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9752063751221</t>
+    <t xml:space="preserve">18.4090461730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.453275680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9752044677734</t>
   </si>
   <si>
     <t xml:space="preserve">18.1348114013672</t>
@@ -152,52 +152,52 @@
     <t xml:space="preserve">17.9048080444336</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3471202850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0194358825684</t>
+    <t xml:space="preserve">18.3471221923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.019437789917</t>
   </si>
   <si>
     <t xml:space="preserve">19.0017433166504</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8513584136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3113613128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.992525100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9482898712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7271347045898</t>
+    <t xml:space="preserve">18.8513565063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3113632202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9925231933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9482917785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7271327972412</t>
   </si>
   <si>
     <t xml:space="preserve">19.3379020690918</t>
   </si>
   <si>
-    <t xml:space="preserve">19.647518157959</t>
+    <t xml:space="preserve">19.6475200653076</t>
   </si>
   <si>
     <t xml:space="preserve">19.9836769104004</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1167449951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.444055557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0367546081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.178295135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4971351623535</t>
+    <t xml:space="preserve">19.1167469024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4440574645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0367527008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1782932281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4971332550049</t>
   </si>
   <si>
     <t xml:space="preserve">19.4705944061279</t>
@@ -209,61 +209,61 @@
     <t xml:space="preserve">19.4794425964355</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9129066467285</t>
+    <t xml:space="preserve">19.9129085540771</t>
   </si>
   <si>
     <t xml:space="preserve">19.868673324585</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4175148010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8690490722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.833667755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5152015686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9309749603271</t>
+    <t xml:space="preserve">19.4175186157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.869047164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8336639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5152034759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9309730529785</t>
   </si>
   <si>
     <t xml:space="preserve">18.8955898284912</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5240478515625</t>
+    <t xml:space="preserve">18.5240459442139</t>
   </si>
   <si>
     <t xml:space="preserve">18.9486656188965</t>
   </si>
   <si>
-    <t xml:space="preserve">18.798282623291</t>
+    <t xml:space="preserve">18.7982807159424</t>
   </si>
   <si>
     <t xml:space="preserve">18.8778991699219</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2936687469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8071269989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3205795288086</t>
+    <t xml:space="preserve">19.2936706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.80712890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3205814361572</t>
   </si>
   <si>
     <t xml:space="preserve">18.3648147583008</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8251934051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0640411376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3117370605469</t>
+    <t xml:space="preserve">17.8251914978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0640392303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3117351531982</t>
   </si>
   <si>
     <t xml:space="preserve">17.8782691955566</t>
@@ -272,13 +272,13 @@
     <t xml:space="preserve">18.0021171569824</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7190361022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.444803237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1440334320068</t>
+    <t xml:space="preserve">17.7190399169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4448013305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1440315246582</t>
   </si>
   <si>
     <t xml:space="preserve">17.5509586334229</t>
@@ -290,37 +290,37 @@
     <t xml:space="preserve">17.4182643890381</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9313488006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7367286682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.648265838623</t>
+    <t xml:space="preserve">17.9313468933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7367305755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6482696533203</t>
   </si>
   <si>
     <t xml:space="preserve">17.593936920166</t>
   </si>
   <si>
-    <t xml:space="preserve">17.81125831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.702600479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.530553817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4128360748291</t>
+    <t xml:space="preserve">17.8112564086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7025966644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5305519104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4128341674805</t>
   </si>
   <si>
     <t xml:space="preserve">17.3041763305664</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4762210845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4309482574463</t>
+    <t xml:space="preserve">17.4762191772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4309463500977</t>
   </si>
   <si>
     <t xml:space="preserve">17.4852752685547</t>
@@ -332,31 +332,31 @@
     <t xml:space="preserve">17.6844863891602</t>
   </si>
   <si>
-    <t xml:space="preserve">17.150239944458</t>
+    <t xml:space="preserve">17.1502418518066</t>
   </si>
   <si>
     <t xml:space="preserve">16.7155990600586</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5435523986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0415802001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0777988433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8384265899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9380302429199</t>
+    <t xml:space="preserve">16.5435543060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0415782928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0778007507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8384227752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9380283355713</t>
   </si>
   <si>
     <t xml:space="preserve">17.7297630310059</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8655853271484</t>
+    <t xml:space="preserve">17.8655872344971</t>
   </si>
   <si>
     <t xml:space="preserve">18.1825141906738</t>
@@ -371,58 +371,58 @@
     <t xml:space="preserve">16.6793785095215</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2628479003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5254421234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6069393157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8061485290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8242588043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0726909637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8734798431396</t>
+    <t xml:space="preserve">16.2628440856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5254402160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6069412231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8061466217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8242607116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0726890563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8734817504883</t>
   </si>
   <si>
     <t xml:space="preserve">16.3624515533447</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4439487457275</t>
+    <t xml:space="preserve">16.4439468383789</t>
   </si>
   <si>
     <t xml:space="preserve">16.69748878479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0959091186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1321296691895</t>
+    <t xml:space="preserve">17.095911026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1321277618408</t>
   </si>
   <si>
     <t xml:space="preserve">17.086856842041</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0325260162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3403949737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9018115997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1372375488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.92897605896</t>
+    <t xml:space="preserve">17.0325241088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3403968811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9018077850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1372413635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9289741516113</t>
   </si>
   <si>
     <t xml:space="preserve">18.7710914611816</t>
@@ -431,19 +431,19 @@
     <t xml:space="preserve">18.6352672576904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0699100494385</t>
+    <t xml:space="preserve">19.0699062347412</t>
   </si>
   <si>
     <t xml:space="preserve">19.2147884368896</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6262130737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4994411468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2187347412109</t>
+    <t xml:space="preserve">18.6262111663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4994430541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2187366485596</t>
   </si>
   <si>
     <t xml:space="preserve">18.7167625427246</t>
@@ -455,19 +455,19 @@
     <t xml:space="preserve">18.762035369873</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8073120117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9431381225586</t>
+    <t xml:space="preserve">18.8073139190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.94313621521</t>
   </si>
   <si>
     <t xml:space="preserve">19.0427436828613</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6624336242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4722747802734</t>
+    <t xml:space="preserve">18.6624317169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4722728729248</t>
   </si>
   <si>
     <t xml:space="preserve">18.6171569824219</t>
@@ -476,22 +476,22 @@
     <t xml:space="preserve">18.7529811859131</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9703044891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6805381774902</t>
+    <t xml:space="preserve">18.9703025817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6805400848389</t>
   </si>
   <si>
     <t xml:space="preserve">18.6081027984619</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6533794403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5175533294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.870698928833</t>
+    <t xml:space="preserve">18.653377532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5175514221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8706970214844</t>
   </si>
   <si>
     <t xml:space="preserve">18.6986522674561</t>
@@ -500,73 +500,73 @@
     <t xml:space="preserve">19.106128692627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9210834503174</t>
+    <t xml:space="preserve">19.9210815429688</t>
   </si>
   <si>
     <t xml:space="preserve">19.6947059631348</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5588836669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4592742919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3143939971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8888092041016</t>
+    <t xml:space="preserve">19.5588798522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4592723846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.314395904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8888111114502</t>
   </si>
   <si>
     <t xml:space="preserve">19.1332912445068</t>
   </si>
   <si>
-    <t xml:space="preserve">19.160457611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9391918182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4553279876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3557224273682</t>
+    <t xml:space="preserve">19.1604595184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9391899108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4553298950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3557243347168</t>
   </si>
   <si>
     <t xml:space="preserve">20.3104476928711</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3919410705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4643859863281</t>
+    <t xml:space="preserve">20.3919429779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4643840789795</t>
   </si>
   <si>
     <t xml:space="preserve">20.6907596588135</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8446960449219</t>
+    <t xml:space="preserve">20.8446979522705</t>
   </si>
   <si>
     <t xml:space="preserve">20.7994174957275</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4009990692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1021842956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5277690887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3647785186768</t>
+    <t xml:space="preserve">20.4010009765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1021823883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5277709960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3647766113281</t>
   </si>
   <si>
     <t xml:space="preserve">20.5458812713623</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7541465759277</t>
+    <t xml:space="preserve">20.7541484832764</t>
   </si>
   <si>
     <t xml:space="preserve">20.4191074371338</t>
@@ -575,19 +575,19 @@
     <t xml:space="preserve">20.0116329193115</t>
   </si>
   <si>
-    <t xml:space="preserve">20.265172958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3285617828369</t>
+    <t xml:space="preserve">20.2651748657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3285598754883</t>
   </si>
   <si>
     <t xml:space="preserve">20.0387954711914</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1474571228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2289562225342</t>
+    <t xml:space="preserve">20.1474590301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2289543151855</t>
   </si>
   <si>
     <t xml:space="preserve">20.5006046295166</t>
@@ -596,22 +596,22 @@
     <t xml:space="preserve">20.5639896392822</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1836776733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.549825668335</t>
+    <t xml:space="preserve">20.1836795806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5498237609863</t>
   </si>
   <si>
     <t xml:space="preserve">19.4140033721924</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5045490264893</t>
+    <t xml:space="preserve">19.5045528411865</t>
   </si>
   <si>
     <t xml:space="preserve">19.7218704223633</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7943115234375</t>
+    <t xml:space="preserve">19.7943134307861</t>
   </si>
   <si>
     <t xml:space="preserve">19.5226593017578</t>
@@ -620,16 +620,16 @@
     <t xml:space="preserve">19.830530166626</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9120273590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7490367889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0919628143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3002300262451</t>
+    <t xml:space="preserve">19.9120254516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7490348815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0919609069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3002281188965</t>
   </si>
   <si>
     <t xml:space="preserve">18.3273944854736</t>
@@ -641,37 +641,37 @@
     <t xml:space="preserve">18.0104675292969</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7388172149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8565311431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8203125</t>
+    <t xml:space="preserve">17.7388191223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8565330505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8203163146973</t>
   </si>
   <si>
     <t xml:space="preserve">17.6392135620117</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3455066680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3907814025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.151403427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2872295379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3958892822266</t>
+    <t xml:space="preserve">18.3455047607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3907794952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1514015197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2872314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3958911895752</t>
   </si>
   <si>
     <t xml:space="preserve">19.377779006958</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1151828765869</t>
+    <t xml:space="preserve">19.1151847839355</t>
   </si>
   <si>
     <t xml:space="preserve">19.5860462188721</t>
@@ -683,58 +683,58 @@
     <t xml:space="preserve">20.3738346099854</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3466682434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2380104064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1293468475342</t>
+    <t xml:space="preserve">20.3466701507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2380084991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1293449401855</t>
   </si>
   <si>
     <t xml:space="preserve">20.1565132141113</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8084774017334</t>
+    <t xml:space="preserve">20.8084754943848</t>
   </si>
   <si>
     <t xml:space="preserve">20.6183185577393</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4785461425781</t>
+    <t xml:space="preserve">21.4785480499268</t>
   </si>
   <si>
     <t xml:space="preserve">21.5328769683838</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0671272277832</t>
+    <t xml:space="preserve">22.0671253204346</t>
   </si>
   <si>
     <t xml:space="preserve">22.058069229126</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2572822570801</t>
+    <t xml:space="preserve">22.2572784423828</t>
   </si>
   <si>
     <t xml:space="preserve">22.2935028076172</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3025569915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3206653594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2753925323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2391738891602</t>
+    <t xml:space="preserve">22.3025588989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3206634521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2753944396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2391719818115</t>
   </si>
   <si>
     <t xml:space="preserve">22.8186950683594</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0722351074219</t>
+    <t xml:space="preserve">23.0722332000732</t>
   </si>
   <si>
     <t xml:space="preserve">22.891134262085</t>
@@ -746,40 +746,40 @@
     <t xml:space="preserve">23.0993995666504</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5923194885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3568897247314</t>
+    <t xml:space="preserve">22.5923175811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3568878173828</t>
   </si>
   <si>
     <t xml:space="preserve">22.9092445373535</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1757850646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1395664215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6064853668213</t>
+    <t xml:space="preserve">22.1757869720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1395645141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.606481552124</t>
   </si>
   <si>
     <t xml:space="preserve">23.7513637542725</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1226177215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6427040100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6879749298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.561206817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7423076629639</t>
+    <t xml:space="preserve">24.1226196289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6427059173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6879768371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5612087249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7423057556152</t>
   </si>
   <si>
     <t xml:space="preserve">23.7241992950439</t>
@@ -788,37 +788,37 @@
     <t xml:space="preserve">23.6336479187012</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8238010406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6970348358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0139617919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2856121063232</t>
+    <t xml:space="preserve">23.823802947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6970329284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0139598846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2856101989746</t>
   </si>
   <si>
     <t xml:space="preserve">24.0682888031006</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9777393341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2946662902832</t>
+    <t xml:space="preserve">23.9777374267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2946643829346</t>
   </si>
   <si>
     <t xml:space="preserve">24.4304904937744</t>
   </si>
   <si>
-    <t xml:space="preserve">24.61159324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7655258178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1911125183105</t>
+    <t xml:space="preserve">24.6115913391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7655239105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1911144256592</t>
   </si>
   <si>
     <t xml:space="preserve">25.3903255462646</t>
@@ -839,28 +839,28 @@
     <t xml:space="preserve">25.7615814208984</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5352039337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9556846618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9013519287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0643444061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8017463684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6206455230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9375743865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3722133636475</t>
+    <t xml:space="preserve">25.5352077484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9556827545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9013538360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0643463134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8017482757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6206474304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.937572479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3722152709961</t>
   </si>
   <si>
     <t xml:space="preserve">25.6257553100586</t>
@@ -872,19 +872,19 @@
     <t xml:space="preserve">25.173002243042</t>
   </si>
   <si>
-    <t xml:space="preserve">25.163948059082</t>
+    <t xml:space="preserve">25.1639499664307</t>
   </si>
   <si>
     <t xml:space="preserve">25.399377822876</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7253608703613</t>
+    <t xml:space="preserve">25.7253589630127</t>
   </si>
   <si>
     <t xml:space="preserve">25.2907199859619</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1277275085449</t>
+    <t xml:space="preserve">25.1277294158936</t>
   </si>
   <si>
     <t xml:space="preserve">25.7434711456299</t>
@@ -899,7 +899,7 @@
     <t xml:space="preserve">25.5080394744873</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2635536193848</t>
+    <t xml:space="preserve">25.2635555267334</t>
   </si>
   <si>
     <t xml:space="preserve">25.0824527740479</t>
@@ -911,16 +911,16 @@
     <t xml:space="preserve">24.4214363098145</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2674999237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5261516571045</t>
+    <t xml:space="preserve">24.2674961090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5261497497559</t>
   </si>
   <si>
     <t xml:space="preserve">26.1237812042236</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1871681213379</t>
+    <t xml:space="preserve">26.1871662139893</t>
   </si>
   <si>
     <t xml:space="preserve">26.6308650970459</t>
@@ -929,22 +929,22 @@
     <t xml:space="preserve">26.4859809875488</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3229942321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.676139831543</t>
+    <t xml:space="preserve">26.3229961395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6761379241943</t>
   </si>
   <si>
     <t xml:space="preserve">26.8934593200684</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2596073150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.667085647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9115715026855</t>
+    <t xml:space="preserve">26.2596092224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6670837402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9115695953369</t>
   </si>
   <si>
     <t xml:space="preserve">26.6036987304688</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">25.3088302612305</t>
   </si>
   <si>
-    <t xml:space="preserve">25.326940536499</t>
+    <t xml:space="preserve">25.3269367218018</t>
   </si>
   <si>
     <t xml:space="preserve">25.834020614624</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">25.8984432220459</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0641078948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.71120262146</t>
+    <t xml:space="preserve">26.0641059875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7112045288086</t>
   </si>
   <si>
     <t xml:space="preserve">23.6159954071045</t>
@@ -980,10 +980,10 @@
     <t xml:space="preserve">23.1282119750977</t>
   </si>
   <si>
-    <t xml:space="preserve">22.962553024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8705177307129</t>
+    <t xml:space="preserve">22.9625511169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8705196380615</t>
   </si>
   <si>
     <t xml:space="preserve">22.8613128662109</t>
@@ -998,10 +998,10 @@
     <t xml:space="preserve">23.0453834533691</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8889236450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0882263183594</t>
+    <t xml:space="preserve">22.8889255523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0882244110107</t>
   </si>
   <si>
     <t xml:space="preserve">22.3183116912842</t>
@@ -1019,7 +1019,7 @@
     <t xml:space="preserve">22.7416687011719</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9533500671387</t>
+    <t xml:space="preserve">22.95334815979</t>
   </si>
   <si>
     <t xml:space="preserve">22.8797206878662</t>
@@ -1028,28 +1028,28 @@
     <t xml:space="preserve">23.2846717834473</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4871463775635</t>
+    <t xml:space="preserve">23.4871482849121</t>
   </si>
   <si>
     <t xml:space="preserve">23.4319248199463</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8060913085938</t>
+    <t xml:space="preserve">22.8060932159424</t>
   </si>
   <si>
     <t xml:space="preserve">23.0269756317139</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6036205291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2538890838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5452213287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4900016784668</t>
+    <t xml:space="preserve">22.6036167144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2538871765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.545223236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4900035858154</t>
   </si>
   <si>
     <t xml:space="preserve">21.7200889587402</t>
@@ -1058,13 +1058,13 @@
     <t xml:space="preserve">21.5544261932373</t>
   </si>
   <si>
-    <t xml:space="preserve">21.674072265625</t>
+    <t xml:space="preserve">21.6740703582764</t>
   </si>
   <si>
     <t xml:space="preserve">21.6280536651611</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1678810119629</t>
+    <t xml:space="preserve">21.1678829193115</t>
   </si>
   <si>
     <t xml:space="preserve">21.2046966552734</t>
@@ -1076,13 +1076,13 @@
     <t xml:space="preserve">21.4163761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5084095001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9133625030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8857479095459</t>
+    <t xml:space="preserve">21.5084114074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9133586883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8857498168945</t>
   </si>
   <si>
     <t xml:space="preserve">21.9685821533203</t>
@@ -1091,16 +1091,16 @@
     <t xml:space="preserve">22.6220245361328</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3735332489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2170715332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4103450775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5299873352051</t>
+    <t xml:space="preserve">22.3735313415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2170734405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4103469848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5299892425537</t>
   </si>
   <si>
     <t xml:space="preserve">22.6312294006348</t>
@@ -1109,13 +1109,13 @@
     <t xml:space="preserve">22.6404323577881</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5575981140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4255790710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6556644439697</t>
+    <t xml:space="preserve">22.5576000213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4255809783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6556663513184</t>
   </si>
   <si>
     <t xml:space="preserve">22.2630920410156</t>
@@ -1130,61 +1130,61 @@
     <t xml:space="preserve">22.0514125823975</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7876853942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3367195129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.115837097168</t>
+    <t xml:space="preserve">22.7876873016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3367176055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1158390045166</t>
   </si>
   <si>
     <t xml:space="preserve">21.7661037445068</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0606136322021</t>
+    <t xml:space="preserve">22.0606117248535</t>
   </si>
   <si>
     <t xml:space="preserve">21.7569007873535</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9961910247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7016830444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.005392074585</t>
+    <t xml:space="preserve">21.9961891174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.701681137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0053939819336</t>
   </si>
   <si>
     <t xml:space="preserve">21.8765468597412</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1250400543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7753086090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0238037109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9041557312012</t>
+    <t xml:space="preserve">22.1250381469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7753124237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0238018035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9041576385498</t>
   </si>
   <si>
     <t xml:space="preserve">21.6832752227783</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8273544311523</t>
+    <t xml:space="preserve">20.827356338501</t>
   </si>
   <si>
     <t xml:space="preserve">21.0574398040771</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9470024108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.799747467041</t>
+    <t xml:space="preserve">20.94700050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7997455596924</t>
   </si>
   <si>
     <t xml:space="preserve">21.103458404541</t>
@@ -1193,58 +1193,58 @@
     <t xml:space="preserve">21.0758476257324</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3243427276611</t>
+    <t xml:space="preserve">21.3243408203125</t>
   </si>
   <si>
     <t xml:space="preserve">21.9501762390137</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0974292755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8581371307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6372585296631</t>
+    <t xml:space="preserve">22.0974311828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8581409454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6372566223145</t>
   </si>
   <si>
     <t xml:space="preserve">21.2967319488525</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9746131896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9838161468506</t>
+    <t xml:space="preserve">20.9746112823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.983814239502</t>
   </si>
   <si>
     <t xml:space="preserve">21.1402702331543</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0666446685791</t>
+    <t xml:space="preserve">21.0666465759277</t>
   </si>
   <si>
     <t xml:space="preserve">20.7077121734619</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0942573547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1586799621582</t>
+    <t xml:space="preserve">21.0942554473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1586780548096</t>
   </si>
   <si>
     <t xml:space="preserve">21.0206279754639</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0022220611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6340866088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4500160217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.385591506958</t>
+    <t xml:space="preserve">21.0022239685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6340827941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4500141143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3855895996094</t>
   </si>
   <si>
     <t xml:space="preserve">20.3947944641113</t>
@@ -1256,19 +1256,19 @@
     <t xml:space="preserve">19.9714393615723</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0634708404541</t>
+    <t xml:space="preserve">20.0634727478027</t>
   </si>
   <si>
     <t xml:space="preserve">20.4868297576904</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7445259094238</t>
+    <t xml:space="preserve">20.7445278167725</t>
   </si>
   <si>
     <t xml:space="preserve">20.8917808532715</t>
   </si>
   <si>
-    <t xml:space="preserve">21.241512298584</t>
+    <t xml:space="preserve">21.2415103912354</t>
   </si>
   <si>
     <t xml:space="preserve">20.9285926818848</t>
@@ -1277,13 +1277,13 @@
     <t xml:space="preserve">20.2475414276123</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1647071838379</t>
+    <t xml:space="preserve">20.1647109985352</t>
   </si>
   <si>
     <t xml:space="preserve">20.0910816192627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2719783782959</t>
+    <t xml:space="preserve">19.2719764709473</t>
   </si>
   <si>
     <t xml:space="preserve">19.695333480835</t>
@@ -1298,31 +1298,31 @@
     <t xml:space="preserve">20.1831169128418</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0450649261475</t>
+    <t xml:space="preserve">20.0450630187988</t>
   </si>
   <si>
     <t xml:space="preserve">20.2935581207275</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4316101074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5696620941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6616973876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.131067276001</t>
+    <t xml:space="preserve">20.4316082000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5696601867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6616954803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1310691833496</t>
   </si>
   <si>
     <t xml:space="preserve">21.0482387542725</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1954917907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4531879425049</t>
+    <t xml:space="preserve">21.1954956054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4531898498535</t>
   </si>
   <si>
     <t xml:space="preserve">20.8089504241943</t>
@@ -1343,22 +1343,22 @@
     <t xml:space="preserve">19.8609962463379</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0174541473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2199306488037</t>
+    <t xml:space="preserve">20.0174522399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2199287414551</t>
   </si>
   <si>
     <t xml:space="preserve">20.229133605957</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5236415863037</t>
+    <t xml:space="preserve">20.5236434936523</t>
   </si>
   <si>
     <t xml:space="preserve">20.6524925231934</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9101867675781</t>
+    <t xml:space="preserve">20.9101848602295</t>
   </si>
   <si>
     <t xml:space="preserve">20.2659473419189</t>
@@ -1367,43 +1367,43 @@
     <t xml:space="preserve">20.4684219360352</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1555042266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1739139556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2599182128906</t>
+    <t xml:space="preserve">20.1555061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1739120483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.259916305542</t>
   </si>
   <si>
     <t xml:space="preserve">21.3703575134277</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5176105499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8549652099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9193916320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5052356719971</t>
+    <t xml:space="preserve">21.5176124572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8549671173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9193897247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5052375793457</t>
   </si>
   <si>
     <t xml:space="preserve">20.3487777709961</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0266571044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7229461669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9162158966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5604591369629</t>
+    <t xml:space="preserve">20.0266590118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7229442596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9162178039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5604572296143</t>
   </si>
   <si>
     <t xml:space="preserve">20.7169151306152</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">20.8365592956543</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6004447937012</t>
+    <t xml:space="preserve">21.6004428863525</t>
   </si>
   <si>
     <t xml:space="preserve">20.6248817443848</t>
@@ -1424,10 +1424,10 @@
     <t xml:space="preserve">20.2751502990723</t>
   </si>
   <si>
-    <t xml:space="preserve">20.109489440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6493167877197</t>
+    <t xml:space="preserve">20.1094875335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6493186950684</t>
   </si>
   <si>
     <t xml:space="preserve">19.9990482330322</t>
@@ -1439,31 +1439,31 @@
     <t xml:space="preserve">20.3303718566895</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8733730316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3763847351074</t>
+    <t xml:space="preserve">20.8733749389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3763885498047</t>
   </si>
   <si>
     <t xml:space="preserve">20.5328464508057</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3027610778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6432876586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6156768798828</t>
+    <t xml:space="preserve">20.3027591705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6432857513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6156787872314</t>
   </si>
   <si>
     <t xml:space="preserve">20.7261161804199</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2783241271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3151359558105</t>
+    <t xml:space="preserve">21.2783279418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3151378631592</t>
   </si>
   <si>
     <t xml:space="preserve">21.5360202789307</t>
@@ -1472,19 +1472,19 @@
     <t xml:space="preserve">21.7937164306641</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6496353149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.548397064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.419548034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2078666687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5668029785156</t>
+    <t xml:space="preserve">22.6496334075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5483989715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4195499420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2078685760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5668048858643</t>
   </si>
   <si>
     <t xml:space="preserve">22.6128215789795</t>
@@ -1493,22 +1493,22 @@
     <t xml:space="preserve">22.9165325164795</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6864471435547</t>
+    <t xml:space="preserve">22.6864452362061</t>
   </si>
   <si>
     <t xml:space="preserve">22.7324657440186</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8337020874023</t>
+    <t xml:space="preserve">22.8337001800537</t>
   </si>
   <si>
     <t xml:space="preserve">22.7692775726318</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9073276519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2754688262939</t>
+    <t xml:space="preserve">22.9073314666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2754669189453</t>
   </si>
   <si>
     <t xml:space="preserve">22.991304397583</t>
@@ -1523,34 +1523,34 @@
     <t xml:space="preserve">22.9071884155273</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9819564819336</t>
+    <t xml:space="preserve">22.9819583892822</t>
   </si>
   <si>
     <t xml:space="preserve">22.7296123504639</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3557720184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6174621582031</t>
+    <t xml:space="preserve">22.355770111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6174583435059</t>
   </si>
   <si>
     <t xml:space="preserve">23.07541847229</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3557987213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1969184875488</t>
+    <t xml:space="preserve">23.3558006286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1969165802002</t>
   </si>
   <si>
     <t xml:space="preserve">23.206262588501</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4586029052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6548461914062</t>
+    <t xml:space="preserve">23.4586067199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6548442840576</t>
   </si>
   <si>
     <t xml:space="preserve">22.7389602661133</t>
@@ -1583,19 +1583,19 @@
     <t xml:space="preserve">19.9912166595459</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7388763427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5612983703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3089542388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.533260345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4958782196045</t>
+    <t xml:space="preserve">19.7388744354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5613021850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3089561462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5332622528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4958801269531</t>
   </si>
   <si>
     <t xml:space="preserve">19.346342086792</t>
@@ -1607,25 +1607,25 @@
     <t xml:space="preserve">18.6266937255859</t>
   </si>
   <si>
-    <t xml:space="preserve">18.383695602417</t>
+    <t xml:space="preserve">18.3836975097656</t>
   </si>
   <si>
     <t xml:space="preserve">18.0752754211426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6220226287842</t>
+    <t xml:space="preserve">18.6220207214355</t>
   </si>
   <si>
     <t xml:space="preserve">18.0799503326416</t>
   </si>
   <si>
-    <t xml:space="preserve">18.603328704834</t>
+    <t xml:space="preserve">18.6033306121826</t>
   </si>
   <si>
     <t xml:space="preserve">18.6360397338867</t>
   </si>
   <si>
-    <t xml:space="preserve">18.794921875</t>
+    <t xml:space="preserve">18.7949237823486</t>
   </si>
   <si>
     <t xml:space="preserve">18.7762317657471</t>
@@ -1655,55 +1655,55 @@
     <t xml:space="preserve">18.491174697876</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2435054779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8042373657227</t>
+    <t xml:space="preserve">18.2435073852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8042392730713</t>
   </si>
   <si>
     <t xml:space="preserve">17.7715282440186</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1079883575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6734237670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7575397491455</t>
+    <t xml:space="preserve">18.1079845428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6734218597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7575378417969</t>
   </si>
   <si>
     <t xml:space="preserve">18.7295017242432</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2762184143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2528533935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2107944488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3790225982666</t>
+    <t xml:space="preserve">18.276216506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2528514862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2107963562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3790245056152</t>
   </si>
   <si>
     <t xml:space="preserve">19.1407260894775</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4398021697998</t>
+    <t xml:space="preserve">19.4398002624512</t>
   </si>
   <si>
     <t xml:space="preserve">19.4024181365967</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4117641448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4304542541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3650302886963</t>
+    <t xml:space="preserve">19.4117622375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.430456161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3650321960449</t>
   </si>
   <si>
     <t xml:space="preserve">19.1594181060791</t>
@@ -1715,25 +1715,25 @@
     <t xml:space="preserve">19.1126899719238</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0939960479736</t>
+    <t xml:space="preserve">19.0939979553223</t>
   </si>
   <si>
     <t xml:space="preserve">18.7388439178467</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0566101074219</t>
+    <t xml:space="preserve">19.0566120147705</t>
   </si>
   <si>
     <t xml:space="preserve">18.8416538238525</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6080303192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2528800964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5239162445068</t>
+    <t xml:space="preserve">19.6080284118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2528820037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5239143371582</t>
   </si>
   <si>
     <t xml:space="preserve">19.4211082458496</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">19.8136444091797</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0753307342529</t>
+    <t xml:space="preserve">20.0753326416016</t>
   </si>
   <si>
     <t xml:space="preserve">19.7482204437256</t>
@@ -1754,10 +1754,10 @@
     <t xml:space="preserve">19.7669124603271</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7856063842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5706462860107</t>
+    <t xml:space="preserve">19.7856044769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5706443786621</t>
   </si>
   <si>
     <t xml:space="preserve">19.2809162139893</t>
@@ -1775,13 +1775,13 @@
     <t xml:space="preserve">18.8790378570557</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1780834197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6453857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8556442260742</t>
+    <t xml:space="preserve">18.1780853271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6453876495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8556423187256</t>
   </si>
   <si>
     <t xml:space="preserve">17.2528228759766</t>
@@ -1790,7 +1790,7 @@
     <t xml:space="preserve">17.1546897888184</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9817867279053</t>
+    <t xml:space="preserve">16.9817886352539</t>
   </si>
   <si>
     <t xml:space="preserve">18.1360263824463</t>
@@ -1802,7 +1802,7 @@
     <t xml:space="preserve">18.1173343658447</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2154655456543</t>
+    <t xml:space="preserve">18.2154674530029</t>
   </si>
   <si>
     <t xml:space="preserve">19.1874580383301</t>
@@ -1811,7 +1811,7 @@
     <t xml:space="preserve">19.0098819732666</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5986824035645</t>
+    <t xml:space="preserve">19.5986843109131</t>
   </si>
   <si>
     <t xml:space="preserve">19.5893363952637</t>
@@ -1832,40 +1832,40 @@
     <t xml:space="preserve">20.0005626678467</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6267204284668</t>
+    <t xml:space="preserve">19.6267242431641</t>
   </si>
   <si>
     <t xml:space="preserve">19.4865303039551</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7014904022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3930683135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7481918334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7855777740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0659580230713</t>
+    <t xml:space="preserve">19.701488494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3930702209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7481937408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7855758666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0659561157227</t>
   </si>
   <si>
     <t xml:space="preserve">19.5145683288574</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2061500549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0472087860107</t>
+    <t xml:space="preserve">19.206148147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0472106933594</t>
   </si>
   <si>
     <t xml:space="preserve">16.710750579834</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8135566711426</t>
+    <t xml:space="preserve">16.8135585784912</t>
   </si>
   <si>
     <t xml:space="preserve">16.5845813751221</t>
@@ -1874,7 +1874,7 @@
     <t xml:space="preserve">16.5471973419189</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5378494262695</t>
+    <t xml:space="preserve">16.5378475189209</t>
   </si>
   <si>
     <t xml:space="preserve">16.7200965881348</t>
@@ -1886,10 +1886,10 @@
     <t xml:space="preserve">16.7528076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5004653930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4630813598633</t>
+    <t xml:space="preserve">16.500467300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4630832672119</t>
   </si>
   <si>
     <t xml:space="preserve">16.0425090789795</t>
@@ -1901,10 +1901,10 @@
     <t xml:space="preserve">16.5425224304199</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8415966033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6640205383301</t>
+    <t xml:space="preserve">16.8415946960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6640224456787</t>
   </si>
   <si>
     <t xml:space="preserve">16.5331783294678</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">16.5986003875732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4256973266602</t>
+    <t xml:space="preserve">16.4256954193115</t>
   </si>
   <si>
     <t xml:space="preserve">16.1266212463379</t>
@@ -1931,10 +1931,10 @@
     <t xml:space="preserve">16.4490623474121</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1920471191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2154083251953</t>
+    <t xml:space="preserve">16.192045211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2154102325439</t>
   </si>
   <si>
     <t xml:space="preserve">16.4817733764648</t>
@@ -1949,13 +1949,13 @@
     <t xml:space="preserve">16.299524307251</t>
   </si>
   <si>
-    <t xml:space="preserve">16.579906463623</t>
+    <t xml:space="preserve">16.5799083709717</t>
   </si>
   <si>
     <t xml:space="preserve">17.1874008178711</t>
   </si>
   <si>
-    <t xml:space="preserve">17.785551071167</t>
+    <t xml:space="preserve">17.7855491638184</t>
   </si>
   <si>
     <t xml:space="preserve">17.1967468261719</t>
@@ -1967,16 +1967,16 @@
     <t xml:space="preserve">17.5752620697021</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5518970489502</t>
+    <t xml:space="preserve">17.5518989562988</t>
   </si>
   <si>
     <t xml:space="preserve">17.4163780212402</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1079597473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1313228607178</t>
+    <t xml:space="preserve">17.1079578399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1313247680664</t>
   </si>
   <si>
     <t xml:space="preserve">17.2294578552246</t>
@@ -1985,19 +1985,19 @@
     <t xml:space="preserve">17.4911479949951</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4397449493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.453763961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.729471206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6547031402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3369388580322</t>
+    <t xml:space="preserve">17.4397430419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4537620544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7294731140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6547012329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3369369506836</t>
   </si>
   <si>
     <t xml:space="preserve">17.1453418731689</t>
@@ -2006,7 +2006,7 @@
     <t xml:space="preserve">16.8462696075439</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1687107086182</t>
+    <t xml:space="preserve">17.1687088012695</t>
   </si>
   <si>
     <t xml:space="preserve">16.822904586792</t>
@@ -2024,13 +2024,13 @@
     <t xml:space="preserve">17.6593780517578</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7948951721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6360111236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3275909423828</t>
+    <t xml:space="preserve">17.7948970794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6360130310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3275928497314</t>
   </si>
   <si>
     <t xml:space="preserve">17.3976879119873</t>
@@ -2045,16 +2045,16 @@
     <t xml:space="preserve">17.869665145874</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3135986328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.056583404541</t>
+    <t xml:space="preserve">18.3136005401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0565853118896</t>
   </si>
   <si>
     <t xml:space="preserve">18.2855625152588</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0192012786865</t>
+    <t xml:space="preserve">18.0191993713379</t>
   </si>
   <si>
     <t xml:space="preserve">17.9677982330322</t>
@@ -2063,10 +2063,10 @@
     <t xml:space="preserve">17.9070472717285</t>
   </si>
   <si>
-    <t xml:space="preserve">18.69211769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5051956176758</t>
+    <t xml:space="preserve">18.6921157836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5051937103271</t>
   </si>
   <si>
     <t xml:space="preserve">18.3416385650635</t>
@@ -2075,7 +2075,7 @@
     <t xml:space="preserve">18.5565967559814</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4397716522217</t>
+    <t xml:space="preserve">18.439769744873</t>
   </si>
   <si>
     <t xml:space="preserve">18.5472507476807</t>
@@ -2087,19 +2087,19 @@
     <t xml:space="preserve">18.8603458404541</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3696784973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5893096923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0238742828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8603172302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0612564086914</t>
+    <t xml:space="preserve">18.3696765899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5893077850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0238723754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8603191375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.06125831604</t>
   </si>
   <si>
     <t xml:space="preserve">17.5986270904541</t>
@@ -2120,25 +2120,25 @@
     <t xml:space="preserve">19.4607124328613</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9735870361328</t>
+    <t xml:space="preserve">19.9735889434814</t>
   </si>
   <si>
     <t xml:space="preserve">19.4132251739502</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2042751312256</t>
+    <t xml:space="preserve">19.2042770385742</t>
   </si>
   <si>
     <t xml:space="preserve">19.4892063140869</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1187973022461</t>
+    <t xml:space="preserve">19.1187953948975</t>
   </si>
   <si>
     <t xml:space="preserve">19.2327690124512</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9525871276855</t>
+    <t xml:space="preserve">18.9525890350342</t>
   </si>
   <si>
     <t xml:space="preserve">18.4397163391113</t>
@@ -2147,19 +2147,19 @@
     <t xml:space="preserve">17.7131423950195</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7273921966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8318614959717</t>
+    <t xml:space="preserve">17.7273902893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8318634033203</t>
   </si>
   <si>
     <t xml:space="preserve">18.3732299804688</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6534099578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1757850646973</t>
+    <t xml:space="preserve">18.6534118652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1757831573486</t>
   </si>
   <si>
     <t xml:space="preserve">19.3657360076904</t>
@@ -2171,13 +2171,13 @@
     <t xml:space="preserve">19.213773727417</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9810791015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9050998687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.033317565918</t>
+    <t xml:space="preserve">18.9810810089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.905101776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0333194732666</t>
   </si>
   <si>
     <t xml:space="preserve">19.6601657867432</t>
@@ -2192,46 +2192,46 @@
     <t xml:space="preserve">20.0210742950439</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8026294708252</t>
+    <t xml:space="preserve">19.8026275634766</t>
   </si>
   <si>
     <t xml:space="preserve">19.7171497344971</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8121280670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.745641708374</t>
+    <t xml:space="preserve">19.812126159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7456436157227</t>
   </si>
   <si>
     <t xml:space="preserve">19.926097869873</t>
   </si>
   <si>
-    <t xml:space="preserve">20.135046005249</t>
+    <t xml:space="preserve">20.1350498199463</t>
   </si>
   <si>
     <t xml:space="preserve">20.1920337677002</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4674663543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4864616394043</t>
+    <t xml:space="preserve">20.4674644470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4864597320557</t>
   </si>
   <si>
     <t xml:space="preserve">20.2870101928711</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2775135040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8406200408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.821626663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8501167297363</t>
+    <t xml:space="preserve">20.2775115966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8406181335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8216247558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.850118637085</t>
   </si>
   <si>
     <t xml:space="preserve">19.9545917510986</t>
@@ -2240,16 +2240,16 @@
     <t xml:space="preserve">19.8881092071533</t>
   </si>
   <si>
-    <t xml:space="preserve">20.030574798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8691139221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9640884399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0020809173584</t>
+    <t xml:space="preserve">20.0305728912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8691120147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.96409034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0020790100098</t>
   </si>
   <si>
     <t xml:space="preserve">19.9450931549072</t>
@@ -2261,19 +2261,19 @@
     <t xml:space="preserve">18.0218181610107</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9315872192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5754261016846</t>
+    <t xml:space="preserve">17.9315891265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5754241943359</t>
   </si>
   <si>
     <t xml:space="preserve">17.2952442169189</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2762489318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.266752243042</t>
+    <t xml:space="preserve">17.276252746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2667541503906</t>
   </si>
   <si>
     <t xml:space="preserve">17.3854732513428</t>
@@ -2285,7 +2285,7 @@
     <t xml:space="preserve">16.8963451385498</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0150680541992</t>
+    <t xml:space="preserve">17.0150661468506</t>
   </si>
   <si>
     <t xml:space="preserve">16.59716796875</t>
@@ -2303,28 +2303,28 @@
     <t xml:space="preserve">17.0530548095703</t>
   </si>
   <si>
-    <t xml:space="preserve">16.915340423584</t>
+    <t xml:space="preserve">16.9153385162354</t>
   </si>
   <si>
     <t xml:space="preserve">16.6636505126953</t>
   </si>
   <si>
-    <t xml:space="preserve">16.734884262085</t>
+    <t xml:space="preserve">16.7348861694336</t>
   </si>
   <si>
     <t xml:space="preserve">16.948579788208</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7491302490234</t>
+    <t xml:space="preserve">16.7491321563721</t>
   </si>
   <si>
     <t xml:space="preserve">16.8441066741943</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4974422454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.668399810791</t>
+    <t xml:space="preserve">16.497444152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6683979034424</t>
   </si>
   <si>
     <t xml:space="preserve">16.6304092407227</t>
@@ -2333,7 +2333,7 @@
     <t xml:space="preserve">16.9248371124268</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4329624176025</t>
+    <t xml:space="preserve">17.4329605102539</t>
   </si>
   <si>
     <t xml:space="preserve">17.3807239532471</t>
@@ -2351,16 +2351,16 @@
     <t xml:space="preserve">17.2857475280762</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2002696990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6968936920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7538795471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2267570495605</t>
+    <t xml:space="preserve">17.2002716064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.696891784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7538776397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2267551422119</t>
   </si>
   <si>
     <t xml:space="preserve">16.1887664794922</t>
@@ -2378,7 +2378,7 @@
     <t xml:space="preserve">16.1032905578613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0178089141846</t>
+    <t xml:space="preserve">16.0178108215332</t>
   </si>
   <si>
     <t xml:space="preserve">15.4811916351318</t>
@@ -2411,10 +2411,10 @@
     <t xml:space="preserve">15.4052095413208</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3244800567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2722434997559</t>
+    <t xml:space="preserve">15.324481010437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2722425460815</t>
   </si>
   <si>
     <t xml:space="preserve">15.2579975128174</t>
@@ -2423,7 +2423,7 @@
     <t xml:space="preserve">15.1772661209106</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0680437088013</t>
+    <t xml:space="preserve">15.068042755127</t>
   </si>
   <si>
     <t xml:space="preserve">15.0348024368286</t>
@@ -2435,13 +2435,13 @@
     <t xml:space="preserve">15.9608240127563</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7661218643188</t>
+    <t xml:space="preserve">15.7661228179932</t>
   </si>
   <si>
     <t xml:space="preserve">15.8800926208496</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9085874557495</t>
+    <t xml:space="preserve">15.9085865020752</t>
   </si>
   <si>
     <t xml:space="preserve">15.922833442688</t>
@@ -2456,10 +2456,10 @@
     <t xml:space="preserve">16.4024639129639</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5781726837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5734233856201</t>
+    <t xml:space="preserve">16.5781707763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5734252929688</t>
   </si>
   <si>
     <t xml:space="preserve">16.6066665649414</t>
@@ -2468,10 +2468,10 @@
     <t xml:space="preserve">17.2809982299805</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9723262786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4404563903809</t>
+    <t xml:space="preserve">16.9723281860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4404544830322</t>
   </si>
   <si>
     <t xml:space="preserve">16.3074893951416</t>
@@ -2483,40 +2483,40 @@
     <t xml:space="preserve">16.3977165222168</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6209106445312</t>
+    <t xml:space="preserve">16.6209125518799</t>
   </si>
   <si>
     <t xml:space="preserve">17.3047428131104</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1290378570557</t>
+    <t xml:space="preserve">17.129035949707</t>
   </si>
   <si>
     <t xml:space="preserve">17.1860218048096</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6873970031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9695796966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1120452880859</t>
+    <t xml:space="preserve">16.6873950958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9695816040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1120433807373</t>
   </si>
   <si>
     <t xml:space="preserve">17.4282131195068</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3474826812744</t>
+    <t xml:space="preserve">17.3474807739258</t>
   </si>
   <si>
     <t xml:space="preserve">17.2477569580078</t>
   </si>
   <si>
-    <t xml:space="preserve">17.337984085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4092178344727</t>
+    <t xml:space="preserve">17.3379859924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.409215927124</t>
   </si>
   <si>
     <t xml:space="preserve">17.62766456604</t>
@@ -2528,19 +2528,19 @@
     <t xml:space="preserve">17.4804515838623</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8033714294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1167964935303</t>
+    <t xml:space="preserve">17.803373336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.116792678833</t>
   </si>
   <si>
     <t xml:space="preserve">17.8556079864502</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8081207275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0028228759766</t>
+    <t xml:space="preserve">17.8081188201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0028209686279</t>
   </si>
   <si>
     <t xml:space="preserve">17.6704025268555</t>
@@ -2549,31 +2549,31 @@
     <t xml:space="preserve">17.6229152679443</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6799030303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9885768890381</t>
+    <t xml:space="preserve">17.6799011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9885749816895</t>
   </si>
   <si>
     <t xml:space="preserve">18.4207191467285</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0930480957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.90309715271</t>
+    <t xml:space="preserve">18.0930500030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9030952453613</t>
   </si>
   <si>
     <t xml:space="preserve">17.8508586883545</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2620029449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.228759765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.095796585083</t>
+    <t xml:space="preserve">17.2620048522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2287616729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0957946777344</t>
   </si>
   <si>
     <t xml:space="preserve">16.8868465423584</t>
@@ -2582,13 +2582,13 @@
     <t xml:space="preserve">16.6161632537842</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5924186706543</t>
+    <t xml:space="preserve">16.5924167633057</t>
   </si>
   <si>
     <t xml:space="preserve">15.8611001968384</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2694969177246</t>
+    <t xml:space="preserve">16.2694988250732</t>
   </si>
   <si>
     <t xml:space="preserve">16.2979907989502</t>
@@ -2597,7 +2597,7 @@
     <t xml:space="preserve">16.1175346374512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8468494415283</t>
+    <t xml:space="preserve">15.8468523025513</t>
   </si>
   <si>
     <t xml:space="preserve">16.3217353820801</t>
@@ -2612,10 +2612,10 @@
     <t xml:space="preserve">15.7186317443848</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3434762954712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9845685958862</t>
+    <t xml:space="preserve">15.3434772491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9845676422119</t>
   </si>
   <si>
     <t xml:space="preserve">15.7471265792847</t>
@@ -2624,37 +2624,37 @@
     <t xml:space="preserve">15.6046619415283</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7043867111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8848438262939</t>
+    <t xml:space="preserve">15.7043857574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8848428726196</t>
   </si>
   <si>
     <t xml:space="preserve">15.5429258346558</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1582717895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8096036911011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8665895462036</t>
+    <t xml:space="preserve">15.1582708358765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8096027374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8665885925293</t>
   </si>
   <si>
     <t xml:space="preserve">14.1420221328735</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6054039001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5721607208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0735340118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0497894287109</t>
+    <t xml:space="preserve">13.6054029464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5721616744995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0735349655151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0497903823853</t>
   </si>
   <si>
     <t xml:space="preserve">12.9738092422485</t>
@@ -2663,22 +2663,22 @@
     <t xml:space="preserve">12.3184700012207</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0477876663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2784757614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6563787460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7845973968506</t>
+    <t xml:space="preserve">12.0477867126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2784767150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.656379699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7845964431763</t>
   </si>
   <si>
     <t xml:space="preserve">9.08166599273682</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65437412261963</t>
+    <t xml:space="preserve">9.65437507629395</t>
   </si>
   <si>
     <t xml:space="preserve">10.0057888031006</t>
@@ -2687,13 +2687,13 @@
     <t xml:space="preserve">9.97254657745361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49766445159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6183891296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8625812530518</t>
+    <t xml:space="preserve">9.4976634979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6183881759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8625822067261</t>
   </si>
   <si>
     <t xml:space="preserve">12.1665077209473</t>
@@ -2702,28 +2702,28 @@
     <t xml:space="preserve">13.0877809524536</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3964548110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9690589904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2519865036011</t>
+    <t xml:space="preserve">13.3964538574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9690599441528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2519855499268</t>
   </si>
   <si>
     <t xml:space="preserve">11.9195680618286</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4921731948853</t>
+    <t xml:space="preserve">11.4921741485596</t>
   </si>
   <si>
     <t xml:space="preserve">11.2072429656982</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1597547531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1882467269897</t>
+    <t xml:space="preserve">11.1597557067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1882476806641</t>
   </si>
   <si>
     <t xml:space="preserve">11.5681552886963</t>
@@ -2732,10 +2732,10 @@
     <t xml:space="preserve">11.5586566925049</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6251401901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9765529632568</t>
+    <t xml:space="preserve">11.6251411437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9765539169312</t>
   </si>
   <si>
     <t xml:space="preserve">11.4541835784912</t>
@@ -2744,31 +2744,31 @@
     <t xml:space="preserve">11.2927227020264</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5396604537964</t>
+    <t xml:space="preserve">11.5396614074707</t>
   </si>
   <si>
     <t xml:space="preserve">10.8178396224976</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3999423980713</t>
+    <t xml:space="preserve">10.3999404907227</t>
   </si>
   <si>
     <t xml:space="preserve">10.4474306106567</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3809471130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7323608398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9128150939941</t>
+    <t xml:space="preserve">10.3809461593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7323598861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9128160476685</t>
   </si>
   <si>
     <t xml:space="preserve">10.7228622436523</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3049650192261</t>
+    <t xml:space="preserve">10.3049659729004</t>
   </si>
   <si>
     <t xml:space="preserve">10.3524532318115</t>
@@ -2777,37 +2777,37 @@
     <t xml:space="preserve">10.3144626617432</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3429574966431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4094390869141</t>
+    <t xml:space="preserve">10.3429555892944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4094400405884</t>
   </si>
   <si>
     <t xml:space="preserve">10.2574768066406</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0295333862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9060640335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89656639099121</t>
+    <t xml:space="preserve">10.0295324325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90606307983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89656543731689</t>
   </si>
   <si>
     <t xml:space="preserve">9.64962577819824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78259468078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4949188232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3469638824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9005727767944</t>
+    <t xml:space="preserve">9.78259372711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4949178695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.346962928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9005718231201</t>
   </si>
   <si>
     <t xml:space="preserve">12.2614841461182</t>
@@ -2822,28 +2822,28 @@
     <t xml:space="preserve">13.6576404571533</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2872314453125</t>
+    <t xml:space="preserve">13.2872304916382</t>
   </si>
   <si>
     <t xml:space="preserve">13.1542644500732</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8218460083008</t>
+    <t xml:space="preserve">12.8218469619751</t>
   </si>
   <si>
     <t xml:space="preserve">11.8815774917603</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7771024703979</t>
+    <t xml:space="preserve">11.7771034240723</t>
   </si>
   <si>
     <t xml:space="preserve">12.062032699585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1190185546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2899770736694</t>
+    <t xml:space="preserve">12.1190195083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2899761199951</t>
   </si>
   <si>
     <t xml:space="preserve">12.3089714050293</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">12.7078742980957</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5749073028564</t>
+    <t xml:space="preserve">12.5749063491821</t>
   </si>
   <si>
     <t xml:space="preserve">12.5844049453735</t>
@@ -2864,7 +2864,7 @@
     <t xml:space="preserve">11.8055963516235</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5111684799194</t>
+    <t xml:space="preserve">11.5111694335938</t>
   </si>
   <si>
     <t xml:space="preserve">11.7296152114868</t>
@@ -2873,10 +2873,10 @@
     <t xml:space="preserve">11.4446849822998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5206670761108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7581071853638</t>
+    <t xml:space="preserve">11.5206661224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7581081390381</t>
   </si>
   <si>
     <t xml:space="preserve">11.5871496200562</t>
@@ -2885,7 +2885,7 @@
     <t xml:space="preserve">11.4826755523682</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3402109146118</t>
+    <t xml:space="preserve">11.3402099609375</t>
   </si>
   <si>
     <t xml:space="preserve">10.9887962341309</t>
@@ -2894,19 +2894,19 @@
     <t xml:space="preserve">11.1787509918213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2262382507324</t>
+    <t xml:space="preserve">11.2262372970581</t>
   </si>
   <si>
     <t xml:space="preserve">11.2452335357666</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1027679443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1312618255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0267868041992</t>
+    <t xml:space="preserve">11.1027688980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1312627792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0267877578735</t>
   </si>
   <si>
     <t xml:space="preserve">11.0837736129761</t>
@@ -2915,10 +2915,10 @@
     <t xml:space="preserve">10.8368349075317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0552816390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2167406082153</t>
+    <t xml:space="preserve">11.0552806854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2167415618896</t>
   </si>
   <si>
     <t xml:space="preserve">10.5708999633789</t>
@@ -2933,7 +2933,7 @@
     <t xml:space="preserve">10.3619508743286</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6441354751587</t>
+    <t xml:space="preserve">11.644136428833</t>
   </si>
   <si>
     <t xml:space="preserve">11.3307132720947</t>
@@ -2942,46 +2942,46 @@
     <t xml:space="preserve">11.0932712554932</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9603042602539</t>
+    <t xml:space="preserve">10.9603033065796</t>
   </si>
   <si>
     <t xml:space="preserve">10.7608528137207</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7798480987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6753749847412</t>
+    <t xml:space="preserve">10.7798500061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6753740310669</t>
   </si>
   <si>
     <t xml:space="preserve">11.6156425476074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.463680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3971967697144</t>
+    <t xml:space="preserve">11.4636793136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3971977233887</t>
   </si>
   <si>
     <t xml:space="preserve">11.5016708374023</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7960996627808</t>
+    <t xml:space="preserve">11.7960987091064</t>
   </si>
   <si>
     <t xml:space="preserve">11.4731779098511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4256887435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5179214477539</t>
+    <t xml:space="preserve">11.4256896972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5179204940796</t>
   </si>
   <si>
     <t xml:space="preserve">12.565408706665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0810289382935</t>
+    <t xml:space="preserve">12.0810279846191</t>
   </si>
   <si>
     <t xml:space="preserve">11.6821269989014</t>
@@ -2990,16 +2990,16 @@
     <t xml:space="preserve">11.6061458587646</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1095209121704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0145454406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9385633468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.957558631897</t>
+    <t xml:space="preserve">12.1095218658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0145435333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9385623931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9575576782227</t>
   </si>
   <si>
     <t xml:space="preserve">11.9860515594482</t>
@@ -3020,19 +3020,19 @@
     <t xml:space="preserve">12.5464134216309</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2044973373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4039497375488</t>
+    <t xml:space="preserve">12.2044982910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4039487838745</t>
   </si>
   <si>
     <t xml:space="preserve">12.8978271484375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1950006484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8910751342773</t>
+    <t xml:space="preserve">12.1949996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8910760879517</t>
   </si>
   <si>
     <t xml:space="preserve">11.67262840271</t>
@@ -3044,43 +3044,43 @@
     <t xml:space="preserve">10.6943693161011</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5139141082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7988433837891</t>
+    <t xml:space="preserve">10.5139131546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7988443374634</t>
   </si>
   <si>
     <t xml:space="preserve">11.0647783279419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.359206199646</t>
+    <t xml:space="preserve">11.3592052459717</t>
   </si>
   <si>
     <t xml:space="preserve">12.3659582138062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7933540344238</t>
+    <t xml:space="preserve">12.7933530807495</t>
   </si>
   <si>
     <t xml:space="preserve">13.3537158966064</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7811098098755</t>
+    <t xml:space="preserve">13.7811107635498</t>
   </si>
   <si>
     <t xml:space="preserve">13.7146263122559</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9235754013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9330739974976</t>
+    <t xml:space="preserve">13.9235744476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9330730438232</t>
   </si>
   <si>
     <t xml:space="preserve">14.2369976043701</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3414716720581</t>
+    <t xml:space="preserve">14.3414726257324</t>
   </si>
   <si>
     <t xml:space="preserve">14.0470447540283</t>
@@ -3095,16 +3095,16 @@
     <t xml:space="preserve">14.1515197753906</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2464962005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4269514083862</t>
+    <t xml:space="preserve">14.2464952468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4269504547119</t>
   </si>
   <si>
     <t xml:space="preserve">14.4649410247803</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9113311767578</t>
+    <t xml:space="preserve">14.9113321304321</t>
   </si>
   <si>
     <t xml:space="preserve">14.4934358596802</t>
@@ -3113,16 +3113,16 @@
     <t xml:space="preserve">14.3509693145752</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5979099273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7498712539673</t>
+    <t xml:space="preserve">14.5979080200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7498722076416</t>
   </si>
   <si>
     <t xml:space="preserve">15.1487741470337</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8828392028809</t>
+    <t xml:space="preserve">14.8828401565552</t>
   </si>
   <si>
     <t xml:space="preserve">14.8543462753296</t>
@@ -3149,19 +3149,19 @@
     <t xml:space="preserve">15.0632944107056</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9493227005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7688674926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7118816375732</t>
+    <t xml:space="preserve">14.9493217468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7688684463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7118806838989</t>
   </si>
   <si>
     <t xml:space="preserve">14.5884113311768</t>
   </si>
   <si>
-    <t xml:space="preserve">14.578914642334</t>
+    <t xml:space="preserve">14.5789136886597</t>
   </si>
   <si>
     <t xml:space="preserve">14.4079561233521</t>
@@ -3170,16 +3170,16 @@
     <t xml:space="preserve">14.5504207611084</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5314254760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9615659713745</t>
+    <t xml:space="preserve">14.5314264297485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9615650177002</t>
   </si>
   <si>
     <t xml:space="preserve">14.2085056304932</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4459457397461</t>
+    <t xml:space="preserve">14.4459466934204</t>
   </si>
   <si>
     <t xml:space="preserve">15.29123878479</t>
@@ -3191,10 +3191,10 @@
     <t xml:space="preserve">15.0537977218628</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8041124343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6711444854736</t>
+    <t xml:space="preserve">15.8041133880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6711454391479</t>
   </si>
   <si>
     <t xml:space="preserve">15.2627458572388</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">14.9588203430176</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0443000793457</t>
+    <t xml:space="preserve">15.0442991256714</t>
   </si>
   <si>
     <t xml:space="preserve">14.721378326416</t>
@@ -3215,22 +3215,22 @@
     <t xml:space="preserve">14.4364490509033</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7403745651245</t>
+    <t xml:space="preserve">14.7403755187988</t>
   </si>
   <si>
     <t xml:space="preserve">15.006308555603</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0822906494141</t>
+    <t xml:space="preserve">15.0822896957397</t>
   </si>
   <si>
     <t xml:space="preserve">14.9778165817261</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6928863525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7783641815186</t>
+    <t xml:space="preserve">14.6928853988647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7783651351929</t>
   </si>
   <si>
     <t xml:space="preserve">14.8258533477783</t>
@@ -3239,7 +3239,7 @@
     <t xml:space="preserve">15.2057600021362</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1202802658081</t>
+    <t xml:space="preserve">15.1202812194824</t>
   </si>
   <si>
     <t xml:space="preserve">15.0917882919312</t>
@@ -3254,7 +3254,7 @@
     <t xml:space="preserve">14.9873132705688</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8705949783325</t>
+    <t xml:space="preserve">15.8705959320068</t>
   </si>
   <si>
     <t xml:space="preserve">16.0225601196289</t>
@@ -3263,13 +3263,13 @@
     <t xml:space="preserve">16.0320568084717</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8231086730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9370803833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7376270294189</t>
+    <t xml:space="preserve">15.8231077194214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9370794296265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7376279830933</t>
   </si>
   <si>
     <t xml:space="preserve">15.4906892776489</t>
@@ -3278,31 +3278,31 @@
     <t xml:space="preserve">15.7091360092163</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3102350234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3672208786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3387260437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6996402740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6853904724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6189069747925</t>
+    <t xml:space="preserve">15.3102340698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3672199249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3387269973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6996374130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6853914260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6189079284668</t>
   </si>
   <si>
     <t xml:space="preserve">15.428955078125</t>
   </si>
   <si>
-    <t xml:space="preserve">15.637903213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.739631652832</t>
+    <t xml:space="preserve">15.6379022598267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7396335601807</t>
   </si>
   <si>
     <t xml:space="preserve">16.8678512573242</t>
@@ -3311,7 +3311,7 @@
     <t xml:space="preserve">16.8725986480713</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4784488677979</t>
+    <t xml:space="preserve">16.4784469604492</t>
   </si>
   <si>
     <t xml:space="preserve">17.0340595245361</t>
@@ -3323,10 +3323,10 @@
     <t xml:space="preserve">17.4567050933838</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0388088226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2904987335205</t>
+    <t xml:space="preserve">17.0388107299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2904968261719</t>
   </si>
   <si>
     <t xml:space="preserve">17.0815486907959</t>
@@ -3335,31 +3335,31 @@
     <t xml:space="preserve">17.0245628356934</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9770736694336</t>
+    <t xml:space="preserve">16.9770755767822</t>
   </si>
   <si>
     <t xml:space="preserve">17.2572555541992</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4614562988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4187164306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2117691040039</t>
+    <t xml:space="preserve">17.4614543914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4187145233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2117710113525</t>
   </si>
   <si>
     <t xml:space="preserve">18.3589839935303</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1975231170654</t>
+    <t xml:space="preserve">18.1975250244141</t>
   </si>
   <si>
     <t xml:space="preserve">18.1500358581543</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2307662963867</t>
+    <t xml:space="preserve">18.2307643890381</t>
   </si>
   <si>
     <t xml:space="preserve">18.0360641479492</t>
@@ -3371,16 +3371,16 @@
     <t xml:space="preserve">17.9553356170654</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6846504211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0408115386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3304920196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3209934234619</t>
+    <t xml:space="preserve">17.6846523284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0408134460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3304901123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3209953308105</t>
   </si>
   <si>
     <t xml:space="preserve">18.368480682373</t>
@@ -3389,7 +3389,7 @@
     <t xml:space="preserve">18.3019981384277</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3542366027832</t>
+    <t xml:space="preserve">18.3542346954346</t>
   </si>
   <si>
     <t xml:space="preserve">18.3969745635986</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">18.1832790374756</t>
   </si>
   <si>
-    <t xml:space="preserve">18.444465637207</t>
+    <t xml:space="preserve">18.4444637298584</t>
   </si>
   <si>
     <t xml:space="preserve">18.8956031799316</t>
@@ -3416,10 +3416,10 @@
     <t xml:space="preserve">18.6961498260498</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5584373474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.335241317749</t>
+    <t xml:space="preserve">18.5584354400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3352394104004</t>
   </si>
   <si>
     <t xml:space="preserve">17.8461112976074</t>
@@ -3428,7 +3428,7 @@
     <t xml:space="preserve">17.1527805328369</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1812744140625</t>
+    <t xml:space="preserve">17.1812725067139</t>
   </si>
   <si>
     <t xml:space="preserve">17.0673007965088</t>
@@ -3437,22 +3437,22 @@
     <t xml:space="preserve">17.1575298309326</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6114120483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5021896362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7253856658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8773498535156</t>
+    <t xml:space="preserve">16.6114139556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5021915435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7253875732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.877347946167</t>
   </si>
   <si>
     <t xml:space="preserve">16.4214611053467</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9798192977905</t>
+    <t xml:space="preserve">15.9798202514648</t>
   </si>
   <si>
     <t xml:space="preserve">16.0985412597656</t>
@@ -3461,28 +3461,28 @@
     <t xml:space="preserve">16.0083122253418</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2505054473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4736976623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1697731018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0463027954102</t>
+    <t xml:space="preserve">16.2505035400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4736957550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.169771194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0463047027588</t>
   </si>
   <si>
     <t xml:space="preserve">16.0368061065674</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9988136291504</t>
+    <t xml:space="preserve">15.9988145828247</t>
   </si>
   <si>
     <t xml:space="preserve">16.2600021362305</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0652980804443</t>
+    <t xml:space="preserve">16.065299987793</t>
   </si>
   <si>
     <t xml:space="preserve">16.0510520935059</t>
@@ -3491,7 +3491,7 @@
     <t xml:space="preserve">17.1100406646729</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3949699401855</t>
+    <t xml:space="preserve">17.3949718475342</t>
   </si>
   <si>
     <t xml:space="preserve">18.4919509887695</t>
@@ -3500,34 +3500,34 @@
     <t xml:space="preserve">17.5896739959717</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6609058380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0008163452148</t>
+    <t xml:space="preserve">17.6609039306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0008182525635</t>
   </si>
   <si>
     <t xml:space="preserve">16.6731491088867</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5164356231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7328796386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7423791885376</t>
+    <t xml:space="preserve">16.5164375305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7328805923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7423782348633</t>
   </si>
   <si>
     <t xml:space="preserve">16.1460285186768</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9275808334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9703226089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6541538238525</t>
+    <t xml:space="preserve">15.9275827407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9703216552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6541519165039</t>
   </si>
   <si>
     <t xml:space="preserve">16.7586288452148</t>
@@ -3548,13 +3548,13 @@
     <t xml:space="preserve">16.8251113891602</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7206363677979</t>
+    <t xml:space="preserve">16.7206382751465</t>
   </si>
   <si>
     <t xml:space="preserve">16.9628295898438</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9438323974609</t>
+    <t xml:space="preserve">16.9438304901123</t>
   </si>
   <si>
     <t xml:space="preserve">16.8298587799072</t>
@@ -3575,19 +3575,19 @@
     <t xml:space="preserve">16.7111377716064</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2145156860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4424591064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3427352905273</t>
+    <t xml:space="preserve">17.2145175933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4424610137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3427333831787</t>
   </si>
   <si>
     <t xml:space="preserve">17.4662036895752</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7178916931152</t>
+    <t xml:space="preserve">17.7178936004639</t>
   </si>
   <si>
     <t xml:space="preserve">17.7748775482178</t>
@@ -3605,22 +3605,22 @@
     <t xml:space="preserve">18.7911281585693</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9715824127197</t>
+    <t xml:space="preserve">18.9715843200684</t>
   </si>
   <si>
     <t xml:space="preserve">17.945837020874</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4302158355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5536880493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7626323699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0903034210205</t>
+    <t xml:space="preserve">18.4302177429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5536861419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7626342773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0903053283691</t>
   </si>
   <si>
     <t xml:space="preserve">19.3752346038818</t>
@@ -3638,28 +3638,28 @@
     <t xml:space="preserve">20.5529441833496</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6221733093262</t>
+    <t xml:space="preserve">19.6221752166748</t>
   </si>
   <si>
     <t xml:space="preserve">19.1377925872803</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6316699981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4579696655273</t>
+    <t xml:space="preserve">19.6316719055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4579677581787</t>
   </si>
   <si>
     <t xml:space="preserve">20.6289253234863</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0373249053955</t>
+    <t xml:space="preserve">21.0373229980469</t>
   </si>
   <si>
     <t xml:space="preserve">21.4457244873047</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9898376464844</t>
+    <t xml:space="preserve">20.9898357391357</t>
   </si>
   <si>
     <t xml:space="preserve">20.7523956298828</t>
@@ -3674,46 +3674,46 @@
     <t xml:space="preserve">20.0970573425293</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7903842926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7144050598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0278282165527</t>
+    <t xml:space="preserve">20.7903861999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7144031524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0278263092041</t>
   </si>
   <si>
     <t xml:space="preserve">21.0183296203613</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0943088531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4172325134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3982391357422</t>
+    <t xml:space="preserve">21.094310760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4172306060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3982372283936</t>
   </si>
   <si>
     <t xml:space="preserve">21.7021617889404</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5691947937012</t>
+    <t xml:space="preserve">21.5691928863525</t>
   </si>
   <si>
     <t xml:space="preserve">22.0820693969727</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5976867675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6261825561523</t>
+    <t xml:space="preserve">21.5976886749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6261806488037</t>
   </si>
   <si>
     <t xml:space="preserve">19.4797096252441</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0998020172119</t>
+    <t xml:space="preserve">19.0998001098633</t>
   </si>
   <si>
     <t xml:space="preserve">19.536693572998</t>
@@ -3728,13 +3728,13 @@
     <t xml:space="preserve">18.0550594329834</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4946956634521</t>
+    <t xml:space="preserve">17.4946975708008</t>
   </si>
   <si>
     <t xml:space="preserve">18.2212677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9743270874023</t>
+    <t xml:space="preserve">17.974328994751</t>
   </si>
   <si>
     <t xml:space="preserve">18.5916767120361</t>
@@ -3743,7 +3743,7 @@
     <t xml:space="preserve">18.5394401550293</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0977973937988</t>
+    <t xml:space="preserve">18.0977993011475</t>
   </si>
   <si>
     <t xml:space="preserve">18.0503082275391</t>
@@ -3764,7 +3764,7 @@
     <t xml:space="preserve">18.68190574646</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7721328735352</t>
+    <t xml:space="preserve">18.7721309661865</t>
   </si>
   <si>
     <t xml:space="preserve">18.8006267547607</t>
@@ -3782,40 +3782,40 @@
     <t xml:space="preserve">18.6581611633301</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4492111206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6324138641357</t>
+    <t xml:space="preserve">18.4492130279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6324119567871</t>
   </si>
   <si>
     <t xml:space="preserve">17.7368869781494</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1242904663086</t>
+    <t xml:space="preserve">17.12428855896</t>
   </si>
   <si>
     <t xml:space="preserve">15.1867637634277</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8306016921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5076818466187</t>
+    <t xml:space="preserve">14.8306007385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5076808929443</t>
   </si>
   <si>
     <t xml:space="preserve">15.9133348464966</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3529739379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.457447052002</t>
+    <t xml:space="preserve">15.3529748916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4574489593506</t>
   </si>
   <si>
     <t xml:space="preserve">14.8733415603638</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5856676101685</t>
+    <t xml:space="preserve">15.5856657028198</t>
   </si>
   <si>
     <t xml:space="preserve">15.81360912323</t>
@@ -3824,10 +3824,10 @@
     <t xml:space="preserve">15.5334281921387</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2390012741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2532482147217</t>
+    <t xml:space="preserve">15.2390022277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2532472610474</t>
   </si>
   <si>
     <t xml:space="preserve">15.5191822052002</t>
@@ -3836,7 +3836,7 @@
     <t xml:space="preserve">15.8278579711914</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7681274414062</t>
+    <t xml:space="preserve">16.7681255340576</t>
   </si>
   <si>
     <t xml:space="preserve">16.316987991333</t>
@@ -3851,13 +3851,13 @@
     <t xml:space="preserve">15.6331548690796</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6521482467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.889591217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5096845626831</t>
+    <t xml:space="preserve">15.6521492004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8895902633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5096855163574</t>
   </si>
   <si>
     <t xml:space="preserve">14.7308769226074</t>
@@ -3866,10 +3866,10 @@
     <t xml:space="preserve">14.8638439178467</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1392765045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7851181030273</t>
+    <t xml:space="preserve">15.1392755508423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7851190567017</t>
   </si>
   <si>
     <t xml:space="preserve">14.3034820556641</t>
@@ -3881,7 +3881,7 @@
     <t xml:space="preserve">13.8285989761353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.812349319458</t>
+    <t xml:space="preserve">12.8123483657837</t>
   </si>
   <si>
     <t xml:space="preserve">14.1040306091309</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">14.1990070343018</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0158061981201</t>
+    <t xml:space="preserve">15.0158071517944</t>
   </si>
   <si>
     <t xml:space="preserve">14.5219278335571</t>
@@ -6141,6 +6141,9 @@
   </si>
   <si>
     <t xml:space="preserve">6.15000009536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07000017166138</t>
   </si>
 </sst>
 </file>
@@ -73689,7 +73692,7 @@
     </row>
     <row r="2586">
       <c r="A2586" s="1" t="n">
-        <v>46086.6912152778</v>
+        <v>46086.3333333333</v>
       </c>
       <c r="B2586" t="n">
         <v>337752</v>
@@ -73710,6 +73713,32 @@
         <v>2042</v>
       </c>
       <c r="H2586" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2587">
+      <c r="A2587" s="1" t="n">
+        <v>46087.6911458333</v>
+      </c>
+      <c r="B2587" t="n">
+        <v>226755</v>
+      </c>
+      <c r="C2587" t="n">
+        <v>6.20499992370605</v>
+      </c>
+      <c r="D2587" t="n">
+        <v>5.95499992370605</v>
+      </c>
+      <c r="E2587" t="n">
+        <v>6.17999982833862</v>
+      </c>
+      <c r="F2587" t="n">
+        <v>6.07000017166138</v>
+      </c>
+      <c r="G2587" t="s">
+        <v>2043</v>
+      </c>
+      <c r="H2587" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2049" uniqueCount="2049">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2050" uniqueCount="2050">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,61 +38,61 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2763500213623</t>
+    <t xml:space="preserve">18.2763538360596</t>
   </si>
   <si>
     <t xml:space="preserve">SFER.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">18.01096534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4978809356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9401950836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6836528778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2498149871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4086742401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1344375610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8425121307373</t>
+    <t xml:space="preserve">18.0109634399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4978828430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9401931762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.683650970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.249813079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4086723327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1344394683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8425102233887</t>
   </si>
   <si>
     <t xml:space="preserve">18.4621238708496</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2851982116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0994262695312</t>
+    <t xml:space="preserve">18.2851963043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0994281768799</t>
   </si>
   <si>
     <t xml:space="preserve">17.6394214630127</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5686550140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1878871917725</t>
+    <t xml:space="preserve">17.5686511993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1878910064697</t>
   </si>
   <si>
     <t xml:space="preserve">18.4798145294189</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2232761383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7632675170898</t>
+    <t xml:space="preserve">18.223274230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7632694244385</t>
   </si>
   <si>
     <t xml:space="preserve">18.3913536071777</t>
@@ -101,40 +101,40 @@
     <t xml:space="preserve">18.6744327545166</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9578838348389</t>
+    <t xml:space="preserve">17.9578857421875</t>
   </si>
   <si>
     <t xml:space="preserve">18.2055835723877</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2586555480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0817317962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3563423156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9051818847656</t>
+    <t xml:space="preserve">18.2586574554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0817337036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3563442230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9051837921143</t>
   </si>
   <si>
     <t xml:space="preserve">17.1617221832275</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6486415863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0201835632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.48903465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6305770874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4090461730957</t>
+    <t xml:space="preserve">16.6486434936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0201816558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4890384674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6305751800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4090442657471</t>
   </si>
   <si>
     <t xml:space="preserve">18.4532775878906</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">18.9752063751221</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1348133087158</t>
+    <t xml:space="preserve">18.1348114013672</t>
   </si>
   <si>
     <t xml:space="preserve">17.3121109008789</t>
@@ -158,25 +158,25 @@
     <t xml:space="preserve">19.0194358825684</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0017433166504</t>
+    <t xml:space="preserve">19.001745223999</t>
   </si>
   <si>
     <t xml:space="preserve">18.8513584136963</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3113613128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9925212860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9482917785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7271327972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3379039764404</t>
+    <t xml:space="preserve">19.3113632202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.992525100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9482936859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7271366119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3379020690918</t>
   </si>
   <si>
     <t xml:space="preserve">19.6475200653076</t>
@@ -185,40 +185,40 @@
     <t xml:space="preserve">19.9836769104004</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1167469024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.444055557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0367546081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1782932281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4971313476562</t>
+    <t xml:space="preserve">19.1167449951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4440574645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0367565155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1782970428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4971370697021</t>
   </si>
   <si>
     <t xml:space="preserve">19.4705963134766</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9663600921631</t>
+    <t xml:space="preserve">18.9663581848145</t>
   </si>
   <si>
     <t xml:space="preserve">19.4794406890869</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9129047393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8686771392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4175205230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.869047164917</t>
+    <t xml:space="preserve">19.9129066467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.868673324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4175186157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8690509796143</t>
   </si>
   <si>
     <t xml:space="preserve">18.8336658477783</t>
@@ -227,34 +227,34 @@
     <t xml:space="preserve">18.5151996612549</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9309711456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8955879211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5240459442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9486656188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7982807159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8778972625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2936687469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8071250915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3205795288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3648109436035</t>
+    <t xml:space="preserve">18.9309749603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8955898284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5240478515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9486694335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7982788085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8778953552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2936706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8071269989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3205814361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3648128509521</t>
   </si>
   <si>
     <t xml:space="preserve">17.8251934051514</t>
@@ -266,64 +266,64 @@
     <t xml:space="preserve">18.3117351531982</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8782691955566</t>
+    <t xml:space="preserve">17.878267288208</t>
   </si>
   <si>
     <t xml:space="preserve">18.0021190643311</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7190380096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.444803237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1440296173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5509605407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9844284057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4182662963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9313488006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7367286682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.648265838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.593936920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.81125831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7025966644287</t>
+    <t xml:space="preserve">17.7190399169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4448051452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1440315246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5509586334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9844245910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4182682037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9313468933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7367305755615</t>
   </si>
   <si>
     <t xml:space="preserve">17.6482677459717</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5305519104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4128379821777</t>
+    <t xml:space="preserve">17.5939388275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8112602233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7025985717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6482696533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.530553817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4128360748291</t>
   </si>
   <si>
     <t xml:space="preserve">17.3041763305664</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4762229919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4309482574463</t>
+    <t xml:space="preserve">17.4762191772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.430944442749</t>
   </si>
   <si>
     <t xml:space="preserve">17.4852771759033</t>
@@ -335,25 +335,25 @@
     <t xml:space="preserve">17.6844882965088</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1502437591553</t>
+    <t xml:space="preserve">17.150239944458</t>
   </si>
   <si>
     <t xml:space="preserve">16.7155990600586</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5435543060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0415782928467</t>
+    <t xml:space="preserve">16.5435523986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0415802001953</t>
   </si>
   <si>
     <t xml:space="preserve">17.0778007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8384208679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9380302429199</t>
+    <t xml:space="preserve">17.8384246826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9380264282227</t>
   </si>
   <si>
     <t xml:space="preserve">17.7297630310059</t>
@@ -365,16 +365,16 @@
     <t xml:space="preserve">18.1825141906738</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8514232635498</t>
+    <t xml:space="preserve">16.8514251708984</t>
   </si>
   <si>
     <t xml:space="preserve">16.3896179199219</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6793804168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2628479003906</t>
+    <t xml:space="preserve">16.6793766021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.262845993042</t>
   </si>
   <si>
     <t xml:space="preserve">16.5254440307617</t>
@@ -386,22 +386,22 @@
     <t xml:space="preserve">16.8061485290527</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8242588043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0726890563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8734827041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3624496459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4439487457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6974906921387</t>
+    <t xml:space="preserve">16.8242568969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0726909637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8734798431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3624515533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4439468383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.69748878479</t>
   </si>
   <si>
     <t xml:space="preserve">17.0959091186523</t>
@@ -413,34 +413,34 @@
     <t xml:space="preserve">17.086856842041</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0325241088867</t>
+    <t xml:space="preserve">17.0325260162354</t>
   </si>
   <si>
     <t xml:space="preserve">17.3403968811035</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9018077850342</t>
+    <t xml:space="preserve">17.9018115997314</t>
   </si>
   <si>
     <t xml:space="preserve">18.1372413635254</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9289741516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.771089553833</t>
+    <t xml:space="preserve">17.9289722442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7710914611816</t>
   </si>
   <si>
     <t xml:space="preserve">18.6352672576904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0699081420898</t>
+    <t xml:space="preserve">19.0699100494385</t>
   </si>
   <si>
     <t xml:space="preserve">19.2147903442383</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6262130737305</t>
+    <t xml:space="preserve">18.6262111663818</t>
   </si>
   <si>
     <t xml:space="preserve">18.4994411468506</t>
@@ -449,13 +449,13 @@
     <t xml:space="preserve">18.2187347412109</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7167625427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5809364318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.762035369873</t>
+    <t xml:space="preserve">18.716760635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5809383392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7620372772217</t>
   </si>
   <si>
     <t xml:space="preserve">18.8073120117188</t>
@@ -464,25 +464,25 @@
     <t xml:space="preserve">18.9431381225586</t>
   </si>
   <si>
-    <t xml:space="preserve">19.04274559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6624317169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4722747802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6171550750732</t>
+    <t xml:space="preserve">19.0427417755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6624355316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4722766876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6171569824219</t>
   </si>
   <si>
     <t xml:space="preserve">18.7529792785645</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9703025817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6805400848389</t>
+    <t xml:space="preserve">18.9703044891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6805419921875</t>
   </si>
   <si>
     <t xml:space="preserve">18.6081008911133</t>
@@ -491,37 +491,37 @@
     <t xml:space="preserve">18.653377532959</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5175514221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.870698928833</t>
+    <t xml:space="preserve">18.5175552368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8706970214844</t>
   </si>
   <si>
     <t xml:space="preserve">18.6986503601074</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1061305999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9210815429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6947040557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5588817596436</t>
+    <t xml:space="preserve">19.106128692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9210796356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6947059631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5588798522949</t>
   </si>
   <si>
     <t xml:space="preserve">19.4592742919922</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3143939971924</t>
+    <t xml:space="preserve">19.314395904541</t>
   </si>
   <si>
     <t xml:space="preserve">18.8888092041016</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1332950592041</t>
+    <t xml:space="preserve">19.1332931518555</t>
   </si>
   <si>
     <t xml:space="preserve">19.1604595184326</t>
@@ -530,94 +530,94 @@
     <t xml:space="preserve">19.9391918182373</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4553298950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3557224273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3104496002197</t>
+    <t xml:space="preserve">20.4553279876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3557205200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3104476928711</t>
   </si>
   <si>
     <t xml:space="preserve">20.3919448852539</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4643840789795</t>
+    <t xml:space="preserve">20.4643859863281</t>
   </si>
   <si>
     <t xml:space="preserve">20.6907596588135</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8446979522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7994194030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4009990692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1021842956543</t>
+    <t xml:space="preserve">20.8446960449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7994213104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4009971618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1021823883057</t>
   </si>
   <si>
     <t xml:space="preserve">20.5277690887451</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3647785186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5458793640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7541446685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4191074371338</t>
+    <t xml:space="preserve">20.3647766113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.545877456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7541465759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4191093444824</t>
   </si>
   <si>
     <t xml:space="preserve">20.0116329193115</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2651748657227</t>
+    <t xml:space="preserve">20.2651710510254</t>
   </si>
   <si>
     <t xml:space="preserve">20.3285598754883</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0387992858887</t>
+    <t xml:space="preserve">20.0387954711914</t>
   </si>
   <si>
     <t xml:space="preserve">20.1474590301514</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2289524078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5006046295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5639877319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1836795806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.549825668335</t>
+    <t xml:space="preserve">20.2289543151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.500602722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5639896392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1836814880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5498237609863</t>
   </si>
   <si>
     <t xml:space="preserve">19.4140014648438</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5045490264893</t>
+    <t xml:space="preserve">19.5045509338379</t>
   </si>
   <si>
     <t xml:space="preserve">19.7218723297119</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7943134307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5226612091064</t>
+    <t xml:space="preserve">19.7943115234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5226593017578</t>
   </si>
   <si>
     <t xml:space="preserve">19.8305320739746</t>
@@ -626,19 +626,19 @@
     <t xml:space="preserve">19.9120273590088</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7490348815918</t>
+    <t xml:space="preserve">19.7490367889404</t>
   </si>
   <si>
     <t xml:space="preserve">18.0919647216797</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3002300262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3273983001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2459011077881</t>
+    <t xml:space="preserve">18.3002281188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3273963928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2458992004395</t>
   </si>
   <si>
     <t xml:space="preserve">18.0104675292969</t>
@@ -647,49 +647,49 @@
     <t xml:space="preserve">17.7388191223145</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8565330505371</t>
+    <t xml:space="preserve">17.8565349578857</t>
   </si>
   <si>
     <t xml:space="preserve">17.8203125</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6392097473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3455066680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3907833099365</t>
+    <t xml:space="preserve">17.6392116546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3455047607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3907794952393</t>
   </si>
   <si>
     <t xml:space="preserve">19.1514053344727</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2872314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3958892822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.377779006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1151828765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5860443115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2600650787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3738327026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3466682434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2380104064941</t>
+    <t xml:space="preserve">19.2872276306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3958930969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3777809143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1151847839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5860462188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.260066986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.373836517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3466663360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2380084991455</t>
   </si>
   <si>
     <t xml:space="preserve">20.1293487548828</t>
@@ -698,16 +698,16 @@
     <t xml:space="preserve">20.1565132141113</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8084754943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6183204650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4785480499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5328788757324</t>
+    <t xml:space="preserve">20.8084774017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6183223724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4785461425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5328807830811</t>
   </si>
   <si>
     <t xml:space="preserve">22.0671272277832</t>
@@ -716,10 +716,10 @@
     <t xml:space="preserve">22.0580711364746</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2572822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2935009002686</t>
+    <t xml:space="preserve">22.2572803497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2935047149658</t>
   </si>
   <si>
     <t xml:space="preserve">22.3025550842285</t>
@@ -728,34 +728,34 @@
     <t xml:space="preserve">22.3206653594971</t>
   </si>
   <si>
-    <t xml:space="preserve">22.275390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2391700744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8186931610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0722332000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8911361694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1537303924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0993995666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5923175811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3568840026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9092464447021</t>
+    <t xml:space="preserve">22.2753925323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2391719818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8186950683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0722351074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.891134262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1537284851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.099401473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5923156738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3568897247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9092426300049</t>
   </si>
   <si>
     <t xml:space="preserve">22.1757869720459</t>
@@ -764,19 +764,19 @@
     <t xml:space="preserve">22.1395664215088</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6064853668213</t>
+    <t xml:space="preserve">23.606481552124</t>
   </si>
   <si>
     <t xml:space="preserve">23.7513618469238</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1226177215576</t>
+    <t xml:space="preserve">24.1226196289062</t>
   </si>
   <si>
     <t xml:space="preserve">23.6427021026611</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6879787445068</t>
+    <t xml:space="preserve">23.6879768371582</t>
   </si>
   <si>
     <t xml:space="preserve">23.561206817627</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">23.7423076629639</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7241992950439</t>
+    <t xml:space="preserve">23.7242012023926</t>
   </si>
   <si>
     <t xml:space="preserve">23.6336498260498</t>
@@ -794,85 +794,85 @@
     <t xml:space="preserve">23.823802947998</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6970348358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0139579772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.285608291626</t>
+    <t xml:space="preserve">23.6970329284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0139598846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2856101989746</t>
   </si>
   <si>
     <t xml:space="preserve">24.0682888031006</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9777374267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2946624755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4304885864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6115913391113</t>
+    <t xml:space="preserve">23.9777393341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2946643829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4304904937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.61159324646</t>
   </si>
   <si>
     <t xml:space="preserve">24.7655277252197</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1911106109619</t>
+    <t xml:space="preserve">25.1911125183105</t>
   </si>
   <si>
     <t xml:space="preserve">25.3903255462646</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4265441894531</t>
+    <t xml:space="preserve">25.4265460968018</t>
   </si>
   <si>
     <t xml:space="preserve">25.6167011260986</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6710338592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6529216766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7615833282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5352058410645</t>
+    <t xml:space="preserve">25.6710319519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6529197692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7615814208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5352077484131</t>
   </si>
   <si>
     <t xml:space="preserve">24.955680847168</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9013519287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0643444061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8017482757568</t>
+    <t xml:space="preserve">24.9013538360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0643424987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8017463684082</t>
   </si>
   <si>
     <t xml:space="preserve">24.6206474304199</t>
   </si>
   <si>
-    <t xml:space="preserve">24.937572479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3722171783447</t>
+    <t xml:space="preserve">24.9375743865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3722133636475</t>
   </si>
   <si>
     <t xml:space="preserve">25.62575340271</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2273330688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1730041503906</t>
+    <t xml:space="preserve">25.2273368835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.173002243042</t>
   </si>
   <si>
     <t xml:space="preserve">25.1639499664307</t>
@@ -887,10 +887,10 @@
     <t xml:space="preserve">25.2907199859619</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1277294158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7434711456299</t>
+    <t xml:space="preserve">25.1277275085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7434692382812</t>
   </si>
   <si>
     <t xml:space="preserve">25.5442600250244</t>
@@ -905,43 +905,43 @@
     <t xml:space="preserve">25.2635536193848</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0824527740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7836399078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4214344024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2674999237061</t>
+    <t xml:space="preserve">25.0824565887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7836360931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4214363098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2674980163574</t>
   </si>
   <si>
     <t xml:space="preserve">25.5261516571045</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1237812042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1871662139893</t>
+    <t xml:space="preserve">26.1237831115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1871681213379</t>
   </si>
   <si>
     <t xml:space="preserve">26.6308650970459</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4859848022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3229942321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6761360168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.893461227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2596111297607</t>
+    <t xml:space="preserve">26.4859828948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3229923248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6761379241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8934631347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2596092224121</t>
   </si>
   <si>
     <t xml:space="preserve">26.6670837402344</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">26.9115695953369</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6037006378174</t>
+    <t xml:space="preserve">26.6036987304688</t>
   </si>
   <si>
     <t xml:space="preserve">26.5946464538574</t>
@@ -962,16 +962,16 @@
     <t xml:space="preserve">25.3269386291504</t>
   </si>
   <si>
-    <t xml:space="preserve">25.834020614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8984451293945</t>
+    <t xml:space="preserve">25.8340225219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8984432220459</t>
   </si>
   <si>
     <t xml:space="preserve">26.0641059875488</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7112045288086</t>
+    <t xml:space="preserve">24.7112007141113</t>
   </si>
   <si>
     <t xml:space="preserve">23.6159934997559</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">22.8705158233643</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8613109588623</t>
+    <t xml:space="preserve">22.8613147735596</t>
   </si>
   <si>
     <t xml:space="preserve">23.2662658691406</t>
@@ -998,10 +998,10 @@
     <t xml:space="preserve">23.2386531829834</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0453853607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8889217376709</t>
+    <t xml:space="preserve">23.0453834533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8889236450195</t>
   </si>
   <si>
     <t xml:space="preserve">22.0882263183594</t>
@@ -1013,22 +1013,22 @@
     <t xml:space="preserve">22.2262763977051</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3827342987061</t>
+    <t xml:space="preserve">22.3827323913574</t>
   </si>
   <si>
     <t xml:space="preserve">22.3643283843994</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7416667938232</t>
+    <t xml:space="preserve">22.7416687011719</t>
   </si>
   <si>
     <t xml:space="preserve">22.95334815979</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8797206878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2846717834473</t>
+    <t xml:space="preserve">22.8797225952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2846698760986</t>
   </si>
   <si>
     <t xml:space="preserve">23.4871463775635</t>
@@ -1037,13 +1037,13 @@
     <t xml:space="preserve">23.4319248199463</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8060932159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0269775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6036167144775</t>
+    <t xml:space="preserve">22.806095123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0269756317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6036186218262</t>
   </si>
   <si>
     <t xml:space="preserve">22.2538871765137</t>
@@ -1058,28 +1058,28 @@
     <t xml:space="preserve">21.7200889587402</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5544261932373</t>
+    <t xml:space="preserve">21.5544281005859</t>
   </si>
   <si>
     <t xml:space="preserve">21.6740703582764</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6280536651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1678810119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2046966552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1218662261963</t>
+    <t xml:space="preserve">21.6280555725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1678829193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2046985626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1218681335449</t>
   </si>
   <si>
     <t xml:space="preserve">21.4163761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5084075927734</t>
+    <t xml:space="preserve">21.5084095001221</t>
   </si>
   <si>
     <t xml:space="preserve">21.9133605957031</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">22.3735313415527</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2170715332031</t>
+    <t xml:space="preserve">22.2170734405518</t>
   </si>
   <si>
     <t xml:space="preserve">22.4103450775146</t>
@@ -1106,7 +1106,7 @@
     <t xml:space="preserve">22.5299911499023</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6312274932861</t>
+    <t xml:space="preserve">22.6312294006348</t>
   </si>
   <si>
     <t xml:space="preserve">22.6404323577881</t>
@@ -1115,61 +1115,61 @@
     <t xml:space="preserve">22.5576019287109</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4255790710449</t>
+    <t xml:space="preserve">21.4255809783936</t>
   </si>
   <si>
     <t xml:space="preserve">21.6556663513184</t>
   </si>
   <si>
-    <t xml:space="preserve">22.263090133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5391941070557</t>
+    <t xml:space="preserve">22.2630920410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.539192199707</t>
   </si>
   <si>
     <t xml:space="preserve">22.3551254272461</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0514106750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7876853942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3367195129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.115837097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7661056518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0606174468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7569026947021</t>
+    <t xml:space="preserve">22.0514125823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7876873016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3367176055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1158351898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7661037445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0606155395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7569007873535</t>
   </si>
   <si>
     <t xml:space="preserve">21.9961910247803</t>
   </si>
   <si>
-    <t xml:space="preserve">21.701681137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0053939819336</t>
+    <t xml:space="preserve">21.7016830444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0053958892822</t>
   </si>
   <si>
     <t xml:space="preserve">21.8765468597412</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1250419616699</t>
+    <t xml:space="preserve">22.1250400543213</t>
   </si>
   <si>
     <t xml:space="preserve">21.7753086090088</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0237998962402</t>
+    <t xml:space="preserve">22.0238018035889</t>
   </si>
   <si>
     <t xml:space="preserve">21.9041576385498</t>
@@ -1178,34 +1178,34 @@
     <t xml:space="preserve">21.6832733154297</t>
   </si>
   <si>
-    <t xml:space="preserve">20.827356338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0574417114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9470024108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7997455596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.103458404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0758495330811</t>
+    <t xml:space="preserve">20.8273544311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0574398040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.94700050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.799747467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1034603118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0758476257324</t>
   </si>
   <si>
     <t xml:space="preserve">21.3243427276611</t>
   </si>
   <si>
-    <t xml:space="preserve">21.950174331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0974311828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8581409454346</t>
+    <t xml:space="preserve">21.9501762390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0974292755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8581390380859</t>
   </si>
   <si>
     <t xml:space="preserve">21.6372566223145</t>
@@ -1229,19 +1229,19 @@
     <t xml:space="preserve">20.7077121734619</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0942554473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1586799621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0206279754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0022201538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6340847015381</t>
+    <t xml:space="preserve">21.0942573547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1586780548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0206298828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0022220611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6340827941895</t>
   </si>
   <si>
     <t xml:space="preserve">20.4500160217285</t>
@@ -1250,25 +1250,25 @@
     <t xml:space="preserve">20.385591506958</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3947944641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0082511901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9714393615723</t>
+    <t xml:space="preserve">20.39479637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0082492828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9714374542236</t>
   </si>
   <si>
     <t xml:space="preserve">20.0634708404541</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4868278503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7445259094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8917808532715</t>
+    <t xml:space="preserve">20.4868297576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7445240020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8917827606201</t>
   </si>
   <si>
     <t xml:space="preserve">21.2415103912354</t>
@@ -1277,52 +1277,52 @@
     <t xml:space="preserve">20.9285926818848</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2475395202637</t>
+    <t xml:space="preserve">20.2475414276123</t>
   </si>
   <si>
     <t xml:space="preserve">20.1647090911865</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0910816192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2719783782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6953353881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8057765960693</t>
+    <t xml:space="preserve">20.0910835266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2719764709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.695333480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8057746887207</t>
   </si>
   <si>
     <t xml:space="preserve">19.7321491241455</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1831150054932</t>
+    <t xml:space="preserve">20.1831169128418</t>
   </si>
   <si>
     <t xml:space="preserve">20.0450668334961</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2935543060303</t>
+    <t xml:space="preserve">20.2935581207275</t>
   </si>
   <si>
     <t xml:space="preserve">20.4316101074219</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5696620941162</t>
+    <t xml:space="preserve">20.5696601867676</t>
   </si>
   <si>
     <t xml:space="preserve">20.6616954803467</t>
   </si>
   <si>
-    <t xml:space="preserve">21.131067276001</t>
+    <t xml:space="preserve">21.1310691833496</t>
   </si>
   <si>
     <t xml:space="preserve">21.0482387542725</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1954936981201</t>
+    <t xml:space="preserve">21.1954956054688</t>
   </si>
   <si>
     <t xml:space="preserve">21.4531879425049</t>
@@ -1337,10 +1337,10 @@
     <t xml:space="preserve">20.7721347808838</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4652500152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7965717315674</t>
+    <t xml:space="preserve">19.4652481079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7965698242188</t>
   </si>
   <si>
     <t xml:space="preserve">19.8609962463379</t>
@@ -1349,25 +1349,25 @@
     <t xml:space="preserve">20.0174541473389</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2199268341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2291316986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5236415863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6524925231934</t>
+    <t xml:space="preserve">20.2199287414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.229133605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5236434936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6524906158447</t>
   </si>
   <si>
     <t xml:space="preserve">20.9101867675781</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2659454345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4684219360352</t>
+    <t xml:space="preserve">20.2659473419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4684238433838</t>
   </si>
   <si>
     <t xml:space="preserve">20.1555042266846</t>
@@ -1376,25 +1376,25 @@
     <t xml:space="preserve">20.1739139556885</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2599182128906</t>
+    <t xml:space="preserve">21.259916305542</t>
   </si>
   <si>
     <t xml:space="preserve">21.3703575134277</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5176105499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8549690246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9193916320801</t>
+    <t xml:space="preserve">21.5176124572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8549671173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9193897247314</t>
   </si>
   <si>
     <t xml:space="preserve">20.5052375793457</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3487777709961</t>
+    <t xml:space="preserve">20.3487796783447</t>
   </si>
   <si>
     <t xml:space="preserve">20.0266571044922</t>
@@ -1406,7 +1406,7 @@
     <t xml:space="preserve">19.9162158966064</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5604572296143</t>
+    <t xml:space="preserve">20.5604553222656</t>
   </si>
   <si>
     <t xml:space="preserve">20.7169151306152</t>
@@ -1415,94 +1415,94 @@
     <t xml:space="preserve">20.9377975463867</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8365612030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6004428863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6248817443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2751502990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1094913482666</t>
+    <t xml:space="preserve">20.8365573883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6004447937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6248798370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2751541137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1094875335693</t>
   </si>
   <si>
     <t xml:space="preserve">19.6493186950684</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9990482330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1278972625732</t>
+    <t xml:space="preserve">19.9990463256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1278953552246</t>
   </si>
   <si>
     <t xml:space="preserve">20.3303699493408</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8733749389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3763885498047</t>
+    <t xml:space="preserve">20.8733730316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3763904571533</t>
   </si>
   <si>
     <t xml:space="preserve">20.5328464508057</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3027591705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.64328956604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6156787872314</t>
+    <t xml:space="preserve">20.3027629852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6432857513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6156768798828</t>
   </si>
   <si>
     <t xml:space="preserve">20.7261180877686</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2783241271973</t>
+    <t xml:space="preserve">21.2783260345459</t>
   </si>
   <si>
     <t xml:space="preserve">21.3151378631592</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5360164642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7937183380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6496353149414</t>
+    <t xml:space="preserve">21.536018371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7937164306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.64963722229</t>
   </si>
   <si>
     <t xml:space="preserve">22.5483989715576</t>
   </si>
   <si>
-    <t xml:space="preserve">22.419548034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2078704833984</t>
+    <t xml:space="preserve">22.4195499420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2078666687012</t>
   </si>
   <si>
     <t xml:space="preserve">22.5668048858643</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6128215789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9165344238281</t>
+    <t xml:space="preserve">22.6128196716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9165325164795</t>
   </si>
   <si>
     <t xml:space="preserve">22.6864471435547</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7324638366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8337020874023</t>
+    <t xml:space="preserve">22.7324657440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.833703994751</t>
   </si>
   <si>
     <t xml:space="preserve">22.7692794799805</t>
@@ -1511,25 +1511,25 @@
     <t xml:space="preserve">22.9073295593262</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2754688262939</t>
+    <t xml:space="preserve">23.2754707336426</t>
   </si>
   <si>
     <t xml:space="preserve">22.991304397583</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3090686798096</t>
+    <t xml:space="preserve">23.3090705871582</t>
   </si>
   <si>
     <t xml:space="preserve">23.4118747711182</t>
   </si>
   <si>
-    <t xml:space="preserve">22.907190322876</t>
+    <t xml:space="preserve">22.9071884155273</t>
   </si>
   <si>
     <t xml:space="preserve">22.9819564819336</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7296123504639</t>
+    <t xml:space="preserve">22.7296142578125</t>
   </si>
   <si>
     <t xml:space="preserve">22.355770111084</t>
@@ -1538,13 +1538,13 @@
     <t xml:space="preserve">22.6174602508545</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0754165649414</t>
+    <t xml:space="preserve">23.07541847229</t>
   </si>
   <si>
     <t xml:space="preserve">23.3557987213135</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1969146728516</t>
+    <t xml:space="preserve">23.1969165802002</t>
   </si>
   <si>
     <t xml:space="preserve">23.206262588501</t>
@@ -1562,34 +1562,34 @@
     <t xml:space="preserve">23.1595325469971</t>
   </si>
   <si>
-    <t xml:space="preserve">23.505334854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3838386535645</t>
+    <t xml:space="preserve">23.5053367614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3838367462158</t>
   </si>
   <si>
     <t xml:space="preserve">23.3931846618652</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2623386383057</t>
+    <t xml:space="preserve">23.2623405456543</t>
   </si>
   <si>
     <t xml:space="preserve">22.9258823394775</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9912452697754</t>
+    <t xml:space="preserve">20.991247177124</t>
   </si>
   <si>
     <t xml:space="preserve">20.3370227813721</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9912166595459</t>
+    <t xml:space="preserve">19.9912185668945</t>
   </si>
   <si>
     <t xml:space="preserve">19.7388763427734</t>
   </si>
   <si>
-    <t xml:space="preserve">19.56130027771</t>
+    <t xml:space="preserve">19.5612983703613</t>
   </si>
   <si>
     <t xml:space="preserve">19.3089561462402</t>
@@ -1598,16 +1598,16 @@
     <t xml:space="preserve">19.533260345459</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4958782196045</t>
+    <t xml:space="preserve">19.4958763122559</t>
   </si>
   <si>
     <t xml:space="preserve">19.3463401794434</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0285739898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6266937255859</t>
+    <t xml:space="preserve">19.0285758972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6266956329346</t>
   </si>
   <si>
     <t xml:space="preserve">18.383695602417</t>
@@ -1622,7 +1622,7 @@
     <t xml:space="preserve">18.079948425293</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6033306121826</t>
+    <t xml:space="preserve">18.603328704834</t>
   </si>
   <si>
     <t xml:space="preserve">18.6360397338867</t>
@@ -1640,10 +1640,10 @@
     <t xml:space="preserve">18.5752906799316</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3930416107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5285587310791</t>
+    <t xml:space="preserve">18.3930435180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5285606384277</t>
   </si>
   <si>
     <t xml:space="preserve">18.495849609375</t>
@@ -1652,25 +1652,25 @@
     <t xml:space="preserve">18.4351005554199</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3883686065674</t>
+    <t xml:space="preserve">18.388370513916</t>
   </si>
   <si>
     <t xml:space="preserve">18.491174697876</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2435054779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8042411804199</t>
+    <t xml:space="preserve">18.2435073852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8042373657227</t>
   </si>
   <si>
     <t xml:space="preserve">17.7715282440186</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1079883575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6734256744385</t>
+    <t xml:space="preserve">18.1079864501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6734237670898</t>
   </si>
   <si>
     <t xml:space="preserve">18.7575378417969</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">18.276216506958</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2528533935547</t>
+    <t xml:space="preserve">18.2528514862061</t>
   </si>
   <si>
     <t xml:space="preserve">18.2107944488525</t>
@@ -1694,19 +1694,19 @@
     <t xml:space="preserve">19.1407260894775</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4398021697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4024143218994</t>
+    <t xml:space="preserve">19.4397983551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4024181365967</t>
   </si>
   <si>
     <t xml:space="preserve">19.4117641448975</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4304580688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3650302886963</t>
+    <t xml:space="preserve">19.4304542541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3650341033936</t>
   </si>
   <si>
     <t xml:space="preserve">19.1594200134277</t>
@@ -1724,19 +1724,19 @@
     <t xml:space="preserve">18.7388458251953</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0566120147705</t>
+    <t xml:space="preserve">19.0566101074219</t>
   </si>
   <si>
     <t xml:space="preserve">18.8416519165039</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6080284118652</t>
+    <t xml:space="preserve">19.6080303192139</t>
   </si>
   <si>
     <t xml:space="preserve">19.2528800964355</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5239162445068</t>
+    <t xml:space="preserve">19.5239143371582</t>
   </si>
   <si>
     <t xml:space="preserve">19.4211101531982</t>
@@ -1745,43 +1745,43 @@
     <t xml:space="preserve">19.8136425018311</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0753307342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.748218536377</t>
+    <t xml:space="preserve">20.0753326416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7482204437256</t>
   </si>
   <si>
     <t xml:space="preserve">20.0192565917969</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7669124603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7856044769287</t>
+    <t xml:space="preserve">19.7669105529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7856063842773</t>
   </si>
   <si>
     <t xml:space="preserve">19.5706462860107</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2809162139893</t>
+    <t xml:space="preserve">19.2809181213379</t>
   </si>
   <si>
     <t xml:space="preserve">19.1500720977783</t>
   </si>
   <si>
-    <t xml:space="preserve">18.89772605896</t>
+    <t xml:space="preserve">18.8977298736572</t>
   </si>
   <si>
     <t xml:space="preserve">18.8042697906494</t>
   </si>
   <si>
-    <t xml:space="preserve">18.879035949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1780853271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6453857421875</t>
+    <t xml:space="preserve">18.8790378570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1780834197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6453876495361</t>
   </si>
   <si>
     <t xml:space="preserve">17.8556442260742</t>
@@ -1793,19 +1793,19 @@
     <t xml:space="preserve">17.1546878814697</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9817886352539</t>
+    <t xml:space="preserve">16.9817867279053</t>
   </si>
   <si>
     <t xml:space="preserve">18.1360263824463</t>
   </si>
   <si>
-    <t xml:space="preserve">17.949104309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1173324584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2154693603516</t>
+    <t xml:space="preserve">17.9491062164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1173343658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2154674530029</t>
   </si>
   <si>
     <t xml:space="preserve">19.1874580383301</t>
@@ -1814,13 +1814,13 @@
     <t xml:space="preserve">19.0098819732666</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5986824035645</t>
+    <t xml:space="preserve">19.5986843109131</t>
   </si>
   <si>
     <t xml:space="preserve">19.5893363952637</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6454124450684</t>
+    <t xml:space="preserve">19.645414352417</t>
   </si>
   <si>
     <t xml:space="preserve">19.4771862030029</t>
@@ -1832,7 +1832,7 @@
     <t xml:space="preserve">19.5799922943115</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0005645751953</t>
+    <t xml:space="preserve">20.0005626678467</t>
   </si>
   <si>
     <t xml:space="preserve">19.6267204284668</t>
@@ -1862,34 +1862,34 @@
     <t xml:space="preserve">19.206148147583</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0472087860107</t>
+    <t xml:space="preserve">17.0472106933594</t>
   </si>
   <si>
     <t xml:space="preserve">16.7107524871826</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8135566711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5845813751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5471954345703</t>
+    <t xml:space="preserve">16.8135585784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5845794677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5471973419189</t>
   </si>
   <si>
     <t xml:space="preserve">16.5378494262695</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7200965881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4957942962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7528076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5004653930664</t>
+    <t xml:space="preserve">16.7200984954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4957904815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7528095245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.500467300415</t>
   </si>
   <si>
     <t xml:space="preserve">16.4630813598633</t>
@@ -1907,10 +1907,10 @@
     <t xml:space="preserve">16.8415966033936</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6640205383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5331783294678</t>
+    <t xml:space="preserve">16.6640224456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5331764221191</t>
   </si>
   <si>
     <t xml:space="preserve">16.5892524719238</t>
@@ -1919,37 +1919,37 @@
     <t xml:space="preserve">16.6827125549316</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5986003875732</t>
+    <t xml:space="preserve">16.5985984802246</t>
   </si>
   <si>
     <t xml:space="preserve">16.4256973266602</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1266250610352</t>
+    <t xml:space="preserve">16.1266212463379</t>
   </si>
   <si>
     <t xml:space="preserve">16.1593341827393</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4490642547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1920471191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2154102325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4817733764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5238304138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4023303985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2995262145996</t>
+    <t xml:space="preserve">16.4490623474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.192045211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2154121398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4817752838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.523832321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4023323059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.299524307251</t>
   </si>
   <si>
     <t xml:space="preserve">16.5799083709717</t>
@@ -1964,25 +1964,25 @@
     <t xml:space="preserve">17.1967468261719</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2201099395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5752620697021</t>
+    <t xml:space="preserve">17.2201118469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5752601623535</t>
   </si>
   <si>
     <t xml:space="preserve">17.5518970489502</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4163799285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1079616546631</t>
+    <t xml:space="preserve">17.4163780212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1079597473145</t>
   </si>
   <si>
     <t xml:space="preserve">17.1313228607178</t>
   </si>
   <si>
-    <t xml:space="preserve">17.229455947876</t>
+    <t xml:space="preserve">17.2294578552246</t>
   </si>
   <si>
     <t xml:space="preserve">17.4911479949951</t>
@@ -1991,19 +1991,19 @@
     <t xml:space="preserve">17.4397449493408</t>
   </si>
   <si>
-    <t xml:space="preserve">17.453763961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7294731140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6547012329102</t>
+    <t xml:space="preserve">17.4537620544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.729471206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6547031402588</t>
   </si>
   <si>
     <t xml:space="preserve">17.3369369506836</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1453437805176</t>
+    <t xml:space="preserve">17.1453418731689</t>
   </si>
   <si>
     <t xml:space="preserve">16.8462696075439</t>
@@ -2015,13 +2015,13 @@
     <t xml:space="preserve">16.822904586792</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9911613464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9117221832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0378913879395</t>
+    <t xml:space="preserve">17.9911594390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9117202758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0378932952881</t>
   </si>
   <si>
     <t xml:space="preserve">17.6593761444092</t>
@@ -2030,7 +2030,7 @@
     <t xml:space="preserve">17.7948951721191</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6360111236572</t>
+    <t xml:space="preserve">17.6360130310059</t>
   </si>
   <si>
     <t xml:space="preserve">17.3275928497314</t>
@@ -2042,10 +2042,10 @@
     <t xml:space="preserve">17.6266651153564</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5004940032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.869665145874</t>
+    <t xml:space="preserve">17.5004959106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8696632385254</t>
   </si>
   <si>
     <t xml:space="preserve">18.3136005401611</t>
@@ -2063,16 +2063,16 @@
     <t xml:space="preserve">17.9677963256836</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9070472717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.69211769104</t>
+    <t xml:space="preserve">17.9070491790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6921157836914</t>
   </si>
   <si>
     <t xml:space="preserve">18.5051937103271</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3416404724121</t>
+    <t xml:space="preserve">18.3416385650635</t>
   </si>
   <si>
     <t xml:space="preserve">18.5565986633301</t>
@@ -2081,13 +2081,13 @@
     <t xml:space="preserve">18.4397716522217</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5472526550293</t>
+    <t xml:space="preserve">18.5472507476807</t>
   </si>
   <si>
     <t xml:space="preserve">18.3089275360107</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8603439331055</t>
+    <t xml:space="preserve">18.8603458404541</t>
   </si>
   <si>
     <t xml:space="preserve">18.3696784973145</t>
@@ -2108,10 +2108,10 @@
     <t xml:space="preserve">17.5986270904541</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0939674377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.860372543335</t>
+    <t xml:space="preserve">18.0939693450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8603744506836</t>
   </si>
   <si>
     <t xml:space="preserve">20.0472965240479</t>
@@ -2123,16 +2123,16 @@
     <t xml:space="preserve">19.4607124328613</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9735889434814</t>
+    <t xml:space="preserve">19.9735870361328</t>
   </si>
   <si>
     <t xml:space="preserve">19.4132251739502</t>
   </si>
   <si>
-    <t xml:space="preserve">19.204273223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4892082214355</t>
+    <t xml:space="preserve">19.2042751312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4892063140869</t>
   </si>
   <si>
     <t xml:space="preserve">19.1187953948975</t>
@@ -2153,16 +2153,16 @@
     <t xml:space="preserve">17.7273902893066</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8318614959717</t>
+    <t xml:space="preserve">17.8318634033203</t>
   </si>
   <si>
     <t xml:space="preserve">18.3732299804688</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6534099578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1757831573486</t>
+    <t xml:space="preserve">18.6534118652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1757850646973</t>
   </si>
   <si>
     <t xml:space="preserve">19.3657360076904</t>
@@ -2174,7 +2174,7 @@
     <t xml:space="preserve">19.2137718200684</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9810829162598</t>
+    <t xml:space="preserve">18.9810810089111</t>
   </si>
   <si>
     <t xml:space="preserve">18.905101776123</t>
@@ -2189,22 +2189,22 @@
     <t xml:space="preserve">19.6886558532715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9355945587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0210762023926</t>
+    <t xml:space="preserve">19.9355964660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0210742950439</t>
   </si>
   <si>
     <t xml:space="preserve">19.8026294708252</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7171478271484</t>
+    <t xml:space="preserve">19.7171497344971</t>
   </si>
   <si>
     <t xml:space="preserve">19.8121280670166</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7456455230713</t>
+    <t xml:space="preserve">19.7456436157227</t>
   </si>
   <si>
     <t xml:space="preserve">19.926097869873</t>
@@ -2216,13 +2216,13 @@
     <t xml:space="preserve">20.1920337677002</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4674625396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4864616394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2870121002197</t>
+    <t xml:space="preserve">20.4674644470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4864597320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2870101928711</t>
   </si>
   <si>
     <t xml:space="preserve">20.2775135040283</t>
@@ -2249,10 +2249,10 @@
     <t xml:space="preserve">20.0305728912354</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8691120147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9640884399414</t>
+    <t xml:space="preserve">19.8691139221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.96409034729</t>
   </si>
   <si>
     <t xml:space="preserve">20.0020790100098</t>
@@ -2273,7 +2273,7 @@
     <t xml:space="preserve">17.5754261016846</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2952461242676</t>
+    <t xml:space="preserve">17.2952442169189</t>
   </si>
   <si>
     <t xml:space="preserve">17.2762508392334</t>
@@ -2282,7 +2282,7 @@
     <t xml:space="preserve">17.2667541503906</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3854751586914</t>
+    <t xml:space="preserve">17.3854732513428</t>
   </si>
   <si>
     <t xml:space="preserve">17.0198135375977</t>
@@ -2291,13 +2291,13 @@
     <t xml:space="preserve">16.8963451385498</t>
   </si>
   <si>
-    <t xml:space="preserve">17.015064239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.59716796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2837448120117</t>
+    <t xml:space="preserve">17.0150661468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5971660614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2837467193604</t>
   </si>
   <si>
     <t xml:space="preserve">16.8108654022217</t>
@@ -2318,16 +2318,16 @@
     <t xml:space="preserve">16.7348861694336</t>
   </si>
   <si>
-    <t xml:space="preserve">16.948579788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7491302490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.844108581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.497444152832</t>
+    <t xml:space="preserve">16.9485816955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7491321563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8441066741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4974422454834</t>
   </si>
   <si>
     <t xml:space="preserve">16.6683979034424</t>
@@ -2336,7 +2336,7 @@
     <t xml:space="preserve">16.6304092407227</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9248352050781</t>
+    <t xml:space="preserve">16.9248371124268</t>
   </si>
   <si>
     <t xml:space="preserve">17.4329605102539</t>
@@ -2348,7 +2348,7 @@
     <t xml:space="preserve">17.2097682952881</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1385364532471</t>
+    <t xml:space="preserve">17.1385345458984</t>
   </si>
   <si>
     <t xml:space="preserve">17.5231895446777</t>
@@ -2369,13 +2369,13 @@
     <t xml:space="preserve">16.2267570495605</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1887683868408</t>
+    <t xml:space="preserve">16.1887664794922</t>
   </si>
   <si>
     <t xml:space="preserve">16.1365299224854</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3454780578613</t>
+    <t xml:space="preserve">16.34547996521</t>
   </si>
   <si>
     <t xml:space="preserve">16.1840190887451</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">16.1032886505127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0178089141846</t>
+    <t xml:space="preserve">16.0178108215332</t>
   </si>
   <si>
     <t xml:space="preserve">15.4811906814575</t>
@@ -2393,7 +2393,7 @@
     <t xml:space="preserve">15.538179397583</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5619220733643</t>
+    <t xml:space="preserve">15.5619230270386</t>
   </si>
   <si>
     <t xml:space="preserve">15.1725187301636</t>
@@ -2405,16 +2405,16 @@
     <t xml:space="preserve">15.3577222824097</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5904169082642</t>
+    <t xml:space="preserve">15.5904159545898</t>
   </si>
   <si>
     <t xml:space="preserve">15.4716949462891</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6806421279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4052104949951</t>
+    <t xml:space="preserve">15.680643081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4052095413208</t>
   </si>
   <si>
     <t xml:space="preserve">15.324481010437</t>
@@ -2435,25 +2435,25 @@
     <t xml:space="preserve">15.0348014831543</t>
   </si>
   <si>
-    <t xml:space="preserve">15.319730758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9608249664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7661228179932</t>
+    <t xml:space="preserve">15.3197317123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.960823059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7661218643188</t>
   </si>
   <si>
     <t xml:space="preserve">15.8800916671753</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9085855484009</t>
+    <t xml:space="preserve">15.9085874557495</t>
   </si>
   <si>
     <t xml:space="preserve">15.922833442688</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1412811279297</t>
+    <t xml:space="preserve">16.1412792205811</t>
   </si>
   <si>
     <t xml:space="preserve">16.1745204925537</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">16.4024658203125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5781726837158</t>
+    <t xml:space="preserve">16.5781707763672</t>
   </si>
   <si>
     <t xml:space="preserve">16.5734233856201</t>
@@ -2477,7 +2477,7 @@
     <t xml:space="preserve">16.9723262786865</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4404544830322</t>
+    <t xml:space="preserve">16.4404563903809</t>
   </si>
   <si>
     <t xml:space="preserve">16.3074893951416</t>
@@ -2498,7 +2498,7 @@
     <t xml:space="preserve">17.1290378570557</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1860237121582</t>
+    <t xml:space="preserve">17.1860218048096</t>
   </si>
   <si>
     <t xml:space="preserve">16.6873950958252</t>
@@ -2516,7 +2516,7 @@
     <t xml:space="preserve">17.3474826812744</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2477588653564</t>
+    <t xml:space="preserve">17.2477569580078</t>
   </si>
   <si>
     <t xml:space="preserve">17.3379859924316</t>
@@ -2537,25 +2537,25 @@
     <t xml:space="preserve">17.8033714294434</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1167964935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8556060791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8081188201904</t>
+    <t xml:space="preserve">18.1167945861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8556079864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8081207275391</t>
   </si>
   <si>
     <t xml:space="preserve">18.0028228759766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6704044342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.622917175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6799011230469</t>
+    <t xml:space="preserve">17.6704025268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6229152679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6799030303955</t>
   </si>
   <si>
     <t xml:space="preserve">17.9885749816895</t>
@@ -2564,19 +2564,19 @@
     <t xml:space="preserve">18.4207191467285</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0930500030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9030952453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8508605957031</t>
+    <t xml:space="preserve">18.0930480957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.90309715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8508586883545</t>
   </si>
   <si>
     <t xml:space="preserve">17.2620029449463</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2287635803223</t>
+    <t xml:space="preserve">17.2287616729736</t>
   </si>
   <si>
     <t xml:space="preserve">17.0957946777344</t>
@@ -2588,13 +2588,13 @@
     <t xml:space="preserve">16.6161632537842</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5924167633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8610982894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2694988250732</t>
+    <t xml:space="preserve">16.5924186706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8611001968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2694969177246</t>
   </si>
   <si>
     <t xml:space="preserve">16.2979927062988</t>
@@ -2603,7 +2603,7 @@
     <t xml:space="preserve">16.1175346374512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8468523025513</t>
+    <t xml:space="preserve">15.8468503952026</t>
   </si>
   <si>
     <t xml:space="preserve">16.3217353820801</t>
@@ -2612,31 +2612,31 @@
     <t xml:space="preserve">16.0842933654785</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7803678512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7186336517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3434762954712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9845695495605</t>
+    <t xml:space="preserve">15.7803688049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7186326980591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3434772491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9845676422119</t>
   </si>
   <si>
     <t xml:space="preserve">15.747127532959</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6046619415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7043867111206</t>
+    <t xml:space="preserve">15.604660987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7043857574463</t>
   </si>
   <si>
     <t xml:space="preserve">15.8848428726196</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5429258346558</t>
+    <t xml:space="preserve">15.5429267883301</t>
   </si>
   <si>
     <t xml:space="preserve">15.1582717895508</t>
@@ -2651,7 +2651,7 @@
     <t xml:space="preserve">14.1420221328735</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6054029464722</t>
+    <t xml:space="preserve">13.6054039001465</t>
   </si>
   <si>
     <t xml:space="preserve">13.5721616744995</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">13.0497894287109</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9738082885742</t>
+    <t xml:space="preserve">12.9738092422485</t>
   </si>
   <si>
     <t xml:space="preserve">12.3184700012207</t>
@@ -2678,13 +2678,13 @@
     <t xml:space="preserve">10.6563787460327</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7845973968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08166694641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65437602996826</t>
+    <t xml:space="preserve">10.7845964431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08166599273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65437507629395</t>
   </si>
   <si>
     <t xml:space="preserve">10.0057888031006</t>
@@ -2744,34 +2744,34 @@
     <t xml:space="preserve">11.9765529632568</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4541826248169</t>
+    <t xml:space="preserve">11.4541835784912</t>
   </si>
   <si>
     <t xml:space="preserve">11.2927227020264</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5396614074707</t>
+    <t xml:space="preserve">11.5396604537964</t>
   </si>
   <si>
     <t xml:space="preserve">10.8178396224976</t>
   </si>
   <si>
-    <t xml:space="preserve">10.399941444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4474296569824</t>
+    <t xml:space="preserve">10.3999423980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4474306106567</t>
   </si>
   <si>
     <t xml:space="preserve">10.3809471130371</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7323598861694</t>
+    <t xml:space="preserve">10.7323608398438</t>
   </si>
   <si>
     <t xml:space="preserve">10.9128150939941</t>
   </si>
   <si>
-    <t xml:space="preserve">10.722861289978</t>
+    <t xml:space="preserve">10.7228622436523</t>
   </si>
   <si>
     <t xml:space="preserve">10.3049659729004</t>
@@ -2786,7 +2786,7 @@
     <t xml:space="preserve">10.3429565429688</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4094400405884</t>
+    <t xml:space="preserve">10.4094390869141</t>
   </si>
   <si>
     <t xml:space="preserve">10.2574768066406</t>
@@ -2831,22 +2831,22 @@
     <t xml:space="preserve">13.2872314453125</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1542654037476</t>
+    <t xml:space="preserve">13.1542644500732</t>
   </si>
   <si>
     <t xml:space="preserve">12.8218460083008</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8815784454346</t>
+    <t xml:space="preserve">11.8815774917603</t>
   </si>
   <si>
     <t xml:space="preserve">11.7771024703979</t>
   </si>
   <si>
-    <t xml:space="preserve">12.062032699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1190185546875</t>
+    <t xml:space="preserve">12.0620336532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1190195083618</t>
   </si>
   <si>
     <t xml:space="preserve">12.2899770736694</t>
@@ -2858,22 +2858,22 @@
     <t xml:space="preserve">12.7078742980957</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5749063491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5844039916992</t>
+    <t xml:space="preserve">12.5749073028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5844049453735</t>
   </si>
   <si>
     <t xml:space="preserve">11.9955492019653</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8055963516235</t>
+    <t xml:space="preserve">11.8055953979492</t>
   </si>
   <si>
     <t xml:space="preserve">11.5111684799194</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7296142578125</t>
+    <t xml:space="preserve">11.7296152114868</t>
   </si>
   <si>
     <t xml:space="preserve">11.4446849822998</t>
@@ -2882,7 +2882,7 @@
     <t xml:space="preserve">11.5206661224365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7581081390381</t>
+    <t xml:space="preserve">11.7581071853638</t>
   </si>
   <si>
     <t xml:space="preserve">11.5871486663818</t>
@@ -2897,13 +2897,13 @@
     <t xml:space="preserve">10.9887971878052</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1787509918213</t>
+    <t xml:space="preserve">11.1787519454956</t>
   </si>
   <si>
     <t xml:space="preserve">11.2262382507324</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2452344894409</t>
+    <t xml:space="preserve">11.2452335357666</t>
   </si>
   <si>
     <t xml:space="preserve">11.1027679443359</t>
@@ -2912,13 +2912,13 @@
     <t xml:space="preserve">11.1312618255615</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0267877578735</t>
+    <t xml:space="preserve">11.0267868041992</t>
   </si>
   <si>
     <t xml:space="preserve">11.0837736129761</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8368339538574</t>
+    <t xml:space="preserve">10.8368349075317</t>
   </si>
   <si>
     <t xml:space="preserve">11.0552806854248</t>
@@ -2936,22 +2936,22 @@
     <t xml:space="preserve">10.4379320144653</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3619518280029</t>
+    <t xml:space="preserve">10.3619508743286</t>
   </si>
   <si>
     <t xml:space="preserve">11.644136428833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3307123184204</t>
+    <t xml:space="preserve">11.3307132720947</t>
   </si>
   <si>
     <t xml:space="preserve">11.0932712554932</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9603042602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.760853767395</t>
+    <t xml:space="preserve">10.9603052139282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7608528137207</t>
   </si>
   <si>
     <t xml:space="preserve">10.7798490524292</t>
@@ -2963,7 +2963,7 @@
     <t xml:space="preserve">11.6156425476074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4636793136597</t>
+    <t xml:space="preserve">11.463680267334</t>
   </si>
   <si>
     <t xml:space="preserve">11.3971967697144</t>
@@ -2972,7 +2972,7 @@
     <t xml:space="preserve">11.5016708374023</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7960977554321</t>
+    <t xml:space="preserve">11.7960987091064</t>
   </si>
   <si>
     <t xml:space="preserve">11.4731779098511</t>
@@ -2996,7 +2996,7 @@
     <t xml:space="preserve">11.6061458587646</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1095209121704</t>
+    <t xml:space="preserve">12.1095218658447</t>
   </si>
   <si>
     <t xml:space="preserve">12.0145444869995</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">11.957558631897</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9860506057739</t>
+    <t xml:space="preserve">11.9860515594482</t>
   </si>
   <si>
     <t xml:space="preserve">12.1285171508789</t>
@@ -3023,10 +3023,10 @@
     <t xml:space="preserve">12.6034002304077</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5464143753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2044982910156</t>
+    <t xml:space="preserve">12.5464134216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2044973373413</t>
   </si>
   <si>
     <t xml:space="preserve">12.4039497375488</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">12.8978281021118</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1949996948242</t>
+    <t xml:space="preserve">12.1950006484985</t>
   </si>
   <si>
     <t xml:space="preserve">11.8910760879517</t>
@@ -3056,7 +3056,7 @@
     <t xml:space="preserve">10.7988433837891</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0647773742676</t>
+    <t xml:space="preserve">11.0647783279419</t>
   </si>
   <si>
     <t xml:space="preserve">11.3592052459717</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">13.7146253585815</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9235744476318</t>
+    <t xml:space="preserve">13.9235754013062</t>
   </si>
   <si>
     <t xml:space="preserve">13.9330730438232</t>
@@ -3095,13 +3095,13 @@
     <t xml:space="preserve">14.6264009475708</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3129787445068</t>
+    <t xml:space="preserve">14.3129796981812</t>
   </si>
   <si>
     <t xml:space="preserve">14.1515188217163</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2464952468872</t>
+    <t xml:space="preserve">14.2464962005615</t>
   </si>
   <si>
     <t xml:space="preserve">14.4269514083862</t>
@@ -3113,7 +3113,7 @@
     <t xml:space="preserve">14.9113321304321</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4934349060059</t>
+    <t xml:space="preserve">14.4934358596802</t>
   </si>
   <si>
     <t xml:space="preserve">14.3509693145752</t>
@@ -3131,13 +3131,13 @@
     <t xml:space="preserve">14.8828401565552</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8543462753296</t>
+    <t xml:space="preserve">14.8543472290039</t>
   </si>
   <si>
     <t xml:space="preserve">14.7593698501587</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3794622421265</t>
+    <t xml:space="preserve">14.3794631958008</t>
   </si>
   <si>
     <t xml:space="preserve">14.5694160461426</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">14.6074066162109</t>
   </si>
   <si>
-    <t xml:space="preserve">15.110782623291</t>
+    <t xml:space="preserve">15.1107835769653</t>
   </si>
   <si>
     <t xml:space="preserve">15.0632944107056</t>
@@ -3161,22 +3161,22 @@
     <t xml:space="preserve">14.7688674926758</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7118806838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5884103775024</t>
+    <t xml:space="preserve">14.7118816375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5884113311768</t>
   </si>
   <si>
     <t xml:space="preserve">14.5789136886597</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4079561233521</t>
+    <t xml:space="preserve">14.4079551696777</t>
   </si>
   <si>
     <t xml:space="preserve">14.5504207611084</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5314264297485</t>
+    <t xml:space="preserve">14.5314254760742</t>
   </si>
   <si>
     <t xml:space="preserve">13.9615650177002</t>
@@ -3188,22 +3188,22 @@
     <t xml:space="preserve">14.4459466934204</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2912397384644</t>
+    <t xml:space="preserve">15.29123878479</t>
   </si>
   <si>
     <t xml:space="preserve">14.683388710022</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0537967681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8041124343872</t>
+    <t xml:space="preserve">15.0537977218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8041114807129</t>
   </si>
   <si>
     <t xml:space="preserve">15.6711444854736</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2627458572388</t>
+    <t xml:space="preserve">15.2627449035645</t>
   </si>
   <si>
     <t xml:space="preserve">14.9588203430176</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">14.6359004974365</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4364490509033</t>
+    <t xml:space="preserve">14.4364500045776</t>
   </si>
   <si>
     <t xml:space="preserve">14.7403745651245</t>
@@ -3230,7 +3230,7 @@
     <t xml:space="preserve">15.0822906494141</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9778156280518</t>
+    <t xml:space="preserve">14.9778165817261</t>
   </si>
   <si>
     <t xml:space="preserve">14.6928863525391</t>
@@ -3245,19 +3245,19 @@
     <t xml:space="preserve">15.2057600021362</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1202802658081</t>
+    <t xml:space="preserve">15.1202812194824</t>
   </si>
   <si>
     <t xml:space="preserve">15.0917882919312</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1012849807739</t>
+    <t xml:space="preserve">15.1012859344482</t>
   </si>
   <si>
     <t xml:space="preserve">14.8448476791382</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9873123168945</t>
+    <t xml:space="preserve">14.9873132705688</t>
   </si>
   <si>
     <t xml:space="preserve">15.8705949783325</t>
@@ -3266,7 +3266,7 @@
     <t xml:space="preserve">16.0225601196289</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0320568084717</t>
+    <t xml:space="preserve">16.032054901123</t>
   </si>
   <si>
     <t xml:space="preserve">15.8231077194214</t>
@@ -3275,7 +3275,7 @@
     <t xml:space="preserve">15.9370803833008</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7376298904419</t>
+    <t xml:space="preserve">15.7376289367676</t>
   </si>
   <si>
     <t xml:space="preserve">15.4906892776489</t>
@@ -3287,34 +3287,34 @@
     <t xml:space="preserve">15.3102350234985</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3672199249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3387269973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6996374130249</t>
+    <t xml:space="preserve">15.3672208786011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3387260437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6996393203735</t>
   </si>
   <si>
     <t xml:space="preserve">15.6853904724121</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6189079284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4289560317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6379041671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7396335601807</t>
+    <t xml:space="preserve">15.6189069747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.428955078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.637903213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.739631652832</t>
   </si>
   <si>
     <t xml:space="preserve">16.8678512573242</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8726005554199</t>
+    <t xml:space="preserve">16.8725986480713</t>
   </si>
   <si>
     <t xml:space="preserve">16.4784469604492</t>
@@ -3326,13 +3326,13 @@
     <t xml:space="preserve">17.513692855835</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4567050933838</t>
+    <t xml:space="preserve">17.4567031860352</t>
   </si>
   <si>
     <t xml:space="preserve">17.0388088226318</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2904968261719</t>
+    <t xml:space="preserve">17.2904987335205</t>
   </si>
   <si>
     <t xml:space="preserve">17.0815467834473</t>
@@ -3350,7 +3350,7 @@
     <t xml:space="preserve">17.4614543914795</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4187145233154</t>
+    <t xml:space="preserve">17.4187164306641</t>
   </si>
   <si>
     <t xml:space="preserve">18.2117691040039</t>
@@ -3359,13 +3359,13 @@
     <t xml:space="preserve">18.3589839935303</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1975231170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1500358581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2307643890381</t>
+    <t xml:space="preserve">18.1975250244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1500377655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2307662963867</t>
   </si>
   <si>
     <t xml:space="preserve">18.0360641479492</t>
@@ -3395,25 +3395,25 @@
     <t xml:space="preserve">18.3019981384277</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3542366027832</t>
+    <t xml:space="preserve">18.3542346954346</t>
   </si>
   <si>
     <t xml:space="preserve">18.3969745635986</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5299434661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2972469329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1690292358398</t>
+    <t xml:space="preserve">18.5299415588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.297248840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1690311431885</t>
   </si>
   <si>
     <t xml:space="preserve">18.1832790374756</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4444637298584</t>
+    <t xml:space="preserve">18.444465637207</t>
   </si>
   <si>
     <t xml:space="preserve">18.8956031799316</t>
@@ -3428,7 +3428,7 @@
     <t xml:space="preserve">18.3352394104004</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8461112976074</t>
+    <t xml:space="preserve">17.8461093902588</t>
   </si>
   <si>
     <t xml:space="preserve">17.1527805328369</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">16.7253875732422</t>
   </si>
   <si>
-    <t xml:space="preserve">16.877347946167</t>
+    <t xml:space="preserve">16.8773498535156</t>
   </si>
   <si>
     <t xml:space="preserve">16.4214611053467</t>
@@ -3473,13 +3473,13 @@
     <t xml:space="preserve">16.4736976623535</t>
   </si>
   <si>
-    <t xml:space="preserve">16.169771194458</t>
+    <t xml:space="preserve">16.1697731018066</t>
   </si>
   <si>
     <t xml:space="preserve">16.0463027954102</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0368041992188</t>
+    <t xml:space="preserve">16.0368061065674</t>
   </si>
   <si>
     <t xml:space="preserve">15.9988136291504</t>
@@ -3488,7 +3488,7 @@
     <t xml:space="preserve">16.2600021362305</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0652980804443</t>
+    <t xml:space="preserve">16.065299987793</t>
   </si>
   <si>
     <t xml:space="preserve">16.0510520935059</t>
@@ -3509,28 +3509,28 @@
     <t xml:space="preserve">17.6609058380127</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0008182525635</t>
+    <t xml:space="preserve">17.0008163452148</t>
   </si>
   <si>
     <t xml:space="preserve">16.6731491088867</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5164375305176</t>
+    <t xml:space="preserve">16.5164356231689</t>
   </si>
   <si>
     <t xml:space="preserve">15.7328805923462</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7423782348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1460266113281</t>
+    <t xml:space="preserve">15.7423791885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1460285186768</t>
   </si>
   <si>
     <t xml:space="preserve">15.9275808334351</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9703216552734</t>
+    <t xml:space="preserve">15.9703235626221</t>
   </si>
   <si>
     <t xml:space="preserve">16.6541538238525</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">18.0123195648193</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8698558807373</t>
+    <t xml:space="preserve">17.8698539733887</t>
   </si>
   <si>
     <t xml:space="preserve">18.0693054199219</t>
@@ -3557,10 +3557,10 @@
     <t xml:space="preserve">16.7206382751465</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9628295898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9438304901123</t>
+    <t xml:space="preserve">16.9628276824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9438323974609</t>
   </si>
   <si>
     <t xml:space="preserve">16.8298606872559</t>
@@ -3572,7 +3572,7 @@
     <t xml:space="preserve">16.8346099853516</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0435562133789</t>
+    <t xml:space="preserve">17.0435581207275</t>
   </si>
   <si>
     <t xml:space="preserve">16.8013687133789</t>
@@ -3593,7 +3593,7 @@
     <t xml:space="preserve">17.4662036895752</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7178936004639</t>
+    <t xml:space="preserve">17.7178916931152</t>
   </si>
   <si>
     <t xml:space="preserve">17.7748775482178</t>
@@ -3605,7 +3605,7 @@
     <t xml:space="preserve">18.1405372619629</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7008991241455</t>
+    <t xml:space="preserve">18.7009010314941</t>
   </si>
   <si>
     <t xml:space="preserve">18.7911262512207</t>
@@ -3623,7 +3623,7 @@
     <t xml:space="preserve">18.5536861419678</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7626323699951</t>
+    <t xml:space="preserve">18.7626342773438</t>
   </si>
   <si>
     <t xml:space="preserve">19.0903053283691</t>
@@ -3647,13 +3647,13 @@
     <t xml:space="preserve">19.6221733093262</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1377906799316</t>
+    <t xml:space="preserve">19.1377925872803</t>
   </si>
   <si>
     <t xml:space="preserve">19.6316699981689</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4579677581787</t>
+    <t xml:space="preserve">20.4579696655273</t>
   </si>
   <si>
     <t xml:space="preserve">20.6289253234863</t>
@@ -3662,19 +3662,19 @@
     <t xml:space="preserve">21.0373268127441</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4457225799561</t>
+    <t xml:space="preserve">21.4457244873047</t>
   </si>
   <si>
     <t xml:space="preserve">20.9898376464844</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7523975372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6384239196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1635398864746</t>
+    <t xml:space="preserve">20.7523956298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6384220123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1635417938232</t>
   </si>
   <si>
     <t xml:space="preserve">20.0970554351807</t>
@@ -3683,13 +3683,13 @@
     <t xml:space="preserve">20.7903861999512</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7144031524658</t>
+    <t xml:space="preserve">20.7144050598145</t>
   </si>
   <si>
     <t xml:space="preserve">21.0278282165527</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0183296203613</t>
+    <t xml:space="preserve">21.0183277130127</t>
   </si>
   <si>
     <t xml:space="preserve">21.094310760498</t>
@@ -3698,13 +3698,13 @@
     <t xml:space="preserve">21.4172306060791</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3982353210449</t>
+    <t xml:space="preserve">21.3982372283936</t>
   </si>
   <si>
     <t xml:space="preserve">21.7021617889404</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5691947937012</t>
+    <t xml:space="preserve">21.5691928863525</t>
   </si>
   <si>
     <t xml:space="preserve">22.0820693969727</t>
@@ -3713,7 +3713,7 @@
     <t xml:space="preserve">21.5976867675781</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6261806488037</t>
+    <t xml:space="preserve">21.6261825561523</t>
   </si>
   <si>
     <t xml:space="preserve">19.4797096252441</t>
@@ -3731,10 +3731,10 @@
     <t xml:space="preserve">18.7103977203369</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0550594329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4946975708008</t>
+    <t xml:space="preserve">18.055061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4946956634521</t>
   </si>
   <si>
     <t xml:space="preserve">18.2212677001953</t>
@@ -3743,10 +3743,10 @@
     <t xml:space="preserve">17.9743270874023</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5916786193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5394401550293</t>
+    <t xml:space="preserve">18.5916767120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5394420623779</t>
   </si>
   <si>
     <t xml:space="preserve">18.0977993011475</t>
@@ -3755,7 +3755,7 @@
     <t xml:space="preserve">18.0503101348877</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2830028533936</t>
+    <t xml:space="preserve">18.2830009460449</t>
   </si>
   <si>
     <t xml:space="preserve">18.1927757263184</t>
@@ -3779,19 +3779,19 @@
     <t xml:space="preserve">18.5964260101318</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7768821716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9220905303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6581611633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4492130279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6324138641357</t>
+    <t xml:space="preserve">18.7768802642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9220924377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6581592559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4492111206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6324157714844</t>
   </si>
   <si>
     <t xml:space="preserve">17.7368869781494</t>
@@ -3806,13 +3806,13 @@
     <t xml:space="preserve">14.8306016921997</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5076818466187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9133348464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3529739379883</t>
+    <t xml:space="preserve">14.5076808929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9133329391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3529748916626</t>
   </si>
   <si>
     <t xml:space="preserve">15.457447052002</t>
@@ -3821,10 +3821,10 @@
     <t xml:space="preserve">14.8733415603638</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5856657028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8136100769043</t>
+    <t xml:space="preserve">15.5856666564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.81360912323</t>
   </si>
   <si>
     <t xml:space="preserve">15.5334281921387</t>
@@ -3833,16 +3833,16 @@
     <t xml:space="preserve">15.2390012741089</t>
   </si>
   <si>
-    <t xml:space="preserve">15.253246307373</t>
+    <t xml:space="preserve">15.2532472610474</t>
   </si>
   <si>
     <t xml:space="preserve">15.5191831588745</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8278589248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7681255340576</t>
+    <t xml:space="preserve">15.8278579711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7681274414062</t>
   </si>
   <si>
     <t xml:space="preserve">16.316987991333</t>
@@ -3854,7 +3854,7 @@
     <t xml:space="preserve">15.0253038406372</t>
   </si>
   <si>
-    <t xml:space="preserve">15.633152961731</t>
+    <t xml:space="preserve">15.6331539154053</t>
   </si>
   <si>
     <t xml:space="preserve">15.6521482467651</t>
@@ -3863,7 +3863,7 @@
     <t xml:space="preserve">15.8895902633667</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5096855163574</t>
+    <t xml:space="preserve">15.5096845626831</t>
   </si>
   <si>
     <t xml:space="preserve">14.7308769226074</t>
@@ -3872,7 +3872,7 @@
     <t xml:space="preserve">14.8638439178467</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1392765045166</t>
+    <t xml:space="preserve">15.1392755508423</t>
   </si>
   <si>
     <t xml:space="preserve">15.7851181030273</t>
@@ -3881,7 +3881,7 @@
     <t xml:space="preserve">14.3034820556641</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3224763870239</t>
+    <t xml:space="preserve">14.3224773406982</t>
   </si>
   <si>
     <t xml:space="preserve">13.8285989761353</t>
@@ -3896,7 +3896,7 @@
     <t xml:space="preserve">14.1990079879761</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0158071517944</t>
+    <t xml:space="preserve">15.0158061981201</t>
   </si>
   <si>
     <t xml:space="preserve">14.5219278335571</t>
@@ -6159,6 +6159,9 @@
   </si>
   <si>
     <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6399998664856</t>
   </si>
 </sst>
 </file>
@@ -73929,9 +73932,11 @@
       <c r="E2594" t="n">
         <v>6.82000017166138</v>
       </c>
-      <c r="F2594"/>
+      <c r="F2594" t="n">
+        <v>6.80499982833862</v>
+      </c>
       <c r="G2594" t="s">
-        <v>2048</v>
+        <v>1857</v>
       </c>
       <c r="H2594" t="s">
         <v>9</v>
@@ -73939,27 +73944,51 @@
     </row>
     <row r="2595">
       <c r="A2595" s="1" t="n">
-        <v>46098.6912731481</v>
+        <v>46099.3333333333</v>
       </c>
       <c r="B2595" t="n">
-        <v>202632</v>
+        <v>401486</v>
       </c>
       <c r="C2595" t="n">
-        <v>6.86499977111816</v>
+        <v>6.875</v>
       </c>
       <c r="D2595" t="n">
-        <v>6.73000001907349</v>
+        <v>6.5</v>
       </c>
       <c r="E2595" t="n">
-        <v>6.82000017166138</v>
-      </c>
-      <c r="F2595" t="n">
-        <v>6.80499982833862</v>
-      </c>
+        <v>6.875</v>
+      </c>
+      <c r="F2595"/>
       <c r="G2595" t="s">
-        <v>1857</v>
+        <v>2048</v>
       </c>
       <c r="H2595" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2596">
+      <c r="A2596" s="1" t="n">
+        <v>46099.6912152778</v>
+      </c>
+      <c r="B2596" t="n">
+        <v>401486</v>
+      </c>
+      <c r="C2596" t="n">
+        <v>6.875</v>
+      </c>
+      <c r="D2596" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E2596" t="n">
+        <v>6.875</v>
+      </c>
+      <c r="F2596" t="n">
+        <v>6.6399998664856</v>
+      </c>
+      <c r="G2596" t="s">
+        <v>2049</v>
+      </c>
+      <c r="H2596" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -47,13 +47,13 @@
     <t xml:space="preserve">18.01096534729</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4978809356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9401950836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.683650970459</t>
+    <t xml:space="preserve">17.4978828430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9401969909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6836528778076</t>
   </si>
   <si>
     <t xml:space="preserve">18.2498149871826</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">19.4086742401123</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1344375610352</t>
+    <t xml:space="preserve">19.1344356536865</t>
   </si>
   <si>
     <t xml:space="preserve">18.8425121307373</t>
@@ -71,25 +71,25 @@
     <t xml:space="preserve">18.4621238708496</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2851982116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0994243621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6394233703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5686550140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1878890991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4798145294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2232761383057</t>
+    <t xml:space="preserve">18.2852001190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0994281768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6394214630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5686531066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1878871917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4798126220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.223274230957</t>
   </si>
   <si>
     <t xml:space="preserve">17.7632675170898</t>
@@ -101,16 +101,16 @@
     <t xml:space="preserve">18.6744327545166</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9578838348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2055835723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2586574554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0817337036133</t>
+    <t xml:space="preserve">17.9578857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2055816650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2586555480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0817356109619</t>
   </si>
   <si>
     <t xml:space="preserve">17.3563423156738</t>
@@ -119,10 +119,10 @@
     <t xml:space="preserve">16.9051837921143</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1617221832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6486396789551</t>
+    <t xml:space="preserve">17.1617240905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6486415863037</t>
   </si>
   <si>
     <t xml:space="preserve">17.0201835632324</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">17.4890365600586</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6305770874023</t>
+    <t xml:space="preserve">17.6305732727051</t>
   </si>
   <si>
     <t xml:space="preserve">18.4090442657471</t>
@@ -140,43 +140,43 @@
     <t xml:space="preserve">18.4532775878906</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9752044677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1348114013672</t>
+    <t xml:space="preserve">18.9752063751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1348133087158</t>
   </si>
   <si>
     <t xml:space="preserve">17.3121089935303</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9048099517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3471183776855</t>
+    <t xml:space="preserve">17.9048118591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3471202850342</t>
   </si>
   <si>
     <t xml:space="preserve">19.0194358825684</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0017433166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8513603210449</t>
+    <t xml:space="preserve">19.0017414093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8513584136963</t>
   </si>
   <si>
     <t xml:space="preserve">19.3113613128662</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9925212860107</t>
+    <t xml:space="preserve">19.9925231933594</t>
   </si>
   <si>
     <t xml:space="preserve">19.9482917785645</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7271327972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3379039764404</t>
+    <t xml:space="preserve">19.7271366119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3379001617432</t>
   </si>
   <si>
     <t xml:space="preserve">19.6475200653076</t>
@@ -185,34 +185,34 @@
     <t xml:space="preserve">19.9836769104004</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1167469024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4440574645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0367565155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1782913208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4971313476562</t>
+    <t xml:space="preserve">19.1167449951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.444055557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0367527008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1782932281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4971332550049</t>
   </si>
   <si>
     <t xml:space="preserve">19.4705963134766</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9663600921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4794406890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9129047393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8686771392822</t>
+    <t xml:space="preserve">18.9663619995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4794425964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9129085540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.868673324585</t>
   </si>
   <si>
     <t xml:space="preserve">19.4175205230713</t>
@@ -230,28 +230,28 @@
     <t xml:space="preserve">18.9309730529785</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8955917358398</t>
+    <t xml:space="preserve">18.8955898284912</t>
   </si>
   <si>
     <t xml:space="preserve">18.5240459442139</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9486656188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7982788085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8778972625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2936668395996</t>
+    <t xml:space="preserve">18.9486694335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.798282623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8778953552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2936706542969</t>
   </si>
   <si>
     <t xml:space="preserve">18.8071269989014</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3205795288086</t>
+    <t xml:space="preserve">18.3205814361572</t>
   </si>
   <si>
     <t xml:space="preserve">18.3648109436035</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">17.8251914978027</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0640392303467</t>
+    <t xml:space="preserve">18.0640430450439</t>
   </si>
   <si>
     <t xml:space="preserve">18.3117351531982</t>
@@ -269,49 +269,49 @@
     <t xml:space="preserve">17.878267288208</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0021190643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7190380096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.444803237915</t>
+    <t xml:space="preserve">18.0021171569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7190399169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4448051452637</t>
   </si>
   <si>
     <t xml:space="preserve">17.1440296173096</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5509605407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9844284057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4182662963867</t>
+    <t xml:space="preserve">17.5509586334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9844264984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4182682037354</t>
   </si>
   <si>
     <t xml:space="preserve">17.9313468933105</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7367286682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.648265838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.593936920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.81125831604</t>
+    <t xml:space="preserve">17.7367305755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6482677459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5939388275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8112602233887</t>
   </si>
   <si>
     <t xml:space="preserve">17.7025966644287</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5305519104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4128379821777</t>
+    <t xml:space="preserve">17.530553817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4128360748291</t>
   </si>
   <si>
     <t xml:space="preserve">17.3041763305664</t>
@@ -320,94 +320,94 @@
     <t xml:space="preserve">17.4762229919434</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4309463500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4852771759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7478733062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6844882965088</t>
+    <t xml:space="preserve">17.430944442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4852752685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7478713989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6844902038574</t>
   </si>
   <si>
     <t xml:space="preserve">17.1502418518066</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7155990600586</t>
+    <t xml:space="preserve">16.71559715271</t>
   </si>
   <si>
     <t xml:space="preserve">16.5435543060303</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0415782928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0778007507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8384227752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9380283355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7297630310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8655872344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1825141906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8514213562012</t>
+    <t xml:space="preserve">17.0415802001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0778026580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8384246826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9380264282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7297611236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8655891418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1825122833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8514251708984</t>
   </si>
   <si>
     <t xml:space="preserve">16.3896179199219</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6793823242188</t>
+    <t xml:space="preserve">16.6793785095215</t>
   </si>
   <si>
     <t xml:space="preserve">16.262845993042</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5254440307617</t>
+    <t xml:space="preserve">16.5254421234131</t>
   </si>
   <si>
     <t xml:space="preserve">16.6069393157959</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8061485290527</t>
+    <t xml:space="preserve">16.8061466217041</t>
   </si>
   <si>
     <t xml:space="preserve">16.8242588043213</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0726890563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8734827041626</t>
+    <t xml:space="preserve">16.0726909637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.873480796814</t>
   </si>
   <si>
     <t xml:space="preserve">16.3624515533447</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4439506530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6974906921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0959091186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1321296691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0868549346924</t>
+    <t xml:space="preserve">16.4439468383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.69748878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.095911026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1321315765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0868587493896</t>
   </si>
   <si>
     <t xml:space="preserve">17.0325260162354</t>
@@ -419,10 +419,10 @@
     <t xml:space="preserve">17.9018096923828</t>
   </si>
   <si>
-    <t xml:space="preserve">18.137243270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9289741516113</t>
+    <t xml:space="preserve">18.1372394561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9289722442627</t>
   </si>
   <si>
     <t xml:space="preserve">18.7710914611816</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">19.0699081420898</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2147903442383</t>
+    <t xml:space="preserve">19.2147884368896</t>
   </si>
   <si>
     <t xml:space="preserve">18.6262111663818</t>
@@ -443,16 +443,16 @@
     <t xml:space="preserve">18.4994411468506</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2187366485596</t>
+    <t xml:space="preserve">18.2187347412109</t>
   </si>
   <si>
     <t xml:space="preserve">18.7167625427246</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5809383392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.762035369873</t>
+    <t xml:space="preserve">18.5809364318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7620334625244</t>
   </si>
   <si>
     <t xml:space="preserve">18.8073120117188</t>
@@ -461,16 +461,16 @@
     <t xml:space="preserve">18.9431381225586</t>
   </si>
   <si>
-    <t xml:space="preserve">19.04274559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6624317169189</t>
+    <t xml:space="preserve">19.0427417755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6624336242676</t>
   </si>
   <si>
     <t xml:space="preserve">18.4722766876221</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6171550750732</t>
+    <t xml:space="preserve">18.6171569824219</t>
   </si>
   <si>
     <t xml:space="preserve">18.7529792785645</t>
@@ -479,10 +479,10 @@
     <t xml:space="preserve">18.9703025817871</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6805400848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6080989837646</t>
+    <t xml:space="preserve">18.6805419921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6081008911133</t>
   </si>
   <si>
     <t xml:space="preserve">18.653377532959</t>
@@ -503,31 +503,31 @@
     <t xml:space="preserve">19.9210815429688</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6947040557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5588817596436</t>
+    <t xml:space="preserve">19.6947059631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5588798522949</t>
   </si>
   <si>
     <t xml:space="preserve">19.4592723846436</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3143939971924</t>
+    <t xml:space="preserve">19.3143978118896</t>
   </si>
   <si>
     <t xml:space="preserve">18.8888072967529</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1332931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1604595184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9391918182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4553298950195</t>
+    <t xml:space="preserve">19.1332950592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1604614257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9391937255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4553279876709</t>
   </si>
   <si>
     <t xml:space="preserve">20.3557224273682</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">20.3104496002197</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3919448852539</t>
+    <t xml:space="preserve">20.3919429779053</t>
   </si>
   <si>
     <t xml:space="preserve">20.4643840789795</t>
@@ -548,46 +548,46 @@
     <t xml:space="preserve">20.8446960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7994194030762</t>
+    <t xml:space="preserve">20.7994213104248</t>
   </si>
   <si>
     <t xml:space="preserve">20.4009990692139</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1021862030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5277690887451</t>
+    <t xml:space="preserve">20.1021842956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5277671813965</t>
   </si>
   <si>
     <t xml:space="preserve">20.3647766113281</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5458812713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7541465759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4191074371338</t>
+    <t xml:space="preserve">20.545877456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7541446685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4191055297852</t>
   </si>
   <si>
     <t xml:space="preserve">20.0116348266602</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2651748657227</t>
+    <t xml:space="preserve">20.2651710510254</t>
   </si>
   <si>
     <t xml:space="preserve">20.3285598754883</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0387992858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1474571228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2289543151855</t>
+    <t xml:space="preserve">20.03879737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1474609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2289524078369</t>
   </si>
   <si>
     <t xml:space="preserve">20.5006046295166</t>
@@ -599,7 +599,7 @@
     <t xml:space="preserve">20.1836814880371</t>
   </si>
   <si>
-    <t xml:space="preserve">19.549825668335</t>
+    <t xml:space="preserve">19.5498237609863</t>
   </si>
   <si>
     <t xml:space="preserve">19.4140014648438</t>
@@ -608,46 +608,46 @@
     <t xml:space="preserve">19.5045490264893</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7218723297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7943134307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5226612091064</t>
+    <t xml:space="preserve">19.7218704223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7943096160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5226593017578</t>
   </si>
   <si>
     <t xml:space="preserve">19.830530166626</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9120273590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7490348815918</t>
+    <t xml:space="preserve">19.9120254516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7490367889404</t>
   </si>
   <si>
     <t xml:space="preserve">18.0919647216797</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3002281188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3273983001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2458992004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0104675292969</t>
+    <t xml:space="preserve">18.3002300262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3273963928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2459011077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0104656219482</t>
   </si>
   <si>
     <t xml:space="preserve">17.7388172149658</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8565349578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8203125</t>
+    <t xml:space="preserve">17.8565330505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8203144073486</t>
   </si>
   <si>
     <t xml:space="preserve">17.6392116546631</t>
@@ -656,46 +656,46 @@
     <t xml:space="preserve">18.3455066680908</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3907833099365</t>
+    <t xml:space="preserve">18.3907814025879</t>
   </si>
   <si>
     <t xml:space="preserve">19.1514053344727</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2872314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3958892822266</t>
+    <t xml:space="preserve">19.2872295379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3958930969238</t>
   </si>
   <si>
     <t xml:space="preserve">19.3777809143066</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1151828765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5860443115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2600631713867</t>
+    <t xml:space="preserve">19.1151847839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5860424041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.260066986084</t>
   </si>
   <si>
     <t xml:space="preserve">20.3738327026367</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3466663360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2380104064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1293468475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1565132141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8084754943848</t>
+    <t xml:space="preserve">20.3466682434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2380084991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1293487548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.15651512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8084735870361</t>
   </si>
   <si>
     <t xml:space="preserve">20.6183204650879</t>
@@ -704,22 +704,22 @@
     <t xml:space="preserve">21.4785480499268</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5328788757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0671291351318</t>
+    <t xml:space="preserve">21.5328807830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0671272277832</t>
   </si>
   <si>
     <t xml:space="preserve">22.0580730438232</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2572822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2935028076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3025531768799</t>
+    <t xml:space="preserve">22.2572803497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2935009002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3025569915771</t>
   </si>
   <si>
     <t xml:space="preserve">22.3206672668457</t>
@@ -728,16 +728,16 @@
     <t xml:space="preserve">22.2753925323486</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2391681671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8186931610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0722332000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8911361694336</t>
+    <t xml:space="preserve">22.2391700744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8186950683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0722351074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.891134262085</t>
   </si>
   <si>
     <t xml:space="preserve">23.1537303924561</t>
@@ -746,25 +746,25 @@
     <t xml:space="preserve">23.0993995666504</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5923175811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3568859100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9092464447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1757850646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1395664215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6064834594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7513618469238</t>
+    <t xml:space="preserve">22.5923156738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3568897247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9092426300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1757831573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1395645141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.606481552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7513656616211</t>
   </si>
   <si>
     <t xml:space="preserve">24.1226177215576</t>
@@ -773,10 +773,10 @@
     <t xml:space="preserve">23.6427021026611</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6879787445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.561206817627</t>
+    <t xml:space="preserve">23.6879768371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5612087249756</t>
   </si>
   <si>
     <t xml:space="preserve">23.7423076629639</t>
@@ -788,13 +788,13 @@
     <t xml:space="preserve">23.6336479187012</t>
   </si>
   <si>
-    <t xml:space="preserve">23.823802947998</t>
+    <t xml:space="preserve">23.8238048553467</t>
   </si>
   <si>
     <t xml:space="preserve">23.6970329284668</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0139579772949</t>
+    <t xml:space="preserve">24.0139617919922</t>
   </si>
   <si>
     <t xml:space="preserve">24.285608291626</t>
@@ -803,58 +803,58 @@
     <t xml:space="preserve">24.0682888031006</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9777355194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2946624755859</t>
+    <t xml:space="preserve">23.9777374267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2946662902832</t>
   </si>
   <si>
     <t xml:space="preserve">24.4304904937744</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6115913391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7655277252197</t>
+    <t xml:space="preserve">24.6115951538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.765531539917</t>
   </si>
   <si>
     <t xml:space="preserve">25.1911125183105</t>
   </si>
   <si>
-    <t xml:space="preserve">25.390323638916</t>
+    <t xml:space="preserve">25.3903255462646</t>
   </si>
   <si>
     <t xml:space="preserve">25.4265441894531</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6167030334473</t>
+    <t xml:space="preserve">25.6167011260986</t>
   </si>
   <si>
     <t xml:space="preserve">25.6710319519043</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6529197692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7615833282471</t>
+    <t xml:space="preserve">25.6529216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7615795135498</t>
   </si>
   <si>
     <t xml:space="preserve">25.5352058410645</t>
   </si>
   <si>
-    <t xml:space="preserve">24.955680847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9013519287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0643424987793</t>
+    <t xml:space="preserve">24.9556789398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9013500213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0643444061279</t>
   </si>
   <si>
     <t xml:space="preserve">24.8017463684082</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6206493377686</t>
+    <t xml:space="preserve">24.6206474304199</t>
   </si>
   <si>
     <t xml:space="preserve">24.937572479248</t>
@@ -863,28 +863,28 @@
     <t xml:space="preserve">25.3722152709961</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6257553100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2273330688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1730041503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1639499664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3993797302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7253589630127</t>
+    <t xml:space="preserve">25.6257572174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2273349761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.173002243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.163948059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.399377822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7253608703613</t>
   </si>
   <si>
     <t xml:space="preserve">25.2907199859619</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1277294158936</t>
+    <t xml:space="preserve">25.1277275085449</t>
   </si>
   <si>
     <t xml:space="preserve">25.7434711456299</t>
@@ -902,10 +902,10 @@
     <t xml:space="preserve">25.2635536193848</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0824527740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7836380004883</t>
+    <t xml:space="preserve">25.0824546813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7836399078369</t>
   </si>
   <si>
     <t xml:space="preserve">24.4214344024658</t>
@@ -926,16 +926,16 @@
     <t xml:space="preserve">26.6308650970459</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4859848022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3229923248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6761360168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8934593200684</t>
+    <t xml:space="preserve">26.4859828948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3229942321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6761379241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.893461227417</t>
   </si>
   <si>
     <t xml:space="preserve">26.2596092224121</t>
@@ -944,7 +944,7 @@
     <t xml:space="preserve">26.6670837402344</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9115676879883</t>
+    <t xml:space="preserve">26.9115695953369</t>
   </si>
   <si>
     <t xml:space="preserve">26.6037006378174</t>
@@ -953,13 +953,13 @@
     <t xml:space="preserve">26.5946445465088</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3088302612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3269386291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.834020614624</t>
+    <t xml:space="preserve">25.3088321685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.326940536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8340225219727</t>
   </si>
   <si>
     <t xml:space="preserve">25.8984451293945</t>
@@ -971,31 +971,31 @@
     <t xml:space="preserve">24.7112045288086</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6159934997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2202472686768</t>
+    <t xml:space="preserve">23.6159954071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2202491760254</t>
   </si>
   <si>
     <t xml:space="preserve">23.1282119750977</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9625511169434</t>
+    <t xml:space="preserve">22.9625492095947</t>
   </si>
   <si>
     <t xml:space="preserve">22.8705158233643</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8613109588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2662658691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2386531829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0453853607178</t>
+    <t xml:space="preserve">22.8613147735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.266263961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.238655090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0453815460205</t>
   </si>
   <si>
     <t xml:space="preserve">22.8889217376709</t>
@@ -1004,7 +1004,7 @@
     <t xml:space="preserve">22.0882263183594</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3183116912842</t>
+    <t xml:space="preserve">22.3183097839355</t>
   </si>
   <si>
     <t xml:space="preserve">22.2262763977051</t>
@@ -1016,34 +1016,34 @@
     <t xml:space="preserve">22.3643283843994</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7416667938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.95334815979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8797206878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2846717834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4871463775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4319248199463</t>
+    <t xml:space="preserve">22.7416706085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9533500671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8797225952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2846698760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4871501922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4319267272949</t>
   </si>
   <si>
     <t xml:space="preserve">22.8060932159424</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0269775390625</t>
+    <t xml:space="preserve">23.0269737243652</t>
   </si>
   <si>
     <t xml:space="preserve">22.6036167144775</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2538871765137</t>
+    <t xml:space="preserve">22.253885269165</t>
   </si>
   <si>
     <t xml:space="preserve">21.545223236084</t>
@@ -1070,16 +1070,16 @@
     <t xml:space="preserve">21.2046966552734</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1218662261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4163761138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5084075927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9133605957031</t>
+    <t xml:space="preserve">21.1218681335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.416374206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5084114074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9133586883545</t>
   </si>
   <si>
     <t xml:space="preserve">21.8857517242432</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">21.9685821533203</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6220245361328</t>
+    <t xml:space="preserve">22.6220226287842</t>
   </si>
   <si>
     <t xml:space="preserve">22.3735313415527</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">22.4103450775146</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5299911499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6312274932861</t>
+    <t xml:space="preserve">22.5299892425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6312294006348</t>
   </si>
   <si>
     <t xml:space="preserve">22.6404323577881</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">22.5576019287109</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4255790710449</t>
+    <t xml:space="preserve">21.4255809783936</t>
   </si>
   <si>
     <t xml:space="preserve">21.6556663513184</t>
@@ -1121,10 +1121,10 @@
     <t xml:space="preserve">22.263090133667</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5391941070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3551254272461</t>
+    <t xml:space="preserve">22.539192199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3551235198975</t>
   </si>
   <si>
     <t xml:space="preserve">22.0514106750488</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">22.7876853942871</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3367195129395</t>
+    <t xml:space="preserve">22.3367176055908</t>
   </si>
   <si>
     <t xml:space="preserve">22.115837097168</t>
@@ -1148,34 +1148,34 @@
     <t xml:space="preserve">21.7569026947021</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9961910247803</t>
+    <t xml:space="preserve">21.9961929321289</t>
   </si>
   <si>
     <t xml:space="preserve">21.701681137085</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0053939819336</t>
+    <t xml:space="preserve">22.0053958892822</t>
   </si>
   <si>
     <t xml:space="preserve">21.8765468597412</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1250419616699</t>
+    <t xml:space="preserve">22.1250381469727</t>
   </si>
   <si>
     <t xml:space="preserve">21.7753086090088</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0237998962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9041576385498</t>
+    <t xml:space="preserve">22.0238037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9041595458984</t>
   </si>
   <si>
     <t xml:space="preserve">21.6832733154297</t>
   </si>
   <si>
-    <t xml:space="preserve">20.827356338501</t>
+    <t xml:space="preserve">20.8273525238037</t>
   </si>
   <si>
     <t xml:space="preserve">21.0574417114258</t>
@@ -1187,37 +1187,37 @@
     <t xml:space="preserve">20.7997455596924</t>
   </si>
   <si>
-    <t xml:space="preserve">21.103458404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0758495330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3243427276611</t>
+    <t xml:space="preserve">21.1034603118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0758476257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3243408203125</t>
   </si>
   <si>
     <t xml:space="preserve">21.950174331665</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0974311828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8581409454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6372566223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2967319488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9746112823486</t>
+    <t xml:space="preserve">22.0974292755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8581390380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6372585296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2967338562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9746131896973</t>
   </si>
   <si>
     <t xml:space="preserve">20.983814239502</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1402721405029</t>
+    <t xml:space="preserve">21.1402740478516</t>
   </si>
   <si>
     <t xml:space="preserve">21.0666446685791</t>
@@ -1229,7 +1229,7 @@
     <t xml:space="preserve">21.0942554473877</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1586799621582</t>
+    <t xml:space="preserve">21.1586818695068</t>
   </si>
   <si>
     <t xml:space="preserve">21.0206279754639</t>
@@ -1238,52 +1238,52 @@
     <t xml:space="preserve">21.0022201538086</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6340847015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4500160217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.385591506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3947944641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0082511901855</t>
+    <t xml:space="preserve">20.6340827941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4500179290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3855895996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.39479637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0082492828369</t>
   </si>
   <si>
     <t xml:space="preserve">19.9714393615723</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0634708404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4868278503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7445259094238</t>
+    <t xml:space="preserve">20.0634689331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4868297576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7445278167725</t>
   </si>
   <si>
     <t xml:space="preserve">20.8917808532715</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2415103912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9285926818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2475395202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1647090911865</t>
+    <t xml:space="preserve">21.241512298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9285945892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2475414276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1647109985352</t>
   </si>
   <si>
     <t xml:space="preserve">20.0910816192627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2719783782959</t>
+    <t xml:space="preserve">19.2719764709473</t>
   </si>
   <si>
     <t xml:space="preserve">19.6953353881836</t>
@@ -1292,22 +1292,22 @@
     <t xml:space="preserve">19.8057765960693</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7321491241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1831150054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0450668334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2935543060303</t>
+    <t xml:space="preserve">19.7321510314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1831169128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0450649261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2935562133789</t>
   </si>
   <si>
     <t xml:space="preserve">20.4316101074219</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5696620941162</t>
+    <t xml:space="preserve">20.5696601867676</t>
   </si>
   <si>
     <t xml:space="preserve">20.6616954803467</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">21.131067276001</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0482387542725</t>
+    <t xml:space="preserve">21.0482406616211</t>
   </si>
   <si>
     <t xml:space="preserve">21.1954936981201</t>
@@ -1325,19 +1325,19 @@
     <t xml:space="preserve">21.4531879425049</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8089504241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6708965301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7721347808838</t>
+    <t xml:space="preserve">20.8089485168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6708946228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7721328735352</t>
   </si>
   <si>
     <t xml:space="preserve">19.4652500152588</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7965717315674</t>
+    <t xml:space="preserve">19.7965698242188</t>
   </si>
   <si>
     <t xml:space="preserve">19.8609962463379</t>
@@ -1346,34 +1346,34 @@
     <t xml:space="preserve">20.0174541473389</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2199268341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2291316986084</t>
+    <t xml:space="preserve">20.2199287414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.229133605957</t>
   </si>
   <si>
     <t xml:space="preserve">20.5236415863037</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6524925231934</t>
+    <t xml:space="preserve">20.6524906158447</t>
   </si>
   <si>
     <t xml:space="preserve">20.9101867675781</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2659454345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4684219360352</t>
+    <t xml:space="preserve">20.2659492492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4684238433838</t>
   </si>
   <si>
     <t xml:space="preserve">20.1555042266846</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1739139556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2599182128906</t>
+    <t xml:space="preserve">20.1739120483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2599201202393</t>
   </si>
   <si>
     <t xml:space="preserve">21.3703575134277</t>
@@ -1382,16 +1382,16 @@
     <t xml:space="preserve">21.5176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8549690246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9193916320801</t>
+    <t xml:space="preserve">20.8549671173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9193897247314</t>
   </si>
   <si>
     <t xml:space="preserve">20.5052375793457</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3487777709961</t>
+    <t xml:space="preserve">20.3487796783447</t>
   </si>
   <si>
     <t xml:space="preserve">20.0266571044922</t>
@@ -1403,22 +1403,22 @@
     <t xml:space="preserve">19.9162158966064</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5604572296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7169151306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9377975463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8365612030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6004428863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6248817443848</t>
+    <t xml:space="preserve">20.5604553222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7169170379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9377956390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8365592956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6004447937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6248798370361</t>
   </si>
   <si>
     <t xml:space="preserve">20.2751502990723</t>
@@ -1445,58 +1445,58 @@
     <t xml:space="preserve">20.3763885498047</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5328464508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3027591705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.64328956604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6156787872314</t>
+    <t xml:space="preserve">20.5328483581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3027610778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6432876586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6156749725342</t>
   </si>
   <si>
     <t xml:space="preserve">20.7261180877686</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2783241271973</t>
+    <t xml:space="preserve">21.2783260345459</t>
   </si>
   <si>
     <t xml:space="preserve">21.3151378631592</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5360164642334</t>
+    <t xml:space="preserve">21.536018371582</t>
   </si>
   <si>
     <t xml:space="preserve">21.7937183380127</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6496353149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5483989715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.419548034668</t>
+    <t xml:space="preserve">22.64963722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.548397064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4195499420166</t>
   </si>
   <si>
     <t xml:space="preserve">22.2078704833984</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5668048858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6128215789795</t>
+    <t xml:space="preserve">22.5668029785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6128234863281</t>
   </si>
   <si>
     <t xml:space="preserve">22.9165344238281</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6864471435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7324638366699</t>
+    <t xml:space="preserve">22.6864490509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7324657440186</t>
   </si>
   <si>
     <t xml:space="preserve">22.8337020874023</t>
@@ -1514,13 +1514,13 @@
     <t xml:space="preserve">22.991304397583</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3090686798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4118747711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.907190322876</t>
+    <t xml:space="preserve">23.3090667724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4118766784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9071884155273</t>
   </si>
   <si>
     <t xml:space="preserve">22.9819564819336</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">23.4586067199707</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6548442840576</t>
+    <t xml:space="preserve">22.6548461914062</t>
   </si>
   <si>
     <t xml:space="preserve">22.7389583587646</t>
@@ -1562,7 +1562,7 @@
     <t xml:space="preserve">23.505334854126</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3838386535645</t>
+    <t xml:space="preserve">23.3838367462158</t>
   </si>
   <si>
     <t xml:space="preserve">23.3931846618652</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">23.2623386383057</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9258823394775</t>
+    <t xml:space="preserve">22.9258804321289</t>
   </si>
   <si>
     <t xml:space="preserve">20.9912452697754</t>
@@ -1613,16 +1613,16 @@
     <t xml:space="preserve">18.0752754211426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6220207214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.079948425293</t>
+    <t xml:space="preserve">18.6220188140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0799503326416</t>
   </si>
   <si>
     <t xml:space="preserve">18.6033306121826</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6360397338867</t>
+    <t xml:space="preserve">18.6360416412354</t>
   </si>
   <si>
     <t xml:space="preserve">18.7949237823486</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">18.7762317657471</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7201557159424</t>
+    <t xml:space="preserve">18.7201538085938</t>
   </si>
   <si>
     <t xml:space="preserve">18.5752906799316</t>
@@ -1640,7 +1640,7 @@
     <t xml:space="preserve">18.3930416107178</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5285587310791</t>
+    <t xml:space="preserve">18.5285606384277</t>
   </si>
   <si>
     <t xml:space="preserve">18.495849609375</t>
@@ -1652,7 +1652,7 @@
     <t xml:space="preserve">18.3883686065674</t>
   </si>
   <si>
-    <t xml:space="preserve">18.491174697876</t>
+    <t xml:space="preserve">18.4911766052246</t>
   </si>
   <si>
     <t xml:space="preserve">18.2435054779053</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">18.2528533935547</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2107944488525</t>
+    <t xml:space="preserve">18.2107925415039</t>
   </si>
   <si>
     <t xml:space="preserve">18.3790245056152</t>
@@ -1691,7 +1691,7 @@
     <t xml:space="preserve">19.1407260894775</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4398021697998</t>
+    <t xml:space="preserve">19.4398002624512</t>
   </si>
   <si>
     <t xml:space="preserve">19.4024143218994</t>
@@ -1706,13 +1706,13 @@
     <t xml:space="preserve">19.3650302886963</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1594200134277</t>
+    <t xml:space="preserve">19.1594219207764</t>
   </si>
   <si>
     <t xml:space="preserve">19.1687660217285</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1126899719238</t>
+    <t xml:space="preserve">19.1126880645752</t>
   </si>
   <si>
     <t xml:space="preserve">19.0939960479736</t>
@@ -1733,16 +1733,16 @@
     <t xml:space="preserve">19.2528800964355</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5239162445068</t>
+    <t xml:space="preserve">19.5239143371582</t>
   </si>
   <si>
     <t xml:space="preserve">19.4211101531982</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8136425018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0753307342529</t>
+    <t xml:space="preserve">19.8136444091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0753326416016</t>
   </si>
   <si>
     <t xml:space="preserve">19.748218536377</t>
@@ -1760,13 +1760,13 @@
     <t xml:space="preserve">19.5706462860107</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2809162139893</t>
+    <t xml:space="preserve">19.2809181213379</t>
   </si>
   <si>
     <t xml:space="preserve">19.1500720977783</t>
   </si>
   <si>
-    <t xml:space="preserve">18.89772605896</t>
+    <t xml:space="preserve">18.8977279663086</t>
   </si>
   <si>
     <t xml:space="preserve">18.8042697906494</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">18.1780853271484</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6453857421875</t>
+    <t xml:space="preserve">18.6453838348389</t>
   </si>
   <si>
     <t xml:space="preserve">17.8556442260742</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">17.949104309082</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1173324584961</t>
+    <t xml:space="preserve">18.1173343658447</t>
   </si>
   <si>
     <t xml:space="preserve">18.2154693603516</t>
@@ -1814,13 +1814,13 @@
     <t xml:space="preserve">19.5986824035645</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5893363952637</t>
+    <t xml:space="preserve">19.589334487915</t>
   </si>
   <si>
     <t xml:space="preserve">19.6454124450684</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4771862030029</t>
+    <t xml:space="preserve">19.4771842956543</t>
   </si>
   <si>
     <t xml:space="preserve">19.5426082611084</t>
@@ -1844,19 +1844,19 @@
     <t xml:space="preserve">19.3930702209473</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7481918334961</t>
+    <t xml:space="preserve">18.7481937408447</t>
   </si>
   <si>
     <t xml:space="preserve">18.7855777740479</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0659580230713</t>
+    <t xml:space="preserve">19.0659561157227</t>
   </si>
   <si>
     <t xml:space="preserve">19.5145683288574</t>
   </si>
   <si>
-    <t xml:space="preserve">19.206148147583</t>
+    <t xml:space="preserve">19.2061500549316</t>
   </si>
   <si>
     <t xml:space="preserve">17.0472087860107</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">16.7107524871826</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8135566711426</t>
+    <t xml:space="preserve">16.8135585784912</t>
   </si>
   <si>
     <t xml:space="preserve">16.5845813751221</t>
@@ -1874,13 +1874,13 @@
     <t xml:space="preserve">16.5471954345703</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5378494262695</t>
+    <t xml:space="preserve">16.5378475189209</t>
   </si>
   <si>
     <t xml:space="preserve">16.7200965881348</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4957942962646</t>
+    <t xml:space="preserve">16.495792388916</t>
   </si>
   <si>
     <t xml:space="preserve">16.7528076171875</t>
@@ -1889,7 +1889,7 @@
     <t xml:space="preserve">16.5004653930664</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4630813598633</t>
+    <t xml:space="preserve">16.4630794525146</t>
   </si>
   <si>
     <t xml:space="preserve">16.0425090789795</t>
@@ -1910,25 +1910,25 @@
     <t xml:space="preserve">16.5331783294678</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5892524719238</t>
+    <t xml:space="preserve">16.5892543792725</t>
   </si>
   <si>
     <t xml:space="preserve">16.6827125549316</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5986003875732</t>
+    <t xml:space="preserve">16.5985984802246</t>
   </si>
   <si>
     <t xml:space="preserve">16.4256973266602</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1266250610352</t>
+    <t xml:space="preserve">16.1266231536865</t>
   </si>
   <si>
     <t xml:space="preserve">16.1593341827393</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4490642547607</t>
+    <t xml:space="preserve">16.4490623474121</t>
   </si>
   <si>
     <t xml:space="preserve">16.1920471191406</t>
@@ -1973,7 +1973,7 @@
     <t xml:space="preserve">17.4163799285889</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1079616546631</t>
+    <t xml:space="preserve">17.1079597473145</t>
   </si>
   <si>
     <t xml:space="preserve">17.1313228607178</t>
@@ -1988,10 +1988,10 @@
     <t xml:space="preserve">17.4397449493408</t>
   </si>
   <si>
-    <t xml:space="preserve">17.453763961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7294731140137</t>
+    <t xml:space="preserve">17.4537620544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.729471206665</t>
   </si>
   <si>
     <t xml:space="preserve">17.6547012329102</t>
@@ -2012,22 +2012,22 @@
     <t xml:space="preserve">16.822904586792</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9911613464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9117221832275</t>
+    <t xml:space="preserve">17.9911632537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9117202758789</t>
   </si>
   <si>
     <t xml:space="preserve">18.0378913879395</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6593761444092</t>
+    <t xml:space="preserve">17.6593780517578</t>
   </si>
   <si>
     <t xml:space="preserve">17.7948951721191</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6360111236572</t>
+    <t xml:space="preserve">17.6360130310059</t>
   </si>
   <si>
     <t xml:space="preserve">17.3275928497314</t>
@@ -2045,19 +2045,19 @@
     <t xml:space="preserve">17.869665145874</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3136005401611</t>
+    <t xml:space="preserve">18.3136024475098</t>
   </si>
   <si>
     <t xml:space="preserve">18.056583404541</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2855625152588</t>
+    <t xml:space="preserve">18.2855606079102</t>
   </si>
   <si>
     <t xml:space="preserve">18.0192012786865</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9677963256836</t>
+    <t xml:space="preserve">17.9677982330322</t>
   </si>
   <si>
     <t xml:space="preserve">17.9070472717285</t>
@@ -2066,16 +2066,16 @@
     <t xml:space="preserve">18.69211769104</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5051937103271</t>
+    <t xml:space="preserve">18.5051956176758</t>
   </si>
   <si>
     <t xml:space="preserve">18.3416404724121</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5565986633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4397716522217</t>
+    <t xml:space="preserve">18.5565967559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4397735595703</t>
   </si>
   <si>
     <t xml:space="preserve">18.5472526550293</t>
@@ -2084,13 +2084,13 @@
     <t xml:space="preserve">18.3089275360107</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8603439331055</t>
+    <t xml:space="preserve">18.8603458404541</t>
   </si>
   <si>
     <t xml:space="preserve">18.3696784973145</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5893096923828</t>
+    <t xml:space="preserve">18.5893077850342</t>
   </si>
   <si>
     <t xml:space="preserve">18.0238723754883</t>
@@ -2105,13 +2105,13 @@
     <t xml:space="preserve">17.5986270904541</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0939674377441</t>
+    <t xml:space="preserve">18.0939693450928</t>
   </si>
   <si>
     <t xml:space="preserve">19.860372543335</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0472965240479</t>
+    <t xml:space="preserve">20.0472946166992</t>
   </si>
   <si>
     <t xml:space="preserve">19.9071044921875</t>
@@ -2126,34 +2126,34 @@
     <t xml:space="preserve">19.4132251739502</t>
   </si>
   <si>
-    <t xml:space="preserve">19.204273223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4892082214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1187953948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2327690124512</t>
+    <t xml:space="preserve">19.2042751312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4892063140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1187973022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2327709197998</t>
   </si>
   <si>
     <t xml:space="preserve">18.9525890350342</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4397163391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7131443023682</t>
+    <t xml:space="preserve">18.4397144317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7131423950195</t>
   </si>
   <si>
     <t xml:space="preserve">17.7273902893066</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8318614959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3732299804688</t>
+    <t xml:space="preserve">17.8318634033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3732318878174</t>
   </si>
   <si>
     <t xml:space="preserve">18.6534099578857</t>
@@ -2165,13 +2165,13 @@
     <t xml:space="preserve">19.3657360076904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2802562713623</t>
+    <t xml:space="preserve">19.2802581787109</t>
   </si>
   <si>
     <t xml:space="preserve">19.2137718200684</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9810829162598</t>
+    <t xml:space="preserve">18.9810810089111</t>
   </si>
   <si>
     <t xml:space="preserve">18.905101776123</t>
@@ -2186,10 +2186,10 @@
     <t xml:space="preserve">19.6886558532715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9355945587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0210762023926</t>
+    <t xml:space="preserve">19.9355964660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0210742950439</t>
   </si>
   <si>
     <t xml:space="preserve">19.8026294708252</t>
@@ -2207,16 +2207,16 @@
     <t xml:space="preserve">19.926097869873</t>
   </si>
   <si>
-    <t xml:space="preserve">20.135046005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1920337677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4674625396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4864616394043</t>
+    <t xml:space="preserve">20.1350479125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1920318603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4674644470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4864597320557</t>
   </si>
   <si>
     <t xml:space="preserve">20.2870121002197</t>
@@ -2225,7 +2225,7 @@
     <t xml:space="preserve">20.2775135040283</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8406200408936</t>
+    <t xml:space="preserve">19.8406181335449</t>
   </si>
   <si>
     <t xml:space="preserve">19.821626663208</t>
@@ -2234,10 +2234,10 @@
     <t xml:space="preserve">19.8501167297363</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9545917510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9071025848389</t>
+    <t xml:space="preserve">19.95458984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9071006774902</t>
   </si>
   <si>
     <t xml:space="preserve">19.8881092071533</t>
@@ -2252,7 +2252,7 @@
     <t xml:space="preserve">19.9640884399414</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0020790100098</t>
+    <t xml:space="preserve">20.0020809173584</t>
   </si>
   <si>
     <t xml:space="preserve">19.9450931549072</t>
@@ -2264,22 +2264,22 @@
     <t xml:space="preserve">18.0218181610107</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9315872192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5754261016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2952461242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2762508392334</t>
+    <t xml:space="preserve">17.9315891265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5754241943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2952442169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.276252746582</t>
   </si>
   <si>
     <t xml:space="preserve">17.2667541503906</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3854751586914</t>
+    <t xml:space="preserve">17.3854732513428</t>
   </si>
   <si>
     <t xml:space="preserve">17.0198135375977</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">17.015064239502</t>
   </si>
   <si>
-    <t xml:space="preserve">16.59716796875</t>
+    <t xml:space="preserve">16.5971698760986</t>
   </si>
   <si>
     <t xml:space="preserve">16.2837448120117</t>
@@ -2315,13 +2315,13 @@
     <t xml:space="preserve">16.7348861694336</t>
   </si>
   <si>
-    <t xml:space="preserve">16.948579788208</t>
+    <t xml:space="preserve">16.9485816955566</t>
   </si>
   <si>
     <t xml:space="preserve">16.7491302490234</t>
   </si>
   <si>
-    <t xml:space="preserve">16.844108581543</t>
+    <t xml:space="preserve">16.8441066741943</t>
   </si>
   <si>
     <t xml:space="preserve">16.497444152832</t>
@@ -2330,10 +2330,10 @@
     <t xml:space="preserve">16.6683979034424</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6304092407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9248352050781</t>
+    <t xml:space="preserve">16.630407333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9248371124268</t>
   </si>
   <si>
     <t xml:space="preserve">17.4329605102539</t>
@@ -2345,28 +2345,28 @@
     <t xml:space="preserve">17.2097682952881</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1385364532471</t>
+    <t xml:space="preserve">17.1385345458984</t>
   </si>
   <si>
     <t xml:space="preserve">17.5231895446777</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2857494354248</t>
+    <t xml:space="preserve">17.2857475280762</t>
   </si>
   <si>
     <t xml:space="preserve">17.2002696990967</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6968936920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7538795471191</t>
+    <t xml:space="preserve">16.696891784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7538776397705</t>
   </si>
   <si>
     <t xml:space="preserve">16.2267570495605</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1887683868408</t>
+    <t xml:space="preserve">16.1887664794922</t>
   </si>
   <si>
     <t xml:space="preserve">16.1365299224854</t>
@@ -2378,19 +2378,19 @@
     <t xml:space="preserve">16.1840190887451</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1032886505127</t>
+    <t xml:space="preserve">16.1032905578613</t>
   </si>
   <si>
     <t xml:space="preserve">16.0178089141846</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4811906814575</t>
+    <t xml:space="preserve">15.4811916351318</t>
   </si>
   <si>
     <t xml:space="preserve">15.538179397583</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5619220733643</t>
+    <t xml:space="preserve">15.5619211196899</t>
   </si>
   <si>
     <t xml:space="preserve">15.1725187301636</t>
@@ -2408,7 +2408,7 @@
     <t xml:space="preserve">15.4716949462891</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6806421279907</t>
+    <t xml:space="preserve">15.680643081665</t>
   </si>
   <si>
     <t xml:space="preserve">15.4052104949951</t>
@@ -2429,22 +2429,22 @@
     <t xml:space="preserve">15.0680437088013</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0348014831543</t>
+    <t xml:space="preserve">15.0348024368286</t>
   </si>
   <si>
     <t xml:space="preserve">15.319730758667</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9608249664307</t>
+    <t xml:space="preserve">15.9608240127563</t>
   </si>
   <si>
     <t xml:space="preserve">15.7661228179932</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8800916671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9085855484009</t>
+    <t xml:space="preserve">15.8800926208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9085865020752</t>
   </si>
   <si>
     <t xml:space="preserve">15.922833442688</t>
@@ -2456,7 +2456,7 @@
     <t xml:space="preserve">16.1745204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4024658203125</t>
+    <t xml:space="preserve">16.4024639129639</t>
   </si>
   <si>
     <t xml:space="preserve">16.5781726837158</t>
@@ -2471,7 +2471,7 @@
     <t xml:space="preserve">17.2809982299805</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9723262786865</t>
+    <t xml:space="preserve">16.9723281860352</t>
   </si>
   <si>
     <t xml:space="preserve">16.4404544830322</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">16.3977165222168</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6209106445312</t>
+    <t xml:space="preserve">16.6209125518799</t>
   </si>
   <si>
     <t xml:space="preserve">17.3047428131104</t>
@@ -2501,10 +2501,10 @@
     <t xml:space="preserve">16.6873950958252</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9695796966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1120452880859</t>
+    <t xml:space="preserve">17.9695816040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1120433807373</t>
   </si>
   <si>
     <t xml:space="preserve">17.4282131195068</t>
@@ -2513,7 +2513,7 @@
     <t xml:space="preserve">17.3474826812744</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2477588653564</t>
+    <t xml:space="preserve">17.2477569580078</t>
   </si>
   <si>
     <t xml:space="preserve">17.3379859924316</t>
@@ -2525,37 +2525,37 @@
     <t xml:space="preserve">17.62766456604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5421829223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4804496765137</t>
+    <t xml:space="preserve">17.5421848297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4804515838623</t>
   </si>
   <si>
     <t xml:space="preserve">17.8033714294434</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1167964935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8556060791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8081188201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0028228759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6704044342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.622917175293</t>
+    <t xml:space="preserve">18.1167945861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8556079864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8081207275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0028209686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6704025268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6229152679443</t>
   </si>
   <si>
     <t xml:space="preserve">17.6799011230469</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9885749816895</t>
+    <t xml:space="preserve">17.9885768890381</t>
   </si>
   <si>
     <t xml:space="preserve">18.4207191467285</t>
@@ -2567,13 +2567,13 @@
     <t xml:space="preserve">17.9030952453613</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8508605957031</t>
+    <t xml:space="preserve">17.8508586883545</t>
   </si>
   <si>
     <t xml:space="preserve">17.2620029449463</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2287635803223</t>
+    <t xml:space="preserve">17.2287616729736</t>
   </si>
   <si>
     <t xml:space="preserve">17.0957946777344</t>
@@ -2594,7 +2594,7 @@
     <t xml:space="preserve">16.2694988250732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2979927062988</t>
+    <t xml:space="preserve">16.2979907989502</t>
   </si>
   <si>
     <t xml:space="preserve">16.1175346374512</t>
@@ -2603,13 +2603,13 @@
     <t xml:space="preserve">15.8468523025513</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3217353820801</t>
+    <t xml:space="preserve">16.3217334747314</t>
   </si>
   <si>
     <t xml:space="preserve">16.0842933654785</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7803678512573</t>
+    <t xml:space="preserve">15.780366897583</t>
   </si>
   <si>
     <t xml:space="preserve">15.7186336517334</t>
@@ -2618,19 +2618,19 @@
     <t xml:space="preserve">15.3434762954712</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9845695495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.747127532959</t>
+    <t xml:space="preserve">15.9845676422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7471265792847</t>
   </si>
   <si>
     <t xml:space="preserve">15.6046619415283</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7043867111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8848428726196</t>
+    <t xml:space="preserve">15.7043876647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8848447799683</t>
   </si>
   <si>
     <t xml:space="preserve">15.5429258346558</t>
@@ -2639,10 +2639,10 @@
     <t xml:space="preserve">15.1582717895508</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8096036911011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8665895462036</t>
+    <t xml:space="preserve">13.8096027374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8665885925293</t>
   </si>
   <si>
     <t xml:space="preserve">14.1420221328735</t>
@@ -2654,10 +2654,10 @@
     <t xml:space="preserve">13.5721616744995</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0735340118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0497894287109</t>
+    <t xml:space="preserve">13.0735349655151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0497903823853</t>
   </si>
   <si>
     <t xml:space="preserve">12.9738082885742</t>
@@ -2669,19 +2669,19 @@
     <t xml:space="preserve">12.0477876663208</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2784757614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6563787460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7845973968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08166694641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65437602996826</t>
+    <t xml:space="preserve">11.2784767150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.656379699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7845964431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08166599273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65437507629395</t>
   </si>
   <si>
     <t xml:space="preserve">10.0057888031006</t>
@@ -2699,7 +2699,7 @@
     <t xml:space="preserve">11.8625812530518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1665077209473</t>
+    <t xml:space="preserve">12.1665086746216</t>
   </si>
   <si>
     <t xml:space="preserve">13.0877799987793</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">13.3964548110962</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9690599441528</t>
+    <t xml:space="preserve">12.9690589904785</t>
   </si>
   <si>
     <t xml:space="preserve">12.2519865036011</t>
@@ -2720,16 +2720,16 @@
     <t xml:space="preserve">11.4921731948853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2072439193726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1597547531128</t>
+    <t xml:space="preserve">11.2072429656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1597557067871</t>
   </si>
   <si>
     <t xml:space="preserve">11.1882476806641</t>
   </si>
   <si>
-    <t xml:space="preserve">11.568154335022</t>
+    <t xml:space="preserve">11.5681552886963</t>
   </si>
   <si>
     <t xml:space="preserve">11.5586566925049</t>
@@ -2741,7 +2741,7 @@
     <t xml:space="preserve">11.9765529632568</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4541826248169</t>
+    <t xml:space="preserve">11.4541835784912</t>
   </si>
   <si>
     <t xml:space="preserve">11.2927227020264</t>
@@ -2756,7 +2756,7 @@
     <t xml:space="preserve">10.399941444397</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4474296569824</t>
+    <t xml:space="preserve">10.4474306106567</t>
   </si>
   <si>
     <t xml:space="preserve">10.3809471130371</t>
@@ -2765,13 +2765,13 @@
     <t xml:space="preserve">10.7323598861694</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9128150939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.722861289978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3049659729004</t>
+    <t xml:space="preserve">10.9128160476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7228622436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3049650192261</t>
   </si>
   <si>
     <t xml:space="preserve">10.3524532318115</t>
@@ -2780,13 +2780,13 @@
     <t xml:space="preserve">10.3144626617432</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3429565429688</t>
+    <t xml:space="preserve">10.3429555892944</t>
   </si>
   <si>
     <t xml:space="preserve">10.4094400405884</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2574768066406</t>
+    <t xml:space="preserve">10.2574777603149</t>
   </si>
   <si>
     <t xml:space="preserve">10.0295333862305</t>
@@ -2795,10 +2795,10 @@
     <t xml:space="preserve">9.9060640335083</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89656639099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64962673187256</t>
+    <t xml:space="preserve">9.89656543731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64962577819824</t>
   </si>
   <si>
     <t xml:space="preserve">9.78259372711182</t>
@@ -2807,7 +2807,7 @@
     <t xml:space="preserve">10.4949188232422</t>
   </si>
   <si>
-    <t xml:space="preserve">12.346962928772</t>
+    <t xml:space="preserve">12.3469619750977</t>
   </si>
   <si>
     <t xml:space="preserve">11.9005727767944</t>
@@ -2828,16 +2828,16 @@
     <t xml:space="preserve">13.2872314453125</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1542654037476</t>
+    <t xml:space="preserve">13.1542644500732</t>
   </si>
   <si>
     <t xml:space="preserve">12.8218460083008</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8815784454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7771024703979</t>
+    <t xml:space="preserve">11.8815774917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7771034240723</t>
   </si>
   <si>
     <t xml:space="preserve">12.062032699585</t>
@@ -2846,7 +2846,7 @@
     <t xml:space="preserve">12.1190185546875</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2899770736694</t>
+    <t xml:space="preserve">12.2899761199951</t>
   </si>
   <si>
     <t xml:space="preserve">12.3089723587036</t>
@@ -2867,7 +2867,7 @@
     <t xml:space="preserve">11.8055963516235</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5111684799194</t>
+    <t xml:space="preserve">11.5111694335938</t>
   </si>
   <si>
     <t xml:space="preserve">11.7296142578125</t>
@@ -2882,7 +2882,7 @@
     <t xml:space="preserve">11.7581081390381</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5871486663818</t>
+    <t xml:space="preserve">11.5871496200562</t>
   </si>
   <si>
     <t xml:space="preserve">11.4826755523682</t>
@@ -2897,7 +2897,7 @@
     <t xml:space="preserve">11.1787509918213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2262382507324</t>
+    <t xml:space="preserve">11.2262372970581</t>
   </si>
   <si>
     <t xml:space="preserve">11.2452344894409</t>
@@ -2924,7 +2924,7 @@
     <t xml:space="preserve">11.2167415618896</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5708999633789</t>
+    <t xml:space="preserve">10.5708990097046</t>
   </si>
   <si>
     <t xml:space="preserve">10.580397605896</t>
@@ -2933,19 +2933,19 @@
     <t xml:space="preserve">10.4379320144653</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3619518280029</t>
+    <t xml:space="preserve">10.3619508743286</t>
   </si>
   <si>
     <t xml:space="preserve">11.644136428833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3307123184204</t>
+    <t xml:space="preserve">11.3307132720947</t>
   </si>
   <si>
     <t xml:space="preserve">11.0932712554932</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9603042602539</t>
+    <t xml:space="preserve">10.9603033065796</t>
   </si>
   <si>
     <t xml:space="preserve">10.760853767395</t>
@@ -2957,19 +2957,19 @@
     <t xml:space="preserve">10.6753740310669</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6156425476074</t>
+    <t xml:space="preserve">11.6156415939331</t>
   </si>
   <si>
     <t xml:space="preserve">11.4636793136597</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3971967697144</t>
+    <t xml:space="preserve">11.3971977233887</t>
   </si>
   <si>
     <t xml:space="preserve">11.5016708374023</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7960977554321</t>
+    <t xml:space="preserve">11.7960987091064</t>
   </si>
   <si>
     <t xml:space="preserve">11.4731779098511</t>
@@ -2984,13 +2984,13 @@
     <t xml:space="preserve">12.565408706665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0810289382935</t>
+    <t xml:space="preserve">12.0810279846191</t>
   </si>
   <si>
     <t xml:space="preserve">11.6821269989014</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6061458587646</t>
+    <t xml:space="preserve">11.6061449050903</t>
   </si>
   <si>
     <t xml:space="preserve">12.1095209121704</t>
@@ -2999,16 +2999,16 @@
     <t xml:space="preserve">12.0145444869995</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9385633468628</t>
+    <t xml:space="preserve">11.9385623931885</t>
   </si>
   <si>
     <t xml:space="preserve">11.957558631897</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9860506057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1285171508789</t>
+    <t xml:space="preserve">11.9860515594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1285181045532</t>
   </si>
   <si>
     <t xml:space="preserve">12.2804803848267</t>
@@ -3032,13 +3032,13 @@
     <t xml:space="preserve">12.8978281021118</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1949996948242</t>
+    <t xml:space="preserve">12.1950006484985</t>
   </si>
   <si>
     <t xml:space="preserve">11.8910760879517</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6726293563843</t>
+    <t xml:space="preserve">11.67262840271</t>
   </si>
   <si>
     <t xml:space="preserve">11.3117170333862</t>
@@ -3047,13 +3047,13 @@
     <t xml:space="preserve">10.6943693161011</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5139141082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7988433837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0647773742676</t>
+    <t xml:space="preserve">10.5139131546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7988443374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0647783279419</t>
   </si>
   <si>
     <t xml:space="preserve">11.3592052459717</t>
@@ -3089,22 +3089,22 @@
     <t xml:space="preserve">14.0470447540283</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6264009475708</t>
+    <t xml:space="preserve">14.6264019012451</t>
   </si>
   <si>
     <t xml:space="preserve">14.3129787445068</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1515188217163</t>
+    <t xml:space="preserve">14.1515197753906</t>
   </si>
   <si>
     <t xml:space="preserve">14.2464952468872</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4269514083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4649419784546</t>
+    <t xml:space="preserve">14.4269504547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4649410247803</t>
   </si>
   <si>
     <t xml:space="preserve">14.9113321304321</t>
@@ -3134,10 +3134,10 @@
     <t xml:space="preserve">14.7593698501587</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3794622421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5694160461426</t>
+    <t xml:space="preserve">14.3794631958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5694169998169</t>
   </si>
   <si>
     <t xml:space="preserve">14.6453981399536</t>
@@ -3155,13 +3155,13 @@
     <t xml:space="preserve">14.9493227005005</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7688674926758</t>
+    <t xml:space="preserve">14.7688684463501</t>
   </si>
   <si>
     <t xml:space="preserve">14.7118806838989</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5884103775024</t>
+    <t xml:space="preserve">14.5884113311768</t>
   </si>
   <si>
     <t xml:space="preserve">14.5789136886597</t>
@@ -3185,19 +3185,19 @@
     <t xml:space="preserve">14.4459466934204</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2912397384644</t>
+    <t xml:space="preserve">15.29123878479</t>
   </si>
   <si>
     <t xml:space="preserve">14.683388710022</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0537967681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8041124343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6711444854736</t>
+    <t xml:space="preserve">15.0537977218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8041114807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6711454391479</t>
   </si>
   <si>
     <t xml:space="preserve">15.2627458572388</t>
@@ -3212,7 +3212,7 @@
     <t xml:space="preserve">14.721378326416</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6359004974365</t>
+    <t xml:space="preserve">14.6358995437622</t>
   </si>
   <si>
     <t xml:space="preserve">14.4364490509033</t>
@@ -3224,19 +3224,19 @@
     <t xml:space="preserve">15.006308555603</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0822906494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9778156280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6928863525391</t>
+    <t xml:space="preserve">15.0822896957397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9778165817261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6928853988647</t>
   </si>
   <si>
     <t xml:space="preserve">14.7783651351929</t>
   </si>
   <si>
-    <t xml:space="preserve">14.825852394104</t>
+    <t xml:space="preserve">14.8258533477783</t>
   </si>
   <si>
     <t xml:space="preserve">15.2057600021362</t>
@@ -3251,13 +3251,13 @@
     <t xml:space="preserve">15.1012849807739</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8448476791382</t>
+    <t xml:space="preserve">14.8448486328125</t>
   </si>
   <si>
     <t xml:space="preserve">14.9873123168945</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8705949783325</t>
+    <t xml:space="preserve">15.8705940246582</t>
   </si>
   <si>
     <t xml:space="preserve">16.0225601196289</t>
@@ -3269,7 +3269,7 @@
     <t xml:space="preserve">15.8231077194214</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9370803833008</t>
+    <t xml:space="preserve">15.9370794296265</t>
   </si>
   <si>
     <t xml:space="preserve">15.7376298904419</t>
@@ -3278,7 +3278,7 @@
     <t xml:space="preserve">15.4906892776489</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7091369628906</t>
+    <t xml:space="preserve">15.7091379165649</t>
   </si>
   <si>
     <t xml:space="preserve">15.3102350234985</t>
@@ -3293,22 +3293,22 @@
     <t xml:space="preserve">15.6996374130249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6853904724121</t>
+    <t xml:space="preserve">15.6853914260864</t>
   </si>
   <si>
     <t xml:space="preserve">15.6189079284668</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4289560317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6379041671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7396335601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8678512573242</t>
+    <t xml:space="preserve">15.428955078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.637903213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.739631652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8678493499756</t>
   </si>
   <si>
     <t xml:space="preserve">16.8726005554199</t>
@@ -3317,16 +3317,16 @@
     <t xml:space="preserve">16.4784469604492</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0340576171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.513692855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4567050933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0388088226318</t>
+    <t xml:space="preserve">17.0340595245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5136947631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4567070007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0388107299805</t>
   </si>
   <si>
     <t xml:space="preserve">17.2904968261719</t>
@@ -3371,19 +3371,19 @@
     <t xml:space="preserve">17.9125938415527</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9553337097168</t>
+    <t xml:space="preserve">17.9553356170654</t>
   </si>
   <si>
     <t xml:space="preserve">17.6846504211426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0408134460449</t>
+    <t xml:space="preserve">18.0408115386963</t>
   </si>
   <si>
     <t xml:space="preserve">18.3304901123047</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3209934234619</t>
+    <t xml:space="preserve">18.3209953308105</t>
   </si>
   <si>
     <t xml:space="preserve">18.368480682373</t>
@@ -3395,22 +3395,22 @@
     <t xml:space="preserve">18.3542366027832</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3969745635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5299434661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2972469329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1690292358398</t>
+    <t xml:space="preserve">18.3969764709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5299415588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.297248840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1690311431885</t>
   </si>
   <si>
     <t xml:space="preserve">18.1832790374756</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4444637298584</t>
+    <t xml:space="preserve">18.4444618225098</t>
   </si>
   <si>
     <t xml:space="preserve">18.8956031799316</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">18.6961498260498</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5584373474121</t>
+    <t xml:space="preserve">18.5584354400635</t>
   </si>
   <si>
     <t xml:space="preserve">18.3352394104004</t>
@@ -3431,16 +3431,16 @@
     <t xml:space="preserve">17.1527805328369</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1812744140625</t>
+    <t xml:space="preserve">17.1812725067139</t>
   </si>
   <si>
     <t xml:space="preserve">17.0673007965088</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1575317382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6114120483398</t>
+    <t xml:space="preserve">17.1575298309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6114139556885</t>
   </si>
   <si>
     <t xml:space="preserve">16.5021896362305</t>
@@ -3458,10 +3458,10 @@
     <t xml:space="preserve">15.9798202514648</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0985412597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0083122253418</t>
+    <t xml:space="preserve">16.098539352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0083103179932</t>
   </si>
   <si>
     <t xml:space="preserve">16.2505035400391</t>
@@ -3470,7 +3470,7 @@
     <t xml:space="preserve">16.4736976623535</t>
   </si>
   <si>
-    <t xml:space="preserve">16.169771194458</t>
+    <t xml:space="preserve">16.1697731018066</t>
   </si>
   <si>
     <t xml:space="preserve">16.0463027954102</t>
@@ -3479,25 +3479,25 @@
     <t xml:space="preserve">16.0368041992188</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9988136291504</t>
+    <t xml:space="preserve">15.9988145828247</t>
   </si>
   <si>
     <t xml:space="preserve">16.2600021362305</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0652980804443</t>
+    <t xml:space="preserve">16.065299987793</t>
   </si>
   <si>
     <t xml:space="preserve">16.0510520935059</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1100406646729</t>
+    <t xml:space="preserve">17.1100425720215</t>
   </si>
   <si>
     <t xml:space="preserve">17.3949718475342</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4919528961182</t>
+    <t xml:space="preserve">18.4919509887695</t>
   </si>
   <si>
     <t xml:space="preserve">17.5896739959717</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">16.6731491088867</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5164375305176</t>
+    <t xml:space="preserve">16.5164356231689</t>
   </si>
   <si>
     <t xml:space="preserve">15.7328805923462</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">15.7423782348633</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1460266113281</t>
+    <t xml:space="preserve">16.1460285186768</t>
   </si>
   <si>
     <t xml:space="preserve">15.9275808334351</t>
@@ -3551,7 +3551,7 @@
     <t xml:space="preserve">16.8251113891602</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7206382751465</t>
+    <t xml:space="preserve">16.7206363677979</t>
   </si>
   <si>
     <t xml:space="preserve">16.9628295898438</t>
@@ -3560,13 +3560,13 @@
     <t xml:space="preserve">16.9438304901123</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8298606872559</t>
+    <t xml:space="preserve">16.8298587799072</t>
   </si>
   <si>
     <t xml:space="preserve">16.9913196563721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8346099853516</t>
+    <t xml:space="preserve">16.8346118927002</t>
   </si>
   <si>
     <t xml:space="preserve">17.0435562133789</t>
@@ -3602,16 +3602,16 @@
     <t xml:space="preserve">18.1405372619629</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7008991241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7911262512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9715843200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9458351135254</t>
+    <t xml:space="preserve">18.7009010314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7911281585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9715824127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.945837020874</t>
   </si>
   <si>
     <t xml:space="preserve">18.4302177429199</t>
@@ -3620,19 +3620,19 @@
     <t xml:space="preserve">18.5536861419678</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7626323699951</t>
+    <t xml:space="preserve">18.7626342773438</t>
   </si>
   <si>
     <t xml:space="preserve">19.0903053283691</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3752346038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9240951538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1662845611572</t>
+    <t xml:space="preserve">19.3752326965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.92409324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1662864685059</t>
   </si>
   <si>
     <t xml:space="preserve">19.4037265777588</t>
@@ -3647,7 +3647,7 @@
     <t xml:space="preserve">19.1377906799316</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6316699981689</t>
+    <t xml:space="preserve">19.6316719055176</t>
   </si>
   <si>
     <t xml:space="preserve">20.4579677581787</t>
@@ -3656,25 +3656,25 @@
     <t xml:space="preserve">20.6289253234863</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0373268127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4457225799561</t>
+    <t xml:space="preserve">21.0373249053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4457244873047</t>
   </si>
   <si>
     <t xml:space="preserve">20.9898376464844</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7523975372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6384239196777</t>
+    <t xml:space="preserve">20.7523956298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6384220123291</t>
   </si>
   <si>
     <t xml:space="preserve">20.1635398864746</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0970554351807</t>
+    <t xml:space="preserve">20.0970573425293</t>
   </si>
   <si>
     <t xml:space="preserve">20.7903861999512</t>
@@ -3683,7 +3683,7 @@
     <t xml:space="preserve">20.7144031524658</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0278282165527</t>
+    <t xml:space="preserve">21.0278263092041</t>
   </si>
   <si>
     <t xml:space="preserve">21.0183296203613</t>
@@ -3695,19 +3695,19 @@
     <t xml:space="preserve">21.4172306060791</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3982353210449</t>
+    <t xml:space="preserve">21.3982372283936</t>
   </si>
   <si>
     <t xml:space="preserve">21.7021617889404</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5691947937012</t>
+    <t xml:space="preserve">21.5691928863525</t>
   </si>
   <si>
     <t xml:space="preserve">22.0820693969727</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5976867675781</t>
+    <t xml:space="preserve">21.5976886749268</t>
   </si>
   <si>
     <t xml:space="preserve">21.6261806488037</t>
@@ -3749,10 +3749,10 @@
     <t xml:space="preserve">18.0977993011475</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0503101348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2830028533936</t>
+    <t xml:space="preserve">18.0503082275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2830047607422</t>
   </si>
   <si>
     <t xml:space="preserve">18.1927757263184</t>
@@ -3773,31 +3773,31 @@
     <t xml:space="preserve">18.8006248474121</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5964260101318</t>
+    <t xml:space="preserve">18.5964241027832</t>
   </si>
   <si>
     <t xml:space="preserve">18.7768821716309</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9220905303955</t>
+    <t xml:space="preserve">17.9220924377441</t>
   </si>
   <si>
     <t xml:space="preserve">18.6581611633301</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4492130279541</t>
+    <t xml:space="preserve">18.4492111206055</t>
   </si>
   <si>
     <t xml:space="preserve">17.6324138641357</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7368869781494</t>
+    <t xml:space="preserve">17.7368850708008</t>
   </si>
   <si>
     <t xml:space="preserve">17.12428855896</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1867637634277</t>
+    <t xml:space="preserve">15.1867647171021</t>
   </si>
   <si>
     <t xml:space="preserve">14.8306016921997</t>
@@ -3812,16 +3812,16 @@
     <t xml:space="preserve">15.3529739379883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.457447052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8733415603638</t>
+    <t xml:space="preserve">15.4574480056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8733406066895</t>
   </si>
   <si>
     <t xml:space="preserve">15.5856657028198</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8136100769043</t>
+    <t xml:space="preserve">15.81360912323</t>
   </si>
   <si>
     <t xml:space="preserve">15.5334281921387</t>
@@ -3836,7 +3836,7 @@
     <t xml:space="preserve">15.5191831588745</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8278589248657</t>
+    <t xml:space="preserve">15.82785987854</t>
   </si>
   <si>
     <t xml:space="preserve">16.7681255340576</t>
@@ -3845,16 +3845,16 @@
     <t xml:space="preserve">16.316987991333</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9750709533691</t>
+    <t xml:space="preserve">15.9750719070435</t>
   </si>
   <si>
     <t xml:space="preserve">15.0253038406372</t>
   </si>
   <si>
-    <t xml:space="preserve">15.633152961731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6521482467651</t>
+    <t xml:space="preserve">15.6331539154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6521492004395</t>
   </si>
   <si>
     <t xml:space="preserve">15.8895902633667</t>
@@ -3869,19 +3869,19 @@
     <t xml:space="preserve">14.8638439178467</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1392765045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7851181030273</t>
+    <t xml:space="preserve">15.1392755508423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7851190567017</t>
   </si>
   <si>
     <t xml:space="preserve">14.3034820556641</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3224763870239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8285989761353</t>
+    <t xml:space="preserve">14.3224773406982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8285980224609</t>
   </si>
   <si>
     <t xml:space="preserve">12.8123483657837</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">14.1040306091309</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1990079879761</t>
+    <t xml:space="preserve">14.1990070343018</t>
   </si>
   <si>
     <t xml:space="preserve">15.0158071517944</t>
@@ -74156,6 +74156,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2603">
+      <c r="A2603" s="1" t="n">
+        <v>46111.2916666667</v>
+      </c>
+      <c r="B2603" t="n">
+        <v>738749</v>
+      </c>
+      <c r="C2603" t="n">
+        <v>6.94999980926514</v>
+      </c>
+      <c r="D2603" t="n">
+        <v>6.33500003814697</v>
+      </c>
+      <c r="E2603" t="n">
+        <v>6.73999977111816</v>
+      </c>
+      <c r="F2603" t="n">
+        <v>6.90500020980835</v>
+      </c>
+      <c r="G2603" t="s">
+        <v>2038</v>
+      </c>
+      <c r="H2603" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2763481140137</t>
+    <t xml:space="preserve">18.2763519287109</t>
   </si>
   <si>
     <t xml:space="preserve">SFER.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">18.0109672546387</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4978828430176</t>
+    <t xml:space="preserve">17.4978809356689</t>
   </si>
   <si>
     <t xml:space="preserve">17.9401950836182</t>
   </si>
   <si>
-    <t xml:space="preserve">17.683650970459</t>
+    <t xml:space="preserve">17.6836528778076</t>
   </si>
   <si>
     <t xml:space="preserve">18.2498111724854</t>
@@ -71,34 +71,34 @@
     <t xml:space="preserve">18.4621238708496</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2851982116699</t>
+    <t xml:space="preserve">18.2851963043213</t>
   </si>
   <si>
     <t xml:space="preserve">18.0994262695312</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6394195556641</t>
+    <t xml:space="preserve">17.6394233703613</t>
   </si>
   <si>
     <t xml:space="preserve">17.5686531066895</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1878871917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4798145294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.223274230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7632675170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3913555145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6744346618652</t>
+    <t xml:space="preserve">18.1878890991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4798164367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2232761383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7632694244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3913516998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.674430847168</t>
   </si>
   <si>
     <t xml:space="preserve">17.9578857421875</t>
@@ -110,49 +110,49 @@
     <t xml:space="preserve">18.2586574554443</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0817337036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3563404083252</t>
+    <t xml:space="preserve">18.0817356109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3563423156738</t>
   </si>
   <si>
     <t xml:space="preserve">16.9051837921143</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1617221832275</t>
+    <t xml:space="preserve">17.1617240905762</t>
   </si>
   <si>
     <t xml:space="preserve">16.6486434936523</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0201854705811</t>
+    <t xml:space="preserve">17.0201835632324</t>
   </si>
   <si>
     <t xml:space="preserve">17.48903465271</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6305732727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4090423583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4532775878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9752063751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1348114013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3121089935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9048099517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3471183776855</t>
+    <t xml:space="preserve">17.6305770874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4090442657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.453275680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9752082824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1348094940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3121109008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.904806137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3471202850342</t>
   </si>
   <si>
     <t xml:space="preserve">19.019437789917</t>
@@ -164,10 +164,10 @@
     <t xml:space="preserve">18.8513584136963</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3113651275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.992525100708</t>
+    <t xml:space="preserve">19.3113632202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9925231933594</t>
   </si>
   <si>
     <t xml:space="preserve">19.9482917785645</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">19.3379039764404</t>
   </si>
   <si>
-    <t xml:space="preserve">19.647518157959</t>
+    <t xml:space="preserve">19.6475219726562</t>
   </si>
   <si>
     <t xml:space="preserve">19.9836769104004</t>
@@ -191,49 +191,49 @@
     <t xml:space="preserve">19.444055557251</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0367565155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.178295135498</t>
+    <t xml:space="preserve">20.0367527008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1782932281494</t>
   </si>
   <si>
     <t xml:space="preserve">19.4971351623535</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4705963134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9663600921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4794425964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9129066467285</t>
+    <t xml:space="preserve">19.4705944061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9663581848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4794406890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9129085540771</t>
   </si>
   <si>
     <t xml:space="preserve">19.8686752319336</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4175186157227</t>
+    <t xml:space="preserve">19.4175205230713</t>
   </si>
   <si>
     <t xml:space="preserve">18.8690490722656</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8336658477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5151996612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9309730529785</t>
+    <t xml:space="preserve">18.833667755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5152015686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9309711456299</t>
   </si>
   <si>
     <t xml:space="preserve">18.8955879211426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5240497589111</t>
+    <t xml:space="preserve">18.5240478515625</t>
   </si>
   <si>
     <t xml:space="preserve">18.9486675262451</t>
@@ -245,13 +245,13 @@
     <t xml:space="preserve">18.8778972625732</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2936687469482</t>
+    <t xml:space="preserve">19.2936706542969</t>
   </si>
   <si>
     <t xml:space="preserve">18.8071269989014</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3205814361572</t>
+    <t xml:space="preserve">18.3205833435059</t>
   </si>
   <si>
     <t xml:space="preserve">18.3648147583008</t>
@@ -263,10 +263,10 @@
     <t xml:space="preserve">18.0640411376953</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3117408752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8782711029053</t>
+    <t xml:space="preserve">18.3117370605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8782653808594</t>
   </si>
   <si>
     <t xml:space="preserve">18.0021171569824</t>
@@ -275,46 +275,46 @@
     <t xml:space="preserve">17.7190399169922</t>
   </si>
   <si>
-    <t xml:space="preserve">17.444803237915</t>
+    <t xml:space="preserve">17.4448013305664</t>
   </si>
   <si>
     <t xml:space="preserve">17.1440296173096</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5509605407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9844264984131</t>
+    <t xml:space="preserve">17.5509586334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9844245910645</t>
   </si>
   <si>
     <t xml:space="preserve">17.4182662963867</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9313488006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7367286682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6482696533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5939388275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8112564086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7025947570801</t>
+    <t xml:space="preserve">17.9313507080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7367267608643</t>
   </si>
   <si>
     <t xml:space="preserve">17.6482677459717</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5305500030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4128360748291</t>
+    <t xml:space="preserve">17.593936920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.81125831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7025985717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.648265838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5305519104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4128341674805</t>
   </si>
   <si>
     <t xml:space="preserve">17.3041763305664</t>
@@ -323,16 +323,16 @@
     <t xml:space="preserve">17.4762191772461</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4309463500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4852771759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7478733062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6844863891602</t>
+    <t xml:space="preserve">17.4309482574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4852752685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.747875213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6844882965088</t>
   </si>
   <si>
     <t xml:space="preserve">17.1502418518066</t>
@@ -341,28 +341,28 @@
     <t xml:space="preserve">16.71559715271</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5435562133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0415802001953</t>
+    <t xml:space="preserve">16.5435543060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0415782928467</t>
   </si>
   <si>
     <t xml:space="preserve">17.0778007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8384227752686</t>
+    <t xml:space="preserve">17.8384246826172</t>
   </si>
   <si>
     <t xml:space="preserve">17.9380283355713</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7297630310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8655872344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1825141906738</t>
+    <t xml:space="preserve">17.7297649383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8655891418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1825122833252</t>
   </si>
   <si>
     <t xml:space="preserve">16.8514251708984</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">16.262845993042</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5254440307617</t>
+    <t xml:space="preserve">16.5254402160645</t>
   </si>
   <si>
     <t xml:space="preserve">16.6069393157959</t>
@@ -386,22 +386,22 @@
     <t xml:space="preserve">16.8061485290527</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8242607116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0726890563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8734817504883</t>
+    <t xml:space="preserve">16.8242588043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0726928710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8734798431396</t>
   </si>
   <si>
     <t xml:space="preserve">16.3624515533447</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4439468383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.69748878479</t>
+    <t xml:space="preserve">16.4439487457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6974868774414</t>
   </si>
   <si>
     <t xml:space="preserve">17.0959091186523</t>
@@ -410,43 +410,43 @@
     <t xml:space="preserve">17.1321296691895</t>
   </si>
   <si>
-    <t xml:space="preserve">17.086856842041</t>
+    <t xml:space="preserve">17.0868530273438</t>
   </si>
   <si>
     <t xml:space="preserve">17.0325260162354</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3403968811035</t>
+    <t xml:space="preserve">17.3403949737549</t>
   </si>
   <si>
     <t xml:space="preserve">17.9018077850342</t>
   </si>
   <si>
-    <t xml:space="preserve">18.137243270874</t>
+    <t xml:space="preserve">18.1372394561768</t>
   </si>
   <si>
     <t xml:space="preserve">17.9289741516113</t>
   </si>
   <si>
-    <t xml:space="preserve">18.771089553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6352653503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0699062347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.214786529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6262130737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4994430541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2187347412109</t>
+    <t xml:space="preserve">18.7710914611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6352672576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0699081420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2147884368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6262111663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4994411468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2187366485596</t>
   </si>
   <si>
     <t xml:space="preserve">18.7167625427246</t>
@@ -458,13 +458,13 @@
     <t xml:space="preserve">18.762035369873</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8073120117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.94313621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0427417755127</t>
+    <t xml:space="preserve">18.8073139190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9431381225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0427436828613</t>
   </si>
   <si>
     <t xml:space="preserve">18.6624317169189</t>
@@ -473,10 +473,10 @@
     <t xml:space="preserve">18.4722747802734</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6171569824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7529830932617</t>
+    <t xml:space="preserve">18.6171550750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7529792785645</t>
   </si>
   <si>
     <t xml:space="preserve">18.9703044891357</t>
@@ -485,22 +485,22 @@
     <t xml:space="preserve">18.6805400848389</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6081027984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.653377532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5175495147705</t>
+    <t xml:space="preserve">18.6081008911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6533756256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5175533294678</t>
   </si>
   <si>
     <t xml:space="preserve">18.870698928833</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6986522674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1061305999756</t>
+    <t xml:space="preserve">18.6986503601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.106128692627</t>
   </si>
   <si>
     <t xml:space="preserve">19.9210815429688</t>
@@ -509,52 +509,52 @@
     <t xml:space="preserve">19.6947059631348</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5588798522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4592742919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.314395904541</t>
+    <t xml:space="preserve">19.5588817596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4592761993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3143939971924</t>
   </si>
   <si>
     <t xml:space="preserve">18.8888092041016</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1332912445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.160457611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9391937255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4553318023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3557205200195</t>
+    <t xml:space="preserve">19.1332950592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1604595184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9391899108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4553279876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3557224273682</t>
   </si>
   <si>
     <t xml:space="preserve">20.3104496002197</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3919429779053</t>
+    <t xml:space="preserve">20.3919448852539</t>
   </si>
   <si>
     <t xml:space="preserve">20.4643840789795</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6907615661621</t>
+    <t xml:space="preserve">20.6907596588135</t>
   </si>
   <si>
     <t xml:space="preserve">20.8446960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7994194030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4010009765625</t>
+    <t xml:space="preserve">20.7994213104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4009990692139</t>
   </si>
   <si>
     <t xml:space="preserve">20.1021823883057</t>
@@ -563,67 +563,67 @@
     <t xml:space="preserve">20.5277690887451</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3647804260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5458793640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7541465759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4191093444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0116329193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.265172958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3285598754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.03879737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1474571228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2289524078369</t>
+    <t xml:space="preserve">20.3647766113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5458812713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7541446685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4191074371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0116348266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2651710510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3285579681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0387954711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1474590301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2289543151855</t>
   </si>
   <si>
     <t xml:space="preserve">20.5006046295166</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5639896392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1836776733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5498275756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4140014648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5045509338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7218742370605</t>
+    <t xml:space="preserve">20.5639877319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1836795806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.549825668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4140033721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5045528411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7218723297119</t>
   </si>
   <si>
     <t xml:space="preserve">19.7943115234375</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5226593017578</t>
+    <t xml:space="preserve">19.5226612091064</t>
   </si>
   <si>
     <t xml:space="preserve">19.830530166626</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9120254516602</t>
+    <t xml:space="preserve">19.9120273590088</t>
   </si>
   <si>
     <t xml:space="preserve">19.7490348815918</t>
@@ -656,13 +656,13 @@
     <t xml:space="preserve">17.6392116546631</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3455047607422</t>
+    <t xml:space="preserve">18.3455066680908</t>
   </si>
   <si>
     <t xml:space="preserve">18.3907794952393</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1514015197754</t>
+    <t xml:space="preserve">19.151403427124</t>
   </si>
   <si>
     <t xml:space="preserve">19.2872276306152</t>
@@ -671,31 +671,31 @@
     <t xml:space="preserve">19.3958911895752</t>
   </si>
   <si>
-    <t xml:space="preserve">19.377779006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1151847839355</t>
+    <t xml:space="preserve">19.3777770996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1151828765869</t>
   </si>
   <si>
     <t xml:space="preserve">19.5860462188721</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2600650787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3738346099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3466701507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2380084991455</t>
+    <t xml:space="preserve">19.2600631713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.373836517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3466682434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2380065917969</t>
   </si>
   <si>
     <t xml:space="preserve">20.1293468475342</t>
   </si>
   <si>
-    <t xml:space="preserve">20.15651512146</t>
+    <t xml:space="preserve">20.1565132141113</t>
   </si>
   <si>
     <t xml:space="preserve">20.8084754943848</t>
@@ -710,37 +710,37 @@
     <t xml:space="preserve">21.5328788757324</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0671253204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0580711364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2572803497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2935009002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3025588989258</t>
+    <t xml:space="preserve">22.0671272277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.058069229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2572822570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2935028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3025550842285</t>
   </si>
   <si>
     <t xml:space="preserve">22.3206653594971</t>
   </si>
   <si>
-    <t xml:space="preserve">22.275390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2391719818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8186950683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0722351074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8911361694336</t>
+    <t xml:space="preserve">22.2753925323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2391738891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.818696975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0722332000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.891134262085</t>
   </si>
   <si>
     <t xml:space="preserve">23.1537303924561</t>
@@ -749,16 +749,16 @@
     <t xml:space="preserve">23.0993995666504</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5923194885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3568859100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9092426300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1757869720459</t>
+    <t xml:space="preserve">22.5923175811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3568897247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9092445373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1757831573486</t>
   </si>
   <si>
     <t xml:space="preserve">22.1395664215088</t>
@@ -767,55 +767,55 @@
     <t xml:space="preserve">23.606481552124</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7513637542725</t>
+    <t xml:space="preserve">23.7513618469238</t>
   </si>
   <si>
     <t xml:space="preserve">24.1226196289062</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6427040100098</t>
+    <t xml:space="preserve">23.6427021026611</t>
   </si>
   <si>
     <t xml:space="preserve">23.6879768371582</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5612087249756</t>
+    <t xml:space="preserve">23.561206817627</t>
   </si>
   <si>
     <t xml:space="preserve">23.7423057556152</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7241973876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6336460113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8238010406494</t>
+    <t xml:space="preserve">23.7241992950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6336498260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.823802947998</t>
   </si>
   <si>
     <t xml:space="preserve">23.6970329284668</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0139598846436</t>
+    <t xml:space="preserve">24.0139617919922</t>
   </si>
   <si>
     <t xml:space="preserve">24.2856101989746</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0682907104492</t>
+    <t xml:space="preserve">24.068286895752</t>
   </si>
   <si>
     <t xml:space="preserve">23.9777374267578</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2946624755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4304904937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6115913391113</t>
+    <t xml:space="preserve">24.2946643829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4304885864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.61159324646</t>
   </si>
   <si>
     <t xml:space="preserve">24.7655277252197</t>
@@ -824,7 +824,7 @@
     <t xml:space="preserve">25.1911144256592</t>
   </si>
   <si>
-    <t xml:space="preserve">25.390323638916</t>
+    <t xml:space="preserve">25.3903274536133</t>
   </si>
   <si>
     <t xml:space="preserve">25.4265441894531</t>
@@ -833,55 +833,55 @@
     <t xml:space="preserve">25.6167030334473</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6710300445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6529216766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7615814208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5352039337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9556827545166</t>
+    <t xml:space="preserve">25.6710338592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6529235839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7615833282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5352058410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9556789398193</t>
   </si>
   <si>
     <t xml:space="preserve">24.9013538360596</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0643444061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8017463684082</t>
+    <t xml:space="preserve">25.0643463134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8017482757568</t>
   </si>
   <si>
     <t xml:space="preserve">24.6206474304199</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9375743865967</t>
+    <t xml:space="preserve">24.937572479248</t>
   </si>
   <si>
     <t xml:space="preserve">25.3722152709961</t>
   </si>
   <si>
-    <t xml:space="preserve">25.62575340271</t>
+    <t xml:space="preserve">25.6257553100586</t>
   </si>
   <si>
     <t xml:space="preserve">25.2273349761963</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1730041503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.163948059082</t>
+    <t xml:space="preserve">25.173002243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1639499664307</t>
   </si>
   <si>
     <t xml:space="preserve">25.399377822876</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7253608703613</t>
+    <t xml:space="preserve">25.7253589630127</t>
   </si>
   <si>
     <t xml:space="preserve">25.2907199859619</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">25.7434711456299</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5442600250244</t>
+    <t xml:space="preserve">25.5442562103271</t>
   </si>
   <si>
     <t xml:space="preserve">25.4808731079102</t>
@@ -902,19 +902,19 @@
     <t xml:space="preserve">25.5080394744873</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2635536193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0824527740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7836399078369</t>
+    <t xml:space="preserve">25.2635555267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0824546813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7836380004883</t>
   </si>
   <si>
     <t xml:space="preserve">24.4214344024658</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2674999237061</t>
+    <t xml:space="preserve">24.2674980163574</t>
   </si>
   <si>
     <t xml:space="preserve">25.5261497497559</t>
@@ -923,40 +923,40 @@
     <t xml:space="preserve">26.1237812042236</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1871681213379</t>
+    <t xml:space="preserve">26.1871700286865</t>
   </si>
   <si>
     <t xml:space="preserve">26.6308650970459</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4859848022461</t>
+    <t xml:space="preserve">26.4859828948975</t>
   </si>
   <si>
     <t xml:space="preserve">26.3229942321777</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6761360168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8934631347656</t>
+    <t xml:space="preserve">26.676139831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.893461227417</t>
   </si>
   <si>
     <t xml:space="preserve">26.2596092224121</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6670875549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9115676879883</t>
+    <t xml:space="preserve">26.667085647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9115695953369</t>
   </si>
   <si>
     <t xml:space="preserve">26.6036987304688</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5946464538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3088302612305</t>
+    <t xml:space="preserve">26.5946426391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3088283538818</t>
   </si>
   <si>
     <t xml:space="preserve">25.3269386291504</t>
@@ -971,10 +971,10 @@
     <t xml:space="preserve">26.0641059875488</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7112045288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6159954071045</t>
+    <t xml:space="preserve">24.71120262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6159934997559</t>
   </si>
   <si>
     <t xml:space="preserve">23.2202472686768</t>
@@ -983,28 +983,28 @@
     <t xml:space="preserve">23.1282119750977</t>
   </si>
   <si>
-    <t xml:space="preserve">22.962553024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8705177307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8613147735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2662658691406</t>
+    <t xml:space="preserve">22.9625511169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8705196380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8613109588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.266263961792</t>
   </si>
   <si>
     <t xml:space="preserve">23.238655090332</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0453815460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8889255523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0882263183594</t>
+    <t xml:space="preserve">23.0453834533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8889236450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0882244110107</t>
   </si>
   <si>
     <t xml:space="preserve">22.3183116912842</t>
@@ -1016,40 +1016,40 @@
     <t xml:space="preserve">22.3827342987061</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3643283843994</t>
+    <t xml:space="preserve">22.3643264770508</t>
   </si>
   <si>
     <t xml:space="preserve">22.7416687011719</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9533500671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8797187805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2846717834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4871482849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4319248199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8060932159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0269775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6036167144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2538871765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.545223236084</t>
+    <t xml:space="preserve">22.95334815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8797225952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2846698760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4871463775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4319267272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.806095123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0269756317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6036205291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2538890838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5452251434326</t>
   </si>
   <si>
     <t xml:space="preserve">21.4900035858154</t>
@@ -1058,22 +1058,22 @@
     <t xml:space="preserve">21.7200889587402</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5544261932373</t>
+    <t xml:space="preserve">21.5544281005859</t>
   </si>
   <si>
     <t xml:space="preserve">21.674072265625</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6280536651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1678829193115</t>
+    <t xml:space="preserve">21.6280555725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1678810119629</t>
   </si>
   <si>
     <t xml:space="preserve">21.2046985626221</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1218662261963</t>
+    <t xml:space="preserve">21.1218681335449</t>
   </si>
   <si>
     <t xml:space="preserve">21.4163761138916</t>
@@ -1082,10 +1082,10 @@
     <t xml:space="preserve">21.5084114074707</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9133605957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8857517242432</t>
+    <t xml:space="preserve">21.9133586883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8857498168945</t>
   </si>
   <si>
     <t xml:space="preserve">21.9685802459717</t>
@@ -1094,25 +1094,25 @@
     <t xml:space="preserve">22.6220245361328</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3735313415527</t>
+    <t xml:space="preserve">22.3735332489014</t>
   </si>
   <si>
     <t xml:space="preserve">22.2170734405518</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4103469848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5299911499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6312274932861</t>
+    <t xml:space="preserve">22.4103450775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5299892425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6312294006348</t>
   </si>
   <si>
     <t xml:space="preserve">22.6404323577881</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5576000213623</t>
+    <t xml:space="preserve">22.5575981140137</t>
   </si>
   <si>
     <t xml:space="preserve">21.4255809783936</t>
@@ -1121,19 +1121,19 @@
     <t xml:space="preserve">21.6556663513184</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2630920410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5391941070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3551273345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0514106750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7876873016357</t>
+    <t xml:space="preserve">22.263090133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.539192199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3551254272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0514125823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7876853942871</t>
   </si>
   <si>
     <t xml:space="preserve">22.3367195129395</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">22.115837097168</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7661056518555</t>
+    <t xml:space="preserve">21.7661037445068</t>
   </si>
   <si>
     <t xml:space="preserve">22.0606136322021</t>
@@ -1157,40 +1157,40 @@
     <t xml:space="preserve">21.701681137085</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0053939819336</t>
+    <t xml:space="preserve">22.0053958892822</t>
   </si>
   <si>
     <t xml:space="preserve">21.8765468597412</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1250381469727</t>
+    <t xml:space="preserve">22.1250400543213</t>
   </si>
   <si>
     <t xml:space="preserve">21.7753105163574</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0238018035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9041557312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6832714080811</t>
+    <t xml:space="preserve">22.0238037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9041576385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6832752227783</t>
   </si>
   <si>
     <t xml:space="preserve">20.827356338501</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0574378967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.94700050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.799747467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.103458404541</t>
+    <t xml:space="preserve">21.0574398040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9470024108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7997455596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1034603118896</t>
   </si>
   <si>
     <t xml:space="preserve">21.0758495330811</t>
@@ -1199,46 +1199,46 @@
     <t xml:space="preserve">21.3243408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9501762390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0974292755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8581409454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6372566223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2967319488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9746112823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9838161468506</t>
+    <t xml:space="preserve">21.950174331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0974311828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8581371307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6372585296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2967300415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9746150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.983814239502</t>
   </si>
   <si>
     <t xml:space="preserve">21.1402721405029</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0666465759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7077102661133</t>
+    <t xml:space="preserve">21.0666446685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7077121734619</t>
   </si>
   <si>
     <t xml:space="preserve">21.0942554473877</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1586799621582</t>
+    <t xml:space="preserve">21.1586780548096</t>
   </si>
   <si>
     <t xml:space="preserve">21.0206279754639</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0022201538086</t>
+    <t xml:space="preserve">21.0022220611572</t>
   </si>
   <si>
     <t xml:space="preserve">20.6340827941895</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">20.0082511901855</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9714374542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0634727478027</t>
+    <t xml:space="preserve">19.9714393615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0634708404541</t>
   </si>
   <si>
     <t xml:space="preserve">20.4868297576904</t>
@@ -1271,16 +1271,16 @@
     <t xml:space="preserve">20.8917808532715</t>
   </si>
   <si>
-    <t xml:space="preserve">21.241512298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9285926818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2475414276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1647109985352</t>
+    <t xml:space="preserve">21.2415103912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9285945892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2475395202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1647071838379</t>
   </si>
   <si>
     <t xml:space="preserve">20.0910816192627</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">19.2719783782959</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6953353881836</t>
+    <t xml:space="preserve">19.6953315734863</t>
   </si>
   <si>
     <t xml:space="preserve">19.8057765960693</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">19.7321491241455</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1831169128418</t>
+    <t xml:space="preserve">20.1831150054932</t>
   </si>
   <si>
     <t xml:space="preserve">20.0450649261475</t>
@@ -1307,13 +1307,13 @@
     <t xml:space="preserve">20.2935581207275</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4316101074219</t>
+    <t xml:space="preserve">20.4316082000732</t>
   </si>
   <si>
     <t xml:space="preserve">20.5696601867676</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6616954803467</t>
+    <t xml:space="preserve">20.661693572998</t>
   </si>
   <si>
     <t xml:space="preserve">21.1310691833496</t>
@@ -1331,28 +1331,28 @@
     <t xml:space="preserve">20.8089485168457</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6708984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7721347808838</t>
+    <t xml:space="preserve">20.6708965301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7721366882324</t>
   </si>
   <si>
     <t xml:space="preserve">19.4652481079102</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7965717315674</t>
+    <t xml:space="preserve">19.796573638916</t>
   </si>
   <si>
     <t xml:space="preserve">19.8609962463379</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0174522399902</t>
+    <t xml:space="preserve">20.0174541473389</t>
   </si>
   <si>
     <t xml:space="preserve">20.2199287414551</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2291355133057</t>
+    <t xml:space="preserve">20.2291316986084</t>
   </si>
   <si>
     <t xml:space="preserve">20.5236415863037</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">20.6524925231934</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9101886749268</t>
+    <t xml:space="preserve">20.9101867675781</t>
   </si>
   <si>
     <t xml:space="preserve">20.2659473419189</t>
@@ -1370,64 +1370,64 @@
     <t xml:space="preserve">20.4684219360352</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1555061340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1739120483398</t>
+    <t xml:space="preserve">20.1555042266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1739139556885</t>
   </si>
   <si>
     <t xml:space="preserve">21.259916305542</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3703556060791</t>
+    <t xml:space="preserve">21.3703575134277</t>
   </si>
   <si>
     <t xml:space="preserve">21.5176124572754</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8549671173096</t>
+    <t xml:space="preserve">20.8549690246582</t>
   </si>
   <si>
     <t xml:space="preserve">20.9193916320801</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5052356719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3487777709961</t>
+    <t xml:space="preserve">20.5052375793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3487796783447</t>
   </si>
   <si>
     <t xml:space="preserve">20.0266590118408</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7229442596436</t>
+    <t xml:space="preserve">19.7229461669922</t>
   </si>
   <si>
     <t xml:space="preserve">19.9162178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5604553222656</t>
+    <t xml:space="preserve">20.5604572296143</t>
   </si>
   <si>
     <t xml:space="preserve">20.7169151306152</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9377956390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8365573883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6004428863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6248798370361</t>
+    <t xml:space="preserve">20.9377975463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8365592956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6004447937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6248817443848</t>
   </si>
   <si>
     <t xml:space="preserve">20.2751522064209</t>
   </si>
   <si>
-    <t xml:space="preserve">20.109489440918</t>
+    <t xml:space="preserve">20.1094875335693</t>
   </si>
   <si>
     <t xml:space="preserve">19.6493186950684</t>
@@ -1436,22 +1436,22 @@
     <t xml:space="preserve">19.9990482330322</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1278953552246</t>
+    <t xml:space="preserve">20.1278972625732</t>
   </si>
   <si>
     <t xml:space="preserve">20.3303699493408</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8733730316162</t>
+    <t xml:space="preserve">20.8733749389648</t>
   </si>
   <si>
     <t xml:space="preserve">20.3763885498047</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5328483581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3027591705322</t>
+    <t xml:space="preserve">20.532844543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3027610778809</t>
   </si>
   <si>
     <t xml:space="preserve">20.6432876586914</t>
@@ -1463,16 +1463,16 @@
     <t xml:space="preserve">20.7261180877686</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2783241271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3151378631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5360202789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7937164306641</t>
+    <t xml:space="preserve">21.2783260345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3151359558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5360221862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7937145233154</t>
   </si>
   <si>
     <t xml:space="preserve">22.6496353149414</t>
@@ -1481,19 +1481,19 @@
     <t xml:space="preserve">22.548397064209</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4195518493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2078704833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5668048858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6128196716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9165344238281</t>
+    <t xml:space="preserve">22.419548034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2078685760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5668029785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6128215789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9165325164795</t>
   </si>
   <si>
     <t xml:space="preserve">22.6864471435547</t>
@@ -1502,10 +1502,10 @@
     <t xml:space="preserve">22.7324657440186</t>
   </si>
   <si>
-    <t xml:space="preserve">22.833703994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7692775726318</t>
+    <t xml:space="preserve">22.8337001800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7692794799805</t>
   </si>
   <si>
     <t xml:space="preserve">22.9073314666748</t>
@@ -1517,7 +1517,7 @@
     <t xml:space="preserve">22.991304397583</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3090705871582</t>
+    <t xml:space="preserve">23.3090686798096</t>
   </si>
   <si>
     <t xml:space="preserve">23.4118747711182</t>
@@ -1532,16 +1532,16 @@
     <t xml:space="preserve">22.7296123504639</t>
   </si>
   <si>
-    <t xml:space="preserve">22.355770111084</t>
+    <t xml:space="preserve">22.3557720184326</t>
   </si>
   <si>
     <t xml:space="preserve">22.6174621582031</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0754165649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3557987213135</t>
+    <t xml:space="preserve">23.07541847229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3557968139648</t>
   </si>
   <si>
     <t xml:space="preserve">23.1969165802002</t>
@@ -1550,13 +1550,13 @@
     <t xml:space="preserve">23.206262588501</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4586067199707</t>
+    <t xml:space="preserve">23.4586048126221</t>
   </si>
   <si>
     <t xml:space="preserve">22.6548442840576</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7389583587646</t>
+    <t xml:space="preserve">22.7389602661133</t>
   </si>
   <si>
     <t xml:space="preserve">23.1595325469971</t>
@@ -1586,7 +1586,7 @@
     <t xml:space="preserve">19.9912185668945</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7388763427734</t>
+    <t xml:space="preserve">19.7388782501221</t>
   </si>
   <si>
     <t xml:space="preserve">19.5612983703613</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">18.7949237823486</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7762298583984</t>
+    <t xml:space="preserve">18.7762317657471</t>
   </si>
   <si>
     <t xml:space="preserve">18.7201557159424</t>
@@ -1640,16 +1640,16 @@
     <t xml:space="preserve">18.5752925872803</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3930416107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5285606384277</t>
+    <t xml:space="preserve">18.3930435180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5285587310791</t>
   </si>
   <si>
     <t xml:space="preserve">18.495849609375</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4351005554199</t>
+    <t xml:space="preserve">18.4350986480713</t>
   </si>
   <si>
     <t xml:space="preserve">18.388370513916</t>
@@ -1658,10 +1658,10 @@
     <t xml:space="preserve">18.491174697876</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2435073852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8042392730713</t>
+    <t xml:space="preserve">18.2435054779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8042373657227</t>
   </si>
   <si>
     <t xml:space="preserve">17.7715282440186</t>
@@ -1697,7 +1697,7 @@
     <t xml:space="preserve">19.4398002624512</t>
   </si>
   <si>
-    <t xml:space="preserve">19.402416229248</t>
+    <t xml:space="preserve">19.4024181365967</t>
   </si>
   <si>
     <t xml:space="preserve">19.4117641448975</t>
@@ -1706,7 +1706,7 @@
     <t xml:space="preserve">19.4304523468018</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3650321960449</t>
+    <t xml:space="preserve">19.3650302886963</t>
   </si>
   <si>
     <t xml:space="preserve">19.1594181060791</t>
@@ -1721,10 +1721,10 @@
     <t xml:space="preserve">19.0939960479736</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7388458251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0566120147705</t>
+    <t xml:space="preserve">18.7388439178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0566101074219</t>
   </si>
   <si>
     <t xml:space="preserve">18.8416538238525</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">19.4211101531982</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8136405944824</t>
+    <t xml:space="preserve">19.8136425018311</t>
   </si>
   <si>
     <t xml:space="preserve">20.0753307342529</t>
@@ -1763,7 +1763,7 @@
     <t xml:space="preserve">19.5706462860107</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2809181213379</t>
+    <t xml:space="preserve">19.2809162139893</t>
   </si>
   <si>
     <t xml:space="preserve">19.1500720977783</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">18.1780834197998</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6453876495361</t>
+    <t xml:space="preserve">18.6453857421875</t>
   </si>
   <si>
     <t xml:space="preserve">17.8556423187256</t>
@@ -1808,31 +1808,31 @@
     <t xml:space="preserve">18.2154655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1874580383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0098838806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5986843109131</t>
+    <t xml:space="preserve">19.1874561309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0098819732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5986824035645</t>
   </si>
   <si>
     <t xml:space="preserve">19.5893363952637</t>
   </si>
   <si>
-    <t xml:space="preserve">19.645414352417</t>
+    <t xml:space="preserve">19.6454162597656</t>
   </si>
   <si>
     <t xml:space="preserve">19.4771862030029</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5426063537598</t>
+    <t xml:space="preserve">19.5426082611084</t>
   </si>
   <si>
     <t xml:space="preserve">19.5799922943115</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0005645751953</t>
+    <t xml:space="preserve">20.0005626678467</t>
   </si>
   <si>
     <t xml:space="preserve">19.6267204284668</t>
@@ -1844,13 +1844,13 @@
     <t xml:space="preserve">19.701488494873</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3930721282959</t>
+    <t xml:space="preserve">19.3930702209473</t>
   </si>
   <si>
     <t xml:space="preserve">18.7481918334961</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7855796813965</t>
+    <t xml:space="preserve">18.7855777740479</t>
   </si>
   <si>
     <t xml:space="preserve">19.0659580230713</t>
@@ -1859,10 +1859,10 @@
     <t xml:space="preserve">19.5145683288574</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2061462402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0472106933594</t>
+    <t xml:space="preserve">19.206148147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0472087860107</t>
   </si>
   <si>
     <t xml:space="preserve">16.7107524871826</t>
@@ -1871,19 +1871,19 @@
     <t xml:space="preserve">16.8135566711426</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5845794677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5471954345703</t>
+    <t xml:space="preserve">16.5845813751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5471973419189</t>
   </si>
   <si>
     <t xml:space="preserve">16.5378494262695</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7200984954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4957904815674</t>
+    <t xml:space="preserve">16.7200965881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.495792388916</t>
   </si>
   <si>
     <t xml:space="preserve">16.7528095245361</t>
@@ -1895,7 +1895,7 @@
     <t xml:space="preserve">16.4630813598633</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0425090789795</t>
+    <t xml:space="preserve">16.0425109863281</t>
   </si>
   <si>
     <t xml:space="preserve">16.3509292602539</t>
@@ -1907,7 +1907,7 @@
     <t xml:space="preserve">16.8415985107422</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6640224456787</t>
+    <t xml:space="preserve">16.6640205383301</t>
   </si>
   <si>
     <t xml:space="preserve">16.5331764221191</t>
@@ -1928,16 +1928,16 @@
     <t xml:space="preserve">16.1266212463379</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1593341827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4490642547607</t>
+    <t xml:space="preserve">16.1593360900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4490623474121</t>
   </si>
   <si>
     <t xml:space="preserve">16.192045211792</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2154121398926</t>
+    <t xml:space="preserve">16.2154102325439</t>
   </si>
   <si>
     <t xml:space="preserve">16.4817733764648</t>
@@ -1958,7 +1958,7 @@
     <t xml:space="preserve">17.1874008178711</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7855491638184</t>
+    <t xml:space="preserve">17.785551071167</t>
   </si>
   <si>
     <t xml:space="preserve">17.1967449188232</t>
@@ -1967,7 +1967,7 @@
     <t xml:space="preserve">17.2201118469238</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5752601623535</t>
+    <t xml:space="preserve">17.5752620697021</t>
   </si>
   <si>
     <t xml:space="preserve">17.5518970489502</t>
@@ -1976,7 +1976,7 @@
     <t xml:space="preserve">17.4163780212402</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1079616546631</t>
+    <t xml:space="preserve">17.1079597473145</t>
   </si>
   <si>
     <t xml:space="preserve">17.1313228607178</t>
@@ -1997,10 +1997,10 @@
     <t xml:space="preserve">17.729471206665</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6547050476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3369369506836</t>
+    <t xml:space="preserve">17.6547031402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3369388580322</t>
   </si>
   <si>
     <t xml:space="preserve">17.1453418731689</t>
@@ -2018,13 +2018,13 @@
     <t xml:space="preserve">17.9911613464355</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9117183685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0378932952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6593761444092</t>
+    <t xml:space="preserve">17.9117202758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0378913879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6593780517578</t>
   </si>
   <si>
     <t xml:space="preserve">17.7948951721191</t>
@@ -2033,7 +2033,7 @@
     <t xml:space="preserve">17.6360130310059</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3275928497314</t>
+    <t xml:space="preserve">17.3275909423828</t>
   </si>
   <si>
     <t xml:space="preserve">17.3976879119873</t>
@@ -2051,7 +2051,7 @@
     <t xml:space="preserve">18.3136005401611</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0565814971924</t>
+    <t xml:space="preserve">18.056583404541</t>
   </si>
   <si>
     <t xml:space="preserve">18.2855625152588</t>
@@ -2060,7 +2060,7 @@
     <t xml:space="preserve">18.0192012786865</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9677963256836</t>
+    <t xml:space="preserve">17.9677982330322</t>
   </si>
   <si>
     <t xml:space="preserve">17.9070472717285</t>
@@ -2069,7 +2069,7 @@
     <t xml:space="preserve">18.69211769104</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5051918029785</t>
+    <t xml:space="preserve">18.5051937103271</t>
   </si>
   <si>
     <t xml:space="preserve">18.3416385650635</t>
@@ -2084,7 +2084,7 @@
     <t xml:space="preserve">18.5472526550293</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3089294433594</t>
+    <t xml:space="preserve">18.3089275360107</t>
   </si>
   <si>
     <t xml:space="preserve">18.8603458404541</t>
@@ -2099,13 +2099,13 @@
     <t xml:space="preserve">18.0238723754883</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8603191375732</t>
+    <t xml:space="preserve">17.8603172302246</t>
   </si>
   <si>
     <t xml:space="preserve">18.06125831604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5986289978027</t>
+    <t xml:space="preserve">17.5986270904541</t>
   </si>
   <si>
     <t xml:space="preserve">18.0939693450928</t>
@@ -74237,6 +74237,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2606">
+      <c r="A2606" s="1" t="n">
+        <v>46114.2916666667</v>
+      </c>
+      <c r="B2606" t="n">
+        <v>327481</v>
+      </c>
+      <c r="C2606" t="n">
+        <v>7.05499982833862</v>
+      </c>
+      <c r="D2606" t="n">
+        <v>6.78999996185303</v>
+      </c>
+      <c r="E2606" t="n">
+        <v>6.84000015258789</v>
+      </c>
+      <c r="F2606" t="n">
+        <v>7.03000020980835</v>
+      </c>
+      <c r="G2606" t="s">
+        <v>2025</v>
+      </c>
+      <c r="H2606" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2763500213623</t>
+    <t xml:space="preserve">18.2763519287109</t>
   </si>
   <si>
     <t xml:space="preserve">SFER.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">18.01096534729</t>
+    <t xml:space="preserve">18.0109672546387</t>
   </si>
   <si>
     <t xml:space="preserve">17.4978809356689</t>
@@ -53,52 +53,52 @@
     <t xml:space="preserve">17.9401931762695</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6836528778076</t>
+    <t xml:space="preserve">17.683650970459</t>
   </si>
   <si>
     <t xml:space="preserve">18.2498111724854</t>
   </si>
   <si>
-    <t xml:space="preserve">19.408670425415</t>
+    <t xml:space="preserve">19.4086723327637</t>
   </si>
   <si>
     <t xml:space="preserve">19.1344356536865</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8425121307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4621238708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2851963043213</t>
+    <t xml:space="preserve">18.8425102233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.462121963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2851982116699</t>
   </si>
   <si>
     <t xml:space="preserve">18.0994262695312</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6394214630127</t>
+    <t xml:space="preserve">17.6394195556641</t>
   </si>
   <si>
     <t xml:space="preserve">17.5686531066895</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1878871917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4798145294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.223274230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7632656097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3913497924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6744365692139</t>
+    <t xml:space="preserve">18.1878890991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4798164367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2232761383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7632694244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3913516998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6744346618652</t>
   </si>
   <si>
     <t xml:space="preserve">17.9578857421875</t>
@@ -107,31 +107,31 @@
     <t xml:space="preserve">18.2055816650391</t>
   </si>
   <si>
-    <t xml:space="preserve">18.258659362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0817337036133</t>
+    <t xml:space="preserve">18.2586574554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0817356109619</t>
   </si>
   <si>
     <t xml:space="preserve">17.3563423156738</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9051856994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1617240905762</t>
+    <t xml:space="preserve">16.9051837921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1617259979248</t>
   </si>
   <si>
     <t xml:space="preserve">16.6486434936523</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0201835632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4890365600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6305770874023</t>
+    <t xml:space="preserve">17.0201816558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.48903465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6305751800537</t>
   </si>
   <si>
     <t xml:space="preserve">18.4090442657471</t>
@@ -143,31 +143,31 @@
     <t xml:space="preserve">18.9752063751221</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1348094940186</t>
+    <t xml:space="preserve">18.1348114013672</t>
   </si>
   <si>
     <t xml:space="preserve">17.3121109008789</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9048099517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3471202850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0194396972656</t>
+    <t xml:space="preserve">17.9048080444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3471221923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.019437789917</t>
   </si>
   <si>
     <t xml:space="preserve">19.0017433166504</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8513565063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3113613128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.992525100708</t>
+    <t xml:space="preserve">18.8513584136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3113632202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9925231933594</t>
   </si>
   <si>
     <t xml:space="preserve">19.9482936859131</t>
@@ -185,7 +185,7 @@
     <t xml:space="preserve">19.9836769104004</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1167469024658</t>
+    <t xml:space="preserve">19.1167430877686</t>
   </si>
   <si>
     <t xml:space="preserve">19.4440574645996</t>
@@ -194,43 +194,43 @@
     <t xml:space="preserve">20.0367546081543</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1782932281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4971332550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4705924987793</t>
+    <t xml:space="preserve">20.178295135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4971351623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4705944061279</t>
   </si>
   <si>
     <t xml:space="preserve">18.9663581848145</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4794425964355</t>
+    <t xml:space="preserve">19.4794406890869</t>
   </si>
   <si>
     <t xml:space="preserve">19.9129066467285</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8686771392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.417516708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8690509796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8336658477783</t>
+    <t xml:space="preserve">19.868673324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4175186157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8690490722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.833667755127</t>
   </si>
   <si>
     <t xml:space="preserve">18.5151996612549</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9309749603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8955898284912</t>
+    <t xml:space="preserve">18.9309730529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8955917358398</t>
   </si>
   <si>
     <t xml:space="preserve">18.5240478515625</t>
@@ -242,10 +242,10 @@
     <t xml:space="preserve">18.7982807159424</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8778972625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2936706542969</t>
+    <t xml:space="preserve">18.8778953552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2936725616455</t>
   </si>
   <si>
     <t xml:space="preserve">18.8071269989014</t>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">18.3648128509521</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8251914978027</t>
+    <t xml:space="preserve">17.8251934051514</t>
   </si>
   <si>
     <t xml:space="preserve">18.0640411376953</t>
@@ -266,34 +266,34 @@
     <t xml:space="preserve">18.3117370605469</t>
   </si>
   <si>
-    <t xml:space="preserve">17.878267288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0021152496338</t>
+    <t xml:space="preserve">17.8782691955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0021190643311</t>
   </si>
   <si>
     <t xml:space="preserve">17.7190380096436</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4448051452637</t>
+    <t xml:space="preserve">17.4448013305664</t>
   </si>
   <si>
     <t xml:space="preserve">17.1440296173096</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5509586334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9844245910645</t>
+    <t xml:space="preserve">17.5509567260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9844226837158</t>
   </si>
   <si>
     <t xml:space="preserve">17.4182662963867</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9313468933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7367305755615</t>
+    <t xml:space="preserve">17.9313488006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7367324829102</t>
   </si>
   <si>
     <t xml:space="preserve">17.6482696533203</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">17.593936920166</t>
   </si>
   <si>
-    <t xml:space="preserve">17.81125831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7025985717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6482639312744</t>
+    <t xml:space="preserve">17.8112602233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7025966644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6482677459717</t>
   </si>
   <si>
     <t xml:space="preserve">17.530553817749</t>
@@ -317,25 +317,25 @@
     <t xml:space="preserve">17.4128379821777</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3041801452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4762229919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4309482574463</t>
+    <t xml:space="preserve">17.3041763305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4762210845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.430944442749</t>
   </si>
   <si>
     <t xml:space="preserve">17.4852771759033</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7478733062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6844882965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1502418518066</t>
+    <t xml:space="preserve">17.747875213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6844902038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.150239944458</t>
   </si>
   <si>
     <t xml:space="preserve">16.7155990600586</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">17.0415821075439</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0778007507324</t>
+    <t xml:space="preserve">17.0777988433838</t>
   </si>
   <si>
     <t xml:space="preserve">17.8384246826172</t>
@@ -359,10 +359,10 @@
     <t xml:space="preserve">17.7297630310059</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8655853271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1825122833252</t>
+    <t xml:space="preserve">17.8655891418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1825160980225</t>
   </si>
   <si>
     <t xml:space="preserve">16.8514251708984</t>
@@ -371,25 +371,25 @@
     <t xml:space="preserve">16.3896179199219</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6793785095215</t>
+    <t xml:space="preserve">16.6793766021729</t>
   </si>
   <si>
     <t xml:space="preserve">16.262845993042</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5254459381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6069374084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8061485290527</t>
+    <t xml:space="preserve">16.5254421234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6069393157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8061504364014</t>
   </si>
   <si>
     <t xml:space="preserve">16.8242588043213</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0726909637451</t>
+    <t xml:space="preserve">16.0726928710938</t>
   </si>
   <si>
     <t xml:space="preserve">15.8734798431396</t>
@@ -401,13 +401,13 @@
     <t xml:space="preserve">16.4439468383789</t>
   </si>
   <si>
-    <t xml:space="preserve">16.69748878479</t>
+    <t xml:space="preserve">16.6974906921387</t>
   </si>
   <si>
     <t xml:space="preserve">17.0959091186523</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1321296691895</t>
+    <t xml:space="preserve">17.1321315765381</t>
   </si>
   <si>
     <t xml:space="preserve">17.086856842041</t>
@@ -422,19 +422,19 @@
     <t xml:space="preserve">17.9018096923828</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1372394561768</t>
+    <t xml:space="preserve">18.1372413635254</t>
   </si>
   <si>
     <t xml:space="preserve">17.9289722442627</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7710914611816</t>
+    <t xml:space="preserve">18.7710933685303</t>
   </si>
   <si>
     <t xml:space="preserve">18.6352672576904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0699081420898</t>
+    <t xml:space="preserve">19.0699100494385</t>
   </si>
   <si>
     <t xml:space="preserve">19.2147884368896</t>
@@ -449,61 +449,61 @@
     <t xml:space="preserve">18.2187366485596</t>
   </si>
   <si>
-    <t xml:space="preserve">18.716760635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5809364318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.762035369873</t>
+    <t xml:space="preserve">18.7167625427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5809383392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7620372772217</t>
   </si>
   <si>
     <t xml:space="preserve">18.8073139190674</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9431400299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0427417755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6624336242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4722766876221</t>
+    <t xml:space="preserve">18.94313621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.04274559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6624317169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4722728729248</t>
   </si>
   <si>
     <t xml:space="preserve">18.6171550750732</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7529811859131</t>
+    <t xml:space="preserve">18.7529792785645</t>
   </si>
   <si>
     <t xml:space="preserve">18.9703025817871</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6805400848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6080989837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.653377532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5175533294678</t>
+    <t xml:space="preserve">18.6805419921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6081008911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6533794403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5175514221191</t>
   </si>
   <si>
     <t xml:space="preserve">18.870698928833</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6986522674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.106128692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9210834503174</t>
+    <t xml:space="preserve">18.6986541748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1061267852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9210815429688</t>
   </si>
   <si>
     <t xml:space="preserve">19.6947059631348</t>
@@ -521,49 +521,49 @@
     <t xml:space="preserve">18.8888092041016</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1332912445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1604614257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9391937255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4553298950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3557224273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3104496002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3919448852539</t>
+    <t xml:space="preserve">19.1332931518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1604595184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9391918182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4553279876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3557262420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3104515075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3919429779053</t>
   </si>
   <si>
     <t xml:space="preserve">20.4643859863281</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6907615661621</t>
+    <t xml:space="preserve">20.6907577514648</t>
   </si>
   <si>
     <t xml:space="preserve">20.8446960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7994194030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4009971618652</t>
+    <t xml:space="preserve">20.7994213104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4010009765625</t>
   </si>
   <si>
     <t xml:space="preserve">20.1021823883057</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5277690887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3647804260254</t>
+    <t xml:space="preserve">20.5277709960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3647785186768</t>
   </si>
   <si>
     <t xml:space="preserve">20.5458793640137</t>
@@ -572,10 +572,10 @@
     <t xml:space="preserve">20.7541446685791</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4191112518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0116329193115</t>
+    <t xml:space="preserve">20.4191093444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0116348266602</t>
   </si>
   <si>
     <t xml:space="preserve">20.2651710510254</t>
@@ -584,10 +584,10 @@
     <t xml:space="preserve">20.3285579681396</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0387935638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1474609375</t>
+    <t xml:space="preserve">20.0387954711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1474590301514</t>
   </si>
   <si>
     <t xml:space="preserve">20.2289543151855</t>
@@ -596,13 +596,13 @@
     <t xml:space="preserve">20.500602722168</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5639877319336</t>
+    <t xml:space="preserve">20.5639896392822</t>
   </si>
   <si>
     <t xml:space="preserve">20.1836776733398</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5498275756836</t>
+    <t xml:space="preserve">19.549825668335</t>
   </si>
   <si>
     <t xml:space="preserve">19.4139995574951</t>
@@ -611,13 +611,13 @@
     <t xml:space="preserve">19.5045509338379</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7218704223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7943134307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5226593017578</t>
+    <t xml:space="preserve">19.7218723297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7943115234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5226573944092</t>
   </si>
   <si>
     <t xml:space="preserve">19.830530166626</t>
@@ -626,22 +626,22 @@
     <t xml:space="preserve">19.9120254516602</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7490367889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0919628143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3002281188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3273963928223</t>
+    <t xml:space="preserve">19.7490386962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0919666290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3002300262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3273944854736</t>
   </si>
   <si>
     <t xml:space="preserve">18.2458992004395</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0104675292969</t>
+    <t xml:space="preserve">18.0104694366455</t>
   </si>
   <si>
     <t xml:space="preserve">17.7388191223145</t>
@@ -665,25 +665,25 @@
     <t xml:space="preserve">19.151403427124</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2872295379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3958892822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3777809143066</t>
+    <t xml:space="preserve">19.2872276306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3958930969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.377779006958</t>
   </si>
   <si>
     <t xml:space="preserve">19.1151866912842</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5860424041748</t>
+    <t xml:space="preserve">19.5860443115234</t>
   </si>
   <si>
     <t xml:space="preserve">19.2600650787354</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3738327026367</t>
+    <t xml:space="preserve">20.3738346099854</t>
   </si>
   <si>
     <t xml:space="preserve">20.3466663360596</t>
@@ -692,25 +692,25 @@
     <t xml:space="preserve">20.2380084991455</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1293449401855</t>
+    <t xml:space="preserve">20.1293468475342</t>
   </si>
   <si>
     <t xml:space="preserve">20.1565113067627</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8084754943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6183185577393</t>
+    <t xml:space="preserve">20.8084735870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6183204650879</t>
   </si>
   <si>
     <t xml:space="preserve">21.4785480499268</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5328807830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0671272277832</t>
+    <t xml:space="preserve">21.5328788757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0671253204346</t>
   </si>
   <si>
     <t xml:space="preserve">22.0580711364746</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">22.2572822570801</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2934989929199</t>
+    <t xml:space="preserve">22.2935028076172</t>
   </si>
   <si>
     <t xml:space="preserve">22.3025550842285</t>
@@ -731,10 +731,10 @@
     <t xml:space="preserve">22.2753925323486</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2391700744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8186931610107</t>
+    <t xml:space="preserve">22.2391719818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.818696975708</t>
   </si>
   <si>
     <t xml:space="preserve">23.0722351074219</t>
@@ -746,13 +746,13 @@
     <t xml:space="preserve">23.1537303924561</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0993995666504</t>
+    <t xml:space="preserve">23.0993976593018</t>
   </si>
   <si>
     <t xml:space="preserve">22.5923175811768</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3568859100342</t>
+    <t xml:space="preserve">22.3568878173828</t>
   </si>
   <si>
     <t xml:space="preserve">22.9092426300049</t>
@@ -764,13 +764,13 @@
     <t xml:space="preserve">22.1395645141602</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6064834594727</t>
+    <t xml:space="preserve">23.606481552124</t>
   </si>
   <si>
     <t xml:space="preserve">23.7513618469238</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1226177215576</t>
+    <t xml:space="preserve">24.1226196289062</t>
   </si>
   <si>
     <t xml:space="preserve">23.6427021026611</t>
@@ -785,73 +785,73 @@
     <t xml:space="preserve">23.7423076629639</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7241954803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6336479187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8238010406494</t>
+    <t xml:space="preserve">23.7241973876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6336498260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8238048553467</t>
   </si>
   <si>
     <t xml:space="preserve">23.6970329284668</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0139617919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2856121063232</t>
+    <t xml:space="preserve">24.0139579772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2856101989746</t>
   </si>
   <si>
     <t xml:space="preserve">24.0682888031006</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9777393341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2946643829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.430492401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6115913391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7655258178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1911144256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3903255462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4265441894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.61669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.671028137207</t>
+    <t xml:space="preserve">23.9777374267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2946662902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4304904937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.61159324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7655277252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1911125183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3903274536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4265460968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6167030334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6710300445557</t>
   </si>
   <si>
     <t xml:space="preserve">25.6529216766357</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7615814208984</t>
+    <t xml:space="preserve">25.7615833282471</t>
   </si>
   <si>
     <t xml:space="preserve">25.5352039337158</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9556827545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9013538360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0643463134766</t>
+    <t xml:space="preserve">24.955680847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9013519287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0643444061279</t>
   </si>
   <si>
     <t xml:space="preserve">24.8017482757568</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">24.6206455230713</t>
   </si>
   <si>
-    <t xml:space="preserve">24.937572479248</t>
+    <t xml:space="preserve">24.9375762939453</t>
   </si>
   <si>
     <t xml:space="preserve">25.3722152709961</t>
@@ -869,10 +869,10 @@
     <t xml:space="preserve">25.6257553100586</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2273330688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.173002243042</t>
+    <t xml:space="preserve">25.2273349761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1730041503906</t>
   </si>
   <si>
     <t xml:space="preserve">25.163948059082</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">25.399377822876</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7253608703613</t>
+    <t xml:space="preserve">25.7253589630127</t>
   </si>
   <si>
     <t xml:space="preserve">25.2907199859619</t>
@@ -890,43 +890,43 @@
     <t xml:space="preserve">25.1277275085449</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7434730529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5442600250244</t>
+    <t xml:space="preserve">25.7434711456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.544261932373</t>
   </si>
   <si>
     <t xml:space="preserve">25.4808750152588</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5080394744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2635536193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0824508666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7836399078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4214363098145</t>
+    <t xml:space="preserve">25.5080413818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.263557434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0824546813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7836380004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4214324951172</t>
   </si>
   <si>
     <t xml:space="preserve">24.2674980163574</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5261516571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1237812042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1871662139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6308650970459</t>
+    <t xml:space="preserve">25.5261497497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1237850189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1871681213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6308631896973</t>
   </si>
   <si>
     <t xml:space="preserve">26.4859848022461</t>
@@ -941,22 +941,22 @@
     <t xml:space="preserve">26.893461227417</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2596073150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6670837402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9115695953369</t>
+    <t xml:space="preserve">26.2596054077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.667085647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9115676879883</t>
   </si>
   <si>
     <t xml:space="preserve">26.6036968231201</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5946464538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3088283538818</t>
+    <t xml:space="preserve">26.5946483612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3088321685791</t>
   </si>
   <si>
     <t xml:space="preserve">25.3269386291504</t>
@@ -968,13 +968,13 @@
     <t xml:space="preserve">25.8984451293945</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0641059875488</t>
+    <t xml:space="preserve">26.0641040802002</t>
   </si>
   <si>
     <t xml:space="preserve">24.71120262146</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6159954071045</t>
+    <t xml:space="preserve">23.6159934997559</t>
   </si>
   <si>
     <t xml:space="preserve">23.2202472686768</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">22.8705177307129</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8613147735596</t>
+    <t xml:space="preserve">22.8613128662109</t>
   </si>
   <si>
     <t xml:space="preserve">23.2662658691406</t>
@@ -1001,7 +1001,7 @@
     <t xml:space="preserve">23.0453815460205</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8889255523682</t>
+    <t xml:space="preserve">22.8889236450195</t>
   </si>
   <si>
     <t xml:space="preserve">22.0882263183594</t>
@@ -1016,7 +1016,7 @@
     <t xml:space="preserve">22.3827342987061</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3643283843994</t>
+    <t xml:space="preserve">22.3643264770508</t>
   </si>
   <si>
     <t xml:space="preserve">22.7416687011719</t>
@@ -1025,34 +1025,34 @@
     <t xml:space="preserve">22.9533500671387</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8797206878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2846698760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4871482849121</t>
+    <t xml:space="preserve">22.8797225952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.28466796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4871463775635</t>
   </si>
   <si>
     <t xml:space="preserve">23.4319267272949</t>
   </si>
   <si>
-    <t xml:space="preserve">22.806095123291</t>
+    <t xml:space="preserve">22.8060932159424</t>
   </si>
   <si>
     <t xml:space="preserve">23.0269775390625</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6036167144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2538890838623</t>
+    <t xml:space="preserve">22.6036186218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2538871765137</t>
   </si>
   <si>
     <t xml:space="preserve">21.545223236084</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4900016784668</t>
+    <t xml:space="preserve">21.4900035858154</t>
   </si>
   <si>
     <t xml:space="preserve">21.7200889587402</t>
@@ -1079,34 +1079,34 @@
     <t xml:space="preserve">21.4163761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5084114074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9133586883545</t>
+    <t xml:space="preserve">21.5084095001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9133605957031</t>
   </si>
   <si>
     <t xml:space="preserve">21.8857517242432</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9685802459717</t>
+    <t xml:space="preserve">21.9685821533203</t>
   </si>
   <si>
     <t xml:space="preserve">22.6220245361328</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3735313415527</t>
+    <t xml:space="preserve">22.3735332489014</t>
   </si>
   <si>
     <t xml:space="preserve">22.2170734405518</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4103450775146</t>
+    <t xml:space="preserve">22.410343170166</t>
   </si>
   <si>
     <t xml:space="preserve">22.5299911499023</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6312294006348</t>
+    <t xml:space="preserve">22.6312274932861</t>
   </si>
   <si>
     <t xml:space="preserve">22.6404323577881</t>
@@ -1115,7 +1115,7 @@
     <t xml:space="preserve">22.5576000213623</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4255809783936</t>
+    <t xml:space="preserve">21.4255790710449</t>
   </si>
   <si>
     <t xml:space="preserve">21.6556663513184</t>
@@ -1136,7 +1136,7 @@
     <t xml:space="preserve">22.7876853942871</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3367195129395</t>
+    <t xml:space="preserve">22.3367176055908</t>
   </si>
   <si>
     <t xml:space="preserve">22.115837097168</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">22.0606136322021</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7569007873535</t>
+    <t xml:space="preserve">21.7569026947021</t>
   </si>
   <si>
     <t xml:space="preserve">21.9961910247803</t>
@@ -1160,13 +1160,13 @@
     <t xml:space="preserve">22.0053958892822</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8765487670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1250381469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7753105163574</t>
+    <t xml:space="preserve">21.8765468597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1250400543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7753086090088</t>
   </si>
   <si>
     <t xml:space="preserve">22.0238037109375</t>
@@ -1175,13 +1175,13 @@
     <t xml:space="preserve">21.9041557312012</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6832714080811</t>
+    <t xml:space="preserve">21.6832733154297</t>
   </si>
   <si>
     <t xml:space="preserve">20.827356338501</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0574378967285</t>
+    <t xml:space="preserve">21.0574417114258</t>
   </si>
   <si>
     <t xml:space="preserve">20.94700050354</t>
@@ -1190,31 +1190,31 @@
     <t xml:space="preserve">20.799747467041</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1034603118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0758495330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3243408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9501762390137</t>
+    <t xml:space="preserve">21.103458404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0758476257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3243427276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.950174331665</t>
   </si>
   <si>
     <t xml:space="preserve">22.0974292755127</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8581390380859</t>
+    <t xml:space="preserve">21.8581371307373</t>
   </si>
   <si>
     <t xml:space="preserve">21.6372566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2967319488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9746112823486</t>
+    <t xml:space="preserve">21.2967300415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9746131896973</t>
   </si>
   <si>
     <t xml:space="preserve">20.983814239502</t>
@@ -1223,7 +1223,7 @@
     <t xml:space="preserve">21.1402721405029</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0666465759277</t>
+    <t xml:space="preserve">21.0666446685791</t>
   </si>
   <si>
     <t xml:space="preserve">20.7077102661133</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">20.385591506958</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3947944641113</t>
+    <t xml:space="preserve">20.3947925567627</t>
   </si>
   <si>
     <t xml:space="preserve">20.0082511901855</t>
@@ -1265,7 +1265,7 @@
     <t xml:space="preserve">20.4868278503418</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7445240020752</t>
+    <t xml:space="preserve">20.7445259094238</t>
   </si>
   <si>
     <t xml:space="preserve">20.8917808532715</t>
@@ -1274,13 +1274,13 @@
     <t xml:space="preserve">21.2415103912354</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9285926818848</t>
+    <t xml:space="preserve">20.9285945892334</t>
   </si>
   <si>
     <t xml:space="preserve">20.2475414276123</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1647109985352</t>
+    <t xml:space="preserve">20.1647090911865</t>
   </si>
   <si>
     <t xml:space="preserve">20.0910816192627</t>
@@ -1289,10 +1289,10 @@
     <t xml:space="preserve">19.2719783782959</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6953353881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8057765960693</t>
+    <t xml:space="preserve">19.695333480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8057746887207</t>
   </si>
   <si>
     <t xml:space="preserve">19.7321472167969</t>
@@ -1328,22 +1328,22 @@
     <t xml:space="preserve">21.4531898498535</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8089504241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6708984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7721347808838</t>
+    <t xml:space="preserve">20.8089485168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6708965301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7721366882324</t>
   </si>
   <si>
     <t xml:space="preserve">19.4652481079102</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7965717315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8609943389893</t>
+    <t xml:space="preserve">19.796573638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8609962463379</t>
   </si>
   <si>
     <t xml:space="preserve">20.0174541473389</t>
@@ -1364,10 +1364,10 @@
     <t xml:space="preserve">20.9101867675781</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2659492492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4684219360352</t>
+    <t xml:space="preserve">20.2659473419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4684238433838</t>
   </si>
   <si>
     <t xml:space="preserve">20.1555042266846</t>
@@ -1376,19 +1376,19 @@
     <t xml:space="preserve">20.1739120483398</t>
   </si>
   <si>
-    <t xml:space="preserve">21.259916305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3703556060791</t>
+    <t xml:space="preserve">21.2599182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3703575134277</t>
   </si>
   <si>
     <t xml:space="preserve">21.5176124572754</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8549690246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9193916320801</t>
+    <t xml:space="preserve">20.8549671173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9193897247314</t>
   </si>
   <si>
     <t xml:space="preserve">20.5052375793457</t>
@@ -1418,10 +1418,10 @@
     <t xml:space="preserve">20.8365573883057</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6004428863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6248817443848</t>
+    <t xml:space="preserve">21.6004447937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6248836517334</t>
   </si>
   <si>
     <t xml:space="preserve">20.2751522064209</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">19.6493186950684</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9990482330322</t>
+    <t xml:space="preserve">19.9990463256836</t>
   </si>
   <si>
     <t xml:space="preserve">20.1278972625732</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">20.3303699493408</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8733749389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3763904571533</t>
+    <t xml:space="preserve">20.8733730316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3763885498047</t>
   </si>
   <si>
     <t xml:space="preserve">20.5328464508057</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3027591705322</t>
+    <t xml:space="preserve">20.3027610778809</t>
   </si>
   <si>
     <t xml:space="preserve">20.64328956604</t>
@@ -1460,22 +1460,22 @@
     <t xml:space="preserve">20.6156749725342</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7261199951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2783241271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3151378631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.536018371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7937164306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6496353149414</t>
+    <t xml:space="preserve">20.7261180877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2783260345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3151359558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5360202789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7937145233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6496334075928</t>
   </si>
   <si>
     <t xml:space="preserve">22.5483989715576</t>
@@ -1487,13 +1487,13 @@
     <t xml:space="preserve">22.2078685760498</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5668048858643</t>
+    <t xml:space="preserve">22.5668029785156</t>
   </si>
   <si>
     <t xml:space="preserve">22.6128196716309</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9165325164795</t>
+    <t xml:space="preserve">22.9165344238281</t>
   </si>
   <si>
     <t xml:space="preserve">22.6864471435547</t>
@@ -74265,7 +74265,7 @@
     </row>
     <row r="2607">
       <c r="A2607" s="1" t="n">
-        <v>46119.6516666667</v>
+        <v>46119.2916666667</v>
       </c>
       <c r="B2607" t="n">
         <v>1176079</v>
@@ -74286,6 +74286,32 @@
         <v>1835</v>
       </c>
       <c r="H2607" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2608">
+      <c r="A2608" s="1" t="n">
+        <v>46120.2916666667</v>
+      </c>
+      <c r="B2608" t="n">
+        <v>683281</v>
+      </c>
+      <c r="C2608" t="n">
+        <v>7.76000022888184</v>
+      </c>
+      <c r="D2608" t="n">
+        <v>7.55999994277954</v>
+      </c>
+      <c r="E2608" t="n">
+        <v>7.76000022888184</v>
+      </c>
+      <c r="F2608" t="n">
+        <v>7.63000011444092</v>
+      </c>
+      <c r="G2608" t="s">
+        <v>1735</v>
+      </c>
+      <c r="H2608" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2058" uniqueCount="2058">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2059" uniqueCount="2059">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2763538360596</t>
+    <t xml:space="preserve">18.2763519287109</t>
   </si>
   <si>
     <t xml:space="preserve">SFER.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0109634399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4978809356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9401950836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6836490631104</t>
+    <t xml:space="preserve">18.0109615325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4978847503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9401931762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6836528778076</t>
   </si>
   <si>
     <t xml:space="preserve">18.2498111724854</t>
@@ -74,13 +74,13 @@
     <t xml:space="preserve">18.2851963043213</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0994262695312</t>
+    <t xml:space="preserve">18.0994243621826</t>
   </si>
   <si>
     <t xml:space="preserve">17.6394214630127</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5686492919922</t>
+    <t xml:space="preserve">17.5686531066895</t>
   </si>
   <si>
     <t xml:space="preserve">18.1878871917725</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">18.4798145294189</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2232761383057</t>
+    <t xml:space="preserve">18.223274230957</t>
   </si>
   <si>
     <t xml:space="preserve">17.7632694244385</t>
@@ -98,7 +98,7 @@
     <t xml:space="preserve">18.3913536071777</t>
   </si>
   <si>
-    <t xml:space="preserve">18.674430847168</t>
+    <t xml:space="preserve">18.6744346618652</t>
   </si>
   <si>
     <t xml:space="preserve">17.9578857421875</t>
@@ -107,31 +107,31 @@
     <t xml:space="preserve">18.2055816650391</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2586612701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0817356109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3563404083252</t>
+    <t xml:space="preserve">18.258659362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0817337036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3563442230225</t>
   </si>
   <si>
     <t xml:space="preserve">16.9051818847656</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1617240905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6486396789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0201854705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4890365600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6305751800537</t>
+    <t xml:space="preserve">17.1617221832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6486415863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0201835632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4890384674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6305732727051</t>
   </si>
   <si>
     <t xml:space="preserve">18.4090442657471</t>
@@ -140,64 +140,64 @@
     <t xml:space="preserve">18.453275680542</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9752063751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1348133087158</t>
+    <t xml:space="preserve">18.9752082824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1348114013672</t>
   </si>
   <si>
     <t xml:space="preserve">17.3121070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9048099517822</t>
+    <t xml:space="preserve">17.9048080444336</t>
   </si>
   <si>
     <t xml:space="preserve">18.3471202850342</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0194358825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0017433166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8513565063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3113613128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9925231933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9482917785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7271366119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3379001617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6475200653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9836750030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1167430877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4440574645996</t>
+    <t xml:space="preserve">19.019437789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.001745223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8513584136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3113632202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9925270080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9482936859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7271347045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3379020690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6475219726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9836769104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1167449951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.444055557251</t>
   </si>
   <si>
     <t xml:space="preserve">20.0367546081543</t>
   </si>
   <si>
-    <t xml:space="preserve">20.178295135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4971332550049</t>
+    <t xml:space="preserve">20.1782932281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4971351623535</t>
   </si>
   <si>
     <t xml:space="preserve">19.4705944061279</t>
@@ -209,58 +209,58 @@
     <t xml:space="preserve">19.4794425964355</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9129085540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8686771392822</t>
+    <t xml:space="preserve">19.9129047393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8686752319336</t>
   </si>
   <si>
     <t xml:space="preserve">19.4175186157227</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8690509796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8336658477783</t>
+    <t xml:space="preserve">18.8690528869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.833667755127</t>
   </si>
   <si>
     <t xml:space="preserve">18.5151996612549</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9309711456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8955879211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5240459442139</t>
+    <t xml:space="preserve">18.9309749603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8955860137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5240478515625</t>
   </si>
   <si>
     <t xml:space="preserve">18.9486656188965</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7982807159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8778972625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2936687469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8071250915527</t>
+    <t xml:space="preserve">18.798282623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8778953552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2936706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8071269989014</t>
   </si>
   <si>
     <t xml:space="preserve">18.3205814361572</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3648147583008</t>
+    <t xml:space="preserve">18.3648166656494</t>
   </si>
   <si>
     <t xml:space="preserve">17.8251914978027</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0640411376953</t>
+    <t xml:space="preserve">18.0640430450439</t>
   </si>
   <si>
     <t xml:space="preserve">18.3117370605469</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">18.0021190643311</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7190380096436</t>
+    <t xml:space="preserve">17.7190361022949</t>
   </si>
   <si>
     <t xml:space="preserve">17.444803237915</t>
@@ -281,40 +281,40 @@
     <t xml:space="preserve">17.1440315246582</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5509567260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9844264984131</t>
+    <t xml:space="preserve">17.5509586334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9844284057617</t>
   </si>
   <si>
     <t xml:space="preserve">17.4182643890381</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9313507080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7367286682129</t>
+    <t xml:space="preserve">17.9313488006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7367267608643</t>
   </si>
   <si>
     <t xml:space="preserve">17.6482677459717</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5939388275146</t>
+    <t xml:space="preserve">17.593936920166</t>
   </si>
   <si>
     <t xml:space="preserve">17.81125831604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7025966644287</t>
+    <t xml:space="preserve">17.7025985717773</t>
   </si>
   <si>
     <t xml:space="preserve">17.530553817749</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4128379821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3041763305664</t>
+    <t xml:space="preserve">17.4128360748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.304178237915</t>
   </si>
   <si>
     <t xml:space="preserve">17.4762210845947</t>
@@ -329,13 +329,13 @@
     <t xml:space="preserve">17.7478733062744</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6844882965088</t>
+    <t xml:space="preserve">17.6844863891602</t>
   </si>
   <si>
     <t xml:space="preserve">17.1502418518066</t>
   </si>
   <si>
-    <t xml:space="preserve">16.71559715271</t>
+    <t xml:space="preserve">16.7155990600586</t>
   </si>
   <si>
     <t xml:space="preserve">16.5435523986816</t>
@@ -350,16 +350,16 @@
     <t xml:space="preserve">17.8384246826172</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9380283355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7297630310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8655910491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1825160980225</t>
+    <t xml:space="preserve">17.9380264282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7297611236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8655872344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1825141906738</t>
   </si>
   <si>
     <t xml:space="preserve">16.8514232635498</t>
@@ -368,13 +368,13 @@
     <t xml:space="preserve">16.3896179199219</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6793785095215</t>
+    <t xml:space="preserve">16.6793804168701</t>
   </si>
   <si>
     <t xml:space="preserve">16.2628440856934</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5254421234131</t>
+    <t xml:space="preserve">16.5254440307617</t>
   </si>
   <si>
     <t xml:space="preserve">16.6069374084473</t>
@@ -389,16 +389,16 @@
     <t xml:space="preserve">16.0726890563965</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8734798431396</t>
+    <t xml:space="preserve">15.8734817504883</t>
   </si>
   <si>
     <t xml:space="preserve">16.3624496459961</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4439487457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6974906921387</t>
+    <t xml:space="preserve">16.4439468383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.69748878479</t>
   </si>
   <si>
     <t xml:space="preserve">17.0959091186523</t>
@@ -410,13 +410,13 @@
     <t xml:space="preserve">17.086856842041</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0325260162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3403987884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9018096923828</t>
+    <t xml:space="preserve">17.0325241088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3403968811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9018077850342</t>
   </si>
   <si>
     <t xml:space="preserve">18.1372413635254</t>
@@ -425,16 +425,16 @@
     <t xml:space="preserve">17.9289722442627</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7710933685303</t>
+    <t xml:space="preserve">18.7710914611816</t>
   </si>
   <si>
     <t xml:space="preserve">18.6352653503418</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0699062347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2147884368896</t>
+    <t xml:space="preserve">19.0699081420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2147903442383</t>
   </si>
   <si>
     <t xml:space="preserve">18.6262111663818</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">18.7167625427246</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5809383392334</t>
+    <t xml:space="preserve">18.5809364318848</t>
   </si>
   <si>
     <t xml:space="preserve">18.7620372772217</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">18.9431381225586</t>
   </si>
   <si>
-    <t xml:space="preserve">19.04274559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6624298095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4722766876221</t>
+    <t xml:space="preserve">19.0427436828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6624317169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4722785949707</t>
   </si>
   <si>
     <t xml:space="preserve">18.6171550750732</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">18.6080989837646</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6533756256104</t>
+    <t xml:space="preserve">18.653377532959</t>
   </si>
   <si>
     <t xml:space="preserve">18.5175533294678</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">18.6986541748047</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1061267852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9210834503174</t>
+    <t xml:space="preserve">19.106128692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9210815429688</t>
   </si>
   <si>
     <t xml:space="preserve">19.6947059631348</t>
@@ -509,10 +509,10 @@
     <t xml:space="preserve">19.5588798522949</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4592761993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3143939971924</t>
+    <t xml:space="preserve">19.4592742919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.314395904541</t>
   </si>
   <si>
     <t xml:space="preserve">18.8888072967529</t>
@@ -542,28 +542,28 @@
     <t xml:space="preserve">20.4643840789795</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6907596588135</t>
+    <t xml:space="preserve">20.6907577514648</t>
   </si>
   <si>
     <t xml:space="preserve">20.8446960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7994194030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4009990692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1021862030029</t>
+    <t xml:space="preserve">20.7994213104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4009971618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1021823883057</t>
   </si>
   <si>
     <t xml:space="preserve">20.5277709960938</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3647804260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5458793640137</t>
+    <t xml:space="preserve">20.3647785186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5458812713623</t>
   </si>
   <si>
     <t xml:space="preserve">20.7541484832764</t>
@@ -578,16 +578,16 @@
     <t xml:space="preserve">20.265172958374</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3285617828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.03879737854</t>
+    <t xml:space="preserve">20.3285598754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0387954711914</t>
   </si>
   <si>
     <t xml:space="preserve">20.1474590301514</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2289543151855</t>
+    <t xml:space="preserve">20.2289524078369</t>
   </si>
   <si>
     <t xml:space="preserve">20.5006046295166</t>
@@ -596,19 +596,19 @@
     <t xml:space="preserve">20.5639896392822</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1836795806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.549825668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4140014648438</t>
+    <t xml:space="preserve">20.1836776733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5498237609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4139995574951</t>
   </si>
   <si>
     <t xml:space="preserve">19.5045490264893</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7218723297119</t>
+    <t xml:space="preserve">19.7218704223633</t>
   </si>
   <si>
     <t xml:space="preserve">19.7943115234375</t>
@@ -620,13 +620,13 @@
     <t xml:space="preserve">19.8305282592773</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9120292663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7490348815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0919647216797</t>
+    <t xml:space="preserve">19.9120273590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7490367889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0919628143311</t>
   </si>
   <si>
     <t xml:space="preserve">18.3002300262451</t>
@@ -641,10 +641,10 @@
     <t xml:space="preserve">18.0104694366455</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7388172149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8565330505371</t>
+    <t xml:space="preserve">17.7388191223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8565349578857</t>
   </si>
   <si>
     <t xml:space="preserve">17.8203144073486</t>
@@ -668,22 +668,22 @@
     <t xml:space="preserve">19.3958911895752</t>
   </si>
   <si>
-    <t xml:space="preserve">19.377779006958</t>
+    <t xml:space="preserve">19.3777809143066</t>
   </si>
   <si>
     <t xml:space="preserve">19.1151828765869</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5860462188721</t>
+    <t xml:space="preserve">19.5860443115234</t>
   </si>
   <si>
     <t xml:space="preserve">19.2600631713867</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3738346099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3466663360596</t>
+    <t xml:space="preserve">20.3738327026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3466682434082</t>
   </si>
   <si>
     <t xml:space="preserve">20.2380084991455</t>
@@ -692,34 +692,34 @@
     <t xml:space="preserve">20.1293468475342</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1565132141113</t>
+    <t xml:space="preserve">20.15651512146</t>
   </si>
   <si>
     <t xml:space="preserve">20.8084754943848</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6183204650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4785480499268</t>
+    <t xml:space="preserve">20.6183185577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4785499572754</t>
   </si>
   <si>
     <t xml:space="preserve">21.5328788757324</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0671253204346</t>
+    <t xml:space="preserve">22.0671272277832</t>
   </si>
   <si>
     <t xml:space="preserve">22.0580711364746</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2572803497314</t>
+    <t xml:space="preserve">22.2572822570801</t>
   </si>
   <si>
     <t xml:space="preserve">22.2935009002686</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3025569915771</t>
+    <t xml:space="preserve">22.3025550842285</t>
   </si>
   <si>
     <t xml:space="preserve">22.3206653594971</t>
@@ -728,25 +728,25 @@
     <t xml:space="preserve">22.2753925323486</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2391719818115</t>
+    <t xml:space="preserve">22.2391700744629</t>
   </si>
   <si>
     <t xml:space="preserve">22.8186931610107</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0722370147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8911361694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1537303924561</t>
+    <t xml:space="preserve">23.0722351074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.891134262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1537284851074</t>
   </si>
   <si>
     <t xml:space="preserve">23.099401473999</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5923175811768</t>
+    <t xml:space="preserve">22.5923194885254</t>
   </si>
   <si>
     <t xml:space="preserve">22.3568859100342</t>
@@ -767,37 +767,37 @@
     <t xml:space="preserve">23.7513618469238</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1226196289062</t>
+    <t xml:space="preserve">24.1226177215576</t>
   </si>
   <si>
     <t xml:space="preserve">23.6427040100098</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6879768371582</t>
+    <t xml:space="preserve">23.6879787445068</t>
   </si>
   <si>
     <t xml:space="preserve">23.561206817627</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7423095703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7241973876953</t>
+    <t xml:space="preserve">23.7423076629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7241992950439</t>
   </si>
   <si>
     <t xml:space="preserve">23.6336498260498</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8238010406494</t>
+    <t xml:space="preserve">23.823802947998</t>
   </si>
   <si>
     <t xml:space="preserve">23.6970310211182</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0139598846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2856121063232</t>
+    <t xml:space="preserve">24.0139617919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2856101989746</t>
   </si>
   <si>
     <t xml:space="preserve">24.0682888031006</t>
@@ -809,10 +809,10 @@
     <t xml:space="preserve">24.2946662902832</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4304904937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6115913391113</t>
+    <t xml:space="preserve">24.4304885864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6115894317627</t>
   </si>
   <si>
     <t xml:space="preserve">24.7655258178711</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">25.1911163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3903274536133</t>
+    <t xml:space="preserve">25.3903255462646</t>
   </si>
   <si>
     <t xml:space="preserve">25.4265441894531</t>
@@ -836,10 +836,10 @@
     <t xml:space="preserve">25.6529216766357</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7615814208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5352058410645</t>
+    <t xml:space="preserve">25.7615795135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5352039337158</t>
   </si>
   <si>
     <t xml:space="preserve">24.9556827545166</t>
@@ -851,19 +851,19 @@
     <t xml:space="preserve">25.0643444061279</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8017482757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6206474304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9375743865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3722133636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.62575340271</t>
+    <t xml:space="preserve">24.8017463684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6206455230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.937572479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3722171783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6257553100586</t>
   </si>
   <si>
     <t xml:space="preserve">25.2273349761963</t>
@@ -872,7 +872,7 @@
     <t xml:space="preserve">25.173002243042</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1639499664307</t>
+    <t xml:space="preserve">25.163948059082</t>
   </si>
   <si>
     <t xml:space="preserve">25.3993797302246</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">25.2907180786133</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1277313232422</t>
+    <t xml:space="preserve">25.1277294158936</t>
   </si>
   <si>
     <t xml:space="preserve">25.7434711456299</t>
@@ -899,22 +899,22 @@
     <t xml:space="preserve">25.5080394744873</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2635536193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0824546813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7836380004883</t>
+    <t xml:space="preserve">25.2635517120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0824527740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7836399078369</t>
   </si>
   <si>
     <t xml:space="preserve">24.4214344024658</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2674980163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5261516571045</t>
+    <t xml:space="preserve">24.2674999237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5261497497559</t>
   </si>
   <si>
     <t xml:space="preserve">26.1237812042236</t>
@@ -923,13 +923,13 @@
     <t xml:space="preserve">26.1871662139893</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6308650970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4859848022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3229923248291</t>
+    <t xml:space="preserve">26.6308631896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4859828948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3229942321777</t>
   </si>
   <si>
     <t xml:space="preserve">26.6761379241943</t>
@@ -938,13 +938,13 @@
     <t xml:space="preserve">26.893461227417</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2596111297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.667085647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9115695953369</t>
+    <t xml:space="preserve">26.2596092224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6670837402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9115715026855</t>
   </si>
   <si>
     <t xml:space="preserve">26.6036987304688</t>
@@ -971,19 +971,19 @@
     <t xml:space="preserve">24.71120262146</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6159934997559</t>
+    <t xml:space="preserve">23.6159954071045</t>
   </si>
   <si>
     <t xml:space="preserve">23.2202472686768</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1282119750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9625511169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8705177307129</t>
+    <t xml:space="preserve">23.128210067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.962553024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8705196380615</t>
   </si>
   <si>
     <t xml:space="preserve">22.8613147735596</t>
@@ -998,13 +998,13 @@
     <t xml:space="preserve">23.0453834533691</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8889217376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.088228225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3183116912842</t>
+    <t xml:space="preserve">22.8889236450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0882263183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3183097839355</t>
   </si>
   <si>
     <t xml:space="preserve">22.2262763977051</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">22.3827342987061</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3643264770508</t>
+    <t xml:space="preserve">22.3643283843994</t>
   </si>
   <si>
     <t xml:space="preserve">22.7416687011719</t>
@@ -1055,10 +1055,10 @@
     <t xml:space="preserve">21.7200889587402</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5544261932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6740703582764</t>
+    <t xml:space="preserve">21.5544242858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.674072265625</t>
   </si>
   <si>
     <t xml:space="preserve">21.6280536651611</t>
@@ -1067,16 +1067,16 @@
     <t xml:space="preserve">21.1678829193115</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2046966552734</t>
+    <t xml:space="preserve">21.2046985626221</t>
   </si>
   <si>
     <t xml:space="preserve">21.1218662261963</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4163761138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5084095001221</t>
+    <t xml:space="preserve">21.416374206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5084114074707</t>
   </si>
   <si>
     <t xml:space="preserve">21.9133625030518</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">22.5576000213623</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4255809783936</t>
+    <t xml:space="preserve">21.4255790710449</t>
   </si>
   <si>
     <t xml:space="preserve">21.6556644439697</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">22.7876853942871</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3367176055908</t>
+    <t xml:space="preserve">22.3367195129395</t>
   </si>
   <si>
     <t xml:space="preserve">22.115837097168</t>
@@ -1151,13 +1151,13 @@
     <t xml:space="preserve">21.9961891174316</t>
   </si>
   <si>
-    <t xml:space="preserve">21.701681137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.005392074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8765487670898</t>
+    <t xml:space="preserve">21.7016830444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0053939819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8765468597412</t>
   </si>
   <si>
     <t xml:space="preserve">22.1250419616699</t>
@@ -1178,16 +1178,16 @@
     <t xml:space="preserve">20.827356338501</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0574417114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.94700050354</t>
+    <t xml:space="preserve">21.0574398040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9470024108887</t>
   </si>
   <si>
     <t xml:space="preserve">20.7997455596924</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1034603118896</t>
+    <t xml:space="preserve">21.1034622192383</t>
   </si>
   <si>
     <t xml:space="preserve">21.0758476257324</t>
@@ -1205,34 +1205,34 @@
     <t xml:space="preserve">21.8581409454346</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6372566223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2967281341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9746112823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9838123321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1402721405029</t>
+    <t xml:space="preserve">21.6372585296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2967300415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9746131896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.983814239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1402740478516</t>
   </si>
   <si>
     <t xml:space="preserve">21.0666446685791</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7077121734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0942573547363</t>
+    <t xml:space="preserve">20.7077102661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0942554473877</t>
   </si>
   <si>
     <t xml:space="preserve">21.1586799621582</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0206279754639</t>
+    <t xml:space="preserve">21.0206260681152</t>
   </si>
   <si>
     <t xml:space="preserve">21.0022220611572</t>
@@ -1241,7 +1241,7 @@
     <t xml:space="preserve">20.6340847015381</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4500141143799</t>
+    <t xml:space="preserve">20.4500160217285</t>
   </si>
   <si>
     <t xml:space="preserve">20.3855895996094</t>
@@ -1262,7 +1262,7 @@
     <t xml:space="preserve">20.4868297576904</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7445240020752</t>
+    <t xml:space="preserve">20.7445259094238</t>
   </si>
   <si>
     <t xml:space="preserve">20.8917827606201</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">20.1647109985352</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0910816192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2719783782959</t>
+    <t xml:space="preserve">20.0910835266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2719764709473</t>
   </si>
   <si>
     <t xml:space="preserve">19.695333480835</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">20.4316101074219</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5696582794189</t>
+    <t xml:space="preserve">20.5696601867676</t>
   </si>
   <si>
     <t xml:space="preserve">20.6616973876953</t>
@@ -1343,16 +1343,16 @@
     <t xml:space="preserve">19.8609962463379</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0174560546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2199268341064</t>
+    <t xml:space="preserve">20.0174541473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2199287414551</t>
   </si>
   <si>
     <t xml:space="preserve">20.229133605957</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5236434936523</t>
+    <t xml:space="preserve">20.5236415863037</t>
   </si>
   <si>
     <t xml:space="preserve">20.6524925231934</t>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">20.1555042266846</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1739139556885</t>
+    <t xml:space="preserve">20.1739120483398</t>
   </si>
   <si>
     <t xml:space="preserve">21.2599182128906</t>
@@ -1397,13 +1397,13 @@
     <t xml:space="preserve">20.0266590118408</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7229442596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9162158966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5604572296143</t>
+    <t xml:space="preserve">19.7229461669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9162178039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5604553222656</t>
   </si>
   <si>
     <t xml:space="preserve">20.7169170379639</t>
@@ -1430,13 +1430,13 @@
     <t xml:space="preserve">19.6493167877197</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9990482330322</t>
+    <t xml:space="preserve">19.9990463256836</t>
   </si>
   <si>
     <t xml:space="preserve">20.1278972625732</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3303718566895</t>
+    <t xml:space="preserve">20.3303699493408</t>
   </si>
   <si>
     <t xml:space="preserve">20.8733749389648</t>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">20.7261199951172</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2783241271973</t>
+    <t xml:space="preserve">21.2783260345459</t>
   </si>
   <si>
     <t xml:space="preserve">21.3151378631592</t>
@@ -1493,10 +1493,10 @@
     <t xml:space="preserve">22.9165325164795</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6864490509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7324657440186</t>
+    <t xml:space="preserve">22.6864471435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7324676513672</t>
   </si>
   <si>
     <t xml:space="preserve">22.833703994751</t>
@@ -6186,6 +6186,9 @@
   </si>
   <si>
     <t xml:space="preserve">7.7350001335144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70499992370605</t>
   </si>
 </sst>
 </file>
@@ -74460,6 +74463,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2614">
+      <c r="A2614" s="1" t="n">
+        <v>46128.2916666667</v>
+      </c>
+      <c r="B2614" t="n">
+        <v>283015</v>
+      </c>
+      <c r="C2614" t="n">
+        <v>7.88500022888184</v>
+      </c>
+      <c r="D2614" t="n">
+        <v>7.70499992370605</v>
+      </c>
+      <c r="E2614" t="n">
+        <v>7.80000019073486</v>
+      </c>
+      <c r="F2614" t="n">
+        <v>7.70499992370605</v>
+      </c>
+      <c r="G2614" t="s">
+        <v>2058</v>
+      </c>
+      <c r="H2614" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2763519287109</t>
+    <t xml:space="preserve">18.2763481140137</t>
   </si>
   <si>
     <t xml:space="preserve">SFER.MI</t>
@@ -50,115 +50,115 @@
     <t xml:space="preserve">17.4978809356689</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9401969909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6836547851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.249813079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4086723327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1344394683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8425102233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4621257781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2851963043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0994262695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6394214630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5686531066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1878871917725</t>
+    <t xml:space="preserve">17.9401950836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6836528778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2498111724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4086742401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1344375610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.84250831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4621238708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2851982116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0994281768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6394233703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5686511993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1878890991211</t>
   </si>
   <si>
     <t xml:space="preserve">18.4798145294189</t>
   </si>
   <si>
-    <t xml:space="preserve">18.223274230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7632694244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3913497924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.674430847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9578857421875</t>
+    <t xml:space="preserve">18.2232723236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7632675170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3913536071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6744327545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9578838348389</t>
   </si>
   <si>
     <t xml:space="preserve">18.2055816650391</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2586574554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0817337036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3563423156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9051856994629</t>
+    <t xml:space="preserve">18.258659362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0817356109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3563404083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9051837921143</t>
   </si>
   <si>
     <t xml:space="preserve">17.1617240905762</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6486434936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0201835632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4890365600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6305770874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4090461730957</t>
+    <t xml:space="preserve">16.6486415863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0201854705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4890327453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6305732727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4090423583984</t>
   </si>
   <si>
     <t xml:space="preserve">18.4532775878906</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9752082824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1348094940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3121128082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9048080444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3471202850342</t>
+    <t xml:space="preserve">18.9752063751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1348114013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3121089935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9048099517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3471183776855</t>
   </si>
   <si>
     <t xml:space="preserve">19.019437789917</t>
   </si>
   <si>
-    <t xml:space="preserve">19.001745223999</t>
+    <t xml:space="preserve">19.0017414093018</t>
   </si>
   <si>
     <t xml:space="preserve">18.8513584136963</t>
@@ -167,46 +167,46 @@
     <t xml:space="preserve">19.3113632202148</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9925212860107</t>
+    <t xml:space="preserve">19.992525100708</t>
   </si>
   <si>
     <t xml:space="preserve">19.9482917785645</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7271366119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3379039764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6475238800049</t>
+    <t xml:space="preserve">19.7271347045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3379020690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.647518157959</t>
   </si>
   <si>
     <t xml:space="preserve">19.983678817749</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1167430877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4440574645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0367527008057</t>
+    <t xml:space="preserve">19.1167488098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.444055557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0367565155029</t>
   </si>
   <si>
     <t xml:space="preserve">20.178295135498</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4971370697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4705963134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9663562774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4794387817383</t>
+    <t xml:space="preserve">19.4971351623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4705944061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9663619995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4794406890869</t>
   </si>
   <si>
     <t xml:space="preserve">19.9129066467285</t>
@@ -215,40 +215,40 @@
     <t xml:space="preserve">19.868673324585</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4175186157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8690509796143</t>
+    <t xml:space="preserve">19.417516708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8690490722656</t>
   </si>
   <si>
     <t xml:space="preserve">18.8336658477783</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5151996612549</t>
+    <t xml:space="preserve">18.5152015686035</t>
   </si>
   <si>
     <t xml:space="preserve">18.9309730529785</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8955898284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5240459442139</t>
+    <t xml:space="preserve">18.8955879211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5240497589111</t>
   </si>
   <si>
     <t xml:space="preserve">18.9486675262451</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7982807159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8778953552246</t>
+    <t xml:space="preserve">18.7982788085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8778972625732</t>
   </si>
   <si>
     <t xml:space="preserve">19.2936687469482</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8071250915527</t>
+    <t xml:space="preserve">18.8071269989014</t>
   </si>
   <si>
     <t xml:space="preserve">18.3205833435059</t>
@@ -257,25 +257,25 @@
     <t xml:space="preserve">18.3648147583008</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8251934051514</t>
+    <t xml:space="preserve">17.8251914978027</t>
   </si>
   <si>
     <t xml:space="preserve">18.0640411376953</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3117370605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.878267288208</t>
+    <t xml:space="preserve">18.3117389678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8782711029053</t>
   </si>
   <si>
     <t xml:space="preserve">18.0021190643311</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7190380096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.444803237915</t>
+    <t xml:space="preserve">17.7190399169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4448051452637</t>
   </si>
   <si>
     <t xml:space="preserve">17.1440296173096</t>
@@ -287,34 +287,34 @@
     <t xml:space="preserve">17.9844245910645</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4182682037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9313488006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7367305755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6482677459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.593936920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8112602233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7025985717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.530553817749</t>
+    <t xml:space="preserve">17.4182662963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9313468933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7367286682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6482696533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5939388275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.81125831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7025947570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5305500030518</t>
   </si>
   <si>
     <t xml:space="preserve">17.4128360748291</t>
   </si>
   <si>
-    <t xml:space="preserve">17.304178237915</t>
+    <t xml:space="preserve">17.3041763305664</t>
   </si>
   <si>
     <t xml:space="preserve">17.4762191772461</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">17.4309463500977</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4852771759033</t>
+    <t xml:space="preserve">17.4852752685547</t>
   </si>
   <si>
     <t xml:space="preserve">17.7478733062744</t>
@@ -335,31 +335,31 @@
     <t xml:space="preserve">17.1502418518066</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7155990600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5435523986816</t>
+    <t xml:space="preserve">16.71559715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5435543060303</t>
   </si>
   <si>
     <t xml:space="preserve">17.0415802001953</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0777988433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8384265899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9380283355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7297649383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8655872344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1825141906738</t>
+    <t xml:space="preserve">17.0778007507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8384227752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9380302429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7297630310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8655891418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1825160980225</t>
   </si>
   <si>
     <t xml:space="preserve">16.8514270782471</t>
@@ -368,25 +368,25 @@
     <t xml:space="preserve">16.3896179199219</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6793785095215</t>
+    <t xml:space="preserve">16.6793804168701</t>
   </si>
   <si>
     <t xml:space="preserve">16.262845993042</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5254421234131</t>
+    <t xml:space="preserve">16.5254440307617</t>
   </si>
   <si>
     <t xml:space="preserve">16.6069393157959</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8061504364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8242588043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0726909637451</t>
+    <t xml:space="preserve">16.8061466217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8242607116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0726890563965</t>
   </si>
   <si>
     <t xml:space="preserve">15.8734817504883</t>
@@ -395,7 +395,7 @@
     <t xml:space="preserve">16.3624515533447</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4439487457275</t>
+    <t xml:space="preserve">16.4439468383789</t>
   </si>
   <si>
     <t xml:space="preserve">16.69748878479</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">17.095911026001</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1321315765381</t>
+    <t xml:space="preserve">17.1321296691895</t>
   </si>
   <si>
     <t xml:space="preserve">17.086856842041</t>
@@ -413,91 +413,91 @@
     <t xml:space="preserve">17.0325260162354</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3403930664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9018096923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1372394561768</t>
+    <t xml:space="preserve">17.3403949737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9018077850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.137243270874</t>
   </si>
   <si>
     <t xml:space="preserve">17.9289741516113</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7710914611816</t>
+    <t xml:space="preserve">18.771089553833</t>
   </si>
   <si>
     <t xml:space="preserve">18.6352653503418</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0699081420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2147922515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6262149810791</t>
+    <t xml:space="preserve">19.0699062347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.214786529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6262111663818</t>
   </si>
   <si>
     <t xml:space="preserve">18.4994411468506</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2187366485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.716760635376</t>
+    <t xml:space="preserve">18.2187347412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7167625427246</t>
   </si>
   <si>
     <t xml:space="preserve">18.5809383392334</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7620372772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8073139190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9431381225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0427417755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6624317169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4722766876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6171531677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7529811859131</t>
+    <t xml:space="preserve">18.762035369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8073120117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.94313621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0427436828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6624336242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4722747802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6171569824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7529830932617</t>
   </si>
   <si>
     <t xml:space="preserve">18.9703044891357</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6805419921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6080989837646</t>
+    <t xml:space="preserve">18.6805400848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6081027984619</t>
   </si>
   <si>
     <t xml:space="preserve">18.653377532959</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5175533294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8706970214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6986503601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1061305999756</t>
+    <t xml:space="preserve">18.5175495147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.870698928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6986522674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.106128692627</t>
   </si>
   <si>
     <t xml:space="preserve">19.9210815429688</t>
@@ -506,10 +506,10 @@
     <t xml:space="preserve">19.6947059631348</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5588836669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4592723846436</t>
+    <t xml:space="preserve">19.5588798522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4592742919922</t>
   </si>
   <si>
     <t xml:space="preserve">19.314395904541</t>
@@ -518,37 +518,37 @@
     <t xml:space="preserve">18.8888092041016</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1332931518555</t>
+    <t xml:space="preserve">19.1332912445068</t>
   </si>
   <si>
     <t xml:space="preserve">19.1604595184326</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9391899108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4553298950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3557243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3104476928711</t>
+    <t xml:space="preserve">19.9391918182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4553318023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3557205200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3104496002197</t>
   </si>
   <si>
     <t xml:space="preserve">20.3919448852539</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4643821716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6907596588135</t>
+    <t xml:space="preserve">20.4643840789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6907615661621</t>
   </si>
   <si>
     <t xml:space="preserve">20.8446960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7994213104248</t>
+    <t xml:space="preserve">20.7994194030762</t>
   </si>
   <si>
     <t xml:space="preserve">20.4010009765625</t>
@@ -557,34 +557,34 @@
     <t xml:space="preserve">20.1021823883057</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5277671813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3647766113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5458812713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7541446685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4191074371338</t>
+    <t xml:space="preserve">20.5277690887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3647785186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5458793640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7541465759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4191093444824</t>
   </si>
   <si>
     <t xml:space="preserve">20.0116329193115</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2651710510254</t>
+    <t xml:space="preserve">20.2651748657227</t>
   </si>
   <si>
     <t xml:space="preserve">20.3285598754883</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0387954711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1474590301514</t>
+    <t xml:space="preserve">20.03879737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1474571228027</t>
   </si>
   <si>
     <t xml:space="preserve">20.2289543151855</t>
@@ -599,34 +599,34 @@
     <t xml:space="preserve">20.1836776733398</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5498237609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4139995574951</t>
+    <t xml:space="preserve">19.5498275756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4140014648438</t>
   </si>
   <si>
     <t xml:space="preserve">19.5045509338379</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7218704223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7943134307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5226593017578</t>
+    <t xml:space="preserve">19.7218723297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7943096160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5226612091064</t>
   </si>
   <si>
     <t xml:space="preserve">19.830530166626</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9120273590088</t>
+    <t xml:space="preserve">19.9120254516602</t>
   </si>
   <si>
     <t xml:space="preserve">19.7490348815918</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0919647216797</t>
+    <t xml:space="preserve">18.0919628143311</t>
   </si>
   <si>
     <t xml:space="preserve">18.3002281188965</t>
@@ -641,25 +641,25 @@
     <t xml:space="preserve">18.0104694366455</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7388172149658</t>
+    <t xml:space="preserve">17.7388191223145</t>
   </si>
   <si>
     <t xml:space="preserve">17.8565330505371</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8203105926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6392116546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3455028533936</t>
+    <t xml:space="preserve">17.8203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6392097473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3455047607422</t>
   </si>
   <si>
     <t xml:space="preserve">18.3907794952393</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1514053344727</t>
+    <t xml:space="preserve">19.151403427124</t>
   </si>
   <si>
     <t xml:space="preserve">19.2872276306152</t>
@@ -668,34 +668,34 @@
     <t xml:space="preserve">19.3958911895752</t>
   </si>
   <si>
-    <t xml:space="preserve">19.377779006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1151828765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5860481262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2600650787354</t>
+    <t xml:space="preserve">19.3777809143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1151847839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5860462188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2600631713867</t>
   </si>
   <si>
     <t xml:space="preserve">20.373836517334</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3466682434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2380104064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1293487548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1565113067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8084774017334</t>
+    <t xml:space="preserve">20.3466701507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2380084991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1293468475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.15651512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8084754943848</t>
   </si>
   <si>
     <t xml:space="preserve">20.6183204650879</t>
@@ -704,10 +704,10 @@
     <t xml:space="preserve">21.4785480499268</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5328769683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0671272277832</t>
+    <t xml:space="preserve">21.5328788757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0671253204346</t>
   </si>
   <si>
     <t xml:space="preserve">22.058069229126</t>
@@ -716,61 +716,61 @@
     <t xml:space="preserve">22.2572803497314</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2935047149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3025550842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3206634521484</t>
+    <t xml:space="preserve">22.2935028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3025569915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3206672668457</t>
   </si>
   <si>
     <t xml:space="preserve">22.275390625</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2391700744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.818696975708</t>
+    <t xml:space="preserve">22.2391719818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8186950683594</t>
   </si>
   <si>
     <t xml:space="preserve">23.0722332000732</t>
   </si>
   <si>
-    <t xml:space="preserve">22.891134262085</t>
+    <t xml:space="preserve">22.8911361694336</t>
   </si>
   <si>
     <t xml:space="preserve">23.1537303924561</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0993995666504</t>
+    <t xml:space="preserve">23.0993976593018</t>
   </si>
   <si>
     <t xml:space="preserve">22.5923175811768</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3568897247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9092426300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1757850646973</t>
+    <t xml:space="preserve">22.3568859100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9092445373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1757869720459</t>
   </si>
   <si>
     <t xml:space="preserve">22.1395664215088</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6064834594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7513618469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1226177215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6427021026611</t>
+    <t xml:space="preserve">23.606481552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7513637542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1226196289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6427040100098</t>
   </si>
   <si>
     <t xml:space="preserve">23.6879768371582</t>
@@ -779,37 +779,37 @@
     <t xml:space="preserve">23.5612087249756</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7423076629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7241992950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6336498260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.823802947998</t>
+    <t xml:space="preserve">23.7423038482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7241973876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6336460113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8238010406494</t>
   </si>
   <si>
     <t xml:space="preserve">23.6970329284668</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0139579772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.285608291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.068286895752</t>
+    <t xml:space="preserve">24.0139598846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2856101989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0682907104492</t>
   </si>
   <si>
     <t xml:space="preserve">23.9777374267578</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2946643829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.430492401123</t>
+    <t xml:space="preserve">24.2946624755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4304904937744</t>
   </si>
   <si>
     <t xml:space="preserve">24.61159324646</t>
@@ -818,43 +818,43 @@
     <t xml:space="preserve">24.7655277252197</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1911125183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3903255462646</t>
+    <t xml:space="preserve">25.1911144256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.390323638916</t>
   </si>
   <si>
     <t xml:space="preserve">25.4265460968018</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6167030334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6710319519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6529235839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7615814208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5352058410645</t>
+    <t xml:space="preserve">25.6167011260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6710300445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6529216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7615833282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5352039337158</t>
   </si>
   <si>
     <t xml:space="preserve">24.9556827545166</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9013519287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0643463134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8017482757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6206455230713</t>
+    <t xml:space="preserve">24.9013557434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0643444061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8017463684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6206474304199</t>
   </si>
   <si>
     <t xml:space="preserve">24.9375743865967</t>
@@ -863,16 +863,16 @@
     <t xml:space="preserve">25.3722152709961</t>
   </si>
   <si>
-    <t xml:space="preserve">25.62575340271</t>
+    <t xml:space="preserve">25.6257553100586</t>
   </si>
   <si>
     <t xml:space="preserve">25.2273349761963</t>
   </si>
   <si>
-    <t xml:space="preserve">25.173002243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1639499664307</t>
+    <t xml:space="preserve">25.1730041503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.163948059082</t>
   </si>
   <si>
     <t xml:space="preserve">25.399377822876</t>
@@ -881,10 +881,10 @@
     <t xml:space="preserve">25.7253608703613</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2907180786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1277275085449</t>
+    <t xml:space="preserve">25.2907199859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1277294158936</t>
   </si>
   <si>
     <t xml:space="preserve">25.7434711456299</t>
@@ -896,10 +896,10 @@
     <t xml:space="preserve">25.4808750152588</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5080413818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2635555267334</t>
+    <t xml:space="preserve">25.5080394744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2635536193848</t>
   </si>
   <si>
     <t xml:space="preserve">25.0824527740479</t>
@@ -914,13 +914,13 @@
     <t xml:space="preserve">24.2674999237061</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5261516571045</t>
+    <t xml:space="preserve">25.5261478424072</t>
   </si>
   <si>
     <t xml:space="preserve">26.1237831115723</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1871662139893</t>
+    <t xml:space="preserve">26.1871681213379</t>
   </si>
   <si>
     <t xml:space="preserve">26.6308650970459</t>
@@ -929,46 +929,46 @@
     <t xml:space="preserve">26.4859848022461</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3229942321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.676139831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.893461227417</t>
+    <t xml:space="preserve">26.3229923248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6761360168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8934631347656</t>
   </si>
   <si>
     <t xml:space="preserve">26.2596073150635</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6670837402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9115695953369</t>
+    <t xml:space="preserve">26.6670875549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9115676879883</t>
   </si>
   <si>
     <t xml:space="preserve">26.6036987304688</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5946464538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3088302612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.326940536499</t>
+    <t xml:space="preserve">26.5946445465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3088283538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3269386291504</t>
   </si>
   <si>
     <t xml:space="preserve">25.8340225219727</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8984451293945</t>
+    <t xml:space="preserve">25.8984413146973</t>
   </si>
   <si>
     <t xml:space="preserve">26.0641059875488</t>
   </si>
   <si>
-    <t xml:space="preserve">24.71120262146</t>
+    <t xml:space="preserve">24.7112045288086</t>
   </si>
   <si>
     <t xml:space="preserve">23.6159954071045</t>
@@ -977,16 +977,16 @@
     <t xml:space="preserve">23.2202453613281</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1282119750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9625511169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8705177307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8613147735596</t>
+    <t xml:space="preserve">23.128210067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.962553024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8705196380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8613128662109</t>
   </si>
   <si>
     <t xml:space="preserve">23.266263961792</t>
@@ -1016,7 +1016,7 @@
     <t xml:space="preserve">22.3643283843994</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7416667938232</t>
+    <t xml:space="preserve">22.7416687011719</t>
   </si>
   <si>
     <t xml:space="preserve">22.95334815979</t>
@@ -1025,13 +1025,13 @@
     <t xml:space="preserve">22.8797206878662</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2846698760986</t>
+    <t xml:space="preserve">23.2846717834473</t>
   </si>
   <si>
     <t xml:space="preserve">23.4871482849121</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4319267272949</t>
+    <t xml:space="preserve">23.4319248199463</t>
   </si>
   <si>
     <t xml:space="preserve">22.8060932159424</t>
@@ -1040,34 +1040,34 @@
     <t xml:space="preserve">23.0269775390625</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6036167144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2538890838623</t>
+    <t xml:space="preserve">22.6036186218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2538871765137</t>
   </si>
   <si>
     <t xml:space="preserve">21.5452251434326</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4900016784668</t>
+    <t xml:space="preserve">21.4900035858154</t>
   </si>
   <si>
     <t xml:space="preserve">21.7200889587402</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5544261932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6740703582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6280555725098</t>
+    <t xml:space="preserve">21.5544242858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.674072265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6280536651611</t>
   </si>
   <si>
     <t xml:space="preserve">21.1678829193115</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2046966552734</t>
+    <t xml:space="preserve">21.2046985626221</t>
   </si>
   <si>
     <t xml:space="preserve">21.1218662261963</t>
@@ -1076,40 +1076,40 @@
     <t xml:space="preserve">21.4163780212402</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5084095001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9133586883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8857479095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9685821533203</t>
+    <t xml:space="preserve">21.5084114074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9133605957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8857498168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9685802459717</t>
   </si>
   <si>
     <t xml:space="preserve">22.6220226287842</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3735332489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2170753479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4103450775146</t>
+    <t xml:space="preserve">22.3735313415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2170734405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4103469848633</t>
   </si>
   <si>
     <t xml:space="preserve">22.5299892425537</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6312313079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6404304504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5575981140137</t>
+    <t xml:space="preserve">22.6312274932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6404323577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5576000213623</t>
   </si>
   <si>
     <t xml:space="preserve">21.4255809783936</t>
@@ -1121,46 +1121,46 @@
     <t xml:space="preserve">22.263090133667</t>
   </si>
   <si>
-    <t xml:space="preserve">22.539192199707</t>
+    <t xml:space="preserve">22.5391941070557</t>
   </si>
   <si>
     <t xml:space="preserve">22.3551254272461</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0514125823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7876853942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3367195129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1158351898193</t>
+    <t xml:space="preserve">22.0514106750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7876873016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3367214202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.115837097168</t>
   </si>
   <si>
     <t xml:space="preserve">21.7661037445068</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0606136322021</t>
+    <t xml:space="preserve">22.0606117248535</t>
   </si>
   <si>
     <t xml:space="preserve">21.7569007873535</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9961910247803</t>
+    <t xml:space="preserve">21.9961891174316</t>
   </si>
   <si>
     <t xml:space="preserve">21.701681137085</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0053958892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8765487670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1250400543213</t>
+    <t xml:space="preserve">22.0053939819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8765468597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1250381469727</t>
   </si>
   <si>
     <t xml:space="preserve">21.7753105163574</t>
@@ -1172,13 +1172,13 @@
     <t xml:space="preserve">21.9041576385498</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6832752227783</t>
+    <t xml:space="preserve">21.6832733154297</t>
   </si>
   <si>
     <t xml:space="preserve">20.827356338501</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0574398040771</t>
+    <t xml:space="preserve">21.0574378967285</t>
   </si>
   <si>
     <t xml:space="preserve">20.9470024108887</t>
@@ -1187,10 +1187,10 @@
     <t xml:space="preserve">20.7997455596924</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1034622192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0758476257324</t>
+    <t xml:space="preserve">21.1034603118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0758495330811</t>
   </si>
   <si>
     <t xml:space="preserve">21.3243408203125</t>
@@ -1199,10 +1199,10 @@
     <t xml:space="preserve">21.9501762390137</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0974311828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8581390380859</t>
+    <t xml:space="preserve">22.0974292755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8581409454346</t>
   </si>
   <si>
     <t xml:space="preserve">21.6372585296631</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">21.2967319488525</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9746112823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9838123321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1402702331543</t>
+    <t xml:space="preserve">20.9746131896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9838161468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1402721405029</t>
   </si>
   <si>
     <t xml:space="preserve">21.0666446685791</t>
@@ -1229,28 +1229,28 @@
     <t xml:space="preserve">21.0942554473877</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1586780548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0206279754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0022220611572</t>
+    <t xml:space="preserve">21.1586799621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0206260681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0022201538086</t>
   </si>
   <si>
     <t xml:space="preserve">20.6340827941895</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4500141143799</t>
+    <t xml:space="preserve">20.4500160217285</t>
   </si>
   <si>
     <t xml:space="preserve">20.385591506958</t>
   </si>
   <si>
-    <t xml:space="preserve">20.39479637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0082492828369</t>
+    <t xml:space="preserve">20.3947944641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0082511901855</t>
   </si>
   <si>
     <t xml:space="preserve">19.9714393615723</t>
@@ -1259,19 +1259,19 @@
     <t xml:space="preserve">20.0634727478027</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4868278503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7445259094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8917789459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2415103912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9285945892334</t>
+    <t xml:space="preserve">20.4868297576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7445278167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8917808532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.241512298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9285926818848</t>
   </si>
   <si>
     <t xml:space="preserve">20.2475414276123</t>
@@ -1283,16 +1283,16 @@
     <t xml:space="preserve">20.0910816192627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2719764709473</t>
+    <t xml:space="preserve">19.2719783782959</t>
   </si>
   <si>
     <t xml:space="preserve">19.695333480835</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8057746887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7321472167969</t>
+    <t xml:space="preserve">19.8057765960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7321491241455</t>
   </si>
   <si>
     <t xml:space="preserve">20.1831169128418</t>
@@ -1307,28 +1307,28 @@
     <t xml:space="preserve">20.4316082000732</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5696620941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.661693572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1310691833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0482387542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1954956054688</t>
+    <t xml:space="preserve">20.5696601867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6616954803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.131067276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0482406616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1954936981201</t>
   </si>
   <si>
     <t xml:space="preserve">21.4531898498535</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8089504241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6708965301514</t>
+    <t xml:space="preserve">20.8089485168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6708984375</t>
   </si>
   <si>
     <t xml:space="preserve">20.7721366882324</t>
@@ -1337,37 +1337,37 @@
     <t xml:space="preserve">19.4652481079102</t>
   </si>
   <si>
-    <t xml:space="preserve">19.796573638916</t>
+    <t xml:space="preserve">19.7965717315674</t>
   </si>
   <si>
     <t xml:space="preserve">19.8609962463379</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0174560546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2199268341064</t>
+    <t xml:space="preserve">20.0174522399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2199287414551</t>
   </si>
   <si>
     <t xml:space="preserve">20.229133605957</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5236434936523</t>
+    <t xml:space="preserve">20.5236415863037</t>
   </si>
   <si>
     <t xml:space="preserve">20.6524925231934</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9101829528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2659473419189</t>
+    <t xml:space="preserve">20.9101867675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2659454345703</t>
   </si>
   <si>
     <t xml:space="preserve">20.4684219360352</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1555042266846</t>
+    <t xml:space="preserve">20.1555061340332</t>
   </si>
   <si>
     <t xml:space="preserve">20.1739139556885</t>
@@ -1382,7 +1382,7 @@
     <t xml:space="preserve">21.5176124572754</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8549690246582</t>
+    <t xml:space="preserve">20.8549671173096</t>
   </si>
   <si>
     <t xml:space="preserve">20.9193916320801</t>
@@ -1391,19 +1391,19 @@
     <t xml:space="preserve">20.5052375793457</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3487796783447</t>
+    <t xml:space="preserve">20.3487777709961</t>
   </si>
   <si>
     <t xml:space="preserve">20.0266590118408</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7229461669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9162158966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5604572296143</t>
+    <t xml:space="preserve">19.7229442596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9162178039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5604553222656</t>
   </si>
   <si>
     <t xml:space="preserve">20.7169151306152</t>
@@ -1418,13 +1418,13 @@
     <t xml:space="preserve">21.6004428863525</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6248817443848</t>
+    <t xml:space="preserve">20.6248798370361</t>
   </si>
   <si>
     <t xml:space="preserve">20.2751522064209</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1094875335693</t>
+    <t xml:space="preserve">20.109489440918</t>
   </si>
   <si>
     <t xml:space="preserve">19.6493186950684</t>
@@ -1433,31 +1433,31 @@
     <t xml:space="preserve">19.9990482330322</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1278972625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3303718566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8733749389648</t>
+    <t xml:space="preserve">20.1278953552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3303699493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8733730316162</t>
   </si>
   <si>
     <t xml:space="preserve">20.3763866424561</t>
   </si>
   <si>
-    <t xml:space="preserve">20.532844543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3027610778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6432876586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6156768798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7261199951172</t>
+    <t xml:space="preserve">20.5328464508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3027591705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6432857513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6156787872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7261180877686</t>
   </si>
   <si>
     <t xml:space="preserve">21.2783260345459</t>
@@ -1466,31 +1466,31 @@
     <t xml:space="preserve">21.3151378631592</t>
   </si>
   <si>
-    <t xml:space="preserve">21.536018371582</t>
+    <t xml:space="preserve">21.5360221862793</t>
   </si>
   <si>
     <t xml:space="preserve">21.7937164306641</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6496334075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5483989715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.419548034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2078666687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5668048858643</t>
+    <t xml:space="preserve">22.6496353149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.548397064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4195499420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2078704833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5668029785156</t>
   </si>
   <si>
     <t xml:space="preserve">22.6128215789795</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9165325164795</t>
+    <t xml:space="preserve">22.9165344238281</t>
   </si>
   <si>
     <t xml:space="preserve">22.6864452362061</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">22.7324638366699</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8337001800537</t>
+    <t xml:space="preserve">22.8337020874023</t>
   </si>
   <si>
     <t xml:space="preserve">22.7692794799805</t>
@@ -1511,7 +1511,7 @@
     <t xml:space="preserve">23.2754688262939</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9913024902344</t>
+    <t xml:space="preserve">22.991304397583</t>
   </si>
   <si>
     <t xml:space="preserve">23.3090686798096</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">23.4118747711182</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9071865081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9819583892822</t>
+    <t xml:space="preserve">22.9071884155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9819564819336</t>
   </si>
   <si>
     <t xml:space="preserve">22.7296123504639</t>
@@ -1532,13 +1532,13 @@
     <t xml:space="preserve">22.3557720184326</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6174602508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0754203796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3557987213135</t>
+    <t xml:space="preserve">22.6174621582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.07541847229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3557968139648</t>
   </si>
   <si>
     <t xml:space="preserve">23.1969165802002</t>
@@ -1547,7 +1547,7 @@
     <t xml:space="preserve">23.206262588501</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4586067199707</t>
+    <t xml:space="preserve">23.4586048126221</t>
   </si>
   <si>
     <t xml:space="preserve">22.6548442840576</t>
@@ -1556,7 +1556,7 @@
     <t xml:space="preserve">22.7389602661133</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1595306396484</t>
+    <t xml:space="preserve">23.1595325469971</t>
   </si>
   <si>
     <t xml:space="preserve">23.5053367614746</t>
@@ -1571,10 +1571,10 @@
     <t xml:space="preserve">23.2623386383057</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9258804321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9912452697754</t>
+    <t xml:space="preserve">22.9258823394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.991247177124</t>
   </si>
   <si>
     <t xml:space="preserve">20.3370227813721</t>
@@ -1586,13 +1586,13 @@
     <t xml:space="preserve">19.7388782501221</t>
   </si>
   <si>
-    <t xml:space="preserve">19.56130027771</t>
+    <t xml:space="preserve">19.5612983703613</t>
   </si>
   <si>
     <t xml:space="preserve">19.3089542388916</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5332622528076</t>
+    <t xml:space="preserve">19.533260345459</t>
   </si>
   <si>
     <t xml:space="preserve">19.4958763122559</t>
@@ -1601,13 +1601,13 @@
     <t xml:space="preserve">19.346342086792</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0285739898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6266937255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3836975097656</t>
+    <t xml:space="preserve">19.0285758972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6266956329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.383695602417</t>
   </si>
   <si>
     <t xml:space="preserve">18.0752754211426</t>
@@ -1619,10 +1619,10 @@
     <t xml:space="preserve">18.079948425293</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6033306121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6360416412354</t>
+    <t xml:space="preserve">18.603328704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6360397338867</t>
   </si>
   <si>
     <t xml:space="preserve">18.7949237823486</t>
@@ -1637,34 +1637,34 @@
     <t xml:space="preserve">18.5752925872803</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3930416107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5285606384277</t>
+    <t xml:space="preserve">18.3930435180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5285587310791</t>
   </si>
   <si>
     <t xml:space="preserve">18.495849609375</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4351005554199</t>
+    <t xml:space="preserve">18.4350986480713</t>
   </si>
   <si>
     <t xml:space="preserve">18.388370513916</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4911766052246</t>
+    <t xml:space="preserve">18.491174697876</t>
   </si>
   <si>
     <t xml:space="preserve">18.2435054779053</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8042392730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7715263366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1079883575439</t>
+    <t xml:space="preserve">17.8042373657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7715282440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1079864501953</t>
   </si>
   <si>
     <t xml:space="preserve">18.6734237670898</t>
@@ -1703,13 +1703,13 @@
     <t xml:space="preserve">19.4304523468018</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3650321960449</t>
+    <t xml:space="preserve">19.3650302886963</t>
   </si>
   <si>
     <t xml:space="preserve">19.1594181060791</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1687660217285</t>
+    <t xml:space="preserve">19.1687679290771</t>
   </si>
   <si>
     <t xml:space="preserve">19.1126899719238</t>
@@ -1721,10 +1721,10 @@
     <t xml:space="preserve">18.7388439178467</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0566120147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8416519165039</t>
+    <t xml:space="preserve">19.0566101074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8416538238525</t>
   </si>
   <si>
     <t xml:space="preserve">19.6080303192139</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">19.8136425018311</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0753326416016</t>
+    <t xml:space="preserve">20.0753307342529</t>
   </si>
   <si>
     <t xml:space="preserve">19.748218536377</t>
@@ -1754,10 +1754,10 @@
     <t xml:space="preserve">19.7669124603271</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7856063842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5706443786621</t>
+    <t xml:space="preserve">19.7856044769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5706462860107</t>
   </si>
   <si>
     <t xml:space="preserve">19.2809162139893</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">18.6453857421875</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8556442260742</t>
+    <t xml:space="preserve">17.8556423187256</t>
   </si>
   <si>
     <t xml:space="preserve">17.2528228759766</t>
@@ -1796,13 +1796,13 @@
     <t xml:space="preserve">18.1360263824463</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9491062164307</t>
+    <t xml:space="preserve">17.949104309082</t>
   </si>
   <si>
     <t xml:space="preserve">18.1173343658447</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2154674530029</t>
+    <t xml:space="preserve">18.2154655456543</t>
   </si>
   <si>
     <t xml:space="preserve">19.1874561309814</t>
@@ -1811,7 +1811,7 @@
     <t xml:space="preserve">19.0098819732666</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5986843109131</t>
+    <t xml:space="preserve">19.5986824035645</t>
   </si>
   <si>
     <t xml:space="preserve">19.5893363952637</t>
@@ -1820,10 +1820,10 @@
     <t xml:space="preserve">19.6454162597656</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4771842956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5426063537598</t>
+    <t xml:space="preserve">19.4771862030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5426082611084</t>
   </si>
   <si>
     <t xml:space="preserve">19.5799922943115</t>
@@ -1832,7 +1832,7 @@
     <t xml:space="preserve">20.0005626678467</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6267223358154</t>
+    <t xml:space="preserve">19.6267204284668</t>
   </si>
   <si>
     <t xml:space="preserve">19.4865322113037</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">16.5378494262695</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7200984954834</t>
+    <t xml:space="preserve">16.7200965881348</t>
   </si>
   <si>
     <t xml:space="preserve">16.495792388916</t>
@@ -1898,10 +1898,10 @@
     <t xml:space="preserve">16.3509292602539</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5425205230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8415966033936</t>
+    <t xml:space="preserve">16.5425224304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8415985107422</t>
   </si>
   <si>
     <t xml:space="preserve">16.6640205383301</t>
@@ -1925,7 +1925,7 @@
     <t xml:space="preserve">16.1266212463379</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1593341827393</t>
+    <t xml:space="preserve">16.1593360900879</t>
   </si>
   <si>
     <t xml:space="preserve">16.4490623474121</t>
@@ -1934,13 +1934,13 @@
     <t xml:space="preserve">16.192045211792</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2154121398926</t>
+    <t xml:space="preserve">16.2154102325439</t>
   </si>
   <si>
     <t xml:space="preserve">16.4817733764648</t>
   </si>
   <si>
-    <t xml:space="preserve">16.523832321167</t>
+    <t xml:space="preserve">16.5238304138184</t>
   </si>
   <si>
     <t xml:space="preserve">16.4023323059082</t>
@@ -1955,7 +1955,7 @@
     <t xml:space="preserve">17.1874008178711</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7855491638184</t>
+    <t xml:space="preserve">17.785551071167</t>
   </si>
   <si>
     <t xml:space="preserve">17.1967449188232</t>
@@ -1976,19 +1976,19 @@
     <t xml:space="preserve">17.1079597473145</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1313247680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.229455947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4911479949951</t>
+    <t xml:space="preserve">17.1313228607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2294578552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4911499023438</t>
   </si>
   <si>
     <t xml:space="preserve">17.4397449493408</t>
   </si>
   <si>
-    <t xml:space="preserve">17.453763961792</t>
+    <t xml:space="preserve">17.4537620544434</t>
   </si>
   <si>
     <t xml:space="preserve">17.729471206665</t>
@@ -1997,13 +1997,13 @@
     <t xml:space="preserve">17.6547031402588</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3369369506836</t>
+    <t xml:space="preserve">17.3369388580322</t>
   </si>
   <si>
     <t xml:space="preserve">17.1453418731689</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8462677001953</t>
+    <t xml:space="preserve">16.8462696075439</t>
   </si>
   <si>
     <t xml:space="preserve">17.1687088012695</t>
@@ -2030,10 +2030,10 @@
     <t xml:space="preserve">17.6360130310059</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3275928497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3976860046387</t>
+    <t xml:space="preserve">17.3275909423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3976879119873</t>
   </si>
   <si>
     <t xml:space="preserve">17.6266651153564</t>
@@ -2042,10 +2042,10 @@
     <t xml:space="preserve">17.5004940032959</t>
   </si>
   <si>
-    <t xml:space="preserve">17.869665145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3135986328125</t>
+    <t xml:space="preserve">17.8696632385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3136005401611</t>
   </si>
   <si>
     <t xml:space="preserve">18.056583404541</t>
@@ -2054,16 +2054,16 @@
     <t xml:space="preserve">18.2855625152588</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0191993713379</t>
+    <t xml:space="preserve">18.0192012786865</t>
   </si>
   <si>
     <t xml:space="preserve">17.9677982330322</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9070491790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6921157836914</t>
+    <t xml:space="preserve">17.9070472717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.69211769104</t>
   </si>
   <si>
     <t xml:space="preserve">18.5051937103271</t>
@@ -2072,13 +2072,13 @@
     <t xml:space="preserve">18.3416385650635</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5565986633301</t>
+    <t xml:space="preserve">18.5565967559814</t>
   </si>
   <si>
     <t xml:space="preserve">18.439769744873</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5472507476807</t>
+    <t xml:space="preserve">18.5472526550293</t>
   </si>
   <si>
     <t xml:space="preserve">18.3089275360107</t>
@@ -2099,13 +2099,13 @@
     <t xml:space="preserve">17.8603172302246</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0612602233887</t>
+    <t xml:space="preserve">18.06125831604</t>
   </si>
   <si>
     <t xml:space="preserve">17.5986270904541</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0939712524414</t>
+    <t xml:space="preserve">18.0939693450928</t>
   </si>
   <si>
     <t xml:space="preserve">19.8603744506836</t>
@@ -2120,16 +2120,16 @@
     <t xml:space="preserve">19.4607124328613</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9735889434814</t>
+    <t xml:space="preserve">19.9735870361328</t>
   </si>
   <si>
     <t xml:space="preserve">19.4132251739502</t>
   </si>
   <si>
-    <t xml:space="preserve">19.204273223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4892082214355</t>
+    <t xml:space="preserve">19.2042751312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4892063140869</t>
   </si>
   <si>
     <t xml:s